--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" style="158" min="1" max="1"/>
@@ -3763,7 +3763,7 @@
         <v>140</v>
       </c>
       <c r="C8" s="121" t="n">
-        <v>26.89</v>
+        <v>24.2</v>
       </c>
       <c r="D8" s="69" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="121" t="n">
-        <v>38.23</v>
+        <v>34.41</v>
       </c>
       <c r="D10" s="69" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>90</v>
       </c>
       <c r="C12" s="121" t="n">
-        <v>18.23</v>
+        <v>20.26</v>
       </c>
       <c r="D12" s="69" t="n">
         <v>0</v>
@@ -4606,7 +4606,14 @@
     <row r="33">
       <c r="A33" s="216" t="inlineStr">
         <is>
-          <t>CUSTOS: Refil Everest e Pré-Filtro = Eversoft (26/08). Pro Life, Carbon Tech, E3, Plissado = Filtros Planeta Água. C+3 = Culligan (22/04). Registro = Everest (19/05). Purificadores = Everest, última nota de cada modelo. Mangueira = R$ 1,72/m (rolo 50 m por R$ 86,01). Termostato: sem compra em 2026.</t>
+          <t>CUSTOS (conferidos nos XMLs de compra em 12/09/2026): Refil Everest e Pré-Filtro = Eversoft NF 75472 (26/08). Pro Life, Carbon Tech 5" e Plissado = Filtros Planeta Água NF 133812 (28/08). Carbon Tech 9" = NF 133138 (12/08). E3 = NF 131997 (08/07). C+3 = Culligan (22/04). Registro = Everest (19/05). Purificadores = Everest, última nota de cada modelo (Fit/Star branco e preto e Plus prata reajustados em 17/07; Foz em 04/08). Mangueira = R$ 1,72/m (rolo 50 m por R$ 86,01). Termostato: sem compra em 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="216" t="inlineStr">
+        <is>
+          <t>ATENÇÃO — a Filtros Planeta Água cobra por volume, não por tabela: o mesmo código muda de preço conforme a quantidade da nota. Carbon Tech 9" saiu a R$ 49,00/un comprando 10 un (17/06) e a R$ 30,87/un comprando 30 un (12/08). O Plissado subiu para R$ 20,26 na última compra só porque foram 4 unidades (era R$ 18,23 comprando 20). Comprar em lote maior nessa fornecedora derruba bastante o custo.</t>
         </is>
       </c>
     </row>
@@ -34225,7 +34232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U94"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="158" min="1" max="1"/>
@@ -34373,11 +34380,11 @@
         </is>
       </c>
       <c r="L5" s="92">
-        <f>SUMIF(H5:H92,K5,G5:G92)</f>
+        <f>SUMIF(H5:H98,K5,G5:G98)</f>
         <v/>
       </c>
       <c r="N5" s="237">
-        <f>D93-F93-T5</f>
+        <f>D99-F99-T5</f>
         <v/>
       </c>
       <c r="P5" s="189">
@@ -34385,11 +34392,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D94</f>
+        <f>D100</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E92,"Aguardando Pagamento",D5:D92)</f>
+        <f>SUMIF(E5:E98,"Aguardando Pagamento",D5:D98)</f>
         <v/>
       </c>
     </row>
@@ -34429,7 +34436,7 @@
         </is>
       </c>
       <c r="L6" s="92">
-        <f>SUMIF(H5:H92,K6,G5:G92)</f>
+        <f>SUMIF(H5:H98,K6,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34469,7 +34476,7 @@
         </is>
       </c>
       <c r="L7" s="92">
-        <f>SUMIF(H5:H92,K7,G5:G92)</f>
+        <f>SUMIF(H5:H98,K7,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34509,7 +34516,7 @@
         </is>
       </c>
       <c r="L8" s="92">
-        <f>SUMIF(H5:H92,K8,G5:G92)</f>
+        <f>SUMIF(H5:H98,K8,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34549,7 +34556,7 @@
         </is>
       </c>
       <c r="L9" s="92">
-        <f>SUMIF(H5:H92,K9,G5:G92)</f>
+        <f>SUMIF(H5:H98,K9,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34589,7 +34596,7 @@
         </is>
       </c>
       <c r="L10" s="92">
-        <f>SUMIF(H5:H92,K10,G5:G92)</f>
+        <f>SUMIF(H5:H98,K10,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34629,7 +34636,7 @@
         </is>
       </c>
       <c r="L11" s="92">
-        <f>SUMIF(H5:H92,K11,G5:G92)</f>
+        <f>SUMIF(H5:H98,K11,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34669,7 +34676,7 @@
         </is>
       </c>
       <c r="L12" s="92">
-        <f>SUMIF(H5:H92,K12,G5:G92)</f>
+        <f>SUMIF(H5:H98,K12,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34705,7 +34712,7 @@
         </is>
       </c>
       <c r="L13" s="92">
-        <f>SUMIF(H5:H92,K13,G5:G92)</f>
+        <f>SUMIF(H5:H98,K13,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34745,7 +34752,7 @@
         </is>
       </c>
       <c r="L14" s="92">
-        <f>SUMIF(H5:H92,K14,G5:G92)</f>
+        <f>SUMIF(H5:H98,K14,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34785,7 +34792,7 @@
         </is>
       </c>
       <c r="L15" s="92">
-        <f>SUMIF(H5:H92,K15,G5:G92)</f>
+        <f>SUMIF(H5:H98,K15,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34821,7 +34828,7 @@
         </is>
       </c>
       <c r="L16" s="92">
-        <f>SUMIF(H5:H92,K16,G5:G92)</f>
+        <f>SUMIF(H5:H98,K16,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -34861,7 +34868,7 @@
         </is>
       </c>
       <c r="L17" s="97">
-        <f>SUMIF(H5:H92,K17,G5:G92)</f>
+        <f>SUMIF(H5:H98,K17,G5:G98)</f>
         <v/>
       </c>
     </row>
@@ -36775,13 +36782,17 @@
       </c>
       <c r="E85" s="90" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F85" s="91" t="n"/>
       <c r="G85" s="91" t="n"/>
       <c r="H85" s="90" t="n"/>
-      <c r="I85" s="90" t="n"/>
+      <c r="I85" s="90" t="inlineStr">
+        <is>
+          <t>Venda de 11/09/2026 — pagamento recebido via Pix em 14/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="93" t="n">
@@ -36961,46 +36972,215 @@
       <c r="I92" s="94" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="102" t="n"/>
-      <c r="B93" s="102" t="inlineStr">
+      <c r="A93" s="89" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B93" s="90" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C93" s="90" t="inlineStr">
+        <is>
+          <t>Refil E3</t>
+        </is>
+      </c>
+      <c r="D93" s="91" t="n">
+        <v>90</v>
+      </c>
+      <c r="E93" s="90" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F93" s="91" t="n"/>
+      <c r="G93" s="91" t="n"/>
+      <c r="H93" s="90" t="n"/>
+      <c r="I93" s="90" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="93" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B94" s="94" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="C94" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D94" s="95" t="n">
+        <v>200</v>
+      </c>
+      <c r="E94" s="94" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F94" s="95" t="n"/>
+      <c r="G94" s="95" t="n"/>
+      <c r="H94" s="94" t="n"/>
+      <c r="I94" s="94" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="89" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B95" s="90" t="inlineStr">
+        <is>
+          <t>Cliente de Armando</t>
+        </is>
+      </c>
+      <c r="C95" s="90" t="n"/>
+      <c r="D95" s="91" t="n">
+        <v>145</v>
+      </c>
+      <c r="E95" s="90" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F95" s="91" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="G95" s="91" t="n"/>
+      <c r="H95" s="90" t="n"/>
+      <c r="I95" s="90" t="inlineStr">
+        <is>
+          <t>Crédito em 3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="93" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B96" s="94" t="inlineStr">
+        <is>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C96" s="94" t="n"/>
+      <c r="D96" s="95" t="n">
+        <v>800</v>
+      </c>
+      <c r="E96" s="94" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F96" s="95" t="n"/>
+      <c r="G96" s="95" t="n"/>
+      <c r="H96" s="94" t="n"/>
+      <c r="I96" s="94" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="89" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B97" s="90" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C97" s="90" t="inlineStr">
+        <is>
+          <t>Suporte Fit (para Carcaça) + Refil Plissado + Refil Carbon Tech 9"</t>
+        </is>
+      </c>
+      <c r="D97" s="91" t="n">
+        <v>205</v>
+      </c>
+      <c r="E97" s="90" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F97" s="91" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="G97" s="91" t="n"/>
+      <c r="H97" s="90" t="n"/>
+      <c r="I97" s="90" t="inlineStr">
+        <is>
+          <t>Crédito em 4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="93" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B98" s="94" t="inlineStr">
+        <is>
+          <t>Jaqueline da Silva Oliveira Nunes</t>
+        </is>
+      </c>
+      <c r="C98" s="94" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D98" s="95" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="94" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F98" s="95" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="G98" s="95" t="n"/>
+      <c r="H98" s="94" t="n"/>
+      <c r="I98" s="94" t="inlineStr">
+        <is>
+          <t>Crédito em 4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="29" t="n"/>
+      <c r="B99" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C93" s="102" t="n"/>
-      <c r="D93" s="103">
-        <f>SUM(D5:D92)</f>
-        <v/>
-      </c>
-      <c r="E93" s="102" t="n"/>
-      <c r="F93" s="103">
-        <f>SUM(F5:F92)</f>
-        <v/>
-      </c>
-      <c r="G93" s="103">
-        <f>SUM(G5:G92)</f>
-        <v/>
-      </c>
-      <c r="H93" s="102" t="n"/>
-      <c r="I93" s="102" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="104" t="n"/>
-      <c r="B94" s="104" t="inlineStr">
+      <c r="C99" s="161" t="n"/>
+      <c r="D99" s="8">
+        <f>SUM(D5:D98)</f>
+        <v/>
+      </c>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="29">
+        <f>SUM(F5:F98)</f>
+        <v/>
+      </c>
+      <c r="G99" s="8">
+        <f>SUM(G5:G98)</f>
+        <v/>
+      </c>
+      <c r="H99" s="29" t="n"/>
+      <c r="I99" s="29" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="30" t="n"/>
+      <c r="B100" s="154" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="C94" s="104" t="n"/>
-      <c r="D94" s="105">
-        <f>(D93-F93-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="E94" s="104" t="n"/>
-      <c r="F94" s="105" t="n"/>
-      <c r="G94" s="105" t="n"/>
-      <c r="H94" s="104" t="n"/>
-      <c r="I94" s="104" t="n"/>
+      <c r="D100" s="153">
+        <f>(D99-F99-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F100" s="30" t="n"/>
+      <c r="H100" s="30" t="n"/>
+      <c r="I100" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37017,10 +37197,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -41284,7 +41464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -41348,6 +41528,8 @@
       </c>
     </row>
     <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="21.95" customHeight="1" s="158">
       <c r="A9" s="201" t="inlineStr">
         <is>
@@ -43023,6 +43205,10 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="98" t="inlineStr">
         <is>
@@ -43071,6 +43257,8 @@
       <c r="F68" s="128" t="n"/>
       <c r="G68" s="98" t="n"/>
     </row>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="202" t="inlineStr">
         <is>
@@ -44285,7 +44473,7 @@
       </c>
       <c r="E110" s="124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F110" s="124">
@@ -44299,42 +44487,69 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="98" t="inlineStr">
+      <c r="A111" s="90" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="B111" s="90" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C111" s="89" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D111" s="91" t="n">
+        <v>200</v>
+      </c>
+      <c r="E111" s="124" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F111" s="124">
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="90" t="inlineStr">
+        <is>
+          <t>Troca do dia 14/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="98" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="B111" s="98" t="n"/>
-      <c r="C111" s="126" t="n"/>
-      <c r="D111" s="127">
-        <f>SUMIF(E74:E110,"Pendente",D74:D110)</f>
-        <v/>
-      </c>
-      <c r="E111" s="128" t="n"/>
-      <c r="F111" s="128" t="n"/>
-      <c r="G111" s="98" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="129" t="inlineStr">
+      <c r="D112" s="127">
+        <f>SUMIF(E74:E111,"Pendente",D74:D111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="129" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B112" s="160" t="n"/>
-      <c r="C112" s="160" t="n"/>
-      <c r="D112" s="160" t="n"/>
-      <c r="E112" s="160" t="n"/>
-      <c r="F112" s="160" t="n"/>
-      <c r="G112" s="161" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="200">
-        <f>IF(ROUND(D111-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D111-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B113" s="160" t="n"/>
+      <c r="C113" s="160" t="n"/>
+      <c r="D113" s="160" t="n"/>
+      <c r="E113" s="160" t="n"/>
+      <c r="F113" s="160" t="n"/>
+      <c r="G113" s="161" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="200" t="inlineStr">
+      <c r="A114" s="200">
+        <f>IF(ROUND(D112-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D112-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="200" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -44346,12 +44561,12 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A114:G114"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A112:G112"/>
     <mergeCell ref="A113:G113"/>
     <mergeCell ref="A71:G71"/>
     <mergeCell ref="C4:D4"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="B12" s="57" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C12" s="109" t="n">
         <v>20.26</v>
@@ -4529,7 +4529,7 @@
     <row r="31">
       <c r="A31" s="221" t="inlineStr">
         <is>
-          <t>PREÇOS: purificadores conforme o Catálogo de Purificadores (pasta Catálogos) — valor total do parcelamento em 10x, que é como as vendas entram na planilha. À vista sai mais barato: Residencial branco R$ 1.329, demais cores R$ 1.376; Plus branco R$ 1.429, demais R$ 1.476; Foz branco R$ 1.489, cinza/grafite R$ 1.589; Baby R$ 379. Carbon Tech 9": R$ 85,00 no balcão; pode ir a R$ 90,00 quando entra viagem/instalação.</t>
+          <t>PREÇOS: purificadores conforme o Catálogo de Purificadores (pasta Catálogos) — valor total do parcelamento em 10x, que é como as vendas entram na planilha. À vista sai mais barato: Residencial branco R$ 1.329, demais cores R$ 1.376; Plus branco R$ 1.429, demais R$ 1.476; Foz branco R$ 1.489, cinza/grafite R$ 1.589; Baby R$ 379. Preço de balcão x preço com serviço: Carbon Tech 9" R$ 85,00 e Plissado R$ 80,00 no balcão; os dois podem ir a R$ 90,00 quando há deslocamento do técnico, instalação ou outra despesa envolvida.</t>
         </is>
       </c>
     </row>
@@ -34175,7 +34175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U111"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -34330,11 +34330,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H109,K5,G5:G109)</f>
+        <f>SUMIF(H5:H115,K5,G5:G115)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D110-F110-T5</f>
+        <f>D116-F116-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -34342,11 +34342,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D111</f>
+        <f>D117</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E109,"Aguardando Pagamento",D5:D109)</f>
+        <f>SUMIF(E5:E115,"Aguardando Pagamento",D5:D115)</f>
         <v/>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H109,K6,G5:G109)</f>
+        <f>SUMIF(H5:H115,K6,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H109,K7,G5:G109)</f>
+        <f>SUMIF(H5:H115,K7,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34466,7 +34466,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H109,K8,G5:G109)</f>
+        <f>SUMIF(H5:H115,K8,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34506,7 +34506,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H109,K9,G5:G109)</f>
+        <f>SUMIF(H5:H115,K9,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H109,K10,G5:G109)</f>
+        <f>SUMIF(H5:H115,K10,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34586,7 +34586,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H109,K11,G5:G109)</f>
+        <f>SUMIF(H5:H115,K11,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H109,K12,G5:G109)</f>
+        <f>SUMIF(H5:H115,K12,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H109,K13,G5:G109)</f>
+        <f>SUMIF(H5:H115,K13,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H109,K14,G5:G109)</f>
+        <f>SUMIF(H5:H115,K14,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34742,7 +34742,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H109,K15,G5:G109)</f>
+        <f>SUMIF(H5:H115,K15,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H109,K16,G5:G109)</f>
+        <f>SUMIF(H5:H115,K16,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H109,K17,G5:G109)</f>
+        <f>SUMIF(H5:H115,K17,G5:G115)</f>
         <v/>
       </c>
     </row>
@@ -37391,43 +37391,219 @@
       <c r="I109" s="78" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="158">
-      <c r="A110" s="29" t="n"/>
-      <c r="B110" s="43" t="inlineStr">
+      <c r="A110" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="82" t="inlineStr">
+        <is>
+          <t>Maria Lopes dos Santos</t>
+        </is>
+      </c>
+      <c r="C110" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D110" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E110" s="82" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F110" s="83" t="n"/>
+      <c r="G110" s="83" t="n"/>
+      <c r="H110" s="82" t="n"/>
+      <c r="I110" s="82" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B111" s="78" t="inlineStr">
+        <is>
+          <t>Gardenia Ribeiro de Paula</t>
+        </is>
+      </c>
+      <c r="C111" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D111" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E111" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F111" s="79" t="n"/>
+      <c r="G111" s="79" t="n"/>
+      <c r="H111" s="78" t="n"/>
+      <c r="I111" s="78" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B112" s="82" t="inlineStr">
+        <is>
+          <t>Gildete Pinho</t>
+        </is>
+      </c>
+      <c r="C112" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D112" s="83" t="n">
+        <v>145</v>
+      </c>
+      <c r="E112" s="82" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F112" s="83" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G112" s="83" t="n"/>
+      <c r="H112" s="82" t="n"/>
+      <c r="I112" s="82" t="inlineStr">
+        <is>
+          <t>Crédito em 3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B113" s="78" t="inlineStr">
+        <is>
+          <t>Atacadão das Confecções e Utilidades</t>
+        </is>
+      </c>
+      <c r="C113" s="78" t="inlineStr">
+        <is>
+          <t>Válvula Reguladora de Pressão</t>
+        </is>
+      </c>
+      <c r="D113" s="79" t="n">
+        <v>80</v>
+      </c>
+      <c r="E113" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F113" s="79" t="n"/>
+      <c r="G113" s="79" t="n"/>
+      <c r="H113" s="78" t="n"/>
+      <c r="I113" s="78" t="inlineStr">
+        <is>
+          <t>Instalação feita em 15/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B114" s="82" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C114" s="82" t="inlineStr">
+        <is>
+          <t>2x Refil Carbon Tech 5" Rosca</t>
+        </is>
+      </c>
+      <c r="D114" s="83" t="n">
+        <v>60</v>
+      </c>
+      <c r="E114" s="82" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F114" s="83" t="n"/>
+      <c r="G114" s="83" t="n"/>
+      <c r="H114" s="82" t="n"/>
+      <c r="I114" s="82" t="inlineStr">
+        <is>
+          <t>R$ 30,00 cada (preço normal R$ 60,00). Versão com encaixe de rosca em vez de borracha de vedação — duas últimas unidades, paradas no estoque havia muito tempo; preço reduzido para girar. Estoque zerado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B115" s="78" t="inlineStr">
+        <is>
+          <t>Dínamo Engenharia Ltda</t>
+        </is>
+      </c>
+      <c r="C115" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Carbon Tech 9" + 2x Refil Plissado</t>
+        </is>
+      </c>
+      <c r="D115" s="79" t="n">
+        <v>310</v>
+      </c>
+      <c r="E115" s="78" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F115" s="79" t="n"/>
+      <c r="G115" s="79" t="n"/>
+      <c r="H115" s="78" t="n"/>
+      <c r="I115" s="78" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="29" t="n"/>
+      <c r="B116" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C110" s="161" t="n"/>
-      <c r="D110" s="8">
-        <f>SUM(D5:D109)</f>
-        <v/>
-      </c>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="29">
-        <f>SUM(F5:F109)</f>
-        <v/>
-      </c>
-      <c r="G110" s="8">
-        <f>SUM(G5:G109)</f>
-        <v/>
-      </c>
-      <c r="H110" s="29" t="n"/>
-      <c r="I110" s="29" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="30" t="n"/>
-      <c r="B111" s="135" t="inlineStr">
+      <c r="C116" s="161" t="n"/>
+      <c r="D116" s="8">
+        <f>SUM(D5:D115)</f>
+        <v/>
+      </c>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="29">
+        <f>SUM(F5:F115)</f>
+        <v/>
+      </c>
+      <c r="G116" s="8">
+        <f>SUM(G5:G115)</f>
+        <v/>
+      </c>
+      <c r="H116" s="29" t="n"/>
+      <c r="I116" s="29" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="n"/>
+      <c r="B117" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D111" s="134">
-        <f>(D110-F110-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F111" s="30" t="n"/>
-      <c r="H111" s="30" t="n"/>
-      <c r="I111" s="30" t="n"/>
+      <c r="D117" s="134">
+        <f>(D116-F116-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F117" s="30" t="n"/>
+      <c r="H117" s="30" t="n"/>
+      <c r="I117" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37444,10 +37620,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -3950,14 +3950,14 @@
     <row r="15">
       <c r="A15" s="52" t="inlineStr">
         <is>
-          <t>Mangueira (2 m)</t>
+          <t>Mangueira (por metro)</t>
         </is>
       </c>
       <c r="B15" s="55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C15" s="109" t="n">
-        <v>3.44</v>
+        <v>1.72</v>
       </c>
       <c r="D15" s="55" t="n">
         <v>0</v>
@@ -34175,7 +34175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U117"/>
+  <dimension ref="A1:U122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -34330,11 +34330,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H115,K5,G5:G115)</f>
+        <f>SUMIF(H5:H120,K5,G5:G120)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D116-F116-T5</f>
+        <f>D121-F121-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -34342,11 +34342,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D117</f>
+        <f>D122</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E115,"Aguardando Pagamento",D5:D115)</f>
+        <f>SUMIF(E5:E120,"Aguardando Pagamento",D5:D120)</f>
         <v/>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H115,K6,G5:G115)</f>
+        <f>SUMIF(H5:H120,K6,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H115,K7,G5:G115)</f>
+        <f>SUMIF(H5:H120,K7,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34466,7 +34466,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H115,K8,G5:G115)</f>
+        <f>SUMIF(H5:H120,K8,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34506,7 +34506,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H115,K9,G5:G115)</f>
+        <f>SUMIF(H5:H120,K9,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H115,K10,G5:G115)</f>
+        <f>SUMIF(H5:H120,K10,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34586,7 +34586,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H115,K11,G5:G115)</f>
+        <f>SUMIF(H5:H120,K11,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H115,K12,G5:G115)</f>
+        <f>SUMIF(H5:H120,K12,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H115,K13,G5:G115)</f>
+        <f>SUMIF(H5:H120,K13,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H115,K14,G5:G115)</f>
+        <f>SUMIF(H5:H120,K14,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34742,7 +34742,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H115,K15,G5:G115)</f>
+        <f>SUMIF(H5:H120,K15,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H115,K16,G5:G115)</f>
+        <f>SUMIF(H5:H120,K16,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H115,K17,G5:G115)</f>
+        <f>SUMIF(H5:H120,K17,G5:G120)</f>
         <v/>
       </c>
     </row>
@@ -36209,7 +36209,7 @@
       </c>
       <c r="E66" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F66" s="83" t="n"/>
@@ -37567,43 +37567,174 @@
       <c r="I115" s="78" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="29" t="n"/>
-      <c r="B116" s="43" t="inlineStr">
+      <c r="A116" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B116" s="82" t="inlineStr">
+        <is>
+          <t>Clínica Santa Cecília</t>
+        </is>
+      </c>
+      <c r="C116" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D116" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E116" s="82" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F116" s="83" t="n"/>
+      <c r="G116" s="83" t="n"/>
+      <c r="H116" s="82" t="n"/>
+      <c r="I116" s="82" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B117" s="78" t="inlineStr">
+        <is>
+          <t>Posto Payaya</t>
+        </is>
+      </c>
+      <c r="C117" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D117" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E117" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F117" s="79" t="n"/>
+      <c r="G117" s="79" t="n"/>
+      <c r="H117" s="78" t="n"/>
+      <c r="I117" s="78" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B118" s="82" t="inlineStr">
+        <is>
+          <t>App 99</t>
+        </is>
+      </c>
+      <c r="C118" s="82" t="n"/>
+      <c r="D118" s="83" t="n"/>
+      <c r="E118" s="82" t="n"/>
+      <c r="F118" s="83" t="n"/>
+      <c r="G118" s="83" t="n">
+        <v>20</v>
+      </c>
+      <c r="H118" s="82" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I118" s="82" t="inlineStr">
+        <is>
+          <t>Corrida para ir fazer serviços</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B119" s="78" t="inlineStr">
+        <is>
+          <t>Gasolina</t>
+        </is>
+      </c>
+      <c r="C119" s="78" t="n"/>
+      <c r="D119" s="79" t="n"/>
+      <c r="E119" s="78" t="n"/>
+      <c r="F119" s="79" t="n"/>
+      <c r="G119" s="79" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" s="78" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I119" s="78" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B120" s="82" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C120" s="82" t="inlineStr">
+        <is>
+          <t>Mangueira (2m)</t>
+        </is>
+      </c>
+      <c r="D120" s="83" t="n">
+        <v>20</v>
+      </c>
+      <c r="E120" s="82" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F120" s="83" t="n"/>
+      <c r="G120" s="83" t="n"/>
+      <c r="H120" s="82" t="n"/>
+      <c r="I120" s="82" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="29" t="n"/>
+      <c r="B121" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C116" s="161" t="n"/>
-      <c r="D116" s="8">
-        <f>SUM(D5:D115)</f>
-        <v/>
-      </c>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="29">
-        <f>SUM(F5:F115)</f>
-        <v/>
-      </c>
-      <c r="G116" s="8">
-        <f>SUM(G5:G115)</f>
-        <v/>
-      </c>
-      <c r="H116" s="29" t="n"/>
-      <c r="I116" s="29" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="30" t="n"/>
-      <c r="B117" s="135" t="inlineStr">
+      <c r="C121" s="161" t="n"/>
+      <c r="D121" s="8">
+        <f>SUM(D5:D120)</f>
+        <v/>
+      </c>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="29">
+        <f>SUM(F5:F120)</f>
+        <v/>
+      </c>
+      <c r="G121" s="8">
+        <f>SUM(G5:G120)</f>
+        <v/>
+      </c>
+      <c r="H121" s="29" t="n"/>
+      <c r="I121" s="29" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="30" t="n"/>
+      <c r="B122" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D117" s="134">
-        <f>(D116-F116-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F117" s="30" t="n"/>
-      <c r="H117" s="30" t="n"/>
-      <c r="I117" s="30" t="n"/>
+      <c r="D122" s="134">
+        <f>(D121-F121-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F122" s="30" t="n"/>
+      <c r="H122" s="30" t="n"/>
+      <c r="I122" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37620,10 +37751,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -34175,7 +34175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U122"/>
+  <dimension ref="A1:U126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -34330,11 +34330,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H120,K5,G5:G120)</f>
+        <f>SUMIF(H5:H124,K5,G5:G124)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D121-F121-T5</f>
+        <f>D125-F125-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -34342,11 +34342,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D122</f>
+        <f>D126</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E120,"Aguardando Pagamento",D5:D120)</f>
+        <f>SUMIF(E5:E124,"Aguardando Pagamento",D5:D124)</f>
         <v/>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H120,K6,G5:G120)</f>
+        <f>SUMIF(H5:H124,K6,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H120,K7,G5:G120)</f>
+        <f>SUMIF(H5:H124,K7,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34466,7 +34466,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H120,K8,G5:G120)</f>
+        <f>SUMIF(H5:H124,K8,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34506,7 +34506,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H120,K9,G5:G120)</f>
+        <f>SUMIF(H5:H124,K9,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H120,K10,G5:G120)</f>
+        <f>SUMIF(H5:H124,K10,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34586,7 +34586,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H120,K11,G5:G120)</f>
+        <f>SUMIF(H5:H124,K11,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H120,K12,G5:G120)</f>
+        <f>SUMIF(H5:H124,K12,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H120,K13,G5:G120)</f>
+        <f>SUMIF(H5:H124,K13,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H120,K14,G5:G120)</f>
+        <f>SUMIF(H5:H124,K14,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34742,7 +34742,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H120,K15,G5:G120)</f>
+        <f>SUMIF(H5:H124,K15,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H120,K16,G5:G120)</f>
+        <f>SUMIF(H5:H124,K16,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H120,K17,G5:G120)</f>
+        <f>SUMIF(H5:H124,K17,G5:G124)</f>
         <v/>
       </c>
     </row>
@@ -37577,11 +37577,11 @@
       </c>
       <c r="C116" s="82" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="D116" s="83" t="n">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="E116" s="82" t="inlineStr">
         <is>
@@ -37698,43 +37698,151 @@
       <c r="I120" s="82" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="29" t="n"/>
-      <c r="B121" s="43" t="inlineStr">
+      <c r="A121" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B121" s="78" t="inlineStr">
+        <is>
+          <t>Luciana dos Santos Freire</t>
+        </is>
+      </c>
+      <c r="C121" s="78" t="inlineStr">
+        <is>
+          <t>Purificador Everest Baby Branco</t>
+        </is>
+      </c>
+      <c r="D121" s="79" t="n">
+        <v>379</v>
+      </c>
+      <c r="E121" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F121" s="79" t="n"/>
+      <c r="G121" s="79" t="n"/>
+      <c r="H121" s="78" t="n"/>
+      <c r="I121" s="78" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B122" s="82" t="inlineStr">
+        <is>
+          <t>Patrus Transportes</t>
+        </is>
+      </c>
+      <c r="C122" s="82" t="n"/>
+      <c r="D122" s="83" t="n"/>
+      <c r="E122" s="82" t="n"/>
+      <c r="F122" s="83" t="n"/>
+      <c r="G122" s="83" t="n">
+        <v>292.68</v>
+      </c>
+      <c r="H122" s="82" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I122" s="82" t="inlineStr">
+        <is>
+          <t>Frete da fatura 26-08-913041 (CT-e 2117850, remetente Eversoft, NF 75472) — venc. 16/09/2026. Pago em 16/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B123" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
+      <c r="C123" s="78" t="n"/>
+      <c r="D123" s="79" t="n"/>
+      <c r="E123" s="78" t="n"/>
+      <c r="F123" s="79" t="n"/>
+      <c r="G123" s="79" t="n">
+        <v>139.31</v>
+      </c>
+      <c r="H123" s="78" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I123" s="78" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377737 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B124" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
+      <c r="C124" s="82" t="n"/>
+      <c r="D124" s="83" t="n"/>
+      <c r="E124" s="82" t="n"/>
+      <c r="F124" s="83" t="n"/>
+      <c r="G124" s="83" t="n">
+        <v>856.35</v>
+      </c>
+      <c r="H124" s="82" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I124" s="82" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377739 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="29" t="n"/>
+      <c r="B125" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C121" s="161" t="n"/>
-      <c r="D121" s="8">
-        <f>SUM(D5:D120)</f>
-        <v/>
-      </c>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="29">
-        <f>SUM(F5:F120)</f>
-        <v/>
-      </c>
-      <c r="G121" s="8">
-        <f>SUM(G5:G120)</f>
-        <v/>
-      </c>
-      <c r="H121" s="29" t="n"/>
-      <c r="I121" s="29" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="30" t="n"/>
-      <c r="B122" s="135" t="inlineStr">
+      <c r="C125" s="161" t="n"/>
+      <c r="D125" s="8">
+        <f>SUM(D5:D124)</f>
+        <v/>
+      </c>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="29">
+        <f>SUM(F5:F124)</f>
+        <v/>
+      </c>
+      <c r="G125" s="8">
+        <f>SUM(G5:G124)</f>
+        <v/>
+      </c>
+      <c r="H125" s="29" t="n"/>
+      <c r="I125" s="29" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="30" t="n"/>
+      <c r="B126" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D122" s="134">
-        <f>(D121-F121-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F122" s="30" t="n"/>
-      <c r="H122" s="30" t="n"/>
-      <c r="I122" s="30" t="n"/>
+      <c r="D126" s="134">
+        <f>(D125-F125-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F126" s="30" t="n"/>
+      <c r="H126" s="30" t="n"/>
+      <c r="I126" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37751,10 +37859,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -42613,7 +42721,7 @@
       </c>
       <c r="E25" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F25" s="113">
@@ -42622,7 +42730,7 @@
       </c>
       <c r="G25" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840262224-4, cedente 6348-/017737-7. Após o vencimento: R$ 0,44 por dia de atraso; protesto a partir do 7º dia.</t>
+          <t>Categoria: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840262224-4, cedente 6348-/017737-7. Frete da fatura 26-08-913041 (CT-e 2117850, remetente Eversoft, NF 75472). Pago em 16/09/2026 — lançado em "Set 2026" como "Patrus Transportes".</t>
         </is>
       </c>
     </row>
@@ -42965,7 +43073,7 @@
       </c>
       <c r="E36" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F36" s="113">
@@ -42974,7 +43082,7 @@
       </c>
       <c r="G36" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336084-8. Linha digitável 34191.12218 33608.480308 52238.850003 9 15710000013931. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336084-8. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -43029,7 +43137,7 @@
       </c>
       <c r="E38" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F38" s="113">
@@ -43038,7 +43146,7 @@
       </c>
       <c r="G38" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336008-7. Linha digitável 34191.12218 33600.870308 52238.850003 9 15710000085635. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336008-7. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -34175,7 +34175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U126"/>
+  <dimension ref="A1:U129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -34330,11 +34330,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H124,K5,G5:G124)</f>
+        <f>SUMIF(H5:H127,K5,G5:G127)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D125-F125-T5</f>
+        <f>D128-F128-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -34342,11 +34342,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D126</f>
+        <f>D129</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E124,"Aguardando Pagamento",D5:D124)</f>
+        <f>SUMIF(E5:E127,"Aguardando Pagamento",D5:D127)</f>
         <v/>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H124,K6,G5:G124)</f>
+        <f>SUMIF(H5:H127,K6,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H124,K7,G5:G124)</f>
+        <f>SUMIF(H5:H127,K7,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34466,7 +34466,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H124,K8,G5:G124)</f>
+        <f>SUMIF(H5:H127,K8,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34506,7 +34506,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H124,K9,G5:G124)</f>
+        <f>SUMIF(H5:H127,K9,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H124,K10,G5:G124)</f>
+        <f>SUMIF(H5:H127,K10,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34586,7 +34586,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H124,K11,G5:G124)</f>
+        <f>SUMIF(H5:H127,K11,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H124,K12,G5:G124)</f>
+        <f>SUMIF(H5:H127,K12,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H124,K13,G5:G124)</f>
+        <f>SUMIF(H5:H127,K13,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H124,K14,G5:G124)</f>
+        <f>SUMIF(H5:H127,K14,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34742,7 +34742,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H124,K15,G5:G124)</f>
+        <f>SUMIF(H5:H127,K15,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H124,K16,G5:G124)</f>
+        <f>SUMIF(H5:H127,K16,G5:G127)</f>
         <v/>
       </c>
     </row>
@@ -37806,43 +37806,124 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="29" t="n"/>
-      <c r="B125" s="43" t="inlineStr">
+      <c r="A125" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B125" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
+      <c r="C125" s="78" t="n"/>
+      <c r="D125" s="79" t="n"/>
+      <c r="E125" s="78" t="n"/>
+      <c r="F125" s="79" t="n"/>
+      <c r="G125" s="79" t="n">
+        <v>865.5</v>
+      </c>
+      <c r="H125" s="78" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I125" s="78" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377738 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B126" s="82" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C126" s="82" t="n"/>
+      <c r="D126" s="83" t="n"/>
+      <c r="E126" s="82" t="n"/>
+      <c r="F126" s="83" t="n"/>
+      <c r="G126" s="83" t="n">
+        <v>1385.85</v>
+      </c>
+      <c r="H126" s="82" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I126" s="82" t="inlineStr">
+        <is>
+          <t>Boleto doc. 131997/4 (emissão 08/07/2026) · parcela 4/4 (última) — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="77" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B127" s="78" t="inlineStr">
+        <is>
+          <t>Centro Medico Boa Saude</t>
+        </is>
+      </c>
+      <c r="C127" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D127" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="E127" s="78" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F127" s="79" t="n"/>
+      <c r="G127" s="79" t="n"/>
+      <c r="H127" s="78" t="n"/>
+      <c r="I127" s="78" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="29" t="n"/>
+      <c r="B128" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C125" s="161" t="n"/>
-      <c r="D125" s="8">
-        <f>SUM(D5:D124)</f>
-        <v/>
-      </c>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="29">
-        <f>SUM(F5:F124)</f>
-        <v/>
-      </c>
-      <c r="G125" s="8">
-        <f>SUM(G5:G124)</f>
-        <v/>
-      </c>
-      <c r="H125" s="29" t="n"/>
-      <c r="I125" s="29" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="30" t="n"/>
-      <c r="B126" s="135" t="inlineStr">
+      <c r="C128" s="161" t="n"/>
+      <c r="D128" s="8">
+        <f>SUM(D5:D127)</f>
+        <v/>
+      </c>
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="29">
+        <f>SUM(F5:F127)</f>
+        <v/>
+      </c>
+      <c r="G128" s="8">
+        <f>SUM(G5:G127)</f>
+        <v/>
+      </c>
+      <c r="H128" s="29" t="n"/>
+      <c r="I128" s="29" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="n"/>
+      <c r="B129" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D126" s="134">
-        <f>(D125-F125-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F126" s="30" t="n"/>
-      <c r="H126" s="30" t="n"/>
-      <c r="I126" s="30" t="n"/>
+      <c r="D129" s="134">
+        <f>(D128-F128-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F129" s="30" t="n"/>
+      <c r="H129" s="30" t="n"/>
+      <c r="I129" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37859,10 +37940,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -42147,7 +42228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -42198,7 +42279,7 @@
     </row>
     <row r="5">
       <c r="A5" s="190">
-        <f>D68</f>
+        <f>D69</f>
         <v/>
       </c>
       <c r="C5" s="203">
@@ -43105,7 +43186,7 @@
       </c>
       <c r="E37" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F37" s="112">
@@ -43114,7 +43195,7 @@
       </c>
       <c r="G37" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336022-8. Linha digitável 34191.12218 33602.280308 52238.850003 5 15710000086550. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336022-8. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -43617,7 +43698,7 @@
       </c>
       <c r="E53" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F53" s="112">
@@ -43626,7 +43707,7 @@
       </c>
       <c r="G53" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00255359-0. Linha digitável 34191.09008 25535.901430 81531.550002 9 15710000138585. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00255359-0. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -43886,1073 +43967,1203 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B62" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386188 (emissão 15/09/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C62" s="81" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D62" s="83" t="n">
+        <v>574.27</v>
+      </c>
+      <c r="E62" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F62" s="113">
+        <f>IF(OR($E62="Pago",$C62=""),"",MAX(0,TODAY()-$C62))</f>
+        <v/>
+      </c>
+      <c r="G62" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B63" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386188 (emissão 15/09/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C63" s="77" t="n">
+        <v>46340</v>
+      </c>
+      <c r="D63" s="79" t="n">
+        <v>574.27</v>
+      </c>
+      <c r="E63" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F63" s="112">
+        <f>IF(OR($E63="Pago",$C63=""),"",MAX(0,TODAY()-$C63))</f>
+        <v/>
+      </c>
+      <c r="G63" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842013. Linha digitável 34191.12358 84201.340308 52238.850003 8 16300000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B64" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386188 (emissão 15/09/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C64" s="81" t="n">
+        <v>46370</v>
+      </c>
+      <c r="D64" s="83" t="n">
+        <v>574.27</v>
+      </c>
+      <c r="E64" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F64" s="113">
+        <f>IF(OR($E64="Pago",$C64=""),"",MAX(0,TODAY()-$C64))</f>
+        <v/>
+      </c>
+      <c r="G64" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841927. Linha digitável 34191.12358 84192.760308 52238.850003 8 16600000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B65" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386188 (emissão 15/09/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C65" s="77" t="n">
+        <v>46400</v>
+      </c>
+      <c r="D65" s="79" t="n">
+        <v>574.27</v>
+      </c>
+      <c r="E65" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F65" s="112">
+        <f>IF(OR($E65="Pago",$C65=""),"",MAX(0,TODAY()-$C65))</f>
+        <v/>
+      </c>
+      <c r="G65" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842031. Linha digitável 34191.12358 84203.160308 52238.850003 1 16900000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="86" t="inlineStr">
+      <c r="A66" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B66" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386188 (emissão 15/09/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C66" s="81" t="n">
+        <v>46430</v>
+      </c>
+      <c r="D66" s="83" t="n">
+        <v>574.28</v>
+      </c>
+      <c r="E66" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F66" s="113">
+        <f>IF(OR($E66="Pago",$C66=""),"",MAX(0,TODAY()-$C66))</f>
+        <v/>
+      </c>
+      <c r="G66" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842128. Linha digitável 34191.12358 84212.800308 52238.850003 3 17200000057428. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B66" s="86" t="n"/>
-      <c r="C66" s="114" t="n"/>
-      <c r="D66" s="115">
-        <f>SUMIF(E11:E65,"Pendente",D11:D65)</f>
-        <v/>
-      </c>
-      <c r="E66" s="116" t="n"/>
-      <c r="F66" s="116" t="n"/>
-      <c r="G66" s="86" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="154" t="inlineStr">
+      <c r="B67" s="86" t="n"/>
+      <c r="C67" s="114" t="n"/>
+      <c r="D67" s="115">
+        <f>SUMIF(E11:E66,"Pendente",D11:D66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="116" t="n"/>
+      <c r="F67" s="116" t="n"/>
+      <c r="G67" s="86" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="154" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B67" s="154" t="n"/>
-      <c r="C67" s="155" t="n"/>
-      <c r="D67" s="156">
-        <f>SUMIF(E11:E65,"Previsto",D11:D65)</f>
-        <v/>
-      </c>
-      <c r="E67" s="152" t="n"/>
-      <c r="F67" s="152" t="n"/>
-      <c r="G67" s="154" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="86" t="inlineStr">
+      <c r="B68" s="154" t="n"/>
+      <c r="C68" s="155" t="n"/>
+      <c r="D68" s="156">
+        <f>SUMIF(E11:E66,"Previsto",D11:D66)</f>
+        <v/>
+      </c>
+      <c r="E68" s="152" t="n"/>
+      <c r="F68" s="152" t="n"/>
+      <c r="G68" s="154" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B68" s="86" t="n"/>
-      <c r="C68" s="114" t="n"/>
-      <c r="D68" s="115">
-        <f>D66+D67</f>
-        <v/>
-      </c>
-      <c r="E68" s="116" t="n"/>
-      <c r="F68" s="116" t="n"/>
-      <c r="G68" s="86" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" s="158">
-      <c r="A71" s="206" t="inlineStr">
+      <c r="B69" s="86" t="n"/>
+      <c r="C69" s="114" t="n"/>
+      <c r="D69" s="115">
+        <f>D67+D68</f>
+        <v/>
+      </c>
+      <c r="E69" s="116" t="n"/>
+      <c r="F69" s="116" t="n"/>
+      <c r="G69" s="86" t="n"/>
+    </row>
+    <row r="70"/>
+    <row r="71" ht="15.75" customHeight="1" s="158"/>
+    <row r="72">
+      <c r="A72" s="206" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="195" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="195" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="111" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B73" s="111" t="inlineStr">
+      <c r="B74" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C73" s="111" t="inlineStr">
+      <c r="C74" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D73" s="111" t="inlineStr">
+      <c r="D74" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E73" s="111" t="inlineStr">
+      <c r="E74" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F73" s="111" t="inlineStr">
+      <c r="F74" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G73" s="111" t="inlineStr">
+      <c r="G74" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="78" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B74" s="78" t="inlineStr">
+      <c r="B75" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C74" s="77" t="n">
+      <c r="C75" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D74" s="79" t="n">
+      <c r="D75" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E74" s="112" t="inlineStr">
+      <c r="E75" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F74" s="112">
+      <c r="F75" s="112">
         <f>IF(OR($E74="Recebido",$C74=""),"",MAX(0,TODAY()-$C74))</f>
         <v/>
       </c>
-      <c r="G74" s="78" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="82" t="inlineStr">
+      <c r="G75" s="78" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B75" s="82" t="inlineStr">
+      <c r="B76" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C75" s="81" t="n">
+      <c r="C76" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D75" s="83" t="n">
+      <c r="D76" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E75" s="113" t="inlineStr">
+      <c r="E76" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F75" s="113">
+      <c r="F76" s="113">
         <f>IF(OR($E75="Recebido",$C75=""),"",MAX(0,TODAY()-$C75))</f>
         <v/>
       </c>
-      <c r="G75" s="82" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="78" t="inlineStr">
+      <c r="G76" s="82" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B76" s="78" t="inlineStr">
+      <c r="B77" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C76" s="77" t="n">
+      <c r="C77" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D76" s="79" t="n">
+      <c r="D77" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E76" s="112" t="inlineStr">
+      <c r="E77" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F76" s="112">
+      <c r="F77" s="112">
         <f>IF(OR($E76="Recebido",$C76=""),"",MAX(0,TODAY()-$C76))</f>
         <v/>
       </c>
-      <c r="G76" s="78" t="inlineStr">
+      <c r="G77" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="82" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B77" s="82" t="inlineStr">
+      <c r="B78" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C77" s="81" t="n">
+      <c r="C78" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D77" s="83" t="n">
+      <c r="D78" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E77" s="113" t="inlineStr">
+      <c r="E78" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F77" s="113">
+      <c r="F78" s="113">
         <f>IF(OR($E77="Recebido",$C77=""),"",MAX(0,TODAY()-$C77))</f>
         <v/>
       </c>
-      <c r="G77" s="82" t="inlineStr">
+      <c r="G78" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="78" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B78" s="78" t="inlineStr">
+      <c r="B79" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C78" s="77" t="n">
+      <c r="C79" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D78" s="79" t="n">
+      <c r="D79" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E78" s="112" t="inlineStr">
+      <c r="E79" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F78" s="112">
+      <c r="F79" s="112">
         <f>IF(OR($E78="Recebido",$C78=""),"",MAX(0,TODAY()-$C78))</f>
         <v/>
       </c>
-      <c r="G78" s="78" t="inlineStr">
+      <c r="G79" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="82" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B79" s="82" t="inlineStr">
+      <c r="B80" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C79" s="81" t="n">
+      <c r="C80" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D79" s="83" t="n">
+      <c r="D80" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E79" s="113" t="inlineStr">
+      <c r="E80" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F79" s="113">
+      <c r="F80" s="113">
         <f>IF(OR($E79="Recebido",$C79=""),"",MAX(0,TODAY()-$C79))</f>
         <v/>
       </c>
-      <c r="G79" s="82" t="inlineStr">
+      <c r="G80" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="78" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B80" s="78" t="inlineStr">
+      <c r="B81" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C80" s="77" t="n">
+      <c r="C81" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D80" s="79" t="n">
+      <c r="D81" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E80" s="112" t="inlineStr">
+      <c r="E81" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F80" s="112">
+      <c r="F81" s="112">
         <f>IF(OR($E80="Recebido",$C80=""),"",MAX(0,TODAY()-$C80))</f>
         <v/>
       </c>
-      <c r="G80" s="78" t="inlineStr">
+      <c r="G81" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="82" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B81" s="82" t="inlineStr">
+      <c r="B82" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C81" s="81" t="n">
+      <c r="C82" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D81" s="83" t="n">
+      <c r="D82" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E81" s="113" t="inlineStr">
+      <c r="E82" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F81" s="113">
+      <c r="F82" s="113">
         <f>IF(OR($E81="Recebido",$C81=""),"",MAX(0,TODAY()-$C81))</f>
         <v/>
       </c>
-      <c r="G81" s="82" t="inlineStr">
+      <c r="G82" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="78" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B82" s="78" t="inlineStr">
+      <c r="B83" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C82" s="77" t="n">
+      <c r="C83" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D82" s="79" t="n">
+      <c r="D83" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E82" s="112" t="inlineStr">
+      <c r="E83" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F82" s="112">
+      <c r="F83" s="112">
         <f>IF(OR($E82="Recebido",$C82=""),"",MAX(0,TODAY()-$C82))</f>
         <v/>
       </c>
-      <c r="G82" s="78" t="inlineStr">
+      <c r="G83" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="82" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B83" s="82" t="inlineStr">
+      <c r="B84" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C83" s="81" t="n">
+      <c r="C84" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D83" s="83" t="n">
+      <c r="D84" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E83" s="113" t="inlineStr">
+      <c r="E84" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F83" s="113">
+      <c r="F84" s="113">
         <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
         <v/>
       </c>
-      <c r="G83" s="82" t="inlineStr">
+      <c r="G84" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="78" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B84" s="78" t="inlineStr">
+      <c r="B85" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C84" s="77" t="n">
+      <c r="C85" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D84" s="79" t="n">
+      <c r="D85" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E84" s="112" t="inlineStr">
+      <c r="E85" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F84" s="112">
+      <c r="F85" s="112">
         <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
         <v/>
       </c>
-      <c r="G84" s="78" t="inlineStr">
+      <c r="G85" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="82" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B85" s="82" t="inlineStr">
+      <c r="B86" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C85" s="81" t="n">
+      <c r="C86" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D85" s="83" t="n">
+      <c r="D86" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E85" s="113" t="inlineStr">
+      <c r="E86" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F85" s="113">
+      <c r="F86" s="113">
         <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
         <v/>
       </c>
-      <c r="G85" s="82" t="inlineStr">
+      <c r="G86" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="78" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B86" s="78" t="inlineStr">
+      <c r="B87" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C86" s="77" t="n">
+      <c r="C87" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D86" s="79" t="n">
+      <c r="D87" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E86" s="112" t="inlineStr">
+      <c r="E87" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F86" s="112">
+      <c r="F87" s="112">
         <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
         <v/>
       </c>
-      <c r="G86" s="78" t="inlineStr">
+      <c r="G87" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="82" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B87" s="82" t="inlineStr">
+      <c r="B88" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C87" s="81" t="n">
+      <c r="C88" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D87" s="83" t="n">
+      <c r="D88" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E87" s="113" t="inlineStr">
+      <c r="E88" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F87" s="113">
+      <c r="F88" s="113">
         <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
         <v/>
       </c>
-      <c r="G87" s="82" t="inlineStr">
+      <c r="G88" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="78" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B88" s="78" t="inlineStr">
+      <c r="B89" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C88" s="77" t="n">
+      <c r="C89" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D88" s="79" t="n">
+      <c r="D89" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E88" s="112" t="inlineStr">
+      <c r="E89" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F88" s="112">
+      <c r="F89" s="112">
         <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
         <v/>
       </c>
-      <c r="G88" s="78" t="inlineStr">
+      <c r="G89" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="82" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B89" s="82" t="inlineStr">
+      <c r="B90" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C89" s="81" t="n">
+      <c r="C90" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D89" s="83" t="n">
+      <c r="D90" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E89" s="113" t="inlineStr">
+      <c r="E90" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F89" s="113">
+      <c r="F90" s="113">
         <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
         <v/>
       </c>
-      <c r="G89" s="82" t="inlineStr">
+      <c r="G90" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="78" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B90" s="78" t="inlineStr">
+      <c r="B91" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C90" s="77" t="n">
+      <c r="C91" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D90" s="79" t="n">
+      <c r="D91" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E90" s="112" t="inlineStr">
+      <c r="E91" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F90" s="112">
+      <c r="F91" s="112">
         <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
         <v/>
       </c>
-      <c r="G90" s="78" t="inlineStr">
+      <c r="G91" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="82" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B91" s="82" t="inlineStr">
+      <c r="B92" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C91" s="81" t="n">
+      <c r="C92" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D91" s="83" t="n">
+      <c r="D92" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E91" s="113" t="inlineStr">
+      <c r="E92" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F91" s="113">
+      <c r="F92" s="113">
         <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
         <v/>
       </c>
-      <c r="G91" s="82" t="inlineStr">
+      <c r="G92" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="78" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B92" s="78" t="inlineStr">
+      <c r="B93" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C92" s="77" t="n">
+      <c r="C93" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D92" s="79" t="n">
+      <c r="D93" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E92" s="112" t="inlineStr">
+      <c r="E93" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F92" s="112">
+      <c r="F93" s="112">
         <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
         <v/>
       </c>
-      <c r="G92" s="78" t="inlineStr">
+      <c r="G93" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="82" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B93" s="82" t="inlineStr">
+      <c r="B94" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C94" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D93" s="83" t="n">
+      <c r="D94" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E93" s="113" t="inlineStr">
+      <c r="E94" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F93" s="113">
+      <c r="F94" s="113">
         <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
         <v/>
       </c>
-      <c r="G93" s="82" t="inlineStr">
+      <c r="G94" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="78" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B94" s="78" t="inlineStr">
+      <c r="B95" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C94" s="77" t="n">
+      <c r="C95" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D94" s="79" t="n">
+      <c r="D95" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E94" s="112" t="inlineStr">
+      <c r="E95" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="112">
+      <c r="F95" s="112">
         <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
         <v/>
       </c>
-      <c r="G94" s="78" t="inlineStr">
+      <c r="G95" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="82" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B96" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C96" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D95" s="83" t="n">
+      <c r="D96" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E95" s="113" t="inlineStr">
+      <c r="E96" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F95" s="113">
+      <c r="F96" s="113">
         <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
         <v/>
       </c>
-      <c r="G95" s="82" t="inlineStr">
+      <c r="G96" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="78" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B96" s="78" t="inlineStr">
+      <c r="B97" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C96" s="77" t="n">
+      <c r="C97" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D96" s="79" t="n">
+      <c r="D97" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E96" s="112" t="inlineStr">
+      <c r="E97" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F96" s="112">
+      <c r="F97" s="112">
         <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
         <v/>
       </c>
-      <c r="G96" s="78" t="inlineStr">
+      <c r="G97" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="82" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="82" t="inlineStr">
         <is>
           <t>Instituto Paulo Leão</t>
         </is>
       </c>
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
-      <c r="C97" s="81" t="n">
+      <c r="C98" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D97" s="83" t="n">
+      <c r="D98" s="83" t="n">
         <v>160</v>
       </c>
-      <c r="E97" s="113" t="inlineStr">
+      <c r="E98" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F97" s="113">
+      <c r="F98" s="113">
         <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
         <v/>
       </c>
-      <c r="G97" s="82" t="inlineStr">
+      <c r="G98" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="78" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="78" t="inlineStr">
         <is>
           <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
-      <c r="B98" s="78" t="inlineStr">
+      <c r="B99" s="78" t="inlineStr">
         <is>
           <t>Pré Filtro</t>
         </is>
       </c>
-      <c r="C98" s="77" t="n">
+      <c r="C99" s="77" t="n">
         <v>46265</v>
       </c>
-      <c r="D98" s="79" t="n">
+      <c r="D99" s="79" t="n">
         <v>60</v>
       </c>
-      <c r="E98" s="112" t="inlineStr">
+      <c r="E99" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="112">
+      <c r="F99" s="112">
         <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
         <v/>
       </c>
-      <c r="G98" s="78" t="inlineStr">
+      <c r="G99" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="82" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="82" t="inlineStr">
         <is>
           <t>Clube dos Mineiros</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C99" s="81" t="n">
+      <c r="C100" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D99" s="83" t="n">
+      <c r="D100" s="83" t="n">
         <v>150</v>
       </c>
-      <c r="E99" s="113" t="inlineStr">
+      <c r="E100" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F99" s="113">
+      <c r="F100" s="113">
         <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
         <v/>
       </c>
-      <c r="G99" s="82" t="inlineStr">
+      <c r="G100" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="78" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="78" t="inlineStr">
         <is>
           <t>Armazem Cecilio Mota</t>
         </is>
       </c>
-      <c r="B100" s="78" t="inlineStr">
+      <c r="B101" s="78" t="inlineStr">
         <is>
           <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
-      <c r="C100" s="77" t="n">
+      <c r="C101" s="77" t="n">
         <v>46266</v>
       </c>
-      <c r="D100" s="79" t="n">
+      <c r="D101" s="79" t="n">
         <v>225</v>
       </c>
-      <c r="E100" s="112" t="inlineStr">
+      <c r="E101" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F100" s="112">
+      <c r="F101" s="112">
         <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
         <v/>
       </c>
-      <c r="G100" s="78" t="inlineStr">
+      <c r="G101" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B101" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C101" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D101" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E101" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F101" s="113">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="82" t="inlineStr">
         <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B102" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C102" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D102" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E102" s="113" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F102" s="113">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="82" t="inlineStr">
+        <is>
           <t>Tesla Imagem Medicina Diagnostica Ltda</t>
         </is>
       </c>
-      <c r="B102" s="82" t="inlineStr">
+      <c r="B103" s="82" t="inlineStr">
         <is>
           <t>3x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
-      <c r="C102" s="81" t="n">
+      <c r="C103" s="81" t="n">
         <v>46267</v>
       </c>
-      <c r="D102" s="83" t="n">
+      <c r="D103" s="83" t="n">
         <v>540</v>
       </c>
-      <c r="E102" s="113" t="inlineStr">
+      <c r="E103" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F102" s="113">
+      <c r="F103" s="113">
         <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
         <v/>
       </c>
-      <c r="G102" s="82" t="inlineStr">
+      <c r="G103" s="82" t="inlineStr">
         <is>
           <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="78" t="inlineStr">
-        <is>
-          <t>Cecilio Mota Junior</t>
-        </is>
-      </c>
-      <c r="B103" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C103" s="77" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D103" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E103" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F103" s="112">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="78" t="inlineStr">
         <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B104" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C104" s="77" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D104" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E104" s="112" t="inlineStr">
         <is>
@@ -44960,31 +45171,31 @@
         </is>
       </c>
       <c r="F104" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
         <v/>
       </c>
       <c r="G104" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B105" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C105" s="77" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="D105" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E105" s="112" t="inlineStr">
         <is>
@@ -44992,95 +45203,95 @@
         </is>
       </c>
       <c r="F105" s="112">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
         <v/>
       </c>
       <c r="G105" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="78" t="inlineStr">
         <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B106" s="78" t="inlineStr">
         <is>
-          <t>Refil Plissado + Refil BAG</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C106" s="77" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="D106" s="79" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E106" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F106" s="112">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
         <v/>
       </c>
       <c r="G106" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="78" t="inlineStr">
         <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B107" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C107" s="77" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="D107" s="79" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E107" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F107" s="112">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
         <v/>
       </c>
       <c r="G107" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B108" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C108" s="77" t="n">
         <v>46275</v>
       </c>
       <c r="D108" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E108" s="112" t="inlineStr">
         <is>
@@ -45088,7 +45299,7 @@
         </is>
       </c>
       <c r="F108" s="112">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
         <v/>
       </c>
       <c r="G108" s="78" t="inlineStr">
@@ -45100,131 +45311,163 @@
     <row r="109">
       <c r="A109" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B109" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C109" s="77" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D109" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E109" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F109" s="112">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
         <v/>
       </c>
       <c r="G109" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B110" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C110" s="77" t="n">
         <v>46276</v>
       </c>
       <c r="D110" s="79" t="n">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="E110" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F110" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
         <v/>
       </c>
       <c r="G110" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="78" t="inlineStr">
         <is>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
+        </is>
+      </c>
+      <c r="B111" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C111" s="77" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D111" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E111" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F111" s="112">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G111" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 11/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="78" t="inlineStr">
+        <is>
           <t>IOB</t>
         </is>
       </c>
-      <c r="B111" s="78" t="inlineStr">
+      <c r="B112" s="78" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C111" s="77" t="n">
+      <c r="C112" s="77" t="n">
         <v>46279</v>
       </c>
-      <c r="D111" s="79" t="n">
+      <c r="D112" s="79" t="n">
         <v>200</v>
       </c>
-      <c r="E111" s="112" t="inlineStr">
+      <c r="E112" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="112">
+      <c r="F112" s="112">
         <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
         <v/>
       </c>
-      <c r="G111" s="78" t="inlineStr">
+      <c r="G112" s="78" t="inlineStr">
         <is>
           <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="86" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D112" s="115">
-        <f>SUMIF(E74:E111,"Pendente",D74:D111)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="205" t="inlineStr">
+      <c r="D113" s="115">
+        <f>SUMIF(E75:E112,"Pendente",D75:D112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="205" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B113" s="160" t="n"/>
-      <c r="C113" s="160" t="n"/>
-      <c r="D113" s="160" t="n"/>
-      <c r="E113" s="160" t="n"/>
-      <c r="F113" s="160" t="n"/>
-      <c r="G113" s="161" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="202">
-        <f>IF(ROUND(D112-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D112-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B114" s="160" t="n"/>
+      <c r="C114" s="160" t="n"/>
+      <c r="D114" s="160" t="n"/>
+      <c r="E114" s="160" t="n"/>
+      <c r="F114" s="160" t="n"/>
+      <c r="G114" s="161" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="202" t="inlineStr">
+      <c r="A115" s="202">
+        <f>IF(ROUND(D113-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D113-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="202" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -45242,15 +45485,15 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A115:G115"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E74:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E75:E112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -7243,7 +7243,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -7306,6 +7306,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -7393,6 +7398,11 @@
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0653</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Aluguel</t>
@@ -7423,6 +7433,11 @@
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="21" t="n"/>
       <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0652</t>
+        </is>
+      </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Água, Energia e Internet</t>
@@ -7521,6 +7536,11 @@
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
       <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
@@ -7551,6 +7571,11 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0655</t>
+        </is>
+      </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Salários, Comissões e Encargos</t>
@@ -7765,6 +7790,11 @@
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="26" t="n"/>
       <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0188</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7795,6 +7825,11 @@
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="21" t="n"/>
       <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0201</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="n">
@@ -7841,6 +7876,11 @@
       <c r="E21" s="19" t="n"/>
       <c r="F21" s="21" t="n"/>
       <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0201</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="n">
@@ -7862,6 +7902,11 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
       <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0194</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -7904,6 +7949,11 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
       <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0656</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -7925,6 +7975,11 @@
       <c r="E25" s="19" t="n"/>
       <c r="F25" s="21" t="n"/>
       <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0035</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="n">
@@ -7946,6 +8001,11 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="26" t="n"/>
       <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0100</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -8713,6 +8773,11 @@
       <c r="E61" s="19" t="n"/>
       <c r="F61" s="21" t="n"/>
       <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0662</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="22" t="n">
@@ -8734,6 +8799,11 @@
       <c r="E62" s="25" t="n"/>
       <c r="F62" s="26" t="n"/>
       <c r="G62" s="23" t="n"/>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0651</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n">
@@ -8755,6 +8825,11 @@
       <c r="E63" s="19" t="n"/>
       <c r="F63" s="21" t="n"/>
       <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0661</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="22" t="n">
@@ -8797,6 +8872,11 @@
       <c r="E65" s="19" t="n"/>
       <c r="F65" s="21" t="n"/>
       <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0077</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="22" t="n">
@@ -8860,6 +8940,11 @@
       <c r="E68" s="25" t="n"/>
       <c r="F68" s="26" t="n"/>
       <c r="G68" s="23" t="n"/>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0244</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -9090,6 +9175,11 @@
       <c r="E78" s="25" t="n"/>
       <c r="F78" s="26" t="n"/>
       <c r="G78" s="23" t="n"/>
+      <c r="H78" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0676</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n">
@@ -9153,6 +9243,11 @@
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="21" t="n"/>
       <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0665</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="n">
@@ -9266,6 +9361,11 @@
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
       <c r="G86" s="23" t="n"/>
+      <c r="H86" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0669</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -9287,6 +9387,11 @@
       <c r="E87" s="19" t="n"/>
       <c r="F87" s="21" t="n"/>
       <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0316</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="22" t="n">
@@ -9492,6 +9597,11 @@
       <c r="E96" s="25" t="n"/>
       <c r="F96" s="26" t="n"/>
       <c r="G96" s="23" t="n"/>
+      <c r="H96" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0668</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -9534,6 +9644,11 @@
       <c r="E98" s="25" t="n"/>
       <c r="F98" s="26" t="n"/>
       <c r="G98" s="23" t="n"/>
+      <c r="H98" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0030</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
@@ -9555,6 +9670,11 @@
       <c r="E99" s="19" t="n"/>
       <c r="F99" s="21" t="n"/>
       <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0306</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="22" t="n">
@@ -9639,6 +9759,11 @@
       <c r="E103" s="19" t="n"/>
       <c r="F103" s="21" t="n"/>
       <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0220</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="22" t="n">
@@ -9752,6 +9877,11 @@
       <c r="E108" s="25" t="n"/>
       <c r="F108" s="26" t="n"/>
       <c r="G108" s="23" t="n"/>
+      <c r="H108" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0055</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n">
@@ -9815,6 +9945,11 @@
       <c r="E111" s="19" t="n"/>
       <c r="F111" s="21" t="n"/>
       <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0184</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="22" t="n">
@@ -10087,6 +10222,11 @@
       <c r="E123" s="19" t="n"/>
       <c r="F123" s="21" t="n"/>
       <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0696</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="22" t="n">
@@ -10108,6 +10248,11 @@
       <c r="E124" s="25" t="n"/>
       <c r="F124" s="26" t="n"/>
       <c r="G124" s="23" t="n"/>
+      <c r="H124" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0138</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="n">
@@ -10129,6 +10274,11 @@
       <c r="E125" s="19" t="n"/>
       <c r="F125" s="21" t="n"/>
       <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0296</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="22" t="n">
@@ -10171,6 +10321,11 @@
       <c r="E127" s="19" t="n"/>
       <c r="F127" s="21" t="n"/>
       <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0034</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="22" t="n">
@@ -10192,6 +10347,11 @@
       <c r="E128" s="25" t="n"/>
       <c r="F128" s="26" t="n"/>
       <c r="G128" s="23" t="n"/>
+      <c r="H128" s="23" t="inlineStr">
+        <is>
+          <t>ESC-0016</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="n">
@@ -10234,6 +10394,11 @@
       <c r="E130" s="25" t="n"/>
       <c r="F130" s="26" t="n"/>
       <c r="G130" s="23" t="n"/>
+      <c r="H130" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0597</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="n">
@@ -10358,7 +10523,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -10421,6 +10586,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -10508,6 +10678,11 @@
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0644</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Aluguel</t>
@@ -10568,6 +10743,11 @@
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0687</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -10598,6 +10778,11 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0686</t>
+        </is>
+      </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
@@ -10628,6 +10813,11 @@
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
       <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0147</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
@@ -10688,6 +10878,11 @@
       <c r="E12" s="25" t="n"/>
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0051</t>
+        </is>
+      </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Contabilidade</t>
@@ -10898,6 +11093,11 @@
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="21" t="n"/>
       <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0681</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="n">
@@ -10961,6 +11161,11 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
       <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0361</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -11003,6 +11208,11 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
       <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>ESC-0017</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -11066,6 +11276,11 @@
       <c r="E27" s="19" t="n"/>
       <c r="F27" s="21" t="n"/>
       <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0691</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="n">
@@ -11426,6 +11641,11 @@
       <c r="E43" s="19" t="n"/>
       <c r="F43" s="21" t="n"/>
       <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0270</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="n">
@@ -11447,6 +11667,11 @@
       <c r="E44" s="25" t="n"/>
       <c r="F44" s="26" t="n"/>
       <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0643</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -11468,6 +11693,11 @@
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="21" t="n"/>
       <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0176</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="n">
@@ -11531,6 +11761,11 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
       <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0696</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -11573,6 +11808,11 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
       <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0305</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -11615,6 +11855,11 @@
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="26" t="n"/>
       <c r="G52" s="23" t="n"/>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0697</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -11636,6 +11881,11 @@
       <c r="E53" s="19" t="n"/>
       <c r="F53" s="21" t="n"/>
       <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0316</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="n">
@@ -11678,6 +11928,11 @@
       <c r="E55" s="19" t="n"/>
       <c r="F55" s="21" t="n"/>
       <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0700</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="n">
@@ -11720,6 +11975,11 @@
       <c r="E57" s="19" t="n"/>
       <c r="F57" s="21" t="n"/>
       <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0701</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="22" t="n">
@@ -11892,6 +12152,11 @@
       <c r="E65" s="19" t="n"/>
       <c r="F65" s="21" t="n"/>
       <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0704</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="22" t="n">
@@ -11913,6 +12178,11 @@
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="26" t="n"/>
       <c r="G66" s="23" t="n"/>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0216</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -11934,6 +12204,11 @@
       <c r="E67" s="19" t="n"/>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0679</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="n">
@@ -11955,6 +12230,11 @@
       <c r="E68" s="25" t="n"/>
       <c r="F68" s="26" t="n"/>
       <c r="G68" s="23" t="n"/>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0243</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -11976,6 +12256,11 @@
       <c r="E69" s="19" t="n"/>
       <c r="F69" s="21" t="n"/>
       <c r="G69" s="18" t="n"/>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0702</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="n">
@@ -12085,6 +12370,11 @@
       <c r="E74" s="25" t="n"/>
       <c r="F74" s="26" t="n"/>
       <c r="G74" s="23" t="n"/>
+      <c r="H74" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0706</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -12127,6 +12417,11 @@
       <c r="E76" s="25" t="n"/>
       <c r="F76" s="26" t="n"/>
       <c r="G76" s="23" t="n"/>
+      <c r="H76" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0702</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n">
@@ -12190,6 +12485,11 @@
       <c r="E79" s="19" t="n"/>
       <c r="F79" s="21" t="n"/>
       <c r="G79" s="18" t="n"/>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0711</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="22" t="n">
@@ -12232,6 +12532,11 @@
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="21" t="n"/>
       <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0255</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="n">
@@ -12274,6 +12579,11 @@
       <c r="E83" s="19" t="n"/>
       <c r="F83" s="21" t="n"/>
       <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0715</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="22" t="n">
@@ -12295,6 +12605,11 @@
       <c r="E84" s="25" t="n"/>
       <c r="F84" s="26" t="n"/>
       <c r="G84" s="23" t="n"/>
+      <c r="H84" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0713</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="17" t="n">
@@ -12337,6 +12652,11 @@
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
       <c r="G86" s="23" t="n"/>
+      <c r="H86" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0335</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -12358,6 +12678,11 @@
       <c r="E87" s="19" t="n"/>
       <c r="F87" s="21" t="n"/>
       <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0044</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="22" t="n">
@@ -12379,6 +12704,11 @@
       <c r="E88" s="25" t="n"/>
       <c r="F88" s="26" t="n"/>
       <c r="G88" s="23" t="n"/>
+      <c r="H88" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0018</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
@@ -12400,6 +12730,11 @@
       <c r="E89" s="19" t="n"/>
       <c r="F89" s="21" t="n"/>
       <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0716</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="22" t="n">
@@ -12546,6 +12881,11 @@
       <c r="E95" s="19" t="n"/>
       <c r="F95" s="21" t="n"/>
       <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0289</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="22" t="n">
@@ -12567,6 +12907,11 @@
       <c r="E96" s="25" t="n"/>
       <c r="F96" s="26" t="n"/>
       <c r="G96" s="23" t="n"/>
+      <c r="H96" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0717</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -12672,6 +13017,11 @@
       <c r="E101" s="19" t="n"/>
       <c r="F101" s="21" t="n"/>
       <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0720</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="22" t="n">
@@ -12923,6 +13273,11 @@
       <c r="E112" s="25" t="n"/>
       <c r="F112" s="26" t="n"/>
       <c r="G112" s="23" t="n"/>
+      <c r="H112" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0723</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="n">
@@ -13082,6 +13437,11 @@
       <c r="E119" s="19" t="n"/>
       <c r="F119" s="21" t="n"/>
       <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0726</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="22" t="n">
@@ -13103,6 +13463,11 @@
       <c r="E120" s="25" t="n"/>
       <c r="F120" s="26" t="n"/>
       <c r="G120" s="23" t="n"/>
+      <c r="H120" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0727</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n">
@@ -13124,6 +13489,11 @@
       <c r="E121" s="19" t="n"/>
       <c r="F121" s="21" t="n"/>
       <c r="G121" s="18" t="n"/>
+      <c r="H121" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0728</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="22" t="n">
@@ -13166,6 +13536,11 @@
       <c r="E123" s="19" t="n"/>
       <c r="F123" s="21" t="n"/>
       <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0729</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="22" t="n">
@@ -13187,6 +13562,11 @@
       <c r="E124" s="25" t="n"/>
       <c r="F124" s="26" t="n"/>
       <c r="G124" s="23" t="n"/>
+      <c r="H124" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0730</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="n">
@@ -13208,6 +13588,11 @@
       <c r="E125" s="19" t="n"/>
       <c r="F125" s="21" t="n"/>
       <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0727</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="22" t="n">
@@ -13271,6 +13656,11 @@
       <c r="E128" s="25" t="n"/>
       <c r="F128" s="26" t="n"/>
       <c r="G128" s="23" t="n"/>
+      <c r="H128" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0287</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="n">
@@ -13355,6 +13745,11 @@
       <c r="E132" s="25" t="n"/>
       <c r="F132" s="26" t="n"/>
       <c r="G132" s="23" t="n"/>
+      <c r="H132" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0733</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="n">
@@ -13376,6 +13771,11 @@
       <c r="E133" s="19" t="n"/>
       <c r="F133" s="21" t="n"/>
       <c r="G133" s="18" t="n"/>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0734</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="22" t="n">
@@ -13397,6 +13797,11 @@
       <c r="E134" s="25" t="n"/>
       <c r="F134" s="26" t="n"/>
       <c r="G134" s="23" t="n"/>
+      <c r="H134" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0274</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="n">
@@ -13568,6 +13973,11 @@
       <c r="E141" s="19" t="n"/>
       <c r="F141" s="21" t="n"/>
       <c r="G141" s="18" t="n"/>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0125</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="22" t="n">
@@ -13734,7 +14144,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -13797,6 +14207,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -13944,6 +14359,11 @@
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0494</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -13974,6 +14394,11 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0740</t>
+        </is>
+      </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
@@ -14064,6 +14489,11 @@
       <c r="E12" s="25" t="n"/>
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0737</t>
+        </is>
+      </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Contabilidade</t>
@@ -14128,6 +14558,11 @@
       <c r="E14" s="25" t="n"/>
       <c r="F14" s="26" t="n"/>
       <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0220</t>
+        </is>
+      </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Material de Limpeza e Escritório</t>
@@ -14158,6 +14593,11 @@
       <c r="E15" s="19" t="n"/>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0057</t>
+        </is>
+      </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Estornos de Vendas (Cancelamentos)</t>
@@ -14218,6 +14658,11 @@
       <c r="E17" s="19" t="n"/>
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0742</t>
+        </is>
+      </c>
       <c r="I17" s="42" t="inlineStr">
         <is>
           <t>Pro Labore Edilânia</t>
@@ -14248,6 +14693,11 @@
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="26" t="n"/>
       <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0507</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -14278,6 +14728,11 @@
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="21" t="n"/>
       <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0741</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="n">
@@ -14299,6 +14754,11 @@
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="26" t="n"/>
       <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0747</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -14320,6 +14780,11 @@
       <c r="E21" s="19" t="n"/>
       <c r="F21" s="21" t="n"/>
       <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0039</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="n">
@@ -14341,6 +14806,11 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
       <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0746</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -14425,6 +14895,11 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="26" t="n"/>
       <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0276</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -14446,6 +14921,11 @@
       <c r="E27" s="19" t="n"/>
       <c r="F27" s="21" t="n"/>
       <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0125</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="n">
@@ -14509,6 +14989,11 @@
       <c r="E30" s="25" t="n"/>
       <c r="F30" s="26" t="n"/>
       <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0061</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
@@ -14530,6 +15015,11 @@
       <c r="E31" s="19" t="n"/>
       <c r="F31" s="21" t="n"/>
       <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0116</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="n">
@@ -14551,6 +15041,11 @@
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="26" t="n"/>
       <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0134</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
@@ -14572,6 +15067,11 @@
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="21" t="n"/>
       <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0752</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="n">
@@ -14848,6 +15348,11 @@
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="21" t="n"/>
       <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0043</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="n">
@@ -14869,6 +15374,11 @@
       <c r="E46" s="25" t="n"/>
       <c r="F46" s="26" t="n"/>
       <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0755</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -14890,6 +15400,11 @@
       <c r="E47" s="19" t="n"/>
       <c r="F47" s="21" t="n"/>
       <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="n">
@@ -14911,6 +15426,11 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
       <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -14974,6 +15494,11 @@
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="21" t="n"/>
       <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0756</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="22" t="n">
@@ -14995,6 +15520,11 @@
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="26" t="n"/>
       <c r="G52" s="23" t="n"/>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0272</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -15058,6 +15588,11 @@
       <c r="E55" s="19" t="n"/>
       <c r="F55" s="21" t="n"/>
       <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0066</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="n">
@@ -15121,6 +15656,11 @@
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
       <c r="G58" s="23" t="n"/>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0144</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -15142,6 +15682,11 @@
       <c r="E59" s="19" t="n"/>
       <c r="F59" s="21" t="n"/>
       <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0758</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="n">
@@ -15331,6 +15876,11 @@
       <c r="E68" s="25" t="n"/>
       <c r="F68" s="26" t="n"/>
       <c r="G68" s="23" t="n"/>
+      <c r="H68" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0020</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -15415,6 +15965,11 @@
       <c r="E72" s="25" t="n"/>
       <c r="F72" s="26" t="n"/>
       <c r="G72" s="23" t="n"/>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0763</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -15436,6 +15991,11 @@
       <c r="E73" s="19" t="n"/>
       <c r="F73" s="21" t="n"/>
       <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0765</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="22" t="n">
@@ -15628,6 +16188,11 @@
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="21" t="n"/>
       <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0061</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="n">
@@ -15649,6 +16214,11 @@
       <c r="E82" s="25" t="n"/>
       <c r="F82" s="26" t="n"/>
       <c r="G82" s="23" t="n"/>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0055</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -15712,6 +16282,11 @@
       <c r="E85" s="19" t="n"/>
       <c r="F85" s="21" t="n"/>
       <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0011</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="22" t="n">
@@ -15775,6 +16350,11 @@
       <c r="E88" s="25" t="n"/>
       <c r="F88" s="26" t="n"/>
       <c r="G88" s="23" t="n"/>
+      <c r="H88" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0063</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
@@ -15796,6 +16376,11 @@
       <c r="E89" s="19" t="n"/>
       <c r="F89" s="21" t="n"/>
       <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0221</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="22" t="n">
@@ -15859,6 +16444,11 @@
       <c r="E92" s="25" t="n"/>
       <c r="F92" s="26" t="n"/>
       <c r="G92" s="23" t="n"/>
+      <c r="H92" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0520</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n">
@@ -15880,6 +16470,11 @@
       <c r="E93" s="19" t="n"/>
       <c r="F93" s="21" t="n"/>
       <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0067</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="n">
@@ -15943,6 +16538,11 @@
       <c r="E96" s="25" t="n"/>
       <c r="F96" s="26" t="n"/>
       <c r="G96" s="23" t="n"/>
+      <c r="H96" s="23" t="inlineStr">
+        <is>
+          <t>ESC-0005</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -16185,6 +16785,11 @@
       <c r="E106" s="25" t="n"/>
       <c r="F106" s="26" t="n"/>
       <c r="G106" s="23" t="n"/>
+      <c r="H106" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0508</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n">
@@ -16206,6 +16811,11 @@
       <c r="E107" s="19" t="n"/>
       <c r="F107" s="21" t="n"/>
       <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0769</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="22" t="n">
@@ -16248,6 +16858,11 @@
       <c r="E109" s="19" t="n"/>
       <c r="F109" s="21" t="n"/>
       <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0055</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="22" t="n">
@@ -16290,6 +16905,11 @@
       <c r="E111" s="19" t="n"/>
       <c r="F111" s="21" t="n"/>
       <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0768</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="22" t="n">
@@ -16598,7 +17218,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -16661,6 +17281,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -16748,6 +17373,11 @@
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0696</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Aluguel</t>
@@ -16808,6 +17438,11 @@
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0754</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -16932,6 +17567,11 @@
       <c r="E12" s="25" t="n"/>
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0067</t>
+        </is>
+      </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Contabilidade</t>
@@ -17022,6 +17662,11 @@
       <c r="E15" s="19" t="n"/>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0774</t>
+        </is>
+      </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Estornos de Vendas (Cancelamentos)</t>
@@ -17052,6 +17697,11 @@
       <c r="E16" s="25" t="n"/>
       <c r="F16" s="26" t="n"/>
       <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0776</t>
+        </is>
+      </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Outras Despesas</t>
@@ -17082,6 +17732,11 @@
       <c r="E17" s="19" t="n"/>
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0040</t>
+        </is>
+      </c>
       <c r="I17" s="42" t="inlineStr">
         <is>
           <t>Pro Labore Edilânia</t>
@@ -17112,6 +17767,11 @@
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="26" t="n"/>
       <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0778</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -17184,6 +17844,11 @@
       <c r="E21" s="19" t="n"/>
       <c r="F21" s="21" t="n"/>
       <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0777</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="n">
@@ -17205,6 +17870,11 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
       <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0779</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -17226,6 +17896,11 @@
       <c r="E23" s="19" t="n"/>
       <c r="F23" s="21" t="n"/>
       <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0109</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="n">
@@ -17247,6 +17922,11 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
       <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -17268,6 +17948,11 @@
       <c r="E25" s="19" t="n"/>
       <c r="F25" s="21" t="n"/>
       <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0312</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="n">
@@ -17289,6 +17974,11 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="26" t="n"/>
       <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0297</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -17310,6 +18000,11 @@
       <c r="E27" s="19" t="n"/>
       <c r="F27" s="21" t="n"/>
       <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0781</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="n">
@@ -17436,6 +18131,11 @@
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="21" t="n"/>
       <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0782</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="n">
@@ -17478,6 +18178,11 @@
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="21" t="n"/>
       <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0787</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="n">
@@ -17499,6 +18204,11 @@
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="26" t="n"/>
       <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0136</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -17671,6 +18381,11 @@
       <c r="E44" s="25" t="n"/>
       <c r="F44" s="26" t="n"/>
       <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -17713,6 +18428,11 @@
       <c r="E46" s="25" t="n"/>
       <c r="F46" s="26" t="n"/>
       <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0101</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -17734,6 +18454,11 @@
       <c r="E47" s="19" t="n"/>
       <c r="F47" s="21" t="n"/>
       <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0789</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="n">
@@ -17755,6 +18480,11 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
       <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0273</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -17797,6 +18527,11 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
       <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0791</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -17960,6 +18695,11 @@
       <c r="E57" s="19" t="n"/>
       <c r="F57" s="21" t="n"/>
       <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0793</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="22" t="n">
@@ -17981,6 +18721,11 @@
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
       <c r="G58" s="23" t="n"/>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0184</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -18002,6 +18747,11 @@
       <c r="E59" s="19" t="n"/>
       <c r="F59" s="21" t="n"/>
       <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0791</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="n">
@@ -18086,6 +18836,11 @@
       <c r="E63" s="19" t="n"/>
       <c r="F63" s="21" t="n"/>
       <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0391</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="22" t="n">
@@ -18149,6 +18904,11 @@
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="26" t="n"/>
       <c r="G66" s="23" t="n"/>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0296</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -18170,6 +18930,11 @@
       <c r="E67" s="19" t="n"/>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0659</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="n">
@@ -18254,6 +19019,11 @@
       <c r="E71" s="19" t="n"/>
       <c r="F71" s="21" t="n"/>
       <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0795</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="22" t="n">
@@ -18488,6 +19258,11 @@
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="21" t="n"/>
       <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="n">
@@ -18509,6 +19284,11 @@
       <c r="E82" s="25" t="n"/>
       <c r="F82" s="26" t="n"/>
       <c r="G82" s="23" t="n"/>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0798</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -18593,6 +19373,11 @@
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
       <c r="G86" s="23" t="n"/>
+      <c r="H86" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0181</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -18677,6 +19462,11 @@
       <c r="E90" s="25" t="n"/>
       <c r="F90" s="26" t="n"/>
       <c r="G90" s="23" t="n"/>
+      <c r="H90" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0796</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -18698,6 +19488,11 @@
       <c r="E91" s="19" t="n"/>
       <c r="F91" s="21" t="n"/>
       <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0014</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="22" t="n">
@@ -18740,6 +19535,11 @@
       <c r="E93" s="19" t="n"/>
       <c r="F93" s="21" t="n"/>
       <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0799</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="n">
@@ -18761,6 +19561,11 @@
       <c r="E94" s="25" t="n"/>
       <c r="F94" s="26" t="n"/>
       <c r="G94" s="23" t="n"/>
+      <c r="H94" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0067</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n">
@@ -18845,6 +19650,11 @@
       <c r="E98" s="25" t="n"/>
       <c r="F98" s="26" t="n"/>
       <c r="G98" s="23" t="n"/>
+      <c r="H98" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0802</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
@@ -18979,6 +19789,11 @@
       <c r="E104" s="25" t="n"/>
       <c r="F104" s="26" t="n"/>
       <c r="G104" s="23" t="n"/>
+      <c r="H104" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0066</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n">
@@ -19109,6 +19924,11 @@
       <c r="E110" s="25" t="n"/>
       <c r="F110" s="26" t="n"/>
       <c r="G110" s="23" t="n"/>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0258</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n">
@@ -19130,6 +19950,11 @@
       <c r="E111" s="19" t="n"/>
       <c r="F111" s="21" t="n"/>
       <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0807</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="22" t="n">
@@ -19151,6 +19976,11 @@
       <c r="E112" s="25" t="n"/>
       <c r="F112" s="26" t="n"/>
       <c r="G112" s="23" t="n"/>
+      <c r="H112" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0804</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="n">
@@ -19214,6 +20044,11 @@
       <c r="E115" s="19" t="n"/>
       <c r="F115" s="21" t="n"/>
       <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0806</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="22" t="n">
@@ -19310,6 +20145,11 @@
       <c r="E119" s="19" t="n"/>
       <c r="F119" s="21" t="n"/>
       <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0570</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="22" t="n">
@@ -19331,6 +20171,11 @@
       <c r="E120" s="25" t="n"/>
       <c r="F120" s="26" t="n"/>
       <c r="G120" s="23" t="n"/>
+      <c r="H120" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0569</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n">
@@ -19476,7 +20321,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -19539,6 +20384,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -19660,6 +20510,11 @@
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="21" t="n"/>
       <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0802</t>
+        </is>
+      </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Água, Energia e Internet</t>
@@ -19690,6 +20545,11 @@
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0220</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -19878,6 +20738,11 @@
       <c r="E14" s="25" t="n"/>
       <c r="F14" s="26" t="n"/>
       <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0810</t>
+        </is>
+      </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Material de Limpeza e Escritório</t>
@@ -19938,6 +20803,11 @@
       <c r="E16" s="25" t="n"/>
       <c r="F16" s="26" t="n"/>
       <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0812</t>
+        </is>
+      </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Outras Despesas</t>
@@ -20466,6 +21336,11 @@
       <c r="E37" s="19" t="n"/>
       <c r="F37" s="21" t="n"/>
       <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0779</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="n">
@@ -20550,6 +21425,11 @@
       <c r="E41" s="19" t="n"/>
       <c r="F41" s="21" t="n"/>
       <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0817</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="n">
@@ -20634,6 +21514,11 @@
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="21" t="n"/>
       <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0248</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="n">
@@ -20655,6 +21540,11 @@
       <c r="E46" s="25" t="n"/>
       <c r="F46" s="26" t="n"/>
       <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0216</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -20722,6 +21612,11 @@
       <c r="E49" s="19" t="n"/>
       <c r="F49" s="21" t="n"/>
       <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0819</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="22" t="n">
@@ -20743,6 +21638,11 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
       <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0814</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -20852,6 +21752,11 @@
       <c r="E55" s="19" t="n"/>
       <c r="F55" s="21" t="n"/>
       <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0820</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="n">
@@ -20915,6 +21820,11 @@
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
       <c r="G58" s="23" t="n"/>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0821</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -21087,6 +21997,11 @@
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="26" t="n"/>
       <c r="G66" s="23" t="n"/>
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0063</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -21238,6 +22153,11 @@
       <c r="E73" s="19" t="n"/>
       <c r="F73" s="21" t="n"/>
       <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0677</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="22" t="n">
@@ -21259,6 +22179,11 @@
       <c r="E74" s="25" t="n"/>
       <c r="F74" s="26" t="n"/>
       <c r="G74" s="23" t="n"/>
+      <c r="H74" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0818</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -21280,6 +22205,11 @@
       <c r="E75" s="19" t="n"/>
       <c r="F75" s="21" t="n"/>
       <c r="G75" s="18" t="n"/>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0316</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="22" t="n">
@@ -21385,6 +22315,11 @@
       <c r="E80" s="25" t="n"/>
       <c r="F80" s="26" t="n"/>
       <c r="G80" s="23" t="n"/>
+      <c r="H80" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0130</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n">
@@ -21406,6 +22341,11 @@
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="21" t="n"/>
       <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>ESC-0012</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="n">
@@ -21490,6 +22430,11 @@
       <c r="E85" s="19" t="n"/>
       <c r="F85" s="21" t="n"/>
       <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0829</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="22" t="n">
@@ -21674,6 +22619,11 @@
       <c r="E93" s="19" t="n"/>
       <c r="F93" s="21" t="n"/>
       <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0830</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="n">
@@ -21758,6 +22708,11 @@
       <c r="E97" s="19" t="n"/>
       <c r="F97" s="21" t="n"/>
       <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0069</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="22" t="n">
@@ -21804,6 +22759,11 @@
       <c r="E99" s="19" t="n"/>
       <c r="F99" s="21" t="n"/>
       <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0052</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="22" t="n">
@@ -21825,6 +22785,11 @@
       <c r="E100" s="25" t="n"/>
       <c r="F100" s="26" t="n"/>
       <c r="G100" s="23" t="n"/>
+      <c r="H100" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0086</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n">
@@ -21867,6 +22832,11 @@
       <c r="E102" s="25" t="n"/>
       <c r="F102" s="26" t="n"/>
       <c r="G102" s="23" t="n"/>
+      <c r="H102" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0182</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
@@ -21976,6 +22946,11 @@
       <c r="E107" s="19" t="n"/>
       <c r="F107" s="21" t="n"/>
       <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0117</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="22" t="n">
@@ -21997,6 +22972,11 @@
       <c r="E108" s="25" t="n"/>
       <c r="F108" s="26" t="n"/>
       <c r="G108" s="23" t="n"/>
+      <c r="H108" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0836</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n">
@@ -22252,6 +23232,11 @@
       <c r="E119" s="19" t="n"/>
       <c r="F119" s="21" t="n"/>
       <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0303</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="22" t="n">
@@ -22273,6 +23258,11 @@
       <c r="E120" s="25" t="n"/>
       <c r="F120" s="26" t="n"/>
       <c r="G120" s="23" t="n"/>
+      <c r="H120" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0837</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n">
@@ -22389,7 +23379,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -22452,6 +23442,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -22493,6 +23488,11 @@
       <c r="E5" s="19" t="n"/>
       <c r="F5" s="21" t="n"/>
       <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0838</t>
+        </is>
+      </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Fornecedores / Mercadoria</t>
@@ -22535,6 +23535,11 @@
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0005</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Aluguel</t>
@@ -22565,6 +23570,11 @@
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="21" t="n"/>
       <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0839</t>
+        </is>
+      </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Água, Energia e Internet</t>
@@ -22595,6 +23605,11 @@
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0741</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -22625,6 +23640,11 @@
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0207</t>
+        </is>
+      </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
@@ -22655,6 +23675,11 @@
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
       <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0840</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
@@ -22745,6 +23770,11 @@
       <c r="E13" s="19" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0848</t>
+        </is>
+      </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Manutenção e Reparos</t>
@@ -22835,6 +23865,11 @@
       <c r="E16" s="25" t="n"/>
       <c r="F16" s="26" t="n"/>
       <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0842</t>
+        </is>
+      </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Outras Despesas</t>
@@ -22865,6 +23900,11 @@
       <c r="E17" s="19" t="n"/>
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0030</t>
+        </is>
+      </c>
       <c r="I17" s="42" t="inlineStr">
         <is>
           <t>Pro Labore Edilânia</t>
@@ -23163,6 +24203,11 @@
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="21" t="n"/>
       <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0845</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="n">
@@ -23247,6 +24292,11 @@
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="21" t="n"/>
       <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0278</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="n">
@@ -23289,6 +24339,11 @@
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="21" t="n"/>
       <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0030</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="n">
@@ -23385,6 +24440,11 @@
       <c r="E39" s="19" t="n"/>
       <c r="F39" s="21" t="n"/>
       <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0113</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="n">
@@ -23406,6 +24466,11 @@
       <c r="E40" s="25" t="n"/>
       <c r="F40" s="26" t="n"/>
       <c r="G40" s="23" t="n"/>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0112</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
@@ -23427,6 +24492,11 @@
       <c r="E41" s="19" t="n"/>
       <c r="F41" s="21" t="n"/>
       <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0002</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="n">
@@ -23448,6 +24518,11 @@
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="26" t="n"/>
       <c r="G42" s="23" t="n"/>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0125</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
@@ -23574,6 +24649,11 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
       <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0850</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -23658,6 +24738,11 @@
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="26" t="n"/>
       <c r="G52" s="23" t="n"/>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0851</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -23679,6 +24764,11 @@
       <c r="E53" s="19" t="n"/>
       <c r="F53" s="21" t="n"/>
       <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0627</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="n">
@@ -23700,6 +24790,11 @@
       <c r="E54" s="25" t="n"/>
       <c r="F54" s="26" t="n"/>
       <c r="G54" s="23" t="n"/>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0846</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
@@ -23805,6 +24900,11 @@
       <c r="E59" s="19" t="n"/>
       <c r="F59" s="21" t="n"/>
       <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0463</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="n">
@@ -23918,6 +25018,11 @@
       <c r="E64" s="25" t="n"/>
       <c r="F64" s="26" t="n"/>
       <c r="G64" s="23" t="n"/>
+      <c r="H64" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
@@ -23939,6 +25044,11 @@
       <c r="E65" s="19" t="n"/>
       <c r="F65" s="21" t="n"/>
       <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0853</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="22" t="n">
@@ -23981,6 +25091,11 @@
       <c r="E67" s="19" t="n"/>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0855</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="n">
@@ -24023,6 +25138,11 @@
       <c r="E69" s="19" t="n"/>
       <c r="F69" s="21" t="n"/>
       <c r="G69" s="18" t="n"/>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0192</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="n">
@@ -24044,6 +25164,11 @@
       <c r="E70" s="25" t="n"/>
       <c r="F70" s="26" t="n"/>
       <c r="G70" s="23" t="n"/>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>OUT-0006</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -24086,6 +25211,11 @@
       <c r="E72" s="25" t="n"/>
       <c r="F72" s="26" t="n"/>
       <c r="G72" s="23" t="n"/>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0063</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -24191,6 +25321,11 @@
       <c r="E77" s="19" t="n"/>
       <c r="F77" s="21" t="n"/>
       <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>ESC-0016</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="22" t="n">
@@ -24337,6 +25472,11 @@
       <c r="E83" s="19" t="n"/>
       <c r="F83" s="21" t="n"/>
       <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0858</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="22" t="n">
@@ -24484,6 +25624,11 @@
       <c r="E90" s="25" t="n"/>
       <c r="F90" s="26" t="n"/>
       <c r="G90" s="23" t="n"/>
+      <c r="H90" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0098</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -24547,6 +25692,11 @@
       <c r="E93" s="19" t="n"/>
       <c r="F93" s="21" t="n"/>
       <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>ESC-0020</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="n">
@@ -24568,6 +25718,11 @@
       <c r="E94" s="25" t="n"/>
       <c r="F94" s="26" t="n"/>
       <c r="G94" s="23" t="n"/>
+      <c r="H94" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0861</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n">
@@ -24698,6 +25853,11 @@
       <c r="E100" s="25" t="n"/>
       <c r="F100" s="26" t="n"/>
       <c r="G100" s="23" t="n"/>
+      <c r="H100" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0095</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n">
@@ -24911,6 +26071,11 @@
       <c r="E109" s="19" t="n"/>
       <c r="F109" s="21" t="n"/>
       <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0052</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="22" t="n">
@@ -24932,6 +26097,11 @@
       <c r="E110" s="25" t="n"/>
       <c r="F110" s="26" t="n"/>
       <c r="G110" s="23" t="n"/>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0003</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n">
@@ -25123,7 +26293,7 @@
     <col width="14" customWidth="1" style="158" min="4" max="5"/>
     <col width="26" customWidth="1" style="158" min="6" max="6"/>
     <col width="30" customWidth="1" style="158" min="7" max="7"/>
-    <col width="3" customWidth="1" style="158" min="8" max="8"/>
+    <col width="11" customWidth="1" style="158" min="8" max="8"/>
     <col width="32" customWidth="1" style="158" min="9" max="9"/>
     <col width="14" customWidth="1" style="158" min="10" max="10"/>
     <col width="15" customWidth="1" style="158" min="12" max="17"/>
@@ -25186,6 +26356,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="I4" s="224" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -25227,6 +26402,11 @@
       <c r="E5" s="19" t="n"/>
       <c r="F5" s="21" t="n"/>
       <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0864</t>
+        </is>
+      </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Fornecedores / Mercadoria</t>
@@ -25397,6 +26577,11 @@
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
       <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0105</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
@@ -25427,6 +26612,11 @@
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0865</t>
+        </is>
+      </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Salários, Comissões e Encargos</t>
@@ -25491,6 +26681,11 @@
       <c r="E13" s="19" t="n"/>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0169</t>
+        </is>
+      </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Manutenção e Reparos</t>
@@ -25750,6 +26945,11 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
       <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0228</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -25792,6 +26992,11 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
       <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0877</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -25813,6 +27018,11 @@
       <c r="E25" s="19" t="n"/>
       <c r="F25" s="21" t="n"/>
       <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0870</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="n">
@@ -25880,6 +27090,11 @@
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="26" t="n"/>
       <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0079</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
@@ -25901,6 +27116,11 @@
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="21" t="n"/>
       <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="n">
@@ -25964,6 +27184,11 @@
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="26" t="n"/>
       <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0871</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
@@ -26006,6 +27231,11 @@
       <c r="E34" s="25" t="n"/>
       <c r="F34" s="26" t="n"/>
       <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0078</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
@@ -26048,6 +27278,11 @@
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="26" t="n"/>
       <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0241</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -26244,6 +27479,11 @@
       <c r="E44" s="25" t="n"/>
       <c r="F44" s="26" t="n"/>
       <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0161</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -26265,6 +27505,11 @@
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="21" t="n"/>
       <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0873</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="n">
@@ -26328,6 +27573,11 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
       <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0875</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -26370,6 +27620,11 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
       <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0160</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -26437,6 +27692,11 @@
       <c r="E53" s="19" t="n"/>
       <c r="F53" s="21" t="n"/>
       <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0878</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="n">
@@ -26479,6 +27739,11 @@
       <c r="E55" s="19" t="n"/>
       <c r="F55" s="21" t="n"/>
       <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0879</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="n">
@@ -26542,6 +27807,11 @@
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
       <c r="G58" s="23" t="n"/>
+      <c r="H58" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0178</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -26563,6 +27833,11 @@
       <c r="E59" s="19" t="n"/>
       <c r="F59" s="21" t="n"/>
       <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0178</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="n">
@@ -26634,6 +27909,11 @@
       <c r="E62" s="25" t="n"/>
       <c r="F62" s="26" t="n"/>
       <c r="G62" s="23" t="n"/>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0145</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n">
@@ -26826,6 +28106,11 @@
       <c r="E70" s="25" t="n"/>
       <c r="F70" s="26" t="n"/>
       <c r="G70" s="23" t="n"/>
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0881</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -26931,6 +28216,11 @@
       <c r="E75" s="19" t="n"/>
       <c r="F75" s="21" t="n"/>
       <c r="G75" s="18" t="n"/>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0061</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="22" t="n">
@@ -26998,6 +28288,11 @@
       <c r="E78" s="25" t="n"/>
       <c r="F78" s="26" t="n"/>
       <c r="G78" s="23" t="n"/>
+      <c r="H78" s="23" t="inlineStr">
+        <is>
+          <t>OUT-0061</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n">
@@ -27111,6 +28406,11 @@
       <c r="E83" s="19" t="n"/>
       <c r="F83" s="21" t="n"/>
       <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0702</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="22" t="n">
@@ -27353,6 +28653,11 @@
       <c r="E93" s="19" t="n"/>
       <c r="F93" s="21" t="n"/>
       <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0026</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="n">
@@ -27374,6 +28679,11 @@
       <c r="E94" s="25" t="n"/>
       <c r="F94" s="26" t="n"/>
       <c r="G94" s="23" t="n"/>
+      <c r="H94" s="23" t="inlineStr">
+        <is>
+          <t>EMP-0077</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n">
@@ -27395,6 +28705,11 @@
       <c r="E95" s="19" t="n"/>
       <c r="F95" s="21" t="n"/>
       <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0036</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="22" t="n">
@@ -27462,6 +28777,11 @@
       <c r="E98" s="25" t="n"/>
       <c r="F98" s="26" t="n"/>
       <c r="G98" s="23" t="n"/>
+      <c r="H98" s="23" t="inlineStr">
+        <is>
+          <t>CLI-0513</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
@@ -27709,6 +29029,11 @@
       <c r="E109" s="19" t="n"/>
       <c r="F109" s="21" t="n"/>
       <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0435</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="22" t="n">
@@ -29048,7 +30373,7 @@
     <col width="14" customWidth="1" style="158" min="7" max="7"/>
     <col width="26" customWidth="1" style="158" min="8" max="8"/>
     <col width="30" customWidth="1" style="158" min="9" max="9"/>
-    <col width="3" customWidth="1" style="158" min="10" max="10"/>
+    <col width="11" customWidth="1" style="158" min="10" max="10"/>
     <col width="30" customWidth="1" style="158" min="11" max="11"/>
     <col width="14" customWidth="1" style="158" min="12" max="13"/>
     <col width="3" customWidth="1" style="158" min="13" max="13"/>
@@ -29129,6 +30454,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="K4" s="235" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -29184,6 +30514,11 @@
       <c r="G5" s="19" t="n"/>
       <c r="H5" s="21" t="n"/>
       <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0058</t>
+        </is>
+      </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Fornecedores / Mercadoria</t>
@@ -29478,6 +30813,11 @@
       <c r="G13" s="19" t="n"/>
       <c r="H13" s="21" t="n"/>
       <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0207</t>
+        </is>
+      </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Manutenção e Reparos</t>
@@ -29610,6 +30950,11 @@
       <c r="G17" s="19" t="n"/>
       <c r="H17" s="21" t="n"/>
       <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0016</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Pro Labore Edilânia</t>
@@ -29646,6 +30991,11 @@
       <c r="G18" s="48" t="n"/>
       <c r="H18" s="49" t="n"/>
       <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0018</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -29714,6 +31064,11 @@
       <c r="G20" s="48" t="n"/>
       <c r="H20" s="49" t="n"/>
       <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0295</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -29745,6 +31100,11 @@
           <t>Pago via Pix em 13/08/2026 (venda de 05/08)</t>
         </is>
       </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0225</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="44" t="n">
@@ -29772,6 +31132,11 @@
       <c r="G22" s="48" t="n"/>
       <c r="H22" s="49" t="n"/>
       <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0017</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -29799,6 +31164,11 @@
       <c r="G23" s="19" t="n"/>
       <c r="H23" s="21" t="n"/>
       <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0147</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="44" t="n">
@@ -29830,6 +31200,11 @@
       <c r="I24" s="45" t="inlineStr">
         <is>
           <t>Venda de 05/08/2026 — pagamento recebido em 20/08/2026</t>
+        </is>
+      </c>
+      <c r="J24" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0401</t>
         </is>
       </c>
     </row>
@@ -29859,6 +31234,11 @@
       <c r="G25" s="19" t="n"/>
       <c r="H25" s="21" t="n"/>
       <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0277</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="44" t="n">
@@ -29886,6 +31266,11 @@
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
       <c r="I26" s="45" t="n"/>
+      <c r="J26" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -29913,6 +31298,11 @@
       <c r="G27" s="19" t="n"/>
       <c r="H27" s="21" t="n"/>
       <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0501</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="44" t="n">
@@ -29940,6 +31330,11 @@
       <c r="G28" s="48" t="n"/>
       <c r="H28" s="49" t="n"/>
       <c r="I28" s="45" t="n"/>
+      <c r="J28" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0004</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="158">
       <c r="A29" s="17" t="n">
@@ -29967,6 +31362,11 @@
       <c r="G29" s="19" t="n"/>
       <c r="H29" s="21" t="n"/>
       <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0303</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="44" t="n">
@@ -30117,6 +31517,11 @@
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="21" t="n"/>
       <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0259</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="44" t="n">
@@ -30271,6 +31676,11 @@
       <c r="G41" s="19" t="n"/>
       <c r="H41" s="21" t="n"/>
       <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0433</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="158">
       <c r="A42" s="44" t="n">
@@ -30302,6 +31712,11 @@
           <t>Venda de 10/08/2026 — pagamento recebido em 17/08/2026</t>
         </is>
       </c>
+      <c r="J42" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0216</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
@@ -30333,6 +31748,11 @@
           <t>Venda de 10/08/2026 — pagamento recebido em 20/08/2026</t>
         </is>
       </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0073</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="44" t="n">
@@ -30414,6 +31834,11 @@
       <c r="I46" s="45" t="inlineStr">
         <is>
           <t>Pago via Pix em 11/08/2026 (venda de 10/08)</t>
+        </is>
+      </c>
+      <c r="J46" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0165</t>
         </is>
       </c>
     </row>
@@ -30493,6 +31918,11 @@
           <t>Venda de 11/08/2026 — pagamento recebido em 20/08/2026</t>
         </is>
       </c>
+      <c r="J49" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0073</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="44" t="n">
@@ -30522,6 +31952,11 @@
       <c r="G50" s="48" t="n"/>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="45" t="n"/>
+      <c r="J50" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0222</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -30549,6 +31984,11 @@
       <c r="G51" s="19" t="n"/>
       <c r="H51" s="21" t="n"/>
       <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0231</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="44" t="n">
@@ -30603,6 +32043,11 @@
           <t>Venda de 11/08/2026 — pagamento recebido em 25/08/2026 via TED. NF conferida: 3x Refil Original Everest (R$420) + Refil Pro Life Especial OC (R$140) + 3x Pré Filtro (R$180) + Válvula Reguladora de Pressão Soft (R$80) = R$820, faltava a válvula no lançamento original</t>
         </is>
       </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0296</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="44" t="n">
@@ -30632,6 +32077,11 @@
       <c r="G54" s="48" t="n"/>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="45" t="n"/>
+      <c r="J54" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0454</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
@@ -30661,6 +32111,11 @@
       <c r="I55" s="18" t="inlineStr">
         <is>
           <t>Venda de 11/08/2026 — pagamento recebido em 19/08/2026</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0085</t>
         </is>
       </c>
     </row>
@@ -30828,6 +32283,11 @@
       <c r="G62" s="48" t="n"/>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="45" t="n"/>
+      <c r="J62" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0023</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="158">
       <c r="A63" s="17" t="n">
@@ -30907,6 +32367,11 @@
       <c r="G65" s="19" t="n"/>
       <c r="H65" s="21" t="n"/>
       <c r="I65" s="18" t="n"/>
+      <c r="J65" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0024</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="44" t="n">
@@ -30938,6 +32403,11 @@
           <t>Venda de 13/08/2026 — pagamento recebido em 20/08/2026 (desconto de R$ 10,00)</t>
         </is>
       </c>
+      <c r="J66" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0018</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -30965,6 +32435,11 @@
       <c r="G67" s="19" t="n"/>
       <c r="H67" s="21" t="n"/>
       <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0216</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="44" t="n">
@@ -31052,6 +32527,11 @@
       <c r="G70" s="48" t="n"/>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="45" t="n"/>
+      <c r="J70" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0051</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -31081,6 +32561,11 @@
       <c r="G71" s="19" t="n"/>
       <c r="H71" s="21" t="n"/>
       <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0450</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="44" t="n">
@@ -31141,6 +32626,11 @@
       <c r="G73" s="19" t="n"/>
       <c r="H73" s="21" t="n"/>
       <c r="I73" s="18" t="n"/>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0401</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="44" t="n">
@@ -31168,6 +32658,11 @@
       <c r="G74" s="48" t="n"/>
       <c r="H74" s="49" t="n"/>
       <c r="I74" s="45" t="n"/>
+      <c r="J74" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0401</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -31195,6 +32690,11 @@
       <c r="G75" s="19" t="n"/>
       <c r="H75" s="21" t="n"/>
       <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0731</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="44" t="n">
@@ -31439,6 +32939,11 @@
       <c r="G85" s="19" t="n"/>
       <c r="H85" s="21" t="n"/>
       <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0054</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="44" t="n">
@@ -31466,6 +32971,11 @@
       <c r="G86" s="48" t="n"/>
       <c r="H86" s="49" t="n"/>
       <c r="I86" s="45" t="n"/>
+      <c r="J86" s="45" t="inlineStr">
+        <is>
+          <t>OUT-0078</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -31495,6 +33005,11 @@
       <c r="G87" s="19" t="n"/>
       <c r="H87" s="21" t="n"/>
       <c r="I87" s="18" t="n"/>
+      <c r="J87" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0016</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="44" t="n">
@@ -31551,6 +33066,11 @@
       <c r="G89" s="19" t="n"/>
       <c r="H89" s="21" t="n"/>
       <c r="I89" s="18" t="n"/>
+      <c r="J89" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0362</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="44" t="n">
@@ -31582,6 +33102,11 @@
       <c r="I90" s="45" t="inlineStr">
         <is>
           <t>Venda de 19/08/2026 — pagamento recebido em 20/08/2026 (crédito 3x)</t>
+        </is>
+      </c>
+      <c r="J90" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0211</t>
         </is>
       </c>
     </row>
@@ -31611,6 +33136,11 @@
       <c r="G91" s="19" t="n"/>
       <c r="H91" s="21" t="n"/>
       <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0263</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="44" t="n">
@@ -31711,6 +33241,11 @@
       <c r="G95" s="19" t="n"/>
       <c r="H95" s="21" t="n"/>
       <c r="I95" s="18" t="n"/>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0120</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="44" t="n">
@@ -31738,6 +33273,11 @@
       <c r="G96" s="48" t="n"/>
       <c r="H96" s="49" t="n"/>
       <c r="I96" s="45" t="n"/>
+      <c r="J96" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0309</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -31788,6 +33328,11 @@
       <c r="G98" s="48" t="n"/>
       <c r="H98" s="49" t="n"/>
       <c r="I98" s="45" t="n"/>
+      <c r="J98" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
@@ -31840,6 +33385,11 @@
       <c r="G100" s="48" t="n"/>
       <c r="H100" s="49" t="n"/>
       <c r="I100" s="45" t="n"/>
+      <c r="J100" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0885</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n">
@@ -31898,6 +33448,11 @@
       <c r="G102" s="48" t="n"/>
       <c r="H102" s="49" t="n"/>
       <c r="I102" s="45" t="n"/>
+      <c r="J102" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0219</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
@@ -31927,6 +33482,11 @@
       <c r="G103" s="19" t="n"/>
       <c r="H103" s="21" t="n"/>
       <c r="I103" s="18" t="n"/>
+      <c r="J103" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0268</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="158">
       <c r="A104" s="44" t="n">
@@ -32037,6 +33597,11 @@
       <c r="G107" s="19" t="n"/>
       <c r="H107" s="21" t="n"/>
       <c r="I107" s="18" t="n"/>
+      <c r="J107" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0887</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="44" t="n">
@@ -32189,6 +33754,11 @@
       <c r="G113" s="19" t="n"/>
       <c r="H113" s="21" t="n"/>
       <c r="I113" s="18" t="n"/>
+      <c r="J113" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0172</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="44" t="n">
@@ -32243,6 +33813,11 @@
       <c r="G115" s="19" t="n"/>
       <c r="H115" s="21" t="n"/>
       <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0310</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="44" t="n">
@@ -32270,6 +33845,11 @@
       <c r="G116" s="48" t="n"/>
       <c r="H116" s="49" t="n"/>
       <c r="I116" s="45" t="n"/>
+      <c r="J116" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0245</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="n">
@@ -33102,6 +34682,11 @@
       <c r="G146" s="47" t="n"/>
       <c r="H146" s="49" t="n"/>
       <c r="I146" s="45" t="n"/>
+      <c r="J146" s="45" t="inlineStr">
+        <is>
+          <t>EMP-0243</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="n">
@@ -33131,6 +34716,11 @@
       <c r="I147" s="18" t="inlineStr">
         <is>
           <t>Venda de 24/08/2026 — pagamento recebido via Pix em 25/08/2026</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0471</t>
         </is>
       </c>
     </row>
@@ -33218,6 +34808,11 @@
           <t>Crédito em 10x</t>
         </is>
       </c>
+      <c r="J150" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0886</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="n">
@@ -33345,6 +34940,11 @@
       <c r="G155" s="20" t="n"/>
       <c r="H155" s="21" t="n"/>
       <c r="I155" s="18" t="n"/>
+      <c r="J155" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0887</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="44" t="n">
@@ -33372,6 +34972,11 @@
       <c r="G156" s="47" t="n"/>
       <c r="H156" s="49" t="n"/>
       <c r="I156" s="45" t="n"/>
+      <c r="J156" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0738</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="17" t="n">
@@ -33772,6 +35377,11 @@
       <c r="G170" s="48" t="n"/>
       <c r="H170" s="49" t="n"/>
       <c r="I170" s="45" t="n"/>
+      <c r="J170" s="45" t="inlineStr">
+        <is>
+          <t>CLI-0449</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="17" t="n">
@@ -33903,6 +35513,11 @@
       <c r="I175" s="18" t="inlineStr">
         <is>
           <t>Crédito em 4x</t>
+        </is>
+      </c>
+      <c r="J175" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0405</t>
         </is>
       </c>
     </row>
@@ -34175,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U129"/>
+  <dimension ref="A1:U131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -34187,7 +35802,7 @@
     <col width="14" customWidth="1" style="158" min="7" max="7"/>
     <col width="26" customWidth="1" style="158" min="8" max="8"/>
     <col width="30" customWidth="1" style="158" min="9" max="9"/>
-    <col width="3" customWidth="1" style="158" min="10" max="10"/>
+    <col width="11" customWidth="1" style="158" min="10" max="10"/>
     <col width="30" customWidth="1" style="158" min="11" max="11"/>
     <col width="14" customWidth="1" style="158" min="12" max="12"/>
     <col width="3" customWidth="1" style="158" min="13" max="13"/>
@@ -34268,6 +35883,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="J4" s="76" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="K4" s="237" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -34324,17 +35944,22 @@
           <t>Grupo Ânima — OC AEMPPO00004359 · NF 000.004.294 de 05/08/2026 · prazo 30 dias · vencimento 04/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 04/09/2026</t>
         </is>
       </c>
+      <c r="J5" s="78" t="inlineStr">
+        <is>
+          <t>ESC-0005</t>
+        </is>
+      </c>
       <c r="K5" s="78" t="inlineStr">
         <is>
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H127,K5,G5:G127)</f>
+        <f>SUMIF(H5:H129,K5,G5:G129)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D128-F128-T5</f>
+        <f>D130-F130-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -34342,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D129</f>
+        <f>D131</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E127,"Aguardando Pagamento",D5:D127)</f>
+        <f>SUMIF(E5:E129,"Aguardando Pagamento",D5:D129)</f>
         <v/>
       </c>
     </row>
@@ -34386,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H127,K6,G5:G127)</f>
+        <f>SUMIF(H5:H129,K6,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34420,13 +36045,18 @@
           <t>Grupo Ânima — OC AEDPO00004751 · NF 000.004.298 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
+      <c r="J7" s="78" t="inlineStr">
+        <is>
+          <t>ESC-0007</t>
+        </is>
+      </c>
       <c r="K7" s="78" t="inlineStr">
         <is>
           <t>Água, Energia e Internet</t>
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H127,K7,G5:G127)</f>
+        <f>SUMIF(H5:H129,K7,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34466,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H127,K8,G5:G127)</f>
+        <f>SUMIF(H5:H129,K8,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34500,13 +36130,18 @@
           <t>Grupo Ânima — OC AEDPO00004743 · NF 000.004.300 de 06/08/2026 · prazo 30 dias · vencimento 05/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 08/09/2026</t>
         </is>
       </c>
+      <c r="J9" s="78" t="inlineStr">
+        <is>
+          <t>ESC-0006</t>
+        </is>
+      </c>
       <c r="K9" s="78" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H127,K9,G5:G127)</f>
+        <f>SUMIF(H5:H129,K9,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34546,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H127,K10,G5:G127)</f>
+        <f>SUMIF(H5:H129,K10,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34586,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H127,K11,G5:G127)</f>
+        <f>SUMIF(H5:H129,K11,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34626,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H127,K12,G5:G127)</f>
+        <f>SUMIF(H5:H129,K12,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34656,13 +36291,18 @@
       <c r="G13" s="79" t="n"/>
       <c r="H13" s="78" t="n"/>
       <c r="I13" s="78" t="n"/>
+      <c r="J13" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0475</t>
+        </is>
+      </c>
       <c r="K13" s="78" t="inlineStr">
         <is>
           <t>Manutenção e Reparos</t>
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H127,K13,G5:G127)</f>
+        <f>SUMIF(H5:H129,K13,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34696,13 +36336,18 @@
           <t>Vendas de 20 e 21/08/2026 (R$ 140,00 + R$ 40,00) — pagamento recebido em 01/09/2026 com desconto de R$ 10,00</t>
         </is>
       </c>
+      <c r="J14" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0014</t>
+        </is>
+      </c>
       <c r="K14" s="78" t="inlineStr">
         <is>
           <t>Material de Limpeza e Escritório</t>
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H127,K14,G5:G127)</f>
+        <f>SUMIF(H5:H129,K14,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34736,13 +36381,18 @@
           <t>Venda de 01/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
         </is>
       </c>
+      <c r="J15" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0014</t>
+        </is>
+      </c>
       <c r="K15" s="78" t="inlineStr">
         <is>
           <t>Estornos de Vendas (Cancelamentos)</t>
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H127,K15,G5:G127)</f>
+        <f>SUMIF(H5:H129,K15,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34772,13 +36422,18 @@
       <c r="G16" s="83" t="n"/>
       <c r="H16" s="82" t="n"/>
       <c r="I16" s="82" t="n"/>
+      <c r="J16" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0460</t>
+        </is>
+      </c>
       <c r="K16" s="78" t="inlineStr">
         <is>
           <t>Outras Despesas</t>
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H127,K16,G5:G127)</f>
+        <f>SUMIF(H5:H129,K16,G5:G129)</f>
         <v/>
       </c>
     </row>
@@ -34812,6 +36467,11 @@
           <t>Venda de 01/09/2026 — pagamento recebido em 02/09/2026</t>
         </is>
       </c>
+      <c r="J17" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0465</t>
+        </is>
+      </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
           <t>Pro Labore Edilânia</t>
@@ -34848,6 +36508,11 @@
       <c r="G18" s="83" t="n"/>
       <c r="H18" s="82" t="n"/>
       <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0311</t>
+        </is>
+      </c>
       <c r="K18" s="86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -34886,6 +36551,11 @@
       <c r="G19" s="79" t="n"/>
       <c r="H19" s="78" t="n"/>
       <c r="I19" s="78" t="n"/>
+      <c r="J19" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0472</t>
+        </is>
+      </c>
       <c r="K19" s="88" t="inlineStr">
         <is>
           <t>Capital de Giro (BB) — ainda a devolver</t>
@@ -34922,6 +36592,11 @@
       <c r="G20" s="83" t="n"/>
       <c r="H20" s="82" t="n"/>
       <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="77" t="n">
@@ -34949,6 +36624,11 @@
       <c r="G21" s="79" t="n"/>
       <c r="H21" s="78" t="n"/>
       <c r="I21" s="78" t="n"/>
+      <c r="J21" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0482</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="81" t="n">
@@ -35026,6 +36706,11 @@
       <c r="G24" s="83" t="n"/>
       <c r="H24" s="82" t="n"/>
       <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0289</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="77" t="n">
@@ -35053,6 +36738,11 @@
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="78" t="n"/>
       <c r="I25" s="78" t="n"/>
+      <c r="J25" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0196</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="81" t="n">
@@ -35084,6 +36774,11 @@
       <c r="I26" s="82" t="inlineStr">
         <is>
           <t>Crédito em 5x</t>
+        </is>
+      </c>
+      <c r="J26" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0888</t>
         </is>
       </c>
     </row>
@@ -35117,6 +36812,11 @@
           <t>Venda de 02/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
         </is>
       </c>
+      <c r="J27" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0473</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="81" t="n">
@@ -35148,6 +36848,11 @@
       <c r="I28" s="82" t="inlineStr">
         <is>
           <t>Crédito em 3x</t>
+        </is>
+      </c>
+      <c r="J28" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0064</t>
         </is>
       </c>
     </row>
@@ -35177,6 +36882,11 @@
       <c r="G29" s="79" t="n"/>
       <c r="H29" s="78" t="n"/>
       <c r="I29" s="78" t="n"/>
+      <c r="J29" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0452</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="81" t="n">
@@ -35206,6 +36916,11 @@
       <c r="I30" s="82" t="inlineStr">
         <is>
           <t>Venda de 03/09/2026 — pagamento recebido via Pix em 04/09/2026</t>
+        </is>
+      </c>
+      <c r="J30" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0483</t>
         </is>
       </c>
     </row>
@@ -35289,6 +37004,11 @@
           <t>Venda de 17/08/2026 — pagamento recebido em 02/09/2026 via TED</t>
         </is>
       </c>
+      <c r="J33" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0156</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="81" t="n">
@@ -35320,6 +37040,11 @@
           <t>Venda de 31/08/2026 — pagamento recebido em 01/09/2026 via Pix (Sindicato dos Mineiros de Jacobina)</t>
         </is>
       </c>
+      <c r="J34" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0179</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="77" t="n">
@@ -35349,6 +37074,11 @@
       <c r="I35" s="78" t="inlineStr">
         <is>
           <t>Venda de 31/08/2026 — pagamento recebido em 03/09/2026 via Pix</t>
+        </is>
+      </c>
+      <c r="J35" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0133</t>
         </is>
       </c>
     </row>
@@ -35492,6 +37222,11 @@
           <t>Venda de 27/08/2026 — pagamento recebido em dinheiro em 03/09/2026</t>
         </is>
       </c>
+      <c r="J40" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0494</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="77" t="n">
@@ -35519,6 +37254,11 @@
       <c r="G41" s="79" t="n"/>
       <c r="H41" s="78" t="n"/>
       <c r="I41" s="78" t="n"/>
+      <c r="J41" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0312</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="81" t="n">
@@ -35546,6 +37286,11 @@
           <t>Permuta: purificador entregue em troca de divulgação no Instagram (instalação em 02/09/2026). Sem entrada em caixa — valor de tabela do aparelho R$ 1.366,00.</t>
         </is>
       </c>
+      <c r="J42" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0844</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="77" t="n">
@@ -35573,6 +37318,11 @@
       <c r="G43" s="79" t="n"/>
       <c r="H43" s="78" t="n"/>
       <c r="I43" s="78" t="n"/>
+      <c r="J43" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0313</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="81" t="n">
@@ -35600,6 +37350,11 @@
       <c r="G44" s="83" t="n"/>
       <c r="H44" s="82" t="n"/>
       <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0889</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="77" t="n">
@@ -35627,6 +37382,11 @@
       <c r="G45" s="79" t="n"/>
       <c r="H45" s="78" t="n"/>
       <c r="I45" s="78" t="n"/>
+      <c r="J45" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0630</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="81" t="n">
@@ -35654,6 +37414,11 @@
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="82" t="n"/>
       <c r="I46" s="82" t="n"/>
+      <c r="J46" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0419</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="77" t="n">
@@ -35685,6 +37450,11 @@
           <t>Venda de 04/09/2026 — pagamento recebido via Pix em 10/09/2026</t>
         </is>
       </c>
+      <c r="J47" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0508</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="81" t="n">
@@ -35712,6 +37482,11 @@
       <c r="G48" s="83" t="n"/>
       <c r="H48" s="82" t="n"/>
       <c r="I48" s="82" t="n"/>
+      <c r="J48" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0035</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="77" t="n">
@@ -35795,6 +37570,11 @@
       <c r="I51" s="78" t="inlineStr">
         <is>
           <t>Venda de 31/08/2026 — pagamento recebido via Pix em 08/09/2026</t>
+        </is>
+      </c>
+      <c r="J51" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0183</t>
         </is>
       </c>
     </row>
@@ -35853,6 +37633,11 @@
           <t>Crédito em 10x</t>
         </is>
       </c>
+      <c r="J53" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0890</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="81" t="n">
@@ -35880,6 +37665,11 @@
       <c r="G54" s="83" t="n"/>
       <c r="H54" s="82" t="n"/>
       <c r="I54" s="82" t="n"/>
+      <c r="J54" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0441</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="77" t="n">
@@ -35907,6 +37697,11 @@
       <c r="G55" s="79" t="n"/>
       <c r="H55" s="78" t="n"/>
       <c r="I55" s="78" t="n"/>
+      <c r="J55" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0314</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="81" t="n">
@@ -35971,6 +37766,11 @@
           <t>Venda de 24/08/2026 — pagamento recebido em dinheiro em 08/09/2026</t>
         </is>
       </c>
+      <c r="J57" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="81" t="n">
@@ -35998,6 +37798,11 @@
       <c r="G58" s="83" t="n"/>
       <c r="H58" s="82" t="n"/>
       <c r="I58" s="82" t="n"/>
+      <c r="J58" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="77" t="n">
@@ -36052,6 +37857,11 @@
       <c r="G60" s="83" t="n"/>
       <c r="H60" s="82" t="n"/>
       <c r="I60" s="82" t="n"/>
+      <c r="J60" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0055</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="77" t="n">
@@ -36162,6 +37972,11 @@
       <c r="G64" s="83" t="n"/>
       <c r="H64" s="82" t="n"/>
       <c r="I64" s="82" t="n"/>
+      <c r="J64" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0492</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="77" t="n">
@@ -36189,6 +38004,11 @@
       <c r="G65" s="79" t="n"/>
       <c r="H65" s="78" t="n"/>
       <c r="I65" s="78" t="n"/>
+      <c r="J65" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0891</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="81" t="n">
@@ -36216,6 +38036,11 @@
       <c r="G66" s="83" t="n"/>
       <c r="H66" s="82" t="n"/>
       <c r="I66" s="82" t="n"/>
+      <c r="J66" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0188</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="77" t="n">
@@ -36320,6 +38145,11 @@
       <c r="G70" s="83" t="n"/>
       <c r="H70" s="82" t="n"/>
       <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0424</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="77" t="n">
@@ -36347,6 +38177,11 @@
       <c r="G71" s="79" t="n"/>
       <c r="H71" s="78" t="n"/>
       <c r="I71" s="78" t="n"/>
+      <c r="J71" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0262</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="81" t="n">
@@ -36374,6 +38209,11 @@
       <c r="G72" s="83" t="n"/>
       <c r="H72" s="82" t="n"/>
       <c r="I72" s="82" t="n"/>
+      <c r="J72" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0055</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="77" t="n">
@@ -36401,6 +38241,11 @@
       <c r="G73" s="79" t="n"/>
       <c r="H73" s="78" t="n"/>
       <c r="I73" s="78" t="n"/>
+      <c r="J73" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0892</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="81" t="n">
@@ -36594,6 +38439,11 @@
           <t>Crédito em 2x</t>
         </is>
       </c>
+      <c r="J80" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0493</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="77" t="n">
@@ -36654,6 +38504,11 @@
           <t>Venda de 10/09/2026 — pagamento recebido via Pix em 11/09/2026</t>
         </is>
       </c>
+      <c r="J82" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0801</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="77" t="n">
@@ -36685,6 +38540,11 @@
           <t>Venda de 10/09/2026 — pagamento recebido via Pix em 11/09/2026</t>
         </is>
       </c>
+      <c r="J83" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0251</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="81" t="n">
@@ -36712,6 +38572,11 @@
       <c r="G84" s="83" t="n"/>
       <c r="H84" s="82" t="n"/>
       <c r="I84" s="82" t="n"/>
+      <c r="J84" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0291</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="77" t="n">
@@ -36743,6 +38608,11 @@
           <t>Venda de 11/09/2026 — pagamento recebido via Pix em 14/09/2026</t>
         </is>
       </c>
+      <c r="J85" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0294</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="81" t="n">
@@ -36770,6 +38640,11 @@
       <c r="G86" s="83" t="n"/>
       <c r="H86" s="82" t="n"/>
       <c r="I86" s="82" t="n"/>
+      <c r="J86" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0206</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="77" t="n">
@@ -36974,6 +38849,11 @@
       <c r="G94" s="83" t="n"/>
       <c r="H94" s="82" t="n"/>
       <c r="I94" s="82" t="n"/>
+      <c r="J94" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0185</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="77" t="n">
@@ -37090,6 +38970,11 @@
       <c r="I98" s="82" t="inlineStr">
         <is>
           <t>Crédito em 4x</t>
+        </is>
+      </c>
+      <c r="J98" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0337</t>
         </is>
       </c>
     </row>
@@ -37416,6 +39301,11 @@
       <c r="G110" s="83" t="n"/>
       <c r="H110" s="82" t="n"/>
       <c r="I110" s="82" t="n"/>
+      <c r="J110" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0127</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="77" t="n">
@@ -37443,6 +39333,11 @@
       <c r="G111" s="79" t="n"/>
       <c r="H111" s="78" t="n"/>
       <c r="I111" s="78" t="n"/>
+      <c r="J111" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0456</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="81" t="n">
@@ -37474,6 +39369,11 @@
       <c r="I112" s="82" t="inlineStr">
         <is>
           <t>Crédito em 3x</t>
+        </is>
+      </c>
+      <c r="J112" s="82" t="inlineStr">
+        <is>
+          <t>CLI-0502</t>
         </is>
       </c>
     </row>
@@ -37507,6 +39407,11 @@
           <t>Instalação feita em 15/09/2026.</t>
         </is>
       </c>
+      <c r="J113" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0018</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="81" t="n">
@@ -37592,6 +39497,11 @@
       <c r="G116" s="83" t="n"/>
       <c r="H116" s="82" t="n"/>
       <c r="I116" s="82" t="n"/>
+      <c r="J116" s="82" t="inlineStr">
+        <is>
+          <t>EMP-0090</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="77" t="n">
@@ -37619,6 +39529,11 @@
       <c r="G117" s="79" t="n"/>
       <c r="H117" s="78" t="n"/>
       <c r="I117" s="78" t="n"/>
+      <c r="J117" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0315</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="81" t="n">
@@ -37723,6 +39638,11 @@
       <c r="G121" s="79" t="n"/>
       <c r="H121" s="78" t="n"/>
       <c r="I121" s="78" t="n"/>
+      <c r="J121" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0893</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="81" t="n">
@@ -37885,45 +39805,116 @@
       <c r="G127" s="79" t="n"/>
       <c r="H127" s="78" t="n"/>
       <c r="I127" s="78" t="n"/>
+      <c r="J127" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0061</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="29" t="n"/>
-      <c r="B128" s="43" t="inlineStr">
+      <c r="A128" s="81" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B128" s="82" t="inlineStr">
+        <is>
+          <t>Instituição Adventista Nordeste Brasileiro</t>
+        </is>
+      </c>
+      <c r="C128" s="82" t="inlineStr">
+        <is>
+          <t>Torneira para Bebedouro Industrial</t>
+        </is>
+      </c>
+      <c r="D128" s="83" t="n">
+        <v>60</v>
+      </c>
+      <c r="E128" s="82" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F128" s="83" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G128" s="83" t="n"/>
+      <c r="H128" s="82" t="n"/>
+      <c r="I128" s="82" t="n"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>ESC-0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="77" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B129" s="78" t="inlineStr">
+        <is>
+          <t>Julia Ribeiro Bezerra Santos</t>
+        </is>
+      </c>
+      <c r="C129" s="78" t="inlineStr">
+        <is>
+          <t>Refil FPA14</t>
+        </is>
+      </c>
+      <c r="D129" s="79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E129" s="78" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F129" s="79" t="n"/>
+      <c r="G129" s="79" t="n"/>
+      <c r="H129" s="78" t="n"/>
+      <c r="I129" s="78" t="n"/>
+      <c r="J129" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0894</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="29" t="n"/>
+      <c r="B130" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C128" s="161" t="n"/>
-      <c r="D128" s="8">
-        <f>SUM(D5:D127)</f>
-        <v/>
-      </c>
-      <c r="E128" s="8" t="n"/>
-      <c r="F128" s="29">
-        <f>SUM(F5:F127)</f>
-        <v/>
-      </c>
-      <c r="G128" s="8">
-        <f>SUM(G5:G127)</f>
-        <v/>
-      </c>
-      <c r="H128" s="29" t="n"/>
-      <c r="I128" s="29" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="30" t="n"/>
-      <c r="B129" s="135" t="inlineStr">
+      <c r="C130" s="161" t="n"/>
+      <c r="D130" s="8">
+        <f>SUM(D5:D129)</f>
+        <v/>
+      </c>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="29">
+        <f>SUM(F5:F129)</f>
+        <v/>
+      </c>
+      <c r="G130" s="8">
+        <f>SUM(G5:G129)</f>
+        <v/>
+      </c>
+      <c r="H130" s="29" t="n"/>
+      <c r="I130" s="29" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="30" t="n"/>
+      <c r="B131" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D129" s="134">
-        <f>(D128-F128-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F129" s="30" t="n"/>
-      <c r="H129" s="30" t="n"/>
-      <c r="I129" s="30" t="n"/>
+      <c r="D131" s="134">
+        <f>(D130-F130-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F131" s="30" t="n"/>
+      <c r="H131" s="30" t="n"/>
+      <c r="I131" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -37940,10 +39931,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -37973,7 +39964,7 @@
     <col width="14" customWidth="1" style="158" min="7" max="7"/>
     <col width="26" customWidth="1" style="158" min="8" max="8"/>
     <col width="30" customWidth="1" style="158" min="9" max="9"/>
-    <col width="3" customWidth="1" style="158" min="10" max="10"/>
+    <col width="11" customWidth="1" style="158" min="10" max="10"/>
     <col width="30" customWidth="1" style="158" min="11" max="11"/>
     <col width="14" customWidth="1" style="158" min="12" max="12"/>
     <col width="3" customWidth="1" style="158" min="13" max="13"/>
@@ -38054,6 +40045,11 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="J4" s="76" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
+        </is>
+      </c>
       <c r="K4" s="237" t="inlineStr">
         <is>
           <t>Saídas por Categoria</t>
@@ -38108,6 +40104,11 @@
       <c r="I5" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — OC AEMPPO00004453 · NF 000.004.332 de 26/08/2026 · prazo 45 dias · vencimento 10/10/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="78" t="inlineStr">
+        <is>
+          <t>ESC-0008</t>
         </is>
       </c>
       <c r="K5" s="78" t="inlineStr">
@@ -38891,7 +40892,7 @@
     <col width="14" customWidth="1" style="158" min="7" max="7"/>
     <col width="26" customWidth="1" style="158" min="8" max="8"/>
     <col width="30" customWidth="1" style="158" min="9" max="9"/>
-    <col width="3" customWidth="1" style="158" min="10" max="10"/>
+    <col width="11" customWidth="1" style="158" min="10" max="10"/>
     <col width="30" customWidth="1" style="158" min="11" max="11"/>
     <col width="14" customWidth="1" style="158" min="12" max="12"/>
     <col width="3" customWidth="1" style="158" min="13" max="13"/>
@@ -38970,6 +40971,11 @@
       <c r="I4" s="76" t="inlineStr">
         <is>
           <t>Observações</t>
+        </is>
+      </c>
+      <c r="J4" s="76" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
         </is>
       </c>
       <c r="K4" s="237" t="inlineStr">
@@ -39789,7 +41795,7 @@
     <col width="14" customWidth="1" style="158" min="7" max="7"/>
     <col width="26" customWidth="1" style="158" min="8" max="8"/>
     <col width="30" customWidth="1" style="158" min="9" max="9"/>
-    <col width="3" customWidth="1" style="158" min="10" max="10"/>
+    <col width="11" customWidth="1" style="158" min="10" max="10"/>
     <col width="30" customWidth="1" style="158" min="11" max="11"/>
     <col width="14" customWidth="1" style="158" min="12" max="12"/>
     <col width="3" customWidth="1" style="158" min="13" max="13"/>
@@ -39868,6 +41874,11 @@
       <c r="I4" s="76" t="inlineStr">
         <is>
           <t>Observações</t>
+        </is>
+      </c>
+      <c r="J4" s="76" t="inlineStr">
+        <is>
+          <t>ID Cliente</t>
         </is>
       </c>
       <c r="K4" s="237" t="inlineStr">
@@ -44175,7 +46186,6 @@
       <c r="F69" s="116" t="n"/>
       <c r="G69" s="86" t="n"/>
     </row>
-    <row r="70"/>
     <row r="71" ht="15.75" customHeight="1" s="158"/>
     <row r="72">
       <c r="A72" s="206" t="inlineStr">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -35790,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U131"/>
+  <dimension ref="A1:U134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +35955,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H129,K5,G5:G129)</f>
+        <f>SUMIF(H5:H132,K5,G5:G132)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D130-F130-T5</f>
+        <f>D133-F133-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D131</f>
+        <f>D134</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E129,"Aguardando Pagamento",D5:D129)</f>
+        <f>SUMIF(E5:E132,"Aguardando Pagamento",D5:D132)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H129,K6,G5:G129)</f>
+        <f>SUMIF(H5:H132,K6,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36056,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H129,K7,G5:G129)</f>
+        <f>SUMIF(H5:H132,K7,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H129,K8,G5:G129)</f>
+        <f>SUMIF(H5:H132,K8,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H129,K9,G5:G129)</f>
+        <f>SUMIF(H5:H132,K9,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H129,K10,G5:G129)</f>
+        <f>SUMIF(H5:H132,K10,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H129,K11,G5:G129)</f>
+        <f>SUMIF(H5:H132,K11,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H129,K12,G5:G129)</f>
+        <f>SUMIF(H5:H132,K12,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H129,K13,G5:G129)</f>
+        <f>SUMIF(H5:H132,K13,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H129,K14,G5:G129)</f>
+        <f>SUMIF(H5:H132,K14,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H129,K15,G5:G129)</f>
+        <f>SUMIF(H5:H132,K15,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H129,K16,G5:G129)</f>
+        <f>SUMIF(H5:H132,K16,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H124,K17,G5:G124)</f>
+        <f>SUMIF(H5:H132,K17,G5:G132)</f>
         <v/>
       </c>
     </row>
@@ -39878,43 +39878,139 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="29" t="n"/>
-      <c r="B130" s="43" t="inlineStr">
+      <c r="A130" s="81" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B130" s="82" t="inlineStr">
+        <is>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+        </is>
+      </c>
+      <c r="C130" s="82" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="D130" s="83" t="n">
+        <v>30</v>
+      </c>
+      <c r="E130" s="82" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F130" s="83" t="n"/>
+      <c r="G130" s="83" t="n"/>
+      <c r="H130" s="82" t="n"/>
+      <c r="I130" s="82" t="n"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>EMP-0251</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B131" s="78" t="inlineStr">
+        <is>
+          <t>Salão de Beleza - Tauana Naiara Matos - Pura Beleza</t>
+        </is>
+      </c>
+      <c r="C131" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D131" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="E131" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F131" s="79" t="n"/>
+      <c r="G131" s="79" t="n"/>
+      <c r="H131" s="78" t="n"/>
+      <c r="I131" s="78" t="n"/>
+      <c r="J131" s="78" t="inlineStr">
+        <is>
+          <t>EMP-0267</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="81" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B132" s="82" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="C132" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D132" s="83" t="n">
+        <v>200</v>
+      </c>
+      <c r="E132" s="82" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F132" s="83" t="n"/>
+      <c r="G132" s="83" t="n"/>
+      <c r="H132" s="82" t="n"/>
+      <c r="I132" s="82" t="n"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>CLI-0388</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="29" t="n"/>
+      <c r="B133" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C130" s="161" t="n"/>
-      <c r="D130" s="8">
-        <f>SUM(D5:D129)</f>
-        <v/>
-      </c>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="29">
-        <f>SUM(F5:F129)</f>
-        <v/>
-      </c>
-      <c r="G130" s="8">
-        <f>SUM(G5:G129)</f>
-        <v/>
-      </c>
-      <c r="H130" s="29" t="n"/>
-      <c r="I130" s="29" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="30" t="n"/>
-      <c r="B131" s="135" t="inlineStr">
+      <c r="C133" s="161" t="n"/>
+      <c r="D133" s="8">
+        <f>SUM(D5:D132)</f>
+        <v/>
+      </c>
+      <c r="E133" s="8" t="n"/>
+      <c r="F133" s="29">
+        <f>SUM(F5:F132)</f>
+        <v/>
+      </c>
+      <c r="G133" s="8">
+        <f>SUM(G5:G132)</f>
+        <v/>
+      </c>
+      <c r="H133" s="29" t="n"/>
+      <c r="I133" s="29" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="n"/>
+      <c r="B134" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D131" s="134">
-        <f>(D130-F130-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F131" s="30" t="n"/>
-      <c r="H131" s="30" t="n"/>
-      <c r="I131" s="30" t="n"/>
+      <c r="D134" s="134">
+        <f>(D133-F133-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F134" s="30" t="n"/>
+      <c r="H134" s="30" t="n"/>
+      <c r="I134" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -39931,10 +40027,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -44239,7 +44335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -47382,7 +47478,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" s="158">
       <c r="A111" s="78" t="inlineStr">
         <is>
           <t>J Diesel Motores e Reparos - Gilmara</t>
@@ -47414,7 +47510,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" s="158">
       <c r="A112" s="78" t="inlineStr">
         <is>
           <t>IOB</t>
@@ -47446,38 +47542,102 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="86" t="inlineStr">
+    <row r="113" s="158">
+      <c r="A113" s="78" t="inlineStr">
+        <is>
+          <t>Clínica Santa Cecília</t>
+        </is>
+      </c>
+      <c r="B113" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Termostato</t>
+        </is>
+      </c>
+      <c r="C113" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D113" s="79" t="n">
+        <v>310</v>
+      </c>
+      <c r="E113" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F113" s="112">
+        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" s="158">
+      <c r="A114" s="78" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="B114" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C114" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D114" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F114" s="112">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 18/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" s="158">
+      <c r="A115" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D113" s="115">
-        <f>SUMIF(E75:E112,"Pendente",D75:D112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="205" t="inlineStr">
+      <c r="D115" s="115">
+        <f>SUMIF(E75:E114,"Pendente",D75:D114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" s="158">
+      <c r="A116" s="205" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B114" s="160" t="n"/>
-      <c r="C114" s="160" t="n"/>
-      <c r="D114" s="160" t="n"/>
-      <c r="E114" s="160" t="n"/>
-      <c r="F114" s="160" t="n"/>
-      <c r="G114" s="161" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="202">
-        <f>IF(ROUND(D113-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D113-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="202" t="inlineStr">
+      <c r="B116" s="160" t="n"/>
+      <c r="C116" s="160" t="n"/>
+      <c r="D116" s="160" t="n"/>
+      <c r="E116" s="160" t="n"/>
+      <c r="F116" s="160" t="n"/>
+      <c r="G116" s="161" t="n"/>
+    </row>
+    <row r="117" s="158">
+      <c r="A117" s="202">
+        <f>IF(ROUND(D115-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D115-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" s="158">
+      <c r="A118" s="202" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
@@ -47487,23 +47647,23 @@
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A116:G116"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A114:G114"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A72:G72"/>
     <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A117:G117"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E75:E112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E75:E114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -35790,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U134"/>
+  <dimension ref="A1:U162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +35955,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H132,K5,G5:G132)</f>
+        <f>SUMIF(H5:H160,K5,G5:G160)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D133-F133-T5</f>
+        <f>D161-F161-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D134</f>
+        <f>D162</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E132,"Aguardando Pagamento",D5:D132)</f>
+        <f>SUMIF(E5:E160,"Aguardando Pagamento",D5:D160)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H132,K6,G5:G132)</f>
+        <f>SUMIF(H5:H160,K6,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36056,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H132,K7,G5:G132)</f>
+        <f>SUMIF(H5:H160,K7,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H132,K8,G5:G132)</f>
+        <f>SUMIF(H5:H160,K8,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H132,K9,G5:G132)</f>
+        <f>SUMIF(H5:H160,K9,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H132,K10,G5:G132)</f>
+        <f>SUMIF(H5:H160,K10,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H132,K11,G5:G132)</f>
+        <f>SUMIF(H5:H160,K11,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H132,K12,G5:G132)</f>
+        <f>SUMIF(H5:H160,K12,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H132,K13,G5:G132)</f>
+        <f>SUMIF(H5:H160,K13,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H132,K14,G5:G132)</f>
+        <f>SUMIF(H5:H160,K14,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H132,K15,G5:G132)</f>
+        <f>SUMIF(H5:H160,K15,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H132,K16,G5:G132)</f>
+        <f>SUMIF(H5:H160,K16,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H132,K17,G5:G132)</f>
+        <f>SUMIF(H5:H160,K17,G5:G160)</f>
         <v/>
       </c>
     </row>
@@ -39974,43 +39974,832 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="29" t="n"/>
-      <c r="B133" s="43" t="inlineStr">
+      <c r="A133" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B133" s="78" t="inlineStr">
+        <is>
+          <t>Valdemar</t>
+        </is>
+      </c>
+      <c r="C133" s="78" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D133" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E133" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F133" s="79" t="n"/>
+      <c r="G133" s="79" t="n"/>
+      <c r="H133" s="78" t="n"/>
+      <c r="I133" s="78" t="inlineStr">
+        <is>
+          <t>Instalação do pré-filtro pelo Wiliam. Cliente ainda sem cadastro na Planilha de Clientes.</t>
+        </is>
+      </c>
+      <c r="J133" s="78" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="81" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B134" s="82" t="inlineStr">
+        <is>
+          <t>Dailana Araujo Lima</t>
+        </is>
+      </c>
+      <c r="C134" s="82" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Cinza Claro</t>
+        </is>
+      </c>
+      <c r="D134" s="83" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E134" s="82" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F134" s="83" t="n">
+        <v>148.85</v>
+      </c>
+      <c r="G134" s="83" t="n"/>
+      <c r="H134" s="82" t="n"/>
+      <c r="I134" s="82" t="inlineStr">
+        <is>
+          <t>Crédito em 5x. Instalação feita em 18/09/2026.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>CLI-0895</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B135" s="78" t="inlineStr">
+        <is>
+          <t>Maria Lucia Pinho Guimarães</t>
+        </is>
+      </c>
+      <c r="C135" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D135" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E135" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F135" s="79" t="n"/>
+      <c r="G135" s="79" t="n"/>
+      <c r="H135" s="78" t="n"/>
+      <c r="I135" s="78" t="n"/>
+      <c r="J135" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0065</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="81" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B136" s="82" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C136" s="82" t="inlineStr">
+        <is>
+          <t>Refil FP4</t>
+        </is>
+      </c>
+      <c r="D136" s="83" t="n">
+        <v>60</v>
+      </c>
+      <c r="E136" s="82" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F136" s="83" t="n"/>
+      <c r="G136" s="83" t="n"/>
+      <c r="H136" s="82" t="n"/>
+      <c r="I136" s="82" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B137" s="78" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+      <c r="C137" s="78" t="n"/>
+      <c r="D137" s="79" t="n"/>
+      <c r="E137" s="78" t="n"/>
+      <c r="F137" s="79" t="n"/>
+      <c r="G137" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="H137" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I137" s="78" t="inlineStr">
+        <is>
+          <t>Compra de supermercado — despesa pessoal (Edilânia).</t>
+        </is>
+      </c>
+      <c r="J137" s="78" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B138" s="82" t="inlineStr">
+        <is>
+          <t>Adrielly Costa Fontes</t>
+        </is>
+      </c>
+      <c r="C138" s="82" t="n"/>
+      <c r="D138" s="83" t="n"/>
+      <c r="E138" s="82" t="n"/>
+      <c r="F138" s="83" t="n"/>
+      <c r="G138" s="83" t="n">
+        <v>50</v>
+      </c>
+      <c r="H138" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I138" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 02/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="77" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B139" s="78" t="inlineStr">
+        <is>
+          <t>Dlocal Brasil Instituição de Pagamento</t>
+        </is>
+      </c>
+      <c r="C139" s="78" t="n"/>
+      <c r="D139" s="79" t="n"/>
+      <c r="E139" s="78" t="n"/>
+      <c r="F139" s="79" t="n"/>
+      <c r="G139" s="79" t="n">
+        <v>103.52</v>
+      </c>
+      <c r="H139" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I139" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 02/09/2026.</t>
+        </is>
+      </c>
+      <c r="J139" s="78" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="81" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B140" s="82" t="inlineStr">
+        <is>
+          <t>Appmax Plataforma</t>
+        </is>
+      </c>
+      <c r="C140" s="82" t="n"/>
+      <c r="D140" s="83" t="n"/>
+      <c r="E140" s="82" t="n"/>
+      <c r="F140" s="83" t="n"/>
+      <c r="G140" s="83" t="n">
+        <v>176.67</v>
+      </c>
+      <c r="H140" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I140" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 03/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="77" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B141" s="78" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
+      <c r="C141" s="78" t="n"/>
+      <c r="D141" s="79" t="n"/>
+      <c r="E141" s="78" t="n"/>
+      <c r="F141" s="79" t="n"/>
+      <c r="G141" s="79" t="n">
+        <v>21</v>
+      </c>
+      <c r="H141" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I141" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 04/09/2026.</t>
+        </is>
+      </c>
+      <c r="J141" s="78" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="81" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B142" s="82" t="inlineStr">
+        <is>
+          <t>Dlocal Brasil Instituição de Pagamento</t>
+        </is>
+      </c>
+      <c r="C142" s="82" t="n"/>
+      <c r="D142" s="83" t="n"/>
+      <c r="E142" s="82" t="n"/>
+      <c r="F142" s="83" t="n"/>
+      <c r="G142" s="83" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="H142" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I142" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 04/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="77" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B143" s="78" t="inlineStr">
+        <is>
+          <t>Junior e Oliveira Ltda</t>
+        </is>
+      </c>
+      <c r="C143" s="78" t="n"/>
+      <c r="D143" s="79" t="n"/>
+      <c r="E143" s="78" t="n"/>
+      <c r="F143" s="79" t="n"/>
+      <c r="G143" s="79" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H143" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I143" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 06/09/2026.</t>
+        </is>
+      </c>
+      <c r="J143" s="78" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="81" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B144" s="82" t="inlineStr">
+        <is>
+          <t>Maree Instituição de Pagamento</t>
+        </is>
+      </c>
+      <c r="C144" s="82" t="n"/>
+      <c r="D144" s="83" t="n"/>
+      <c r="E144" s="82" t="n"/>
+      <c r="F144" s="83" t="n"/>
+      <c r="G144" s="83" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="H144" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I144" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 06/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="77" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B145" s="78" t="inlineStr">
+        <is>
+          <t>Japedido Software</t>
+        </is>
+      </c>
+      <c r="C145" s="78" t="n"/>
+      <c r="D145" s="79" t="n"/>
+      <c r="E145" s="78" t="n"/>
+      <c r="F145" s="79" t="n"/>
+      <c r="G145" s="79" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="H145" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I145" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 08/09/2026.</t>
+        </is>
+      </c>
+      <c r="J145" s="78" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="81" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B146" s="82" t="inlineStr">
+        <is>
+          <t>Pagar.me Instituição de Pagamento</t>
+        </is>
+      </c>
+      <c r="C146" s="82" t="n"/>
+      <c r="D146" s="83" t="n"/>
+      <c r="E146" s="82" t="n"/>
+      <c r="F146" s="83" t="n"/>
+      <c r="G146" s="83" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H146" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I146" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 09/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="77" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B147" s="78" t="inlineStr">
+        <is>
+          <t>Isabella Santos Flores</t>
+        </is>
+      </c>
+      <c r="C147" s="78" t="n"/>
+      <c r="D147" s="79" t="n"/>
+      <c r="E147" s="78" t="n"/>
+      <c r="F147" s="79" t="n"/>
+      <c r="G147" s="79" t="n">
+        <v>170</v>
+      </c>
+      <c r="H147" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I147" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 09/09/2026.</t>
+        </is>
+      </c>
+      <c r="J147" s="78" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="81" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B148" s="82" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
+      <c r="C148" s="82" t="n"/>
+      <c r="D148" s="83" t="n"/>
+      <c r="E148" s="82" t="n"/>
+      <c r="F148" s="83" t="n"/>
+      <c r="G148" s="83" t="n">
+        <v>21</v>
+      </c>
+      <c r="H148" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I148" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 10/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="77" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B149" s="78" t="inlineStr">
+        <is>
+          <t>Humberto Fernandes Costa</t>
+        </is>
+      </c>
+      <c r="C149" s="78" t="n"/>
+      <c r="D149" s="79" t="n"/>
+      <c r="E149" s="78" t="n"/>
+      <c r="F149" s="79" t="n"/>
+      <c r="G149" s="79" t="n">
+        <v>964</v>
+      </c>
+      <c r="H149" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I149" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 10/09/2026.</t>
+        </is>
+      </c>
+      <c r="J149" s="78" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="81" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B150" s="82" t="inlineStr">
+        <is>
+          <t>Sinesio Moura da Silva</t>
+        </is>
+      </c>
+      <c r="C150" s="82" t="n"/>
+      <c r="D150" s="83" t="n"/>
+      <c r="E150" s="82" t="n"/>
+      <c r="F150" s="83" t="n"/>
+      <c r="G150" s="83" t="n">
+        <v>100</v>
+      </c>
+      <c r="H150" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I150" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 14/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B151" s="78" t="inlineStr">
+        <is>
+          <t>Eziquiel Soares da Cruz</t>
+        </is>
+      </c>
+      <c r="C151" s="78" t="n"/>
+      <c r="D151" s="79" t="n"/>
+      <c r="E151" s="78" t="n"/>
+      <c r="F151" s="79" t="n"/>
+      <c r="G151" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="H151" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I151" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
+        </is>
+      </c>
+      <c r="J151" s="78" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B152" s="82" t="inlineStr">
+        <is>
+          <t>Lojão JB Mega 25</t>
+        </is>
+      </c>
+      <c r="C152" s="82" t="n"/>
+      <c r="D152" s="83" t="n"/>
+      <c r="E152" s="82" t="n"/>
+      <c r="F152" s="83" t="n"/>
+      <c r="G152" s="83" t="n">
+        <v>50</v>
+      </c>
+      <c r="H152" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I152" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B153" s="78" t="inlineStr">
+        <is>
+          <t>Rivael Sousa Santos</t>
+        </is>
+      </c>
+      <c r="C153" s="78" t="n"/>
+      <c r="D153" s="79" t="n"/>
+      <c r="E153" s="78" t="n"/>
+      <c r="F153" s="79" t="n"/>
+      <c r="G153" s="79" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H153" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I153" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
+        </is>
+      </c>
+      <c r="J153" s="78" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="81" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B154" s="82" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
+      <c r="C154" s="82" t="n"/>
+      <c r="D154" s="83" t="n"/>
+      <c r="E154" s="82" t="n"/>
+      <c r="F154" s="83" t="n"/>
+      <c r="G154" s="83" t="n">
+        <v>28</v>
+      </c>
+      <c r="H154" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I154" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="77" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B155" s="78" t="inlineStr">
+        <is>
+          <t>Luciana Cruz Freire Santos</t>
+        </is>
+      </c>
+      <c r="C155" s="78" t="n"/>
+      <c r="D155" s="79" t="n"/>
+      <c r="E155" s="78" t="n"/>
+      <c r="F155" s="79" t="n"/>
+      <c r="G155" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="H155" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I155" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
+        </is>
+      </c>
+      <c r="J155" s="78" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B156" s="82" t="inlineStr">
+        <is>
+          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
+        </is>
+      </c>
+      <c r="C156" s="82" t="n"/>
+      <c r="D156" s="83" t="n"/>
+      <c r="E156" s="82" t="n"/>
+      <c r="F156" s="83" t="n"/>
+      <c r="G156" s="83" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="H156" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I156" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 16/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B157" s="78" t="inlineStr">
+        <is>
+          <t>Japedido Software</t>
+        </is>
+      </c>
+      <c r="C157" s="78" t="n"/>
+      <c r="D157" s="79" t="n"/>
+      <c r="E157" s="78" t="n"/>
+      <c r="F157" s="79" t="n"/>
+      <c r="G157" s="79" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="H157" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I157" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 18/09/2026.</t>
+        </is>
+      </c>
+      <c r="J157" s="78" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="81" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B158" s="82" t="inlineStr">
+        <is>
+          <t>Jose Barbosa Leal Filho Ltda</t>
+        </is>
+      </c>
+      <c r="C158" s="82" t="n"/>
+      <c r="D158" s="83" t="n"/>
+      <c r="E158" s="82" t="n"/>
+      <c r="F158" s="83" t="n"/>
+      <c r="G158" s="83" t="n">
+        <v>130</v>
+      </c>
+      <c r="H158" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I158" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 18/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B159" s="78" t="inlineStr">
+        <is>
+          <t>L K Abade Ltda</t>
+        </is>
+      </c>
+      <c r="C159" s="78" t="n"/>
+      <c r="D159" s="79" t="n"/>
+      <c r="E159" s="78" t="n"/>
+      <c r="F159" s="79" t="n"/>
+      <c r="G159" s="79" t="n">
+        <v>40</v>
+      </c>
+      <c r="H159" s="78" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I159" s="78" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 18/09/2026.</t>
+        </is>
+      </c>
+      <c r="J159" s="78" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="81" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B160" s="82" t="inlineStr">
+        <is>
+          <t>Multidisplay Comercio e Servicos Tecnologicos</t>
+        </is>
+      </c>
+      <c r="C160" s="82" t="n"/>
+      <c r="D160" s="83" t="n"/>
+      <c r="E160" s="82" t="n"/>
+      <c r="F160" s="83" t="n"/>
+      <c r="G160" s="83" t="n">
+        <v>25</v>
+      </c>
+      <c r="H160" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I160" s="82" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 08/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="29" t="n"/>
+      <c r="B161" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C133" s="161" t="n"/>
-      <c r="D133" s="8">
-        <f>SUM(D5:D132)</f>
-        <v/>
-      </c>
-      <c r="E133" s="8" t="n"/>
-      <c r="F133" s="29">
-        <f>SUM(F5:F132)</f>
-        <v/>
-      </c>
-      <c r="G133" s="8">
-        <f>SUM(G5:G132)</f>
-        <v/>
-      </c>
-      <c r="H133" s="29" t="n"/>
-      <c r="I133" s="29" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="30" t="n"/>
-      <c r="B134" s="135" t="inlineStr">
+      <c r="C161" s="161" t="n"/>
+      <c r="D161" s="8">
+        <f>SUM(D5:D160)</f>
+        <v/>
+      </c>
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="29">
+        <f>SUM(F5:F160)</f>
+        <v/>
+      </c>
+      <c r="G161" s="8">
+        <f>SUM(G5:G160)</f>
+        <v/>
+      </c>
+      <c r="H161" s="29" t="n"/>
+      <c r="I161" s="29" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="30" t="n"/>
+      <c r="B162" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D134" s="134">
-        <f>(D133-F133-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F134" s="30" t="n"/>
-      <c r="H134" s="30" t="n"/>
-      <c r="I134" s="30" t="n"/>
+      <c r="D162" s="134">
+        <f>(D161-F161-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F162" s="30" t="n"/>
+      <c r="H162" s="30" t="n"/>
+      <c r="I162" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -40027,10 +40816,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -44335,7 +45124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -44386,7 +45175,7 @@
     </row>
     <row r="5">
       <c r="A5" s="190">
-        <f>D69</f>
+        <f>D72</f>
         <v/>
       </c>
       <c r="C5" s="203">
@@ -46010,7 +46799,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" s="158">
       <c r="A60" s="149" t="inlineStr">
         <is>
           <t>Wiliam Pinto Bispo</t>
@@ -46042,7 +46831,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" s="158">
       <c r="A61" s="149" t="inlineStr">
         <is>
           <t>Wiliam Pinto Bispo</t>
@@ -46074,7 +46863,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" s="158">
       <c r="A62" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46106,7 +46895,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" s="158">
       <c r="A63" s="78" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46138,7 +46927,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" s="158">
       <c r="A64" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46170,7 +46959,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" s="158">
       <c r="A65" s="78" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46202,7 +46991,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" s="158">
       <c r="A66" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46234,1254 +47023,1255 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="86" t="inlineStr">
+    <row r="67" s="158">
+      <c r="A67" s="82" t="inlineStr">
+        <is>
+          <t>Receita Federal — Simples Nacional (DAS)</t>
+        </is>
+      </c>
+      <c r="B67" s="82" t="inlineStr">
+        <is>
+          <t>DAS — competência agosto/2026 (doc. 07.20.26260.6017058-0)</t>
+        </is>
+      </c>
+      <c r="C67" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D67" s="83" t="n">
+        <v>1958.02</v>
+      </c>
+      <c r="E67" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F67" s="113">
+        <f>IF(OR($E67="Pago",$C67=""),"",MAX(0,TODAY()-$C67))</f>
+        <v/>
+      </c>
+      <c r="G67" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Planeta Agua Ltda, CNPJ 07.341.784/0001-60. Detalhe: IRPJ R$ 187,69 · CSLL R$ 88,53 · COFINS R$ 249,45 · PIS R$ 54,04 · INSS R$ 822,37 · ICMS (BA) R$ 655,94. Linha digitável 85860000019 5 58020328262 0 64072026260 4 60170580750 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" s="158">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
+          <t>SEFAZ-BA — DAE ICMS Antecipação Parcial</t>
+        </is>
+      </c>
+      <c r="B68" s="82" t="inlineStr">
+        <is>
+          <t>ICMS Antecipação Parcial — referência 08/2026 (cód. receita 2175, nº 1965056088)</t>
+        </is>
+      </c>
+      <c r="C68" s="81" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D68" s="83" t="n">
+        <v>1712.7</v>
+      </c>
+      <c r="E68" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F68" s="113">
+        <f>IF(OR($E68="Pago",$C68=""),"",MAX(0,TODAY()-$C68))</f>
+        <v/>
+      </c>
+      <c r="G68" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85890000017 4 12700005202 5 60925196505 0 60882175193 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" s="158">
+      <c r="A69" s="82" t="inlineStr">
+        <is>
+          <t>SEFAZ-BA — DAE ICMS Antecipação Tributária</t>
+        </is>
+      </c>
+      <c r="B69" s="82" t="inlineStr">
+        <is>
+          <t>ICMS Antecipação Tributária — referência 08/2026 (cód. receita 1145, nº 1965056107)</t>
+        </is>
+      </c>
+      <c r="C69" s="81" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D69" s="83" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="E69" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F69" s="113">
+        <f>IF(OR($E69="Pago",$C69=""),"",MAX(0,TODAY()-$C69))</f>
+        <v/>
+      </c>
+      <c r="G69" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85870000000 6 74050005202 0 60925196505 0 61070133812 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" s="158">
+      <c r="A70" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B67" s="86" t="n"/>
-      <c r="C67" s="114" t="n"/>
-      <c r="D67" s="115">
-        <f>SUMIF(E11:E66,"Pendente",D11:D66)</f>
-        <v/>
-      </c>
-      <c r="E67" s="116" t="n"/>
-      <c r="F67" s="116" t="n"/>
-      <c r="G67" s="86" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="154" t="inlineStr">
+      <c r="B70" s="86" t="n"/>
+      <c r="C70" s="114" t="n"/>
+      <c r="D70" s="115">
+        <f>SUMIF(E11:E69,"Pendente",D11:D69)</f>
+        <v/>
+      </c>
+      <c r="E70" s="116" t="n"/>
+      <c r="F70" s="116" t="n"/>
+      <c r="G70" s="86" t="n"/>
+    </row>
+    <row r="71" s="158">
+      <c r="A71" s="154" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B68" s="154" t="n"/>
-      <c r="C68" s="155" t="n"/>
-      <c r="D68" s="156">
-        <f>SUMIF(E11:E66,"Previsto",D11:D66)</f>
-        <v/>
-      </c>
-      <c r="E68" s="152" t="n"/>
-      <c r="F68" s="152" t="n"/>
-      <c r="G68" s="154" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="86" t="inlineStr">
+      <c r="B71" s="154" t="n"/>
+      <c r="C71" s="155" t="n"/>
+      <c r="D71" s="156">
+        <f>SUMIF(E11:E69,"Previsto",D11:D69)</f>
+        <v/>
+      </c>
+      <c r="E71" s="152" t="n"/>
+      <c r="F71" s="152" t="n"/>
+      <c r="G71" s="154" t="n"/>
+    </row>
+    <row r="72" s="158">
+      <c r="A72" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B69" s="86" t="n"/>
-      <c r="C69" s="114" t="n"/>
-      <c r="D69" s="115">
-        <f>D67+D68</f>
-        <v/>
-      </c>
-      <c r="E69" s="116" t="n"/>
-      <c r="F69" s="116" t="n"/>
-      <c r="G69" s="86" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" s="158"/>
-    <row r="72">
-      <c r="A72" s="206" t="inlineStr">
+      <c r="B72" s="86" t="n"/>
+      <c r="C72" s="114" t="n"/>
+      <c r="D72" s="115">
+        <f>D70+D71</f>
+        <v/>
+      </c>
+      <c r="E72" s="116" t="n"/>
+      <c r="F72" s="116" t="n"/>
+      <c r="G72" s="86" t="n"/>
+    </row>
+    <row r="73" s="158"/>
+    <row r="74" ht="15.75" customHeight="1" s="158"/>
+    <row r="75" s="158">
+      <c r="A75" s="206" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="195" t="inlineStr">
+    <row r="76" s="158">
+      <c r="A76" s="195" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="111" t="inlineStr">
+    <row r="77" s="158">
+      <c r="A77" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B74" s="111" t="inlineStr">
+      <c r="B77" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C74" s="111" t="inlineStr">
+      <c r="C77" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D74" s="111" t="inlineStr">
+      <c r="D77" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E74" s="111" t="inlineStr">
+      <c r="E77" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F74" s="111" t="inlineStr">
+      <c r="F77" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G74" s="111" t="inlineStr">
+      <c r="G77" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="78" t="inlineStr">
+    <row r="78" s="158">
+      <c r="A78" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B75" s="78" t="inlineStr">
+      <c r="B78" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C75" s="77" t="n">
+      <c r="C78" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D75" s="79" t="n">
+      <c r="D78" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E75" s="112" t="inlineStr">
+      <c r="E78" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F75" s="112">
-        <f>IF(OR($E74="Recebido",$C74=""),"",MAX(0,TODAY()-$C74))</f>
-        <v/>
-      </c>
-      <c r="G75" s="78" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="82" t="inlineStr">
+      <c r="F78" s="112">
+        <f>IF(OR($E78="Recebido",$C78=""),"",MAX(0,TODAY()-$C78))</f>
+        <v/>
+      </c>
+      <c r="G78" s="78" t="n"/>
+    </row>
+    <row r="79" s="158">
+      <c r="A79" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B76" s="82" t="inlineStr">
+      <c r="B79" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C76" s="81" t="n">
+      <c r="C79" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D76" s="83" t="n">
+      <c r="D79" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E76" s="113" t="inlineStr">
+      <c r="E79" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F76" s="113">
-        <f>IF(OR($E75="Recebido",$C75=""),"",MAX(0,TODAY()-$C75))</f>
-        <v/>
-      </c>
-      <c r="G76" s="82" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="78" t="inlineStr">
+      <c r="F79" s="113">
+        <f>IF(OR($E79="Recebido",$C79=""),"",MAX(0,TODAY()-$C79))</f>
+        <v/>
+      </c>
+      <c r="G79" s="82" t="n"/>
+    </row>
+    <row r="80" s="158">
+      <c r="A80" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B77" s="78" t="inlineStr">
+      <c r="B80" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C77" s="77" t="n">
+      <c r="C80" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D77" s="79" t="n">
+      <c r="D80" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E77" s="112" t="inlineStr">
+      <c r="E80" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F77" s="112">
-        <f>IF(OR($E76="Recebido",$C76=""),"",MAX(0,TODAY()-$C76))</f>
-        <v/>
-      </c>
-      <c r="G77" s="78" t="inlineStr">
+      <c r="F80" s="112">
+        <f>IF(OR($E80="Recebido",$C80=""),"",MAX(0,TODAY()-$C80))</f>
+        <v/>
+      </c>
+      <c r="G80" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="82" t="inlineStr">
+    <row r="81" s="158">
+      <c r="A81" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B78" s="82" t="inlineStr">
+      <c r="B81" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C78" s="81" t="n">
+      <c r="C81" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D78" s="83" t="n">
+      <c r="D81" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E78" s="113" t="inlineStr">
+      <c r="E81" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F78" s="113">
-        <f>IF(OR($E77="Recebido",$C77=""),"",MAX(0,TODAY()-$C77))</f>
-        <v/>
-      </c>
-      <c r="G78" s="82" t="inlineStr">
+      <c r="F81" s="113">
+        <f>IF(OR($E81="Recebido",$C81=""),"",MAX(0,TODAY()-$C81))</f>
+        <v/>
+      </c>
+      <c r="G81" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="78" t="inlineStr">
+    <row r="82" s="158">
+      <c r="A82" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B79" s="78" t="inlineStr">
+      <c r="B82" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C79" s="77" t="n">
+      <c r="C82" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D79" s="79" t="n">
+      <c r="D82" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E79" s="112" t="inlineStr">
+      <c r="E82" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F79" s="112">
-        <f>IF(OR($E78="Recebido",$C78=""),"",MAX(0,TODAY()-$C78))</f>
-        <v/>
-      </c>
-      <c r="G79" s="78" t="inlineStr">
+      <c r="F82" s="112">
+        <f>IF(OR($E82="Recebido",$C82=""),"",MAX(0,TODAY()-$C82))</f>
+        <v/>
+      </c>
+      <c r="G82" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="82" t="inlineStr">
+    <row r="83" s="158">
+      <c r="A83" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="B83" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C80" s="81" t="n">
+      <c r="C83" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D80" s="83" t="n">
+      <c r="D83" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E80" s="113" t="inlineStr">
+      <c r="E83" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F80" s="113">
-        <f>IF(OR($E79="Recebido",$C79=""),"",MAX(0,TODAY()-$C79))</f>
-        <v/>
-      </c>
-      <c r="G80" s="82" t="inlineStr">
+      <c r="F83" s="113">
+        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
+        <v/>
+      </c>
+      <c r="G83" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="78" t="inlineStr">
+    <row r="84" s="158">
+      <c r="A84" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B81" s="78" t="inlineStr">
+      <c r="B84" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C81" s="77" t="n">
+      <c r="C84" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D81" s="79" t="n">
+      <c r="D84" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E81" s="112" t="inlineStr">
+      <c r="E84" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F81" s="112">
-        <f>IF(OR($E80="Recebido",$C80=""),"",MAX(0,TODAY()-$C80))</f>
-        <v/>
-      </c>
-      <c r="G81" s="78" t="inlineStr">
+      <c r="F84" s="112">
+        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
+        <v/>
+      </c>
+      <c r="G84" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="82" t="inlineStr">
+    <row r="85" s="158">
+      <c r="A85" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B82" s="82" t="inlineStr">
+      <c r="B85" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C82" s="81" t="n">
+      <c r="C85" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D82" s="83" t="n">
+      <c r="D85" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E82" s="113" t="inlineStr">
+      <c r="E85" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F82" s="113">
-        <f>IF(OR($E81="Recebido",$C81=""),"",MAX(0,TODAY()-$C81))</f>
-        <v/>
-      </c>
-      <c r="G82" s="82" t="inlineStr">
+      <c r="F85" s="113">
+        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
+        <v/>
+      </c>
+      <c r="G85" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="78" t="inlineStr">
+    <row r="86" s="158">
+      <c r="A86" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B83" s="78" t="inlineStr">
+      <c r="B86" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C83" s="77" t="n">
+      <c r="C86" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D83" s="79" t="n">
+      <c r="D86" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E83" s="112" t="inlineStr">
+      <c r="E86" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F83" s="112">
-        <f>IF(OR($E82="Recebido",$C82=""),"",MAX(0,TODAY()-$C82))</f>
-        <v/>
-      </c>
-      <c r="G83" s="78" t="inlineStr">
+      <c r="F86" s="112">
+        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
+        <v/>
+      </c>
+      <c r="G86" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="82" t="inlineStr">
+    <row r="87" s="158">
+      <c r="A87" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="B87" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C84" s="81" t="n">
+      <c r="C87" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D84" s="83" t="n">
+      <c r="D87" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E84" s="113" t="inlineStr">
+      <c r="E87" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F84" s="113">
-        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
-        <v/>
-      </c>
-      <c r="G84" s="82" t="inlineStr">
+      <c r="F87" s="113">
+        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
+        <v/>
+      </c>
+      <c r="G87" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="78" t="inlineStr">
+    <row r="88" s="158">
+      <c r="A88" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B85" s="78" t="inlineStr">
+      <c r="B88" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C85" s="77" t="n">
+      <c r="C88" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D85" s="79" t="n">
+      <c r="D88" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E85" s="112" t="inlineStr">
+      <c r="E88" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F85" s="112">
-        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
-        <v/>
-      </c>
-      <c r="G85" s="78" t="inlineStr">
+      <c r="F88" s="112">
+        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="82" t="inlineStr">
+    <row r="89" s="158">
+      <c r="A89" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B86" s="82" t="inlineStr">
+      <c r="B89" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C86" s="81" t="n">
+      <c r="C89" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D86" s="83" t="n">
+      <c r="D89" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E86" s="113" t="inlineStr">
+      <c r="E89" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F86" s="113">
-        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
-        <v/>
-      </c>
-      <c r="G86" s="82" t="inlineStr">
+      <c r="F89" s="113">
+        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="78" t="inlineStr">
+    <row r="90" s="158">
+      <c r="A90" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B87" s="78" t="inlineStr">
+      <c r="B90" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C87" s="77" t="n">
+      <c r="C90" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D87" s="79" t="n">
+      <c r="D90" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E87" s="112" t="inlineStr">
+      <c r="E90" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F87" s="112">
-        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
-        <v/>
-      </c>
-      <c r="G87" s="78" t="inlineStr">
+      <c r="F90" s="112">
+        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="82" t="inlineStr">
+    <row r="91" s="158">
+      <c r="A91" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B88" s="82" t="inlineStr">
+      <c r="B91" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C88" s="81" t="n">
+      <c r="C91" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D88" s="83" t="n">
+      <c r="D91" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E88" s="113" t="inlineStr">
+      <c r="E91" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F88" s="113">
-        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
-        <v/>
-      </c>
-      <c r="G88" s="82" t="inlineStr">
+      <c r="F91" s="113">
+        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="78" t="inlineStr">
+    <row r="92" s="158">
+      <c r="A92" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B89" s="78" t="inlineStr">
+      <c r="B92" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C89" s="77" t="n">
+      <c r="C92" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D89" s="79" t="n">
+      <c r="D92" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E89" s="112" t="inlineStr">
+      <c r="E92" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F89" s="112">
-        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
-        <v/>
-      </c>
-      <c r="G89" s="78" t="inlineStr">
+      <c r="F92" s="112">
+        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="82" t="inlineStr">
+    <row r="93" s="158">
+      <c r="A93" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B90" s="82" t="inlineStr">
+      <c r="B93" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C90" s="81" t="n">
+      <c r="C93" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D90" s="83" t="n">
+      <c r="D93" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E90" s="113" t="inlineStr">
+      <c r="E93" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F90" s="113">
-        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
-        <v/>
-      </c>
-      <c r="G90" s="82" t="inlineStr">
+      <c r="F93" s="113">
+        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="78" t="inlineStr">
+    <row r="94" s="158">
+      <c r="A94" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B91" s="78" t="inlineStr">
+      <c r="B94" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C91" s="77" t="n">
+      <c r="C94" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D91" s="79" t="n">
+      <c r="D94" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E91" s="112" t="inlineStr">
+      <c r="E94" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F91" s="112">
-        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
-        <v/>
-      </c>
-      <c r="G91" s="78" t="inlineStr">
+      <c r="F94" s="112">
+        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="82" t="inlineStr">
+    <row r="95" s="158">
+      <c r="A95" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B92" s="82" t="inlineStr">
+      <c r="B95" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C92" s="81" t="n">
+      <c r="C95" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D92" s="83" t="n">
+      <c r="D95" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E92" s="113" t="inlineStr">
+      <c r="E95" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F92" s="113">
-        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
-        <v/>
-      </c>
-      <c r="G92" s="82" t="inlineStr">
+      <c r="F95" s="113">
+        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="78" t="inlineStr">
+    <row r="96" s="158">
+      <c r="A96" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B93" s="78" t="inlineStr">
+      <c r="B96" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C93" s="77" t="n">
+      <c r="C96" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D93" s="79" t="n">
+      <c r="D96" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E93" s="112" t="inlineStr">
+      <c r="E96" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F93" s="112">
-        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
-        <v/>
-      </c>
-      <c r="G93" s="78" t="inlineStr">
+      <c r="F96" s="112">
+        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="82" t="inlineStr">
+    <row r="97" s="158">
+      <c r="A97" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B94" s="82" t="inlineStr">
+      <c r="B97" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C94" s="81" t="n">
+      <c r="C97" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D94" s="83" t="n">
+      <c r="D97" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E94" s="113" t="inlineStr">
+      <c r="E97" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="113">
-        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
-        <v/>
-      </c>
-      <c r="G94" s="82" t="inlineStr">
+      <c r="F97" s="113">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="78" t="inlineStr">
+    <row r="98" s="158">
+      <c r="A98" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B95" s="78" t="inlineStr">
+      <c r="B98" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C95" s="77" t="n">
+      <c r="C98" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D95" s="79" t="n">
+      <c r="D98" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E95" s="112" t="inlineStr">
+      <c r="E98" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F95" s="112">
-        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
-        <v/>
-      </c>
-      <c r="G95" s="78" t="inlineStr">
+      <c r="F98" s="112">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="82" t="inlineStr">
+    <row r="99" s="158">
+      <c r="A99" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B96" s="82" t="inlineStr">
+      <c r="B99" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C96" s="81" t="n">
+      <c r="C99" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D96" s="83" t="n">
+      <c r="D99" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E96" s="113" t="inlineStr">
+      <c r="E99" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F96" s="113">
-        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
-        <v/>
-      </c>
-      <c r="G96" s="82" t="inlineStr">
+      <c r="F99" s="113">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="78" t="inlineStr">
+    <row r="100" s="158">
+      <c r="A100" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B97" s="78" t="inlineStr">
+      <c r="B100" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C97" s="77" t="n">
+      <c r="C100" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D97" s="79" t="n">
+      <c r="D100" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E97" s="112" t="inlineStr">
+      <c r="E100" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F97" s="112">
-        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
-        <v/>
-      </c>
-      <c r="G97" s="78" t="inlineStr">
+      <c r="F100" s="112">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="82" t="inlineStr">
+    <row r="101" s="158">
+      <c r="A101" s="82" t="inlineStr">
         <is>
           <t>Instituto Paulo Leão</t>
         </is>
       </c>
-      <c r="B98" s="82" t="inlineStr">
+      <c r="B101" s="82" t="inlineStr">
         <is>
           <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
-      <c r="C98" s="81" t="n">
+      <c r="C101" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D98" s="83" t="n">
+      <c r="D101" s="83" t="n">
         <v>160</v>
       </c>
-      <c r="E98" s="113" t="inlineStr">
+      <c r="E101" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="113">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G98" s="82" t="inlineStr">
+      <c r="F101" s="113">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="78" t="inlineStr">
+    <row r="102" s="158">
+      <c r="A102" s="78" t="inlineStr">
         <is>
           <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
-      <c r="B99" s="78" t="inlineStr">
+      <c r="B102" s="78" t="inlineStr">
         <is>
           <t>Pré Filtro</t>
         </is>
       </c>
-      <c r="C99" s="77" t="n">
+      <c r="C102" s="77" t="n">
         <v>46265</v>
       </c>
-      <c r="D99" s="79" t="n">
+      <c r="D102" s="79" t="n">
         <v>60</v>
       </c>
-      <c r="E99" s="112" t="inlineStr">
+      <c r="E102" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F99" s="112">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G99" s="78" t="inlineStr">
+      <c r="F102" s="112">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="82" t="inlineStr">
+    <row r="103" s="158">
+      <c r="A103" s="82" t="inlineStr">
         <is>
           <t>Clube dos Mineiros</t>
         </is>
       </c>
-      <c r="B100" s="82" t="inlineStr">
+      <c r="B103" s="82" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C100" s="81" t="n">
+      <c r="C103" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D100" s="83" t="n">
+      <c r="D103" s="83" t="n">
         <v>150</v>
       </c>
-      <c r="E100" s="113" t="inlineStr">
+      <c r="E103" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F100" s="113">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G100" s="82" t="inlineStr">
+      <c r="F103" s="113">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="78" t="inlineStr">
+    <row r="104" s="158">
+      <c r="A104" s="78" t="inlineStr">
         <is>
           <t>Armazem Cecilio Mota</t>
         </is>
       </c>
-      <c r="B101" s="78" t="inlineStr">
+      <c r="B104" s="78" t="inlineStr">
         <is>
           <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
-      <c r="C101" s="77" t="n">
+      <c r="C104" s="77" t="n">
         <v>46266</v>
       </c>
-      <c r="D101" s="79" t="n">
+      <c r="D104" s="79" t="n">
         <v>225</v>
       </c>
-      <c r="E101" s="112" t="inlineStr">
+      <c r="E104" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F101" s="112">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G101" s="78" t="inlineStr">
+      <c r="F104" s="112">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="82" t="inlineStr">
+    <row r="105" s="158">
+      <c r="A105" s="82" t="inlineStr">
         <is>
           <t>Clebson Dantas Da Silva</t>
         </is>
       </c>
-      <c r="B102" s="82" t="inlineStr">
+      <c r="B105" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C102" s="81" t="n">
+      <c r="C105" s="81" t="n">
         <v>46266</v>
       </c>
-      <c r="D102" s="83" t="n">
+      <c r="D105" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E102" s="113" t="inlineStr">
+      <c r="E105" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F102" s="113">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G102" s="82" t="inlineStr">
+      <c r="F105" s="113">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="82" t="inlineStr">
+    <row r="106" s="158">
+      <c r="A106" s="82" t="inlineStr">
         <is>
           <t>Tesla Imagem Medicina Diagnostica Ltda</t>
         </is>
       </c>
-      <c r="B103" s="82" t="inlineStr">
+      <c r="B106" s="82" t="inlineStr">
         <is>
           <t>3x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
-      <c r="C103" s="81" t="n">
+      <c r="C106" s="81" t="n">
         <v>46267</v>
       </c>
-      <c r="D103" s="83" t="n">
+      <c r="D106" s="83" t="n">
         <v>540</v>
       </c>
-      <c r="E103" s="113" t="inlineStr">
+      <c r="E106" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F103" s="113">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G103" s="82" t="inlineStr">
+      <c r="F106" s="113">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="82" t="inlineStr">
         <is>
           <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="78" t="inlineStr">
+    <row r="107" s="158">
+      <c r="A107" s="78" t="inlineStr">
         <is>
           <t>Cecilio Mota Junior</t>
         </is>
       </c>
-      <c r="B104" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C104" s="77" t="n">
+      <c r="C107" s="77" t="n">
         <v>46267</v>
       </c>
-      <c r="D104" s="79" t="n">
+      <c r="D107" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E104" s="112" t="inlineStr">
+      <c r="E107" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F104" s="112">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G104" s="78" t="inlineStr">
+      <c r="F107" s="112">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="78" t="inlineStr">
+    <row r="108" s="158">
+      <c r="A108" s="78" t="inlineStr">
         <is>
           <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
-      <c r="B105" s="78" t="inlineStr">
+      <c r="B108" s="78" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C105" s="77" t="n">
+      <c r="C108" s="77" t="n">
         <v>46268</v>
       </c>
-      <c r="D105" s="79" t="n">
+      <c r="D108" s="79" t="n">
         <v>200</v>
       </c>
-      <c r="E105" s="112" t="inlineStr">
+      <c r="E108" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F105" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G105" s="78" t="inlineStr">
+      <c r="F108" s="112">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="78" t="inlineStr">
+    <row r="109" s="158">
+      <c r="A109" s="78" t="inlineStr">
         <is>
           <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B109" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C106" s="77" t="n">
+      <c r="C109" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D106" s="79" t="n">
+      <c r="D109" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E106" s="112" t="inlineStr">
+      <c r="E109" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F106" s="112">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G106" s="78" t="inlineStr">
+      <c r="F109" s="112">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="78" t="inlineStr">
+    <row r="110" s="158">
+      <c r="A110" s="78" t="inlineStr">
         <is>
           <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
-      <c r="B107" s="78" t="inlineStr">
+      <c r="B110" s="78" t="inlineStr">
         <is>
           <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
-      <c r="C107" s="77" t="n">
+      <c r="C110" s="77" t="n">
         <v>46274</v>
       </c>
-      <c r="D107" s="79" t="n">
+      <c r="D110" s="79" t="n">
         <v>150</v>
       </c>
-      <c r="E107" s="112" t="inlineStr">
+      <c r="E110" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F107" s="112">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G107" s="78" t="inlineStr">
+      <c r="F110" s="112">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="78" t="inlineStr">
         <is>
           <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="78" t="inlineStr">
-        <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
-        </is>
-      </c>
-      <c r="B108" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C108" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D108" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E108" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F108" s="112">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G108" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="78" t="inlineStr">
-        <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
-        </is>
-      </c>
-      <c r="B109" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C109" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D109" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E109" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F109" s="112">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G109" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="78" t="inlineStr">
-        <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
-        </is>
-      </c>
-      <c r="B110" s="78" t="inlineStr">
-        <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C110" s="77" t="n">
-        <v>46276</v>
-      </c>
-      <c r="D110" s="79" t="n">
-        <v>370</v>
-      </c>
-      <c r="E110" s="112" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F110" s="112">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G110" s="78" t="inlineStr">
-        <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="111" s="158">
       <c r="A111" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B111" s="78" t="inlineStr">
@@ -47490,7 +48280,7 @@
         </is>
       </c>
       <c r="C111" s="77" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D111" s="79" t="n">
         <v>140</v>
@@ -47501,19 +48291,19 @@
         </is>
       </c>
       <c r="F111" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
         <v/>
       </c>
       <c r="G111" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="112" s="158">
       <c r="A112" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B112" s="78" t="inlineStr">
@@ -47522,7 +48312,7 @@
         </is>
       </c>
       <c r="C112" s="77" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="D112" s="79" t="n">
         <v>200</v>
@@ -47533,31 +48323,31 @@
         </is>
       </c>
       <c r="F112" s="112">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
         <v/>
       </c>
       <c r="G112" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="113" s="158">
       <c r="A113" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B113" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C113" s="77" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="D113" s="79" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="E113" s="112" t="inlineStr">
         <is>
@@ -47570,30 +48360,30 @@
       </c>
       <c r="G113" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="114" s="158">
       <c r="A114" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B114" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C114" s="77" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="D114" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E114" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F114" s="112">
@@ -47602,68 +48392,170 @@
       </c>
       <c r="G114" s="78" t="inlineStr">
         <is>
+          <t>Troca do dia 11/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" s="158">
+      <c r="A115" s="78" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="B115" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C115" s="77" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D115" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E115" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F115" s="112">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 14/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" s="158">
+      <c r="A116" s="78" t="inlineStr">
+        <is>
+          <t>Clínica Santa Cecília</t>
+        </is>
+      </c>
+      <c r="B116" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Termostato</t>
+        </is>
+      </c>
+      <c r="C116" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D116" s="79" t="n">
+        <v>310</v>
+      </c>
+      <c r="E116" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F116" s="112">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" s="158">
+      <c r="A117" s="78" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="B117" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C117" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D117" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E117" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F117" s="112">
+        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 18/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="115" s="158">
-      <c r="A115" s="86" t="inlineStr">
+    <row r="118" s="158">
+      <c r="A118" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D115" s="115">
-        <f>SUMIF(E75:E114,"Pendente",D75:D114)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" s="158">
-      <c r="A116" s="205" t="inlineStr">
+      <c r="D118" s="115">
+        <f>SUMIF(E78:E117,"Pendente",D78:D117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" s="158">
+      <c r="A119" s="205" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B116" s="160" t="n"/>
-      <c r="C116" s="160" t="n"/>
-      <c r="D116" s="160" t="n"/>
-      <c r="E116" s="160" t="n"/>
-      <c r="F116" s="160" t="n"/>
-      <c r="G116" s="161" t="n"/>
-    </row>
-    <row r="117" s="158">
-      <c r="A117" s="202">
-        <f>IF(ROUND(D115-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D115-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" s="158">
-      <c r="A118" s="202" t="inlineStr">
+      <c r="B119" s="160" t="n"/>
+      <c r="C119" s="160" t="n"/>
+      <c r="D119" s="160" t="n"/>
+      <c r="E119" s="160" t="n"/>
+      <c r="F119" s="160" t="n"/>
+      <c r="G119" s="161" t="n"/>
+    </row>
+    <row r="120" s="158">
+      <c r="A120" s="202">
+        <f>IF(ROUND(D118-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D118-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" s="158">
+      <c r="A121" s="202" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
+    <row r="122" s="158"/>
+    <row r="123" s="158"/>
+    <row r="124" s="158"/>
+    <row r="125" s="158"/>
+    <row r="126" s="158"/>
+    <row r="127" s="158"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A116:G116"/>
+    <mergeCell ref="A119:G119"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A120:G120"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E75:E114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E78:E117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -35790,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U162"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +35955,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H160,K5,G5:G160)</f>
+        <f>SUMIF(H5:H162,K5,G5:G162)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D161-F161-T5</f>
+        <f>D163-F163-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D162</f>
+        <f>D164</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E160,"Aguardando Pagamento",D5:D160)</f>
+        <f>SUMIF(E5:E162,"Aguardando Pagamento",D5:D162)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H160,K6,G5:G160)</f>
+        <f>SUMIF(H5:H162,K6,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36056,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H160,K7,G5:G160)</f>
+        <f>SUMIF(H5:H162,K7,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H160,K8,G5:G160)</f>
+        <f>SUMIF(H5:H162,K8,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H160,K9,G5:G160)</f>
+        <f>SUMIF(H5:H162,K9,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H160,K10,G5:G160)</f>
+        <f>SUMIF(H5:H162,K10,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H160,K11,G5:G160)</f>
+        <f>SUMIF(H5:H162,K11,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H160,K12,G5:G160)</f>
+        <f>SUMIF(H5:H162,K12,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H160,K13,G5:G160)</f>
+        <f>SUMIF(H5:H162,K13,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H160,K14,G5:G160)</f>
+        <f>SUMIF(H5:H162,K14,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H160,K15,G5:G160)</f>
+        <f>SUMIF(H5:H162,K15,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H160,K16,G5:G160)</f>
+        <f>SUMIF(H5:H162,K16,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H160,K17,G5:G160)</f>
+        <f>SUMIF(H5:H162,K17,G5:G162)</f>
         <v/>
       </c>
     </row>
@@ -40763,43 +40763,98 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="29" t="n"/>
-      <c r="B161" s="43" t="inlineStr">
+      <c r="A161" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B161" s="78" t="inlineStr">
+        <is>
+          <t>FGTS Digital (GFD)</t>
+        </is>
+      </c>
+      <c r="C161" s="78" t="n"/>
+      <c r="D161" s="79" t="n"/>
+      <c r="E161" s="78" t="n"/>
+      <c r="F161" s="79" t="n"/>
+      <c r="G161" s="79" t="n">
+        <v>136</v>
+      </c>
+      <c r="H161" s="78" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I161" s="78" t="inlineStr">
+        <is>
+          <t>FGTS mensal — competência 08/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
+        </is>
+      </c>
+      <c r="J161" s="78" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="81" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B162" s="82" t="inlineStr">
+        <is>
+          <t>Receita Federal — DARF / INSS</t>
+        </is>
+      </c>
+      <c r="C162" s="82" t="n"/>
+      <c r="D162" s="83" t="n"/>
+      <c r="E162" s="82" t="n"/>
+      <c r="F162" s="83" t="n"/>
+      <c r="G162" s="83" t="n">
+        <v>306.99</v>
+      </c>
+      <c r="H162" s="82" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I162" s="82" t="inlineStr">
+        <is>
+          <t>DARF / INSS — período de apuração agosto/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="29" t="n"/>
+      <c r="B163" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C161" s="161" t="n"/>
-      <c r="D161" s="8">
-        <f>SUM(D5:D160)</f>
-        <v/>
-      </c>
-      <c r="E161" s="8" t="n"/>
-      <c r="F161" s="29">
-        <f>SUM(F5:F160)</f>
-        <v/>
-      </c>
-      <c r="G161" s="8">
-        <f>SUM(G5:G160)</f>
-        <v/>
-      </c>
-      <c r="H161" s="29" t="n"/>
-      <c r="I161" s="29" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="30" t="n"/>
-      <c r="B162" s="135" t="inlineStr">
+      <c r="C163" s="161" t="n"/>
+      <c r="D163" s="8">
+        <f>SUM(D5:D162)</f>
+        <v/>
+      </c>
+      <c r="E163" s="8" t="n"/>
+      <c r="F163" s="29">
+        <f>SUM(F5:F162)</f>
+        <v/>
+      </c>
+      <c r="G163" s="8">
+        <f>SUM(G5:G162)</f>
+        <v/>
+      </c>
+      <c r="H163" s="29" t="n"/>
+      <c r="I163" s="29" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="30" t="n"/>
+      <c r="B164" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D162" s="134">
-        <f>(D161-F161-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F162" s="30" t="n"/>
-      <c r="H162" s="30" t="n"/>
-      <c r="I162" s="30" t="n"/>
+      <c r="D164" s="134">
+        <f>(D163-F163-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F164" s="30" t="n"/>
+      <c r="H164" s="30" t="n"/>
+      <c r="I164" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -40816,10 +40871,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -45730,7 +45785,7 @@
       </c>
       <c r="E26" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F26" s="113">
@@ -45739,7 +45794,7 @@
       </c>
       <c r="G26" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas.</t>
+          <t>Categoria: Impostos e Taxas. Pago em 16/09/2026 (antecipado, venc. 18/09) — lançado em "Set 2026" como "FGTS Digital (GFD)".</t>
         </is>
       </c>
     </row>
@@ -45762,7 +45817,7 @@
       </c>
       <c r="E27" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F27" s="112">
@@ -45771,7 +45826,7 @@
       </c>
       <c r="G27" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas.</t>
+          <t>Categoria: Impostos e Taxas. Pago em 16/09/2026 (antecipado, venc. 18/09) — lançado em "Set 2026" como "Receita Federal — DARF / INSS".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -45179,7 +45179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -45197,21 +45197,21 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" s="158">
       <c r="A2" s="196" t="inlineStr">
         <is>
           <t>Compromissos em aberto e vendas ainda não recebidas. "Dias em Atraso" é calculado sozinho. O total a receber é puxado automaticamente das abas dos meses — não precisa somar à mão.</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="158">
       <c r="A3" s="129" t="inlineStr">
         <is>
           <t>← Início</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="158">
       <c r="A4" s="199" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR (EM ABERTO)</t>
@@ -45228,9 +45228,9 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="158">
       <c r="A5" s="190">
-        <f>D72</f>
+        <f>D77</f>
         <v/>
       </c>
       <c r="C5" s="203">
@@ -45242,7 +45242,9 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6" s="158"/>
+    <row r="7" s="158"/>
+    <row r="8" s="158"/>
     <row r="9" ht="21.95" customHeight="1" s="158">
       <c r="A9" s="201" t="inlineStr">
         <is>
@@ -45287,7 +45289,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" s="158">
       <c r="A11" s="78" t="inlineStr">
         <is>
           <t>Capital de Giro (BB) — saldo a devolver</t>
@@ -45318,7 +45320,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="158">
       <c r="A12" s="82" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45350,7 +45352,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" s="158">
       <c r="A13" s="78" t="inlineStr">
         <is>
           <t>Empresa Baiana de Aguas e Saneamento SA (Embasa)</t>
@@ -45382,7 +45384,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" s="158">
       <c r="A14" s="82" t="inlineStr">
         <is>
           <t>Vitoria Maria F Santos</t>
@@ -45414,7 +45416,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="158">
       <c r="A15" s="78" t="inlineStr">
         <is>
           <t>Wiliam Pinto Bispo</t>
@@ -45446,7 +45448,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="158">
       <c r="A16" s="82" t="inlineStr">
         <is>
           <t>Erick Feitosa Evangelista</t>
@@ -45478,7 +45480,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="158">
       <c r="A17" s="78" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -45510,7 +45512,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="158">
       <c r="A18" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -45542,7 +45544,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="158">
       <c r="A19" s="78" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45574,7 +45576,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="158">
       <c r="A20" s="82" t="inlineStr">
         <is>
           <t>Neoenergia Coelba</t>
@@ -45606,7 +45608,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" s="158">
       <c r="A21" s="78" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45638,7 +45640,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" s="158">
       <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -45670,7 +45672,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="158">
       <c r="A23" s="78" t="inlineStr">
         <is>
           <t>Sindicato dos Empregados no Comércio de Jacobina</t>
@@ -45702,7 +45704,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" s="158">
       <c r="A24" s="82" t="inlineStr">
         <is>
           <t>Tarcisio Oliveira Lima</t>
@@ -45734,7 +45736,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" s="158">
       <c r="A25" s="78" t="inlineStr">
         <is>
           <t>Patrus Transportes Ltda</t>
@@ -45766,7 +45768,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="158">
       <c r="A26" s="82" t="inlineStr">
         <is>
           <t>FGTS Digital (GFD)</t>
@@ -45798,7 +45800,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" s="158">
       <c r="A27" s="78" t="inlineStr">
         <is>
           <t>Receita Federal</t>
@@ -45830,7 +45832,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" s="158">
       <c r="A28" s="82" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45862,7 +45864,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" s="158">
       <c r="A29" s="78" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45894,7 +45896,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" s="158">
       <c r="A30" s="82" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45926,7 +45928,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" s="158">
       <c r="A31" s="78" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45958,7 +45960,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" s="158">
       <c r="A32" s="82" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -45990,7 +45992,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" s="158">
       <c r="A33" s="78" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46022,7 +46024,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" s="158">
       <c r="A34" s="82" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46054,7 +46056,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" s="158">
       <c r="A35" s="78" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46086,7 +46088,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" s="158">
       <c r="A36" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46118,7 +46120,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" s="158">
       <c r="A37" s="78" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46150,7 +46152,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="158">
       <c r="A38" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46214,7 +46216,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" s="158">
       <c r="A40" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46278,7 +46280,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" s="158">
       <c r="A42" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46310,7 +46312,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" s="158">
       <c r="A43" s="78" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46342,7 +46344,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" s="158">
       <c r="A44" s="82" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46374,7 +46376,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" s="158">
       <c r="A45" s="149" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46406,7 +46408,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" s="158">
       <c r="A46" s="149" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46438,7 +46440,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="158">
       <c r="A47" s="149" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46470,7 +46472,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" s="158">
       <c r="A48" s="149" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46502,7 +46504,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" s="158">
       <c r="A49" s="149" t="inlineStr">
         <is>
           <t>Everest Refrigeracao e Industria</t>
@@ -46534,7 +46536,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" s="158">
       <c r="A50" s="149" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46566,7 +46568,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" s="158">
       <c r="A51" s="149" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46598,7 +46600,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" s="158">
       <c r="A52" s="149" t="inlineStr">
         <is>
           <t>Eversoft Ind e Com de Plasticos Ltda</t>
@@ -46630,7 +46632,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" s="158">
       <c r="A53" s="78" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -46662,7 +46664,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" s="158">
       <c r="A54" s="82" t="inlineStr">
         <is>
           <t>Instituto Euvaldo Lodi — Núcleo Regional da Bahia</t>
@@ -46694,7 +46696,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" s="158">
       <c r="A55" s="78" t="inlineStr">
         <is>
           <t>Proxxima Telecomunicacoes S.A.</t>
@@ -46726,7 +46728,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" s="158">
       <c r="A56" s="82" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -46758,7 +46760,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" s="158">
       <c r="A57" s="78" t="inlineStr">
         <is>
           <t>Empresa Baiana de Aguas e Saneamento SA (Embasa)</t>
@@ -46790,7 +46792,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" s="158">
       <c r="A58" s="82" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -46822,7 +46824,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" s="158">
       <c r="A59" s="78" t="inlineStr">
         <is>
           <t>Filtros Planeta Agua Ind e Com Ltda</t>
@@ -47175,1014 +47177,1014 @@
       </c>
     </row>
     <row r="70" s="158">
-      <c r="A70" s="86" t="inlineStr">
+      <c r="A70" s="82" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B70" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133812/001 (emissão 28/08/2026) · parcela 1/4</t>
+        </is>
+      </c>
+      <c r="C70" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D70" s="83" t="n">
+        <v>591.12</v>
+      </c>
+      <c r="E70" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F70" s="113">
+        <f>IF(OR($E70="Pago",$C70=""),"",MAX(0,TODAY()-$C70))</f>
+        <v/>
+      </c>
+      <c r="G70" s="82" t="inlineStr">
+        <is>
+          <t>Boleto impresso com vencimento 18/09/2026 — pagamento adiado para 21/09/2026 (segunda): após o vencimento só pode ser pago no Itaú, com multa de 1,9% + juros de 0,1% ao dia (cerca de R$ 604,12 em 21/09). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259098-0. Linha digitável 34191.09008 25909.801430 81531.550002 1 15730000059112. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" s="158">
+      <c r="A71" s="82" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B71" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133812/002 (emissão 28/08/2026) · parcela 2/4</t>
+        </is>
+      </c>
+      <c r="C71" s="81" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D71" s="83" t="n">
+        <v>500.81</v>
+      </c>
+      <c r="E71" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F71" s="113">
+        <f>IF(OR($E71="Pago",$C71=""),"",MAX(0,TODAY()-$C71))</f>
+        <v/>
+      </c>
+      <c r="G71" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" s="158">
+      <c r="A72" s="82" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B72" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133812/003 (emissão 28/08/2026) · parcela 3/4</t>
+        </is>
+      </c>
+      <c r="C72" s="81" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D72" s="83" t="n">
+        <v>500.81</v>
+      </c>
+      <c r="E72" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F72" s="113">
+        <f>IF(OR($E72="Pago",$C72=""),"",MAX(0,TODAY()-$C72))</f>
+        <v/>
+      </c>
+      <c r="G72" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259100-4. Linha digitável 34191.09008 25910.041430 81531.550002 2 16150000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" s="158">
+      <c r="A73" s="82" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Agua Ind e Com Ltda</t>
+        </is>
+      </c>
+      <c r="B73" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 133812/004 (emissão 28/08/2026) · parcela 4/4 (última)</t>
+        </is>
+      </c>
+      <c r="C73" s="81" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D73" s="83" t="n">
+        <v>500.81</v>
+      </c>
+      <c r="E73" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F73" s="113">
+        <f>IF(OR($E73="Pago",$C73=""),"",MAX(0,TODAY()-$C73))</f>
+        <v/>
+      </c>
+      <c r="G73" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259101-2. Linha digitável 34191.09008 25910.121430 81531.550002 2 16360000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" s="158">
+      <c r="A74" s="82" t="inlineStr">
+        <is>
+          <t>Patrus Transportes Ltda</t>
+        </is>
+      </c>
+      <c r="B74" s="82" t="inlineStr">
+        <is>
+          <t>Frete — fatura 26-09-904996 (CT-e 2123999, remetente Everest, NF 386188)</t>
+        </is>
+      </c>
+      <c r="C74" s="81" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D74" s="83" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="E74" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F74" s="113">
+        <f>IF(OR($E74="Pago",$C74=""),"",MAX(0,TODAY()-$C74))</f>
+        <v/>
+      </c>
+      <c r="G74" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840000190-0, agência/cedente 1430-0/0030737-8. Linha digitável 23791.43007 93484.000018 90003.073708 7 15870000032345. Emissão 17/09/2026. Após o vencimento: R$ 0,49 por dia de atraso; negativação a partir do 7º dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" s="158">
+      <c r="A75" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B70" s="86" t="n"/>
-      <c r="C70" s="114" t="n"/>
-      <c r="D70" s="115">
-        <f>SUMIF(E11:E69,"Pendente",D11:D69)</f>
-        <v/>
-      </c>
-      <c r="E70" s="116" t="n"/>
-      <c r="F70" s="116" t="n"/>
-      <c r="G70" s="86" t="n"/>
-    </row>
-    <row r="71" s="158">
-      <c r="A71" s="154" t="inlineStr">
+      <c r="B75" s="86" t="n"/>
+      <c r="C75" s="114" t="n"/>
+      <c r="D75" s="115">
+        <f>SUMIF(E11:E74,"Pendente",D11:D74)</f>
+        <v/>
+      </c>
+      <c r="E75" s="116" t="n"/>
+      <c r="F75" s="116" t="n"/>
+      <c r="G75" s="86" t="n"/>
+    </row>
+    <row r="76" s="158">
+      <c r="A76" s="154" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B71" s="154" t="n"/>
-      <c r="C71" s="155" t="n"/>
-      <c r="D71" s="156">
-        <f>SUMIF(E11:E69,"Previsto",D11:D69)</f>
-        <v/>
-      </c>
-      <c r="E71" s="152" t="n"/>
-      <c r="F71" s="152" t="n"/>
-      <c r="G71" s="154" t="n"/>
-    </row>
-    <row r="72" s="158">
-      <c r="A72" s="86" t="inlineStr">
+      <c r="B76" s="154" t="n"/>
+      <c r="C76" s="155" t="n"/>
+      <c r="D76" s="156">
+        <f>SUMIF(E11:E74,"Previsto",D11:D74)</f>
+        <v/>
+      </c>
+      <c r="E76" s="152" t="n"/>
+      <c r="F76" s="152" t="n"/>
+      <c r="G76" s="154" t="n"/>
+    </row>
+    <row r="77" s="158">
+      <c r="A77" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B72" s="86" t="n"/>
-      <c r="C72" s="114" t="n"/>
-      <c r="D72" s="115">
-        <f>D70+D71</f>
-        <v/>
-      </c>
-      <c r="E72" s="116" t="n"/>
-      <c r="F72" s="116" t="n"/>
-      <c r="G72" s="86" t="n"/>
-    </row>
-    <row r="73" s="158"/>
-    <row r="74" ht="15.75" customHeight="1" s="158"/>
-    <row r="75" s="158">
-      <c r="A75" s="206" t="inlineStr">
+      <c r="B77" s="86" t="n"/>
+      <c r="C77" s="114" t="n"/>
+      <c r="D77" s="115">
+        <f>D75+D76</f>
+        <v/>
+      </c>
+      <c r="E77" s="116" t="n"/>
+      <c r="F77" s="116" t="n"/>
+      <c r="G77" s="86" t="n"/>
+    </row>
+    <row r="78" s="158"/>
+    <row r="79" ht="15.75" customHeight="1" s="158"/>
+    <row r="80" s="158">
+      <c r="A80" s="206" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="76" s="158">
-      <c r="A76" s="195" t="inlineStr">
+    <row r="81" s="158">
+      <c r="A81" s="195" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="77" s="158">
-      <c r="A77" s="111" t="inlineStr">
+    <row r="82" s="158">
+      <c r="A82" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B77" s="111" t="inlineStr">
+      <c r="B82" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C77" s="111" t="inlineStr">
+      <c r="C82" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D77" s="111" t="inlineStr">
+      <c r="D82" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E77" s="111" t="inlineStr">
+      <c r="E82" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F77" s="111" t="inlineStr">
+      <c r="F82" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G77" s="111" t="inlineStr">
+      <c r="G82" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="78" s="158">
-      <c r="A78" s="78" t="inlineStr">
+    <row r="83" s="158">
+      <c r="A83" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B78" s="78" t="inlineStr">
+      <c r="B83" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C78" s="77" t="n">
+      <c r="C83" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D78" s="79" t="n">
+      <c r="D83" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E78" s="112" t="inlineStr">
+      <c r="E83" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F78" s="112">
-        <f>IF(OR($E78="Recebido",$C78=""),"",MAX(0,TODAY()-$C78))</f>
-        <v/>
-      </c>
-      <c r="G78" s="78" t="n"/>
-    </row>
-    <row r="79" s="158">
-      <c r="A79" s="82" t="inlineStr">
+      <c r="F83" s="112">
+        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
+        <v/>
+      </c>
+      <c r="G83" s="78" t="n"/>
+    </row>
+    <row r="84" s="158">
+      <c r="A84" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B79" s="82" t="inlineStr">
+      <c r="B84" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C79" s="81" t="n">
+      <c r="C84" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D79" s="83" t="n">
+      <c r="D84" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E79" s="113" t="inlineStr">
+      <c r="E84" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F79" s="113">
-        <f>IF(OR($E79="Recebido",$C79=""),"",MAX(0,TODAY()-$C79))</f>
-        <v/>
-      </c>
-      <c r="G79" s="82" t="n"/>
-    </row>
-    <row r="80" s="158">
-      <c r="A80" s="78" t="inlineStr">
+      <c r="F84" s="113">
+        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
+        <v/>
+      </c>
+      <c r="G84" s="82" t="n"/>
+    </row>
+    <row r="85" s="158">
+      <c r="A85" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B80" s="78" t="inlineStr">
+      <c r="B85" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C80" s="77" t="n">
+      <c r="C85" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D80" s="79" t="n">
+      <c r="D85" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E80" s="112" t="inlineStr">
+      <c r="E85" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F80" s="112">
-        <f>IF(OR($E80="Recebido",$C80=""),"",MAX(0,TODAY()-$C80))</f>
-        <v/>
-      </c>
-      <c r="G80" s="78" t="inlineStr">
+      <c r="F85" s="112">
+        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
+        <v/>
+      </c>
+      <c r="G85" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="81" s="158">
-      <c r="A81" s="82" t="inlineStr">
+    <row r="86" s="158">
+      <c r="A86" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B81" s="82" t="inlineStr">
+      <c r="B86" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C81" s="81" t="n">
+      <c r="C86" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D81" s="83" t="n">
+      <c r="D86" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E81" s="113" t="inlineStr">
+      <c r="E86" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F81" s="113">
-        <f>IF(OR($E81="Recebido",$C81=""),"",MAX(0,TODAY()-$C81))</f>
-        <v/>
-      </c>
-      <c r="G81" s="82" t="inlineStr">
+      <c r="F86" s="113">
+        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
+        <v/>
+      </c>
+      <c r="G86" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="82" s="158">
-      <c r="A82" s="78" t="inlineStr">
+    <row r="87" s="158">
+      <c r="A87" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B82" s="78" t="inlineStr">
+      <c r="B87" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C82" s="77" t="n">
+      <c r="C87" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D82" s="79" t="n">
+      <c r="D87" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E82" s="112" t="inlineStr">
+      <c r="E87" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F82" s="112">
-        <f>IF(OR($E82="Recebido",$C82=""),"",MAX(0,TODAY()-$C82))</f>
-        <v/>
-      </c>
-      <c r="G82" s="78" t="inlineStr">
+      <c r="F87" s="112">
+        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
+        <v/>
+      </c>
+      <c r="G87" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="83" s="158">
-      <c r="A83" s="82" t="inlineStr">
+    <row r="88" s="158">
+      <c r="A88" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B83" s="82" t="inlineStr">
+      <c r="B88" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C83" s="81" t="n">
+      <c r="C88" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D83" s="83" t="n">
+      <c r="D88" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E83" s="113" t="inlineStr">
+      <c r="E88" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F83" s="113">
-        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
-        <v/>
-      </c>
-      <c r="G83" s="82" t="inlineStr">
+      <c r="F88" s="113">
+        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="84" s="158">
-      <c r="A84" s="78" t="inlineStr">
+    <row r="89" s="158">
+      <c r="A89" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B84" s="78" t="inlineStr">
+      <c r="B89" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C84" s="77" t="n">
+      <c r="C89" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D84" s="79" t="n">
+      <c r="D89" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E84" s="112" t="inlineStr">
+      <c r="E89" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F84" s="112">
-        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
-        <v/>
-      </c>
-      <c r="G84" s="78" t="inlineStr">
+      <c r="F89" s="112">
+        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="85" s="158">
-      <c r="A85" s="82" t="inlineStr">
+    <row r="90" s="158">
+      <c r="A90" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B85" s="82" t="inlineStr">
+      <c r="B90" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C85" s="81" t="n">
+      <c r="C90" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D85" s="83" t="n">
+      <c r="D90" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E85" s="113" t="inlineStr">
+      <c r="E90" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F85" s="113">
-        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
-        <v/>
-      </c>
-      <c r="G85" s="82" t="inlineStr">
+      <c r="F90" s="113">
+        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="86" s="158">
-      <c r="A86" s="78" t="inlineStr">
+    <row r="91" s="158">
+      <c r="A91" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B86" s="78" t="inlineStr">
+      <c r="B91" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C86" s="77" t="n">
+      <c r="C91" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D86" s="79" t="n">
+      <c r="D91" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E86" s="112" t="inlineStr">
+      <c r="E91" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F86" s="112">
-        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
-        <v/>
-      </c>
-      <c r="G86" s="78" t="inlineStr">
+      <c r="F91" s="112">
+        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="87" s="158">
-      <c r="A87" s="82" t="inlineStr">
+    <row r="92" s="158">
+      <c r="A92" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B87" s="82" t="inlineStr">
+      <c r="B92" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C87" s="81" t="n">
+      <c r="C92" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D87" s="83" t="n">
+      <c r="D92" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E87" s="113" t="inlineStr">
+      <c r="E92" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F87" s="113">
-        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
-        <v/>
-      </c>
-      <c r="G87" s="82" t="inlineStr">
+      <c r="F92" s="113">
+        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="88" s="158">
-      <c r="A88" s="78" t="inlineStr">
+    <row r="93" s="158">
+      <c r="A93" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B88" s="78" t="inlineStr">
+      <c r="B93" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C88" s="77" t="n">
+      <c r="C93" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D88" s="79" t="n">
+      <c r="D93" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E88" s="112" t="inlineStr">
+      <c r="E93" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F88" s="112">
-        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
-        <v/>
-      </c>
-      <c r="G88" s="78" t="inlineStr">
+      <c r="F93" s="112">
+        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="89" s="158">
-      <c r="A89" s="82" t="inlineStr">
+    <row r="94" s="158">
+      <c r="A94" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B89" s="82" t="inlineStr">
+      <c r="B94" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C89" s="81" t="n">
+      <c r="C94" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D89" s="83" t="n">
+      <c r="D94" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E89" s="113" t="inlineStr">
+      <c r="E94" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F89" s="113">
-        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
-        <v/>
-      </c>
-      <c r="G89" s="82" t="inlineStr">
+      <c r="F94" s="113">
+        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="90" s="158">
-      <c r="A90" s="78" t="inlineStr">
+    <row r="95" s="158">
+      <c r="A95" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B90" s="78" t="inlineStr">
+      <c r="B95" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C90" s="77" t="n">
+      <c r="C95" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D90" s="79" t="n">
+      <c r="D95" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E90" s="112" t="inlineStr">
+      <c r="E95" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F90" s="112">
-        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
-        <v/>
-      </c>
-      <c r="G90" s="78" t="inlineStr">
+      <c r="F95" s="112">
+        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="91" s="158">
-      <c r="A91" s="82" t="inlineStr">
+    <row r="96" s="158">
+      <c r="A96" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B91" s="82" t="inlineStr">
+      <c r="B96" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C91" s="81" t="n">
+      <c r="C96" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D91" s="83" t="n">
+      <c r="D96" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E91" s="113" t="inlineStr">
+      <c r="E96" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F91" s="113">
-        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
-        <v/>
-      </c>
-      <c r="G91" s="82" t="inlineStr">
+      <c r="F96" s="113">
+        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="92" s="158">
-      <c r="A92" s="78" t="inlineStr">
+    <row r="97" s="158">
+      <c r="A97" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B92" s="78" t="inlineStr">
+      <c r="B97" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C92" s="77" t="n">
+      <c r="C97" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D92" s="79" t="n">
+      <c r="D97" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E92" s="112" t="inlineStr">
+      <c r="E97" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F92" s="112">
-        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
-        <v/>
-      </c>
-      <c r="G92" s="78" t="inlineStr">
+      <c r="F97" s="112">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="93" s="158">
-      <c r="A93" s="82" t="inlineStr">
+    <row r="98" s="158">
+      <c r="A98" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B93" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C98" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D93" s="83" t="n">
+      <c r="D98" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E93" s="113" t="inlineStr">
+      <c r="E98" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F93" s="113">
-        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
-        <v/>
-      </c>
-      <c r="G93" s="82" t="inlineStr">
+      <c r="F98" s="113">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="94" s="158">
-      <c r="A94" s="78" t="inlineStr">
+    <row r="99" s="158">
+      <c r="A99" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B94" s="78" t="inlineStr">
+      <c r="B99" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C94" s="77" t="n">
+      <c r="C99" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D94" s="79" t="n">
+      <c r="D99" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E94" s="112" t="inlineStr">
+      <c r="E99" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="112">
-        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
-        <v/>
-      </c>
-      <c r="G94" s="78" t="inlineStr">
+      <c r="F99" s="112">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="95" s="158">
-      <c r="A95" s="82" t="inlineStr">
+    <row r="100" s="158">
+      <c r="A100" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C100" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D95" s="83" t="n">
+      <c r="D100" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E95" s="113" t="inlineStr">
+      <c r="E100" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F95" s="113">
-        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
-        <v/>
-      </c>
-      <c r="G95" s="82" t="inlineStr">
+      <c r="F100" s="113">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="96" s="158">
-      <c r="A96" s="78" t="inlineStr">
+    <row r="101" s="158">
+      <c r="A101" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B96" s="78" t="inlineStr">
+      <c r="B101" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C96" s="77" t="n">
+      <c r="C101" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D96" s="79" t="n">
+      <c r="D101" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E96" s="112" t="inlineStr">
+      <c r="E101" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F96" s="112">
-        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
-        <v/>
-      </c>
-      <c r="G96" s="78" t="inlineStr">
+      <c r="F101" s="112">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="97" s="158">
-      <c r="A97" s="82" t="inlineStr">
+    <row r="102" s="158">
+      <c r="A102" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B102" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C97" s="81" t="n">
+      <c r="C102" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D97" s="83" t="n">
+      <c r="D102" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E97" s="113" t="inlineStr">
+      <c r="E102" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F97" s="113">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="82" t="inlineStr">
+      <c r="F102" s="113">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="98" s="158">
-      <c r="A98" s="78" t="inlineStr">
+    <row r="103" s="158">
+      <c r="A103" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B98" s="78" t="inlineStr">
+      <c r="B103" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C98" s="77" t="n">
+      <c r="C103" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D98" s="79" t="n">
+      <c r="D103" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E98" s="112" t="inlineStr">
+      <c r="E103" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="112">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="78" t="inlineStr">
+      <c r="F103" s="112">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="99" s="158">
-      <c r="A99" s="82" t="inlineStr">
+    <row r="104" s="158">
+      <c r="A104" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B104" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C99" s="81" t="n">
+      <c r="C104" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D99" s="83" t="n">
+      <c r="D104" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E99" s="113" t="inlineStr">
+      <c r="E104" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F99" s="113">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="82" t="inlineStr">
+      <c r="F104" s="113">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
         </is>
       </c>
     </row>
-    <row r="100" s="158">
-      <c r="A100" s="78" t="inlineStr">
+    <row r="105" s="158">
+      <c r="A105" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B100" s="78" t="inlineStr">
+      <c r="B105" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C100" s="77" t="n">
+      <c r="C105" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D100" s="79" t="n">
+      <c r="D105" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E100" s="112" t="inlineStr">
+      <c r="E105" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F100" s="112">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="78" t="inlineStr">
+      <c r="F105" s="112">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" s="158">
-      <c r="A101" s="82" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="B101" s="82" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C101" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D101" s="83" t="n">
-        <v>160</v>
-      </c>
-      <c r="E101" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F101" s="113">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" s="158">
-      <c r="A102" s="78" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B102" s="78" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C102" s="77" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D102" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="E102" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F102" s="112">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" s="158">
-      <c r="A103" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B103" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C103" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D103" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E103" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F103" s="113">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" s="158">
-      <c r="A104" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B104" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C104" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D104" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E104" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F104" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" s="158">
-      <c r="A105" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B105" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C105" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D105" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E105" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F105" s="113">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="106" s="158">
       <c r="A106" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>Instituto Paulo Leão</t>
         </is>
       </c>
       <c r="B106" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
       <c r="C106" s="81" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D106" s="83" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="E106" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F106" s="113">
@@ -48191,26 +48193,26 @@
       </c>
       <c r="G106" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="107" s="158">
       <c r="A107" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
       <c r="B107" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="C107" s="77" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D107" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E107" s="112" t="inlineStr">
         <is>
@@ -48223,58 +48225,58 @@
       </c>
       <c r="G107" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="108" s="158">
-      <c r="A108" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B108" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C108" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D108" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E108" s="112" t="inlineStr">
+      <c r="A108" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B108" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C108" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D108" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E108" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="112">
+      <c r="F108" s="113">
         <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
         <v/>
       </c>
-      <c r="G108" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+      <c r="G108" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="109" s="158">
       <c r="A109" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B109" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C109" s="77" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="D109" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E109" s="112" t="inlineStr">
         <is>
@@ -48292,85 +48294,85 @@
       </c>
     </row>
     <row r="110" s="158">
-      <c r="A110" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B110" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C110" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D110" s="79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E110" s="112" t="inlineStr">
+      <c r="A110" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B110" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C110" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D110" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E110" s="113" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F110" s="113">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" s="158">
+      <c r="A111" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B111" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C111" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D111" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E111" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F110" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="78" t="inlineStr">
-        <is>
-          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" s="158">
-      <c r="A111" s="78" t="inlineStr">
-        <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
-        </is>
-      </c>
-      <c r="B111" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C111" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D111" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E111" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F111" s="112">
+      <c r="F111" s="113">
         <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
         <v/>
       </c>
-      <c r="G111" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+      <c r="G111" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
         </is>
       </c>
     </row>
     <row r="112" s="158">
       <c r="A112" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B112" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C112" s="77" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="D112" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E112" s="112" t="inlineStr">
         <is>
@@ -48383,30 +48385,30 @@
       </c>
       <c r="G112" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="113" s="158">
       <c r="A113" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B113" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C113" s="77" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="D113" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E113" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F113" s="112">
@@ -48415,23 +48417,23 @@
       </c>
       <c r="G113" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="114" s="158">
       <c r="A114" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B114" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C114" s="77" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D114" s="79" t="n">
         <v>140</v>
@@ -48447,30 +48449,30 @@
       </c>
       <c r="G114" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="115" s="158">
       <c r="A115" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B115" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C115" s="77" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D115" s="79" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E115" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F115" s="112">
@@ -48479,30 +48481,30 @@
       </c>
       <c r="G115" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
         </is>
       </c>
     </row>
     <row r="116" s="158">
       <c r="A116" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B116" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C116" s="77" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D116" s="79" t="n">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E116" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F116" s="112">
@@ -48511,14 +48513,14 @@
       </c>
       <c r="G116" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="117" s="158">
       <c r="A117" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B117" s="78" t="inlineStr">
@@ -48527,14 +48529,14 @@
         </is>
       </c>
       <c r="C117" s="77" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="D117" s="79" t="n">
         <v>200</v>
       </c>
       <c r="E117" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F117" s="112">
@@ -48543,74 +48545,241 @@
       </c>
       <c r="G117" s="78" t="inlineStr">
         <is>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" s="158">
+      <c r="A118" s="78" t="inlineStr">
+        <is>
+          <t>Topvel Tropical Veiculos e Pecas</t>
+        </is>
+      </c>
+      <c r="B118" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C118" s="77" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D118" s="79" t="n">
+        <v>370</v>
+      </c>
+      <c r="E118" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F118" s="112">
+        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" s="158">
+      <c r="A119" s="78" t="inlineStr">
+        <is>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
+        </is>
+      </c>
+      <c r="B119" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C119" s="77" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D119" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E119" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F119" s="112">
+        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 11/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" s="158">
+      <c r="A120" s="78" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="B120" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C120" s="77" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D120" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E120" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F120" s="112">
+        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
+        <v/>
+      </c>
+      <c r="G120" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 14/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" s="158">
+      <c r="A121" s="78" t="inlineStr">
+        <is>
+          <t>Clínica Santa Cecília</t>
+        </is>
+      </c>
+      <c r="B121" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Termostato</t>
+        </is>
+      </c>
+      <c r="C121" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D121" s="79" t="n">
+        <v>310</v>
+      </c>
+      <c r="E121" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F121" s="112">
+        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
+        <v/>
+      </c>
+      <c r="G121" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" s="158">
+      <c r="A122" s="78" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="B122" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C122" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D122" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E122" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F122" s="112">
+        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
+        <v/>
+      </c>
+      <c r="G122" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 18/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="118" s="158">
-      <c r="A118" s="86" t="inlineStr">
+    <row r="123" s="158">
+      <c r="A123" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D118" s="115">
-        <f>SUMIF(E78:E117,"Pendente",D78:D117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" s="158">
-      <c r="A119" s="205" t="inlineStr">
+      <c r="D123" s="115">
+        <f>SUMIF(E83:E122,"Pendente",D83:D122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" s="158">
+      <c r="A124" s="205" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B119" s="160" t="n"/>
-      <c r="C119" s="160" t="n"/>
-      <c r="D119" s="160" t="n"/>
-      <c r="E119" s="160" t="n"/>
-      <c r="F119" s="160" t="n"/>
-      <c r="G119" s="161" t="n"/>
-    </row>
-    <row r="120" s="158">
-      <c r="A120" s="202">
-        <f>IF(ROUND(D118-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D118-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" s="158">
-      <c r="A121" s="202" t="inlineStr">
+      <c r="B124" s="160" t="n"/>
+      <c r="C124" s="160" t="n"/>
+      <c r="D124" s="160" t="n"/>
+      <c r="E124" s="160" t="n"/>
+      <c r="F124" s="160" t="n"/>
+      <c r="G124" s="161" t="n"/>
+    </row>
+    <row r="125" s="158">
+      <c r="A125" s="202">
+        <f>IF(ROUND(D123-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D123-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" s="158">
+      <c r="A126" s="202" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="122" s="158"/>
-    <row r="123" s="158"/>
-    <row r="124" s="158"/>
-    <row r="125" s="158"/>
-    <row r="126" s="158"/>
     <row r="127" s="158"/>
+    <row r="128" s="158"/>
+    <row r="129" s="158"/>
+    <row r="130" s="158"/>
+    <row r="131" s="158"/>
+    <row r="132" s="158"/>
+    <row r="133" s="158"/>
+    <row r="134" s="158"/>
+    <row r="135" s="158"/>
+    <row r="136" s="158"/>
+    <row r="137" s="158"/>
+    <row r="138" s="158"/>
+    <row r="139" s="158"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A119:G119"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A120:G120"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A124:G124"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E78:E117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E83:E122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -38012,7 +38012,7 @@
     </row>
     <row r="66">
       <c r="A66" s="81" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B66" s="82" t="inlineStr">
         <is>
@@ -38035,7 +38035,11 @@
       <c r="F66" s="83" t="n"/>
       <c r="G66" s="83" t="n"/>
       <c r="H66" s="82" t="n"/>
-      <c r="I66" s="82" t="n"/>
+      <c r="I66" s="82" t="inlineStr">
+        <is>
+          <t>Venda de 09/09/2026 — pagamento recebido em dinheiro em 16/09/2026</t>
+        </is>
+      </c>
       <c r="J66" s="82" t="inlineStr">
         <is>
           <t>EMP-0188</t>
@@ -39943,7 +39947,7 @@
     </row>
     <row r="132">
       <c r="A132" s="81" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B132" s="82" t="inlineStr">
         <is>
@@ -39960,13 +39964,17 @@
       </c>
       <c r="E132" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F132" s="83" t="n"/>
       <c r="G132" s="83" t="n"/>
       <c r="H132" s="82" t="n"/>
-      <c r="I132" s="82" t="n"/>
+      <c r="I132" s="82" t="inlineStr">
+        <is>
+          <t>Venda de 18/09/2026 — pagamento recebido via Pix em 19/09/2026</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>CLI-0388</t>
@@ -45179,7 +45187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -48472,7 +48480,7 @@
       </c>
       <c r="E115" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F115" s="112">
@@ -48481,7 +48489,7 @@
       </c>
       <c r="G115" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/09/2026 — refil plissado + BAG.</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48704,7 @@
       </c>
       <c r="E122" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F122" s="112">
@@ -48705,7 +48713,7 @@
       </c>
       <c r="G122" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 18/09/2026.</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
@@ -48764,8 +48772,8 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A124:G124"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -47199,7 +47199,7 @@
         <v>46286</v>
       </c>
       <c r="D70" s="83" t="n">
-        <v>591.12</v>
+        <v>592.89</v>
       </c>
       <c r="E70" s="113" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
       </c>
       <c r="G70" s="82" t="inlineStr">
         <is>
-          <t>Boleto impresso com vencimento 18/09/2026 — pagamento adiado para 21/09/2026 (segunda): após o vencimento só pode ser pago no Itaú, com multa de 1,9% + juros de 0,1% ao dia (cerca de R$ 604,12 em 21/09). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259098-0. Linha digitável 34191.09008 25909.801430 81531.550002 1 15730000059112. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Boleto substituído pela 2ª via emitida em 21/09/2026 (original: venc. 18/09/2026, R$ 591,12 — pagamento adiado para segunda 21/09). A 2ª via vale SOMENTE para 21/09/2026; se não pagar hoje, precisa gerar outra. Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/15315-5. Nosso número 109/00259098-5. Linha digitável 34191.09008 25909.801430 81531.550002 7 15760000059289. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -35790,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:U168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +35955,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H162,K5,G5:G162)</f>
+        <f>SUMIF(H5:H166,K5,G5:G166)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D163-F163-T5</f>
+        <f>D167-F167-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D164</f>
+        <f>D168</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E162,"Aguardando Pagamento",D5:D162)</f>
+        <f>SUMIF(E5:E166,"Aguardando Pagamento",D5:D166)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H162,K6,G5:G162)</f>
+        <f>SUMIF(H5:H166,K6,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36056,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H162,K7,G5:G162)</f>
+        <f>SUMIF(H5:H166,K7,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H162,K8,G5:G162)</f>
+        <f>SUMIF(H5:H166,K8,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H162,K9,G5:G162)</f>
+        <f>SUMIF(H5:H166,K9,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H162,K10,G5:G162)</f>
+        <f>SUMIF(H5:H166,K10,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H162,K11,G5:G162)</f>
+        <f>SUMIF(H5:H166,K11,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H162,K12,G5:G162)</f>
+        <f>SUMIF(H5:H166,K12,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H162,K13,G5:G162)</f>
+        <f>SUMIF(H5:H166,K13,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H162,K14,G5:G162)</f>
+        <f>SUMIF(H5:H166,K14,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H162,K15,G5:G162)</f>
+        <f>SUMIF(H5:H166,K15,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H162,K16,G5:G162)</f>
+        <f>SUMIF(H5:H166,K16,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H162,K17,G5:G162)</f>
+        <f>SUMIF(H5:H166,K17,G5:G166)</f>
         <v/>
       </c>
     </row>
@@ -40826,43 +40826,166 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="29" t="n"/>
-      <c r="B163" s="43" t="inlineStr">
+      <c r="A163" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B163" s="78" t="inlineStr">
+        <is>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+      <c r="C163" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D163" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E163" s="78" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F163" s="79" t="n"/>
+      <c r="G163" s="79" t="n"/>
+      <c r="H163" s="78" t="n"/>
+      <c r="I163" s="78" t="n"/>
+      <c r="J163" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0032</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B164" s="82" t="inlineStr">
+        <is>
+          <t>Josimar Souza Santos</t>
+        </is>
+      </c>
+      <c r="C164" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D164" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E164" s="82" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F164" s="83" t="n"/>
+      <c r="G164" s="83" t="n"/>
+      <c r="H164" s="82" t="n"/>
+      <c r="I164" s="82" t="n"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>CLI-0367</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B165" s="78" t="inlineStr">
+        <is>
+          <t>Cleone Gomes de Andrade</t>
+        </is>
+      </c>
+      <c r="C165" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D165" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E165" s="78" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
+      <c r="F165" s="79" t="n"/>
+      <c r="G165" s="79" t="n"/>
+      <c r="H165" s="78" t="n"/>
+      <c r="I165" s="78" t="n"/>
+      <c r="J165" s="78" t="inlineStr">
+        <is>
+          <t>CLI-0296</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B166" s="82" t="inlineStr">
+        <is>
+          <t>Combustível (Etanol) — Transvale</t>
+        </is>
+      </c>
+      <c r="C166" s="82" t="n"/>
+      <c r="D166" s="83" t="n"/>
+      <c r="E166" s="82" t="n"/>
+      <c r="F166" s="83" t="n"/>
+      <c r="G166" s="83" t="n">
+        <v>50</v>
+      </c>
+      <c r="H166" s="82" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I166" s="82" t="inlineStr">
+        <is>
+          <t>10,31 L de etanol hidratado a R$ 4,85/L — NFC-e nº 000284718 (Transvale Derivados de Petróleo, CNPJ 11.271.229/0002-68). Pago em dinheiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="29" t="n"/>
+      <c r="B167" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C163" s="161" t="n"/>
-      <c r="D163" s="8">
-        <f>SUM(D5:D162)</f>
-        <v/>
-      </c>
-      <c r="E163" s="8" t="n"/>
-      <c r="F163" s="29">
-        <f>SUM(F5:F162)</f>
-        <v/>
-      </c>
-      <c r="G163" s="8">
-        <f>SUM(G5:G162)</f>
-        <v/>
-      </c>
-      <c r="H163" s="29" t="n"/>
-      <c r="I163" s="29" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="30" t="n"/>
-      <c r="B164" s="135" t="inlineStr">
+      <c r="C167" s="161" t="n"/>
+      <c r="D167" s="8">
+        <f>SUM(D5:D166)</f>
+        <v/>
+      </c>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="29">
+        <f>SUM(F5:F166)</f>
+        <v/>
+      </c>
+      <c r="G167" s="8">
+        <f>SUM(G5:G166)</f>
+        <v/>
+      </c>
+      <c r="H167" s="29" t="n"/>
+      <c r="I167" s="29" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="30" t="n"/>
+      <c r="B168" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D164" s="134">
-        <f>(D163-F163-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F164" s="30" t="n"/>
-      <c r="H164" s="30" t="n"/>
-      <c r="I164" s="30" t="n"/>
+      <c r="D168" s="134">
+        <f>(D167-F167-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F168" s="30" t="n"/>
+      <c r="H168" s="30" t="n"/>
+      <c r="I168" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -40879,10 +41002,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -45187,7 +45310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="158" min="1" max="1"/>
@@ -48718,44 +48841,106 @@
       </c>
     </row>
     <row r="123" s="158">
-      <c r="A123" s="86" t="inlineStr">
+      <c r="A123" s="78" t="inlineStr">
+        <is>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+      <c r="B123" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C123" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D123" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E123" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F123" s="112">
+        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
+        <v/>
+      </c>
+      <c r="G123" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" s="158">
+      <c r="A124" s="78" t="inlineStr">
+        <is>
+          <t>Cleone Gomes de Andrade</t>
+        </is>
+      </c>
+      <c r="B124" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C124" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D124" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E124" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F124" s="112">
+        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
+        <v/>
+      </c>
+      <c r="G124" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" s="158">
+      <c r="A125" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D123" s="115">
-        <f>SUMIF(E83:E122,"Pendente",D83:D122)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" s="158">
-      <c r="A124" s="205" t="inlineStr">
+      <c r="D125" s="115">
+        <f>SUMIF(E83:E124,"Pendente",D83:D124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" s="158">
+      <c r="A126" s="205" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B124" s="160" t="n"/>
-      <c r="C124" s="160" t="n"/>
-      <c r="D124" s="160" t="n"/>
-      <c r="E124" s="160" t="n"/>
-      <c r="F124" s="160" t="n"/>
-      <c r="G124" s="161" t="n"/>
-    </row>
-    <row r="125" s="158">
-      <c r="A125" s="202">
-        <f>IF(ROUND(D123-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D123-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" s="158">
-      <c r="A126" s="202" t="inlineStr">
+      <c r="B126" s="160" t="n"/>
+      <c r="C126" s="160" t="n"/>
+      <c r="D126" s="160" t="n"/>
+      <c r="E126" s="160" t="n"/>
+      <c r="F126" s="160" t="n"/>
+      <c r="G126" s="161" t="n"/>
+    </row>
+    <row r="127" s="158">
+      <c r="A127" s="202">
+        <f>IF(ROUND(D125-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D125-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" s="158">
+      <c r="A128" s="202" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="127" s="158"/>
-    <row r="128" s="158"/>
     <row r="129" s="158"/>
     <row r="130" s="158"/>
     <row r="131" s="158"/>
@@ -48774,12 +48959,12 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A126:G126"/>
+    <mergeCell ref="A127:G127"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A125:G125"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -48787,7 +48972,7 @@
     <dataValidation sqref="E11:E74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E83:E122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E83:E124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -35790,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U168"/>
+  <dimension ref="A1:U172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +35955,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H166,K5,G5:G166)</f>
+        <f>SUMIF(H5:H170,K5,G5:G170)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D167-F167-T5</f>
+        <f>D171-F171-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +35967,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D168</f>
+        <f>D172</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E166,"Aguardando Pagamento",D5:D166)</f>
+        <f>SUMIF(E5:E170,"Aguardando Pagamento",D5:D170)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H166,K6,G5:G166)</f>
+        <f>SUMIF(H5:H170,K6,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36056,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H166,K7,G5:G166)</f>
+        <f>SUMIF(H5:H170,K7,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H166,K8,G5:G166)</f>
+        <f>SUMIF(H5:H170,K8,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H166,K9,G5:G166)</f>
+        <f>SUMIF(H5:H170,K9,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H166,K10,G5:G166)</f>
+        <f>SUMIF(H5:H170,K10,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H166,K11,G5:G166)</f>
+        <f>SUMIF(H5:H170,K11,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H166,K12,G5:G166)</f>
+        <f>SUMIF(H5:H170,K12,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H166,K13,G5:G166)</f>
+        <f>SUMIF(H5:H170,K13,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H166,K14,G5:G166)</f>
+        <f>SUMIF(H5:H170,K14,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H166,K15,G5:G166)</f>
+        <f>SUMIF(H5:H170,K15,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H166,K16,G5:G166)</f>
+        <f>SUMIF(H5:H170,K16,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H166,K17,G5:G166)</f>
+        <f>SUMIF(H5:H170,K17,G5:G170)</f>
         <v/>
       </c>
     </row>
@@ -40949,43 +40949,153 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="29" t="n"/>
-      <c r="B167" s="43" t="inlineStr">
+      <c r="A167" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B167" s="78" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C167" s="78" t="n"/>
+      <c r="D167" s="79" t="n"/>
+      <c r="E167" s="78" t="n"/>
+      <c r="F167" s="79" t="n"/>
+      <c r="G167" s="79" t="n">
+        <v>592.89</v>
+      </c>
+      <c r="H167" s="78" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I167" s="78" t="inlineStr">
+        <is>
+          <t>Boleto doc. 133812/001 (emissão 28/08/2026) · parcela 1/4 — 2ª via com venc. 21/09/2026 (original R$ 591,12 venc. 18/09). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
+      <c r="J167" s="78" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B168" s="82" t="inlineStr">
+        <is>
+          <t>Receita Federal — Simples Nacional (DAS)</t>
+        </is>
+      </c>
+      <c r="C168" s="82" t="n"/>
+      <c r="D168" s="83" t="n"/>
+      <c r="E168" s="82" t="n"/>
+      <c r="F168" s="83" t="n"/>
+      <c r="G168" s="83" t="n">
+        <v>1958.02</v>
+      </c>
+      <c r="H168" s="82" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I168" s="82" t="inlineStr">
+        <is>
+          <t>DAS competência agosto/2026 (doc. 07.20.26260.6017058-0) — venc. 21/09/2026. Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B169" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
+      <c r="C169" s="78" t="n"/>
+      <c r="D169" s="79" t="n"/>
+      <c r="E169" s="78" t="n"/>
+      <c r="F169" s="79" t="n"/>
+      <c r="G169" s="79" t="n">
+        <v>874.6799999999999</v>
+      </c>
+      <c r="H169" s="78" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I169" s="78" t="inlineStr">
+        <is>
+          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 3/5 — venc. 20/09/2026 (domingo). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
+      <c r="J169" s="78" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B170" s="82" t="inlineStr">
+        <is>
+          <t>Diarista</t>
+        </is>
+      </c>
+      <c r="C170" s="82" t="n"/>
+      <c r="D170" s="83" t="n"/>
+      <c r="E170" s="82" t="n"/>
+      <c r="F170" s="83" t="n"/>
+      <c r="G170" s="83" t="n">
+        <v>340</v>
+      </c>
+      <c r="H170" s="82" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I170" s="82" t="inlineStr">
+        <is>
+          <t>Pagamento de diarista — despesa pessoal (Edilânia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="29" t="n"/>
+      <c r="B171" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C167" s="161" t="n"/>
-      <c r="D167" s="8">
-        <f>SUM(D5:D166)</f>
-        <v/>
-      </c>
-      <c r="E167" s="8" t="n"/>
-      <c r="F167" s="29">
-        <f>SUM(F5:F166)</f>
-        <v/>
-      </c>
-      <c r="G167" s="8">
-        <f>SUM(G5:G166)</f>
-        <v/>
-      </c>
-      <c r="H167" s="29" t="n"/>
-      <c r="I167" s="29" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="30" t="n"/>
-      <c r="B168" s="135" t="inlineStr">
+      <c r="C171" s="161" t="n"/>
+      <c r="D171" s="8">
+        <f>SUM(D5:D170)</f>
+        <v/>
+      </c>
+      <c r="E171" s="8" t="n"/>
+      <c r="F171" s="29">
+        <f>SUM(F5:F170)</f>
+        <v/>
+      </c>
+      <c r="G171" s="8">
+        <f>SUM(G5:G170)</f>
+        <v/>
+      </c>
+      <c r="H171" s="29" t="n"/>
+      <c r="I171" s="29" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="30" t="n"/>
+      <c r="B172" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D168" s="134">
-        <f>(D167-F167-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F168" s="30" t="n"/>
-      <c r="H168" s="30" t="n"/>
-      <c r="I168" s="30" t="n"/>
+      <c r="D172" s="134">
+        <f>(D171-F171-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F172" s="30" t="n"/>
+      <c r="H172" s="30" t="n"/>
+      <c r="I172" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -41002,10 +41112,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -46334,7 +46444,7 @@
       </c>
       <c r="E39" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F39" s="112">
@@ -46343,7 +46453,7 @@
       </c>
       <c r="G39" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528668-7. Linha digitável 34191.12259 52866.870307 52238.850003 7 15750000087468. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528668-7. Linha digitável 34191.12259 52866.870307 52238.850003 7 15750000087468. Após o vencimento: juros ao dia + multa de 2%. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -47230,7 +47340,7 @@
       </c>
       <c r="E67" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F67" s="113">
@@ -47239,7 +47349,7 @@
       </c>
       <c r="G67" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas. Planeta Agua Ltda, CNPJ 07.341.784/0001-60. Detalhe: IRPJ R$ 187,69 · CSLL R$ 88,53 · COFINS R$ 249,45 · PIS R$ 54,04 · INSS R$ 822,37 · ICMS (BA) R$ 655,94. Linha digitável 85860000019 5 58020328262 0 64072026260 4 60170580750 5.</t>
+          <t>Categoria: Impostos e Taxas. Planeta Agua Ltda, CNPJ 07.341.784/0001-60. Detalhe: IRPJ R$ 187,69 · CSLL R$ 88,53 · COFINS R$ 249,45 · PIS R$ 54,04 · INSS R$ 822,37 · ICMS (BA) R$ 655,94. Linha digitável 85860000019 5 58020328262 0 64072026260 4 60170580750 5. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Receita Federal — Simples Nacional (DAS)".</t>
         </is>
       </c>
     </row>
@@ -47326,7 +47436,7 @@
       </c>
       <c r="E70" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F70" s="113">
@@ -47335,7 +47445,7 @@
       </c>
       <c r="G70" s="82" t="inlineStr">
         <is>
-          <t>Boleto substituído pela 2ª via emitida em 21/09/2026 (original: venc. 18/09/2026, R$ 591,12 — pagamento adiado para segunda 21/09). A 2ª via vale SOMENTE para 21/09/2026; se não pagar hoje, precisa gerar outra. Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/15315-5. Nosso número 109/00259098-5. Linha digitável 34191.09008 25909.801430 81531.550002 7 15760000059289. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Boleto substituído pela 2ª via emitida em 21/09/2026 (original: venc. 18/09/2026, R$ 591,12 — pagamento adiado para segunda 21/09). A 2ª via vale SOMENTE para 21/09/2026; se não pagar hoje, precisa gerar outra. Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/15315-5. Nosso número 109/00259098-5. Linha digitável 34191.09008 25909.801430 81531.550002 7 15760000059289. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -30361,7 +30361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U187"/>
+  <dimension ref="A1:U189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="13" bestFit="1" customWidth="1" style="158" min="1" max="1"/>
@@ -30525,11 +30525,11 @@
         </is>
       </c>
       <c r="L5" s="11">
-        <f>SUMIF(H5:H182,K5,G5:G182)</f>
+        <f>SUMIF(H5:H184,K5,G5:G184)</f>
         <v/>
       </c>
       <c r="N5" s="231">
-        <f>D183-F183-T5</f>
+        <f>D185-F185-T5</f>
         <v/>
       </c>
       <c r="P5" s="233">
@@ -30537,11 +30537,11 @@
         <v/>
       </c>
       <c r="R5" s="232">
-        <f>D184</f>
+        <f>D186</f>
         <v/>
       </c>
       <c r="T5" s="213">
-        <f>SUMIF(E5:E182,"Aguardando Pagamento",D5:D182)</f>
+        <f>SUMIF(E5:E184,"Aguardando Pagamento",D5:D184)</f>
         <v/>
       </c>
     </row>
@@ -30579,7 +30579,7 @@
         </is>
       </c>
       <c r="L6" s="14">
-        <f>SUMIF(H5:H182,K6,G5:G182)</f>
+        <f>SUMIF(H5:H184,K6,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30615,7 +30615,7 @@
         </is>
       </c>
       <c r="L7" s="11">
-        <f>SUMIF(H5:H182,K7,G5:G182)</f>
+        <f>SUMIF(H5:H184,K7,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30647,7 +30647,7 @@
         </is>
       </c>
       <c r="L8" s="14">
-        <f>SUMIF(H5:H182,K8,G5:G182)</f>
+        <f>SUMIF(H5:H184,K8,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
         </is>
       </c>
       <c r="L9" s="11">
-        <f>SUMIF(H5:H182,K9,G5:G182)</f>
+        <f>SUMIF(H5:H184,K9,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30719,7 +30719,7 @@
         </is>
       </c>
       <c r="L10" s="14">
-        <f>SUMIF(H5:H182,K10,G5:G182)</f>
+        <f>SUMIF(H5:H184,K10,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30751,7 +30751,7 @@
         </is>
       </c>
       <c r="L11" s="11">
-        <f>SUMIF(H5:H182,K11,G5:G182)</f>
+        <f>SUMIF(H5:H184,K11,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="L12" s="14">
-        <f>SUMIF(H5:H182,K12,G5:G182)</f>
+        <f>SUMIF(H5:H184,K12,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30824,7 +30824,7 @@
         </is>
       </c>
       <c r="L13" s="11">
-        <f>SUMIF(H5:H182,K13,G5:G182)</f>
+        <f>SUMIF(H5:H184,K13,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30856,7 +30856,7 @@
         </is>
       </c>
       <c r="L14" s="14">
-        <f>SUMIF(H5:H182,K14,G5:G182)</f>
+        <f>SUMIF(H5:H184,K14,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30888,7 +30888,7 @@
         </is>
       </c>
       <c r="L15" s="11">
-        <f>SUMIF(H5:H182,K15,G5:G182)</f>
+        <f>SUMIF(H5:H184,K15,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30920,7 +30920,7 @@
         </is>
       </c>
       <c r="L16" s="11">
-        <f>SUMIF(H5:H182,K16,G5:G182)</f>
+        <f>SUMIF(H5:H184,K16,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -30961,7 +30961,7 @@
         </is>
       </c>
       <c r="L17">
-        <f>SUMIF(H5:H182,K17,G5:G182)</f>
+        <f>SUMIF(H5:H184,K17,G5:G184)</f>
         <v/>
       </c>
     </row>
@@ -33065,7 +33065,11 @@
       </c>
       <c r="G89" s="19" t="n"/>
       <c r="H89" s="21" t="n"/>
-      <c r="I89" s="18" t="n"/>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 3x.</t>
+        </is>
+      </c>
       <c r="J89" s="18" t="inlineStr">
         <is>
           <t>CLI-0362</t>
@@ -35699,59 +35703,117 @@
       <c r="I182" s="45" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="29" t="n"/>
-      <c r="B183" s="43" t="inlineStr">
+      <c r="A183" s="17" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>Cliente de Armando</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="n"/>
+      <c r="D183" s="136" t="n">
+        <v>160</v>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F183" s="19" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="G183" s="20" t="n"/>
+      <c r="H183" s="21" t="n"/>
+      <c r="I183" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 3x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1" s="158">
+      <c r="A184" s="44" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B184" s="45" t="inlineStr">
+        <is>
+          <t>Cliente de Armando</t>
+        </is>
+      </c>
+      <c r="C184" s="45" t="n"/>
+      <c r="D184" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="E184" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F184" s="47" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="G184" s="47" t="n"/>
+      <c r="H184" s="49" t="n"/>
+      <c r="I184" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 2x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="29" t="n"/>
+      <c r="B185" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C183" s="161" t="n"/>
-      <c r="D183" s="8">
-        <f>SUM(D5:D182)</f>
-        <v/>
-      </c>
-      <c r="E183" s="8" t="n"/>
-      <c r="F183" s="29">
-        <f>SUM(F5:F182)</f>
-        <v/>
-      </c>
-      <c r="G183" s="8">
-        <f>SUM(G5:G182)</f>
-        <v/>
-      </c>
-      <c r="H183" s="29" t="n"/>
-      <c r="I183" s="29" t="n"/>
-      <c r="K183" s="31" t="n"/>
-      <c r="L183" s="31" t="n"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1" s="158">
-      <c r="A184" s="30" t="n"/>
-      <c r="B184" s="135" t="inlineStr">
-        <is>
-          <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
-        </is>
-      </c>
-      <c r="D184" s="134">
-        <f>(D183-F183-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F184" s="30" t="n"/>
-      <c r="H184" s="30" t="n"/>
-      <c r="I184" s="30" t="n"/>
-      <c r="K184" s="31" t="n"/>
-      <c r="L184" s="31" t="n"/>
-    </row>
-    <row r="185">
+      <c r="C185" s="161" t="n"/>
+      <c r="D185" s="8">
+        <f>SUM(D5:D184)</f>
+        <v/>
+      </c>
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="29">
+        <f>SUM(F5:F184)</f>
+        <v/>
+      </c>
+      <c r="G185" s="8">
+        <f>SUM(G5:G184)</f>
+        <v/>
+      </c>
+      <c r="H185" s="29" t="n"/>
+      <c r="I185" s="29" t="n"/>
       <c r="K185" s="31" t="n"/>
       <c r="L185" s="31" t="n"/>
     </row>
     <row r="186">
+      <c r="A186" s="30" t="n"/>
+      <c r="B186" s="135" t="inlineStr">
+        <is>
+          <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
+        </is>
+      </c>
+      <c r="D186" s="134">
+        <f>(D185-F185-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F186" s="30" t="n"/>
+      <c r="H186" s="30" t="n"/>
+      <c r="I186" s="30" t="n"/>
       <c r="K186" s="31" t="n"/>
       <c r="L186" s="31" t="n"/>
     </row>
     <row r="187">
       <c r="K187" s="31" t="n"/>
       <c r="L187" s="31" t="n"/>
+    </row>
+    <row r="188">
+      <c r="K188" s="31" t="n"/>
+      <c r="L188" s="31" t="n"/>
+    </row>
+    <row r="189">
+      <c r="K189" s="31" t="n"/>
+      <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -35790,7 +35852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U172"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="158" min="1" max="1"/>
@@ -35955,11 +36017,11 @@
         </is>
       </c>
       <c r="L5" s="80">
-        <f>SUMIF(H5:H170,K5,G5:G170)</f>
+        <f>SUMIF(H5:H174,K5,G5:G174)</f>
         <v/>
       </c>
       <c r="N5" s="238">
-        <f>D171-F171-T5</f>
+        <f>D175-F175-T5</f>
         <v/>
       </c>
       <c r="P5" s="190">
@@ -35967,11 +36029,11 @@
         <v/>
       </c>
       <c r="R5" s="204">
-        <f>D172</f>
+        <f>D176</f>
         <v/>
       </c>
       <c r="T5" s="203">
-        <f>SUMIF(E5:E170,"Aguardando Pagamento",D5:D170)</f>
+        <f>SUMIF(E5:E174,"Aguardando Pagamento",D5:D174)</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36073,7 @@
         </is>
       </c>
       <c r="L6" s="80">
-        <f>SUMIF(H5:H170,K6,G5:G170)</f>
+        <f>SUMIF(H5:H174,K6,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36056,7 +36118,7 @@
         </is>
       </c>
       <c r="L7" s="80">
-        <f>SUMIF(H5:H170,K7,G5:G170)</f>
+        <f>SUMIF(H5:H174,K7,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36096,7 +36158,7 @@
         </is>
       </c>
       <c r="L8" s="80">
-        <f>SUMIF(H5:H170,K8,G5:G170)</f>
+        <f>SUMIF(H5:H174,K8,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36141,7 +36203,7 @@
         </is>
       </c>
       <c r="L9" s="80">
-        <f>SUMIF(H5:H170,K9,G5:G170)</f>
+        <f>SUMIF(H5:H174,K9,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36181,7 +36243,7 @@
         </is>
       </c>
       <c r="L10" s="80">
-        <f>SUMIF(H5:H170,K10,G5:G170)</f>
+        <f>SUMIF(H5:H174,K10,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36221,7 +36283,7 @@
         </is>
       </c>
       <c r="L11" s="80">
-        <f>SUMIF(H5:H170,K11,G5:G170)</f>
+        <f>SUMIF(H5:H174,K11,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36261,7 +36323,7 @@
         </is>
       </c>
       <c r="L12" s="80">
-        <f>SUMIF(H5:H170,K12,G5:G170)</f>
+        <f>SUMIF(H5:H174,K12,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36302,7 +36364,7 @@
         </is>
       </c>
       <c r="L13" s="80">
-        <f>SUMIF(H5:H170,K13,G5:G170)</f>
+        <f>SUMIF(H5:H174,K13,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36409,7 @@
         </is>
       </c>
       <c r="L14" s="80">
-        <f>SUMIF(H5:H170,K14,G5:G170)</f>
+        <f>SUMIF(H5:H174,K14,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36392,7 +36454,7 @@
         </is>
       </c>
       <c r="L15" s="80">
-        <f>SUMIF(H5:H170,K15,G5:G170)</f>
+        <f>SUMIF(H5:H174,K15,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36433,7 +36495,7 @@
         </is>
       </c>
       <c r="L16" s="80">
-        <f>SUMIF(H5:H170,K16,G5:G170)</f>
+        <f>SUMIF(H5:H174,K16,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -36478,7 +36540,7 @@
         </is>
       </c>
       <c r="L17" s="85">
-        <f>SUMIF(H5:H170,K17,G5:G170)</f>
+        <f>SUMIF(H5:H174,K17,G5:G174)</f>
         <v/>
       </c>
     </row>
@@ -40908,7 +40970,7 @@
       </c>
       <c r="E165" s="78" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F165" s="79" t="n"/>
@@ -41059,43 +41121,153 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="29" t="n"/>
-      <c r="B171" s="43" t="inlineStr">
+      <c r="A171" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B171" s="78" t="inlineStr">
+        <is>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C171" s="78" t="n"/>
+      <c r="D171" s="79" t="n">
+        <v>500</v>
+      </c>
+      <c r="E171" s="78" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F171" s="79" t="n"/>
+      <c r="G171" s="79" t="n"/>
+      <c r="H171" s="78" t="n"/>
+      <c r="I171" s="78" t="n"/>
+      <c r="J171" s="78" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B172" s="82" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C172" s="82" t="inlineStr">
+        <is>
+          <t>Mangueira (1m)</t>
+        </is>
+      </c>
+      <c r="D172" s="83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E172" s="82" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F172" s="83" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G172" s="83" t="n"/>
+      <c r="H172" s="82" t="n"/>
+      <c r="I172" s="82" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B173" s="78" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C173" s="78" t="inlineStr">
+        <is>
+          <t>Vela Carvão Ativado</t>
+        </is>
+      </c>
+      <c r="D173" s="79" t="n">
+        <v>17</v>
+      </c>
+      <c r="E173" s="78" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F173" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G173" s="79" t="n"/>
+      <c r="H173" s="78" t="n"/>
+      <c r="I173" s="78" t="n"/>
+      <c r="J173" s="78" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="81" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B174" s="82" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C174" s="82" t="inlineStr">
+        <is>
+          <t>Vela Carvão Ativado</t>
+        </is>
+      </c>
+      <c r="D174" s="83" t="n">
+        <v>15</v>
+      </c>
+      <c r="E174" s="82" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F174" s="83" t="n"/>
+      <c r="G174" s="83" t="n"/>
+      <c r="H174" s="82" t="n"/>
+      <c r="I174" s="82" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="29" t="n"/>
+      <c r="B175" s="43" t="inlineStr">
         <is>
           <t>TOTAL DO MÊS</t>
         </is>
       </c>
-      <c r="C171" s="161" t="n"/>
-      <c r="D171" s="8">
-        <f>SUM(D5:D170)</f>
-        <v/>
-      </c>
-      <c r="E171" s="8" t="n"/>
-      <c r="F171" s="29">
-        <f>SUM(F5:F170)</f>
-        <v/>
-      </c>
-      <c r="G171" s="8">
-        <f>SUM(G5:G170)</f>
-        <v/>
-      </c>
-      <c r="H171" s="29" t="n"/>
-      <c r="I171" s="29" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="30" t="n"/>
-      <c r="B172" s="135" t="inlineStr">
+      <c r="C175" s="161" t="n"/>
+      <c r="D175" s="8">
+        <f>SUM(D5:D174)</f>
+        <v/>
+      </c>
+      <c r="E175" s="8" t="n"/>
+      <c r="F175" s="29">
+        <f>SUM(F5:F174)</f>
+        <v/>
+      </c>
+      <c r="G175" s="8">
+        <f>SUM(G5:G174)</f>
+        <v/>
+      </c>
+      <c r="H175" s="29" t="n"/>
+      <c r="I175" s="29" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="30" t="n"/>
+      <c r="B176" s="135" t="inlineStr">
         <is>
           <t>SALDO DO MÊS (Entradas líquidas − Despesas da loja)</t>
         </is>
       </c>
-      <c r="D172" s="134">
-        <f>(D171-F171-T5)-(L18-L19)</f>
-        <v/>
-      </c>
-      <c r="F172" s="30" t="n"/>
-      <c r="H172" s="30" t="n"/>
-      <c r="I172" s="30" t="n"/>
+      <c r="D176" s="134">
+        <f>(D175-F175-T5)-(L18-L19)</f>
+        <v/>
+      </c>
+      <c r="F176" s="30" t="n"/>
+      <c r="H176" s="30" t="n"/>
+      <c r="I176" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -41112,10 +41284,10 @@
     <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>$K$5:$K$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -49001,7 +49173,7 @@
       </c>
       <c r="E124" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F124" s="112">
@@ -49010,7 +49182,7 @@
       </c>
       <c r="G124" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -37868,7 +37868,7 @@
       </c>
       <c r="I59" s="78" t="inlineStr">
         <is>
-          <t>Comissões da quinzena de 24/08 a 05/09/2026</t>
+          <t>Comissões da quinzena de 24/08 a 05/09/2026 — R$ 550,00 de R$ 580,00; os R$ 30,00 restantes foram pagos em 11/09</t>
         </is>
       </c>
     </row>
@@ -38789,7 +38789,11 @@
           <t>Salários, Comissões e Encargos</t>
         </is>
       </c>
-      <c r="I90" s="82" t="n"/>
+      <c r="I90" s="82" t="inlineStr">
+        <is>
+          <t>Complemento da comissão da quinzena de 24/08 a 05/09/2026 (total R$ 580,00 — R$ 550,00 pagos em 05/09 e R$ 30,00 depois, por falta de troco no caixa)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="77" t="n">
@@ -41494,15 +41498,31 @@
       <c r="J183" s="18" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="44" t="n"/>
-      <c r="B184" s="45" t="n"/>
+      <c r="A184" s="44" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B184" s="45" t="inlineStr">
+        <is>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
       <c r="C184" s="45" t="n"/>
       <c r="D184" s="46" t="n"/>
       <c r="E184" s="45" t="n"/>
       <c r="F184" s="47" t="n"/>
-      <c r="G184" s="48" t="n"/>
-      <c r="H184" s="49" t="n"/>
-      <c r="I184" s="45" t="n"/>
+      <c r="G184" s="48" t="n">
+        <v>460</v>
+      </c>
+      <c r="H184" s="49" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I184" s="45" t="inlineStr">
+        <is>
+          <t>Comissões da quinzena de 08/09 a 18/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -2990,11 +2990,11 @@
     </row>
     <row r="11" ht="18.95" customHeight="1" s="157">
       <c r="B11" s="122">
-        <f>'DRE Simplificado'!O22</f>
+        <f>'DRE Simplificado'!O23</f>
         <v/>
       </c>
       <c r="C11" s="123">
-        <f>'DRE Simplificado'!O9</f>
+        <f>'DRE Simplificado'!O10</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -40487,11 +40487,11 @@
     </row>
     <row r="149">
       <c r="A149" s="77" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B149" s="78" t="inlineStr">
         <is>
-          <t>Humberto Fernandes Costa</t>
+          <t>Sinesio Moura da Silva</t>
         </is>
       </c>
       <c r="C149" s="78" t="n"/>
@@ -40499,7 +40499,7 @@
       <c r="E149" s="78" t="n"/>
       <c r="F149" s="79" t="n"/>
       <c r="G149" s="79" t="n">
-        <v>964</v>
+        <v>100</v>
       </c>
       <c r="H149" s="78" t="inlineStr">
         <is>
@@ -40508,18 +40508,18 @@
       </c>
       <c r="I149" s="78" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 10/09/2026.</t>
+          <t>Extrato Stone — saída de 14/09/2026.</t>
         </is>
       </c>
       <c r="J149" s="78" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="81" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B150" s="82" t="inlineStr">
         <is>
-          <t>Sinesio Moura da Silva</t>
+          <t>Eziquiel Soares da Cruz</t>
         </is>
       </c>
       <c r="C150" s="82" t="n"/>
@@ -40527,7 +40527,7 @@
       <c r="E150" s="82" t="n"/>
       <c r="F150" s="83" t="n"/>
       <c r="G150" s="83" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H150" s="82" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
       </c>
       <c r="I150" s="82" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 14/09/2026.</t>
+          <t>Extrato Stone — saída de 15/09/2026.</t>
         </is>
       </c>
     </row>
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B151" s="78" t="inlineStr">
         <is>
-          <t>Eziquiel Soares da Cruz</t>
+          <t>Lojão JB Mega 25</t>
         </is>
       </c>
       <c r="C151" s="78" t="n"/>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="B152" s="82" t="inlineStr">
         <is>
-          <t>Lojão JB Mega 25</t>
+          <t>Rivael Sousa Santos</t>
         </is>
       </c>
       <c r="C152" s="82" t="n"/>
@@ -40582,7 +40582,7 @@
       <c r="E152" s="82" t="n"/>
       <c r="F152" s="83" t="n"/>
       <c r="G152" s="83" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
       <c r="H152" s="82" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
       </c>
       <c r="B153" s="78" t="inlineStr">
         <is>
-          <t>Rivael Sousa Santos</t>
+          <t>Thiago de Jesus Nascimento</t>
         </is>
       </c>
       <c r="C153" s="78" t="n"/>
@@ -40609,7 +40609,7 @@
       <c r="E153" s="78" t="n"/>
       <c r="F153" s="79" t="n"/>
       <c r="G153" s="79" t="n">
-        <v>48.8</v>
+        <v>28</v>
       </c>
       <c r="H153" s="78" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
       </c>
       <c r="B154" s="82" t="inlineStr">
         <is>
-          <t>Thiago de Jesus Nascimento</t>
+          <t>Luciana Cruz Freire Santos</t>
         </is>
       </c>
       <c r="C154" s="82" t="n"/>
@@ -40637,7 +40637,7 @@
       <c r="E154" s="82" t="n"/>
       <c r="F154" s="83" t="n"/>
       <c r="G154" s="83" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="H154" s="82" t="inlineStr">
         <is>
@@ -40652,11 +40652,11 @@
     </row>
     <row r="155">
       <c r="A155" s="77" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B155" s="78" t="inlineStr">
         <is>
-          <t>Luciana Cruz Freire Santos</t>
+          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
         </is>
       </c>
       <c r="C155" s="78" t="n"/>
@@ -40664,7 +40664,7 @@
       <c r="E155" s="78" t="n"/>
       <c r="F155" s="79" t="n"/>
       <c r="G155" s="79" t="n">
-        <v>140</v>
+        <v>44.98</v>
       </c>
       <c r="H155" s="78" t="inlineStr">
         <is>
@@ -40673,18 +40673,18 @@
       </c>
       <c r="I155" s="78" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 15/09/2026.</t>
+          <t>Extrato Stone — saída de 16/09/2026.</t>
         </is>
       </c>
       <c r="J155" s="78" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="81" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B156" s="82" t="inlineStr">
         <is>
-          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
+          <t>Japedido Software</t>
         </is>
       </c>
       <c r="C156" s="82" t="n"/>
@@ -40692,7 +40692,7 @@
       <c r="E156" s="82" t="n"/>
       <c r="F156" s="83" t="n"/>
       <c r="G156" s="83" t="n">
-        <v>44.98</v>
+        <v>62.19</v>
       </c>
       <c r="H156" s="82" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
       </c>
       <c r="I156" s="82" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 16/09/2026.</t>
+          <t>Extrato Stone — saída de 18/09/2026.</t>
         </is>
       </c>
     </row>
@@ -40711,7 +40711,7 @@
       </c>
       <c r="B157" s="78" t="inlineStr">
         <is>
-          <t>Japedido Software</t>
+          <t>Jose Barbosa Leal Filho Ltda</t>
         </is>
       </c>
       <c r="C157" s="78" t="n"/>
@@ -40719,7 +40719,7 @@
       <c r="E157" s="78" t="n"/>
       <c r="F157" s="79" t="n"/>
       <c r="G157" s="79" t="n">
-        <v>62.19</v>
+        <v>130</v>
       </c>
       <c r="H157" s="78" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
       </c>
       <c r="B158" s="82" t="inlineStr">
         <is>
-          <t>Jose Barbosa Leal Filho Ltda</t>
+          <t>L K Abade Ltda</t>
         </is>
       </c>
       <c r="C158" s="82" t="n"/>
@@ -40747,7 +40747,7 @@
       <c r="E158" s="82" t="n"/>
       <c r="F158" s="83" t="n"/>
       <c r="G158" s="83" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="H158" s="82" t="inlineStr">
         <is>
@@ -40762,11 +40762,11 @@
     </row>
     <row r="159">
       <c r="A159" s="77" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B159" s="78" t="inlineStr">
         <is>
-          <t>L K Abade Ltda</t>
+          <t>Multidisplay Comercio e Servicos Tecnologicos</t>
         </is>
       </c>
       <c r="C159" s="78" t="n"/>
@@ -40774,7 +40774,7 @@
       <c r="E159" s="78" t="n"/>
       <c r="F159" s="79" t="n"/>
       <c r="G159" s="79" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H159" s="78" t="inlineStr">
         <is>
@@ -40783,18 +40783,18 @@
       </c>
       <c r="I159" s="78" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 18/09/2026.</t>
+          <t>Extrato Stone — saída de 08/09/2026.</t>
         </is>
       </c>
       <c r="J159" s="78" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="81" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B160" s="82" t="inlineStr">
         <is>
-          <t>Multidisplay Comercio e Servicos Tecnologicos</t>
+          <t>FGTS Digital (GFD)</t>
         </is>
       </c>
       <c r="C160" s="82" t="n"/>
@@ -40802,16 +40802,16 @@
       <c r="E160" s="82" t="n"/>
       <c r="F160" s="83" t="n"/>
       <c r="G160" s="83" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="H160" s="82" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Impostos e Taxas</t>
         </is>
       </c>
       <c r="I160" s="82" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 08/09/2026.</t>
+          <t>FGTS mensal — competência 08/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
         </is>
       </c>
     </row>
@@ -40821,7 +40821,7 @@
       </c>
       <c r="B161" s="78" t="inlineStr">
         <is>
-          <t>FGTS Digital (GFD)</t>
+          <t>Receita Federal — DARF / INSS</t>
         </is>
       </c>
       <c r="C161" s="78" t="n"/>
@@ -40829,7 +40829,7 @@
       <c r="E161" s="78" t="n"/>
       <c r="F161" s="79" t="n"/>
       <c r="G161" s="79" t="n">
-        <v>136</v>
+        <v>306.99</v>
       </c>
       <c r="H161" s="78" t="inlineStr">
         <is>
@@ -40838,35 +40838,40 @@
       </c>
       <c r="I161" s="78" t="inlineStr">
         <is>
-          <t>FGTS mensal — competência 08/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
+          <t>DARF / INSS — período de apuração agosto/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
         </is>
       </c>
       <c r="J161" s="78" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="81" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="B162" s="82" t="inlineStr">
         <is>
-          <t>Receita Federal — DARF / INSS</t>
-        </is>
-      </c>
-      <c r="C162" s="82" t="n"/>
-      <c r="D162" s="83" t="n"/>
-      <c r="E162" s="82" t="n"/>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+      <c r="C162" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D162" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E162" s="82" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F162" s="83" t="n"/>
-      <c r="G162" s="83" t="n">
-        <v>306.99</v>
-      </c>
-      <c r="H162" s="82" t="inlineStr">
-        <is>
-          <t>Impostos e Taxas</t>
-        </is>
-      </c>
-      <c r="I162" s="82" t="inlineStr">
-        <is>
-          <t>DARF / INSS — período de apuração agosto/2026. Venc. 18/09/2026, pago em 16/09/2026.</t>
+      <c r="G162" s="83" t="n"/>
+      <c r="H162" s="82" t="n"/>
+      <c r="I162" s="82" t="n"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>CLI-0032</t>
         </is>
       </c>
     </row>
@@ -40876,7 +40881,7 @@
       </c>
       <c r="B163" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Josimar Souza Santos</t>
         </is>
       </c>
       <c r="C163" s="78" t="inlineStr">
@@ -40889,7 +40894,7 @@
       </c>
       <c r="E163" s="78" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F163" s="79" t="n"/>
@@ -40898,7 +40903,7 @@
       <c r="I163" s="78" t="n"/>
       <c r="J163" s="78" t="inlineStr">
         <is>
-          <t>CLI-0032</t>
+          <t>CLI-0367</t>
         </is>
       </c>
     </row>
@@ -40908,7 +40913,7 @@
       </c>
       <c r="B164" s="82" t="inlineStr">
         <is>
-          <t>Josimar Souza Santos</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="C164" s="82" t="inlineStr">
@@ -40930,7 +40935,7 @@
       <c r="I164" s="82" t="n"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>CLI-0367</t>
+          <t>CLI-0296</t>
         </is>
       </c>
     </row>
@@ -40940,31 +40945,27 @@
       </c>
       <c r="B165" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
-        </is>
-      </c>
-      <c r="C165" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D165" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E165" s="78" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Combustível (Etanol) — Transvale</t>
+        </is>
+      </c>
+      <c r="C165" s="78" t="n"/>
+      <c r="D165" s="79" t="n"/>
+      <c r="E165" s="78" t="n"/>
       <c r="F165" s="79" t="n"/>
-      <c r="G165" s="79" t="n"/>
-      <c r="H165" s="78" t="n"/>
-      <c r="I165" s="78" t="n"/>
-      <c r="J165" s="78" t="inlineStr">
-        <is>
-          <t>CLI-0296</t>
-        </is>
-      </c>
+      <c r="G165" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="H165" s="78" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I165" s="78" t="inlineStr">
+        <is>
+          <t>10,31 L de etanol hidratado a R$ 4,85/L — NFC-e nº 000284718 (Transvale Derivados de Petróleo, CNPJ 11.271.229/0002-68). Pago em dinheiro.</t>
+        </is>
+      </c>
+      <c r="J165" s="78" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="81" t="n">
@@ -40972,7 +40973,7 @@
       </c>
       <c r="B166" s="82" t="inlineStr">
         <is>
-          <t>Combustível (Etanol) — Transvale</t>
+          <t>Filtros Planeta Água</t>
         </is>
       </c>
       <c r="C166" s="82" t="n"/>
@@ -40980,16 +40981,16 @@
       <c r="E166" s="82" t="n"/>
       <c r="F166" s="83" t="n"/>
       <c r="G166" s="83" t="n">
-        <v>50</v>
+        <v>592.89</v>
       </c>
       <c r="H166" s="82" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
+          <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
       <c r="I166" s="82" t="inlineStr">
         <is>
-          <t>10,31 L de etanol hidratado a R$ 4,85/L — NFC-e nº 000284718 (Transvale Derivados de Petróleo, CNPJ 11.271.229/0002-68). Pago em dinheiro.</t>
+          <t>Boleto doc. 133812/001 (emissão 28/08/2026) · parcela 1/4 — 2ª via com venc. 21/09/2026 (original R$ 591,12 venc. 18/09). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
         </is>
       </c>
     </row>
@@ -40999,7 +41000,7 @@
       </c>
       <c r="B167" s="78" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
+          <t>Receita Federal — Simples Nacional (DAS)</t>
         </is>
       </c>
       <c r="C167" s="78" t="n"/>
@@ -41007,16 +41008,16 @@
       <c r="E167" s="78" t="n"/>
       <c r="F167" s="79" t="n"/>
       <c r="G167" s="79" t="n">
-        <v>592.89</v>
+        <v>1958.02</v>
       </c>
       <c r="H167" s="78" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Impostos e Taxas</t>
         </is>
       </c>
       <c r="I167" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 133812/001 (emissão 28/08/2026) · parcela 1/4 — 2ª via com venc. 21/09/2026 (original R$ 591,12 venc. 18/09). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>DAS competência agosto/2026 (doc. 07.20.26260.6017058-0) — venc. 21/09/2026. Pago em 21/09/2026 pelo Banco do Nordeste.</t>
         </is>
       </c>
       <c r="J167" s="78" t="n"/>
@@ -41027,7 +41028,7 @@
       </c>
       <c r="B168" s="82" t="inlineStr">
         <is>
-          <t>Receita Federal — Simples Nacional (DAS)</t>
+          <t>Everest Refrigeração</t>
         </is>
       </c>
       <c r="C168" s="82" t="n"/>
@@ -41035,16 +41036,16 @@
       <c r="E168" s="82" t="n"/>
       <c r="F168" s="83" t="n"/>
       <c r="G168" s="83" t="n">
-        <v>1958.02</v>
+        <v>874.6799999999999</v>
       </c>
       <c r="H168" s="82" t="inlineStr">
         <is>
-          <t>Impostos e Taxas</t>
+          <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
       <c r="I168" s="82" t="inlineStr">
         <is>
-          <t>DAS competência agosto/2026 (doc. 07.20.26260.6017058-0) — venc. 21/09/2026. Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 3/5 — venc. 20/09/2026 (domingo). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
         </is>
       </c>
     </row>
@@ -41054,7 +41055,7 @@
       </c>
       <c r="B169" s="78" t="inlineStr">
         <is>
-          <t>Everest Refrigeração</t>
+          <t>Diarista</t>
         </is>
       </c>
       <c r="C169" s="78" t="n"/>
@@ -41062,16 +41063,16 @@
       <c r="E169" s="78" t="n"/>
       <c r="F169" s="79" t="n"/>
       <c r="G169" s="79" t="n">
-        <v>874.6799999999999</v>
+        <v>340</v>
       </c>
       <c r="H169" s="78" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I169" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 3/5 — venc. 20/09/2026 (domingo). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>Pagamento de diarista — despesa pessoal (Edilânia).</t>
         </is>
       </c>
       <c r="J169" s="78" t="n"/>
@@ -41082,26 +41083,22 @@
       </c>
       <c r="B170" s="82" t="inlineStr">
         <is>
-          <t>Diarista</t>
+          <t>Acerto de Armando</t>
         </is>
       </c>
       <c r="C170" s="82" t="n"/>
-      <c r="D170" s="83" t="n"/>
-      <c r="E170" s="82" t="n"/>
+      <c r="D170" s="83" t="n">
+        <v>500</v>
+      </c>
+      <c r="E170" s="82" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F170" s="83" t="n"/>
-      <c r="G170" s="83" t="n">
-        <v>340</v>
-      </c>
-      <c r="H170" s="82" t="inlineStr">
-        <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I170" s="82" t="inlineStr">
-        <is>
-          <t>Pagamento de diarista — despesa pessoal (Edilânia).</t>
-        </is>
-      </c>
+      <c r="G170" s="83" t="n"/>
+      <c r="H170" s="82" t="n"/>
+      <c r="I170" s="82" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="77" t="n">
@@ -41109,19 +41106,25 @@
       </c>
       <c r="B171" s="78" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
-        </is>
-      </c>
-      <c r="C171" s="78" t="n"/>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C171" s="78" t="inlineStr">
+        <is>
+          <t>Mangueira (1m)</t>
+        </is>
+      </c>
       <c r="D171" s="79" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E171" s="78" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F171" s="79" t="n"/>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F171" s="79" t="n">
+        <v>0.14</v>
+      </c>
       <c r="G171" s="79" t="n"/>
       <c r="H171" s="78" t="n"/>
       <c r="I171" s="78" t="n"/>
@@ -41138,19 +41141,19 @@
       </c>
       <c r="C172" s="82" t="inlineStr">
         <is>
-          <t>Mangueira (1m)</t>
+          <t>Vela Carvão Ativado</t>
         </is>
       </c>
       <c r="D172" s="83" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E172" s="82" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Crédito à Vista</t>
         </is>
       </c>
       <c r="F172" s="83" t="n">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="G172" s="83" t="n"/>
       <c r="H172" s="82" t="n"/>
@@ -41171,16 +41174,14 @@
         </is>
       </c>
       <c r="D173" s="79" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E173" s="78" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F173" s="79" t="n">
-        <v>0.6</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F173" s="79" t="n"/>
       <c r="G173" s="79" t="n"/>
       <c r="H173" s="78" t="n"/>
       <c r="I173" s="78" t="n"/>
@@ -41188,30 +41189,37 @@
     </row>
     <row r="174">
       <c r="A174" s="81" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B174" s="82" t="inlineStr">
         <is>
-          <t>Consumidor Final</t>
+          <t>Colégio Estadual Normal Arnaldo de Oliveira</t>
         </is>
       </c>
       <c r="C174" s="82" t="inlineStr">
         <is>
-          <t>Vela Carvão Ativado</t>
+          <t>9x Refil Carbon Tech 5" + 2x Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="D174" s="83" t="n">
-        <v>15</v>
+        <v>990</v>
       </c>
       <c r="E174" s="82" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F174" s="83" t="n"/>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F174" s="83" t="n">
+        <v>34.75</v>
+      </c>
       <c r="G174" s="83" t="n"/>
       <c r="H174" s="82" t="n"/>
       <c r="I174" s="82" t="n"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>OUT-0018</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="77" t="n">
@@ -41219,31 +41227,29 @@
       </c>
       <c r="B175" s="78" t="inlineStr">
         <is>
-          <t>Colégio Estadual Normal Arnaldo de Oliveira</t>
+          <t>Jacobina Etiquetas e Rotulos LTDA</t>
         </is>
       </c>
       <c r="C175" s="78" t="inlineStr">
         <is>
-          <t>9x Refil Carbon Tech 5" + 2x Refil Everest + Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D175" s="79" t="n">
-        <v>990</v>
+        <v>140</v>
       </c>
       <c r="E175" s="78" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F175" s="79" t="n">
-        <v>34.75</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F175" s="79" t="n"/>
       <c r="G175" s="79" t="n"/>
       <c r="H175" s="78" t="n"/>
       <c r="I175" s="78" t="n"/>
       <c r="J175" s="78" t="inlineStr">
         <is>
-          <t>OUT-0018</t>
+          <t>EMP-0190</t>
         </is>
       </c>
     </row>
@@ -41253,16 +41259,16 @@
       </c>
       <c r="B176" s="45" t="inlineStr">
         <is>
-          <t>Jacobina Etiquetas e Rotulos LTDA</t>
+          <t>Chapada Ouro Serviços Ltda - Motel Privilege</t>
         </is>
       </c>
       <c r="C176" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life + Mangueira (2m)</t>
         </is>
       </c>
       <c r="D176" s="46" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E176" s="45" t="inlineStr">
         <is>
@@ -41275,7 +41281,7 @@
       <c r="I176" s="45" t="n"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>EMP-0190</t>
+          <t>EMP-0066</t>
         </is>
       </c>
     </row>
@@ -41285,16 +41291,16 @@
       </c>
       <c r="B177" s="18" t="inlineStr">
         <is>
-          <t>Chapada Ouro Serviços Ltda - Motel Privilege</t>
+          <t>Casa da Construção Jacobina Ltda - Cavalcanti</t>
         </is>
       </c>
       <c r="C177" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Mangueira (2m)</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D177" s="27" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
@@ -41307,7 +41313,7 @@
       <c r="I177" s="18" t="n"/>
       <c r="J177" s="18" t="inlineStr">
         <is>
-          <t>EMP-0066</t>
+          <t>EMP-0045</t>
         </is>
       </c>
     </row>
@@ -41317,31 +41323,26 @@
       </c>
       <c r="B178" s="45" t="inlineStr">
         <is>
-          <t>Casa da Construção Jacobina Ltda - Cavalcanti</t>
+          <t>Consumidor Final</t>
         </is>
       </c>
       <c r="C178" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Carcaça 9" + Refil Plissado</t>
         </is>
       </c>
       <c r="D178" s="46" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="E178" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F178" s="47" t="n"/>
       <c r="G178" s="48" t="n"/>
       <c r="H178" s="49" t="n"/>
       <c r="I178" s="45" t="n"/>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>EMP-0045</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="17" t="n">
@@ -41349,27 +41350,33 @@
       </c>
       <c r="B179" s="18" t="inlineStr">
         <is>
-          <t>Consumidor Final</t>
+          <t>Isabela Alcantara Mesquita - Ivanete</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>Carcaça 9" + Refil Plissado</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="D179" s="27" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F179" s="19" t="n"/>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F179" s="19" t="n">
+        <v>4.91</v>
+      </c>
       <c r="G179" s="19" t="n"/>
       <c r="H179" s="21" t="n"/>
       <c r="I179" s="18" t="n"/>
-      <c r="J179" s="18" t="n"/>
+      <c r="J179" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0371</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="44" t="n">
@@ -41377,12 +41384,12 @@
       </c>
       <c r="B180" s="45" t="inlineStr">
         <is>
-          <t>Isabela Alcantara Mesquita - Ivanete</t>
+          <t>Jacobina Silk</t>
         </is>
       </c>
       <c r="C180" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D180" s="46" t="n">
@@ -41390,18 +41397,16 @@
       </c>
       <c r="E180" s="45" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F180" s="47" t="n">
-        <v>4.91</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F180" s="47" t="n"/>
       <c r="G180" s="48" t="n"/>
       <c r="H180" s="49" t="n"/>
       <c r="I180" s="45" t="n"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>CLI-0371</t>
+          <t>EMP-0193</t>
         </is>
       </c>
     </row>
@@ -41411,12 +41416,12 @@
       </c>
       <c r="B181" s="18" t="inlineStr">
         <is>
-          <t>Jacobina Silk</t>
+          <t>Clinica Crescer</t>
         </is>
       </c>
       <c r="C181" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="D181" s="27" t="n">
@@ -41433,7 +41438,7 @@
       <c r="I181" s="18" t="n"/>
       <c r="J181" s="18" t="inlineStr">
         <is>
-          <t>EMP-0193</t>
+          <t>EMP-0072</t>
         </is>
       </c>
     </row>
@@ -41443,39 +41448,34 @@
       </c>
       <c r="B182" s="45" t="inlineStr">
         <is>
-          <t>Clinica Crescer</t>
-        </is>
-      </c>
-      <c r="C182" s="45" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="D182" s="46" t="n">
-        <v>140</v>
-      </c>
-      <c r="E182" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Comercial de Tintas Leal Jatobá</t>
+        </is>
+      </c>
+      <c r="C182" s="45" t="n"/>
+      <c r="D182" s="46" t="n"/>
+      <c r="E182" s="45" t="n"/>
       <c r="F182" s="47" t="n"/>
-      <c r="G182" s="48" t="n"/>
-      <c r="H182" s="49" t="n"/>
-      <c r="I182" s="45" t="n"/>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>EMP-0072</t>
+      <c r="G182" s="48" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="H182" s="49" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I182" s="45" t="inlineStr">
+        <is>
+          <t>NF-e 2.879 de 17/09/2026 (CNPJ 40.528.218/0001-38) — parafusos, conexões hidráulicas (niple, tê, junção, fita veda), graxa, tinta, lâmpada LED, lixa e abraçadeiras. Pago em dinheiro em 22/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="17" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B183" s="18" t="inlineStr">
         <is>
-          <t>Comercial de Tintas Leal Jatobá</t>
+          <t>Comissão Wiliam</t>
         </is>
       </c>
       <c r="C183" s="18" t="n"/>
@@ -41483,27 +41483,27 @@
       <c r="E183" s="18" t="n"/>
       <c r="F183" s="19" t="n"/>
       <c r="G183" s="19" t="n">
-        <v>124.2</v>
+        <v>460</v>
       </c>
       <c r="H183" s="21" t="inlineStr">
         <is>
-          <t>Manutenção e Reparos</t>
+          <t>Salários, Comissões e Encargos</t>
         </is>
       </c>
       <c r="I183" s="18" t="inlineStr">
         <is>
-          <t>NF-e 2.879 de 17/09/2026 (CNPJ 40.528.218/0001-38) — parafusos, conexões hidráulicas (niple, tê, junção, fita veda), graxa, tinta, lâmpada LED, lixa e abraçadeiras. Pago em dinheiro em 22/09/2026.</t>
+          <t>Comissões da quinzena de 08/09 a 18/09/2026</t>
         </is>
       </c>
       <c r="J183" s="18" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="44" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B184" s="45" t="inlineStr">
         <is>
-          <t>Comissão Wiliam</t>
+          <t>Supermercado (retirada BNB)</t>
         </is>
       </c>
       <c r="C184" s="45" t="n"/>
@@ -41511,16 +41511,16 @@
       <c r="E184" s="45" t="n"/>
       <c r="F184" s="47" t="n"/>
       <c r="G184" s="48" t="n">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="H184" s="49" t="inlineStr">
         <is>
-          <t>Salários, Comissões e Encargos</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I184" s="45" t="inlineStr">
         <is>
-          <t>Comissões da quinzena de 08/09 a 18/09/2026</t>
+          <t>R$ 240,00 retirados no BNB para supermercado — despesa pessoal (Edilânia). Informado por ela no WhatsApp em 10/09/2026.</t>
         </is>
       </c>
     </row>
@@ -52402,51 +52402,51 @@
         </is>
       </c>
       <c r="B8" s="98">
-        <f>'Jan 2026'!J10-B20</f>
+        <f>'Jan 2026'!J10-B21</f>
         <v/>
       </c>
       <c r="C8" s="98">
-        <f>'Fev 2026'!J10-C20</f>
+        <f>'Fev 2026'!J10-C21</f>
         <v/>
       </c>
       <c r="D8" s="98">
-        <f>'Mar 2026'!J10-D20</f>
+        <f>'Mar 2026'!J10-D21</f>
         <v/>
       </c>
       <c r="E8" s="98">
-        <f>'Abr 2026'!J10-E20</f>
+        <f>'Abr 2026'!J10-E21</f>
         <v/>
       </c>
       <c r="F8" s="98">
-        <f>'Mai 2026'!J10-F20</f>
+        <f>'Mai 2026'!J10-F21</f>
         <v/>
       </c>
       <c r="G8" s="98">
-        <f>'Jun 2026'!J10-G20</f>
+        <f>'Jun 2026'!J10-G21</f>
         <v/>
       </c>
       <c r="H8" s="98">
-        <f>'Jul 2026'!J10-H20</f>
+        <f>'Jul 2026'!J10-H21</f>
         <v/>
       </c>
       <c r="I8" s="98">
-        <f>'Ago 2026'!L10-I20</f>
+        <f>'Ago 2026'!L10-I21</f>
         <v/>
       </c>
       <c r="J8" s="98">
-        <f>'Set 2026'!L10-J20</f>
+        <f>'Set 2026'!L10-J21</f>
         <v/>
       </c>
       <c r="K8" s="98">
-        <f>'Out 2026'!L10-K20</f>
+        <f>'Out 2026'!L10-K21</f>
         <v/>
       </c>
       <c r="L8" s="98">
-        <f>'Nov 2026'!L10-L20</f>
+        <f>'Nov 2026'!L10-L21</f>
         <v/>
       </c>
       <c r="M8" s="98">
-        <f>'Dez 2026'!L10-M20</f>
+        <f>'Dez 2026'!L10-M21</f>
         <v/>
       </c>
       <c r="N8" s="98">
@@ -52458,310 +52458,310 @@
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="99" t="inlineStr">
+    <row r="9" s="157">
+      <c r="A9" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Comissões (Wiliam — por troca/instalação)</t>
+        </is>
+      </c>
+      <c r="B9" s="98">
+        <f>SUMIFS('Jan 2026'!E5:E500,'Jan 2026'!B5:B500,"*omiss*",'Jan 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="C9" s="98">
+        <f>SUMIFS('Fev 2026'!E5:E500,'Fev 2026'!B5:B500,"*omiss*",'Fev 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="D9" s="98">
+        <f>SUMIFS('Mar 2026'!E5:E500,'Mar 2026'!B5:B500,"*omiss*",'Mar 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="E9" s="98">
+        <f>SUMIFS('Abr 2026'!E5:E500,'Abr 2026'!B5:B500,"*omiss*",'Abr 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="F9" s="98">
+        <f>SUMIFS('Mai 2026'!E5:E500,'Mai 2026'!B5:B500,"*omiss*",'Mai 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="G9" s="98">
+        <f>SUMIFS('Jun 2026'!E5:E500,'Jun 2026'!B5:B500,"*omiss*",'Jun 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="H9" s="98">
+        <f>SUMIFS('Jul 2026'!E5:E500,'Jul 2026'!B5:B500,"*omiss*",'Jul 2026'!F5:F500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="I9" s="98">
+        <f>SUMIFS('Ago 2026'!G5:G500,'Ago 2026'!B5:B500,"Comissão*",'Ago 2026'!H5:H500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="J9" s="98">
+        <f>SUMIFS('Set 2026'!G5:G500,'Set 2026'!B5:B500,"Comissão*",'Set 2026'!H5:H500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="K9" s="98">
+        <f>SUMIFS('Out 2026'!G5:G500,'Out 2026'!B5:B500,"Comissão*",'Out 2026'!H5:H500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="L9" s="98">
+        <f>SUMIFS('Nov 2026'!G5:G500,'Nov 2026'!B5:B500,"Comissão*",'Nov 2026'!H5:H500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="M9" s="98">
+        <f>SUMIFS('Dez 2026'!G5:G500,'Dez 2026'!B5:B500,"Comissão*",'Dez 2026'!H5:H500,"Salários, Comissões e Encargos")</f>
+        <v/>
+      </c>
+      <c r="N9" s="98">
+        <f>SUM(B9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="98">
+        <f>IF($B$3=0,0,N9/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" s="157">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>(=) CUSTOS VARIÁVEIS</t>
         </is>
       </c>
-      <c r="B9" s="100">
-        <f>SUM(B6:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="100">
-        <f>SUM(C6:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="100">
-        <f>SUM(D6:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="100">
-        <f>SUM(E6:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="100">
-        <f>SUM(F6:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="100">
-        <f>SUM(G6:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="100">
-        <f>SUM(H6:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="100">
-        <f>SUM(I6:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="100">
-        <f>SUM(J6:J8)</f>
-        <v/>
-      </c>
-      <c r="K9" s="100">
-        <f>SUM(K6:K8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="100">
-        <f>SUM(L6:L8)</f>
-        <v/>
-      </c>
-      <c r="M9" s="100">
-        <f>SUM(M6:M8)</f>
-        <v/>
-      </c>
-      <c r="N9" s="100">
-        <f>SUM(B9:M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="100">
-        <f>IF($B$3=0,0,N9/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="95" t="inlineStr">
+      <c r="B10" s="100">
+        <f>SUM(B6:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="100">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="100">
+        <f>SUM(D6:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="100">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="100">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="100">
+        <f>SUM(G6:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="100">
+        <f>SUM(H6:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="100">
+        <f>SUM(I6:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="100">
+        <f>SUM(J6:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="100">
+        <f>SUM(K6:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="100">
+        <f>SUM(L6:L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="100">
+        <f>SUM(M6:M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="100">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="100">
+        <f>IF($B$3=0,0,N10/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" s="157">
+      <c r="A11" s="95" t="inlineStr">
         <is>
           <t>(=) MARGEM DE CONTRIBUIÇÃO</t>
         </is>
       </c>
-      <c r="B10" s="96">
-        <f>B5-B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="96">
-        <f>C5-C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="96">
-        <f>D5-D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="96">
-        <f>E5-E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="96">
-        <f>F5-F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="96">
-        <f>G5-G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="96">
-        <f>H5-H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="96">
-        <f>I5-I9</f>
-        <v/>
-      </c>
-      <c r="J10" s="96">
-        <f>J5-J9</f>
-        <v/>
-      </c>
-      <c r="K10" s="96">
-        <f>K5-K9</f>
-        <v/>
-      </c>
-      <c r="L10" s="96">
-        <f>L5-L9</f>
-        <v/>
-      </c>
-      <c r="M10" s="96">
-        <f>M5-M9</f>
-        <v/>
-      </c>
-      <c r="N10" s="96">
-        <f>SUM(B10:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="96">
-        <f>IF($B$3=0,0,N10/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="101" t="inlineStr">
+      <c r="B11" s="96">
+        <f>B5-B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="96">
+        <f>C5-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="96">
+        <f>D5-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="96">
+        <f>E5-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="96">
+        <f>F5-F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="96">
+        <f>G5-G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="96">
+        <f>H5-H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="96">
+        <f>I5-I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="96">
+        <f>J5-J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="96">
+        <f>K5-K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="96">
+        <f>L5-L10</f>
+        <v/>
+      </c>
+      <c r="M11" s="96">
+        <f>M5-M10</f>
+        <v/>
+      </c>
+      <c r="N11" s="96">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="96">
+        <f>IF($B$3=0,0,N11/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" s="157">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">      Margem de Contribuição (%)</t>
         </is>
       </c>
-      <c r="B11" s="102">
-        <f>IF(B5=0,"",B10/B5)</f>
-        <v/>
-      </c>
-      <c r="C11" s="102">
-        <f>IF(C5=0,"",C10/C5)</f>
-        <v/>
-      </c>
-      <c r="D11" s="102">
-        <f>IF(D5=0,"",D10/D5)</f>
-        <v/>
-      </c>
-      <c r="E11" s="102">
-        <f>IF(E5=0,"",E10/E5)</f>
-        <v/>
-      </c>
-      <c r="F11" s="102">
-        <f>IF(F5=0,"",F10/F5)</f>
-        <v/>
-      </c>
-      <c r="G11" s="102">
-        <f>IF(G5=0,"",G10/G5)</f>
-        <v/>
-      </c>
-      <c r="H11" s="102">
-        <f>IF(H5=0,"",H10/H5)</f>
-        <v/>
-      </c>
-      <c r="I11" s="102">
-        <f>IF(I5=0,"",I10/I5)</f>
-        <v/>
-      </c>
-      <c r="J11" s="102">
-        <f>IF(J5=0,"",J10/J5)</f>
-        <v/>
-      </c>
-      <c r="K11" s="102">
-        <f>IF(K5=0,"",K10/K5)</f>
-        <v/>
-      </c>
-      <c r="L11" s="102">
-        <f>IF(L5=0,"",L10/L5)</f>
-        <v/>
-      </c>
-      <c r="M11" s="102">
-        <f>IF(M5=0,"",M10/M5)</f>
-        <v/>
-      </c>
-      <c r="N11" s="102">
-        <f>IF(N5=0,"",N10/N5)</f>
-        <v/>
-      </c>
-      <c r="O11" s="102">
-        <f>IF(N5=0,"",N10/N5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="97" t="inlineStr">
+      <c r="B12" s="102">
+        <f>IF(B5=0,"",B11/B5)</f>
+        <v/>
+      </c>
+      <c r="C12" s="102">
+        <f>IF(C5=0,"",C11/C5)</f>
+        <v/>
+      </c>
+      <c r="D12" s="102">
+        <f>IF(D5=0,"",D11/D5)</f>
+        <v/>
+      </c>
+      <c r="E12" s="102">
+        <f>IF(E5=0,"",E11/E5)</f>
+        <v/>
+      </c>
+      <c r="F12" s="102">
+        <f>IF(F5=0,"",F11/F5)</f>
+        <v/>
+      </c>
+      <c r="G12" s="102">
+        <f>IF(G5=0,"",G11/G5)</f>
+        <v/>
+      </c>
+      <c r="H12" s="102">
+        <f>IF(H5=0,"",H11/H5)</f>
+        <v/>
+      </c>
+      <c r="I12" s="102">
+        <f>IF(I5=0,"",I11/I5)</f>
+        <v/>
+      </c>
+      <c r="J12" s="102">
+        <f>IF(J5=0,"",J11/J5)</f>
+        <v/>
+      </c>
+      <c r="K12" s="102">
+        <f>IF(K5=0,"",K11/K5)</f>
+        <v/>
+      </c>
+      <c r="L12" s="102">
+        <f>IF(L5=0,"",L11/L5)</f>
+        <v/>
+      </c>
+      <c r="M12" s="102">
+        <f>IF(M5=0,"",M11/M5)</f>
+        <v/>
+      </c>
+      <c r="N12" s="102">
+        <f>IF(N5=0,"",N11/N5)</f>
+        <v/>
+      </c>
+      <c r="O12" s="102">
+        <f>IF(N5=0,"",N11/N5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" s="157">
+      <c r="A13" s="97" t="inlineStr">
         <is>
           <t xml:space="preserve">   (−) Aluguel</t>
         </is>
       </c>
-      <c r="B12" s="98">
+      <c r="B13" s="98">
         <f>'Jan 2026'!J6</f>
         <v/>
       </c>
-      <c r="C12" s="98">
+      <c r="C13" s="98">
         <f>'Fev 2026'!J6</f>
         <v/>
       </c>
-      <c r="D12" s="98">
+      <c r="D13" s="98">
         <f>'Mar 2026'!J6</f>
         <v/>
       </c>
-      <c r="E12" s="98">
+      <c r="E13" s="98">
         <f>'Abr 2026'!J6</f>
         <v/>
       </c>
-      <c r="F12" s="98">
+      <c r="F13" s="98">
         <f>'Mai 2026'!J6</f>
         <v/>
       </c>
-      <c r="G12" s="98">
+      <c r="G13" s="98">
         <f>'Jun 2026'!J6</f>
         <v/>
       </c>
-      <c r="H12" s="98">
+      <c r="H13" s="98">
         <f>'Jul 2026'!J6</f>
         <v/>
       </c>
-      <c r="I12" s="98">
+      <c r="I13" s="98">
         <f>'Ago 2026'!L6</f>
         <v/>
       </c>
-      <c r="J12" s="98">
+      <c r="J13" s="98">
         <f>'Set 2026'!L6</f>
         <v/>
       </c>
-      <c r="K12" s="98">
+      <c r="K13" s="98">
         <f>'Out 2026'!L6</f>
         <v/>
       </c>
-      <c r="L12" s="98">
+      <c r="L13" s="98">
         <f>'Nov 2026'!L6</f>
         <v/>
       </c>
-      <c r="M12" s="98">
+      <c r="M13" s="98">
         <f>'Dez 2026'!L6</f>
-        <v/>
-      </c>
-      <c r="N12" s="98">
-        <f>SUM(B12:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="98">
-        <f>IF($B$3=0,0,N12/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (−) Água, Energia e Internet</t>
-        </is>
-      </c>
-      <c r="B13" s="98">
-        <f>'Jan 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="C13" s="98">
-        <f>'Fev 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="D13" s="98">
-        <f>'Mar 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="E13" s="98">
-        <f>'Abr 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="F13" s="98">
-        <f>'Mai 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="G13" s="98">
-        <f>'Jun 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="H13" s="98">
-        <f>'Jul 2026'!J7</f>
-        <v/>
-      </c>
-      <c r="I13" s="98">
-        <f>'Ago 2026'!L7</f>
-        <v/>
-      </c>
-      <c r="J13" s="98">
-        <f>'Set 2026'!L7</f>
-        <v/>
-      </c>
-      <c r="K13" s="98">
-        <f>'Out 2026'!L7</f>
-        <v/>
-      </c>
-      <c r="L13" s="98">
-        <f>'Nov 2026'!L7</f>
-        <v/>
-      </c>
-      <c r="M13" s="98">
-        <f>'Dez 2026'!L7</f>
         <v/>
       </c>
       <c r="N13" s="98">
@@ -52773,58 +52773,58 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" s="157">
       <c r="A14" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Tarifas Bancárias e Cartão</t>
+          <t xml:space="preserve">   (−) Água, Energia e Internet</t>
         </is>
       </c>
       <c r="B14" s="98">
-        <f>'Jan 2026'!J9</f>
+        <f>'Jan 2026'!J7</f>
         <v/>
       </c>
       <c r="C14" s="98">
-        <f>'Fev 2026'!J9</f>
+        <f>'Fev 2026'!J7</f>
         <v/>
       </c>
       <c r="D14" s="98">
-        <f>'Mar 2026'!J9</f>
+        <f>'Mar 2026'!J7</f>
         <v/>
       </c>
       <c r="E14" s="98">
-        <f>'Abr 2026'!J9</f>
+        <f>'Abr 2026'!J7</f>
         <v/>
       </c>
       <c r="F14" s="98">
-        <f>'Mai 2026'!J9</f>
+        <f>'Mai 2026'!J7</f>
         <v/>
       </c>
       <c r="G14" s="98">
-        <f>'Jun 2026'!J9</f>
+        <f>'Jun 2026'!J7</f>
         <v/>
       </c>
       <c r="H14" s="98">
-        <f>'Jul 2026'!J9</f>
+        <f>'Jul 2026'!J7</f>
         <v/>
       </c>
       <c r="I14" s="98">
-        <f>'Ago 2026'!L9</f>
+        <f>'Ago 2026'!L7</f>
         <v/>
       </c>
       <c r="J14" s="98">
-        <f>'Set 2026'!L9</f>
+        <f>'Set 2026'!L7</f>
         <v/>
       </c>
       <c r="K14" s="98">
-        <f>'Out 2026'!L9</f>
+        <f>'Out 2026'!L7</f>
         <v/>
       </c>
       <c r="L14" s="98">
-        <f>'Nov 2026'!L9</f>
+        <f>'Nov 2026'!L7</f>
         <v/>
       </c>
       <c r="M14" s="98">
-        <f>'Dez 2026'!L9</f>
+        <f>'Dez 2026'!L7</f>
         <v/>
       </c>
       <c r="N14" s="98">
@@ -52836,58 +52836,58 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="157">
       <c r="A15" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Salários, Comissões e Encargos</t>
+          <t xml:space="preserve">   (−) Tarifas Bancárias e Cartão</t>
         </is>
       </c>
       <c r="B15" s="98">
-        <f>'Jan 2026'!J11</f>
+        <f>'Jan 2026'!J9</f>
         <v/>
       </c>
       <c r="C15" s="98">
-        <f>'Fev 2026'!J11</f>
+        <f>'Fev 2026'!J9</f>
         <v/>
       </c>
       <c r="D15" s="98">
-        <f>'Mar 2026'!J11</f>
+        <f>'Mar 2026'!J9</f>
         <v/>
       </c>
       <c r="E15" s="98">
-        <f>'Abr 2026'!J11</f>
+        <f>'Abr 2026'!J9</f>
         <v/>
       </c>
       <c r="F15" s="98">
-        <f>'Mai 2026'!J11</f>
+        <f>'Mai 2026'!J9</f>
         <v/>
       </c>
       <c r="G15" s="98">
-        <f>'Jun 2026'!J11</f>
+        <f>'Jun 2026'!J9</f>
         <v/>
       </c>
       <c r="H15" s="98">
-        <f>'Jul 2026'!J11</f>
+        <f>'Jul 2026'!J9</f>
         <v/>
       </c>
       <c r="I15" s="98">
-        <f>'Ago 2026'!L11</f>
+        <f>'Ago 2026'!L9</f>
         <v/>
       </c>
       <c r="J15" s="98">
-        <f>'Set 2026'!L11</f>
+        <f>'Set 2026'!L9</f>
         <v/>
       </c>
       <c r="K15" s="98">
-        <f>'Out 2026'!L11</f>
+        <f>'Out 2026'!L9</f>
         <v/>
       </c>
       <c r="L15" s="98">
-        <f>'Nov 2026'!L11</f>
+        <f>'Nov 2026'!L9</f>
         <v/>
       </c>
       <c r="M15" s="98">
-        <f>'Dez 2026'!L11</f>
+        <f>'Dez 2026'!L9</f>
         <v/>
       </c>
       <c r="N15" s="98">
@@ -52899,58 +52899,58 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="157">
       <c r="A16" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Contabilidade</t>
+          <t xml:space="preserve">   (−) Salários e Encargos (sem as comissões)</t>
         </is>
       </c>
       <c r="B16" s="98">
-        <f>'Jan 2026'!J12</f>
+        <f>'Jan 2026'!J11-B9</f>
         <v/>
       </c>
       <c r="C16" s="98">
-        <f>'Fev 2026'!J12</f>
+        <f>'Fev 2026'!J11-C9</f>
         <v/>
       </c>
       <c r="D16" s="98">
-        <f>'Mar 2026'!J12</f>
+        <f>'Mar 2026'!J11-D9</f>
         <v/>
       </c>
       <c r="E16" s="98">
-        <f>'Abr 2026'!J12</f>
+        <f>'Abr 2026'!J11-E9</f>
         <v/>
       </c>
       <c r="F16" s="98">
-        <f>'Mai 2026'!J12</f>
+        <f>'Mai 2026'!J11-F9</f>
         <v/>
       </c>
       <c r="G16" s="98">
-        <f>'Jun 2026'!J12</f>
+        <f>'Jun 2026'!J11-G9</f>
         <v/>
       </c>
       <c r="H16" s="98">
-        <f>'Jul 2026'!J12</f>
+        <f>'Jul 2026'!J11-H9</f>
         <v/>
       </c>
       <c r="I16" s="98">
-        <f>'Ago 2026'!L12</f>
+        <f>'Ago 2026'!L11-I9</f>
         <v/>
       </c>
       <c r="J16" s="98">
-        <f>'Set 2026'!L12</f>
+        <f>'Set 2026'!L11-J9</f>
         <v/>
       </c>
       <c r="K16" s="98">
-        <f>'Out 2026'!L12</f>
+        <f>'Out 2026'!L11-K9</f>
         <v/>
       </c>
       <c r="L16" s="98">
-        <f>'Nov 2026'!L12</f>
+        <f>'Nov 2026'!L11-L9</f>
         <v/>
       </c>
       <c r="M16" s="98">
-        <f>'Dez 2026'!L12</f>
+        <f>'Dez 2026'!L11-M9</f>
         <v/>
       </c>
       <c r="N16" s="98">
@@ -52962,58 +52962,58 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="157">
       <c r="A17" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Manutenção e Reparos</t>
+          <t xml:space="preserve">   (−) Contabilidade</t>
         </is>
       </c>
       <c r="B17" s="98">
-        <f>'Jan 2026'!J13</f>
+        <f>'Jan 2026'!J12</f>
         <v/>
       </c>
       <c r="C17" s="98">
-        <f>'Fev 2026'!J13</f>
+        <f>'Fev 2026'!J12</f>
         <v/>
       </c>
       <c r="D17" s="98">
-        <f>'Mar 2026'!J13</f>
+        <f>'Mar 2026'!J12</f>
         <v/>
       </c>
       <c r="E17" s="98">
-        <f>'Abr 2026'!J13</f>
+        <f>'Abr 2026'!J12</f>
         <v/>
       </c>
       <c r="F17" s="98">
-        <f>'Mai 2026'!J13</f>
+        <f>'Mai 2026'!J12</f>
         <v/>
       </c>
       <c r="G17" s="98">
-        <f>'Jun 2026'!J13</f>
+        <f>'Jun 2026'!J12</f>
         <v/>
       </c>
       <c r="H17" s="98">
-        <f>'Jul 2026'!J13</f>
+        <f>'Jul 2026'!J12</f>
         <v/>
       </c>
       <c r="I17" s="98">
-        <f>'Ago 2026'!L13</f>
+        <f>'Ago 2026'!L12</f>
         <v/>
       </c>
       <c r="J17" s="98">
-        <f>'Set 2026'!L13</f>
+        <f>'Set 2026'!L12</f>
         <v/>
       </c>
       <c r="K17" s="98">
-        <f>'Out 2026'!L13</f>
+        <f>'Out 2026'!L12</f>
         <v/>
       </c>
       <c r="L17" s="98">
-        <f>'Nov 2026'!L13</f>
+        <f>'Nov 2026'!L12</f>
         <v/>
       </c>
       <c r="M17" s="98">
-        <f>'Dez 2026'!L13</f>
+        <f>'Dez 2026'!L12</f>
         <v/>
       </c>
       <c r="N17" s="98">
@@ -53025,58 +53025,58 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="157">
       <c r="A18" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Material de Limpeza e Escritório</t>
+          <t xml:space="preserve">   (−) Manutenção e Reparos</t>
         </is>
       </c>
       <c r="B18" s="98">
-        <f>'Jan 2026'!J14</f>
+        <f>'Jan 2026'!J13</f>
         <v/>
       </c>
       <c r="C18" s="98">
-        <f>'Fev 2026'!J14</f>
+        <f>'Fev 2026'!J13</f>
         <v/>
       </c>
       <c r="D18" s="98">
-        <f>'Mar 2026'!J14</f>
+        <f>'Mar 2026'!J13</f>
         <v/>
       </c>
       <c r="E18" s="98">
-        <f>'Abr 2026'!J14</f>
+        <f>'Abr 2026'!J13</f>
         <v/>
       </c>
       <c r="F18" s="98">
-        <f>'Mai 2026'!J14</f>
+        <f>'Mai 2026'!J13</f>
         <v/>
       </c>
       <c r="G18" s="98">
-        <f>'Jun 2026'!J14</f>
+        <f>'Jun 2026'!J13</f>
         <v/>
       </c>
       <c r="H18" s="98">
-        <f>'Jul 2026'!J14</f>
+        <f>'Jul 2026'!J13</f>
         <v/>
       </c>
       <c r="I18" s="98">
-        <f>'Ago 2026'!L14</f>
+        <f>'Ago 2026'!L13</f>
         <v/>
       </c>
       <c r="J18" s="98">
-        <f>'Set 2026'!L14</f>
+        <f>'Set 2026'!L13</f>
         <v/>
       </c>
       <c r="K18" s="98">
-        <f>'Out 2026'!L14</f>
+        <f>'Out 2026'!L13</f>
         <v/>
       </c>
       <c r="L18" s="98">
-        <f>'Nov 2026'!L14</f>
+        <f>'Nov 2026'!L13</f>
         <v/>
       </c>
       <c r="M18" s="98">
-        <f>'Dez 2026'!L14</f>
+        <f>'Dez 2026'!L13</f>
         <v/>
       </c>
       <c r="N18" s="98">
@@ -53088,58 +53088,58 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="157">
       <c r="A19" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Estornos de Vendas (Cancelamentos)</t>
+          <t xml:space="preserve">   (−) Material de Limpeza e Escritório</t>
         </is>
       </c>
       <c r="B19" s="98">
-        <f>'Jan 2026'!J15</f>
+        <f>'Jan 2026'!J14</f>
         <v/>
       </c>
       <c r="C19" s="98">
-        <f>'Fev 2026'!J15</f>
+        <f>'Fev 2026'!J14</f>
         <v/>
       </c>
       <c r="D19" s="98">
-        <f>'Mar 2026'!J15</f>
+        <f>'Mar 2026'!J14</f>
         <v/>
       </c>
       <c r="E19" s="98">
-        <f>'Abr 2026'!J15</f>
+        <f>'Abr 2026'!J14</f>
         <v/>
       </c>
       <c r="F19" s="98">
-        <f>'Mai 2026'!J15</f>
+        <f>'Mai 2026'!J14</f>
         <v/>
       </c>
       <c r="G19" s="98">
-        <f>'Jun 2026'!J15</f>
+        <f>'Jun 2026'!J14</f>
         <v/>
       </c>
       <c r="H19" s="98">
-        <f>'Jul 2026'!J15</f>
+        <f>'Jul 2026'!J14</f>
         <v/>
       </c>
       <c r="I19" s="98">
-        <f>'Ago 2026'!L15</f>
+        <f>'Ago 2026'!L14</f>
         <v/>
       </c>
       <c r="J19" s="98">
-        <f>'Set 2026'!L15</f>
+        <f>'Set 2026'!L14</f>
         <v/>
       </c>
       <c r="K19" s="98">
-        <f>'Out 2026'!L15</f>
+        <f>'Out 2026'!L14</f>
         <v/>
       </c>
       <c r="L19" s="98">
-        <f>'Nov 2026'!L15</f>
+        <f>'Nov 2026'!L14</f>
         <v/>
       </c>
       <c r="M19" s="98">
-        <f>'Dez 2026'!L15</f>
+        <f>'Dez 2026'!L14</f>
         <v/>
       </c>
       <c r="N19" s="98">
@@ -53151,58 +53151,58 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="157">
       <c r="A20" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Estacionamento (dentro de Transporte e Entregas)</t>
+          <t xml:space="preserve">   (−) Estornos de Vendas (Cancelamentos)</t>
         </is>
       </c>
       <c r="B20" s="98">
-        <f>SUMIF('Jan 2026'!B5:B500,"Estacionamento*",'Jan 2026'!E5:E500)</f>
+        <f>'Jan 2026'!J15</f>
         <v/>
       </c>
       <c r="C20" s="98">
-        <f>SUMIF('Fev 2026'!B5:B500,"Estacionamento*",'Fev 2026'!E5:E500)</f>
+        <f>'Fev 2026'!J15</f>
         <v/>
       </c>
       <c r="D20" s="98">
-        <f>SUMIF('Mar 2026'!B5:B500,"Estacionamento*",'Mar 2026'!E5:E500)</f>
+        <f>'Mar 2026'!J15</f>
         <v/>
       </c>
       <c r="E20" s="98">
-        <f>SUMIF('Abr 2026'!B5:B500,"Estacionamento*",'Abr 2026'!E5:E500)</f>
+        <f>'Abr 2026'!J15</f>
         <v/>
       </c>
       <c r="F20" s="98">
-        <f>SUMIF('Mai 2026'!B5:B500,"Estacionamento*",'Mai 2026'!E5:E500)</f>
+        <f>'Mai 2026'!J15</f>
         <v/>
       </c>
       <c r="G20" s="98">
-        <f>SUMIF('Jun 2026'!B5:B500,"Estacionamento*",'Jun 2026'!E5:E500)</f>
+        <f>'Jun 2026'!J15</f>
         <v/>
       </c>
       <c r="H20" s="98">
-        <f>SUMIF('Jul 2026'!B5:B500,"Estacionamento*",'Jul 2026'!E5:E500)</f>
+        <f>'Jul 2026'!J15</f>
         <v/>
       </c>
       <c r="I20" s="98">
-        <f>SUMIF('Ago 2026'!B5:B500,"Estacionamento*",'Ago 2026'!G5:G500)</f>
+        <f>'Ago 2026'!L15</f>
         <v/>
       </c>
       <c r="J20" s="98">
-        <f>SUMIF('Set 2026'!B5:B500,"Estacionamento*",'Set 2026'!G5:G500)</f>
+        <f>'Set 2026'!L15</f>
         <v/>
       </c>
       <c r="K20" s="98">
-        <f>SUMIF('Out 2026'!B5:B500,"Estacionamento*",'Out 2026'!G5:G500)</f>
+        <f>'Out 2026'!L15</f>
         <v/>
       </c>
       <c r="L20" s="98">
-        <f>SUMIF('Nov 2026'!B5:B500,"Estacionamento*",'Nov 2026'!G5:G500)</f>
+        <f>'Nov 2026'!L15</f>
         <v/>
       </c>
       <c r="M20" s="98">
-        <f>SUMIF('Dez 2026'!B5:B500,"Estacionamento*",'Dez 2026'!G5:G500)</f>
+        <f>'Dez 2026'!L15</f>
         <v/>
       </c>
       <c r="N20" s="98">
@@ -53214,58 +53214,58 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" s="157">
       <c r="A21" s="97" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (−) Outras Despesas</t>
+          <t xml:space="preserve">   (−) Estacionamento (dentro de Transporte e Entregas)</t>
         </is>
       </c>
       <c r="B21" s="98">
-        <f>'Jan 2026'!J16</f>
+        <f>SUMIF('Jan 2026'!B5:B500,"Estacionamento*",'Jan 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="C21" s="98">
-        <f>'Fev 2026'!J16</f>
+        <f>SUMIF('Fev 2026'!B5:B500,"Estacionamento*",'Fev 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="D21" s="98">
-        <f>'Mar 2026'!J16</f>
+        <f>SUMIF('Mar 2026'!B5:B500,"Estacionamento*",'Mar 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="E21" s="98">
-        <f>'Abr 2026'!J16</f>
+        <f>SUMIF('Abr 2026'!B5:B500,"Estacionamento*",'Abr 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="F21" s="98">
-        <f>'Mai 2026'!J16</f>
+        <f>SUMIF('Mai 2026'!B5:B500,"Estacionamento*",'Mai 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="G21" s="98">
-        <f>'Jun 2026'!J16</f>
+        <f>SUMIF('Jun 2026'!B5:B500,"Estacionamento*",'Jun 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="H21" s="98">
-        <f>'Jul 2026'!J16</f>
+        <f>SUMIF('Jul 2026'!B5:B500,"Estacionamento*",'Jul 2026'!E5:E500)</f>
         <v/>
       </c>
       <c r="I21" s="98">
-        <f>'Ago 2026'!L16</f>
+        <f>SUMIF('Ago 2026'!B5:B500,"Estacionamento*",'Ago 2026'!G5:G500)</f>
         <v/>
       </c>
       <c r="J21" s="98">
-        <f>'Set 2026'!L16</f>
+        <f>SUMIF('Set 2026'!B5:B500,"Estacionamento*",'Set 2026'!G5:G500)</f>
         <v/>
       </c>
       <c r="K21" s="98">
-        <f>'Out 2026'!L16</f>
+        <f>SUMIF('Out 2026'!B5:B500,"Estacionamento*",'Out 2026'!G5:G500)</f>
         <v/>
       </c>
       <c r="L21" s="98">
-        <f>'Nov 2026'!L16</f>
+        <f>SUMIF('Nov 2026'!B5:B500,"Estacionamento*",'Nov 2026'!G5:G500)</f>
         <v/>
       </c>
       <c r="M21" s="98">
-        <f>'Dez 2026'!L16</f>
+        <f>SUMIF('Dez 2026'!B5:B500,"Estacionamento*",'Dez 2026'!G5:G500)</f>
         <v/>
       </c>
       <c r="N21" s="98">
@@ -53277,192 +53277,255 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="99" t="inlineStr">
+    <row r="22" s="157">
+      <c r="A22" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Outras Despesas</t>
+        </is>
+      </c>
+      <c r="B22" s="98">
+        <f>'Jan 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="C22" s="98">
+        <f>'Fev 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="D22" s="98">
+        <f>'Mar 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="E22" s="98">
+        <f>'Abr 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="F22" s="98">
+        <f>'Mai 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="G22" s="98">
+        <f>'Jun 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="H22" s="98">
+        <f>'Jul 2026'!J16</f>
+        <v/>
+      </c>
+      <c r="I22" s="98">
+        <f>'Ago 2026'!L16</f>
+        <v/>
+      </c>
+      <c r="J22" s="98">
+        <f>'Set 2026'!L16</f>
+        <v/>
+      </c>
+      <c r="K22" s="98">
+        <f>'Out 2026'!L16</f>
+        <v/>
+      </c>
+      <c r="L22" s="98">
+        <f>'Nov 2026'!L16</f>
+        <v/>
+      </c>
+      <c r="M22" s="98">
+        <f>'Dez 2026'!L16</f>
+        <v/>
+      </c>
+      <c r="N22" s="98">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="98">
+        <f>IF($B$3=0,0,N22/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" s="157">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>(=) CUSTOS FIXOS</t>
         </is>
       </c>
-      <c r="B22" s="100">
-        <f>SUM(B12:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="100">
-        <f>SUM(C12:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="100">
-        <f>SUM(D12:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="100">
-        <f>SUM(E12:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="100">
-        <f>SUM(F12:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="100">
-        <f>SUM(G12:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="100">
-        <f>SUM(H12:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="100">
-        <f>SUM(I12:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="100">
-        <f>SUM(J12:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="100">
-        <f>SUM(K12:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="100">
-        <f>SUM(L12:L21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="100">
-        <f>SUM(M12:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="100">
-        <f>SUM(B22:M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="100">
-        <f>IF($B$3=0,0,N22/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="157">
-      <c r="A23" s="103" t="inlineStr">
+      <c r="B23" s="100">
+        <f>SUM(B13:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="100">
+        <f>SUM(C13:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="100">
+        <f>SUM(D13:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="100">
+        <f>SUM(E13:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="100">
+        <f>SUM(F13:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="100">
+        <f>SUM(G13:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="100">
+        <f>SUM(H13:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="100">
+        <f>SUM(I13:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="100">
+        <f>SUM(J13:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="100">
+        <f>SUM(K13:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="100">
+        <f>SUM(L13:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="100">
+        <f>SUM(M13:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="100">
+        <f>SUM(B23:M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="100">
+        <f>IF($B$3=0,0,N23/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="157">
+      <c r="A24" s="103" t="inlineStr">
         <is>
           <t>(=) RESULTADO DO MÊS</t>
         </is>
       </c>
-      <c r="B23" s="104">
-        <f>B10-B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="104">
-        <f>C10-C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="104">
-        <f>D10-D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="104">
-        <f>E10-E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="104">
-        <f>F10-F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="104">
-        <f>G10-G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="104">
-        <f>H10-H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="104">
-        <f>I10-I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="104">
-        <f>J10-J22</f>
-        <v/>
-      </c>
-      <c r="K23" s="104">
-        <f>K10-K22</f>
-        <v/>
-      </c>
-      <c r="L23" s="104">
-        <f>L10-L22</f>
-        <v/>
-      </c>
-      <c r="M23" s="104">
-        <f>M10-M22</f>
-        <v/>
-      </c>
-      <c r="N23" s="104">
-        <f>SUM(B23:M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="104">
-        <f>IF($B$3=0,0,N23/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="101" t="inlineStr">
+      <c r="B24" s="104">
+        <f>B11-B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="104">
+        <f>C11-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="104">
+        <f>D11-D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="104">
+        <f>E11-E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="104">
+        <f>F11-F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="104">
+        <f>G11-G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="104">
+        <f>H11-H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="104">
+        <f>I11-I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="104">
+        <f>J11-J23</f>
+        <v/>
+      </c>
+      <c r="K24" s="104">
+        <f>K11-K23</f>
+        <v/>
+      </c>
+      <c r="L24" s="104">
+        <f>L11-L23</f>
+        <v/>
+      </c>
+      <c r="M24" s="104">
+        <f>M11-M23</f>
+        <v/>
+      </c>
+      <c r="N24" s="104">
+        <f>SUM(B24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="104">
+        <f>IF($B$3=0,0,N24/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" s="157">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">      Margem Líquida (%)</t>
         </is>
       </c>
-      <c r="B24" s="102">
-        <f>IF(B5=0,"",B23/B5)</f>
-        <v/>
-      </c>
-      <c r="C24" s="102">
-        <f>IF(C5=0,"",C23/C5)</f>
-        <v/>
-      </c>
-      <c r="D24" s="102">
-        <f>IF(D5=0,"",D23/D5)</f>
-        <v/>
-      </c>
-      <c r="E24" s="102">
-        <f>IF(E5=0,"",E23/E5)</f>
-        <v/>
-      </c>
-      <c r="F24" s="102">
-        <f>IF(F5=0,"",F23/F5)</f>
-        <v/>
-      </c>
-      <c r="G24" s="102">
-        <f>IF(G5=0,"",G23/G5)</f>
-        <v/>
-      </c>
-      <c r="H24" s="102">
-        <f>IF(H5=0,"",H23/H5)</f>
-        <v/>
-      </c>
-      <c r="I24" s="102">
-        <f>IF(I5=0,"",I23/I5)</f>
-        <v/>
-      </c>
-      <c r="J24" s="102">
-        <f>IF(J5=0,"",J23/J5)</f>
-        <v/>
-      </c>
-      <c r="K24" s="102">
-        <f>IF(K5=0,"",K23/K5)</f>
-        <v/>
-      </c>
-      <c r="L24" s="102">
-        <f>IF(L5=0,"",L23/L5)</f>
-        <v/>
-      </c>
-      <c r="M24" s="102">
-        <f>IF(M5=0,"",M23/M5)</f>
-        <v/>
-      </c>
-      <c r="N24" s="102">
-        <f>IF(N5=0,"",N23/N5)</f>
-        <v/>
-      </c>
-      <c r="O24" s="102">
-        <f>IF(N5=0,"",N23/N5)</f>
+      <c r="B25" s="102">
+        <f>IF(B5=0,"",B24/B5)</f>
+        <v/>
+      </c>
+      <c r="C25" s="102">
+        <f>IF(C5=0,"",C24/C5)</f>
+        <v/>
+      </c>
+      <c r="D25" s="102">
+        <f>IF(D5=0,"",D24/D5)</f>
+        <v/>
+      </c>
+      <c r="E25" s="102">
+        <f>IF(E5=0,"",E24/E5)</f>
+        <v/>
+      </c>
+      <c r="F25" s="102">
+        <f>IF(F5=0,"",F24/F5)</f>
+        <v/>
+      </c>
+      <c r="G25" s="102">
+        <f>IF(G5=0,"",G24/G5)</f>
+        <v/>
+      </c>
+      <c r="H25" s="102">
+        <f>IF(H5=0,"",H24/H5)</f>
+        <v/>
+      </c>
+      <c r="I25" s="102">
+        <f>IF(I5=0,"",I24/I5)</f>
+        <v/>
+      </c>
+      <c r="J25" s="102">
+        <f>IF(J5=0,"",J24/J5)</f>
+        <v/>
+      </c>
+      <c r="K25" s="102">
+        <f>IF(K5=0,"",K24/K5)</f>
+        <v/>
+      </c>
+      <c r="L25" s="102">
+        <f>IF(L5=0,"",L24/L5)</f>
+        <v/>
+      </c>
+      <c r="M25" s="102">
+        <f>IF(M5=0,"",M24/M5)</f>
+        <v/>
+      </c>
+      <c r="N25" s="102">
+        <f>IF(N5=0,"",N24/N5)</f>
+        <v/>
+      </c>
+      <c r="O25" s="102">
+        <f>IF(N5=0,"",N24/N5)</f>
         <v/>
       </c>
     </row>
@@ -53595,7 +53658,7 @@
     <row r="30" ht="27.95" customHeight="1" s="157">
       <c r="A30" s="182" t="inlineStr">
         <is>
-          <t>Custos Variáveis = sobem/descem com o volume vendido: mercadoria, imposto sobre faturamento (DAS) e transporte ligado ao serviço. Custos Fixos = o que a loja paga mesmo vendendo pouco (aluguel, energia, salários, contabilidade, tarifas e o estacionamento, contratado no mês).</t>
+          <t>Custos Variáveis = sobem/descem com o volume vendido: mercadoria, imposto sobre faturamento (DAS), transporte ligado ao serviço e as comissões do Wiliam (só existem quando tem troca/instalação). Custos Fixos = o que a loja paga mesmo vendendo pouco (aluguel, energia, salários, contabilidade, tarifas e o estacionamento, contratado no mês).</t>
         </is>
       </c>
     </row>
@@ -57739,7 +57802,7 @@
         </is>
       </c>
       <c r="B6" s="57">
-        <f>'DRE Simplificado'!O9</f>
+        <f>'DRE Simplificado'!O10</f>
         <v/>
       </c>
     </row>
@@ -57750,7 +57813,7 @@
         </is>
       </c>
       <c r="B7" s="55">
-        <f>'DRE Simplificado'!O10</f>
+        <f>'DRE Simplificado'!O11</f>
         <v/>
       </c>
     </row>
@@ -57772,7 +57835,7 @@
         </is>
       </c>
       <c r="B9" s="55">
-        <f>'DRE Simplificado'!O22</f>
+        <f>'DRE Simplificado'!O23</f>
         <v/>
       </c>
     </row>
@@ -57794,7 +57857,7 @@
         </is>
       </c>
       <c r="B11" s="55">
-        <f>'DRE Simplificado'!O23</f>
+        <f>'DRE Simplificado'!O24</f>
         <v/>
       </c>
     </row>
@@ -58095,7 +58158,7 @@
         <v/>
       </c>
       <c r="D7" s="65">
-        <f>('DRE Simplificado'!O9+'DRE Simplificado'!O22)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
         <v/>
       </c>
       <c r="E7" s="55">
@@ -58121,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="65">
-        <f>('DRE Simplificado'!O9+'DRE Simplificado'!O22)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
         <v/>
       </c>
       <c r="E8" s="57">
@@ -58147,7 +58210,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="65">
-        <f>('DRE Simplificado'!O9+'DRE Simplificado'!O22)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
         <v/>
       </c>
       <c r="E9" s="55">
@@ -58173,7 +58236,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="65">
-        <f>('DRE Simplificado'!O9+'DRE Simplificado'!O22)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
         <v/>
       </c>
       <c r="E10" s="57">
@@ -58309,7 +58372,7 @@
         </is>
       </c>
       <c r="B6" s="57">
-        <f>'DRE Simplificado'!O22</f>
+        <f>'DRE Simplificado'!O23</f>
         <v/>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -41525,50 +41525,130 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="17" t="n"/>
-      <c r="B185" s="18" t="n"/>
-      <c r="C185" s="18" t="n"/>
-      <c r="D185" s="27" t="n"/>
-      <c r="E185" s="18" t="n"/>
-      <c r="F185" s="19" t="n"/>
+      <c r="A185" s="17" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B185" s="18" t="inlineStr">
+        <is>
+          <t>José Bartolomeu Doria Marques</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D185" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F185" s="19" t="n">
+        <v>4.56</v>
+      </c>
       <c r="G185" s="19" t="n"/>
       <c r="H185" s="21" t="n"/>
       <c r="I185" s="18" t="n"/>
-      <c r="J185" s="18" t="n"/>
+      <c r="J185" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0571</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="44" t="n"/>
-      <c r="B186" s="45" t="n"/>
-      <c r="C186" s="45" t="n"/>
-      <c r="D186" s="46" t="n"/>
-      <c r="E186" s="45" t="n"/>
+      <c r="A186" s="44" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B186" s="45" t="inlineStr">
+        <is>
+          <t>Silmara Variedades</t>
+        </is>
+      </c>
+      <c r="C186" s="45" t="inlineStr">
+        <is>
+          <t>Refil E3 + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D186" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E186" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F186" s="47" t="n"/>
       <c r="G186" s="48" t="n"/>
       <c r="H186" s="49" t="n"/>
       <c r="I186" s="45" t="n"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>EMP-0217</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="17" t="n"/>
-      <c r="B187" s="18" t="n"/>
+      <c r="A187" s="17" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B187" s="18" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
       <c r="C187" s="18" t="n"/>
       <c r="D187" s="27" t="n"/>
       <c r="E187" s="18" t="n"/>
       <c r="F187" s="19" t="n"/>
-      <c r="G187" s="19" t="n"/>
-      <c r="H187" s="21" t="n"/>
-      <c r="I187" s="18" t="n"/>
+      <c r="G187" s="19" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="H187" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I187" s="18" t="inlineStr">
+        <is>
+          <t>Boleto doc. 133138/2 (emissão 12/08/2026) · parcela 2/4 — venc. 23/09/2026. Pago em 23/09/2026.</t>
+        </is>
+      </c>
       <c r="J187" s="18" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="44" t="n"/>
-      <c r="B188" s="45" t="n"/>
-      <c r="C188" s="45" t="n"/>
-      <c r="D188" s="46" t="n"/>
-      <c r="E188" s="45" t="n"/>
+      <c r="A188" s="44" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B188" s="45" t="inlineStr">
+        <is>
+          <t>Colégio Alfa e Ômega</t>
+        </is>
+      </c>
+      <c r="C188" s="45" t="inlineStr">
+        <is>
+          <t>Refil Carbon Tech 9"</t>
+        </is>
+      </c>
+      <c r="D188" s="46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E188" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F188" s="47" t="n"/>
       <c r="G188" s="48" t="n"/>
       <c r="H188" s="49" t="n"/>
       <c r="I188" s="45" t="n"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>ESC-0022</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="17" t="n"/>
@@ -55273,7 +55353,7 @@
       </c>
       <c r="E56" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F56" s="113">
@@ -55282,7 +55362,7 @@
       </c>
       <c r="G56" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257850-6. Linha digitável 34191.09008 25785.061430 81531.550002 4 15780000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257850-6. Linha digitável 34191.09008 25785.061430 81531.550002 4 15780000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 23/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -36723,7 +36723,7 @@
     </row>
     <row r="24">
       <c r="A24" s="81" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B24" s="82" t="inlineStr">
         <is>
@@ -36740,13 +36740,17 @@
       </c>
       <c r="E24" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F24" s="83" t="n"/>
       <c r="G24" s="83" t="n"/>
       <c r="H24" s="82" t="n"/>
-      <c r="I24" s="82" t="n"/>
+      <c r="I24" s="82" t="inlineStr">
+        <is>
+          <t>Venda de 02/09/2026 — pagamento recebido via Pix em 08/09/2026</t>
+        </is>
+      </c>
       <c r="J24" s="82" t="inlineStr">
         <is>
           <t>EMP-0289</t>
@@ -37208,7 +37212,7 @@
     </row>
     <row r="39">
       <c r="A39" s="77" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B39" s="78" t="inlineStr">
         <is>
@@ -37229,7 +37233,7 @@
       </c>
       <c r="I39" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 72869 (emissão 07/05/2026) — venc. 04/09/2026. Pago em 03/09/2026.</t>
+          <t>Boleto doc. 72869 (emissão 07/05/2026) — venc. 04/09/2026. Pago em 04/09/2026 pelo Banco do Nordeste, DOC 5301.</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38352,12 @@
       <c r="H75" s="78" t="n"/>
       <c r="I75" s="78" t="inlineStr">
         <is>
-          <t>Crédito em 10x</t>
+          <t>Crédito em 10x. Instalação feita em 24/09/2026.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>CLI-0896</t>
         </is>
       </c>
     </row>
@@ -41651,119 +41660,299 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="17" t="n"/>
-      <c r="B189" s="18" t="n"/>
+      <c r="A189" s="17" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B189" s="18" t="inlineStr">
+        <is>
+          <t>Tarifa Pix (Cobrança QR Code)</t>
+        </is>
+      </c>
       <c r="C189" s="18" t="n"/>
       <c r="D189" s="27" t="n"/>
       <c r="E189" s="18" t="n"/>
       <c r="F189" s="19" t="n"/>
-      <c r="G189" s="19" t="n"/>
-      <c r="H189" s="21" t="n"/>
-      <c r="I189" s="18" t="n"/>
+      <c r="G189" s="19" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H189" s="21" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I189" s="18" t="inlineStr">
+        <is>
+          <t>DOC 12423</t>
+        </is>
+      </c>
       <c r="J189" s="18" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="44" t="n"/>
-      <c r="B190" s="45" t="n"/>
+      <c r="A190" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B190" s="45" t="inlineStr">
+        <is>
+          <t>Centralmix Soluções Integradas</t>
+        </is>
+      </c>
       <c r="C190" s="45" t="n"/>
       <c r="D190" s="46" t="n"/>
       <c r="E190" s="45" t="n"/>
       <c r="F190" s="47" t="n"/>
-      <c r="G190" s="48" t="n"/>
-      <c r="H190" s="49" t="n"/>
-      <c r="I190" s="45" t="n"/>
+      <c r="G190" s="48" t="n">
+        <v>60</v>
+      </c>
+      <c r="H190" s="49" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I190" s="45" t="inlineStr">
+        <is>
+          <t>Recarga de cartucho da impressora — Pix em 08/09/2026 pelo Banco do Nordeste, DOC 11974.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="17" t="n"/>
-      <c r="B191" s="18" t="n"/>
-      <c r="C191" s="18" t="n"/>
-      <c r="D191" s="27" t="n"/>
-      <c r="E191" s="18" t="n"/>
-      <c r="F191" s="19" t="n"/>
+      <c r="A191" s="17" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B191" s="18" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>Registro + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D191" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E191" s="18" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F191" s="19" t="n">
+        <v>3.16</v>
+      </c>
       <c r="G191" s="19" t="n"/>
       <c r="H191" s="21" t="n"/>
       <c r="I191" s="18" t="n"/>
       <c r="J191" s="18" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="44" t="n"/>
-      <c r="B192" s="45" t="n"/>
-      <c r="C192" s="45" t="n"/>
-      <c r="D192" s="46" t="n"/>
-      <c r="E192" s="45" t="n"/>
+      <c r="A192" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B192" s="45" t="inlineStr">
+        <is>
+          <t>Thainara</t>
+        </is>
+      </c>
+      <c r="C192" s="45" t="inlineStr">
+        <is>
+          <t>Refil FPA14</t>
+        </is>
+      </c>
+      <c r="D192" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E192" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F192" s="47" t="n"/>
       <c r="G192" s="48" t="n"/>
       <c r="H192" s="49" t="n"/>
       <c r="I192" s="45" t="n"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>CLI-0897</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="17" t="n"/>
-      <c r="B193" s="18" t="n"/>
-      <c r="C193" s="18" t="n"/>
-      <c r="D193" s="27" t="n"/>
-      <c r="E193" s="18" t="n"/>
+      <c r="A193" s="17" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B193" s="18" t="inlineStr">
+        <is>
+          <t>4x4 Peças e Serviços</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D193" s="27" t="n">
+        <v>280</v>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F193" s="19" t="n"/>
       <c r="G193" s="19" t="n"/>
       <c r="H193" s="21" t="n"/>
-      <c r="I193" s="18" t="n"/>
-      <c r="J193" s="18" t="n"/>
+      <c r="I193" s="18" t="inlineStr">
+        <is>
+          <t>Dois purificadores: entrada e oficina</t>
+        </is>
+      </c>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0001</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="44" t="n"/>
-      <c r="B194" s="45" t="n"/>
-      <c r="C194" s="45" t="n"/>
-      <c r="D194" s="46" t="n"/>
-      <c r="E194" s="45" t="n"/>
+      <c r="A194" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B194" s="45" t="inlineStr">
+        <is>
+          <t>Labcenter Saude Preventiva e Diagnostico</t>
+        </is>
+      </c>
+      <c r="C194" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D194" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E194" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F194" s="47" t="n"/>
       <c r="G194" s="48" t="n"/>
       <c r="H194" s="49" t="n"/>
       <c r="I194" s="45" t="n"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>EMP-0198</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="17" t="n"/>
-      <c r="B195" s="18" t="n"/>
+      <c r="A195" s="17" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>Combustível (Etanol) — Transvale</t>
+        </is>
+      </c>
       <c r="C195" s="18" t="n"/>
       <c r="D195" s="27" t="n"/>
       <c r="E195" s="18" t="n"/>
       <c r="F195" s="19" t="n"/>
-      <c r="G195" s="19" t="n"/>
-      <c r="H195" s="21" t="n"/>
-      <c r="I195" s="18" t="n"/>
+      <c r="G195" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="H195" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I195" s="18" t="inlineStr">
+        <is>
+          <t>8,248 L de etanol hidratado a R$ 4,85/L — NFC-e nº 000284840 (Transvale Derivados de Petróleo, CNPJ 11.271.229/0002-68). Pago em dinheiro.</t>
+        </is>
+      </c>
       <c r="J195" s="18" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="44" t="n"/>
-      <c r="B196" s="45" t="n"/>
+      <c r="A196" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B196" s="45" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
       <c r="C196" s="45" t="n"/>
       <c r="D196" s="46" t="n"/>
       <c r="E196" s="45" t="n"/>
       <c r="F196" s="47" t="n"/>
-      <c r="G196" s="48" t="n"/>
-      <c r="H196" s="49" t="n"/>
-      <c r="I196" s="45" t="n"/>
+      <c r="G196" s="48" t="n">
+        <v>940.0599999999999</v>
+      </c>
+      <c r="H196" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I196" s="45" t="inlineStr">
+        <is>
+          <t>Boleto doc. 75472 (emissão 26/08/2026) · parcela 1/5 — venc. 25/09/2026. Pago antecipado em 24/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="17" t="n"/>
-      <c r="B197" s="18" t="n"/>
+      <c r="A197" s="17" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B197" s="18" t="inlineStr">
+        <is>
+          <t>SEFAZ-BA — ICMS Antecipação Parcial</t>
+        </is>
+      </c>
       <c r="C197" s="18" t="n"/>
       <c r="D197" s="27" t="n"/>
       <c r="E197" s="18" t="n"/>
       <c r="F197" s="19" t="n"/>
-      <c r="G197" s="19" t="n"/>
-      <c r="H197" s="21" t="n"/>
-      <c r="I197" s="18" t="n"/>
+      <c r="G197" s="19" t="n">
+        <v>1712.7</v>
+      </c>
+      <c r="H197" s="21" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I197" s="18" t="inlineStr">
+        <is>
+          <t>DAE ICMS Antecipação Parcial ref. 08/2026 (cód. 2175, nº 1965056088) — venc. 25/09/2026. Pago antecipado em 24/09/2026.</t>
+        </is>
+      </c>
       <c r="J197" s="18" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="44" t="n"/>
-      <c r="B198" s="45" t="n"/>
+      <c r="A198" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B198" s="45" t="inlineStr">
+        <is>
+          <t>SEFAZ-BA — ICMS Antecipação Tributária</t>
+        </is>
+      </c>
       <c r="C198" s="45" t="n"/>
       <c r="D198" s="46" t="n"/>
       <c r="E198" s="45" t="n"/>
       <c r="F198" s="47" t="n"/>
-      <c r="G198" s="48" t="n"/>
-      <c r="H198" s="49" t="n"/>
-      <c r="I198" s="45" t="n"/>
+      <c r="G198" s="48" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="H198" s="49" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I198" s="45" t="inlineStr">
+        <is>
+          <t>DAE ICMS Antecipação Tributária ref. 08/2026 (cód. 1145, nº 1965056107) — venc. 25/09/2026. Pago antecipado em 24/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="17" t="n"/>
@@ -53787,7 +53976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -53838,7 +54027,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D77</f>
+        <f>D82</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -54178,7 +54367,7 @@
       </c>
       <c r="G19" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 03/09/2026 — lançado em "Set 2026" como "Eversoft" (R$ 980,83).</t>
+          <t>Categoria: Fornecedores / Mercadoria. Pago em 04/09/2026 pelo Banco do Nordeste (DOC 5301) — lançado em "Set 2026" como "Eversoft" (R$ 980,83).</t>
         </is>
       </c>
     </row>
@@ -54489,7 +54678,7 @@
       </c>
       <c r="E29" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F29" s="112">
@@ -54498,7 +54687,7 @@
       </c>
       <c r="G29" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604587-0. Linha digitável 34191.12333 60458.700303 55679.010003 3 15800000094006. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604587-0. Linha digitável 34191.12333 60458.700303 55679.010003 3 15800000094006. Após o vencimento: juros ao dia + multa de 2%. Pago em 24/09/2026 (antecipado, venc. 25/09) — lançado em "Set 2026" como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -55737,7 +55926,7 @@
       </c>
       <c r="E68" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F68" s="113">
@@ -55746,7 +55935,7 @@
       </c>
       <c r="G68" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85890000017 4 12700005202 5 60925196505 0 60882175193 3.</t>
+          <t>Categoria: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85890000017 4 12700005202 5 60925196505 0 60882175193 3. Pago em 24/09/2026 (antecipado, venc. 25/09) — lançado em "Set 2026" como "SEFAZ-BA — ICMS Antecipação Parcial".</t>
         </is>
       </c>
     </row>
@@ -55769,7 +55958,7 @@
       </c>
       <c r="E69" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F69" s="113">
@@ -55778,7 +55967,7 @@
       </c>
       <c r="G69" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85870000000 6 74050005202 0 60925196505 0 61070133812 7.</t>
+          <t>Categoria: Impostos e Taxas. Inscrição Estadual 066.200.856. Linha digitável 85870000000 6 74050005202 0 60925196505 0 61070133812 7. Pago em 24/09/2026 (antecipado, venc. 25/09) — lançado em "Set 2026" como "SEFAZ-BA — ICMS Antecipação Tributária".</t>
         </is>
       </c>
     </row>
@@ -55910,7 +56099,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" s="157">
       <c r="A74" s="82" t="inlineStr">
         <is>
           <t>Patrus Transportes Ltda</t>
@@ -55942,1014 +56131,1015 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="86" t="inlineStr">
+    <row r="75" s="157">
+      <c r="A75" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386838 (emissão 23/09/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C75" s="81" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D75" s="83" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E75" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F75" s="113">
+        <f>IF(OR($E75="Pago",$C75=""),"",MAX(0,TODAY()-$C75))</f>
+        <v/>
+      </c>
+      <c r="G75" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" s="157">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386838 (emissão 23/09/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C76" s="81" t="n">
+        <v>46348</v>
+      </c>
+      <c r="D76" s="83" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E76" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F76" s="113">
+        <f>IF(OR($E76="Pago",$C76=""),"",MAX(0,TODAY()-$C76))</f>
+        <v/>
+      </c>
+      <c r="G76" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910775. Linha digitável 34191.12366 91077.530300 52238.850003 6 16380000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" s="157">
+      <c r="A77" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B77" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386838 (emissão 23/09/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C77" s="81" t="n">
+        <v>46378</v>
+      </c>
+      <c r="D77" s="83" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E77" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F77" s="113">
+        <f>IF(OR($E77="Pago",$C77=""),"",MAX(0,TODAY()-$C77))</f>
+        <v/>
+      </c>
+      <c r="G77" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910730. Linha digitável 34191.12366 91073.080300 52238.850003 7 16680000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="157">
+      <c r="A78" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B78" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386838 (emissão 23/09/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C78" s="81" t="n">
+        <v>46408</v>
+      </c>
+      <c r="D78" s="83" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E78" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F78" s="113">
+        <f>IF(OR($E78="Pago",$C78=""),"",MAX(0,TODAY()-$C78))</f>
+        <v/>
+      </c>
+      <c r="G78" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910821. Linha digitável 34191.12366 91082.150300 52238.850003 9 16980000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" s="157">
+      <c r="A79" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B79" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 386838 (emissão 23/09/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C79" s="81" t="n">
+        <v>46438</v>
+      </c>
+      <c r="D79" s="83" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E79" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F79" s="113">
+        <f>IF(OR($E79="Pago",$C79=""),"",MAX(0,TODAY()-$C79))</f>
+        <v/>
+      </c>
+      <c r="G79" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910791. Linha digitável 34191.12366 91079.100300 52238.850003 7 17280000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" s="157">
+      <c r="A80" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B75" s="86" t="n"/>
-      <c r="C75" s="114" t="n"/>
-      <c r="D75" s="115">
-        <f>SUMIF(E11:E74,"Pendente",D11:D74)</f>
-        <v/>
-      </c>
-      <c r="E75" s="116" t="n"/>
-      <c r="F75" s="116" t="n"/>
-      <c r="G75" s="86" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="144" t="inlineStr">
+      <c r="B80" s="86" t="n"/>
+      <c r="C80" s="114" t="n"/>
+      <c r="D80" s="115">
+        <f>SUMIF(E11:E79,"Pendente",D11:D79)</f>
+        <v/>
+      </c>
+      <c r="E80" s="116" t="n"/>
+      <c r="F80" s="116" t="n"/>
+      <c r="G80" s="86" t="n"/>
+    </row>
+    <row r="81" s="157">
+      <c r="A81" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B76" s="144" t="n"/>
-      <c r="C76" s="145" t="n"/>
-      <c r="D76" s="146">
-        <f>SUMIF(E11:E74,"Previsto",D11:D74)</f>
-        <v/>
-      </c>
-      <c r="E76" s="142" t="n"/>
-      <c r="F76" s="142" t="n"/>
-      <c r="G76" s="144" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="86" t="inlineStr">
+      <c r="B81" s="144" t="n"/>
+      <c r="C81" s="145" t="n"/>
+      <c r="D81" s="146">
+        <f>SUMIF(E11:E79,"Previsto",D11:D79)</f>
+        <v/>
+      </c>
+      <c r="E81" s="142" t="n"/>
+      <c r="F81" s="142" t="n"/>
+      <c r="G81" s="144" t="n"/>
+    </row>
+    <row r="82" s="157">
+      <c r="A82" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B77" s="86" t="n"/>
-      <c r="C77" s="114" t="n"/>
-      <c r="D77" s="115">
-        <f>D75+D76</f>
-        <v/>
-      </c>
-      <c r="E77" s="116" t="n"/>
-      <c r="F77" s="116" t="n"/>
-      <c r="G77" s="86" t="n"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" s="157"/>
-    <row r="80" ht="15.75" customHeight="1" s="157">
-      <c r="A80" s="200" t="inlineStr">
+      <c r="B82" s="86" t="n"/>
+      <c r="C82" s="114" t="n"/>
+      <c r="D82" s="115">
+        <f>D80+D81</f>
+        <v/>
+      </c>
+      <c r="E82" s="116" t="n"/>
+      <c r="F82" s="116" t="n"/>
+      <c r="G82" s="86" t="n"/>
+    </row>
+    <row r="83" s="157"/>
+    <row r="84" ht="15.75" customHeight="1" s="157"/>
+    <row r="85" ht="15.75" customHeight="1" s="157">
+      <c r="A85" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="194" t="inlineStr">
+    <row r="86" s="157">
+      <c r="A86" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="111" t="inlineStr">
+    <row r="87" s="157">
+      <c r="A87" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B82" s="111" t="inlineStr">
+      <c r="B87" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C82" s="111" t="inlineStr">
+      <c r="C87" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D82" s="111" t="inlineStr">
+      <c r="D87" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E82" s="111" t="inlineStr">
+      <c r="E87" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F82" s="111" t="inlineStr">
+      <c r="F87" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G82" s="111" t="inlineStr">
+      <c r="G87" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="78" t="inlineStr">
+    <row r="88" s="157">
+      <c r="A88" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B83" s="78" t="inlineStr">
+      <c r="B88" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C83" s="77" t="n">
+      <c r="C88" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D83" s="79" t="n">
+      <c r="D88" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E83" s="112" t="inlineStr">
+      <c r="E88" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F83" s="112">
-        <f>IF(OR($E83="Recebido",$C83=""),"",MAX(0,TODAY()-$C83))</f>
-        <v/>
-      </c>
-      <c r="G83" s="78" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="82" t="inlineStr">
+      <c r="F88" s="112">
+        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="78" t="n"/>
+    </row>
+    <row r="89" s="157">
+      <c r="A89" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="B89" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C84" s="81" t="n">
+      <c r="C89" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D84" s="83" t="n">
+      <c r="D89" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E84" s="113" t="inlineStr">
+      <c r="E89" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F84" s="113">
-        <f>IF(OR($E84="Recebido",$C84=""),"",MAX(0,TODAY()-$C84))</f>
-        <v/>
-      </c>
-      <c r="G84" s="82" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="78" t="inlineStr">
+      <c r="F89" s="113">
+        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="82" t="n"/>
+    </row>
+    <row r="90" s="157">
+      <c r="A90" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B85" s="78" t="inlineStr">
+      <c r="B90" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C85" s="77" t="n">
+      <c r="C90" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D85" s="79" t="n">
+      <c r="D90" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E85" s="112" t="inlineStr">
+      <c r="E90" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F85" s="112">
-        <f>IF(OR($E85="Recebido",$C85=""),"",MAX(0,TODAY()-$C85))</f>
-        <v/>
-      </c>
-      <c r="G85" s="78" t="inlineStr">
+      <c r="F90" s="112">
+        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="82" t="inlineStr">
+    <row r="91" s="157">
+      <c r="A91" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B86" s="82" t="inlineStr">
+      <c r="B91" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C86" s="81" t="n">
+      <c r="C91" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D86" s="83" t="n">
+      <c r="D91" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E86" s="113" t="inlineStr">
+      <c r="E91" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F86" s="113">
-        <f>IF(OR($E86="Recebido",$C86=""),"",MAX(0,TODAY()-$C86))</f>
-        <v/>
-      </c>
-      <c r="G86" s="82" t="inlineStr">
+      <c r="F91" s="113">
+        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="78" t="inlineStr">
+    <row r="92" s="157">
+      <c r="A92" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B87" s="78" t="inlineStr">
+      <c r="B92" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C87" s="77" t="n">
+      <c r="C92" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D87" s="79" t="n">
+      <c r="D92" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E87" s="112" t="inlineStr">
+      <c r="E92" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F87" s="112">
-        <f>IF(OR($E87="Recebido",$C87=""),"",MAX(0,TODAY()-$C87))</f>
-        <v/>
-      </c>
-      <c r="G87" s="78" t="inlineStr">
+      <c r="F92" s="112">
+        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="82" t="inlineStr">
+    <row r="93" s="157">
+      <c r="A93" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B88" s="82" t="inlineStr">
+      <c r="B93" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C88" s="81" t="n">
+      <c r="C93" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D88" s="83" t="n">
+      <c r="D93" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E88" s="113" t="inlineStr">
+      <c r="E93" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F88" s="113">
-        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
-        <v/>
-      </c>
-      <c r="G88" s="82" t="inlineStr">
+      <c r="F93" s="113">
+        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="78" t="inlineStr">
+    <row r="94" s="157">
+      <c r="A94" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B89" s="78" t="inlineStr">
+      <c r="B94" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C89" s="77" t="n">
+      <c r="C94" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D89" s="79" t="n">
+      <c r="D94" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E89" s="112" t="inlineStr">
+      <c r="E94" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F89" s="112">
-        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
-        <v/>
-      </c>
-      <c r="G89" s="78" t="inlineStr">
+      <c r="F94" s="112">
+        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="82" t="inlineStr">
+    <row r="95" s="157">
+      <c r="A95" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B90" s="82" t="inlineStr">
+      <c r="B95" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C90" s="81" t="n">
+      <c r="C95" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D90" s="83" t="n">
+      <c r="D95" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E90" s="113" t="inlineStr">
+      <c r="E95" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F90" s="113">
-        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
-        <v/>
-      </c>
-      <c r="G90" s="82" t="inlineStr">
+      <c r="F95" s="113">
+        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="78" t="inlineStr">
+    <row r="96" s="157">
+      <c r="A96" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B91" s="78" t="inlineStr">
+      <c r="B96" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C91" s="77" t="n">
+      <c r="C96" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D91" s="79" t="n">
+      <c r="D96" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E91" s="112" t="inlineStr">
+      <c r="E96" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F91" s="112">
-        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
-        <v/>
-      </c>
-      <c r="G91" s="78" t="inlineStr">
+      <c r="F96" s="112">
+        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="82" t="inlineStr">
+    <row r="97" s="157">
+      <c r="A97" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B92" s="82" t="inlineStr">
+      <c r="B97" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C92" s="81" t="n">
+      <c r="C97" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D92" s="83" t="n">
+      <c r="D97" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E92" s="113" t="inlineStr">
+      <c r="E97" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F92" s="113">
-        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
-        <v/>
-      </c>
-      <c r="G92" s="82" t="inlineStr">
+      <c r="F97" s="113">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="78" t="inlineStr">
+    <row r="98" s="157">
+      <c r="A98" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B93" s="78" t="inlineStr">
+      <c r="B98" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C93" s="77" t="n">
+      <c r="C98" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D93" s="79" t="n">
+      <c r="D98" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E93" s="112" t="inlineStr">
+      <c r="E98" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F93" s="112">
-        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
-        <v/>
-      </c>
-      <c r="G93" s="78" t="inlineStr">
+      <c r="F98" s="112">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="82" t="inlineStr">
+    <row r="99" s="157">
+      <c r="A99" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B94" s="82" t="inlineStr">
+      <c r="B99" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C94" s="81" t="n">
+      <c r="C99" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D94" s="83" t="n">
+      <c r="D99" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E94" s="113" t="inlineStr">
+      <c r="E99" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="113">
-        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
-        <v/>
-      </c>
-      <c r="G94" s="82" t="inlineStr">
+      <c r="F99" s="113">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="78" t="inlineStr">
+    <row r="100" s="157">
+      <c r="A100" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B95" s="78" t="inlineStr">
+      <c r="B100" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C95" s="77" t="n">
+      <c r="C100" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D95" s="79" t="n">
+      <c r="D100" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E95" s="112" t="inlineStr">
+      <c r="E100" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F95" s="112">
-        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
-        <v/>
-      </c>
-      <c r="G95" s="78" t="inlineStr">
+      <c r="F100" s="112">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="82" t="inlineStr">
+    <row r="101" s="157">
+      <c r="A101" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B96" s="82" t="inlineStr">
+      <c r="B101" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C96" s="81" t="n">
+      <c r="C101" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D96" s="83" t="n">
+      <c r="D101" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E96" s="113" t="inlineStr">
+      <c r="E101" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F96" s="113">
-        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
-        <v/>
-      </c>
-      <c r="G96" s="82" t="inlineStr">
+      <c r="F101" s="113">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="78" t="inlineStr">
+    <row r="102" s="157">
+      <c r="A102" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B97" s="78" t="inlineStr">
+      <c r="B102" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C97" s="77" t="n">
+      <c r="C102" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D97" s="79" t="n">
+      <c r="D102" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E97" s="112" t="inlineStr">
+      <c r="E102" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F97" s="112">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="78" t="inlineStr">
+      <c r="F102" s="112">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="82" t="inlineStr">
+    <row r="103" s="157">
+      <c r="A103" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B98" s="82" t="inlineStr">
+      <c r="B103" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C98" s="81" t="n">
+      <c r="C103" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D98" s="83" t="n">
+      <c r="D103" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E98" s="113" t="inlineStr">
+      <c r="E103" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="113">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="82" t="inlineStr">
+      <c r="F103" s="113">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="78" t="inlineStr">
+    <row r="104" s="157">
+      <c r="A104" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B99" s="78" t="inlineStr">
+      <c r="B104" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C99" s="77" t="n">
+      <c r="C104" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D99" s="79" t="n">
+      <c r="D104" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E99" s="112" t="inlineStr">
+      <c r="E104" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F99" s="112">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="78" t="inlineStr">
+      <c r="F104" s="112">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="82" t="inlineStr">
+    <row r="105" s="157">
+      <c r="A105" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B100" s="82" t="inlineStr">
+      <c r="B105" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C100" s="81" t="n">
+      <c r="C105" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D100" s="83" t="n">
+      <c r="D105" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E100" s="113" t="inlineStr">
+      <c r="E105" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F100" s="113">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="82" t="inlineStr">
+      <c r="F105" s="113">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="78" t="inlineStr">
+    <row r="106" s="157">
+      <c r="A106" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B101" s="78" t="inlineStr">
+      <c r="B106" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C101" s="77" t="n">
+      <c r="C106" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D101" s="79" t="n">
+      <c r="D106" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E101" s="112" t="inlineStr">
+      <c r="E106" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F101" s="112">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="78" t="inlineStr">
+      <c r="F106" s="112">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="82" t="inlineStr">
+    <row r="107" s="157">
+      <c r="A107" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B102" s="82" t="inlineStr">
+      <c r="B107" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C102" s="81" t="n">
+      <c r="C107" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D102" s="83" t="n">
+      <c r="D107" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E102" s="113" t="inlineStr">
+      <c r="E107" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F102" s="113">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="82" t="inlineStr">
+      <c r="F107" s="113">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="78" t="inlineStr">
+    <row r="108" s="157">
+      <c r="A108" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B103" s="78" t="inlineStr">
+      <c r="B108" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C103" s="77" t="n">
+      <c r="C108" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D103" s="79" t="n">
+      <c r="D108" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E103" s="112" t="inlineStr">
+      <c r="E108" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F103" s="112">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="78" t="inlineStr">
+      <c r="F108" s="112">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="82" t="inlineStr">
+    <row r="109" s="157">
+      <c r="A109" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B104" s="82" t="inlineStr">
+      <c r="B109" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C104" s="81" t="n">
+      <c r="C109" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D104" s="83" t="n">
+      <c r="D109" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E104" s="113" t="inlineStr">
+      <c r="E109" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F104" s="113">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="82" t="inlineStr">
+      <c r="F109" s="113">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="78" t="inlineStr">
+    <row r="110" s="157">
+      <c r="A110" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B105" s="78" t="inlineStr">
+      <c r="B110" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C105" s="77" t="n">
+      <c r="C110" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D105" s="79" t="n">
+      <c r="D110" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E105" s="112" t="inlineStr">
+      <c r="E110" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F105" s="112">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="78" t="inlineStr">
+      <c r="F110" s="112">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="82" t="inlineStr">
+    <row r="111" s="157">
+      <c r="A111" s="82" t="inlineStr">
         <is>
           <t>Instituto Paulo Leão</t>
         </is>
       </c>
-      <c r="B106" s="82" t="inlineStr">
+      <c r="B111" s="82" t="inlineStr">
         <is>
           <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
-      <c r="C106" s="81" t="n">
+      <c r="C111" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D106" s="83" t="n">
+      <c r="D111" s="83" t="n">
         <v>160</v>
       </c>
-      <c r="E106" s="113" t="inlineStr">
+      <c r="E111" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F106" s="113">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="78" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B107" s="78" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C107" s="77" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D107" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="E107" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F107" s="112">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B108" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C108" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D108" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E108" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F108" s="113">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B109" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C109" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D109" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E109" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F109" s="112">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B110" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C110" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D110" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E110" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F110" s="113">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="82" t="inlineStr">
-        <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
-        </is>
-      </c>
-      <c r="B111" s="82" t="inlineStr">
-        <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C111" s="81" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D111" s="83" t="n">
-        <v>540</v>
-      </c>
-      <c r="E111" s="113" t="inlineStr">
-        <is>
-          <t>Pendente</t>
         </is>
       </c>
       <c r="F111" s="113">
@@ -56958,26 +57148,26 @@
       </c>
       <c r="G111" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" s="157">
       <c r="A112" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
       <c r="B112" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="C112" s="77" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D112" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E112" s="112" t="inlineStr">
         <is>
@@ -56990,58 +57180,58 @@
       </c>
       <c r="G112" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B113" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C113" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D113" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E113" s="112" t="inlineStr">
+          <t>Recebido via Pix em 03/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" s="157">
+      <c r="A113" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B113" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C113" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E113" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F113" s="112">
+      <c r="F113" s="113">
         <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
         <v/>
       </c>
-      <c r="G113" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
+      <c r="G113" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" s="157">
       <c r="A114" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B114" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C114" s="77" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="D114" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E114" s="112" t="inlineStr">
         <is>
@@ -57058,86 +57248,86 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B115" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C115" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D115" s="79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E115" s="112" t="inlineStr">
+    <row r="115" s="157">
+      <c r="A115" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B115" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C115" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D115" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E115" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F115" s="112">
+      <c r="F115" s="113">
         <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
         <v/>
       </c>
-      <c r="G115" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="78" t="inlineStr">
-        <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
-        </is>
-      </c>
-      <c r="B116" s="78" t="inlineStr">
+      <c r="G115" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" s="157">
+      <c r="A116" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B116" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C116" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D116" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E116" s="113" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F116" s="113">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" s="157">
+      <c r="A117" s="78" t="inlineStr">
+        <is>
+          <t>Cecilio Mota Junior</t>
+        </is>
+      </c>
+      <c r="B117" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C116" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D116" s="79" t="n">
+      <c r="C117" s="77" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D117" s="79" t="n">
         <v>140</v>
-      </c>
-      <c r="E116" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F116" s="112">
-        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="78" t="inlineStr">
-        <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
-        </is>
-      </c>
-      <c r="B117" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C117" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D117" s="79" t="n">
-        <v>200</v>
       </c>
       <c r="E117" s="112" t="inlineStr">
         <is>
@@ -57150,30 +57340,30 @@
       </c>
       <c r="G117" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" s="157">
       <c r="A118" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B118" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C118" s="77" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="D118" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E118" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F118" s="112">
@@ -57182,23 +57372,23 @@
       </c>
       <c r="G118" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
+          <t>Recebido via Pix em 04/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" s="157">
       <c r="A119" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B119" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C119" s="77" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D119" s="79" t="n">
         <v>140</v>
@@ -57214,26 +57404,26 @@
       </c>
       <c r="G119" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" s="157">
       <c r="A120" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B120" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C120" s="77" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D120" s="79" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E120" s="112" t="inlineStr">
         <is>
@@ -57246,30 +57436,30 @@
       </c>
       <c r="G120" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" s="157">
       <c r="A121" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B121" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C121" s="77" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D121" s="79" t="n">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E121" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F121" s="112">
@@ -57278,14 +57468,14 @@
       </c>
       <c r="G121" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" s="157">
       <c r="A122" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B122" s="78" t="inlineStr">
@@ -57294,7 +57484,7 @@
         </is>
       </c>
       <c r="C122" s="77" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="D122" s="79" t="n">
         <v>200</v>
@@ -57310,26 +57500,26 @@
       </c>
       <c r="G122" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" s="157">
       <c r="A123" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B123" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C123" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D123" s="79" t="n">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="E123" s="112" t="inlineStr">
         <is>
@@ -57342,14 +57532,14 @@
       </c>
       <c r="G123" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" s="157">
       <c r="A124" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B124" s="78" t="inlineStr">
@@ -57358,7 +57548,7 @@
         </is>
       </c>
       <c r="C124" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D124" s="79" t="n">
         <v>140</v>
@@ -57374,68 +57564,299 @@
       </c>
       <c r="G124" s="78" t="inlineStr">
         <is>
+          <t>Troca do dia 11/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" s="157">
+      <c r="A125" s="78" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="B125" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C125" s="77" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D125" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E125" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F125" s="112">
+        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
+        <v/>
+      </c>
+      <c r="G125" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 14/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" s="157">
+      <c r="A126" s="78" t="inlineStr">
+        <is>
+          <t>Clínica Santa Cecília</t>
+        </is>
+      </c>
+      <c r="B126" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Termostato</t>
+        </is>
+      </c>
+      <c r="C126" s="77" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D126" s="79" t="n">
+        <v>310</v>
+      </c>
+      <c r="E126" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F126" s="112">
+        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
+        <v/>
+      </c>
+      <c r="G126" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" s="157">
+      <c r="A127" s="78" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="B127" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C127" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D127" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E127" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F127" s="112">
+        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
+        <v/>
+      </c>
+      <c r="G127" s="78" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" s="157">
+      <c r="A128" s="78" t="inlineStr">
+        <is>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+      <c r="B128" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C128" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D128" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E128" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F128" s="112">
+        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
+        <v/>
+      </c>
+      <c r="G128" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" s="157">
+      <c r="A129" s="78" t="inlineStr">
+        <is>
+          <t>Cleone Gomes de Andrade</t>
+        </is>
+      </c>
+      <c r="B129" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C129" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D129" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E129" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F129" s="112">
+        <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
+        <v/>
+      </c>
+      <c r="G129" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="86" t="inlineStr">
+    <row r="130" s="157">
+      <c r="A130" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D125" s="115">
-        <f>SUMIF(E83:E124,"Pendente",D83:D124)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="202" t="inlineStr">
+      <c r="D130" s="115">
+        <f>SUMIF(E88:E129,"Pendente",D88:D129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" s="157">
+      <c r="A131" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B126" s="159" t="n"/>
-      <c r="C126" s="159" t="n"/>
-      <c r="D126" s="159" t="n"/>
-      <c r="E126" s="159" t="n"/>
-      <c r="F126" s="159" t="n"/>
-      <c r="G126" s="160" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="203">
-        <f>IF(ROUND(D125-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D125-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="203" t="inlineStr">
+      <c r="B131" s="159" t="n"/>
+      <c r="C131" s="159" t="n"/>
+      <c r="D131" s="159" t="n"/>
+      <c r="E131" s="159" t="n"/>
+      <c r="F131" s="159" t="n"/>
+      <c r="G131" s="160" t="n"/>
+    </row>
+    <row r="132" s="157">
+      <c r="A132" s="203">
+        <f>IF(ROUND(D130-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D130-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" s="157">
+      <c r="A133" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
+    <row r="134" s="157"/>
+    <row r="135" s="157"/>
+    <row r="136" s="157"/>
+    <row r="137" s="157"/>
+    <row r="138" s="157"/>
+    <row r="139" s="157"/>
+    <row r="140" s="157"/>
+    <row r="141" s="157"/>
+    <row r="142" s="157"/>
+    <row r="143" s="157"/>
+    <row r="144" s="157"/>
+    <row r="145" s="157"/>
+    <row r="146" s="157"/>
+    <row r="147" s="157"/>
+    <row r="148" s="157"/>
+    <row r="149" s="157"/>
+    <row r="150" s="157"/>
+    <row r="151" s="157"/>
+    <row r="152" s="157"/>
+    <row r="153" s="157"/>
+    <row r="154" s="157"/>
+    <row r="155" s="157"/>
+    <row r="156" s="157"/>
+    <row r="157" s="157"/>
+    <row r="158" s="157"/>
+    <row r="159" s="157"/>
+    <row r="160" s="157"/>
+    <row r="161" s="157"/>
+    <row r="162" s="157"/>
+    <row r="163" s="157"/>
+    <row r="164" s="157"/>
+    <row r="165" s="157"/>
+    <row r="166" s="157"/>
+    <row r="167" s="157"/>
+    <row r="168" s="157"/>
+    <row r="169" s="157"/>
+    <row r="170" s="157"/>
+    <row r="171" s="157"/>
+    <row r="172" s="157"/>
+    <row r="173" s="157"/>
+    <row r="174" s="157"/>
+    <row r="175" s="157"/>
+    <row r="176" s="157"/>
+    <row r="177" s="157"/>
+    <row r="178" s="157"/>
+    <row r="179" s="157"/>
+    <row r="180" s="157"/>
+    <row r="181" s="157"/>
+    <row r="182" s="157"/>
+    <row r="183" s="157"/>
+    <row r="184" s="157"/>
+    <row r="185" s="157"/>
+    <row r="186" s="157"/>
+    <row r="187" s="157"/>
+    <row r="188" s="157"/>
+    <row r="189" s="157"/>
+    <row r="190" s="157"/>
+    <row r="191" s="157"/>
+    <row r="192" s="157"/>
+    <row r="193" s="157"/>
+    <row r="194" s="157"/>
+    <row r="195" s="157"/>
+    <row r="196" s="157"/>
+    <row r="197" s="157"/>
+    <row r="198" s="157"/>
+    <row r="199" s="157"/>
+    <row r="200" s="157"/>
+    <row r="201" s="157"/>
+    <row r="202" s="157"/>
+    <row r="203" s="157"/>
+    <row r="204" s="157"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A132:G132"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="A126:G126"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A131:G131"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E83:E124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E88:E129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -40854,7 +40854,7 @@
     </row>
     <row r="162">
       <c r="A162" s="81" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B162" s="82" t="inlineStr">
         <is>
@@ -40871,13 +40871,17 @@
       </c>
       <c r="E162" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F162" s="83" t="n"/>
       <c r="G162" s="83" t="n"/>
       <c r="H162" s="82" t="n"/>
-      <c r="I162" s="82" t="n"/>
+      <c r="I162" s="82" t="inlineStr">
+        <is>
+          <t>Venda de 21/09/2026 — pagamento recebido via Pix em 22/09/2026</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>CLI-0032</t>
@@ -41955,50 +41959,140 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="17" t="n"/>
-      <c r="B199" s="18" t="n"/>
+      <c r="A199" s="17" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B199" s="18" t="inlineStr">
+        <is>
+          <t>Cliente de Armando</t>
+        </is>
+      </c>
       <c r="C199" s="18" t="n"/>
-      <c r="D199" s="27" t="n"/>
-      <c r="E199" s="18" t="n"/>
-      <c r="F199" s="19" t="n"/>
+      <c r="D199" s="27" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F199" s="19" t="n">
+        <v>202.86</v>
+      </c>
       <c r="G199" s="19" t="n"/>
       <c r="H199" s="21" t="n"/>
-      <c r="I199" s="18" t="n"/>
+      <c r="I199" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
       <c r="J199" s="18" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="44" t="n"/>
-      <c r="B200" s="45" t="n"/>
-      <c r="C200" s="45" t="n"/>
-      <c r="D200" s="46" t="n"/>
-      <c r="E200" s="45" t="n"/>
+      <c r="A200" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B200" s="45" t="inlineStr">
+        <is>
+          <t>4x4 Peças e Serviços</t>
+        </is>
+      </c>
+      <c r="C200" s="45" t="inlineStr">
+        <is>
+          <t>Refil Carbon Tech 5"</t>
+        </is>
+      </c>
+      <c r="D200" s="46" t="n">
+        <v>70</v>
+      </c>
+      <c r="E200" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F200" s="47" t="n"/>
       <c r="G200" s="48" t="n"/>
       <c r="H200" s="49" t="n"/>
-      <c r="I200" s="45" t="n"/>
+      <c r="I200" s="45" t="inlineStr">
+        <is>
+          <t>Purificador da oficina — troca feita em 25/09/2026</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>EMP-0001</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="17" t="n"/>
-      <c r="B201" s="18" t="n"/>
-      <c r="C201" s="18" t="n"/>
-      <c r="D201" s="27" t="n"/>
-      <c r="E201" s="18" t="n"/>
-      <c r="F201" s="19" t="n"/>
+      <c r="A201" s="17" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B201" s="18" t="inlineStr">
+        <is>
+          <t>Rejane Magalhães Borges Maia</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>Carcaça 9" + Refil Plissado</t>
+        </is>
+      </c>
+      <c r="D201" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E201" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F201" s="19" t="n">
+        <v>13.98</v>
+      </c>
       <c r="G201" s="19" t="n"/>
       <c r="H201" s="21" t="n"/>
-      <c r="I201" s="18" t="n"/>
-      <c r="J201" s="18" t="n"/>
+      <c r="I201" s="18" t="inlineStr">
+        <is>
+          <t>Filtro de ponto de entrada — instalação feita em 25/09/2026. Crédito em 2x — pagamento recebido em 25/09/2026.</t>
+        </is>
+      </c>
+      <c r="J201" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0656</t>
+        </is>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="44" t="n"/>
-      <c r="B202" s="45" t="n"/>
-      <c r="C202" s="45" t="n"/>
-      <c r="D202" s="46" t="n"/>
-      <c r="E202" s="45" t="n"/>
+      <c r="A202" s="44" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B202" s="45" t="inlineStr">
+        <is>
+          <t>O Pirulito Bomboniere - Paulo Eric de Souza</t>
+        </is>
+      </c>
+      <c r="C202" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D202" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E202" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F202" s="47" t="n"/>
       <c r="G202" s="48" t="n"/>
       <c r="H202" s="49" t="n"/>
       <c r="I202" s="45" t="n"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>EMP-0232</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="17" t="n"/>
@@ -57683,7 +57777,7 @@
       </c>
       <c r="E128" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F128" s="112">
@@ -57692,7 +57786,7 @@
       </c>
       <c r="G128" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -41990,7 +41990,7 @@
     </row>
     <row r="200">
       <c r="A200" s="44" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B200" s="45" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
       <c r="H200" s="49" t="n"/>
       <c r="I200" s="45" t="inlineStr">
         <is>
-          <t>Purificador da oficina — troca feita em 25/09/2026</t>
+          <t>Purificador da oficina</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -42095,11 +42095,27 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="17" t="n"/>
-      <c r="B203" s="18" t="n"/>
-      <c r="C203" s="18" t="n"/>
-      <c r="D203" s="27" t="n"/>
-      <c r="E203" s="18" t="n"/>
+      <c r="A203" s="17" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B203" s="18" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="D203" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E203" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F203" s="19" t="n"/>
       <c r="G203" s="19" t="n"/>
       <c r="H203" s="21" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -36285,7 +36285,7 @@
       </c>
       <c r="E12" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F12" s="83" t="n"/>
@@ -36293,7 +36293,7 @@
       <c r="H12" s="82" t="n"/>
       <c r="I12" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEMPPO00004452 · NF 000.004.333 de 26/08/2026 · prazo 30 dias · vencimento 25/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEMPPO00004452 · NF 000.004.333 de 26/08/2026 · prazo 30 dias · vencimento 25/09/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · pagamento recebido via Pix em 25/09/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
       <c r="K12" s="78" t="inlineStr">
@@ -57185,7 +57185,7 @@
       </c>
       <c r="E109" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F109" s="113">
@@ -57194,7 +57194,7 @@
       </c>
       <c r="G109" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias</t>
+          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54086,7 +54086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -54137,7 +54137,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D82</f>
+        <f>D85</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -55793,7 +55793,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" s="157">
       <c r="A61" s="139" t="inlineStr">
         <is>
           <t>Wiliam Pinto Bispo</t>
@@ -56402,1010 +56402,1010 @@
       </c>
     </row>
     <row r="80" s="157">
-      <c r="A80" s="86" t="inlineStr">
+      <c r="A80" s="139" t="inlineStr">
+        <is>
+          <t>Vitoria Maria F Santos</t>
+        </is>
+      </c>
+      <c r="B80" s="139" t="inlineStr">
+        <is>
+          <t>Aluguel da loja — outubro/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="140" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D80" s="141" t="n">
+        <v>880</v>
+      </c>
+      <c r="E80" s="142" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F80" s="143">
+        <f>IF(OR($E80="Pago",$C80=""),"",MAX(0,TODAY()-$C80))</f>
+        <v/>
+      </c>
+      <c r="G80" s="139" t="inlineStr">
+        <is>
+          <t>PREVISÃO (fixo mensal) — aluguel da loja, sempre no dia 1º, valor fixo de R$ 880,00. Pagamento direto à locadora (Vitória Maria F Santos), sem boleto. Categoria quando pagar: Aluguel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" s="157">
+      <c r="A81" s="139" t="inlineStr">
+        <is>
+          <t>Vitoria Maria F Santos</t>
+        </is>
+      </c>
+      <c r="B81" s="139" t="inlineStr">
+        <is>
+          <t>Aluguel da loja — novembro/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="140" t="n">
+        <v>46327</v>
+      </c>
+      <c r="D81" s="141" t="n">
+        <v>880</v>
+      </c>
+      <c r="E81" s="142" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F81" s="143">
+        <f>IF(OR($E81="Pago",$C81=""),"",MAX(0,TODAY()-$C81))</f>
+        <v/>
+      </c>
+      <c r="G81" s="139" t="inlineStr">
+        <is>
+          <t>PREVISÃO (fixo mensal) — aluguel da loja, sempre no dia 1º, valor fixo de R$ 880,00. Pagamento direto à locadora (Vitória Maria F Santos), sem boleto. Categoria quando pagar: Aluguel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" s="157">
+      <c r="A82" s="139" t="inlineStr">
+        <is>
+          <t>Vitoria Maria F Santos</t>
+        </is>
+      </c>
+      <c r="B82" s="139" t="inlineStr">
+        <is>
+          <t>Aluguel da loja — dezembro/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="140" t="n">
+        <v>46357</v>
+      </c>
+      <c r="D82" s="141" t="n">
+        <v>880</v>
+      </c>
+      <c r="E82" s="142" t="inlineStr">
+        <is>
+          <t>Previsto</t>
+        </is>
+      </c>
+      <c r="F82" s="143">
+        <f>IF(OR($E82="Pago",$C82=""),"",MAX(0,TODAY()-$C82))</f>
+        <v/>
+      </c>
+      <c r="G82" s="139" t="inlineStr">
+        <is>
+          <t>PREVISÃO (fixo mensal) — aluguel da loja, sempre no dia 1º, valor fixo de R$ 880,00. Pagamento direto à locadora (Vitória Maria F Santos), sem boleto. Categoria quando pagar: Aluguel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" s="157">
+      <c r="A83" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B80" s="86" t="n"/>
-      <c r="C80" s="114" t="n"/>
-      <c r="D80" s="115">
-        <f>SUMIF(E11:E79,"Pendente",D11:D79)</f>
-        <v/>
-      </c>
-      <c r="E80" s="116" t="n"/>
-      <c r="F80" s="116" t="n"/>
-      <c r="G80" s="86" t="n"/>
-    </row>
-    <row r="81" s="157">
-      <c r="A81" s="144" t="inlineStr">
+      <c r="B83" s="86" t="n"/>
+      <c r="C83" s="114" t="n"/>
+      <c r="D83" s="115">
+        <f>SUMIF(E11:E82,"Pendente",D11:D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="116" t="n"/>
+      <c r="F83" s="116" t="n"/>
+      <c r="G83" s="86" t="n"/>
+    </row>
+    <row r="84" s="157">
+      <c r="A84" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B81" s="144" t="n"/>
-      <c r="C81" s="145" t="n"/>
-      <c r="D81" s="146">
-        <f>SUMIF(E11:E79,"Previsto",D11:D79)</f>
-        <v/>
-      </c>
-      <c r="E81" s="142" t="n"/>
-      <c r="F81" s="142" t="n"/>
-      <c r="G81" s="144" t="n"/>
-    </row>
-    <row r="82" s="157">
-      <c r="A82" s="86" t="inlineStr">
+      <c r="B84" s="144" t="n"/>
+      <c r="C84" s="145" t="n"/>
+      <c r="D84" s="146">
+        <f>SUMIF(E11:E82,"Previsto",D11:D82)</f>
+        <v/>
+      </c>
+      <c r="E84" s="142" t="n"/>
+      <c r="F84" s="142" t="n"/>
+      <c r="G84" s="144" t="n"/>
+    </row>
+    <row r="85" s="157">
+      <c r="A85" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B82" s="86" t="n"/>
-      <c r="C82" s="114" t="n"/>
-      <c r="D82" s="115">
-        <f>D80+D81</f>
-        <v/>
-      </c>
-      <c r="E82" s="116" t="n"/>
-      <c r="F82" s="116" t="n"/>
-      <c r="G82" s="86" t="n"/>
-    </row>
-    <row r="83" s="157"/>
-    <row r="84" ht="15.75" customHeight="1" s="157"/>
-    <row r="85" ht="15.75" customHeight="1" s="157">
-      <c r="A85" s="200" t="inlineStr">
+      <c r="B85" s="86" t="n"/>
+      <c r="C85" s="114" t="n"/>
+      <c r="D85" s="115">
+        <f>D83+D84</f>
+        <v/>
+      </c>
+      <c r="E85" s="116" t="n"/>
+      <c r="F85" s="116" t="n"/>
+      <c r="G85" s="86" t="n"/>
+    </row>
+    <row r="86" s="157"/>
+    <row r="87" ht="15.75" customHeight="1" s="157"/>
+    <row r="88" ht="15.75" customHeight="1" s="157">
+      <c r="A88" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="86" s="157">
-      <c r="A86" s="194" t="inlineStr">
+    <row r="89" s="157">
+      <c r="A89" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="87" s="157">
-      <c r="A87" s="111" t="inlineStr">
+    <row r="90" s="157">
+      <c r="A90" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B87" s="111" t="inlineStr">
+      <c r="B90" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C87" s="111" t="inlineStr">
+      <c r="C90" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D87" s="111" t="inlineStr">
+      <c r="D90" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E87" s="111" t="inlineStr">
+      <c r="E90" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F87" s="111" t="inlineStr">
+      <c r="F90" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G87" s="111" t="inlineStr">
+      <c r="G90" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="88" s="157">
-      <c r="A88" s="78" t="inlineStr">
+    <row r="91" s="157">
+      <c r="A91" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B88" s="78" t="inlineStr">
+      <c r="B91" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C88" s="77" t="n">
+      <c r="C91" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D88" s="79" t="n">
+      <c r="D91" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E88" s="112" t="inlineStr">
+      <c r="E91" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F88" s="112">
-        <f>IF(OR($E88="Recebido",$C88=""),"",MAX(0,TODAY()-$C88))</f>
-        <v/>
-      </c>
-      <c r="G88" s="78" t="n"/>
-    </row>
-    <row r="89" s="157">
-      <c r="A89" s="82" t="inlineStr">
+      <c r="F91" s="112">
+        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="78" t="n"/>
+    </row>
+    <row r="92" s="157">
+      <c r="A92" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B89" s="82" t="inlineStr">
+      <c r="B92" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C89" s="81" t="n">
+      <c r="C92" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D89" s="83" t="n">
+      <c r="D92" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E89" s="113" t="inlineStr">
+      <c r="E92" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F89" s="113">
-        <f>IF(OR($E89="Recebido",$C89=""),"",MAX(0,TODAY()-$C89))</f>
-        <v/>
-      </c>
-      <c r="G89" s="82" t="n"/>
-    </row>
-    <row r="90" s="157">
-      <c r="A90" s="78" t="inlineStr">
+      <c r="F92" s="113">
+        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="82" t="n"/>
+    </row>
+    <row r="93" s="157">
+      <c r="A93" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B90" s="78" t="inlineStr">
+      <c r="B93" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C90" s="77" t="n">
+      <c r="C93" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D90" s="79" t="n">
+      <c r="D93" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E90" s="112" t="inlineStr">
+      <c r="E93" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F90" s="112">
-        <f>IF(OR($E90="Recebido",$C90=""),"",MAX(0,TODAY()-$C90))</f>
-        <v/>
-      </c>
-      <c r="G90" s="78" t="inlineStr">
+      <c r="F93" s="112">
+        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="91" s="157">
-      <c r="A91" s="82" t="inlineStr">
+    <row r="94" s="157">
+      <c r="A94" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B91" s="82" t="inlineStr">
+      <c r="B94" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C91" s="81" t="n">
+      <c r="C94" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D91" s="83" t="n">
+      <c r="D94" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E91" s="113" t="inlineStr">
+      <c r="E94" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F91" s="113">
-        <f>IF(OR($E91="Recebido",$C91=""),"",MAX(0,TODAY()-$C91))</f>
-        <v/>
-      </c>
-      <c r="G91" s="82" t="inlineStr">
+      <c r="F94" s="113">
+        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="92" s="157">
-      <c r="A92" s="78" t="inlineStr">
+    <row r="95" s="157">
+      <c r="A95" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B92" s="78" t="inlineStr">
+      <c r="B95" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C92" s="77" t="n">
+      <c r="C95" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D92" s="79" t="n">
+      <c r="D95" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E92" s="112" t="inlineStr">
+      <c r="E95" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F92" s="112">
-        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
-        <v/>
-      </c>
-      <c r="G92" s="78" t="inlineStr">
+      <c r="F95" s="112">
+        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="93" s="157">
-      <c r="A93" s="82" t="inlineStr">
+    <row r="96" s="157">
+      <c r="A96" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B93" s="82" t="inlineStr">
+      <c r="B96" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C96" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D93" s="83" t="n">
+      <c r="D96" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E93" s="113" t="inlineStr">
+      <c r="E96" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F93" s="113">
-        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
-        <v/>
-      </c>
-      <c r="G93" s="82" t="inlineStr">
+      <c r="F96" s="113">
+        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="94" s="157">
-      <c r="A94" s="78" t="inlineStr">
+    <row r="97" s="157">
+      <c r="A97" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B94" s="78" t="inlineStr">
+      <c r="B97" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C94" s="77" t="n">
+      <c r="C97" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D94" s="79" t="n">
+      <c r="D97" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E94" s="112" t="inlineStr">
+      <c r="E97" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="112">
-        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
-        <v/>
-      </c>
-      <c r="G94" s="78" t="inlineStr">
+      <c r="F97" s="112">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="95" s="157">
-      <c r="A95" s="82" t="inlineStr">
+    <row r="98" s="157">
+      <c r="A98" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C98" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D95" s="83" t="n">
+      <c r="D98" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E95" s="113" t="inlineStr">
+      <c r="E98" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F95" s="113">
-        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
-        <v/>
-      </c>
-      <c r="G95" s="82" t="inlineStr">
+      <c r="F98" s="113">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="96" s="157">
-      <c r="A96" s="78" t="inlineStr">
+    <row r="99" s="157">
+      <c r="A99" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B96" s="78" t="inlineStr">
+      <c r="B99" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C96" s="77" t="n">
+      <c r="C99" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D96" s="79" t="n">
+      <c r="D99" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E96" s="112" t="inlineStr">
+      <c r="E99" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F96" s="112">
-        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
-        <v/>
-      </c>
-      <c r="G96" s="78" t="inlineStr">
+      <c r="F99" s="112">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="97" s="157">
-      <c r="A97" s="82" t="inlineStr">
+    <row r="100" s="157">
+      <c r="A100" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C97" s="81" t="n">
+      <c r="C100" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D97" s="83" t="n">
+      <c r="D100" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E97" s="113" t="inlineStr">
+      <c r="E100" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F97" s="113">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="82" t="inlineStr">
+      <c r="F100" s="113">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="98" s="157">
-      <c r="A98" s="78" t="inlineStr">
+    <row r="101" s="157">
+      <c r="A101" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B98" s="78" t="inlineStr">
+      <c r="B101" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C98" s="77" t="n">
+      <c r="C101" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D98" s="79" t="n">
+      <c r="D101" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E98" s="112" t="inlineStr">
+      <c r="E101" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="112">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="78" t="inlineStr">
+      <c r="F101" s="112">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="99" s="157">
-      <c r="A99" s="82" t="inlineStr">
+    <row r="102" s="157">
+      <c r="A102" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B102" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C99" s="81" t="n">
+      <c r="C102" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D99" s="83" t="n">
+      <c r="D102" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E99" s="113" t="inlineStr">
+      <c r="E102" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F99" s="113">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="82" t="inlineStr">
+      <c r="F102" s="113">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="100" s="157">
-      <c r="A100" s="78" t="inlineStr">
+    <row r="103" s="157">
+      <c r="A103" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B100" s="78" t="inlineStr">
+      <c r="B103" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C100" s="77" t="n">
+      <c r="C103" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D100" s="79" t="n">
+      <c r="D103" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E100" s="112" t="inlineStr">
+      <c r="E103" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F100" s="112">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="78" t="inlineStr">
+      <c r="F103" s="112">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="101" s="157">
-      <c r="A101" s="82" t="inlineStr">
+    <row r="104" s="157">
+      <c r="A104" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B101" s="82" t="inlineStr">
+      <c r="B104" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C101" s="81" t="n">
+      <c r="C104" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D101" s="83" t="n">
+      <c r="D104" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E101" s="113" t="inlineStr">
+      <c r="E104" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F101" s="113">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="82" t="inlineStr">
+      <c r="F104" s="113">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="102" s="157">
-      <c r="A102" s="78" t="inlineStr">
+    <row r="105" s="157">
+      <c r="A105" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B102" s="78" t="inlineStr">
+      <c r="B105" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C102" s="77" t="n">
+      <c r="C105" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D102" s="79" t="n">
+      <c r="D105" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E102" s="112" t="inlineStr">
+      <c r="E105" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F102" s="112">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="78" t="inlineStr">
+      <c r="F105" s="112">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="103" s="157">
-      <c r="A103" s="82" t="inlineStr">
+    <row r="106" s="157">
+      <c r="A106" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B103" s="82" t="inlineStr">
+      <c r="B106" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C103" s="81" t="n">
+      <c r="C106" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D103" s="83" t="n">
+      <c r="D106" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E103" s="113" t="inlineStr">
+      <c r="E106" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F103" s="113">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="82" t="inlineStr">
+      <c r="F106" s="113">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="104" s="157">
-      <c r="A104" s="78" t="inlineStr">
+    <row r="107" s="157">
+      <c r="A107" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B104" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C104" s="77" t="n">
+      <c r="C107" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D104" s="79" t="n">
+      <c r="D107" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E104" s="112" t="inlineStr">
+      <c r="E107" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F104" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="78" t="inlineStr">
+      <c r="F107" s="112">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="105" s="157">
-      <c r="A105" s="82" t="inlineStr">
+    <row r="108" s="157">
+      <c r="A108" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B105" s="82" t="inlineStr">
+      <c r="B108" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C105" s="81" t="n">
+      <c r="C108" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D105" s="83" t="n">
+      <c r="D108" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E105" s="113" t="inlineStr">
+      <c r="E108" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F105" s="113">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="82" t="inlineStr">
+      <c r="F108" s="113">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="106" s="157">
-      <c r="A106" s="78" t="inlineStr">
+    <row r="109" s="157">
+      <c r="A109" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B109" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C106" s="77" t="n">
+      <c r="C109" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D106" s="79" t="n">
+      <c r="D109" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E106" s="112" t="inlineStr">
+      <c r="E109" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F106" s="112">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="78" t="inlineStr">
+      <c r="F109" s="112">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="107" s="157">
-      <c r="A107" s="82" t="inlineStr">
+    <row r="110" s="157">
+      <c r="A110" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B107" s="82" t="inlineStr">
+      <c r="B110" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C107" s="81" t="n">
+      <c r="C110" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D107" s="83" t="n">
+      <c r="D110" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E107" s="113" t="inlineStr">
+      <c r="E110" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F107" s="113">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="82" t="inlineStr">
+      <c r="F110" s="113">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="108" s="157">
-      <c r="A108" s="78" t="inlineStr">
+    <row r="111" s="157">
+      <c r="A111" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B108" s="78" t="inlineStr">
+      <c r="B111" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C108" s="77" t="n">
+      <c r="C111" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D108" s="79" t="n">
+      <c r="D111" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E108" s="112" t="inlineStr">
+      <c r="E111" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="112">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="78" t="inlineStr">
+      <c r="F111" s="112">
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="109" s="157">
-      <c r="A109" s="82" t="inlineStr">
+    <row r="112" s="157">
+      <c r="A112" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B109" s="82" t="inlineStr">
+      <c r="B112" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C109" s="81" t="n">
+      <c r="C112" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D109" s="83" t="n">
+      <c r="D112" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E109" s="113" t="inlineStr">
+      <c r="E112" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F109" s="113">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="82" t="inlineStr">
+      <c r="F112" s="113">
+        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
+        <v/>
+      </c>
+      <c r="G112" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
-    <row r="110" s="157">
-      <c r="A110" s="78" t="inlineStr">
+    <row r="113" s="157">
+      <c r="A113" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B110" s="78" t="inlineStr">
+      <c r="B113" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C110" s="77" t="n">
+      <c r="C113" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D110" s="79" t="n">
+      <c r="D113" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E110" s="112" t="inlineStr">
+      <c r="E113" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F110" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="78" t="inlineStr">
+      <c r="F113" s="112">
+        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
-    <row r="111" s="157">
-      <c r="A111" s="82" t="inlineStr">
+    <row r="114" s="157">
+      <c r="A114" s="82" t="inlineStr">
         <is>
           <t>Instituto Paulo Leão</t>
         </is>
       </c>
-      <c r="B111" s="82" t="inlineStr">
+      <c r="B114" s="82" t="inlineStr">
         <is>
           <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
-      <c r="C111" s="81" t="n">
+      <c r="C114" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D111" s="83" t="n">
+      <c r="D114" s="83" t="n">
         <v>160</v>
       </c>
-      <c r="E111" s="113" t="inlineStr">
+      <c r="E114" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="113">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="82" t="inlineStr">
+      <c r="F114" s="113">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="112" s="157">
-      <c r="A112" s="78" t="inlineStr">
+    <row r="115" s="157">
+      <c r="A115" s="78" t="inlineStr">
         <is>
           <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
-      <c r="B112" s="78" t="inlineStr">
+      <c r="B115" s="78" t="inlineStr">
         <is>
           <t>Pré Filtro</t>
         </is>
       </c>
-      <c r="C112" s="77" t="n">
+      <c r="C115" s="77" t="n">
         <v>46265</v>
       </c>
-      <c r="D112" s="79" t="n">
+      <c r="D115" s="79" t="n">
         <v>60</v>
       </c>
-      <c r="E112" s="112" t="inlineStr">
+      <c r="E115" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F112" s="112">
-        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="78" t="inlineStr">
+      <c r="F115" s="112">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" s="157">
-      <c r="A113" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B113" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C113" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D113" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E113" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F113" s="113">
-        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" s="157">
-      <c r="A114" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B114" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C114" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D114" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E114" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F114" s="112">
-        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" s="157">
-      <c r="A115" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B115" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C115" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D115" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E115" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F115" s="113">
-        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="116" s="157">
       <c r="A116" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>Clube dos Mineiros</t>
         </is>
       </c>
       <c r="B116" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C116" s="81" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D116" s="83" t="n">
-        <v>540</v>
+        <v>150</v>
       </c>
       <c r="E116" s="113" t="inlineStr">
         <is>
@@ -57418,26 +57418,26 @@
       </c>
       <c r="G116" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="117" s="157">
       <c r="A117" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B117" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C117" s="77" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D117" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E117" s="112" t="inlineStr">
         <is>
@@ -57455,85 +57455,85 @@
       </c>
     </row>
     <row r="118" s="157">
-      <c r="A118" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B118" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C118" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D118" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E118" s="112" t="inlineStr">
+      <c r="A118" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B118" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C118" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D118" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E118" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F118" s="112">
+      <c r="F118" s="113">
         <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
         <v/>
       </c>
-      <c r="G118" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+      <c r="G118" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="119" s="157">
-      <c r="A119" s="78" t="inlineStr">
-        <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
-        </is>
-      </c>
-      <c r="B119" s="78" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C119" s="77" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D119" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E119" s="112" t="inlineStr">
+      <c r="A119" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B119" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C119" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D119" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E119" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F119" s="112">
+      <c r="F119" s="113">
         <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
         <v/>
       </c>
-      <c r="G119" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+      <c r="G119" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="120" s="157">
       <c r="A120" s="78" t="inlineStr">
         <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B120" s="78" t="inlineStr">
         <is>
-          <t>Refil Plissado + Refil BAG</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C120" s="77" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="D120" s="79" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E120" s="112" t="inlineStr">
         <is>
@@ -57546,26 +57546,26 @@
       </c>
       <c r="G120" s="78" t="inlineStr">
         <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="121" s="157">
       <c r="A121" s="78" t="inlineStr">
         <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B121" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C121" s="77" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="D121" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E121" s="112" t="inlineStr">
         <is>
@@ -57578,26 +57578,26 @@
       </c>
       <c r="G121" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="122" s="157">
       <c r="A122" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B122" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C122" s="77" t="n">
-        <v>46275</v>
+        <v>46269</v>
       </c>
       <c r="D122" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E122" s="112" t="inlineStr">
         <is>
@@ -57610,30 +57610,30 @@
       </c>
       <c r="G122" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="123" s="157">
       <c r="A123" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B123" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C123" s="77" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="D123" s="79" t="n">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="E123" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F123" s="112">
@@ -57642,14 +57642,14 @@
       </c>
       <c r="G123" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="124" s="157">
       <c r="A124" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B124" s="78" t="inlineStr">
@@ -57658,7 +57658,7 @@
         </is>
       </c>
       <c r="C124" s="77" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D124" s="79" t="n">
         <v>140</v>
@@ -57674,14 +57674,14 @@
       </c>
       <c r="G124" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="125" s="157">
       <c r="A125" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B125" s="78" t="inlineStr">
@@ -57690,7 +57690,7 @@
         </is>
       </c>
       <c r="C125" s="77" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="D125" s="79" t="n">
         <v>200</v>
@@ -57706,26 +57706,26 @@
       </c>
       <c r="G125" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="126" s="157">
       <c r="A126" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B126" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C126" s="77" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="D126" s="79" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="E126" s="112" t="inlineStr">
         <is>
@@ -57738,26 +57738,26 @@
       </c>
       <c r="G126" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="127" s="157">
       <c r="A127" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B127" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C127" s="77" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="D127" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E127" s="112" t="inlineStr">
         <is>
@@ -57770,26 +57770,26 @@
       </c>
       <c r="G127" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="128" s="157">
       <c r="A128" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B128" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C128" s="77" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="D128" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E128" s="112" t="inlineStr">
         <is>
@@ -57802,30 +57802,30 @@
       </c>
       <c r="G128" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="129" s="157">
       <c r="A129" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B129" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C129" s="77" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="D129" s="79" t="n">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="E129" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F129" s="112">
@@ -57834,50 +57834,143 @@
       </c>
       <c r="G129" s="78" t="inlineStr">
         <is>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" s="157">
+      <c r="A130" s="78" t="inlineStr">
+        <is>
+          <t>Marilda Macedo / José Luciano Costa</t>
+        </is>
+      </c>
+      <c r="B130" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C130" s="77" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D130" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E130" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F130" s="112">
+        <f>IF(OR($E130="Recebido",$C130=""),"",MAX(0,TODAY()-$C130))</f>
+        <v/>
+      </c>
+      <c r="G130" s="78" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" s="157">
+      <c r="A131" s="78" t="inlineStr">
+        <is>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+      <c r="B131" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C131" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D131" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E131" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F131" s="112">
+        <f>IF(OR($E131="Recebido",$C131=""),"",MAX(0,TODAY()-$C131))</f>
+        <v/>
+      </c>
+      <c r="G131" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" s="157">
+      <c r="A132" s="78" t="inlineStr">
+        <is>
+          <t>Cleone Gomes de Andrade</t>
+        </is>
+      </c>
+      <c r="B132" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C132" s="77" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D132" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E132" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F132" s="112">
+        <f>IF(OR($E132="Recebido",$C132=""),"",MAX(0,TODAY()-$C132))</f>
+        <v/>
+      </c>
+      <c r="G132" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="130" s="157">
-      <c r="A130" s="86" t="inlineStr">
+    <row r="133" s="157">
+      <c r="A133" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D130" s="115">
-        <f>SUMIF(E88:E129,"Pendente",D88:D129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" s="157">
-      <c r="A131" s="202" t="inlineStr">
+      <c r="D133" s="115">
+        <f>SUMIF(E91:E132,"Pendente",D91:D132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" s="157">
+      <c r="A134" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B131" s="159" t="n"/>
-      <c r="C131" s="159" t="n"/>
-      <c r="D131" s="159" t="n"/>
-      <c r="E131" s="159" t="n"/>
-      <c r="F131" s="159" t="n"/>
-      <c r="G131" s="160" t="n"/>
-    </row>
-    <row r="132" s="157">
-      <c r="A132" s="203">
-        <f>IF(ROUND(D130-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D130-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" s="157">
-      <c r="A133" s="203" t="inlineStr">
+      <c r="B134" s="159" t="n"/>
+      <c r="C134" s="159" t="n"/>
+      <c r="D134" s="159" t="n"/>
+      <c r="E134" s="159" t="n"/>
+      <c r="F134" s="159" t="n"/>
+      <c r="G134" s="160" t="n"/>
+    </row>
+    <row r="135" s="157">
+      <c r="A135" s="203">
+        <f>IF(ROUND(D133-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D133-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" s="157">
+      <c r="A136" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="134" s="157"/>
-    <row r="135" s="157"/>
-    <row r="136" s="157"/>
     <row r="137" s="157"/>
     <row r="138" s="157"/>
     <row r="139" s="157"/>
@@ -57950,23 +58043,23 @@
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A132:G132"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A135:G135"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A134:G134"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E88:E129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E91:E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -7544,7 +7544,7 @@
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 358698 (Doc. 358698)</t>
+          <t>NF 358698 de 04/09/2025 · parcela 4/5 (venc. 02/01/2026) · compra total R$ 2.988,70: Purificador Everest Plus Preto + Purificador Everest Star Preto + Purificador Everest Plus Prata + Purificador Everest Fit Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J9" s="18" t="n"/>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I10" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 123868 (Doc. 123868)</t>
+          <t>NF 123868 de 24/10/2025 · parcela 4/5 (venc. 02/01/2026) · compra total R$ 4.058,44 (IPI R$ 200,60): 50x Refil Pro Life + 5x Refil Top Color + 5x Refil Fp4 + 20x Refil Carbon Tech 9.3/4 Pol + 10x Refil Top Multifilter + 5x Refil Top Color Fast + 10x Refil Fpa14 + 5x Refil Fpa22 + 5x Carcaca Fit 9.3/4 Pol Branca + 5x Conexão T + 5x Refil Fpa16 · Livro Caixa</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="I14" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 66404 (Doc. 66404)</t>
+          <t>NF 66404 de 08/08/2025 · parcela 5/5 (venc. 05/01/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I34" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 125587 (Doc. 125587)</t>
+          <t>NF 125587 de 10/12/2025 · parcela 1/4 (venc. 07/01/2026) · compra total R$ 1.793,26 (IPI R$ 86,32): 5x Refil Lacqua + 15x Refil Fit Poe Pp 9.3/4 + 10x Refil Carbon Block 5 Pol + 5x Refil Top Color + 5x Refil Acquatec + 5x Refiil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil Fpa16 + Mangueira · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 361446 (Doc. 361446)</t>
+          <t>NF 361446 de 10/10/2025 · parcela 3/5 (venc. 08/01/2026) · compra total R$ 3.906,99: Purificador Everest Fit Preto + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Branco + 4x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 366264 (Doc. 366264)</t>
+          <t>NF 366264 de 11/12/2025 · parcela 1/5 (venc. 10/01/2026) · compra total R$ 4.205,29: Purificador Everest Slim Branco + Purificador Everest Slim Prata + 2x Purificador Everest Star Branco + Purificador Everest Star Prata + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J55" s="18" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="I56" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 357294 (Doc. 357294)</t>
+          <t>NF 357294 de 14/08/2025 · parcela 5/5 (venc. 11/01/2026) · compra total R$ 2.886,75: 2x Purificador Everest Plus Branco + 2x Purificador Everest Slim Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="I76" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 357493 (Doc. 357493)</t>
+          <t>NF 357493 de 19/08/2025 · parcela 5/5 (venc. 16/01/2026) · compra total R$ 4.123,62: Purificador Everest Star Branco + Purificador Everest Star Prata + Purificador Everest Star Cereja + Purificador Everest Slim Prata + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I77" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 123868 (Doc. 123868)</t>
+          <t>NF 123868 de 24/10/2025 · parcela 5/5 (venc. 16/01/2026) · compra total R$ 4.058,44 (IPI R$ 200,60): 50x Refil Pro Life + 5x Refil Top Color + 5x Refil Fp4 + 20x Refil Carbon Tech 9.3/4 Pol + 10x Refil Top Multifilter + 5x Refil Top Color Fast + 10x Refil Fpa14 + 5x Refil Fpa22 + 5x Carcaca Fit 9.3/4 Pol Branca + 5x Conexão T + 5x Refil Fpa16 · Livro Caixa</t>
         </is>
       </c>
       <c r="J77" s="18" t="n"/>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 67435 (Doc. 67435)</t>
+          <t>NF 67435 de 19/09/2025 · parcela 4/5 (venc. 17/01/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J83" s="18" t="n"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="I92" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 362188 (Doc. 362188)</t>
+          <t>NF 362188 de 22/10/2025 · parcela 3/5 (venc. 20/01/2026) · compra total R$ 4.003,24: Purificador Everest Fit Branco + Purificador Everest Fit Prata + Purificador Everest Slim Branco + Purificador Everest Slim Prata + Purificador Everest Star Branco + 4x Purificador Everest Baby Cereja · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 125587 (Doc. 125587)</t>
+          <t>NF 125587 de 10/12/2025 · parcela 2/4 (venc. 21/01/2026) · compra total R$ 1.793,26 (IPI R$ 86,32): 5x Refil Lacqua + 15x Refil Fit Poe Pp 9.3/4 + 10x Refil Carbon Block 5 Pol + 5x Refil Top Color + 5x Refil Acquatec + 5x Refiil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil Fpa16 + Mangueira · Livro Caixa</t>
         </is>
       </c>
       <c r="J105" s="18" t="n"/>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69107 (Doc. 69107)</t>
+          <t>NF 69107 de 27/11/2025 · parcela 2/5 (venc. 26/01/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
       <c r="J119" s="18" t="n"/>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69886 (Doc. 69886)</t>
+          <t>NF 69886 de 30/12/2025 · parcela 1/5 (venc. 29/01/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 358698 (Doc. 358698)</t>
+          <t>NF 358698 de 04/09/2025 · parcela 5/5 (venc. 01/02/2026) · compra total R$ 2.988,70: Purificador Everest Plus Preto + Purificador Everest Star Preto + Purificador Everest Plus Prata + Purificador Everest Fit Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 125587 (Doc. 125587)</t>
+          <t>NF 125587 de 10/12/2025 · parcela 3/4 (venc. 04/02/2026) · compra total R$ 1.793,26 (IPI R$ 86,32): 5x Refil Lacqua + 15x Refil Fit Poe Pp 9.3/4 + 10x Refil Carbon Block 5 Pol + 5x Refil Top Color + 5x Refil Acquatec + 5x Refiil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil Fpa16 + Mangueira · Livro Caixa</t>
         </is>
       </c>
       <c r="J41" s="18" t="n"/>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="I92" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 361446 (Doc. 361446)</t>
+          <t>NF 361446 de 10/10/2025 · parcela 4/5 (venc. 07/02/2026) · compra total R$ 3.906,99: Purificador Everest Fit Preto + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Branco + 4x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368012 (Doc. 368012)</t>
+          <t>NF 368012 de 08/01/2026 · parcela 1/5 (venc. 07/02/2026) · compra total R$ 4.054,97: Purificador Everest Fit Branco + 2x Purificador Everest Slim Branco + Purificador Everest Slim Preto + 2x Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="J93" s="18" t="n"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="I94" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 366264 (Doc. 366264)</t>
+          <t>NF 366264 de 11/12/2025 · parcela 2/5 (venc. 09/02/2026) · compra total R$ 4.205,29: Purificador Everest Slim Branco + Purificador Everest Slim Prata + 2x Purificador Everest Star Branco + Purificador Everest Star Prata + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="I96" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368529 (Doc. 368529)</t>
+          <t>NF 368529 de 14/01/2026 · parcela 1/5 (venc. 13/02/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Star Prata + Purificador Everest Slim Prata + Purificador Everest Fit Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 67435 (Doc. 67435)</t>
+          <t>NF 67435 de 19/09/2025 · parcela 5/5 (venc. 16/02/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 126565 (Doc. 126565)</t>
+          <t>NF 126565 de 20/01/2026 · parcela 1/4 (venc. 17/02/2026) · compra total R$ 1.771,04 (IPI R$ 87,54): 65x Refil Pro Life · Livro Caixa</t>
         </is>
       </c>
       <c r="J109" s="18" t="n"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="I110" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 125587 (Doc. 125587)</t>
+          <t>NF 125587 de 10/12/2025 · parcela 4/4 (venc. 18/02/2026) · compra total R$ 1.793,26 (IPI R$ 86,32): 5x Refil Lacqua + 15x Refil Fit Poe Pp 9.3/4 + 10x Refil Carbon Block 5 Pol + 5x Refil Top Color + 5x Refil Acquatec + 5x Refiil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil Fpa16 + Mangueira · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 362188 (Doc. 362188)</t>
+          <t>NF 362188 de 22/10/2025 · parcela 4/5 (venc. 19/02/2026) · compra total R$ 4.003,24: Purificador Everest Fit Branco + Purificador Everest Fit Prata + Purificador Everest Slim Branco + Purificador Everest Slim Prata + Purificador Everest Star Branco + 4x Purificador Everest Baby Cereja · Livro Caixa</t>
         </is>
       </c>
       <c r="J111" s="18" t="n"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 68349 (Doc. 68349)</t>
+          <t>NF 68349 de 24/10/2025 · parcela 4/5 (venc. 21/02/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J139" s="18" t="n"/>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="I140" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 360351 (Doc. 360351)</t>
+          <t>NF 360351 de 25/09/2025 · parcela 5/5 (venc. 22/02/2026) · compra total R$ 2.733,82: Purificador Everest Fit Branco + Purificador Everest Fit Prata + Purificador Everest Slim Prata + Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 70444 (Doc. 70444)</t>
+          <t>NF 70444 de 23/01/2026 · parcela 1/5 (venc. 22/02/2026) · compra total R$ 2.706,83: 50x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
       <c r="J141" s="18" t="n"/>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="I142" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69107 (Doc. 69107)</t>
+          <t>NF 69107 de 27/11/2025 · parcela 3/5 (venc. 25/02/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="I144" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 369793 (Doc. 369793)</t>
+          <t>NF 369793 de 28/01/2026 · parcela 1/3 (venc. 27/02/2026) · compra total R$ 3.838,20: Purificador Everest Star Branco + Purificador Everest Fit Preto + Purificador Everest Plus Preto + 8x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 361446 (Doc. 361446)</t>
+          <t>NF 361446 de 10/10/2025 · parcela 5/5 (venc. 09/03/2026) · compra total R$ 3.906,99: Purificador Everest Fit Preto + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Branco + 4x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368012 (Doc. 368012)</t>
+          <t>NF 368012 de 08/01/2026 · parcela 2/5 (venc. 09/03/2026) · compra total R$ 4.054,97: Purificador Everest Fit Branco + 2x Purificador Everest Slim Branco + Purificador Everest Slim Preto + 2x Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="J39" s="18" t="n"/>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="I40" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 366264 (Doc. 366264)</t>
+          <t>NF 366264 de 11/12/2025 · parcela 3/5 (venc. 11/03/2026) · compra total R$ 4.205,29: Purificador Everest Slim Branco + Purificador Everest Slim Prata + 2x Purificador Everest Star Branco + Purificador Everest Star Prata + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 132866 (Doc. 132866)</t>
+          <t>NF 132866 de 10/02/2026 · parcela 1/3 (venc. 12/03/2026) · compra total R$ 4.176,30: 30x Filtro De Agua Protection Lacrado + 50x Cofilter Lacrado - Pre C + 30x Filtro De Agua Natural Max + 10x Filtro De Agua Natural Lacrado · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="I76" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368529 (Doc. 368529)</t>
+          <t>NF 368529 de 14/01/2026 · parcela 2/5 (venc. 15/03/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Star Prata + Purificador Everest Slim Prata + Purificador Everest Fit Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="I78" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 126565 (Doc. 126565)</t>
+          <t>NF 126565 de 20/01/2026 · parcela 3/4 (venc. 17/03/2026) · compra total R$ 1.771,04 (IPI R$ 87,54): 65x Refil Pro Life · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 362188 (Doc. 362188)</t>
+          <t>NF 362188 de 22/10/2025 · parcela 5/5 (venc. 21/03/2026) · compra total R$ 4.003,24: Purificador Everest Fit Branco + Purificador Everest Fit Prata + Purificador Everest Slim Branco + Purificador Everest Slim Prata + Purificador Everest Star Branco + 4x Purificador Everest Baby Cereja · Livro Caixa</t>
         </is>
       </c>
       <c r="J99" s="18" t="n"/>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="I100" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 68349 (Doc. 68349)</t>
+          <t>NF 68349 de 24/10/2025 · parcela 5/5 (venc. 23/03/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 70444 (Doc. 70444)</t>
+          <t>NF 70444 de 23/01/2026 · parcela 2/5 (venc. 24/03/2026) · compra total R$ 2.706,83: 50x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
       <c r="J101" s="18" t="n"/>
@@ -20003,7 +20003,7 @@
       </c>
       <c r="I102" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 71084 (Doc. 71084)</t>
+          <t>NF 71084 de 23/02/2026 · parcela 1/5 (venc. 25/03/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -20085,7 +20085,7 @@
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 371358 (Doc. 371358)</t>
+          <t>NF 371358 de 24/02/2026 · parcela 1/5 (venc. 26/03/2026) · compra total R$ 3.382,95: 2x Purificador Everest Star Branco + Purificador Everest Slim Branco + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J105" s="18" t="n"/>
@@ -20144,7 +20144,7 @@
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69107 (Doc. 69107)</t>
+          <t>NF 69107 de 27/11/2025 · parcela 4/5 (venc. 27/03/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
       <c r="J107" s="18" t="n"/>
@@ -20466,7 +20466,7 @@
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 369793 (Doc. 369793)</t>
+          <t>NF 369793 de 28/01/2026 · parcela 2/3 (venc. 29/03/2026) · compra total R$ 3.838,20: Purificador Everest Star Branco + Purificador Everest Fit Preto + Purificador Everest Plus Preto + 8x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J117" s="18" t="n"/>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="I118" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69886 (Doc. 69886)</t>
+          <t>NF 69886 de 30/12/2025 · parcela 3/5 (venc. 30/03/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 126565 (Doc. 126565)</t>
+          <t>NF 126565 de 20/01/2026 · parcela 4/4 (venc. 31/03/2026) · compra total R$ 1.771,04 (IPI R$ 87,54): 65x Refil Pro Life · Livro Caixa</t>
         </is>
       </c>
       <c r="J123" s="18" t="n"/>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 132866 (Doc. 132866)</t>
+          <t>NF 132866 de 10/02/2026 · parcela 2/3 (venc. 13/04/2026) · compra total R$ 4.176,30: 30x Filtro De Agua Protection Lacrado + 50x Cofilter Lacrado - Pre C + 30x Filtro De Agua Natural Max + 10x Filtro De Agua Natural Lacrado · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -22870,7 +22870,7 @@
       </c>
       <c r="I58" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368529 (Doc. 368529)</t>
+          <t>NF 368529 de 14/01/2026 · parcela 3/5 (venc. 14/04/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Star Prata + Purificador Everest Slim Prata + Purificador Everest Fit Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -23696,7 +23696,7 @@
       </c>
       <c r="I84" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 128882 (Doc. 128882)</t>
+          <t>NF 128882 de 23/03/2026 · parcela 1/4 (venc. 20/04/2026) · compra total R$ 2.113,93 (IPI R$ 96,20): 25x Refil Pro Life + 2x Refil Top Color + 10x Refil Carbon Tech 9.3/4 Pol + 15x Refil Poli Flu Plissado 9.3/4 + 20x Refil E3 + 3x Carcaca Fit 9.3/4 Pol Branca + 15x Conexão T + Mangueira · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -23751,7 +23751,7 @@
       </c>
       <c r="I86" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 70444 (Doc. 70444)</t>
+          <t>NF 70444 de 23/01/2026 · parcela 3/5 (venc. 23/04/2026) · compra total R$ 2.706,83: 50x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 71084 (Doc. 71084)</t>
+          <t>NF 71084 de 23/02/2026 · parcela 2/5 (venc. 24/04/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J87" s="18" t="n"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 371358 (Doc. 371358)</t>
+          <t>NF 371358 de 24/02/2026 · parcela 2/5 (venc. 25/04/2026) · compra total R$ 3.382,95: 2x Purificador Everest Star Branco + Purificador Everest Slim Branco + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J109" s="18" t="n"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="I114" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69107 (Doc. 69107)</t>
+          <t>NF 69107 de 27/11/2025 · parcela 5/5 (venc. 26/04/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 369793 (Doc. 369793)</t>
+          <t>NF 369793 de 28/01/2026 · parcela 3/3 (venc. 28/04/2026) · compra total R$ 3.838,20: Purificador Everest Star Branco + Purificador Everest Fit Preto + Purificador Everest Plus Preto + 8x Purificador Everest Baby Branco + 4x Purificador Everest Baby Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J123" s="18" t="n"/>
@@ -24974,7 +24974,7 @@
       </c>
       <c r="I124" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 129257 (Doc. 129257)</t>
+          <t>NF 129257 de 31/03/2026 · parcela 1/4 (venc. 28/04/2026) · compra total R$ 2.123,99 (IPI R$ 104,98): 5x Refil Fp4 + 10x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 36x Refil Pre-E3 · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69886 (Doc. 69886)</t>
+          <t>NF 69886 de 30/12/2025 · parcela 4/5 (venc. 29/04/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J125" s="18" t="n"/>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 72153 (Doc. 72153)</t>
+          <t>NF 72153 de 02/04/2026 · parcela 1/5 (venc. 02/05/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J11" s="18" t="n"/>
@@ -25773,7 +25773,7 @@
       </c>
       <c r="I12" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 374271 (Doc. 374271)</t>
+          <t>NF 374271 de 06/04/2026 · parcela 1/5 (venc. 06/05/2026) · compra total R$ 3.533,27: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 123868 (Doc. 123868)</t>
+          <t>NF 123868 de 24/10/2025 · parcela 1/5 (venc. 21/11/2025) · compra total R$ 4.058,44 (IPI R$ 200,60): 50x Refil Pro Life + 5x Refil Top Color + 5x Refil Fp4 + 20x Refil Carbon Tech 9.3/4 Pol + 10x Refil Top Multifilter + 5x Refil Top Color Fast + 10x Refil Fpa14 + 5x Refil Fpa22 + 5x Carcaca Fit 9.3/4 Pol Branca + 5x Conexão T + 5x Refil Fpa16 · Livro Caixa</t>
         </is>
       </c>
       <c r="J21" s="18" t="n"/>
@@ -26179,7 +26179,7 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 68349 (Doc. 68349)</t>
+          <t>NF 68349 de 24/10/2025 · parcela 5/5 (venc. 23/03/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J23" s="18" t="n"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="I24" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 360351 (Doc. 360351)</t>
+          <t>NF 360351 de 25/09/2025 · parcela 5/5 (venc. 22/02/2026) · compra total R$ 2.733,82: Purificador Everest Fit Branco + Purificador Everest Fit Prata + Purificador Everest Slim Prata + Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -26234,7 +26234,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69886 (Doc. 69886)</t>
+          <t>NF 69886 de 30/12/2025 · parcela 4/5 (venc. 29/04/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J25" s="18" t="n"/>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 126565 (Doc. 126565)</t>
+          <t>NF 126565 de 20/01/2026 · parcela 4/4 (venc. 31/03/2026) · compra total R$ 1.771,04 (IPI R$ 87,54): 65x Refil Pro Life · Livro Caixa</t>
         </is>
       </c>
       <c r="J27" s="18" t="n"/>
@@ -26317,7 +26317,7 @@
       </c>
       <c r="I28" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69107 (Doc. 69107)</t>
+          <t>NF 69107 de 27/11/2025 · parcela 5/5 (venc. 26/04/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -26372,7 +26372,7 @@
       </c>
       <c r="I30" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368012 (Doc. 368012)</t>
+          <t>NF 368012 de 08/01/2026 · parcela 4/5 (venc. 08/05/2026) · compra total R$ 4.054,97: Purificador Everest Fit Branco + 2x Purificador Everest Slim Branco + Purificador Everest Slim Preto + 2x Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -26399,7 +26399,7 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 366264 (Doc. 366264)</t>
+          <t>NF 366264 de 11/12/2025 · parcela 5/5 (venc. 10/05/2026) · compra total R$ 4.205,29: Purificador Everest Slim Branco + Purificador Everest Slim Prata + 2x Purificador Everest Star Branco + Purificador Everest Star Prata + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J31" s="18" t="n"/>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="I32" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 372597 (Doc. 372597)</t>
+          <t>NF 372597 de 11/03/2026 · parcela 2/5 (venc. 10/05/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 128882 (Doc. 128882)</t>
+          <t>NF 128882 de 23/03/2026 · parcela 2/4 (venc. 04/05/2026) · compra total R$ 2.113,93 (IPI R$ 96,20): 25x Refil Pro Life + 2x Refil Top Color + 10x Refil Carbon Tech 9.3/4 Pol + 15x Refil Poli Flu Plissado 9.3/4 + 20x Refil E3 + 3x Carcaca Fit 9.3/4 Pol Branca + 15x Conexão T + Mangueira · Livro Caixa</t>
         </is>
       </c>
       <c r="J39" s="18" t="n"/>
@@ -26937,7 +26937,7 @@
       </c>
       <c r="I48" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368012 (Doc. 368012)</t>
+          <t>NF 368012 de 08/01/2026 · parcela 4/5 (venc. 08/05/2026) · compra total R$ 4.054,97: Purificador Everest Fit Branco + 2x Purificador Everest Slim Branco + Purificador Everest Slim Preto + 2x Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
       </c>
       <c r="I70" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento à vista: Gerado pelo sistema. (Doc. 138165)</t>
+          <t>NF 138165 de 22/04/2026 · compra total R$ 240,00: 10x Filtro De Agua Natural Lacrado · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 128882 (Doc. 128882)</t>
+          <t>NF 128882 de 23/03/2026 · parcela 3/4 (venc. 18/05/2026) · compra total R$ 2.113,93 (IPI R$ 96,20): 25x Refil Pro Life + 2x Refil Top Color + 10x Refil Carbon Tech 9.3/4 Pol + 15x Refil Poli Flu Plissado 9.3/4 + 20x Refil E3 + 3x Carcaca Fit 9.3/4 Pol Branca + 15x Conexão T + Mangueira · Livro Caixa</t>
         </is>
       </c>
       <c r="J93" s="18" t="n"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="I120" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 70444 (Doc. 70444)</t>
+          <t>NF 70444 de 23/01/2026 · parcela 4/5 (venc. 23/05/2026) · compra total R$ 2.706,83: 50x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -29234,7 +29234,7 @@
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 71084 (Doc. 71084)</t>
+          <t>NF 71084 de 23/02/2026 · parcela 3/5 (venc. 24/05/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J121" s="18" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 371358 (Doc. 371358)</t>
+          <t>NF 371358 de 24/02/2026 · parcela 3/5 (venc. 25/05/2026) · compra total R$ 3.382,95: 2x Purificador Everest Star Branco + Purificador Everest Slim Branco + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -29317,7 +29317,7 @@
       </c>
       <c r="I124" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 129257 (Doc. 129257)</t>
+          <t>NF 129257 de 31/03/2026 · parcela 3/4 (venc. 26/05/2026) · compra total R$ 2.123,99 (IPI R$ 104,98): 5x Refil Fp4 + 10x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 36x Refil Pre-E3 · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -29344,7 +29344,7 @@
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 69886 (Doc. 69886)</t>
+          <t>NF 69886 de 30/12/2025 · parcela 5/5 (venc. 29/05/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J125" s="18" t="n"/>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="I20" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 128882 (Doc. 128882)</t>
+          <t>NF 128882 de 23/03/2026 · parcela 4/4 (venc. 01/06/2026) · compra total R$ 2.113,93 (IPI R$ 96,20): 25x Refil Pro Life + 2x Refil Top Color + 10x Refil Carbon Tech 9.3/4 Pol + 15x Refil Poli Flu Plissado 9.3/4 + 20x Refil E3 + 3x Carcaca Fit 9.3/4 Pol Branca + 15x Conexão T + Mangueira · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 72153 (Doc. 72153)</t>
+          <t>NF 72153 de 02/04/2026 · parcela 2/5 (venc. 01/06/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J21" s="18" t="n"/>
@@ -30629,7 +30629,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 374271 (Doc. 374271)</t>
+          <t>NF 374271 de 06/04/2026 · parcela 2/5 (venc. 05/06/2026) · compra total R$ 3.533,27: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="J25" s="18" t="n"/>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="I26" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 130510 (Doc. 130510)</t>
+          <t>NF 130510 de 08/05/2026 · parcela 1/4 (venc. 05/06/2026) · compra total R$ 2.803,16 (IPI R$ 138,56): 50x Refil Pro Life + 3x Refil Top Color + 5x Refil Acquatec + 5x Refil Fp4 + 6x Refil Carbon Tech 9.3/4 Pol + 6x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 + 5x Refil Top Multifilter + 3x Refil Top Color Fast + 5x Refil Fpa14 · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -31039,7 +31039,7 @@
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368012 (Doc. 368012)</t>
+          <t>NF 368012 de 08/01/2026 · parcela 5/5 (venc. 07/06/2026) · compra total R$ 4.054,97: Purificador Everest Fit Branco + 2x Purificador Everest Slim Branco + Purificador Everest Slim Preto + 2x Purificador Everest Star Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -31066,7 +31066,7 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 372597 (Doc. 372597)</t>
+          <t>NF 372597 de 11/03/2026 · parcela 3/5 (venc. 09/06/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J39" s="18" t="n"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="I40" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 129257 (Doc. 129257)</t>
+          <t>NF 129257 de 31/03/2026 · parcela 4/4 (venc. 09/06/2026) · compra total R$ 2.123,99 (IPI R$ 104,98): 5x Refil Fp4 + 10x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 36x Refil Pre-E3 · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -32041,7 +32041,7 @@
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 368529 (Doc. 368529)</t>
+          <t>NF 368529 de 14/01/2026 · parcela 5/5 (venc. 13/06/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Star Prata + Purificador Everest Slim Prata + Purificador Everest Fit Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="J69" s="18" t="n"/>
@@ -32458,7 +32458,7 @@
       </c>
       <c r="I82" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377739 (Doc. 377739)</t>
+          <t>NF 377739 de 19/05/2026 · parcela 1/5 (venc. 18/06/2026) · compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377738 (Doc. 377738)</t>
+          <t>NF 377738 de 19/05/2026 · parcela 1/5 (venc. 18/06/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J83" s="18" t="n"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="I84" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377737 (Doc. 377737)</t>
+          <t>NF 377737 de 19/05/2026 · parcela 1/5 (venc. 18/06/2026) · compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -32540,7 +32540,7 @@
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 130510 (Doc. 130510)</t>
+          <t>NF 130510 de 08/05/2026 · parcela 2/4 (venc. 19/06/2026) · compra total R$ 2.803,16 (IPI R$ 138,56): 50x Refil Pro Life + 3x Refil Top Color + 5x Refil Acquatec + 5x Refil Fp4 + 6x Refil Carbon Tech 9.3/4 Pol + 6x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 + 5x Refil Top Multifilter + 3x Refil Top Color Fast + 5x Refil Fpa14 · Livro Caixa</t>
         </is>
       </c>
       <c r="J85" s="18" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento à vista: Gerado pelo sistema. (Doc. 73636)</t>
+          <t>NF 73636 de 10/06/2026 · parcela 1/5 (venc. 10/07/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J105" s="18" t="n"/>
@@ -33204,7 +33204,7 @@
       </c>
       <c r="I106" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 70444 (Doc. 70444)</t>
+          <t>NF 70444 de 23/01/2026 · parcela 5/5 (venc. 22/06/2026) · compra total R$ 2.706,83: 50x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -33259,7 +33259,7 @@
       </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 71084 (Doc. 71084)</t>
+          <t>NF 71084 de 23/02/2026 · parcela 4/5 (venc. 23/06/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 371358 (Doc. 371358)</t>
+          <t>NF 371358 de 24/02/2026 · parcela 4/5 (venc. 24/06/2026) · compra total R$ 3.382,95: 2x Purificador Everest Star Branco + Purificador Everest Slim Branco + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J109" s="18" t="n"/>
@@ -33441,7 +33441,7 @@
       </c>
       <c r="I114" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento à vista: Gerado pelo sistema - nº 130511 (Doc. 130511)</t>
+          <t>NF 130511 de 08/05/2026 · compra total R$ 51,55 (IPI R$ 2,55): Refil Carbon Tech 9.3/4 Pol · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 72153 (Doc. 72153)</t>
+          <t>NF 72153 de 02/04/2026 · parcela 3/5 (venc. 01/07/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J11" s="18" t="n"/>
@@ -34490,7 +34490,7 @@
       </c>
       <c r="I20" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 130510 (Doc. 130510)</t>
+          <t>NF 130510 de 08/05/2026 · parcela 3/4 (venc. 03/07/2026) · compra total R$ 2.803,16 (IPI R$ 138,56): 50x Refil Pro Life + 3x Refil Top Color + 5x Refil Acquatec + 5x Refil Fp4 + 6x Refil Carbon Tech 9.3/4 Pol + 6x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 + 5x Refil Top Multifilter + 3x Refil Top Color Fast + 5x Refil Fpa14 · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -35160,7 +35160,7 @@
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 374271 (Doc. 374271)</t>
+          <t>NF 374271 de 06/04/2026 · parcela 3/5 (venc. 05/07/2026) · compra total R$ 3.533,27: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
       <c r="J41" s="18" t="n"/>
@@ -35188,7 +35188,7 @@
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 72869 (Doc. 72869)</t>
+          <t>NF 72869 de 07/05/2026 · parcela 2/5 (venc. 06/07/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 372597 (Doc. 372597)</t>
+          <t>NF 372597 de 11/03/2026 · parcela 4/5 (venc. 09/07/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto · Livro Caixa</t>
         </is>
       </c>
       <c r="J45" s="18" t="n"/>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="I46" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema. (Doc. 73636)</t>
+          <t>NF 73636 de 10/06/2026 · parcela 1/5 (venc. 10/07/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -36136,7 +36136,7 @@
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 131442 (Doc. 131442)</t>
+          <t>NF 131442 de 17/06/2026 · parcela 1/4 (venc. 15/07/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16 · Livro Caixa</t>
         </is>
       </c>
       <c r="J73" s="18" t="n"/>
@@ -36191,7 +36191,7 @@
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 130510 (Doc. 130510)</t>
+          <t>NF 130510 de 08/05/2026 · parcela 4/4 (venc. 17/07/2026) · compra total R$ 2.803,16 (IPI R$ 138,56): 50x Refil Pro Life + 3x Refil Top Color + 5x Refil Acquatec + 5x Refil Fp4 + 6x Refil Carbon Tech 9.3/4 Pol + 6x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 + 5x Refil Top Multifilter + 3x Refil Top Color Fast + 5x Refil Fpa14 · Livro Caixa</t>
         </is>
       </c>
       <c r="J75" s="18" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377739 (Doc. 377739)</t>
+          <t>NF 377739 de 19/05/2026 · parcela 2/5 (venc. 18/07/2026) · compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata · Livro Caixa</t>
         </is>
       </c>
       <c r="J89" s="18" t="n"/>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="I90" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377738 (Doc. 377738)</t>
+          <t>NF 377738 de 19/05/2026 · parcela 2/5 (venc. 18/07/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -36662,7 +36662,7 @@
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 377737 (Doc. 377737)</t>
+          <t>NF 377737 de 19/05/2026 · parcela 2/5 (venc. 18/07/2026) · compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte · Livro Caixa</t>
         </is>
       </c>
       <c r="J91" s="18" t="n"/>
@@ -36936,7 +36936,7 @@
       </c>
       <c r="I100" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 379826 (Doc. 379826)</t>
+          <t>NF 379826 de 22/06/2026 · parcela 1/5 (venc. 22/07/2026) · compra total R$ 4.373,40: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -37031,7 +37031,7 @@
       </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 71084 (Doc. 71084)</t>
+          <t>NF 71084 de 23/02/2026 · parcela 5/5 (venc. 23/07/2026) · compra total R$ 4.394,61: 100x Refil Everest · Livro Caixa</t>
         </is>
       </c>
       <c r="J103" s="18" t="n"/>
@@ -37291,7 +37291,7 @@
       </c>
       <c r="I112" s="45" t="inlineStr">
         <is>
-          <t>Livro Caixa: Pagamento parcela Gerado pelo sistema - nº 371358 (Doc. 371358)</t>
+          <t>NF 371358 de 24/02/2026 · parcela 5/5 (venc. 24/07/2026) · compra total R$ 3.382,95: 2x Purificador Everest Star Branco + Purificador Everest Slim Branco + Purificador Everest Fit Branco + Purificador Everest Fit Prata · Livro Caixa</t>
         </is>
       </c>
     </row>
@@ -39373,7 +39373,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n"/>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>NF 374271 de 06/04/2026 · parcela 4/5 (venc. 04/08/2026) · compra total R$ 3.533,27: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco</t>
+        </is>
+      </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Salários, Comissões e Encargos</t>
@@ -40020,7 +40024,7 @@
       </c>
       <c r="I30" s="45" t="inlineStr">
         <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
         </is>
       </c>
     </row>
@@ -40047,7 +40051,7 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
         </is>
       </c>
     </row>
@@ -40492,7 +40496,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I47" s="18" t="n"/>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>NF 372597 de 11/03/2026 · parcela 5/5 (venc. 08/08/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="157">
       <c r="A48" s="44" t="n">
@@ -40515,7 +40523,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I48" s="45" t="n"/>
+      <c r="I48" s="45" t="inlineStr">
+        <is>
+          <t>NF 73636 de 10/06/2026 · parcela 2/5 (venc. 09/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -40884,7 +40896,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I61" s="18" t="n"/>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>NF 131442 de 17/06/2026 · parcela 3/4 (venc. 12/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="44" t="n">
@@ -41392,7 +41408,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I78" s="45" t="n"/>
+      <c r="I78" s="45" t="inlineStr">
+        <is>
+          <t>NF 377737 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="157">
       <c r="A79" s="17" t="n">
@@ -41415,7 +41435,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I79" s="18" t="n"/>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>NF 377738 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="44" t="n">
@@ -41438,7 +41462,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I80" s="45" t="n"/>
+      <c r="I80" s="45" t="inlineStr">
+        <is>
+          <t>NF 377739 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n">
@@ -41461,7 +41489,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I81" s="18" t="n"/>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>NF 74454 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="44" t="n">
@@ -41484,7 +41516,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I82" s="45" t="n"/>
+      <c r="I82" s="45" t="inlineStr">
+        <is>
+          <t>NF 381554 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.461,49: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -41933,7 +41969,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I97" s="18" t="n"/>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>NF 131997 de 08/07/2026 · parcela 2/4 (venc. 19/08/2026) · compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="44" t="n">
@@ -42359,7 +42399,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I112" s="45" t="n"/>
+      <c r="I112" s="45" t="inlineStr">
+        <is>
+          <t>NF 379826 de 22/06/2026 · parcela 2/5 (venc. 21/08/2026) · compra total R$ 4.373,40: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="n">
@@ -43468,7 +43512,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I151" s="18" t="n"/>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>NF 131442 de 17/06/2026 · parcela 4/4 (venc. 26/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="44" t="n">
@@ -44037,7 +44085,11 @@
           <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
-      <c r="I171" s="18" t="n"/>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>NF 72153 de 02/04/2026 · parcela 5/5 (venc. 30/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="44" t="n">
@@ -45793,7 +45845,7 @@
       </c>
       <c r="I36" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 131997 (emissão 08/07/2026) — venc. 02/09/2026.</t>
+          <t>Boleto doc. 131997 (emissão 08/07/2026) — venc. 02/09/2026 · Compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
         </is>
       </c>
     </row>
@@ -45820,7 +45872,7 @@
       </c>
       <c r="I37" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 374271 (emissão 06/04/2026) — venc. 03/09/2026.</t>
+          <t>Boleto doc. 374271 (emissão 06/04/2026) — venc. 03/09/2026 · Compra total R$ 3.533,27: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco</t>
         </is>
       </c>
     </row>
@@ -45876,7 +45928,7 @@
       </c>
       <c r="I39" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 72869 (emissão 07/05/2026) — venc. 04/09/2026. Pago em 04/09/2026 pelo Banco do Nordeste, DOC 5301.</t>
+          <t>Boleto doc. 72869 (emissão 07/05/2026) — venc. 04/09/2026. Pago em 04/09/2026 pelo Banco do Nordeste, DOC 5301 · Compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
         </is>
       </c>
     </row>
@@ -46628,7 +46680,7 @@
       </c>
       <c r="I63" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 73636 (emissão 10/06/2026) — venc. 08/09/2026. Pago em 08/09/2026.</t>
+          <t>Boleto doc. 73636 (emissão 10/06/2026) — venc. 08/09/2026. Pago em 08/09/2026 · Compra total R$ 4.394,61: 100x Refil Everest</t>
         </is>
       </c>
     </row>
@@ -46757,7 +46809,7 @@
       </c>
       <c r="I67" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 133138/1 (emissão 12/08/2026) — venc. 09/09/2026. Pago em 09/09/2026.</t>
+          <t>Boleto doc. 133138/1 (emissão 12/08/2026) — venc. 09/09/2026. Pago em 09/09/2026 · Compra total R$ 2.263,62 (IPI R$ 111,90): 10x Refil Fit Poe Pp 9.3/4 + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Media + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil Cp500 + 30x Refil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 Compacto + Carcaca Fit 9.3/4 Pol Branca</t>
         </is>
       </c>
     </row>
@@ -47837,7 +47889,7 @@
       </c>
       <c r="I104" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 74454 (emissão 17/07/2026) · parcela 2/5 — venc. 15/09/2026. Pago em 15/09/2026 pelo Banco do Nordeste, DOC 91607814.</t>
+          <t>Boleto doc. 74454 (emissão 17/07/2026) · parcela 2/5 — venc. 15/09/2026. Pago em 15/09/2026 pelo Banco do Nordeste, DOC 91607814 · Compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
         </is>
       </c>
     </row>
@@ -47864,7 +47916,7 @@
       </c>
       <c r="I105" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 381554 (emissão 17/07/2026) · parcela 2/5 — venc. 15/09/2026. Pago em 15/09/2026 pelo Banco do Nordeste, DOC 91630932.</t>
+          <t>Boleto doc. 381554 (emissão 17/07/2026) · parcela 2/5 — venc. 15/09/2026. Pago em 15/09/2026 pelo Banco do Nordeste, DOC 91630932 · Compra total R$ 4.461,49: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata</t>
         </is>
       </c>
     </row>
@@ -48395,7 +48447,7 @@
       </c>
       <c r="I123" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 377737 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026.</t>
+          <t>Boleto doc. 377737 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026 · Compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte</t>
         </is>
       </c>
     </row>
@@ -48422,7 +48474,7 @@
       </c>
       <c r="I124" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 377739 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026.</t>
+          <t>Boleto doc. 377739 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026 · Compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata</t>
         </is>
       </c>
     </row>
@@ -48449,7 +48501,7 @@
       </c>
       <c r="I125" s="78" t="inlineStr">
         <is>
-          <t>Boleto doc. 377738 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste.</t>
+          <t>Boleto doc. 377738 (emissão 19/05/2026) · parcela 4/5 — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste · Compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto</t>
         </is>
       </c>
     </row>
@@ -48476,7 +48528,7 @@
       </c>
       <c r="I126" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 131997/4 (emissão 08/07/2026) · parcela 4/4 (última) — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste.</t>
+          <t>Boleto doc. 131997/4 (emissão 08/07/2026) · parcela 4/4 (última) — venc. 16/09/2026. Pago em 16/09/2026 pelo Banco do Nordeste · Compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
         </is>
       </c>
     </row>
@@ -49646,7 +49698,7 @@
       </c>
       <c r="I166" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 133812/001 (emissão 28/08/2026) · parcela 1/4 — 2ª via com venc. 21/09/2026 (original R$ 591,12 venc. 18/09). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>Boleto doc. 133812/001 (emissão 28/08/2026) · parcela 1/4 — 2ª via com venc. 21/09/2026 (original R$ 591,12 venc. 18/09). Pago em 21/09/2026 pelo Banco do Nordeste · Compra total R$ 2.093,55 (IPI R$ 90,31): 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4 Pol + 15x Refil Carbon Tech 5 Pol + 4x Refil Poli Flu Plissado 9.3/4 + 6x Carcaca Fit 9.3/4 Pol Branca + 5x Regulador De Pressao Tubo 3/8</t>
         </is>
       </c>
     </row>
@@ -49701,7 +49753,7 @@
       </c>
       <c r="I168" s="82" t="inlineStr">
         <is>
-          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 3/5 — venc. 20/09/2026 (domingo). Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 3/5 — venc. 20/09/2026 (domingo). Pago em 21/09/2026 pelo Banco do Nordeste · Compra total R$ 4.373,40: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco</t>
         </is>
       </c>
     </row>
@@ -50269,7 +50321,7 @@
       </c>
       <c r="I187" s="18" t="inlineStr">
         <is>
-          <t>Boleto doc. 133138/2 (emissão 12/08/2026) · parcela 2/4 — venc. 23/09/2026. Pago em 23/09/2026.</t>
+          <t>Boleto doc. 133138/2 (emissão 12/08/2026) · parcela 2/4 — venc. 23/09/2026. Pago em 23/09/2026 · Compra total R$ 2.263,62 (IPI R$ 111,90): 10x Refil Fit Poe Pp 9.3/4 + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Media + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil Cp500 + 30x Refil Carbon Tech 9.3/4 Pol + 20x Refil Poli Flu Plissado 9.3/4 + 5x Refil E3 Compacto + Carcaca Fit 9.3/4 Pol Branca</t>
         </is>
       </c>
       <c r="J187" s="18" t="n"/>
@@ -50542,7 +50594,7 @@
       </c>
       <c r="I196" s="45" t="inlineStr">
         <is>
-          <t>Boleto doc. 75472 (emissão 26/08/2026) · parcela 1/5 — venc. 25/09/2026. Pago antecipado em 24/09/2026.</t>
+          <t>Boleto doc. 75472 (emissão 26/08/2026) · parcela 1/5 — venc. 25/09/2026. Pago antecipado em 24/09/2026 · Compra total R$ 4.700,32: 100x Refil Everest + 30x Pré Filtro</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -50918,16 +50918,36 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="17" t="n"/>
-      <c r="B207" s="18" t="n"/>
-      <c r="C207" s="18" t="n"/>
-      <c r="D207" s="27" t="n"/>
-      <c r="E207" s="18" t="n"/>
+      <c r="A207" s="17" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B207" s="18" t="inlineStr">
+        <is>
+          <t>Verdes Mares Tintas</t>
+        </is>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>Limpeza de Refil</t>
+        </is>
+      </c>
+      <c r="D207" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="E207" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F207" s="19" t="n"/>
       <c r="G207" s="19" t="n"/>
       <c r="H207" s="21" t="n"/>
       <c r="I207" s="18" t="n"/>
-      <c r="J207" s="18" t="n"/>
+      <c r="J207" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0303</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -48226,7 +48226,7 @@
     </row>
     <row r="116">
       <c r="A116" s="81" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="B116" s="82" t="inlineStr">
         <is>
@@ -48243,13 +48243,17 @@
       </c>
       <c r="E116" s="82" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F116" s="83" t="n"/>
       <c r="G116" s="83" t="n"/>
       <c r="H116" s="82" t="n"/>
-      <c r="I116" s="82" t="n"/>
+      <c r="I116" s="82" t="inlineStr">
+        <is>
+          <t>Venda de 16/09/2026 — pagamento recebido em 29/09/2026 (Pix)</t>
+        </is>
+      </c>
       <c r="J116" s="82" t="inlineStr">
         <is>
           <t>EMP-0090</t>
@@ -50950,61 +50954,159 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="44" t="n"/>
-      <c r="B208" s="45" t="n"/>
+      <c r="A208" s="44" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B208" s="45" t="inlineStr">
+        <is>
+          <t>Edivandro de Jesus Bispo - Instalação do Piso da Loja</t>
+        </is>
+      </c>
       <c r="C208" s="45" t="n"/>
       <c r="D208" s="46" t="n"/>
       <c r="E208" s="45" t="n"/>
       <c r="F208" s="47" t="n"/>
-      <c r="G208" s="48" t="n"/>
-      <c r="H208" s="49" t="n"/>
-      <c r="I208" s="45" t="n"/>
+      <c r="G208" s="48" t="n">
+        <v>400</v>
+      </c>
+      <c r="H208" s="49" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I208" s="45" t="inlineStr">
+        <is>
+          <t>Pix de 28/09/2026 20:33 (Banco do Nordeste) — serviço de aplicação de piso na loja. ID E07237373202609282333NQNHHJRS16B</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="17" t="n"/>
-      <c r="B209" s="18" t="n"/>
+      <c r="A209" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B209" s="18" t="inlineStr">
+        <is>
+          <t>Compra na Shopee - Tapete e Fita Metalizada</t>
+        </is>
+      </c>
       <c r="C209" s="18" t="n"/>
       <c r="D209" s="27" t="n"/>
       <c r="E209" s="18" t="n"/>
       <c r="F209" s="19" t="n"/>
-      <c r="G209" s="19" t="n"/>
-      <c r="H209" s="21" t="n"/>
-      <c r="I209" s="18" t="n"/>
+      <c r="G209" s="19" t="n">
+        <v>142.94</v>
+      </c>
+      <c r="H209" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I209" s="18" t="inlineStr">
+        <is>
+          <t>Pix QR Code de 29/09/2026 para Shpp Brasil Instituição de Pagamento (CNPJ 38.372.267/0001-82) — tapete e fita metalizada para a loja. ID E16501555202609290015cce4815a8c1</t>
+        </is>
+      </c>
       <c r="J209" s="18" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="44" t="n"/>
-      <c r="B210" s="45" t="n"/>
-      <c r="C210" s="45" t="n"/>
-      <c r="D210" s="46" t="n"/>
-      <c r="E210" s="45" t="n"/>
+      <c r="A210" s="44" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B210" s="45" t="inlineStr">
+        <is>
+          <t>Sara Andreia Barros de Souza Santana - Escola Educare</t>
+        </is>
+      </c>
+      <c r="C210" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D210" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E210" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F210" s="47" t="n"/>
       <c r="G210" s="48" t="n"/>
       <c r="H210" s="49" t="n"/>
       <c r="I210" s="45" t="n"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>EMP-0272</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="17" t="n"/>
-      <c r="B211" s="18" t="n"/>
-      <c r="C211" s="18" t="n"/>
-      <c r="D211" s="27" t="n"/>
-      <c r="E211" s="18" t="n"/>
+      <c r="A211" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B211" s="18" t="inlineStr">
+        <is>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+        </is>
+      </c>
+      <c r="C211" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D211" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E211" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F211" s="19" t="n"/>
       <c r="G211" s="19" t="n"/>
       <c r="H211" s="21" t="n"/>
       <c r="I211" s="18" t="n"/>
-      <c r="J211" s="18" t="n"/>
+      <c r="J211" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0032</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="44" t="n"/>
-      <c r="B212" s="45" t="n"/>
-      <c r="C212" s="45" t="n"/>
-      <c r="D212" s="46" t="n"/>
-      <c r="E212" s="45" t="n"/>
+      <c r="A212" s="44" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B212" s="45" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="C212" s="45" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
+      <c r="D212" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E212" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F212" s="47" t="n"/>
       <c r="G212" s="48" t="n"/>
       <c r="H212" s="49" t="n"/>
-      <c r="I212" s="45" t="n"/>
+      <c r="I212" s="45" t="inlineStr">
+        <is>
+          <t>Preço com desconto de cliente. Pagamento previsto para 30/09/2026.</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="17" t="n"/>
@@ -62888,7 +62990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -66659,7 +66761,7 @@
       </c>
       <c r="E130" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F130" s="112">
@@ -66668,7 +66770,7 @@
       </c>
       <c r="G130" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato.</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
@@ -66865,44 +66967,106 @@
       </c>
     </row>
     <row r="137" s="157">
-      <c r="A137" s="86" t="inlineStr">
+      <c r="A137" s="78" t="inlineStr">
+        <is>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+        </is>
+      </c>
+      <c r="B137" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C137" s="77" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D137" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E137" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F137" s="112">
+        <f>IF(OR($E137="Recebido",$C137=""),"",MAX(0,TODAY()-$C137))</f>
+        <v/>
+      </c>
+      <c r="G137" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 29/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" s="157">
+      <c r="A138" s="78" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="B138" s="78" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
+      <c r="C138" s="77" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D138" s="79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E138" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F138" s="112">
+        <f>IF(OR($E138="Recebido",$C138=""),"",MAX(0,TODAY()-$C138))</f>
+        <v/>
+      </c>
+      <c r="G138" s="78" t="inlineStr">
+        <is>
+          <t>Pagamento previsto para 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" s="157">
+      <c r="A139" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D137" s="115">
-        <f>SUMIF(E92:E136,"Pendente",D92:D136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" s="157">
-      <c r="A138" s="202" t="inlineStr">
+      <c r="D139" s="115">
+        <f>SUMIF(E92:E138,"Pendente",D92:D138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" s="157">
+      <c r="A140" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B138" s="159" t="n"/>
-      <c r="C138" s="159" t="n"/>
-      <c r="D138" s="159" t="n"/>
-      <c r="E138" s="159" t="n"/>
-      <c r="F138" s="159" t="n"/>
-      <c r="G138" s="160" t="n"/>
-    </row>
-    <row r="139" s="157">
-      <c r="A139" s="203">
-        <f>IF(ROUND(D137-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D137-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" s="157">
-      <c r="A140" s="203" t="inlineStr">
+      <c r="B140" s="159" t="n"/>
+      <c r="C140" s="159" t="n"/>
+      <c r="D140" s="159" t="n"/>
+      <c r="E140" s="159" t="n"/>
+      <c r="F140" s="159" t="n"/>
+      <c r="G140" s="160" t="n"/>
+    </row>
+    <row r="141" s="157">
+      <c r="A141" s="203">
+        <f>IF(ROUND(D139-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D139-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" s="157">
+      <c r="A142" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="141" s="157"/>
-    <row r="142" s="157"/>
     <row r="143" s="157"/>
     <row r="144" s="157"/>
     <row r="145" s="157"/>
@@ -66970,22 +67134,22 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A141:G141"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A140:G140"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A139:G139"/>
     <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A138:G138"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E92:E136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E92:E138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51109,15 +51109,31 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="17" t="n"/>
-      <c r="B213" s="18" t="n"/>
+      <c r="A213" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B213" s="18" t="inlineStr">
+        <is>
+          <t>Mil Coisas (Eletrônicos e Informática) - Pilha palito</t>
+        </is>
+      </c>
       <c r="C213" s="18" t="n"/>
       <c r="D213" s="27" t="n"/>
       <c r="E213" s="18" t="n"/>
       <c r="F213" s="19" t="n"/>
-      <c r="G213" s="19" t="n"/>
-      <c r="H213" s="21" t="n"/>
-      <c r="I213" s="18" t="n"/>
+      <c r="G213" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H213" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I213" s="18" t="inlineStr">
+        <is>
+          <t>Pago em dinheiro — recibo da Mil Coisas.</t>
+        </is>
+      </c>
       <c r="J213" s="18" t="n"/>
     </row>
     <row r="214">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -44231,11 +44231,11 @@
     </row>
     <row r="177">
       <c r="A177" s="17" t="n">
-        <v>46235</v>
+        <v>46265</v>
       </c>
       <c r="B177" s="18" t="inlineStr">
         <is>
-          <t>Tarifa Pacote de Tarifas</t>
+          <t>Tarifa Pix (14 lançamentos)</t>
         </is>
       </c>
       <c r="C177" s="18" t="n"/>
@@ -44243,14 +44243,18 @@
       <c r="E177" s="18" t="n"/>
       <c r="F177" s="19" t="n"/>
       <c r="G177" s="20" t="n">
-        <v>52.5</v>
+        <v>48.25</v>
       </c>
       <c r="H177" s="21" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
         </is>
       </c>
-      <c r="I177" s="18" t="n"/>
+      <c r="I177" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="44" t="n">
@@ -44258,7 +44262,7 @@
       </c>
       <c r="B178" s="45" t="inlineStr">
         <is>
-          <t>Tarifa Pix (14 lançamentos)</t>
+          <t>Pix Pessoal (4 lançamentos)</t>
         </is>
       </c>
       <c r="C178" s="45" t="n"/>
@@ -44266,16 +44270,16 @@
       <c r="E178" s="45" t="n"/>
       <c r="F178" s="47" t="n"/>
       <c r="G178" s="47" t="n">
-        <v>48.25</v>
+        <v>221.5</v>
       </c>
       <c r="H178" s="49" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias e Cartão</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I178" s="45" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
+          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
         </is>
       </c>
     </row>
@@ -44285,7 +44289,7 @@
       </c>
       <c r="B179" s="18" t="inlineStr">
         <is>
-          <t>Pix Pessoal (4 lançamentos)</t>
+          <t>Compras p/Loja (2 lançamentos)</t>
         </is>
       </c>
       <c r="C179" s="18" t="n"/>
@@ -44293,16 +44297,16 @@
       <c r="E179" s="18" t="n"/>
       <c r="F179" s="19" t="n"/>
       <c r="G179" s="20" t="n">
-        <v>221.5</v>
+        <v>131.29</v>
       </c>
       <c r="H179" s="21" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
+          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
         </is>
       </c>
     </row>
@@ -44312,7 +44316,7 @@
       </c>
       <c r="B180" s="45" t="inlineStr">
         <is>
-          <t>Compras p/Loja (2 lançamentos)</t>
+          <t>Estacionamento (2 lançamentos)</t>
         </is>
       </c>
       <c r="C180" s="45" t="n"/>
@@ -44320,16 +44324,16 @@
       <c r="E180" s="45" t="n"/>
       <c r="F180" s="47" t="n"/>
       <c r="G180" s="47" t="n">
-        <v>131.29</v>
+        <v>6</v>
       </c>
       <c r="H180" s="49" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I180" s="45" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
+          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
         </is>
       </c>
     </row>
@@ -44339,7 +44343,7 @@
       </c>
       <c r="B181" s="18" t="inlineStr">
         <is>
-          <t>Estacionamento (2 lançamentos)</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="C181" s="18" t="n"/>
@@ -44347,45 +44351,47 @@
       <c r="E181" s="18" t="n"/>
       <c r="F181" s="19" t="n"/>
       <c r="G181" s="20" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H181" s="21" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
         </is>
       </c>
-      <c r="I181" s="18" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
-        </is>
-      </c>
+      <c r="I181" s="18" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="44" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B182" s="45" t="inlineStr">
         <is>
-          <t>Gasolina</t>
+          <t>Cliente de Armando</t>
         </is>
       </c>
       <c r="C182" s="45" t="n"/>
-      <c r="D182" s="50" t="n"/>
-      <c r="E182" s="45" t="n"/>
-      <c r="F182" s="47" t="n"/>
-      <c r="G182" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="H182" s="49" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I182" s="45" t="n"/>
+      <c r="D182" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="E182" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F182" s="47" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="G182" s="47" t="n"/>
+      <c r="H182" s="49" t="n"/>
+      <c r="I182" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 3x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="17" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B183" s="18" t="inlineStr">
         <is>
@@ -44394,7 +44400,7 @@
       </c>
       <c r="C183" s="18" t="n"/>
       <c r="D183" s="134" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
@@ -44402,44 +44408,26 @@
         </is>
       </c>
       <c r="F183" s="19" t="n">
-        <v>11.18</v>
+        <v>13.98</v>
       </c>
       <c r="G183" s="20" t="n"/>
       <c r="H183" s="21" t="n"/>
       <c r="I183" s="18" t="inlineStr">
         <is>
-          <t>Crédito em 3x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+          <t>Crédito em 2x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="157">
-      <c r="A184" s="44" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B184" s="45" t="inlineStr">
-        <is>
-          <t>Cliente de Armando</t>
-        </is>
-      </c>
+      <c r="A184" s="44" t="n"/>
+      <c r="B184" s="45" t="n"/>
       <c r="C184" s="45" t="n"/>
-      <c r="D184" s="50" t="n">
-        <v>200</v>
-      </c>
-      <c r="E184" s="45" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F184" s="47" t="n">
-        <v>13.98</v>
-      </c>
+      <c r="D184" s="50" t="n"/>
+      <c r="E184" s="45" t="n"/>
+      <c r="F184" s="47" t="n"/>
       <c r="G184" s="47" t="n"/>
       <c r="H184" s="49" t="n"/>
-      <c r="I184" s="45" t="inlineStr">
-        <is>
-          <t>Crédito em 2x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
-        </is>
-      </c>
+      <c r="I184" s="45" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="29" t="n"/>
@@ -49117,7 +49105,7 @@
       </c>
       <c r="B146" s="82" t="inlineStr">
         <is>
-          <t>Pagar.me Instituição de Pagamento</t>
+          <t>Estacionamento (Pagar.me)</t>
         </is>
       </c>
       <c r="C146" s="82" t="n"/>
@@ -49129,12 +49117,12 @@
       </c>
       <c r="H146" s="82" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I146" s="82" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 09/09/2026.</t>
+          <t>Extrato Stone/Ton — Pix de 09/09/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
         </is>
       </c>
     </row>
@@ -49729,7 +49717,7 @@
       </c>
       <c r="I167" s="78" t="inlineStr">
         <is>
-          <t>DAS competência agosto/2026 (doc. 07.20.26260.6017058-0) — venc. 21/09/2026. Pago em 21/09/2026 pelo Banco do Nordeste.</t>
+          <t>DAS competência agosto/2026 (doc. 07.20.26260.6017058-0) — venc. 21/09/2026. Pago em 21/09/2026 pela conta Ton (Stone).</t>
         </is>
       </c>
       <c r="J167" s="78" t="n"/>
@@ -51137,291 +51125,711 @@
       <c r="J213" s="18" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="44" t="n"/>
-      <c r="B214" s="45" t="n"/>
+      <c r="A214" s="44" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B214" s="45" t="inlineStr">
+        <is>
+          <t>Tarifa Pacote de Tarifas</t>
+        </is>
+      </c>
       <c r="C214" s="45" t="n"/>
       <c r="D214" s="46" t="n"/>
       <c r="E214" s="45" t="n"/>
       <c r="F214" s="47" t="n"/>
-      <c r="G214" s="48" t="n"/>
-      <c r="H214" s="49" t="n"/>
-      <c r="I214" s="45" t="n"/>
+      <c r="G214" s="48" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H214" s="49" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I214" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB — TARIFA PACOTE DE TARIFAS, DOC 8227 (01/09/2026)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="17" t="n"/>
-      <c r="B215" s="18" t="n"/>
+      <c r="A215" s="17" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B215" s="18" t="inlineStr">
+        <is>
+          <t>Maria Eva dos Santos</t>
+        </is>
+      </c>
       <c r="C215" s="18" t="n"/>
       <c r="D215" s="27" t="n"/>
       <c r="E215" s="18" t="n"/>
       <c r="F215" s="19" t="n"/>
-      <c r="G215" s="19" t="n"/>
-      <c r="H215" s="21" t="n"/>
-      <c r="I215" s="18" t="n"/>
+      <c r="G215" s="19" t="n">
+        <v>380</v>
+      </c>
+      <c r="H215" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I215" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 08/09/2026 (ref. 07/09), DOC 11974. Marcado como pessoal pela Edilânia.</t>
+        </is>
+      </c>
       <c r="J215" s="18" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="44" t="n"/>
-      <c r="B216" s="45" t="n"/>
+      <c r="A216" s="44" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B216" s="45" t="inlineStr">
+        <is>
+          <t>Shpp Brasil Instituição de Pagamento (Shopee)</t>
+        </is>
+      </c>
       <c r="C216" s="45" t="n"/>
       <c r="D216" s="46" t="n"/>
       <c r="E216" s="45" t="n"/>
       <c r="F216" s="47" t="n"/>
-      <c r="G216" s="48" t="n"/>
-      <c r="H216" s="49" t="n"/>
-      <c r="I216" s="45" t="n"/>
+      <c r="G216" s="48" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="H216" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I216" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 08/09/2026 (ref. 06/09), DOC 11974. Marcado como pessoal pela Edilânia.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="17" t="n"/>
-      <c r="B217" s="18" t="n"/>
+      <c r="A217" s="17" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B217" s="18" t="inlineStr">
+        <is>
+          <t>RC Serviços de Alimentação Ltda</t>
+        </is>
+      </c>
       <c r="C217" s="18" t="n"/>
       <c r="D217" s="27" t="n"/>
       <c r="E217" s="18" t="n"/>
       <c r="F217" s="19" t="n"/>
-      <c r="G217" s="19" t="n"/>
-      <c r="H217" s="21" t="n"/>
-      <c r="I217" s="18" t="n"/>
+      <c r="G217" s="19" t="n">
+        <v>143</v>
+      </c>
+      <c r="H217" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I217" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 08/09/2026 (ref. 06/09), DOC 11974. Marcado como pessoal pela Edilânia.</t>
+        </is>
+      </c>
       <c r="J217" s="18" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="44" t="n"/>
-      <c r="B218" s="45" t="n"/>
+      <c r="A218" s="44" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B218" s="45" t="inlineStr">
+        <is>
+          <t>Daniel Barbosa dos Santos (Moto Táxi)</t>
+        </is>
+      </c>
       <c r="C218" s="45" t="n"/>
       <c r="D218" s="46" t="n"/>
       <c r="E218" s="45" t="n"/>
       <c r="F218" s="47" t="n"/>
-      <c r="G218" s="48" t="n"/>
-      <c r="H218" s="49" t="n"/>
-      <c r="I218" s="45" t="n"/>
+      <c r="G218" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H218" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I218" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 09/09/2026, DOC 11974.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="17" t="n"/>
-      <c r="B219" s="18" t="n"/>
+      <c r="A219" s="17" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B219" s="18" t="inlineStr">
+        <is>
+          <t>Maria Eva dos Santos</t>
+        </is>
+      </c>
       <c r="C219" s="18" t="n"/>
       <c r="D219" s="27" t="n"/>
       <c r="E219" s="18" t="n"/>
       <c r="F219" s="19" t="n"/>
-      <c r="G219" s="19" t="n"/>
-      <c r="H219" s="21" t="n"/>
-      <c r="I219" s="18" t="n"/>
+      <c r="G219" s="19" t="n">
+        <v>380</v>
+      </c>
+      <c r="H219" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I219" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 23/09/2026, DOC 11974. Marcado como pessoal pela Edilânia.</t>
+        </is>
+      </c>
       <c r="J219" s="18" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="44" t="n"/>
-      <c r="B220" s="45" t="n"/>
+      <c r="A220" s="44" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B220" s="45" t="inlineStr">
+        <is>
+          <t>Farmácia Pague Menos</t>
+        </is>
+      </c>
       <c r="C220" s="45" t="n"/>
       <c r="D220" s="46" t="n"/>
       <c r="E220" s="45" t="n"/>
       <c r="F220" s="47" t="n"/>
-      <c r="G220" s="48" t="n"/>
-      <c r="H220" s="49" t="n"/>
-      <c r="I220" s="45" t="n"/>
+      <c r="G220" s="48" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="H220" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I220" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 28/09/2026 (ref. 27/09), DOC 11974. Marcado como pessoal pela Edilânia.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="17" t="n"/>
-      <c r="B221" s="18" t="n"/>
+      <c r="A221" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B221" s="18" t="inlineStr">
+        <is>
+          <t>Atacadão da Limpeza</t>
+        </is>
+      </c>
       <c r="C221" s="18" t="n"/>
       <c r="D221" s="27" t="n"/>
       <c r="E221" s="18" t="n"/>
       <c r="F221" s="19" t="n"/>
-      <c r="G221" s="19" t="n"/>
-      <c r="H221" s="21" t="n"/>
-      <c r="I221" s="18" t="n"/>
+      <c r="G221" s="19" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="H221" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I221" s="18" t="inlineStr">
+        <is>
+          <t>Mop inox Clink (R$ 69,99) + limpa espuma multiuso 400 ml Rodabrill (R$ 29,99) — venda nº 00021875 de 29/09/2026. Pago em dinheiro.</t>
+        </is>
+      </c>
       <c r="J221" s="18" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="44" t="n"/>
-      <c r="B222" s="45" t="n"/>
+      <c r="A222" s="44" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B222" s="45" t="inlineStr">
+        <is>
+          <t>Tarifa Pix (28 lançamentos)</t>
+        </is>
+      </c>
       <c r="C222" s="45" t="n"/>
       <c r="D222" s="46" t="n"/>
       <c r="E222" s="45" t="n"/>
       <c r="F222" s="47" t="n"/>
-      <c r="G222" s="48" t="n"/>
-      <c r="H222" s="49" t="n"/>
-      <c r="I222" s="45" t="n"/>
+      <c r="G222" s="48" t="n">
+        <v>83.61</v>
+      </c>
+      <c r="H222" s="49" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I222" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB setembro/2026 — soma de 28 tarifas Pix (Cobr. QR Code DOC 12423 e Pagto/Transferência DOC 12422) de 01/09 a 30/09 ainda não lançadas: 01/09 37,73 · 11/09 2,38 · 14/09 5,30 · 16/09 4,46 · 21/09 3,23 · 22/09 2,88 · 23/09 4,50 · 24/09 4,65 · 28/09 10,30 · 29/09 6,79 · 30/09 1,39</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="17" t="n"/>
-      <c r="B223" s="18" t="n"/>
+      <c r="A223" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B223" s="18" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C223" s="18" t="n"/>
       <c r="D223" s="27" t="n"/>
       <c r="E223" s="18" t="n"/>
       <c r="F223" s="19" t="n"/>
-      <c r="G223" s="19" t="n"/>
-      <c r="H223" s="21" t="n"/>
-      <c r="I223" s="18" t="n"/>
+      <c r="G223" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H223" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I223" s="18" t="inlineStr">
+        <is>
+          <t>R$ 20,00 tirados da segunda gaveta do caixa. Pago em dinheiro.</t>
+        </is>
+      </c>
       <c r="J223" s="18" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="44" t="n"/>
-      <c r="B224" s="45" t="n"/>
+      <c r="A224" s="44" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B224" s="45" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="C224" s="45" t="n"/>
       <c r="D224" s="46" t="n"/>
       <c r="E224" s="45" t="n"/>
       <c r="F224" s="47" t="n"/>
-      <c r="G224" s="48" t="n"/>
-      <c r="H224" s="49" t="n"/>
-      <c r="I224" s="45" t="n"/>
+      <c r="G224" s="48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H224" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I224" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 01/09/2026 para Edilânia Almeida Silva Costa Fontes, DOC 11974. Pró-labore de setembro (confirmado).</t>
+        </is>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="17" t="n"/>
-      <c r="B225" s="18" t="n"/>
+      <c r="A225" s="17" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B225" s="18" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C225" s="18" t="n"/>
       <c r="D225" s="27" t="n"/>
       <c r="E225" s="18" t="n"/>
       <c r="F225" s="19" t="n"/>
-      <c r="G225" s="19" t="n"/>
-      <c r="H225" s="21" t="n"/>
-      <c r="I225" s="18" t="n"/>
+      <c r="G225" s="19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H225" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I225" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB — Pix de 09/09/2026 para Pagar.me Instituição de Pagamento, DOC 11974 (estacionamento). Outro de R$ 2,40 no mesmo dia saiu pela Ton.</t>
+        </is>
+      </c>
       <c r="J225" s="18" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="44" t="n"/>
-      <c r="B226" s="45" t="n"/>
+      <c r="A226" s="44" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B226" s="45" t="inlineStr">
+        <is>
+          <t>Pampet Club</t>
+        </is>
+      </c>
       <c r="C226" s="45" t="n"/>
       <c r="D226" s="46" t="n"/>
       <c r="E226" s="45" t="n"/>
       <c r="F226" s="47" t="n"/>
-      <c r="G226" s="48" t="n"/>
-      <c r="H226" s="49" t="n"/>
-      <c r="I226" s="45" t="n"/>
+      <c r="G226" s="48" t="n">
+        <v>76</v>
+      </c>
+      <c r="H226" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I226" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 19/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="17" t="n"/>
-      <c r="B227" s="18" t="n"/>
+      <c r="A227" s="17" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B227" s="18" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
       <c r="C227" s="18" t="n"/>
       <c r="D227" s="27" t="n"/>
       <c r="E227" s="18" t="n"/>
       <c r="F227" s="19" t="n"/>
-      <c r="G227" s="19" t="n"/>
-      <c r="H227" s="21" t="n"/>
-      <c r="I227" s="18" t="n"/>
+      <c r="G227" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H227" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I227" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 21/09/2026.</t>
+        </is>
+      </c>
       <c r="J227" s="18" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="44" t="n"/>
-      <c r="B228" s="45" t="n"/>
+      <c r="A228" s="44" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B228" s="45" t="inlineStr">
+        <is>
+          <t>Multidisplay Comercio e Servicos Tecnologicos</t>
+        </is>
+      </c>
       <c r="C228" s="45" t="n"/>
       <c r="D228" s="46" t="n"/>
       <c r="E228" s="45" t="n"/>
       <c r="F228" s="47" t="n"/>
-      <c r="G228" s="48" t="n"/>
-      <c r="H228" s="49" t="n"/>
-      <c r="I228" s="45" t="n"/>
+      <c r="G228" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="H228" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I228" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 21/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="17" t="n"/>
-      <c r="B229" s="18" t="n"/>
+      <c r="A229" s="17" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B229" s="18" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C229" s="18" t="n"/>
       <c r="D229" s="27" t="n"/>
       <c r="E229" s="18" t="n"/>
       <c r="F229" s="19" t="n"/>
-      <c r="G229" s="19" t="n"/>
-      <c r="H229" s="21" t="n"/>
-      <c r="I229" s="18" t="n"/>
+      <c r="G229" s="19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H229" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I229" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 22/09/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
+        </is>
+      </c>
       <c r="J229" s="18" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="44" t="n"/>
-      <c r="B230" s="45" t="n"/>
+      <c r="A230" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B230" s="45" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C230" s="45" t="n"/>
       <c r="D230" s="46" t="n"/>
       <c r="E230" s="45" t="n"/>
       <c r="F230" s="47" t="n"/>
-      <c r="G230" s="48" t="n"/>
-      <c r="H230" s="49" t="n"/>
-      <c r="I230" s="45" t="n"/>
+      <c r="G230" s="48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H230" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I230" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 24/09/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="17" t="n"/>
-      <c r="B231" s="18" t="n"/>
+      <c r="A231" s="17" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B231" s="18" t="inlineStr">
+        <is>
+          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
+        </is>
+      </c>
       <c r="C231" s="18" t="n"/>
       <c r="D231" s="27" t="n"/>
       <c r="E231" s="18" t="n"/>
       <c r="F231" s="19" t="n"/>
-      <c r="G231" s="19" t="n"/>
-      <c r="H231" s="21" t="n"/>
-      <c r="I231" s="18" t="n"/>
+      <c r="G231" s="19" t="n">
+        <v>162.14</v>
+      </c>
+      <c r="H231" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I231" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 25/09/2026.</t>
+        </is>
+      </c>
       <c r="J231" s="18" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="44" t="n"/>
-      <c r="B232" s="45" t="n"/>
+      <c r="A232" s="44" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B232" s="45" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="C232" s="45" t="n"/>
       <c r="D232" s="46" t="n"/>
       <c r="E232" s="45" t="n"/>
       <c r="F232" s="47" t="n"/>
-      <c r="G232" s="48" t="n"/>
-      <c r="H232" s="49" t="n"/>
-      <c r="I232" s="45" t="n"/>
+      <c r="G232" s="48" t="n">
+        <v>400</v>
+      </c>
+      <c r="H232" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I232" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 28/09/2026 para Edilânia Almeida Silva Costa Fontes.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="17" t="n"/>
-      <c r="B233" s="18" t="n"/>
+      <c r="A233" s="17" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B233" s="18" t="inlineStr">
+        <is>
+          <t>Maria Carolina Gomes Vasconcelos &amp; Cia Ltda</t>
+        </is>
+      </c>
       <c r="C233" s="18" t="n"/>
       <c r="D233" s="27" t="n"/>
       <c r="E233" s="18" t="n"/>
       <c r="F233" s="19" t="n"/>
-      <c r="G233" s="19" t="n"/>
-      <c r="H233" s="21" t="n"/>
-      <c r="I233" s="18" t="n"/>
+      <c r="G233" s="19" t="n">
+        <v>220</v>
+      </c>
+      <c r="H233" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I233" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 21/09/2026. Gasto pessoal (confirmado pela Edilânia).</t>
+        </is>
+      </c>
       <c r="J233" s="18" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="44" t="n"/>
-      <c r="B234" s="45" t="n"/>
+      <c r="A234" s="44" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B234" s="45" t="inlineStr">
+        <is>
+          <t>Edinaldo Silva da Cruz</t>
+        </is>
+      </c>
       <c r="C234" s="45" t="n"/>
       <c r="D234" s="46" t="n"/>
       <c r="E234" s="45" t="n"/>
       <c r="F234" s="47" t="n"/>
-      <c r="G234" s="48" t="n"/>
-      <c r="H234" s="49" t="n"/>
-      <c r="I234" s="45" t="n"/>
+      <c r="G234" s="48" t="n">
+        <v>50</v>
+      </c>
+      <c r="H234" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I234" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 21/09/2026. Gasto pessoal (confirmado pela Edilânia).</t>
+        </is>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="17" t="n"/>
-      <c r="B235" s="18" t="n"/>
+      <c r="A235" s="17" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B235" s="18" t="inlineStr">
+        <is>
+          <t>Bytedance Brasil (TikTok)</t>
+        </is>
+      </c>
       <c r="C235" s="18" t="n"/>
       <c r="D235" s="27" t="n"/>
       <c r="E235" s="18" t="n"/>
       <c r="F235" s="19" t="n"/>
-      <c r="G235" s="19" t="n"/>
-      <c r="H235" s="21" t="n"/>
-      <c r="I235" s="18" t="n"/>
+      <c r="G235" s="19" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H235" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I235" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Ton — Pix de 28/09/2026. Gasto pessoal (confirmado pela Edilânia).</t>
+        </is>
+      </c>
       <c r="J235" s="18" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="44" t="n"/>
-      <c r="B236" s="45" t="n"/>
-      <c r="C236" s="45" t="n"/>
-      <c r="D236" s="46" t="n"/>
-      <c r="E236" s="45" t="n"/>
-      <c r="F236" s="47" t="n"/>
+      <c r="A236" s="44" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B236" s="45" t="inlineStr">
+        <is>
+          <t>Milton Ribeiro</t>
+        </is>
+      </c>
+      <c r="C236" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Fit Preto</t>
+        </is>
+      </c>
+      <c r="D236" s="46" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E236" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F236" s="47" t="n">
+        <v>198.66</v>
+      </c>
       <c r="G236" s="48" t="n"/>
       <c r="H236" s="49" t="n"/>
-      <c r="I236" s="45" t="n"/>
+      <c r="I236" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 10x. Instalação agendada para 01/10/2026 (Rua 06, 156 — Morada do Sol).</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>CLI-0898</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="17" t="n"/>
-      <c r="B237" s="18" t="n"/>
-      <c r="C237" s="18" t="n"/>
-      <c r="D237" s="27" t="n"/>
-      <c r="E237" s="18" t="n"/>
+      <c r="A237" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B237" s="18" t="inlineStr">
+        <is>
+          <t>Francilene Santos Silva</t>
+        </is>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D237" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="E237" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F237" s="19" t="n"/>
       <c r="G237" s="19" t="n"/>
       <c r="H237" s="21" t="n"/>
       <c r="I237" s="18" t="n"/>
-      <c r="J237" s="18" t="n"/>
+      <c r="J237" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0325</t>
+        </is>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="44" t="n"/>
-      <c r="B238" s="45" t="n"/>
-      <c r="C238" s="45" t="n"/>
-      <c r="D238" s="46" t="n"/>
-      <c r="E238" s="45" t="n"/>
+      <c r="A238" s="44" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B238" s="45" t="inlineStr">
+        <is>
+          <t>Maria Isabel</t>
+        </is>
+      </c>
+      <c r="C238" s="45" t="inlineStr">
+        <is>
+          <t>Refil FPA16</t>
+        </is>
+      </c>
+      <c r="D238" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E238" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F238" s="47" t="n"/>
       <c r="G238" s="48" t="n"/>
       <c r="H238" s="49" t="n"/>
       <c r="I238" s="45" t="n"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>CLI-0899</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="17" t="n"/>
@@ -68219,11 +68627,11 @@
         </is>
       </c>
       <c r="B9" s="109" t="n">
-        <v>23500</v>
+        <v>26000</v>
       </c>
       <c r="C9" s="131" t="inlineStr">
         <is>
-          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Total guardado: R$ 23.500,00.</t>
+          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Pix do BNB para Adriano guardados como reserva (confirmado pela Edilânia em 30/09/2026): R$ 500,00 em 11/09 e R$ 2.000,00 em 25/09. Total guardado: R$ 26.000,00. Em aberto: Pix de R$ 2.000,00 para Adriano em 09/09 — confirmar se já faz parte dos R$ 6.500,00 do mesmo dia.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51832,15 +51832,31 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="17" t="n"/>
-      <c r="B239" s="18" t="n"/>
+      <c r="A239" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B239" s="18" t="inlineStr">
+        <is>
+          <t>Knox Produtos Refrigerados</t>
+        </is>
+      </c>
       <c r="C239" s="18" t="n"/>
       <c r="D239" s="27" t="n"/>
       <c r="E239" s="18" t="n"/>
       <c r="F239" s="19" t="n"/>
-      <c r="G239" s="19" t="n"/>
-      <c r="H239" s="21" t="n"/>
-      <c r="I239" s="18" t="n"/>
+      <c r="G239" s="19" t="n">
+        <v>3272</v>
+      </c>
+      <c r="H239" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I239" s="18" t="inlineStr">
+        <is>
+          <t>2 bebedouros industriais. Pix de R$ 3.272,00 em 30/09/2026 17:01 para Knox Produtos Refrigerados Ltda (CNPJ 15.719.703/0001-41), pago pelo Adriano no Banco do Brasil com dinheiro da reserva — controle na aba Capital de Giro (BB). ID E0000000020260930200055659998914</t>
+        </is>
+      </c>
       <c r="J239" s="18" t="n"/>
     </row>
     <row r="240">
@@ -67591,7 +67607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="157" min="1" max="1"/>
@@ -67871,7 +67887,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="157">
       <c r="A15" s="40" t="n">
         <v>46254</v>
       </c>
@@ -67902,25 +67918,54 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="164" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="210" t="inlineStr">
+    <row r="16" s="157">
+      <c r="A16" s="40" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Knox Produtos Refrigerados (2 bebedouros industriais)</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>3272</v>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>A Devolver</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>Pago pelo Adriano via Pix do Banco do Brasil com dinheiro da reserva — 30/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" s="157">
+      <c r="A17" s="164" t="n"/>
+    </row>
+    <row r="18" s="157">
+      <c r="A18" s="210" t="inlineStr">
         <is>
           <t>Como registrar uma devolução:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="211" t="inlineStr">
+    <row r="19" s="157">
+      <c r="A19" s="211" t="inlineStr">
         <is>
           <t>1. Trocar "Status" da linha para "Devolvido" e preencher a "Data da Devolução".</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="129" t="inlineStr">
+    <row r="20" s="157">
+      <c r="A20" s="129" t="inlineStr">
         <is>
           <t>2. Só isso. NÃO lançar a devolução como Saída na aba do mês — a despesa já foi lançada uma vez lá. Enquanto o status for "A Devolver", o valor é descontado do total de Despesas do mês (linha "Capital de Giro (BB) — ainda a devolver" do pivô); ao virar "Devolvido", passa a contar normalmente.</t>
         </is>
@@ -67937,7 +67982,7 @@
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="1">
@@ -68627,11 +68672,11 @@
         </is>
       </c>
       <c r="B9" s="109" t="n">
-        <v>26000</v>
+        <v>22728</v>
       </c>
       <c r="C9" s="131" t="inlineStr">
         <is>
-          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Pix do BNB para Adriano guardados como reserva (confirmado pela Edilânia em 30/09/2026): R$ 500,00 em 11/09 e R$ 2.000,00 em 25/09. Total guardado: R$ 26.000,00. Em aberto: Pix de R$ 2.000,00 para Adriano em 09/09 — confirmar se já faz parte dos R$ 6.500,00 do mesmo dia.</t>
+          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Pix do BNB para Adriano guardados como reserva (confirmado pela Edilânia em 30/09/2026): R$ 500,00 em 11/09 e R$ 2.000,00 em 25/09. Em 30/09/2026 saíram R$ 3.272,00 da reserva para pagar 2 bebedouros industriais da Knox (a loja deve devolver — ver aba Capital de Giro (BB)). Total guardado: R$ 22.728,00. Em aberto: Pix de R$ 2.000,00 para Adriano em 09/09 — confirmar se já faz parte dos R$ 6.500,00 do mesmo dia.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51860,38 +51860,98 @@
       <c r="J239" s="18" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="44" t="n"/>
-      <c r="B240" s="45" t="n"/>
-      <c r="C240" s="45" t="n"/>
-      <c r="D240" s="46" t="n"/>
-      <c r="E240" s="45" t="n"/>
-      <c r="F240" s="47" t="n"/>
+      <c r="A240" s="44" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B240" s="45" t="inlineStr">
+        <is>
+          <t>Genilson Teixeira Santana Aguiar</t>
+        </is>
+      </c>
+      <c r="C240" s="45" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D240" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E240" s="45" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F240" s="47" t="n">
+        <v>0.87</v>
+      </c>
       <c r="G240" s="48" t="n"/>
       <c r="H240" s="49" t="n"/>
       <c r="I240" s="45" t="n"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>CLI-0138</t>
+        </is>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="17" t="n"/>
-      <c r="B241" s="18" t="n"/>
+      <c r="A241" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B241" s="18" t="inlineStr">
+        <is>
+          <t>Faca Feira Supermercado</t>
+        </is>
+      </c>
       <c r="C241" s="18" t="n"/>
       <c r="D241" s="27" t="n"/>
       <c r="E241" s="18" t="n"/>
       <c r="F241" s="19" t="n"/>
-      <c r="G241" s="19" t="n"/>
-      <c r="H241" s="21" t="n"/>
-      <c r="I241" s="18" t="n"/>
+      <c r="G241" s="19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H241" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I241" s="18" t="inlineStr">
+        <is>
+          <t>Isqueiro BIC mini — NFC-e nº 000209441 de 30/09/2026. Pago em dinheiro.</t>
+        </is>
+      </c>
       <c r="J241" s="18" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="44" t="n"/>
-      <c r="B242" s="45" t="n"/>
-      <c r="C242" s="45" t="n"/>
-      <c r="D242" s="46" t="n"/>
-      <c r="E242" s="45" t="n"/>
+      <c r="A242" s="44" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B242" s="45" t="inlineStr">
+        <is>
+          <t>PC Jacobina Administradora de Cartões LTDA</t>
+        </is>
+      </c>
+      <c r="C242" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D242" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E242" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F242" s="47" t="n"/>
       <c r="G242" s="48" t="n"/>
       <c r="H242" s="49" t="n"/>
       <c r="I242" s="45" t="n"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>EMP-0244</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="17" t="n"/>
@@ -63430,7 +63490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -63541,12 +63601,12 @@
     <row r="11">
       <c r="A11" s="78" t="inlineStr">
         <is>
-          <t>Capital de Giro (BB) — saldo a devolver</t>
+          <t>Capital de Giro (BB) — saldo a devolver à reserva</t>
         </is>
       </c>
       <c r="B11" s="78" t="inlineStr">
         <is>
-          <t>Empréstimo de reserva usado para pagar contas da loja em Ago/2026</t>
+          <t>Dinheiro da reserva (Banco do Brasil) usado para pagar contas da loja</t>
         </is>
       </c>
       <c r="C11" s="77" t="n"/>
@@ -63556,7 +63616,7 @@
       </c>
       <c r="E11" s="112" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F11" s="112">
@@ -63565,7 +63625,7 @@
       </c>
       <c r="G11" s="78" t="inlineStr">
         <is>
-          <t>Detalhe na aba Capital de Giro (BB). Quitado integralmente em 31/08/2026 (aporte de Adriano na reserva).</t>
+          <t>Detalhe na aba Capital de Giro (BB). Ago/2026 quitado em 31/08/2026. Em 30/09/2026 a reserva pagou R$ 3.272,00 à Knox (2 bebedouros industriais) — a devolver.</t>
         </is>
       </c>
     </row>
@@ -67471,43 +67531,74 @@
       </c>
     </row>
     <row r="139" s="157">
-      <c r="A139" s="86" t="inlineStr">
+      <c r="A139" s="78" t="inlineStr">
+        <is>
+          <t>PC Jacobina Administradora de Cartões LTDA</t>
+        </is>
+      </c>
+      <c r="B139" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C139" s="77" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D139" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E139" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F139" s="112">
+        <f>IF(OR($E139="Recebido",$C139=""),"",MAX(0,TODAY()-$C139))</f>
+        <v/>
+      </c>
+      <c r="G139" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" s="157">
+      <c r="A140" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D139" s="115">
-        <f>SUMIF(E92:E138,"Pendente",D92:D138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" s="157">
-      <c r="A140" s="202" t="inlineStr">
+      <c r="D140" s="115">
+        <f>SUMIF(E92:E139,"Pendente",D92:D139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" s="157">
+      <c r="A141" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B140" s="159" t="n"/>
-      <c r="C140" s="159" t="n"/>
-      <c r="D140" s="159" t="n"/>
-      <c r="E140" s="159" t="n"/>
-      <c r="F140" s="159" t="n"/>
-      <c r="G140" s="160" t="n"/>
-    </row>
-    <row r="141" s="157">
-      <c r="A141" s="203">
-        <f>IF(ROUND(D139-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D139-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B141" s="159" t="n"/>
+      <c r="C141" s="159" t="n"/>
+      <c r="D141" s="159" t="n"/>
+      <c r="E141" s="159" t="n"/>
+      <c r="F141" s="159" t="n"/>
+      <c r="G141" s="160" t="n"/>
     </row>
     <row r="142" s="157">
-      <c r="A142" s="203" t="inlineStr">
+      <c r="A142" s="203">
+        <f>IF(ROUND(D140-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D140-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" s="157">
+      <c r="A143" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="143" s="157"/>
     <row r="144" s="157"/>
     <row r="145" s="157"/>
     <row r="146" s="157"/>
@@ -67577,7 +67668,7 @@
     <mergeCell ref="A141:G141"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A140:G140"/>
+    <mergeCell ref="A142:G142"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
@@ -67589,7 +67680,7 @@
     <dataValidation sqref="E11:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E92:E138" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E92:E139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -52345,15 +52345,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="45" t="n"/>
+      <c r="A6" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Vitoria Maria F Santos</t>
+        </is>
+      </c>
       <c r="C6" s="45" t="n"/>
       <c r="D6" s="46" t="n"/>
       <c r="E6" s="45" t="n"/>
       <c r="F6" s="47" t="n"/>
-      <c r="G6" s="48" t="n"/>
-      <c r="H6" s="49" t="n"/>
-      <c r="I6" s="45" t="n"/>
+      <c r="G6" s="48" t="n">
+        <v>880</v>
+      </c>
+      <c r="H6" s="49" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="I6" s="45" t="inlineStr">
+        <is>
+          <t>Aluguel da loja — outubro/2026. Depósito em dinheiro no Banco do Brasil em 01/10/2026 14:15 (doc. 013573031141511, autenticação 7.05D.31D.295.0FD.388) na conta de Vitoria M F Santos (ag. 3385-5, cc 111.641-X).</t>
+        </is>
+      </c>
       <c r="K6" s="78" t="inlineStr">
         <is>
           <t>Aluguel</t>
@@ -52365,16 +52381,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="18" t="n"/>
+      <c r="A7" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Milton Ribeiro</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F7" s="19" t="n"/>
       <c r="G7" s="19" t="n"/>
       <c r="H7" s="21" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Vendido na instalação do Purificador Everest Fit Preto (compra de 30/09/2026).</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0898</t>
+        </is>
+      </c>
       <c r="K7" s="78" t="inlineStr">
         <is>
           <t>Água, Energia e Internet</t>
@@ -52386,15 +52426,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="45" t="n"/>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="45" t="n"/>
+      <c r="A8" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Eny Cordeiro Lima Santos</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F8" s="47" t="n"/>
       <c r="G8" s="48" t="n"/>
       <c r="H8" s="49" t="n"/>
       <c r="I8" s="45" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CLI-0346</t>
+        </is>
+      </c>
       <c r="K8" s="78" t="inlineStr">
         <is>
           <t>Impostos e Taxas</t>
@@ -52406,16 +52467,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="18" t="n"/>
+      <c r="A9" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Aneilde Rios de Oliveira</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F9" s="19" t="n"/>
       <c r="G9" s="19" t="n"/>
       <c r="H9" s="21" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="18" t="n"/>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Troca na casa (Loteamento Morada Real, Caeira) — segundo purificador; o da Vivencie Turismo foi trocado em 29/09/2026.</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0040</t>
+        </is>
+      </c>
       <c r="K9" s="78" t="inlineStr">
         <is>
           <t>Tarifas Bancárias e Cartão</t>
@@ -63490,7 +63575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -63541,7 +63626,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D86</f>
+        <f>D91</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -63554,6 +63639,8 @@
       </c>
     </row>
     <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="21.95" customHeight="1" s="157">
       <c r="A9" s="201" t="inlineStr">
         <is>
@@ -65824,7 +65911,7 @@
       </c>
       <c r="E80" s="142" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F80" s="143">
@@ -65833,7 +65920,7 @@
       </c>
       <c r="G80" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (fixo mensal) — aluguel da loja, sempre no dia 1º, valor fixo de R$ 880,00. Pagamento direto à locadora (Vitória Maria F Santos), sem boleto. Categoria quando pagar: Aluguel.</t>
+          <t>Categoria: Aluguel. Pago em 01/10/2026 — depósito em dinheiro no Banco do Brasil (doc. 013573031141511) — lançado em "Out 2026" como "Vitoria Maria F Santos".</t>
         </is>
       </c>
     </row>
@@ -65934,1010 +66021,1010 @@
       </c>
     </row>
     <row r="84" s="157">
-      <c r="A84" s="86" t="inlineStr">
+      <c r="A84" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B84" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 387488 (emissão 30/09/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C84" s="81" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D84" s="83" t="n">
+        <v>633.52</v>
+      </c>
+      <c r="E84" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F84" s="113">
+        <f>IF(OR($E84="Pago",$C84=""),"",MAX(0,TODAY()-$C84))</f>
+        <v/>
+      </c>
+      <c r="G84" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879986. Linha digitável 34191.12374 87998.630302 52238.850003 9 16150000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" s="157">
+      <c r="A85" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B85" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 387488 (emissão 30/09/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C85" s="77" t="n">
+        <v>46355</v>
+      </c>
+      <c r="D85" s="79" t="n">
+        <v>633.52</v>
+      </c>
+      <c r="E85" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F85" s="112">
+        <f>IF(OR($E85="Pago",$C85=""),"",MAX(0,TODAY()-$C85))</f>
+        <v/>
+      </c>
+      <c r="G85" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879706. Linha digitável 34191.12374 87970.650302 52238.850003 9 16450000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" s="157">
+      <c r="A86" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B86" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 387488 (emissão 30/09/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C86" s="81" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D86" s="83" t="n">
+        <v>633.52</v>
+      </c>
+      <c r="E86" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F86" s="113">
+        <f>IF(OR($E86="Pago",$C86=""),"",MAX(0,TODAY()-$C86))</f>
+        <v/>
+      </c>
+      <c r="G86" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879936. Linha digitável 34191.12374 87993.680302 52238.850003 5 16750000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" s="157">
+      <c r="A87" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B87" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 387488 (emissão 30/09/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C87" s="77" t="n">
+        <v>46415</v>
+      </c>
+      <c r="D87" s="79" t="n">
+        <v>633.52</v>
+      </c>
+      <c r="E87" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F87" s="112">
+        <f>IF(OR($E87="Pago",$C87=""),"",MAX(0,TODAY()-$C87))</f>
+        <v/>
+      </c>
+      <c r="G87" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879730. Linha digitável 34191.12374 87973.050302 52238.850003 3 17050000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" s="157">
+      <c r="A88" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B88" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 387488 (emissão 30/09/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C88" s="81" t="n">
+        <v>46445</v>
+      </c>
+      <c r="D88" s="83" t="n">
+        <v>633.5</v>
+      </c>
+      <c r="E88" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F88" s="113">
+        <f>IF(OR($E88="Pago",$C88=""),"",MAX(0,TODAY()-$C88))</f>
+        <v/>
+      </c>
+      <c r="G88" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879582. Linha digitável 34191.12374 87958.200302 52238.850003 2 17350000063350. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" s="157">
+      <c r="A89" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B84" s="86" t="n"/>
-      <c r="C84" s="114" t="n"/>
-      <c r="D84" s="115">
-        <f>SUMIF(E11:E83,"Pendente",D11:D83)</f>
-        <v/>
-      </c>
-      <c r="E84" s="116" t="n"/>
-      <c r="F84" s="116" t="n"/>
-      <c r="G84" s="86" t="n"/>
-    </row>
-    <row r="85" s="157">
-      <c r="A85" s="144" t="inlineStr">
+      <c r="B89" s="86" t="n"/>
+      <c r="C89" s="114" t="n"/>
+      <c r="D89" s="115">
+        <f>SUMIF(E11:E88,"Pendente",D11:D88)</f>
+        <v/>
+      </c>
+      <c r="E89" s="116" t="n"/>
+      <c r="F89" s="116" t="n"/>
+      <c r="G89" s="86" t="n"/>
+    </row>
+    <row r="90" s="157">
+      <c r="A90" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B85" s="144" t="n"/>
-      <c r="C85" s="145" t="n"/>
-      <c r="D85" s="146">
-        <f>SUMIF(E11:E83,"Previsto",D11:D83)</f>
-        <v/>
-      </c>
-      <c r="E85" s="142" t="n"/>
-      <c r="F85" s="142" t="n"/>
-      <c r="G85" s="144" t="n"/>
-    </row>
-    <row r="86" s="157">
-      <c r="A86" s="86" t="inlineStr">
+      <c r="B90" s="144" t="n"/>
+      <c r="C90" s="145" t="n"/>
+      <c r="D90" s="146">
+        <f>SUMIF(E11:E88,"Previsto",D11:D88)</f>
+        <v/>
+      </c>
+      <c r="E90" s="142" t="n"/>
+      <c r="F90" s="142" t="n"/>
+      <c r="G90" s="144" t="n"/>
+    </row>
+    <row r="91" s="157">
+      <c r="A91" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B86" s="86" t="n"/>
-      <c r="C86" s="114" t="n"/>
-      <c r="D86" s="115">
-        <f>D84+D85</f>
-        <v/>
-      </c>
-      <c r="E86" s="116" t="n"/>
-      <c r="F86" s="116" t="n"/>
-      <c r="G86" s="86" t="n"/>
-    </row>
-    <row r="87" s="157"/>
-    <row r="88" ht="15.75" customHeight="1" s="157"/>
-    <row r="89" ht="15.75" customHeight="1" s="157">
-      <c r="A89" s="200" t="inlineStr">
+      <c r="B91" s="86" t="n"/>
+      <c r="C91" s="114" t="n"/>
+      <c r="D91" s="115">
+        <f>D89+D90</f>
+        <v/>
+      </c>
+      <c r="E91" s="116" t="n"/>
+      <c r="F91" s="116" t="n"/>
+      <c r="G91" s="86" t="n"/>
+    </row>
+    <row r="92" s="157"/>
+    <row r="93" ht="15.75" customHeight="1" s="157"/>
+    <row r="94" ht="15.75" customHeight="1" s="157">
+      <c r="A94" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="90" s="157">
-      <c r="A90" s="194" t="inlineStr">
+    <row r="95" s="157">
+      <c r="A95" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="91" s="157">
-      <c r="A91" s="111" t="inlineStr">
+    <row r="96" s="157">
+      <c r="A96" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B91" s="111" t="inlineStr">
+      <c r="B96" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C91" s="111" t="inlineStr">
+      <c r="C96" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D91" s="111" t="inlineStr">
+      <c r="D96" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E91" s="111" t="inlineStr">
+      <c r="E96" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F91" s="111" t="inlineStr">
+      <c r="F96" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G91" s="111" t="inlineStr">
+      <c r="G96" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="92" s="157">
-      <c r="A92" s="78" t="inlineStr">
+    <row r="97" s="157">
+      <c r="A97" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B92" s="78" t="inlineStr">
+      <c r="B97" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C92" s="77" t="n">
+      <c r="C97" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D92" s="79" t="n">
+      <c r="D97" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E92" s="112" t="inlineStr">
+      <c r="E97" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F92" s="112">
-        <f>IF(OR($E92="Recebido",$C92=""),"",MAX(0,TODAY()-$C92))</f>
-        <v/>
-      </c>
-      <c r="G92" s="78" t="n"/>
-    </row>
-    <row r="93" s="157">
-      <c r="A93" s="82" t="inlineStr">
+      <c r="F97" s="112">
+        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="78" t="n"/>
+    </row>
+    <row r="98" s="157">
+      <c r="A98" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B93" s="82" t="inlineStr">
+      <c r="B98" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C98" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D93" s="83" t="n">
+      <c r="D98" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E93" s="113" t="inlineStr">
+      <c r="E98" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F93" s="113">
-        <f>IF(OR($E93="Recebido",$C93=""),"",MAX(0,TODAY()-$C93))</f>
-        <v/>
-      </c>
-      <c r="G93" s="82" t="n"/>
-    </row>
-    <row r="94" s="157">
-      <c r="A94" s="78" t="inlineStr">
+      <c r="F98" s="113">
+        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="82" t="n"/>
+    </row>
+    <row r="99" s="157">
+      <c r="A99" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B94" s="78" t="inlineStr">
+      <c r="B99" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C94" s="77" t="n">
+      <c r="C99" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D94" s="79" t="n">
+      <c r="D99" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E94" s="112" t="inlineStr">
+      <c r="E99" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F94" s="112">
-        <f>IF(OR($E94="Recebido",$C94=""),"",MAX(0,TODAY()-$C94))</f>
-        <v/>
-      </c>
-      <c r="G94" s="78" t="inlineStr">
+      <c r="F99" s="112">
+        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="95" s="157">
-      <c r="A95" s="82" t="inlineStr">
+    <row r="100" s="157">
+      <c r="A100" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B100" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C100" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D95" s="83" t="n">
+      <c r="D100" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E95" s="113" t="inlineStr">
+      <c r="E100" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F95" s="113">
-        <f>IF(OR($E95="Recebido",$C95=""),"",MAX(0,TODAY()-$C95))</f>
-        <v/>
-      </c>
-      <c r="G95" s="82" t="inlineStr">
+      <c r="F100" s="113">
+        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="96" s="157">
-      <c r="A96" s="78" t="inlineStr">
+    <row r="101" s="157">
+      <c r="A101" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B96" s="78" t="inlineStr">
+      <c r="B101" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C96" s="77" t="n">
+      <c r="C101" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D96" s="79" t="n">
+      <c r="D101" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E96" s="112" t="inlineStr">
+      <c r="E101" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F96" s="112">
-        <f>IF(OR($E96="Recebido",$C96=""),"",MAX(0,TODAY()-$C96))</f>
-        <v/>
-      </c>
-      <c r="G96" s="78" t="inlineStr">
+      <c r="F101" s="112">
+        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="97" s="157">
-      <c r="A97" s="82" t="inlineStr">
+    <row r="102" s="157">
+      <c r="A102" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B102" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C97" s="81" t="n">
+      <c r="C102" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D97" s="83" t="n">
+      <c r="D102" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E97" s="113" t="inlineStr">
+      <c r="E102" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F97" s="113">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="82" t="inlineStr">
+      <c r="F102" s="113">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="98" s="157">
-      <c r="A98" s="78" t="inlineStr">
+    <row r="103" s="157">
+      <c r="A103" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B98" s="78" t="inlineStr">
+      <c r="B103" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C98" s="77" t="n">
+      <c r="C103" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D98" s="79" t="n">
+      <c r="D103" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E98" s="112" t="inlineStr">
+      <c r="E103" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F98" s="112">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="78" t="inlineStr">
+      <c r="F103" s="112">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="99" s="157">
-      <c r="A99" s="82" t="inlineStr">
+    <row r="104" s="157">
+      <c r="A104" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B104" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C99" s="81" t="n">
+      <c r="C104" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D99" s="83" t="n">
+      <c r="D104" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E99" s="113" t="inlineStr">
+      <c r="E104" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F99" s="113">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="82" t="inlineStr">
+      <c r="F104" s="113">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="100" s="157">
-      <c r="A100" s="78" t="inlineStr">
+    <row r="105" s="157">
+      <c r="A105" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B100" s="78" t="inlineStr">
+      <c r="B105" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C100" s="77" t="n">
+      <c r="C105" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D100" s="79" t="n">
+      <c r="D105" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E100" s="112" t="inlineStr">
+      <c r="E105" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F100" s="112">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="78" t="inlineStr">
+      <c r="F105" s="112">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="101" s="157">
-      <c r="A101" s="82" t="inlineStr">
+    <row r="106" s="157">
+      <c r="A106" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B101" s="82" t="inlineStr">
+      <c r="B106" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C101" s="81" t="n">
+      <c r="C106" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D101" s="83" t="n">
+      <c r="D106" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E101" s="113" t="inlineStr">
+      <c r="E106" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F101" s="113">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="82" t="inlineStr">
+      <c r="F106" s="113">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="102" s="157">
-      <c r="A102" s="78" t="inlineStr">
+    <row r="107" s="157">
+      <c r="A107" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B102" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C102" s="77" t="n">
+      <c r="C107" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D102" s="79" t="n">
+      <c r="D107" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E102" s="112" t="inlineStr">
+      <c r="E107" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F102" s="112">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="78" t="inlineStr">
+      <c r="F107" s="112">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="103" s="157">
-      <c r="A103" s="82" t="inlineStr">
+    <row r="108" s="157">
+      <c r="A108" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B103" s="82" t="inlineStr">
+      <c r="B108" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C103" s="81" t="n">
+      <c r="C108" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D103" s="83" t="n">
+      <c r="D108" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E103" s="113" t="inlineStr">
+      <c r="E108" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F103" s="113">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="82" t="inlineStr">
+      <c r="F108" s="113">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="104" s="157">
-      <c r="A104" s="78" t="inlineStr">
+    <row r="109" s="157">
+      <c r="A109" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B104" s="78" t="inlineStr">
+      <c r="B109" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C104" s="77" t="n">
+      <c r="C109" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D104" s="79" t="n">
+      <c r="D109" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E104" s="112" t="inlineStr">
+      <c r="E109" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F104" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="78" t="inlineStr">
+      <c r="F109" s="112">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="105" s="157">
-      <c r="A105" s="82" t="inlineStr">
+    <row r="110" s="157">
+      <c r="A110" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B105" s="82" t="inlineStr">
+      <c r="B110" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C105" s="81" t="n">
+      <c r="C110" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D105" s="83" t="n">
+      <c r="D110" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E105" s="113" t="inlineStr">
+      <c r="E110" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F105" s="113">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="82" t="inlineStr">
+      <c r="F110" s="113">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="106" s="157">
-      <c r="A106" s="78" t="inlineStr">
+    <row r="111" s="157">
+      <c r="A111" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B111" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C106" s="77" t="n">
+      <c r="C111" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D106" s="79" t="n">
+      <c r="D111" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E106" s="112" t="inlineStr">
+      <c r="E111" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F106" s="112">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="78" t="inlineStr">
+      <c r="F111" s="112">
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="107" s="157">
-      <c r="A107" s="82" t="inlineStr">
+    <row r="112" s="157">
+      <c r="A112" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B107" s="82" t="inlineStr">
+      <c r="B112" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C107" s="81" t="n">
+      <c r="C112" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D107" s="83" t="n">
+      <c r="D112" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E107" s="113" t="inlineStr">
+      <c r="E112" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F107" s="113">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="82" t="inlineStr">
+      <c r="F112" s="113">
+        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
+        <v/>
+      </c>
+      <c r="G112" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="108" s="157">
-      <c r="A108" s="78" t="inlineStr">
+    <row r="113" s="157">
+      <c r="A113" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B108" s="78" t="inlineStr">
+      <c r="B113" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C108" s="77" t="n">
+      <c r="C113" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D108" s="79" t="n">
+      <c r="D113" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E108" s="112" t="inlineStr">
+      <c r="E113" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="112">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="78" t="inlineStr">
+      <c r="F113" s="112">
+        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="109" s="157">
-      <c r="A109" s="82" t="inlineStr">
+    <row r="114" s="157">
+      <c r="A114" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B109" s="82" t="inlineStr">
+      <c r="B114" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C109" s="81" t="n">
+      <c r="C114" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D109" s="83" t="n">
+      <c r="D114" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E109" s="113" t="inlineStr">
+      <c r="E114" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F109" s="113">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="82" t="inlineStr">
+      <c r="F114" s="113">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="110" s="157">
-      <c r="A110" s="78" t="inlineStr">
+    <row r="115" s="157">
+      <c r="A115" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B110" s="78" t="inlineStr">
+      <c r="B115" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C110" s="77" t="n">
+      <c r="C115" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D110" s="79" t="n">
+      <c r="D115" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E110" s="112" t="inlineStr">
+      <c r="E115" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F110" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="78" t="inlineStr">
+      <c r="F115" s="112">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="111" s="157">
-      <c r="A111" s="82" t="inlineStr">
+    <row r="116" s="157">
+      <c r="A116" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B111" s="82" t="inlineStr">
+      <c r="B116" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C111" s="81" t="n">
+      <c r="C116" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D111" s="83" t="n">
+      <c r="D116" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E111" s="113" t="inlineStr">
+      <c r="E116" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="113">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="82" t="inlineStr">
+      <c r="F116" s="113">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="112" s="157">
-      <c r="A112" s="78" t="inlineStr">
+    <row r="117" s="157">
+      <c r="A117" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B112" s="78" t="inlineStr">
+      <c r="B117" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C112" s="77" t="n">
+      <c r="C117" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D112" s="79" t="n">
+      <c r="D117" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E112" s="112" t="inlineStr">
+      <c r="E117" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F112" s="112">
-        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="78" t="inlineStr">
+      <c r="F117" s="112">
+        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="113" s="157">
-      <c r="A113" s="82" t="inlineStr">
+    <row r="118" s="157">
+      <c r="A118" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B113" s="82" t="inlineStr">
+      <c r="B118" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C113" s="81" t="n">
+      <c r="C118" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D113" s="83" t="n">
+      <c r="D118" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E113" s="113" t="inlineStr">
+      <c r="E118" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F113" s="113">
-        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="82" t="inlineStr">
+      <c r="F118" s="113">
+        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
-    <row r="114" s="157">
-      <c r="A114" s="78" t="inlineStr">
+    <row r="119" s="157">
+      <c r="A119" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B114" s="78" t="inlineStr">
+      <c r="B119" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C114" s="77" t="n">
+      <c r="C119" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D114" s="79" t="n">
+      <c r="D119" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E114" s="112" t="inlineStr">
+      <c r="E119" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F114" s="112">
-        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="78" t="inlineStr">
+      <c r="F119" s="112">
+        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" s="157">
-      <c r="A115" s="82" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="B115" s="82" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C115" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D115" s="83" t="n">
-        <v>160</v>
-      </c>
-      <c r="E115" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F115" s="113">
-        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" s="157">
-      <c r="A116" s="78" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B116" s="78" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C116" s="77" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D116" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="E116" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F116" s="112">
-        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" s="157">
-      <c r="A117" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B117" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C117" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D117" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E117" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F117" s="113">
-        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
-        <v/>
-      </c>
-      <c r="G117" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" s="157">
-      <c r="A118" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B118" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C118" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D118" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E118" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F118" s="112">
-        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
-        <v/>
-      </c>
-      <c r="G118" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" s="157">
-      <c r="A119" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B119" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C119" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D119" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E119" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F119" s="113">
-        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
-        <v/>
-      </c>
-      <c r="G119" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="120" s="157">
       <c r="A120" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>Instituto Paulo Leão</t>
         </is>
       </c>
       <c r="B120" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
       <c r="C120" s="81" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D120" s="83" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="E120" s="113" t="inlineStr">
         <is>
@@ -66950,26 +67037,26 @@
       </c>
       <c r="G120" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="121" s="157">
       <c r="A121" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
       <c r="B121" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="C121" s="77" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D121" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E121" s="112" t="inlineStr">
         <is>
@@ -66982,58 +67069,58 @@
       </c>
       <c r="G121" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="122" s="157">
-      <c r="A122" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B122" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C122" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D122" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E122" s="112" t="inlineStr">
+      <c r="A122" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B122" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C122" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D122" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E122" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F122" s="112">
+      <c r="F122" s="113">
         <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
         <v/>
       </c>
-      <c r="G122" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+      <c r="G122" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="123" s="157">
       <c r="A123" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B123" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C123" s="77" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="D123" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E123" s="112" t="inlineStr">
         <is>
@@ -67051,85 +67138,85 @@
       </c>
     </row>
     <row r="124" s="157">
-      <c r="A124" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B124" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C124" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D124" s="79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E124" s="112" t="inlineStr">
+      <c r="A124" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B124" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C124" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D124" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E124" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F124" s="112">
+      <c r="F124" s="113">
         <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
         <v/>
       </c>
-      <c r="G124" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+      <c r="G124" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="125" s="157">
-      <c r="A125" s="78" t="inlineStr">
-        <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
-        </is>
-      </c>
-      <c r="B125" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C125" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D125" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E125" s="112" t="inlineStr">
+      <c r="A125" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B125" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C125" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D125" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E125" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F125" s="112">
+      <c r="F125" s="113">
         <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
         <v/>
       </c>
-      <c r="G125" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+      <c r="G125" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="126" s="157">
       <c r="A126" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B126" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C126" s="77" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="D126" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E126" s="112" t="inlineStr">
         <is>
@@ -67142,30 +67229,30 @@
       </c>
       <c r="G126" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="127" s="157">
       <c r="A127" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B127" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C127" s="77" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="D127" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E127" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F127" s="112">
@@ -67174,23 +67261,23 @@
       </c>
       <c r="G127" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="128" s="157">
       <c r="A128" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B128" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C128" s="77" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D128" s="79" t="n">
         <v>140</v>
@@ -67206,26 +67293,26 @@
       </c>
       <c r="G128" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="129" s="157">
       <c r="A129" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B129" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C129" s="77" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D129" s="79" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E129" s="112" t="inlineStr">
         <is>
@@ -67238,26 +67325,26 @@
       </c>
       <c r="G129" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="130" s="157">
       <c r="A130" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B130" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C130" s="77" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D130" s="79" t="n">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E130" s="112" t="inlineStr">
         <is>
@@ -67270,14 +67357,14 @@
       </c>
       <c r="G130" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="131" s="157">
       <c r="A131" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B131" s="78" t="inlineStr">
@@ -67286,7 +67373,7 @@
         </is>
       </c>
       <c r="C131" s="77" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="D131" s="79" t="n">
         <v>200</v>
@@ -67302,30 +67389,30 @@
       </c>
       <c r="G131" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="132" s="157">
       <c r="A132" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B132" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C132" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D132" s="79" t="n">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="E132" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F132" s="112">
@@ -67334,14 +67421,14 @@
       </c>
       <c r="G132" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="133" s="157">
       <c r="A133" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B133" s="78" t="inlineStr">
@@ -67350,7 +67437,7 @@
         </is>
       </c>
       <c r="C133" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D133" s="79" t="n">
         <v>140</v>
@@ -67366,30 +67453,30 @@
       </c>
       <c r="G133" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="134" s="157">
       <c r="A134" s="78" t="inlineStr">
         <is>
-          <t>Centro de Especialidades Odontomédicas</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B134" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C134" s="77" t="n">
-        <v>46044</v>
+        <v>46279</v>
       </c>
       <c r="D134" s="79" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="E134" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F134" s="112">
@@ -67398,30 +67485,30 @@
       </c>
       <c r="G134" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="135" s="157">
       <c r="A135" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B135" s="78" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C135" s="77" t="n">
-        <v>46073</v>
+        <v>46281</v>
       </c>
       <c r="D135" s="79" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="E135" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F135" s="112">
@@ -67430,30 +67517,30 @@
       </c>
       <c r="G135" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="136" s="157">
       <c r="A136" s="78" t="inlineStr">
         <is>
-          <t>Centro Médico de Jacobina</t>
+          <t>Marilda Macedo / José Luciano Costa</t>
         </is>
       </c>
       <c r="B136" s="78" t="inlineStr">
         <is>
-          <t>2x Botão Completo</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C136" s="77" t="n">
-        <v>46203</v>
+        <v>46283</v>
       </c>
       <c r="D136" s="79" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F136" s="112">
@@ -67462,14 +67549,14 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="137" s="157">
       <c r="A137" s="78" t="inlineStr">
         <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+          <t>Tatiana Rocha</t>
         </is>
       </c>
       <c r="B137" s="78" t="inlineStr">
@@ -67478,14 +67565,14 @@
         </is>
       </c>
       <c r="C137" s="77" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="D137" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E137" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F137" s="112">
@@ -67494,30 +67581,30 @@
       </c>
       <c r="G137" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="138" s="157">
       <c r="A138" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="B138" s="78" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C138" s="77" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="D138" s="79" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E138" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F138" s="112">
@@ -67526,26 +67613,26 @@
       </c>
       <c r="G138" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="139" s="157">
       <c r="A139" s="78" t="inlineStr">
         <is>
-          <t>PC Jacobina Administradora de Cartões LTDA</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B139" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="C139" s="77" t="n">
-        <v>46295</v>
+        <v>46044</v>
       </c>
       <c r="D139" s="79" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E139" s="112" t="inlineStr">
         <is>
@@ -67558,53 +67645,239 @@
       </c>
       <c r="G139" s="78" t="inlineStr">
         <is>
+          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" s="157">
+      <c r="A140" s="78" t="inlineStr">
+        <is>
+          <t>Igreja Messiânica Mundial do Brasil</t>
+        </is>
+      </c>
+      <c r="B140" s="78" t="inlineStr">
+        <is>
+          <t>Mangueira</t>
+        </is>
+      </c>
+      <c r="C140" s="77" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D140" s="79" t="n">
+        <v>30</v>
+      </c>
+      <c r="E140" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F140" s="112">
+        <f>IF(OR($E140="Recebido",$C140=""),"",MAX(0,TODAY()-$C140))</f>
+        <v/>
+      </c>
+      <c r="G140" s="78" t="inlineStr">
+        <is>
+          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" s="157">
+      <c r="A141" s="78" t="inlineStr">
+        <is>
+          <t>Centro Médico de Jacobina</t>
+        </is>
+      </c>
+      <c r="B141" s="78" t="inlineStr">
+        <is>
+          <t>2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="C141" s="77" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D141" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E141" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F141" s="112">
+        <f>IF(OR($E141="Recebido",$C141=""),"",MAX(0,TODAY()-$C141))</f>
+        <v/>
+      </c>
+      <c r="G141" s="78" t="inlineStr">
+        <is>
+          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" s="157">
+      <c r="A142" s="78" t="inlineStr">
+        <is>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+        </is>
+      </c>
+      <c r="B142" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C142" s="77" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D142" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E142" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F142" s="112">
+        <f>IF(OR($E142="Recebido",$C142=""),"",MAX(0,TODAY()-$C142))</f>
+        <v/>
+      </c>
+      <c r="G142" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 29/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" s="157">
+      <c r="A143" s="78" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="B143" s="78" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
+      <c r="C143" s="77" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D143" s="79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E143" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F143" s="112">
+        <f>IF(OR($E143="Recebido",$C143=""),"",MAX(0,TODAY()-$C143))</f>
+        <v/>
+      </c>
+      <c r="G143" s="78" t="inlineStr">
+        <is>
+          <t>Pagamento previsto para 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" s="157">
+      <c r="A144" s="78" t="inlineStr">
+        <is>
+          <t>PC Jacobina Administradora de Cartões LTDA</t>
+        </is>
+      </c>
+      <c r="B144" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C144" s="77" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D144" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E144" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F144" s="112">
+        <f>IF(OR($E144="Recebido",$C144=""),"",MAX(0,TODAY()-$C144))</f>
+        <v/>
+      </c>
+      <c r="G144" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 30/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="140" s="157">
-      <c r="A140" s="86" t="inlineStr">
+    <row r="145" s="157">
+      <c r="A145" s="78" t="inlineStr">
+        <is>
+          <t>Aneilde Rios de Oliveira</t>
+        </is>
+      </c>
+      <c r="B145" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C145" s="77" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D145" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E145" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F145" s="112">
+        <f>IF(OR($E145="Recebido",$C145=""),"",MAX(0,TODAY()-$C145))</f>
+        <v/>
+      </c>
+      <c r="G145" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 01/10/2026 (casa, Caeira).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" s="157">
+      <c r="A146" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D140" s="115">
-        <f>SUMIF(E92:E139,"Pendente",D92:D139)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" s="157">
-      <c r="A141" s="202" t="inlineStr">
+      <c r="D146" s="115">
+        <f>SUMIF(E97:E145,"Pendente",D97:D145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" s="157">
+      <c r="A147" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B141" s="159" t="n"/>
-      <c r="C141" s="159" t="n"/>
-      <c r="D141" s="159" t="n"/>
-      <c r="E141" s="159" t="n"/>
-      <c r="F141" s="159" t="n"/>
-      <c r="G141" s="160" t="n"/>
-    </row>
-    <row r="142" s="157">
-      <c r="A142" s="203">
-        <f>IF(ROUND(D140-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D140-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" s="157">
-      <c r="A143" s="203" t="inlineStr">
+      <c r="B147" s="159" t="n"/>
+      <c r="C147" s="159" t="n"/>
+      <c r="D147" s="159" t="n"/>
+      <c r="E147" s="159" t="n"/>
+      <c r="F147" s="159" t="n"/>
+      <c r="G147" s="160" t="n"/>
+    </row>
+    <row r="148" s="157">
+      <c r="A148" s="203">
+        <f>IF(ROUND(D146-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D146-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" s="157">
+      <c r="A149" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="144" s="157"/>
-    <row r="145" s="157"/>
-    <row r="146" s="157"/>
-    <row r="147" s="157"/>
-    <row r="148" s="157"/>
-    <row r="149" s="157"/>
     <row r="150" s="157"/>
     <row r="151" s="157"/>
     <row r="152" s="157"/>
@@ -67664,23 +67937,23 @@
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A141:G141"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A142:G142"/>
+    <mergeCell ref="A148:G148"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A147:G147"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E92:E139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E97:E145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -52512,15 +52512,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="45" t="n"/>
+      <c r="A10" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C10" s="45" t="n"/>
       <c r="D10" s="46" t="n"/>
       <c r="E10" s="45" t="n"/>
       <c r="F10" s="47" t="n"/>
-      <c r="G10" s="48" t="n"/>
-      <c r="H10" s="49" t="n"/>
-      <c r="I10" s="45" t="n"/>
+      <c r="G10" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I10" s="45" t="inlineStr">
+        <is>
+          <t>Etanol 4,51 L — Posto de Combustíveis Modelo, NFC-e nº 000431786 de 01/10/2026 10:56 (nota de R$ 20,07). Pago R$ 20,00 em dinheiro (uma nota de R$ 20).</t>
+        </is>
+      </c>
       <c r="K10" s="78" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
@@ -52532,11 +52548,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="18" t="n"/>
+      <c r="A11" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
       <c r="C11" s="18" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="18" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F11" s="19" t="n"/>
       <c r="G11" s="19" t="n"/>
       <c r="H11" s="21" t="n"/>
@@ -52553,15 +52581,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="45" t="n"/>
+      <c r="A12" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F12" s="47" t="n"/>
       <c r="G12" s="48" t="n"/>
       <c r="H12" s="49" t="n"/>
-      <c r="I12" s="45" t="n"/>
+      <c r="I12" s="45" t="inlineStr">
+        <is>
+          <t>Subsolo — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada).</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>EMP-0062</t>
+        </is>
+      </c>
       <c r="K12" s="78" t="inlineStr">
         <is>
           <t>Contabilidade</t>
@@ -52573,15 +52626,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="18" t="n"/>
+      <c r="A13" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Cliente de Armando</t>
+        </is>
+      </c>
       <c r="C13" s="18" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="19" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>1486</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>207.89</v>
+      </c>
       <c r="G13" s="19" t="n"/>
       <c r="H13" s="21" t="n"/>
-      <c r="I13" s="18" t="n"/>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
       <c r="J13" s="18" t="n"/>
       <c r="K13" s="78" t="inlineStr">
         <is>
@@ -52594,11 +52665,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="45" t="n"/>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="45" t="n"/>
+      <c r="A14" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>6x Torneira Acquazurra</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F14" s="47" t="n"/>
       <c r="G14" s="48" t="n"/>
       <c r="H14" s="49" t="n"/>
@@ -52614,11 +52701,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="18" t="n"/>
+      <c r="A15" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Refil Top Color Fast</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F15" s="19" t="n"/>
       <c r="G15" s="19" t="n"/>
       <c r="H15" s="21" t="n"/>
@@ -52635,15 +52738,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="n"/>
-      <c r="B16" s="45" t="n"/>
+      <c r="A16" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Patrus Transportes</t>
+        </is>
+      </c>
       <c r="C16" s="45" t="n"/>
       <c r="D16" s="46" t="n"/>
       <c r="E16" s="45" t="n"/>
       <c r="F16" s="47" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="49" t="n"/>
-      <c r="I16" s="45" t="n"/>
+      <c r="G16" s="48" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I16" s="45" t="inlineStr">
+        <is>
+          <t>Frete da fatura 26-09-904996 (CT-e 2123999, remetente Everest, NF 386188) — venc. 02/10/2026. Pago em 01/10/2026.</t>
+        </is>
+      </c>
       <c r="K16" s="78" t="inlineStr">
         <is>
           <t>Outras Despesas</t>
@@ -52655,15 +52774,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="18" t="n"/>
+      <c r="A17" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Salário Wiliam</t>
+        </is>
+      </c>
       <c r="C17" s="18" t="n"/>
       <c r="D17" s="27" t="n"/>
       <c r="E17" s="18" t="n"/>
       <c r="F17" s="19" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="18" t="n"/>
+      <c r="G17" s="19" t="n">
+        <v>1571.32</v>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Salário mensal — competência setembro/2026. Pago em 01/10/2026.</t>
+        </is>
+      </c>
       <c r="J17" s="18" t="n"/>
       <c r="K17" s="84" t="inlineStr">
         <is>
@@ -63575,7 +63710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -63639,8 +63774,6 @@
       </c>
     </row>
     <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9" ht="21.95" customHeight="1" s="157">
       <c r="A9" s="201" t="inlineStr">
         <is>
@@ -65271,7 +65404,7 @@
       </c>
       <c r="E60" s="142" t="inlineStr">
         <is>
-          <t>Previsto</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F60" s="143">
@@ -65280,7 +65413,7 @@
       </c>
       <c r="G60" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (fixo mensal) — despesa recorrente que NUNCA tem boleto: é pagamento direto ao funcionário. Salário mensal do Wiliam, valor fixo de R$ 1.571,32 (mesmo valor de mai, jun e ago/2026). É pago no último dia do mês anterior; o vencimento fica no dia 1º só para padronizar. NÃO inclui as comissões, que saem à parte por quinzena e variam (R$ 150 a R$ 590 nas últimas). Categoria quando pagar: Salários, Comissões e Encargos.</t>
+          <t>Categoria: Salários, Comissões e Encargos. Pago em 01/10/2026 — lançado em "Out 2026" como "Salário Wiliam" (R$ 1.571,32).</t>
         </is>
       </c>
     </row>
@@ -65719,7 +65852,7 @@
       </c>
       <c r="E74" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F74" s="113">
@@ -65728,7 +65861,7 @@
       </c>
       <c r="G74" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840000190-0, agência/cedente 1430-0/0030737-8. Linha digitável 23791.43007 93484.000018 90003.073708 7 15870000032345. Emissão 17/09/2026. Após o vencimento: R$ 0,49 por dia de atraso; negativação a partir do 7º dia.</t>
+          <t>Categoria: Transporte e Entregas. Boleto Bradesco 237-2, nosso número 34840000190-0. Pago em 01/10/2026 (antecipado, venc. 02/10) — lançado em "Out 2026" como "Patrus Transportes".</t>
         </is>
       </c>
     </row>
@@ -67842,43 +67975,74 @@
       </c>
     </row>
     <row r="146" s="157">
-      <c r="A146" s="86" t="inlineStr">
+      <c r="A146" s="78" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="B146" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="C146" s="77" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D146" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E146" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F146" s="112">
+        <f>IF(OR($E146="Recebido",$C146=""),"",MAX(0,TODAY()-$C146))</f>
+        <v/>
+      </c>
+      <c r="G146" s="78" t="inlineStr">
+        <is>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" s="157">
+      <c r="A147" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D146" s="115">
-        <f>SUMIF(E97:E145,"Pendente",D97:D145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" s="157">
-      <c r="A147" s="202" t="inlineStr">
+      <c r="D147" s="115">
+        <f>SUMIF(E97:E146,"Pendente",D97:D146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" s="157">
+      <c r="A148" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B147" s="159" t="n"/>
-      <c r="C147" s="159" t="n"/>
-      <c r="D147" s="159" t="n"/>
-      <c r="E147" s="159" t="n"/>
-      <c r="F147" s="159" t="n"/>
-      <c r="G147" s="160" t="n"/>
-    </row>
-    <row r="148" s="157">
-      <c r="A148" s="203">
-        <f>IF(ROUND(D146-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D146-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B148" s="159" t="n"/>
+      <c r="C148" s="159" t="n"/>
+      <c r="D148" s="159" t="n"/>
+      <c r="E148" s="159" t="n"/>
+      <c r="F148" s="159" t="n"/>
+      <c r="G148" s="160" t="n"/>
     </row>
     <row r="149" s="157">
-      <c r="A149" s="203" t="inlineStr">
+      <c r="A149" s="203">
+        <f>IF(ROUND(D147-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D147-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" s="157">
+      <c r="A150" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="150" s="157"/>
     <row r="151" s="157"/>
     <row r="152" s="157"/>
     <row r="153" s="157"/>
@@ -67940,20 +68104,20 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A94:G94"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A149:G149"/>
     <mergeCell ref="A148:G148"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A147:G147"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E97:E145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E97:E146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -52811,15 +52811,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="n"/>
-      <c r="B18" s="45" t="n"/>
+      <c r="A18" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Conta de Água Adriano</t>
+        </is>
+      </c>
       <c r="C18" s="45" t="n"/>
       <c r="D18" s="46" t="n"/>
       <c r="E18" s="45" t="n"/>
       <c r="F18" s="47" t="n"/>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="49" t="n"/>
-      <c r="I18" s="45" t="n"/>
+      <c r="G18" s="48" t="n">
+        <v>91</v>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I18" s="45" t="inlineStr">
+        <is>
+          <t>Embasa — conta pessoal do Adriano (não é da loja), ref. 10/2026, matrícula 0531718-70. Pago em 01/10/2026.</t>
+        </is>
+      </c>
       <c r="K18" s="86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -52831,16 +52847,36 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="18" t="n"/>
+      <c r="A19" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Armazém Paraíba</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Refil Carbon Tech 5"</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F19" s="19" t="n"/>
       <c r="G19" s="19" t="n"/>
       <c r="H19" s="21" t="n"/>
       <c r="I19" s="18" t="n"/>
-      <c r="J19" s="18" t="n"/>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0317</t>
+        </is>
+      </c>
       <c r="K19" s="88" t="inlineStr">
         <is>
           <t>Capital de Giro (BB) — ainda a devolver</t>
@@ -52852,84 +52888,232 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="n"/>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="45" t="n"/>
+      <c r="A20" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F20" s="47" t="n"/>
       <c r="G20" s="48" t="n"/>
       <c r="H20" s="49" t="n"/>
       <c r="I20" s="45" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="18" t="n"/>
+      <c r="A21" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Joselita Pereira de Almeida</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F21" s="19" t="n"/>
       <c r="G21" s="19" t="n"/>
       <c r="H21" s="21" t="n"/>
       <c r="I21" s="18" t="n"/>
-      <c r="J21" s="18" t="n"/>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="n"/>
-      <c r="B22" s="45" t="n"/>
-      <c r="C22" s="45" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="45" t="n"/>
-      <c r="F22" s="47" t="n"/>
+      <c r="A22" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Adryelle Lima Coelho - Nelia Marques</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E22" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>9.789999999999999</v>
+      </c>
       <c r="G22" s="48" t="n"/>
       <c r="H22" s="49" t="n"/>
-      <c r="I22" s="45" t="n"/>
+      <c r="I22" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 2x</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CLI-0290</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="19" t="n"/>
+      <c r="A23" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Ana Paula</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira + Reinstalação</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>4.75</v>
+      </c>
       <c r="G23" s="19" t="n"/>
       <c r="H23" s="21" t="n"/>
       <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="n"/>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="45" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="45" t="n"/>
-      <c r="F24" s="47" t="n"/>
+      <c r="A24" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E24" s="45" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>2.18</v>
+      </c>
       <c r="G24" s="48" t="n"/>
       <c r="H24" s="49" t="n"/>
       <c r="I24" s="45" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="18" t="n"/>
+      <c r="A25" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Valeriana Studio - Juscelia</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F25" s="19" t="n"/>
       <c r="G25" s="19" t="n"/>
       <c r="H25" s="21" t="n"/>
       <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0318</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="n"/>
-      <c r="B26" s="45" t="n"/>
-      <c r="C26" s="45" t="n"/>
-      <c r="D26" s="46" t="n"/>
-      <c r="E26" s="45" t="n"/>
+      <c r="A26" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F26" s="47" t="n"/>
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
-      <c r="I26" s="45" t="n"/>
+      <c r="I26" s="45" t="inlineStr">
+        <is>
+          <t>1º Andar — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada).</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>EMP-0062</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -63710,7 +63894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -65308,7 +65492,7 @@
       </c>
       <c r="E57" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F57" s="112">
@@ -65317,7 +65501,7 @@
       </c>
       <c r="G57" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Pro Labore Edilânia. Fatura em nome pessoal do sócio, matrícula 0531718-70. Pagável via Pix no QR Code da conta.</t>
+          <t>Categoria: Pro Labore Edilânia. Pago em 01/10/2026 — lançado em Out 2026 como "Conta de Água Adriano". Fatura em nome pessoal do sócio, matrícula 0531718-70.</t>
         </is>
       </c>
     </row>
@@ -68007,43 +68191,74 @@
       </c>
     </row>
     <row r="147" s="157">
-      <c r="A147" s="86" t="inlineStr">
+      <c r="A147" s="78" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="B147" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="C147" s="77" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D147" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E147" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F147" s="112">
+        <f>IF(OR($E147="Recebido",$C147=""),"",MAX(0,TODAY()-$C147))</f>
+        <v/>
+      </c>
+      <c r="G147" s="78" t="inlineStr">
+        <is>
+          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" s="157">
+      <c r="A148" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D147" s="115">
-        <f>SUMIF(E97:E146,"Pendente",D97:D146)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" s="157">
-      <c r="A148" s="202" t="inlineStr">
+      <c r="D148" s="115">
+        <f>SUMIF(E97:E147,"Pendente",D97:D147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" s="157">
+      <c r="A149" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B148" s="159" t="n"/>
-      <c r="C148" s="159" t="n"/>
-      <c r="D148" s="159" t="n"/>
-      <c r="E148" s="159" t="n"/>
-      <c r="F148" s="159" t="n"/>
-      <c r="G148" s="160" t="n"/>
-    </row>
-    <row r="149" s="157">
-      <c r="A149" s="203">
-        <f>IF(ROUND(D147-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D147-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B149" s="159" t="n"/>
+      <c r="C149" s="159" t="n"/>
+      <c r="D149" s="159" t="n"/>
+      <c r="E149" s="159" t="n"/>
+      <c r="F149" s="159" t="n"/>
+      <c r="G149" s="160" t="n"/>
     </row>
     <row r="150" s="157">
-      <c r="A150" s="203" t="inlineStr">
+      <c r="A150" s="203">
+        <f>IF(ROUND(D148-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D148-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" s="157">
+      <c r="A151" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="151" s="157"/>
     <row r="152" s="157"/>
     <row r="153" s="157"/>
     <row r="154" s="157"/>
@@ -68105,7 +68320,7 @@
     <mergeCell ref="A94:G94"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A149:G149"/>
-    <mergeCell ref="A148:G148"/>
+    <mergeCell ref="A150:G150"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
@@ -68117,7 +68332,7 @@
     <dataValidation sqref="E11:E88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E97:E146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E97:E147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -52990,7 +52990,7 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Ana Paula</t>
+          <t>Ana Paula Barbosa Rodrigues</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -53116,27 +53116,59 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="18" t="n"/>
+      <c r="A27" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="27" t="n"/>
       <c r="E27" s="18" t="n"/>
       <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="18" t="n"/>
+      <c r="G27" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>Etanol 4,39 L — Tropical Combustíveis e Lubrificantes, NFC-e nº 000004328 de 02/10/2026 14:41 (nota de R$ 19,97 + R$ 0,03 de acréscimo). Pago R$ 20,00 em dinheiro.</t>
+        </is>
+      </c>
       <c r="J27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="44" t="n"/>
-      <c r="B28" s="45" t="n"/>
+      <c r="A28" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C28" s="45" t="n"/>
       <c r="D28" s="46" t="n"/>
       <c r="E28" s="45" t="n"/>
       <c r="F28" s="47" t="n"/>
-      <c r="G28" s="48" t="n"/>
-      <c r="H28" s="49" t="n"/>
-      <c r="I28" s="45" t="n"/>
+      <c r="G28" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I28" s="45" t="inlineStr">
+        <is>
+          <t>Etanol — Tropical Combustíveis e Lubrificantes (segundo abastecimento do dia).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51394,7 +51394,7 @@
       </c>
       <c r="I223" s="18" t="inlineStr">
         <is>
-          <t>R$ 20,00 tirados da segunda gaveta do caixa. Pago em dinheiro.</t>
+          <t>Posto Beira Rio (Transvale Derivados de Petróleo LTDA, CNPJ 11.271.229/0002-68, Av. Orlando Oliveira Pires, 1164, Centro, Jacobina). R$ 20,00 tirados da segunda gaveta do caixa. Pago em dinheiro.</t>
         </is>
       </c>
       <c r="J223" s="18" t="n"/>
@@ -53166,20 +53166,36 @@
       </c>
       <c r="I28" s="45" t="inlineStr">
         <is>
-          <t>Etanol — Tropical Combustíveis e Lubrificantes (segundo abastecimento do dia).</t>
+          <t>Etanol — Posto da Praça (Lubrinessa XVI Comércio de Petróleo LTDA, CNPJ 29.922.765/0002-41, Rua Dois de Julho, 70, Centro, Jacobina). Segundo abastecimento do dia.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="18" t="n"/>
+      <c r="A29" s="17" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="27" t="n"/>
       <c r="E29" s="18" t="n"/>
       <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="18" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>465</v>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Pagamento de comissão em 03/10/2026.</t>
+        </is>
+      </c>
       <c r="J29" s="18" t="n"/>
     </row>
     <row r="30">
@@ -63926,7 +63942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -63977,7 +63993,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D91</f>
+        <f>D95</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -64669,7 +64685,7 @@
       </c>
       <c r="G30" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 72869 (emissão 07/05/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260508782043000188550060000728691612874239.</t>
         </is>
       </c>
     </row>
@@ -64701,7 +64717,7 @@
       </c>
       <c r="G31" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
         </is>
       </c>
     </row>
@@ -64733,7 +64749,7 @@
       </c>
       <c r="G32" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
         </is>
       </c>
     </row>
@@ -64765,7 +64781,7 @@
       </c>
       <c r="G33" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604663-9. Linha digitável 34191.12333 60466.390303 55679.010003 1 16100000094006. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604663-9. Linha digitável 34191.12333 60466.390303 55679.010003 1 16100000094006. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -64797,7 +64813,7 @@
       </c>
       <c r="G34" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142177-8. Linha digitável 34191.12242 14217.780304 55679.010003 4 16230000087893. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142177-8. Linha digitável 34191.12242 14217.780304 55679.010003 4 16230000087893. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
         </is>
       </c>
     </row>
@@ -64989,7 +65005,7 @@
       </c>
       <c r="G40" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
         </is>
       </c>
     </row>
@@ -65021,7 +65037,7 @@
       </c>
       <c r="G41" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377737 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 725,16 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777371117471168.</t>
         </is>
       </c>
     </row>
@@ -65053,7 +65069,7 @@
       </c>
       <c r="G42" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377738 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.327,52 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777381143358478.</t>
         </is>
       </c>
     </row>
@@ -65085,7 +65101,7 @@
       </c>
       <c r="G43" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377739 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.281,74 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777391313049192.</t>
         </is>
       </c>
     </row>
@@ -65117,7 +65133,7 @@
       </c>
       <c r="G44" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249.</t>
         </is>
       </c>
     </row>
@@ -65149,7 +65165,7 @@
       </c>
       <c r="G45" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
         </is>
       </c>
     </row>
@@ -65181,7 +65197,7 @@
       </c>
       <c r="G46" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
         </is>
       </c>
     </row>
@@ -65213,7 +65229,7 @@
       </c>
       <c r="G47" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249.</t>
         </is>
       </c>
     </row>
@@ -65245,7 +65261,7 @@
       </c>
       <c r="G48" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -65277,7 +65293,7 @@
       </c>
       <c r="G49" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
         </is>
       </c>
     </row>
@@ -65309,7 +65325,7 @@
       </c>
       <c r="G50" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
         </is>
       </c>
     </row>
@@ -65341,7 +65357,7 @@
       </c>
       <c r="G51" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -65373,7 +65389,7 @@
       </c>
       <c r="G52" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar.</t>
+          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -65565,7 +65581,7 @@
       </c>
       <c r="G58" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
         </is>
       </c>
     </row>
@@ -65597,7 +65613,7 @@
       </c>
       <c r="G59" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
         </is>
       </c>
     </row>
@@ -65693,7 +65709,7 @@
       </c>
       <c r="G62" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -65725,7 +65741,7 @@
       </c>
       <c r="G63" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842013. Linha digitável 34191.12358 84201.340308 52238.850003 8 16300000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842013. Linha digitável 34191.12358 84201.340308 52238.850003 8 16300000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -65757,7 +65773,7 @@
       </c>
       <c r="G64" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841927. Linha digitável 34191.12358 84192.760308 52238.850003 8 16600000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841927. Linha digitável 34191.12358 84192.760308 52238.850003 8 16600000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -65789,7 +65805,7 @@
       </c>
       <c r="G65" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842031. Linha digitável 34191.12358 84203.160308 52238.850003 1 16900000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842031. Linha digitável 34191.12358 84203.160308 52238.850003 1 16900000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -65821,7 +65837,7 @@
       </c>
       <c r="G66" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842128. Linha digitável 34191.12358 84212.800308 52238.850003 3 17200000057428. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842128. Linha digitável 34191.12358 84212.800308 52238.850003 3 17200000057428. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -65981,7 +65997,7 @@
       </c>
       <c r="G71" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -66013,7 +66029,7 @@
       </c>
       <c r="G72" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259100-4. Linha digitável 34191.09008 25910.041430 81531.550002 2 16150000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259100-4. Linha digitável 34191.09008 25910.041430 81531.550002 2 16150000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -66045,7 +66061,7 @@
       </c>
       <c r="G73" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259101-2. Linha digitável 34191.09008 25910.121430 81531.550002 2 16360000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259101-2. Linha digitável 34191.09008 25910.121430 81531.550002 2 16360000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -66109,7 +66125,7 @@
       </c>
       <c r="G75" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -66141,7 +66157,7 @@
       </c>
       <c r="G76" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910775. Linha digitável 34191.12366 91077.530300 52238.850003 6 16380000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910775. Linha digitável 34191.12366 91077.530300 52238.850003 6 16380000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66189,7 @@
       </c>
       <c r="G77" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910730. Linha digitável 34191.12366 91073.080300 52238.850003 7 16680000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910730. Linha digitável 34191.12366 91073.080300 52238.850003 7 16680000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -66205,7 +66221,7 @@
       </c>
       <c r="G78" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910821. Linha digitável 34191.12366 91082.150300 52238.850003 9 16980000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910821. Linha digitável 34191.12366 91082.150300 52238.850003 9 16980000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -66237,7 +66253,7 @@
       </c>
       <c r="G79" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910791. Linha digitável 34191.12366 91079.100300 52238.850003 7 17280000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910791. Linha digitável 34191.12366 91079.100300 52238.850003 7 17280000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -66530,306 +66546,306 @@
       </c>
     </row>
     <row r="89" s="157">
-      <c r="A89" s="86" t="inlineStr">
+      <c r="A89" s="78" t="inlineStr">
+        <is>
+          <t>Patrus Transportes Ltda</t>
+        </is>
+      </c>
+      <c r="B89" s="78" t="inlineStr">
+        <is>
+          <t>Frete — boleto Bradesco</t>
+        </is>
+      </c>
+      <c r="C89" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D89" s="79" t="n">
+        <v>277.48</v>
+      </c>
+      <c r="E89" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F89" s="112">
+        <f>IF(OR($E89="Pago",$C89=""),"",MAX(0,TODAY()-$C89))</f>
+        <v/>
+      </c>
+      <c r="G89" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2. Linha digitável 23791.43007 93484.000265 98003.073701 2 16010000027748.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="157">
+      <c r="A90" s="82" t="inlineStr">
+        <is>
+          <t>Tarcisio Oliveira Lima</t>
+        </is>
+      </c>
+      <c r="B90" s="82" t="inlineStr">
+        <is>
+          <t>Boleto Banco do Brasil — serviço contábil</t>
+        </is>
+      </c>
+      <c r="C90" s="81" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D90" s="83" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="E90" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F90" s="113">
+        <f>IF(OR($E90="Pago",$C90=""),"",MAX(0,TODAY()-$C90))</f>
+        <v/>
+      </c>
+      <c r="G90" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Contabilidade. Boleto Banco do Brasil 001-9. Linha digitável 00190.00009 03128.364001 00003.179173 8 16000000048632.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" s="157">
+      <c r="A91" s="78" t="inlineStr">
+        <is>
+          <t>FGTS Digital (GFD)</t>
+        </is>
+      </c>
+      <c r="B91" s="78" t="inlineStr">
+        <is>
+          <t>FGTS mensal — competência 09/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D91" s="79" t="n">
+        <v>136</v>
+      </c>
+      <c r="E91" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F91" s="112">
+        <f>IF(OR($E91="Pago",$C91=""),"",MAX(0,TODAY()-$C91))</f>
+        <v/>
+      </c>
+      <c r="G91" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Pagamento via QR Code Pix no documento original da guia (GFD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" s="157">
+      <c r="A92" s="82" t="inlineStr">
+        <is>
+          <t>Receita Federal</t>
+        </is>
+      </c>
+      <c r="B92" s="82" t="inlineStr">
+        <is>
+          <t>DARF / INSS — período de apuração setembro/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="81" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D92" s="83" t="n">
+        <v>306.99</v>
+      </c>
+      <c r="E92" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F92" s="113">
+        <f>IF(OR($E92="Pago",$C92=""),"",MAX(0,TODAY()-$C92))</f>
+        <v/>
+      </c>
+      <c r="G92" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Código de barras 858300000033 069903852621 930716262672 196301377104.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" s="157">
+      <c r="A93" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B89" s="86" t="n"/>
-      <c r="C89" s="114" t="n"/>
-      <c r="D89" s="115">
-        <f>SUMIF(E11:E88,"Pendente",D11:D88)</f>
-        <v/>
-      </c>
-      <c r="E89" s="116" t="n"/>
-      <c r="F89" s="116" t="n"/>
-      <c r="G89" s="86" t="n"/>
-    </row>
-    <row r="90" s="157">
-      <c r="A90" s="144" t="inlineStr">
+      <c r="B93" s="86" t="n"/>
+      <c r="C93" s="114" t="n"/>
+      <c r="D93" s="115">
+        <f>SUMIF(E11:E92,"Pendente",D11:D92)</f>
+        <v/>
+      </c>
+      <c r="E93" s="116" t="n"/>
+      <c r="F93" s="116" t="n"/>
+      <c r="G93" s="86" t="n"/>
+    </row>
+    <row r="94" s="157">
+      <c r="A94" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B90" s="144" t="n"/>
-      <c r="C90" s="145" t="n"/>
-      <c r="D90" s="146">
-        <f>SUMIF(E11:E88,"Previsto",D11:D88)</f>
-        <v/>
-      </c>
-      <c r="E90" s="142" t="n"/>
-      <c r="F90" s="142" t="n"/>
-      <c r="G90" s="144" t="n"/>
-    </row>
-    <row r="91" s="157">
-      <c r="A91" s="86" t="inlineStr">
+      <c r="B94" s="144" t="n"/>
+      <c r="C94" s="145" t="n"/>
+      <c r="D94" s="146">
+        <f>SUMIF(E11:E92,"Previsto",D11:D92)</f>
+        <v/>
+      </c>
+      <c r="E94" s="142" t="n"/>
+      <c r="F94" s="142" t="n"/>
+      <c r="G94" s="144" t="n"/>
+    </row>
+    <row r="95" s="157">
+      <c r="A95" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B91" s="86" t="n"/>
-      <c r="C91" s="114" t="n"/>
-      <c r="D91" s="115">
-        <f>D89+D90</f>
-        <v/>
-      </c>
-      <c r="E91" s="116" t="n"/>
-      <c r="F91" s="116" t="n"/>
-      <c r="G91" s="86" t="n"/>
-    </row>
-    <row r="92" s="157"/>
-    <row r="93" ht="15.75" customHeight="1" s="157"/>
-    <row r="94" ht="15.75" customHeight="1" s="157">
-      <c r="A94" s="200" t="inlineStr">
+      <c r="B95" s="86" t="n"/>
+      <c r="C95" s="114" t="n"/>
+      <c r="D95" s="115">
+        <f>D93+D94</f>
+        <v/>
+      </c>
+      <c r="E95" s="116" t="n"/>
+      <c r="F95" s="116" t="n"/>
+      <c r="G95" s="86" t="n"/>
+    </row>
+    <row r="96" s="157"/>
+    <row r="97" ht="15.75" customHeight="1" s="157"/>
+    <row r="98" ht="15.75" customHeight="1" s="157">
+      <c r="A98" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="95" s="157">
-      <c r="A95" s="194" t="inlineStr">
+    <row r="99" s="157">
+      <c r="A99" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="96" s="157">
-      <c r="A96" s="111" t="inlineStr">
+    <row r="100" s="157">
+      <c r="A100" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B96" s="111" t="inlineStr">
+      <c r="B100" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C96" s="111" t="inlineStr">
+      <c r="C100" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D96" s="111" t="inlineStr">
+      <c r="D100" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E96" s="111" t="inlineStr">
+      <c r="E100" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F96" s="111" t="inlineStr">
+      <c r="F100" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G96" s="111" t="inlineStr">
+      <c r="G100" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" s="157">
-      <c r="A97" s="78" t="inlineStr">
-        <is>
-          <t>Centro de Especialidades Odontomédicas</t>
-        </is>
-      </c>
-      <c r="B97" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C97" s="77" t="n">
-        <v>46239</v>
-      </c>
-      <c r="D97" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E97" s="112" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F97" s="112">
-        <f>IF(OR($E97="Recebido",$C97=""),"",MAX(0,TODAY()-$C97))</f>
-        <v/>
-      </c>
-      <c r="G97" s="78" t="n"/>
-    </row>
-    <row r="98" s="157">
-      <c r="A98" s="82" t="inlineStr">
-        <is>
-          <t>Supermercado Brasil</t>
-        </is>
-      </c>
-      <c r="B98" s="82" t="inlineStr">
-        <is>
-          <t>2x Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C98" s="81" t="n">
-        <v>46239</v>
-      </c>
-      <c r="D98" s="83" t="n">
-        <v>280</v>
-      </c>
-      <c r="E98" s="113" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="F98" s="113">
-        <f>IF(OR($E98="Recebido",$C98=""),"",MAX(0,TODAY()-$C98))</f>
-        <v/>
-      </c>
-      <c r="G98" s="82" t="n"/>
-    </row>
-    <row r="99" s="157">
-      <c r="A99" s="78" t="inlineStr">
-        <is>
-          <t>Tropical Motos LTDA</t>
-        </is>
-      </c>
-      <c r="B99" s="78" t="inlineStr">
-        <is>
-          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
-        </is>
-      </c>
-      <c r="C99" s="77" t="n">
-        <v>46245</v>
-      </c>
-      <c r="D99" s="79" t="n">
-        <v>820</v>
-      </c>
-      <c r="E99" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F99" s="112">
-        <f>IF(OR($E99="Recebido",$C99=""),"",MAX(0,TODAY()-$C99))</f>
-        <v/>
-      </c>
-      <c r="G99" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" s="157">
-      <c r="A100" s="82" t="inlineStr">
-        <is>
-          <t>Free Way</t>
-        </is>
-      </c>
-      <c r="B100" s="82" t="inlineStr">
-        <is>
-          <t>5x Refil Everest</t>
-        </is>
-      </c>
-      <c r="C100" s="81" t="n">
-        <v>46251</v>
-      </c>
-      <c r="D100" s="83" t="n">
-        <v>700</v>
-      </c>
-      <c r="E100" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F100" s="113">
-        <f>IF(OR($E100="Recebido",$C100=""),"",MAX(0,TODAY()-$C100))</f>
-        <v/>
-      </c>
-      <c r="G100" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="101" s="157">
       <c r="A101" s="78" t="inlineStr">
         <is>
-          <t>Neli Sena Rego</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B101" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C101" s="77" t="n">
-        <v>46254</v>
+        <v>46239</v>
       </c>
       <c r="D101" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E101" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F101" s="112">
         <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
         <v/>
       </c>
-      <c r="G101" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
-        </is>
-      </c>
+      <c r="G101" s="78" t="n"/>
     </row>
     <row r="102" s="157">
       <c r="A102" s="82" t="inlineStr">
         <is>
-          <t>Neli Sena Rego</t>
+          <t>Supermercado Brasil</t>
         </is>
       </c>
       <c r="B102" s="82" t="inlineStr">
         <is>
-          <t>Conexão + Mangueira</t>
+          <t>2x Refil Pro Life</t>
         </is>
       </c>
       <c r="C102" s="81" t="n">
-        <v>46255</v>
+        <v>46239</v>
       </c>
       <c r="D102" s="83" t="n">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="E102" s="113" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F102" s="113">
         <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
         <v/>
       </c>
-      <c r="G102" s="82" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
-        </is>
-      </c>
+      <c r="G102" s="82" t="n"/>
     </row>
     <row r="103" s="157">
       <c r="A103" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Tropical Motos LTDA</t>
         </is>
       </c>
       <c r="B103" s="78" t="inlineStr">
         <is>
-          <t>4x Refil Everest</t>
+          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
       <c r="C103" s="77" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="D103" s="79" t="n">
-        <v>480</v>
+        <v>820</v>
       </c>
       <c r="E103" s="112" t="inlineStr">
         <is>
@@ -66842,26 +66858,26 @@
       </c>
       <c r="G103" s="78" t="inlineStr">
         <is>
-          <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
     <row r="104" s="157">
       <c r="A104" s="82" t="inlineStr">
         <is>
-          <t>Cícero Lima</t>
+          <t>Free Way</t>
         </is>
       </c>
       <c r="B104" s="82" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>5x Refil Everest</t>
         </is>
       </c>
       <c r="C104" s="81" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="D104" s="83" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="E104" s="113" t="inlineStr">
         <is>
@@ -66874,26 +66890,26 @@
       </c>
       <c r="G104" s="82" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 27/08/2026</t>
+          <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="105" s="157">
       <c r="A105" s="78" t="inlineStr">
         <is>
-          <t>Promotoria Regional de Jacobina</t>
+          <t>Neli Sena Rego</t>
         </is>
       </c>
       <c r="B105" s="78" t="inlineStr">
         <is>
-          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C105" s="77" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="D105" s="79" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="E105" s="112" t="inlineStr">
         <is>
@@ -66906,26 +66922,26 @@
       </c>
       <c r="G105" s="78" t="inlineStr">
         <is>
-          <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
+          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
     <row r="106" s="157">
       <c r="A106" s="82" t="inlineStr">
         <is>
-          <t>Lucas Souza</t>
+          <t>Neli Sena Rego</t>
         </is>
       </c>
       <c r="B106" s="82" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Conexão + Mangueira</t>
         </is>
       </c>
       <c r="C106" s="81" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="D106" s="83" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="E106" s="113" t="inlineStr">
         <is>
@@ -66938,26 +66954,26 @@
       </c>
       <c r="G106" s="82" t="inlineStr">
         <is>
-          <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
     <row r="107" s="157">
       <c r="A107" s="78" t="inlineStr">
         <is>
-          <t>FG Boa Vista (Recife/PE)</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B107" s="78" t="inlineStr">
         <is>
-          <t>Refis — troca de julho/2026</t>
+          <t>4x Refil Everest</t>
         </is>
       </c>
       <c r="C107" s="77" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="D107" s="79" t="n">
-        <v>1008.8</v>
+        <v>480</v>
       </c>
       <c r="E107" s="112" t="inlineStr">
         <is>
@@ -66970,26 +66986,26 @@
       </c>
       <c r="G107" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+          <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="108" s="157">
       <c r="A108" s="82" t="inlineStr">
         <is>
-          <t>UNIFG Guanambi (Guanambi/BA)</t>
+          <t>Cícero Lima</t>
         </is>
       </c>
       <c r="B108" s="82" t="inlineStr">
         <is>
-          <t>Refis — troca de julho/2026</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C108" s="81" t="n">
         <v>46261</v>
       </c>
       <c r="D108" s="83" t="n">
-        <v>4534.75</v>
+        <v>140</v>
       </c>
       <c r="E108" s="113" t="inlineStr">
         <is>
@@ -67002,26 +67018,26 @@
       </c>
       <c r="G108" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+          <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
     <row r="109" s="157">
       <c r="A109" s="78" t="inlineStr">
         <is>
-          <t>UNP Zona Norte (Natal/RN)</t>
+          <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
       <c r="B109" s="78" t="inlineStr">
         <is>
-          <t>Refis — troca de julho/2026</t>
+          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
       <c r="C109" s="77" t="n">
         <v>46261</v>
       </c>
       <c r="D109" s="79" t="n">
-        <v>870</v>
+        <v>470</v>
       </c>
       <c r="E109" s="112" t="inlineStr">
         <is>
@@ -67034,26 +67050,26 @@
       </c>
       <c r="G109" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
+          <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
     <row r="110" s="157">
       <c r="A110" s="82" t="inlineStr">
         <is>
-          <t>UNP Caicó (Caicó/RN)</t>
+          <t>Lucas Souza</t>
         </is>
       </c>
       <c r="B110" s="82" t="inlineStr">
         <is>
-          <t>Refis — troca de julho/2026</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C110" s="81" t="n">
         <v>46261</v>
       </c>
       <c r="D110" s="83" t="n">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="E110" s="113" t="inlineStr">
         <is>
@@ -67066,14 +67082,14 @@
       </c>
       <c r="G110" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
+          <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="111" s="157">
       <c r="A111" s="78" t="inlineStr">
         <is>
-          <t>AGES Irecê (Irecê/BA)</t>
+          <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
       <c r="B111" s="78" t="inlineStr">
@@ -67082,10 +67098,10 @@
         </is>
       </c>
       <c r="C111" s="77" t="n">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="D111" s="79" t="n">
-        <v>1338.6</v>
+        <v>1008.8</v>
       </c>
       <c r="E111" s="112" t="inlineStr">
         <is>
@@ -67098,14 +67114,14 @@
       </c>
       <c r="G111" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
     <row r="112" s="157">
       <c r="A112" s="82" t="inlineStr">
         <is>
-          <t>CIS Irecê (Irecê/BA)</t>
+          <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
       <c r="B112" s="82" t="inlineStr">
@@ -67114,10 +67130,10 @@
         </is>
       </c>
       <c r="C112" s="81" t="n">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="D112" s="83" t="n">
-        <v>1358</v>
+        <v>4534.75</v>
       </c>
       <c r="E112" s="113" t="inlineStr">
         <is>
@@ -67130,14 +67146,14 @@
       </c>
       <c r="G112" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
     <row r="113" s="157">
       <c r="A113" s="78" t="inlineStr">
         <is>
-          <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
+          <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
       <c r="B113" s="78" t="inlineStr">
@@ -67146,10 +67162,10 @@
         </is>
       </c>
       <c r="C113" s="77" t="n">
-        <v>46270</v>
+        <v>46261</v>
       </c>
       <c r="D113" s="79" t="n">
-        <v>649.9</v>
+        <v>870</v>
       </c>
       <c r="E113" s="112" t="inlineStr">
         <is>
@@ -67162,14 +67178,14 @@
       </c>
       <c r="G113" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
     <row r="114" s="157">
       <c r="A114" s="82" t="inlineStr">
         <is>
-          <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
+          <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
       <c r="B114" s="82" t="inlineStr">
@@ -67178,10 +67194,10 @@
         </is>
       </c>
       <c r="C114" s="81" t="n">
-        <v>46270</v>
+        <v>46261</v>
       </c>
       <c r="D114" s="83" t="n">
-        <v>562.6</v>
+        <v>440</v>
       </c>
       <c r="E114" s="113" t="inlineStr">
         <is>
@@ -67194,14 +67210,14 @@
       </c>
       <c r="G114" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
     <row r="115" s="157">
       <c r="A115" s="78" t="inlineStr">
         <is>
-          <t>AGES Paripiranga (Paripiranga/BA)</t>
+          <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
       <c r="B115" s="78" t="inlineStr">
@@ -67210,10 +67226,10 @@
         </is>
       </c>
       <c r="C115" s="77" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="D115" s="79" t="n">
-        <v>1086.4</v>
+        <v>1338.6</v>
       </c>
       <c r="E115" s="112" t="inlineStr">
         <is>
@@ -67226,14 +67242,14 @@
       </c>
       <c r="G115" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="116" s="157">
       <c r="A116" s="82" t="inlineStr">
         <is>
-          <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
+          <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
       <c r="B116" s="82" t="inlineStr">
@@ -67242,10 +67258,10 @@
         </is>
       </c>
       <c r="C116" s="81" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="D116" s="83" t="n">
-        <v>1265.85</v>
+        <v>1358</v>
       </c>
       <c r="E116" s="113" t="inlineStr">
         <is>
@@ -67258,14 +67274,14 @@
       </c>
       <c r="G116" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="117" s="157">
       <c r="A117" s="78" t="inlineStr">
         <is>
-          <t>UNP Mossoró (Mossoró/RN)</t>
+          <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
       <c r="B117" s="78" t="inlineStr">
@@ -67277,7 +67293,7 @@
         <v>46270</v>
       </c>
       <c r="D117" s="79" t="n">
-        <v>1867.25</v>
+        <v>649.9</v>
       </c>
       <c r="E117" s="112" t="inlineStr">
         <is>
@@ -67290,14 +67306,14 @@
       </c>
       <c r="G117" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="118" s="157">
       <c r="A118" s="82" t="inlineStr">
         <is>
-          <t>CIS Jacobina (Jacobina/BA)</t>
+          <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
       <c r="B118" s="82" t="inlineStr">
@@ -67306,10 +67322,10 @@
         </is>
       </c>
       <c r="C118" s="81" t="n">
-        <v>46290</v>
+        <v>46270</v>
       </c>
       <c r="D118" s="83" t="n">
-        <v>2095.2</v>
+        <v>562.6</v>
       </c>
       <c r="E118" s="113" t="inlineStr">
         <is>
@@ -67322,14 +67338,14 @@
       </c>
       <c r="G118" s="82" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
+          <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="119" s="157">
       <c r="A119" s="78" t="inlineStr">
         <is>
-          <t>AGES Jacobina (Jacobina/BA)</t>
+          <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
       <c r="B119" s="78" t="inlineStr">
@@ -67338,14 +67354,14 @@
         </is>
       </c>
       <c r="C119" s="77" t="n">
-        <v>46305</v>
+        <v>46270</v>
       </c>
       <c r="D119" s="79" t="n">
-        <v>1188.25</v>
+        <v>1086.4</v>
       </c>
       <c r="E119" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F119" s="112">
@@ -67354,26 +67370,26 @@
       </c>
       <c r="G119" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
+          <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="120" s="157">
       <c r="A120" s="82" t="inlineStr">
         <is>
-          <t>Instituto Paulo Leão</t>
+          <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
       <c r="B120" s="82" t="inlineStr">
         <is>
-          <t>Refil E3 + Pré Filtro</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C120" s="81" t="n">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="D120" s="83" t="n">
-        <v>160</v>
+        <v>1265.85</v>
       </c>
       <c r="E120" s="113" t="inlineStr">
         <is>
@@ -67386,26 +67402,26 @@
       </c>
       <c r="G120" s="82" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="121" s="157">
       <c r="A121" s="78" t="inlineStr">
         <is>
-          <t>Eletronic Segurança Eletronica</t>
+          <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
       <c r="B121" s="78" t="inlineStr">
         <is>
-          <t>Pré Filtro</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C121" s="77" t="n">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="D121" s="79" t="n">
-        <v>60</v>
+        <v>1867.25</v>
       </c>
       <c r="E121" s="112" t="inlineStr">
         <is>
@@ -67418,26 +67434,26 @@
       </c>
       <c r="G121" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
+          <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="122" s="157">
       <c r="A122" s="82" t="inlineStr">
         <is>
-          <t>Clube dos Mineiros</t>
+          <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
       <c r="B122" s="82" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C122" s="81" t="n">
-        <v>46265</v>
+        <v>46290</v>
       </c>
       <c r="D122" s="83" t="n">
-        <v>150</v>
+        <v>2095.2</v>
       </c>
       <c r="E122" s="113" t="inlineStr">
         <is>
@@ -67450,30 +67466,30 @@
       </c>
       <c r="G122" s="82" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
+          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
     <row r="123" s="157">
       <c r="A123" s="78" t="inlineStr">
         <is>
-          <t>Armazem Cecilio Mota</t>
+          <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
       <c r="B123" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C123" s="77" t="n">
-        <v>46266</v>
+        <v>46305</v>
       </c>
       <c r="D123" s="79" t="n">
-        <v>225</v>
+        <v>1188.25</v>
       </c>
       <c r="E123" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F123" s="112">
@@ -67482,26 +67498,26 @@
       </c>
       <c r="G123" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
     <row r="124" s="157">
       <c r="A124" s="82" t="inlineStr">
         <is>
-          <t>Clebson Dantas Da Silva</t>
+          <t>Instituto Paulo Leão</t>
         </is>
       </c>
       <c r="B124" s="82" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
       <c r="C124" s="81" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="D124" s="83" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E124" s="113" t="inlineStr">
         <is>
@@ -67514,90 +67530,90 @@
       </c>
       <c r="G124" s="82" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 02/09/2026</t>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="125" s="157">
-      <c r="A125" s="82" t="inlineStr">
-        <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
-        </is>
-      </c>
-      <c r="B125" s="82" t="inlineStr">
-        <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C125" s="81" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D125" s="83" t="n">
-        <v>540</v>
-      </c>
-      <c r="E125" s="113" t="inlineStr">
+      <c r="A125" s="78" t="inlineStr">
+        <is>
+          <t>Eletronic Segurança Eletronica</t>
+        </is>
+      </c>
+      <c r="B125" s="78" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C125" s="77" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D125" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E125" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F125" s="113">
+      <c r="F125" s="112">
         <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
         <v/>
       </c>
-      <c r="G125" s="82" t="inlineStr">
-        <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+      <c r="G125" s="78" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="126" s="157">
-      <c r="A126" s="78" t="inlineStr">
-        <is>
-          <t>Cecilio Mota Junior</t>
-        </is>
-      </c>
-      <c r="B126" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C126" s="77" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D126" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E126" s="112" t="inlineStr">
+      <c r="A126" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B126" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C126" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D126" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E126" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F126" s="112">
+      <c r="F126" s="113">
         <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
         <v/>
       </c>
-      <c r="G126" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+      <c r="G126" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="127" s="157">
       <c r="A127" s="78" t="inlineStr">
         <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B127" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C127" s="77" t="n">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="D127" s="79" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="E127" s="112" t="inlineStr">
         <is>
@@ -67610,78 +67626,78 @@
       </c>
       <c r="G127" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="128" s="157">
-      <c r="A128" s="78" t="inlineStr">
-        <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
-        </is>
-      </c>
-      <c r="B128" s="78" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C128" s="77" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D128" s="79" t="n">
+      <c r="A128" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B128" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C128" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D128" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E128" s="112" t="inlineStr">
+      <c r="E128" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F128" s="112">
+      <c r="F128" s="113">
         <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
         <v/>
       </c>
-      <c r="G128" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+      <c r="G128" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="129" s="157">
-      <c r="A129" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B129" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C129" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D129" s="79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E129" s="112" t="inlineStr">
+      <c r="A129" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B129" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C129" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D129" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E129" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F129" s="112">
+      <c r="F129" s="113">
         <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
         <v/>
       </c>
-      <c r="G129" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+      <c r="G129" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="130" s="157">
       <c r="A130" s="78" t="inlineStr">
         <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B130" s="78" t="inlineStr">
@@ -67690,7 +67706,7 @@
         </is>
       </c>
       <c r="C130" s="77" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="D130" s="79" t="n">
         <v>140</v>
@@ -67706,14 +67722,14 @@
       </c>
       <c r="G130" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="131" s="157">
       <c r="A131" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B131" s="78" t="inlineStr">
@@ -67722,7 +67738,7 @@
         </is>
       </c>
       <c r="C131" s="77" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="D131" s="79" t="n">
         <v>200</v>
@@ -67738,30 +67754,30 @@
       </c>
       <c r="G131" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="132" s="157">
       <c r="A132" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B132" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C132" s="77" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D132" s="79" t="n">
-        <v>370</v>
+        <v>140</v>
       </c>
       <c r="E132" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F132" s="112">
@@ -67770,26 +67786,26 @@
       </c>
       <c r="G132" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="133" s="157">
       <c r="A133" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B133" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C133" s="77" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="D133" s="79" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E133" s="112" t="inlineStr">
         <is>
@@ -67802,26 +67818,26 @@
       </c>
       <c r="G133" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="134" s="157">
       <c r="A134" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B134" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C134" s="77" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="D134" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E134" s="112" t="inlineStr">
         <is>
@@ -67834,26 +67850,26 @@
       </c>
       <c r="G134" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="135" s="157">
       <c r="A135" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B135" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C135" s="77" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D135" s="79" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="E135" s="112" t="inlineStr">
         <is>
@@ -67866,30 +67882,30 @@
       </c>
       <c r="G135" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="136" s="157">
       <c r="A136" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B136" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C136" s="77" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="D136" s="79" t="n">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F136" s="112">
@@ -67898,14 +67914,14 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
         </is>
       </c>
     </row>
     <row r="137" s="157">
       <c r="A137" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B137" s="78" t="inlineStr">
@@ -67914,7 +67930,7 @@
         </is>
       </c>
       <c r="C137" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D137" s="79" t="n">
         <v>140</v>
@@ -67930,26 +67946,26 @@
       </c>
       <c r="G137" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="138" s="157">
       <c r="A138" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B138" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C138" s="77" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="D138" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E138" s="112" t="inlineStr">
         <is>
@@ -67962,30 +67978,30 @@
       </c>
       <c r="G138" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="139" s="157">
       <c r="A139" s="78" t="inlineStr">
         <is>
-          <t>Centro de Especialidades Odontomédicas</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B139" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C139" s="77" t="n">
-        <v>46044</v>
+        <v>46281</v>
       </c>
       <c r="D139" s="79" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="E139" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F139" s="112">
@@ -67994,30 +68010,30 @@
       </c>
       <c r="G139" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="140" s="157">
       <c r="A140" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Marilda Macedo / José Luciano Costa</t>
         </is>
       </c>
       <c r="B140" s="78" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C140" s="77" t="n">
-        <v>46073</v>
+        <v>46283</v>
       </c>
       <c r="D140" s="79" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E140" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F140" s="112">
@@ -68026,30 +68042,30 @@
       </c>
       <c r="G140" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="141" s="157">
       <c r="A141" s="78" t="inlineStr">
         <is>
-          <t>Centro Médico de Jacobina</t>
+          <t>Tatiana Rocha</t>
         </is>
       </c>
       <c r="B141" s="78" t="inlineStr">
         <is>
-          <t>2x Botão Completo</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C141" s="77" t="n">
-        <v>46203</v>
+        <v>46286</v>
       </c>
       <c r="D141" s="79" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E141" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F141" s="112">
@@ -68058,14 +68074,14 @@
       </c>
       <c r="G141" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="142" s="157">
       <c r="A142" s="78" t="inlineStr">
         <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="B142" s="78" t="inlineStr">
@@ -68074,14 +68090,14 @@
         </is>
       </c>
       <c r="C142" s="77" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="D142" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E142" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F142" s="112">
@@ -68090,26 +68106,26 @@
       </c>
       <c r="G142" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="143" s="157">
       <c r="A143" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B143" s="78" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="C143" s="77" t="n">
-        <v>46294</v>
+        <v>46044</v>
       </c>
       <c r="D143" s="79" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="E143" s="112" t="inlineStr">
         <is>
@@ -68122,26 +68138,26 @@
       </c>
       <c r="G143" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026.</t>
+          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
         </is>
       </c>
     </row>
     <row r="144" s="157">
       <c r="A144" s="78" t="inlineStr">
         <is>
-          <t>PC Jacobina Administradora de Cartões LTDA</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B144" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="C144" s="77" t="n">
-        <v>46295</v>
+        <v>46073</v>
       </c>
       <c r="D144" s="79" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="E144" s="112" t="inlineStr">
         <is>
@@ -68154,26 +68170,26 @@
       </c>
       <c r="G144" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 30/09/2026.</t>
+          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="145" s="157">
       <c r="A145" s="78" t="inlineStr">
         <is>
-          <t>Aneilde Rios de Oliveira</t>
+          <t>Centro Médico de Jacobina</t>
         </is>
       </c>
       <c r="B145" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Botão Completo</t>
         </is>
       </c>
       <c r="C145" s="77" t="n">
-        <v>46296</v>
+        <v>46203</v>
       </c>
       <c r="D145" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E145" s="112" t="inlineStr">
         <is>
@@ -68186,26 +68202,26 @@
       </c>
       <c r="G145" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 01/10/2026 (casa, Caeira).</t>
+          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="146" s="157">
       <c r="A146" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
         </is>
       </c>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C146" s="77" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="D146" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E146" s="112" t="inlineStr">
         <is>
@@ -68218,26 +68234,26 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões).</t>
+          <t>Troca do dia 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="147" s="157">
       <c r="A147" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B147" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>Refil C+3</t>
         </is>
       </c>
       <c r="C147" s="77" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="D147" s="79" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E147" s="112" t="inlineStr">
         <is>
@@ -68250,51 +68266,175 @@
       </c>
       <c r="G147" s="78" t="inlineStr">
         <is>
+          <t>Pagamento previsto para 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" s="157">
+      <c r="A148" s="78" t="inlineStr">
+        <is>
+          <t>PC Jacobina Administradora de Cartões LTDA</t>
+        </is>
+      </c>
+      <c r="B148" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C148" s="77" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D148" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E148" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F148" s="112">
+        <f>IF(OR($E148="Recebido",$C148=""),"",MAX(0,TODAY()-$C148))</f>
+        <v/>
+      </c>
+      <c r="G148" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" s="157">
+      <c r="A149" s="78" t="inlineStr">
+        <is>
+          <t>Aneilde Rios de Oliveira</t>
+        </is>
+      </c>
+      <c r="B149" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C149" s="77" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D149" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E149" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F149" s="112">
+        <f>IF(OR($E149="Recebido",$C149=""),"",MAX(0,TODAY()-$C149))</f>
+        <v/>
+      </c>
+      <c r="G149" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 01/10/2026 (casa, Caeira).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" s="157">
+      <c r="A150" s="78" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="B150" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="C150" s="77" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D150" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E150" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F150" s="112">
+        <f>IF(OR($E150="Recebido",$C150=""),"",MAX(0,TODAY()-$C150))</f>
+        <v/>
+      </c>
+      <c r="G150" s="78" t="inlineStr">
+        <is>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" s="157">
+      <c r="A151" s="78" t="inlineStr">
+        <is>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
+        </is>
+      </c>
+      <c r="B151" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + 2x Botão Completo</t>
+        </is>
+      </c>
+      <c r="C151" s="77" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D151" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E151" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F151" s="112">
+        <f>IF(OR($E151="Recebido",$C151=""),"",MAX(0,TODAY()-$C151))</f>
+        <v/>
+      </c>
+      <c r="G151" s="78" t="inlineStr">
+        <is>
           <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões).</t>
         </is>
       </c>
     </row>
-    <row r="148" s="157">
-      <c r="A148" s="86" t="inlineStr">
+    <row r="152" s="157">
+      <c r="A152" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D148" s="115">
-        <f>SUMIF(E97:E147,"Pendente",D97:D147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" s="157">
-      <c r="A149" s="202" t="inlineStr">
+      <c r="D152" s="115">
+        <f>SUMIF(E101:E151,"Pendente",D101:D151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" s="157">
+      <c r="A153" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B149" s="159" t="n"/>
-      <c r="C149" s="159" t="n"/>
-      <c r="D149" s="159" t="n"/>
-      <c r="E149" s="159" t="n"/>
-      <c r="F149" s="159" t="n"/>
-      <c r="G149" s="160" t="n"/>
-    </row>
-    <row r="150" s="157">
-      <c r="A150" s="203">
-        <f>IF(ROUND(D148-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D148-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" s="157">
-      <c r="A151" s="203" t="inlineStr">
+      <c r="B153" s="159" t="n"/>
+      <c r="C153" s="159" t="n"/>
+      <c r="D153" s="159" t="n"/>
+      <c r="E153" s="159" t="n"/>
+      <c r="F153" s="159" t="n"/>
+      <c r="G153" s="160" t="n"/>
+    </row>
+    <row r="154" s="157">
+      <c r="A154" s="203">
+        <f>IF(ROUND(D152-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D152-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" s="157">
+      <c r="A155" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="152" s="157"/>
-    <row r="153" s="157"/>
-    <row r="154" s="157"/>
-    <row r="155" s="157"/>
     <row r="156" s="157"/>
     <row r="157" s="157"/>
     <row r="158" s="157"/>
@@ -68349,22 +68489,22 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A149:G149"/>
-    <mergeCell ref="A150:G150"/>
+    <mergeCell ref="A154:G154"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A153:G153"/>
+    <mergeCell ref="A98:G98"/>
+    <mergeCell ref="A99:G99"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E97:E147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E101:E151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -38,12 +38,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$ &quot;#,##0.00;[Red]&quot;−R$ &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="78">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -506,6 +507,18 @@
       <color rgb="FFB7791F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF6B46C1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF6B46C1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="24">
     <fill>
@@ -797,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1316,10 +1329,71 @@
     <xf numFmtId="0" fontId="48" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="76" fillId="12" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC0392B"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2893,7 +2967,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="26.1" customHeight="1" s="157">
+    <row r="6" ht="26" customHeight="1" s="157">
       <c r="B6" s="117" t="inlineStr">
         <is>
           <t>ENTRADAS (ANO)</t>
@@ -2906,7 +2980,7 @@
       </c>
       <c r="D6" s="119" t="inlineStr">
         <is>
-          <t>LUCRO EM CAIXA</t>
+          <t>SOBRA FINAL (DEPOIS DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="E6" s="120" t="inlineStr">
@@ -2921,7 +2995,7 @@
       </c>
       <c r="G6" s="121" t="inlineStr">
         <is>
-          <t>MARGEM DO ANO</t>
+          <t>MARGEM FINAL DO ANO</t>
         </is>
       </c>
     </row>
@@ -2958,7 +3032,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" s="157">
+    <row r="10" ht="26" customHeight="1" s="157">
       <c r="B10" s="117" t="inlineStr">
         <is>
           <t>CUSTO FIXO MÉDIO/MÊS</t>
@@ -2971,12 +3045,22 @@
       </c>
       <c r="D10" s="119" t="inlineStr">
         <is>
-          <t>DESPESAS PESSOAIS (ANO)</t>
+          <t>PRÓ-LABORE EDILÂNIA (ANO)</t>
         </is>
       </c>
       <c r="E10" s="120" t="inlineStr">
         <is>
           <t>PONTO DE EQUILÍBRIO (FAT. MÍN./MÊS)</t>
+        </is>
+      </c>
+      <c r="F10" s="238" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE COMBINADO/MÊS</t>
+        </is>
+      </c>
+      <c r="G10" s="117" t="inlineStr">
+        <is>
+          <t>SOBRA MÉDIA/MÊS DEPOIS DELA</t>
         </is>
       </c>
     </row>
@@ -2994,7 +3078,15 @@
         <v/>
       </c>
       <c r="E11" s="125">
-        <f>'Ponto de Equilíbrio'!B10</f>
+        <f>'Ponto de Equilíbrio'!B12</f>
+        <v/>
+      </c>
+      <c r="F11" s="239">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G11" s="122">
+        <f>'Ponto de Equilíbrio'!B14</f>
         <v/>
       </c>
     </row>
@@ -3436,10 +3528,10 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="167" t="inlineStr">
-        <is>
-          <t>4. Despesa pessoal do casal paga pela loja: categoria "Pro Labore Edilânia" — fica registrada, mas fora do resultado da loja.</t>
+    <row r="50" ht="44" customHeight="1" s="157">
+      <c r="B50" s="240" t="inlineStr">
+        <is>
+          <t>4. Tudo o que a Edilânia gasta do dinheiro da loja (contas da casa, Pix pessoais, mercado, diarista...): categoria "Pro Labore Edilânia". Isso é o pró-labore dela — combinado em R$ 4.000,00/mês (valor na aba Ponto de Equilíbrio, B10). Cada mês mostra quanto ela já gastou, quanto ainda pode gastar e a SOBRA FINAL da loja.</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3543,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="C34:G34"/>
@@ -3478,6 +3570,7 @@
     <mergeCell ref="C43:G43"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B50:G50"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="B47:G47"/>
@@ -7328,7 +7421,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -7479,6 +7572,25 @@
         <f>SUMIF(H5:H134,K7,G5:G134)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,1,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -7518,6 +7630,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H134,K8,G5:G134)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -11618,19 +11746,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -11763,7 +11919,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -11910,6 +12066,25 @@
         <f>SUMIF(H5:H148,K7,G5:G148)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,2,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -11953,6 +12128,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H148,K8,G5:G148)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -16573,19 +16764,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -16718,7 +16937,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -16860,6 +17079,25 @@
         <f>SUMIF(H5:H126,K7,G5:G126)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,3,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -16903,6 +17141,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H126,K8,G5:G126)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -20814,19 +21068,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -20959,7 +21241,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -21112,6 +21394,25 @@
       <c r="L7" s="11">
         <f>SUMIF(H5:H132,K7,G5:G132)</f>
         <v/>
+      </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,4,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -21149,6 +21450,22 @@
         <f>SUMIF(H5:H132,K8,G5:G132)</f>
         <v/>
       </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -25307,19 +25624,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -25452,7 +25797,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -25590,6 +25935,25 @@
         <f>SUMIF(H5:H132,K7,G5:G132)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,5,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -25633,6 +25997,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H132,K8,G5:G132)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -29658,19 +30038,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -29803,7 +30211,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -29961,6 +30369,25 @@
       <c r="L7" s="11">
         <f>SUMIF(H5:H120,K7,G5:G120)</f>
         <v/>
+      </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,6,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -30001,6 +30428,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H120,K8,G5:G120)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -33703,19 +34146,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -33848,7 +34319,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -33998,6 +34469,25 @@
         <f>SUMIF(H5:H123,K7,G5:G123)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,7,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -34041,6 +34531,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H123,K8,G5:G123)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -37724,19 +38230,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -37783,7 +38317,7 @@
     <row r="2">
       <c r="A2" s="184" t="inlineStr">
         <is>
-          <t>Jan–Jul: importado do Livro Caixa (DigiSat/G6). Ago–Dez: lançamento manual. Entradas = faturamento recebido (líquido de taxa de máquina e sem vendas pendentes); saídas excluem Pro Labore Edilânia e contas pagas pelo Capital de Giro (BB). Vendas ainda não recebidas ficam na tabela 'Contas a Receber'.</t>
+          <t>Jan–Dez: lançamentos das abas dos meses. Entradas = faturamento recebido (líquido de taxa de máquina e sem vendas pendentes); saídas = despesas da loja (sem o pró-labore e sem as contas pagas pelo Capital de Giro do BB). O pró-labore da Edilânia aparece separado e é descontado na coluna "Sobra final". Vendas ainda não recebidas ficam na tabela "Contas a Receber".</t>
         </is>
       </c>
     </row>
@@ -37809,13 +38343,13 @@
       <c r="D4" s="160" t="n"/>
       <c r="E4" s="181" t="inlineStr">
         <is>
-          <t>LUCRO LÍQUIDO</t>
+          <t>SOBRA FINAL (DEPOIS DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="F4" s="160" t="n"/>
       <c r="G4" s="191" t="inlineStr">
         <is>
-          <t>MARGEM DO ANO</t>
+          <t>MARGEM FINAL DO ANO</t>
         </is>
       </c>
       <c r="H4" s="160" t="n"/>
@@ -37843,12 +38377,12 @@
       </c>
       <c r="D5" s="173" t="n"/>
       <c r="E5" s="188">
-        <f>SUM(D24:D35)</f>
+        <f>SUM(G24:G35)</f>
         <v/>
       </c>
       <c r="F5" s="173" t="n"/>
       <c r="G5" s="176">
-        <f>IF(B36=0,0,D36/B36)</f>
+        <f>IF(B36=0,0,G36/B36)</f>
         <v/>
       </c>
       <c r="H5" s="173" t="n"/>
@@ -37883,19 +38417,19 @@
     </row>
     <row r="9">
       <c r="A9" s="178">
-        <f>"Melhor mês em lucro: "&amp;INDEX(A24:A35,MATCH(MAX(D24:D35),D24:D35,0))&amp;" (lucro de "&amp;TEXT(MAX(D24:D35),"R$ #,##0.00")&amp;")"</f>
+        <f>"Melhor mês (sobra final, depois da Edilânia): "&amp;INDEX(A24:A35,MATCH(MAX(G24:G35),G24:G35,0))&amp;" ("&amp;TEXT(MAX(G24:G35),"R$ #,##0.00")&amp;")"</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="178">
-        <f>"Mês mais fraco em lucro: "&amp;INDEX(A24:A35,MATCH(MIN(D24:D35),D24:D35,0))&amp;" (lucro de "&amp;TEXT(MIN(D24:D35),"R$ #,##0.00")&amp;")"</f>
+        <f>"Mês mais fraco (sobra final, depois da Edilânia): "&amp;INDEX(A24:A35,MATCH(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),G24:G35,0))&amp;" ("&amp;TEXT(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),"R$ #,##0.00")&amp;")"</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="178">
-        <f>"Número de meses com prejuízo: "&amp;COUNTIF(D24:D35,"&lt;0")&amp;" de "&amp;COUNTIF(B24:B35,"&lt;&gt;0")&amp;" meses com dados"</f>
+        <f>"Meses que fecharam no negativo depois de pagar a Edilânia: "&amp;COUNTIF(G24:G35,"&lt;0")&amp;" de "&amp;COUNTIF(B24:B35,"&lt;&gt;0")&amp;" meses com dados  ·  pró-labore do ano: "&amp;TEXT(F36,"R$ #,##0.00")&amp;" (combinado: "&amp;TEXT('Ponto de Equilíbrio'!$B$10,"R$ #,##0.00")&amp;"/mês)"</f>
         <v/>
       </c>
     </row>
@@ -37953,30 +38487,40 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1" s="157">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="23" ht="30" customHeight="1" s="157">
+      <c r="A23" s="241" t="inlineStr">
         <is>
           <t>Mês</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" s="241" t="inlineStr">
         <is>
           <t>Entradas (R$)</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="241" t="inlineStr">
         <is>
           <t>Saídas (R$)</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>Lucro (R$)</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>Margem (%)</t>
+      <c r="D23" s="241" t="inlineStr">
+        <is>
+          <t>Lucro da loja (R$)</t>
+        </is>
+      </c>
+      <c r="E23" s="241" t="inlineStr">
+        <is>
+          <t>Margem da loja (%)</t>
+        </is>
+      </c>
+      <c r="F23" s="241" t="inlineStr">
+        <is>
+          <t>Pró-labore Edilânia (R$)</t>
+        </is>
+      </c>
+      <c r="G23" s="241" t="inlineStr">
+        <is>
+          <t>Sobra final (R$)</t>
         </is>
       </c>
     </row>
@@ -38002,6 +38546,14 @@
         <f>IF(B24=0,0,D24/B24)</f>
         <v/>
       </c>
+      <c r="F24" s="3">
+        <f>'Jan 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G24" s="3">
+        <f>D24-F24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -38025,6 +38577,14 @@
         <f>IF(B25=0,0,D25/B25)</f>
         <v/>
       </c>
+      <c r="F25" s="6">
+        <f>'Fev 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>D25-F25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -38048,6 +38608,14 @@
         <f>IF(B26=0,0,D26/B26)</f>
         <v/>
       </c>
+      <c r="F26" s="3">
+        <f>'Mar 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G26" s="3">
+        <f>D26-F26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -38071,6 +38639,14 @@
         <f>IF(B27=0,0,D27/B27)</f>
         <v/>
       </c>
+      <c r="F27" s="6">
+        <f>'Abr 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G27" s="6">
+        <f>D27-F27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -38094,6 +38670,14 @@
         <f>IF(B28=0,0,D28/B28)</f>
         <v/>
       </c>
+      <c r="F28" s="3">
+        <f>'Mai 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G28" s="3">
+        <f>D28-F28</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -38117,6 +38701,14 @@
         <f>IF(B29=0,0,D29/B29)</f>
         <v/>
       </c>
+      <c r="F29" s="6">
+        <f>'Jun 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G29" s="6">
+        <f>D29-F29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -38140,6 +38732,14 @@
         <f>IF(B30=0,0,D30/B30)</f>
         <v/>
       </c>
+      <c r="F30" s="3">
+        <f>'Jul 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G30" s="3">
+        <f>D30-F30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -38163,6 +38763,14 @@
         <f>IF(B31=0,0,D31/B31)</f>
         <v/>
       </c>
+      <c r="F31" s="6">
+        <f>'Ago 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G31" s="6">
+        <f>D31-F31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -38186,6 +38794,14 @@
         <f>IF(B32=0,0,D32/B32)</f>
         <v/>
       </c>
+      <c r="F32" s="3">
+        <f>'Set 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G32" s="3">
+        <f>D32-F32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -38209,6 +38825,14 @@
         <f>IF(B33=0,0,D33/B33)</f>
         <v/>
       </c>
+      <c r="F33" s="6">
+        <f>'Out 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G33" s="6">
+        <f>D33-F33</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="157">
       <c r="A34" s="2" t="inlineStr">
@@ -38232,6 +38856,14 @@
         <f>IF(B34=0,0,D34/B34)</f>
         <v/>
       </c>
+      <c r="F34" s="3">
+        <f>'Nov 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G34" s="3">
+        <f>D34-F34</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -38255,6 +38887,14 @@
         <f>IF(B35=0,0,D35/B35)</f>
         <v/>
       </c>
+      <c r="F35" s="6">
+        <f>'Dez 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G35" s="6">
+        <f>D35-F35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
@@ -38276,6 +38916,14 @@
       </c>
       <c r="E36" s="9">
         <f>IF(B36=0,0,D36/B36)</f>
+        <v/>
+      </c>
+      <c r="F36" s="8">
+        <f>SUM(F24:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="8">
+        <f>SUM(G24:G35)</f>
         <v/>
       </c>
     </row>
@@ -38981,6 +39629,11 @@
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
+  <conditionalFormatting sqref="G24:G36">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A3" location="'Início'!A1" display="← Início"/>
   </hyperlinks>
@@ -39106,7 +39759,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -39247,6 +39900,25 @@
         <f>SUMIF(H5:H184,K7,G5:G184)</f>
         <v/>
       </c>
+      <c r="N7" s="249" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="208" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="221">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,8,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="224" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -39277,6 +39949,22 @@
       </c>
       <c r="L8" s="14">
         <f>SUMIF(H5:H184,K8,G5:G184)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -44485,19 +45173,47 @@
       <c r="L189" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Forma de pagamento inválida" error="Selecione uma forma de pagamento da lista." type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -44629,7 +45345,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -44783,6 +45499,25 @@
         <f>SUMIF(H5:H254,K7,G5:G254)</f>
         <v/>
       </c>
+      <c r="N7" s="251" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="252" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="199">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,9,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="237" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="81" t="n">
@@ -44821,6 +45556,22 @@
       </c>
       <c r="L8" s="80">
         <f>SUMIF(H5:H254,K8,G5:G254)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -52131,19 +52882,47 @@
       <c r="I256" s="30" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -52274,7 +53053,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -52424,6 +53203,25 @@
         <f>SUMIF(H5:H254,K7,G5:G254)</f>
         <v/>
       </c>
+      <c r="N7" s="251" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="252" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="199">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,10,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="237" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n">
@@ -52463,6 +53261,22 @@
       </c>
       <c r="L8" s="80">
         <f>SUMIF(H5:H254,K8,G5:G254)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -53199,34 +54013,99 @@
       <c r="J29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="44" t="n"/>
-      <c r="B30" s="45" t="n"/>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="47" t="n"/>
+      <c r="A30" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>Tarcisio Cardoso da Silva</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Refil Multifilter + Refil Plissado + Carcaça 9"</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="n">
+        <v>430</v>
+      </c>
+      <c r="E30" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F30" s="47" t="n">
+        <v>30.06</v>
+      </c>
       <c r="G30" s="48" t="n"/>
       <c r="H30" s="49" t="n"/>
-      <c r="I30" s="45" t="n"/>
+      <c r="I30" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 3x</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CLI-0901</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="19" t="n"/>
+      <c r="A31" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Refil FP4</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>6.29</v>
+      </c>
       <c r="G31" s="19" t="n"/>
       <c r="H31" s="21" t="n"/>
-      <c r="I31" s="18" t="n"/>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 2x</t>
+        </is>
+      </c>
       <c r="J31" s="18" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="n"/>
-      <c r="B32" s="45" t="n"/>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="46" t="n"/>
-      <c r="E32" s="45" t="n"/>
+      <c r="A32" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>Carcaça 9" + Refil Carbon Tech 9"</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F32" s="47" t="n"/>
       <c r="G32" s="48" t="n"/>
       <c r="H32" s="49" t="n"/>
@@ -55828,19 +56707,47 @@
       <c r="I256" s="92" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -55971,7 +56878,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -56057,6 +56964,25 @@
         <f>SUMIF(H5:H254,K7,G5:G254)</f>
         <v/>
       </c>
+      <c r="N7" s="251" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="252" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="199">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,11,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="237" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n"/>
@@ -56075,6 +57001,22 @@
       </c>
       <c r="L8" s="80">
         <f>SUMIF(H5:H254,K8,G5:G254)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -59049,19 +59991,47 @@
       <c r="I256" s="92" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -59192,7 +60162,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO</t>
+          <t>SALDO (ANTES DA EDILÂNIA)</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -59278,6 +60248,25 @@
         <f>SUMIF(H5:H254,K7,G5:G254)</f>
         <v/>
       </c>
+      <c r="N7" s="251" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE EDILÂNIA</t>
+        </is>
+      </c>
+      <c r="P7" s="252" t="inlineStr">
+        <is>
+          <t>COMBINADO NO MÊS</t>
+        </is>
+      </c>
+      <c r="R7" s="199">
+        <f>IF(L17&gt;'Ponto de Equilíbrio'!$B$10,"PASSOU DO COMBINADO",IF(TODAY()&gt;EOMONTH(DATE(2026,12,1),0),"ABAIXO DO COMBINADO","AINDA PODE GASTAR"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="237" t="inlineStr">
+        <is>
+          <t>SOBRA FINAL DO MÊS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="n"/>
@@ -59296,6 +60285,22 @@
       </c>
       <c r="L8" s="80">
         <f>SUMIF(H5:H254,K8,G5:G254)</f>
+        <v/>
+      </c>
+      <c r="N8" s="250">
+        <f>L17</f>
+        <v/>
+      </c>
+      <c r="P8" s="215">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="R8" s="205">
+        <f>ABS('Ponto de Equilíbrio'!$B$10-L17)</f>
+        <v/>
+      </c>
+      <c r="T8" s="236">
+        <f>R5-L17</f>
         <v/>
       </c>
     </row>
@@ -62270,19 +63275,47 @@
       <c r="I256" s="92" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="19">
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P8:Q9"/>
+    <mergeCell ref="T8:U9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R8:S9"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="T7:U7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T5:U6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S6"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
+  <conditionalFormatting sqref="R7:S7">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:S9">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT($R$7,6)="PASSOU"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U9">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:S6">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="E5:E254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dinheiro,Pix,Débito,Crédito à Vista,Crédito Parcelado,Aguardando Pagamento"</formula1>
@@ -62305,7 +63338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -62323,7 +63356,7 @@
     <row r="2">
       <c r="A2" s="195" t="inlineStr">
         <is>
-          <t>Receita − Custos Variáveis = Margem de Contribuição.  Margem − Custos Fixos = Resultado. Puxa tudo das abas mensais, sem digitação.</t>
+          <t>Receita − Custos Variáveis = Margem de Contribuição.  Margem − Custos Fixos = Resultado da loja.  Resultado da loja − Pró-labore da Edilânia = SOBRA FINAL. Puxa tudo das abas mensais, sem digitação.</t>
         </is>
       </c>
     </row>
@@ -62334,12 +63367,12 @@
         </is>
       </c>
       <c r="B3" s="94">
-        <f>COUNTIF(B5:M5,"&gt;0")</f>
+        <f>SUM(B38:M38)</f>
         <v/>
       </c>
       <c r="C3" s="194" t="inlineStr">
         <is>
-          <t>← meses já lançados; é a base do cálculo da coluna "Média/mês"</t>
+          <t>← meses já fechados (o mês em andamento fica fora); é a base da coluna "Média/mês"</t>
         </is>
       </c>
     </row>
@@ -62479,7 +63512,7 @@
         <v/>
       </c>
       <c r="O5" s="96">
-        <f>IF($B$3=0,0,N5/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B5:M5,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62542,7 +63575,7 @@
         <v/>
       </c>
       <c r="O6" s="98">
-        <f>IF($B$3=0,0,N6/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B6:M6,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62605,7 +63638,7 @@
         <v/>
       </c>
       <c r="O7" s="98">
-        <f>IF($B$3=0,0,N7/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B7:M7,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62668,7 +63701,7 @@
         <v/>
       </c>
       <c r="O8" s="98">
-        <f>IF($B$3=0,0,N8/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B8:M8,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62731,7 +63764,7 @@
         <v/>
       </c>
       <c r="O9" s="98">
-        <f>IF($B$3=0,0,N9/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B9:M9,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62794,7 +63827,7 @@
         <v/>
       </c>
       <c r="O10" s="100">
-        <f>IF($B$3=0,0,N10/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B10:M10,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62857,7 +63890,7 @@
         <v/>
       </c>
       <c r="O11" s="96">
-        <f>IF($B$3=0,0,N11/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B11:M11,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -62920,7 +63953,7 @@
         <v/>
       </c>
       <c r="O12" s="102">
-        <f>IF(N5=0,"",N11/N5)</f>
+        <f>IF(O5=0,"",O11/O5)</f>
         <v/>
       </c>
     </row>
@@ -62983,7 +64016,7 @@
         <v/>
       </c>
       <c r="O13" s="98">
-        <f>IF($B$3=0,0,N13/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B13:M13,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63046,7 +64079,7 @@
         <v/>
       </c>
       <c r="O14" s="98">
-        <f>IF($B$3=0,0,N14/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B14:M14,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63109,7 +64142,7 @@
         <v/>
       </c>
       <c r="O15" s="98">
-        <f>IF($B$3=0,0,N15/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B15:M15,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63172,7 +64205,7 @@
         <v/>
       </c>
       <c r="O16" s="98">
-        <f>IF($B$3=0,0,N16/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B16:M16,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63235,7 +64268,7 @@
         <v/>
       </c>
       <c r="O17" s="98">
-        <f>IF($B$3=0,0,N17/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B17:M17,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63298,7 +64331,7 @@
         <v/>
       </c>
       <c r="O18" s="98">
-        <f>IF($B$3=0,0,N18/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B18:M18,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63361,7 +64394,7 @@
         <v/>
       </c>
       <c r="O19" s="98">
-        <f>IF($B$3=0,0,N19/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B19:M19,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63424,7 +64457,7 @@
         <v/>
       </c>
       <c r="O20" s="98">
-        <f>IF($B$3=0,0,N20/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B20:M20,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63487,7 +64520,7 @@
         <v/>
       </c>
       <c r="O21" s="98">
-        <f>IF($B$3=0,0,N21/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B21:M21,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63550,7 +64583,7 @@
         <v/>
       </c>
       <c r="O22" s="98">
-        <f>IF($B$3=0,0,N22/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B22:M22,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63613,14 +64646,14 @@
         <v/>
       </c>
       <c r="O23" s="100">
-        <f>IF($B$3=0,0,N23/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B23:M23,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="157">
       <c r="A24" s="103" t="inlineStr">
         <is>
-          <t>(=) RESULTADO DO MÊS</t>
+          <t>(=) RESULTADO DA LOJA (antes do pró-labore)</t>
         </is>
       </c>
       <c r="B24" s="104">
@@ -63676,7 +64709,7 @@
         <v/>
       </c>
       <c r="O24" s="104">
-        <f>IF($B$3=0,0,N24/$B$3)</f>
+        <f>IF($B$3=0,0,SUMPRODUCT(B24:M24,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
@@ -63739,194 +64772,370 @@
         <v/>
       </c>
       <c r="O25" s="102">
-        <f>IF(N5=0,"",N24/N5)</f>
+        <f>IF(O5=0,"",O24/O5)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="105" t="inlineStr">
-        <is>
-          <t>MEMÓRIA (não entram no resultado da loja)</t>
-        </is>
-      </c>
-      <c r="B26" s="106" t="n"/>
-      <c r="C26" s="106" t="n"/>
-      <c r="D26" s="106" t="n"/>
-      <c r="E26" s="106" t="n"/>
-      <c r="F26" s="106" t="n"/>
-      <c r="G26" s="106" t="n"/>
-      <c r="H26" s="106" t="n"/>
-      <c r="I26" s="106" t="n"/>
-      <c r="J26" s="106" t="n"/>
-      <c r="K26" s="106" t="n"/>
-      <c r="L26" s="106" t="n"/>
-      <c r="M26" s="106" t="n"/>
-      <c r="N26" s="106" t="n"/>
-      <c r="O26" s="106" t="n"/>
+      <c r="A26" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Pró-labore Edilânia (tudo o que ela gastou do dinheiro da loja)</t>
+        </is>
+      </c>
+      <c r="B26" s="98">
+        <f>'Jan 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="C26" s="98">
+        <f>'Fev 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="D26" s="98">
+        <f>'Mar 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="E26" s="98">
+        <f>'Abr 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="F26" s="98">
+        <f>'Mai 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="G26" s="98">
+        <f>'Jun 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="H26" s="98">
+        <f>'Jul 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="I26" s="98">
+        <f>'Ago 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="J26" s="98">
+        <f>'Set 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="K26" s="98">
+        <f>'Out 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="L26" s="98">
+        <f>'Nov 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="M26" s="98">
+        <f>'Dez 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="N26" s="98">
+        <f>SUM(B26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="98">
+        <f>IF($B$3=0,0,SUMPRODUCT(B26:M26,$B$38:$M$38)/$B$3)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Pro Labore Edilânia (retirada dos sócios / despesas pessoais)</t>
-        </is>
-      </c>
-      <c r="B27" s="108">
-        <f>'Jan 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="C27" s="108">
-        <f>'Fev 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="D27" s="108">
-        <f>'Mar 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="E27" s="108">
-        <f>'Abr 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="F27" s="108">
-        <f>'Mai 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="G27" s="108">
-        <f>'Jun 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="H27" s="108">
-        <f>'Jul 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="I27" s="108">
-        <f>'Ago 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="J27" s="108">
-        <f>'Set 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="K27" s="108">
-        <f>'Out 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="L27" s="108">
-        <f>'Nov 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="M27" s="108">
-        <f>'Dez 2026'!L17</f>
-        <v/>
-      </c>
-      <c r="N27" s="108">
+      <c r="A27" s="242" t="inlineStr">
+        <is>
+          <t>(=) SOBRA FINAL (depois do pró-labore)</t>
+        </is>
+      </c>
+      <c r="B27" s="243">
+        <f>B24-B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="243">
+        <f>C24-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="243">
+        <f>D24-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="243">
+        <f>E24-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="243">
+        <f>F24-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="243">
+        <f>G24-G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="243">
+        <f>H24-H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="243">
+        <f>I24-I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="243">
+        <f>J24-J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="243">
+        <f>K24-K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="243">
+        <f>L24-L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="243">
+        <f>M24-M26</f>
+        <v/>
+      </c>
+      <c r="N27" s="243">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="O27" s="108">
-        <f>IF($B$3=0,0,N27/$B$3)</f>
+      <c r="O27" s="243">
+        <f>IF($B$3=0,0,SUMPRODUCT(B27:M27,$B$38:$M$38)/$B$3)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="107" t="inlineStr">
+      <c r="A28" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Combinado com ela: sobrou (+) ou passou (−) do combinado</t>
+        </is>
+      </c>
+      <c r="B28" s="244">
+        <f>IF(B5=0,"",'Ponto de Equilíbrio'!$B$10-B26)</f>
+        <v/>
+      </c>
+      <c r="C28" s="244">
+        <f>IF(C5=0,"",'Ponto de Equilíbrio'!$B$10-C26)</f>
+        <v/>
+      </c>
+      <c r="D28" s="244">
+        <f>IF(D5=0,"",'Ponto de Equilíbrio'!$B$10-D26)</f>
+        <v/>
+      </c>
+      <c r="E28" s="244">
+        <f>IF(E5=0,"",'Ponto de Equilíbrio'!$B$10-E26)</f>
+        <v/>
+      </c>
+      <c r="F28" s="244">
+        <f>IF(F5=0,"",'Ponto de Equilíbrio'!$B$10-F26)</f>
+        <v/>
+      </c>
+      <c r="G28" s="244">
+        <f>IF(G5=0,"",'Ponto de Equilíbrio'!$B$10-G26)</f>
+        <v/>
+      </c>
+      <c r="H28" s="244">
+        <f>IF(H5=0,"",'Ponto de Equilíbrio'!$B$10-H26)</f>
+        <v/>
+      </c>
+      <c r="I28" s="244">
+        <f>IF(I5=0,"",'Ponto de Equilíbrio'!$B$10-I26)</f>
+        <v/>
+      </c>
+      <c r="J28" s="244">
+        <f>IF(J5=0,"",'Ponto de Equilíbrio'!$B$10-J26)</f>
+        <v/>
+      </c>
+      <c r="K28" s="244">
+        <f>IF(K5=0,"",'Ponto de Equilíbrio'!$B$10-K26)</f>
+        <v/>
+      </c>
+      <c r="L28" s="244">
+        <f>IF(L5=0,"",'Ponto de Equilíbrio'!$B$10-L26)</f>
+        <v/>
+      </c>
+      <c r="M28" s="244">
+        <f>IF(M5=0,"",'Ponto de Equilíbrio'!$B$10-M26)</f>
+        <v/>
+      </c>
+      <c r="N28" s="244">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="244">
+        <f>IF($B$3=0,0,SUMPRODUCT(B28:M28,$B$38:$M$38)/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="27.95" customHeight="1" s="157">
+      <c r="A30" s="105" t="inlineStr">
+        <is>
+          <t>MEMÓRIA (não entra no resultado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="27.95" customHeight="1" s="157">
+      <c r="A31" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">   Despesas da loja pagas com Capital de Giro (BB) — dívida a devolver</t>
         </is>
       </c>
-      <c r="B28" s="108">
+      <c r="B31" s="108">
         <f>'Jan 2026'!L19</f>
         <v/>
       </c>
-      <c r="C28" s="108">
+      <c r="C31" s="108">
         <f>'Fev 2026'!L19</f>
         <v/>
       </c>
-      <c r="D28" s="108">
+      <c r="D31" s="108">
         <f>'Mar 2026'!L19</f>
         <v/>
       </c>
-      <c r="E28" s="108">
+      <c r="E31" s="108">
         <f>'Abr 2026'!L19</f>
         <v/>
       </c>
-      <c r="F28" s="108">
+      <c r="F31" s="108">
         <f>'Mai 2026'!L19</f>
         <v/>
       </c>
-      <c r="G28" s="108">
+      <c r="G31" s="108">
         <f>'Jun 2026'!L19</f>
         <v/>
       </c>
-      <c r="H28" s="108">
+      <c r="H31" s="108">
         <f>'Jul 2026'!L19</f>
         <v/>
       </c>
-      <c r="I28" s="108">
+      <c r="I31" s="108">
         <f>'Ago 2026'!L19</f>
         <v/>
       </c>
-      <c r="J28" s="108">
+      <c r="J31" s="108">
         <f>'Set 2026'!L19</f>
         <v/>
       </c>
-      <c r="K28" s="108">
+      <c r="K31" s="108">
         <f>'Out 2026'!L19</f>
         <v/>
       </c>
-      <c r="L28" s="108">
+      <c r="L31" s="108">
         <f>'Nov 2026'!L19</f>
         <v/>
       </c>
-      <c r="M28" s="108">
+      <c r="M31" s="108">
         <f>'Dez 2026'!L19</f>
         <v/>
       </c>
-      <c r="N28" s="108">
-        <f>SUM(B28:M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="108">
-        <f>IF($B$3=0,0,N28/$B$3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="27.95" customHeight="1" s="157">
-      <c r="A30" s="182" t="inlineStr">
+      <c r="N31" s="108">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="108">
+        <f>IF($B$3=0,0,SUMPRODUCT(B31:M31,$B$38:$M$38)/$B$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="27.95" customHeight="1" s="157"/>
+    <row r="33" ht="28" customHeight="1" s="157">
+      <c r="A33" s="182" t="inlineStr">
         <is>
           <t>Custos Variáveis = sobem/descem com o volume vendido: mercadoria, imposto sobre faturamento (DAS), transporte ligado ao serviço e as comissões do Wiliam (só existem quando tem troca/instalação). Custos Fixos = o que a loja paga mesmo vendendo pouco (aluguel, energia, salários, contabilidade, tarifas e o estacionamento, contratado no mês).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="27.95" customHeight="1" s="157">
-      <c r="A31" s="182" t="inlineStr">
+    <row r="34" ht="28" customHeight="1" s="157">
+      <c r="A34" s="182" t="inlineStr">
         <is>
           <t>A Receita de Ago–Dez já está líquida: descontadas as taxas de máquina e as vendas ainda não recebidas (A Receber).</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="27.95" customHeight="1" s="157">
-      <c r="A32" s="182" t="inlineStr">
-        <is>
-          <t>A "Média/mês" divide pelo número de meses que já tiveram movimento (célula B3) — meses ainda não lançados não puxam a média para baixo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="27.95" customHeight="1" s="157">
-      <c r="A33" s="196" t="inlineStr">
+    <row r="35" ht="28" customHeight="1" s="157">
+      <c r="A35" s="182" t="inlineStr">
+        <is>
+          <t>A "Média/mês" divide só pelos meses JÁ FECHADOS (linha 38 = 1). O mês em andamento fica fora da média até terminar, para um mês pela metade não puxar o número para baixo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="157">
+      <c r="A36" s="182" t="inlineStr">
         <is>
           <t>ATENÇÃO — este DRE é por COMPETÊNCIA: considera a despesa no mês em que ela aconteceu, mesmo que tenha sido paga pelo Capital de Giro do BB. Por isso o Resultado aqui é menor que o cartão SALDO da aba do mês e que o Lucro do Dashboard, que são CAIXA puro. A diferença está na linha 28.</t>
         </is>
       </c>
     </row>
+    <row r="37" ht="28" customHeight="1" s="157">
+      <c r="A37" s="182" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE: tudo o que a Edilânia gasta do dinheiro da loja (contas da casa, Pix pessoais, mercado, diarista...) é o pró-labore dela. O combinado é o valor da célula B10 da aba "Ponto de Equilíbrio" (R$ 4.000,00/mês desde 05/10/2026). A linha 28 mostra, mês a mês, se sobrou ou se passou do combinado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="101" t="inlineStr">
+        <is>
+          <t>Entra na média? (1 = mês já fechado e com movimento)</t>
+        </is>
+      </c>
+      <c r="B38" s="245">
+        <f>IF(AND(B5&gt;0,1&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="245">
+        <f>IF(AND(C5&gt;0,2&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="245">
+        <f>IF(AND(D5&gt;0,3&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="245">
+        <f>IF(AND(E5&gt;0,4&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="245">
+        <f>IF(AND(F5&gt;0,5&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="245">
+        <f>IF(AND(G5&gt;0,6&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="245">
+        <f>IF(AND(H5&gt;0,7&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="I38" s="245">
+        <f>IF(AND(I5&gt;0,8&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="J38" s="245">
+        <f>IF(AND(J5&gt;0,9&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="K38" s="245">
+        <f>IF(AND(K5&gt;0,10&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="245">
+        <f>IF(AND(L5&gt;0,11&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+      <c r="M38" s="245">
+        <f>IF(AND(M5&gt;0,12&lt;IF(YEAR(TODAY())&gt;2026,13,MONTH(TODAY()))),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A35:O35"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A33:O33"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A34:O34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" location="'Início'!A1" display="← Início"/>
@@ -68919,7 +70128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" style="157" min="1" max="1"/>
@@ -68939,7 +70148,7 @@
     <row r="2">
       <c r="A2" s="218" t="inlineStr">
         <is>
-          <t>Quanto a loja precisa faturar por mês só para não ter prejuízo — e quanto precisa vender para lucrar o que você quiser. Base: média dos meses já lançados em 2026.</t>
+          <t>Quanto a loja precisa faturar por mês para pagar todas as contas E o pró-labore da Edilânia, sem prejuízo. Base: média dos meses já fechados em 2026 (o mês em andamento só entra na média quando terminar).</t>
         </is>
       </c>
     </row>
@@ -69009,7 +70218,7 @@
     <row r="9">
       <c r="A9" s="52" t="inlineStr">
         <is>
-          <t>Custos fixos médios</t>
+          <t>Custos fixos da loja (média por mês)</t>
         </is>
       </c>
       <c r="B9" s="55">
@@ -69018,160 +70227,132 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
-        <is>
-          <t>PONTO DE EQUILÍBRIO (faturamento mínimo/mês)</t>
-        </is>
-      </c>
-      <c r="B10" s="60">
-        <f>IF(B8&lt;=0,"",B9/B8)</f>
-        <v/>
+      <c r="A10" s="130" t="inlineStr">
+        <is>
+          <t>Pró-labore combinado da Edilânia (por mês)</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C10" s="131" t="inlineStr">
+        <is>
+          <t>← valor combinado em 05/10/2026. Se o combinado mudar, troque só aqui — a planilha e o site usam este número.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="inlineStr">
-        <is>
-          <t>Resultado médio atual</t>
-        </is>
-      </c>
-      <c r="B11" s="55">
+      <c r="A11" s="246" t="inlineStr">
+        <is>
+          <t>Total a pagar por mês (custos fixos + pró-labore)</t>
+        </is>
+      </c>
+      <c r="B11" s="247">
+        <f>B9+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>PONTO DE EQUILÍBRIO (faturamento mínimo/mês, já pagando a Edilânia)</t>
+        </is>
+      </c>
+      <c r="B12" s="60">
+        <f>IF(B8&lt;=0,"",B11/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>Sobra média da loja ANTES do pró-labore</t>
+        </is>
+      </c>
+      <c r="B13" s="55">
         <f>'DRE Simplificado'!O24</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="246" t="inlineStr">
+        <is>
+          <t>Sobra média DEPOIS do pró-labore combinado</t>
+        </is>
+      </c>
+      <c r="B14" s="247">
+        <f>B13-B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="157"/>
+    <row r="16" ht="30" customHeight="1" s="157">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>Ticket médio da loja (preencha)</t>
         </is>
       </c>
-      <c r="B13" s="65" t="n">
+      <c r="B16" s="65" t="n">
         <v>140</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>← valor médio de uma venda. Serve para converter R$ em nº de vendas.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="157">
-      <c r="A15" s="66" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>QUANTO PRECISO VENDER PARA...</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="157">
-      <c r="A16" s="51" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="157">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="B16" s="51" t="inlineStr">
-        <is>
-          <t>Lucro desejado (R$)</t>
-        </is>
-      </c>
-      <c r="C16" s="51" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>Lucro desejado (R$) — além do pró-labore</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>Faturamento necessário (R$)</t>
         </is>
       </c>
-      <c r="D16" s="51" t="inlineStr">
+      <c r="D19" s="51" t="inlineStr">
         <is>
           <t>Nº de vendas no mês</t>
         </is>
       </c>
-      <c r="E16" s="51" t="inlineStr">
+      <c r="E19" s="51" t="inlineStr">
         <is>
           <t>Vendas por dia útil (26 dias)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="52" t="inlineStr">
-        <is>
-          <t>Não ter prejuízo (equilíbrio)</t>
-        </is>
-      </c>
-      <c r="B17" s="55" t="n">
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>Pagar tudo e a Edilânia (sem prejuízo)</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="55">
-        <f>IF($B$8&lt;=0,"",($B$9+B17)/$B$8)</f>
-        <v/>
-      </c>
-      <c r="D17" s="56">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C17/$B$13,0))</f>
-        <v/>
-      </c>
-      <c r="E17" s="56">
-        <f>IF(D17="","",ROUND(D17/26,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="54" t="inlineStr">
-        <is>
-          <t>Lucrar R$ 500</t>
-        </is>
-      </c>
-      <c r="B18" s="57" t="n">
-        <v>500</v>
-      </c>
-      <c r="C18" s="57">
-        <f>IF($B$8&lt;=0,"",($B$9+B18)/$B$8)</f>
-        <v/>
-      </c>
-      <c r="D18" s="58">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C18/$B$13,0))</f>
-        <v/>
-      </c>
-      <c r="E18" s="58">
-        <f>IF(D18="","",ROUND(D18/26,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="52" t="inlineStr">
-        <is>
-          <t>Lucrar R$ 1.000</t>
-        </is>
-      </c>
-      <c r="B19" s="55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C19" s="55">
-        <f>IF($B$8&lt;=0,"",($B$9+B19)/$B$8)</f>
-        <v/>
-      </c>
-      <c r="D19" s="56">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C19/$B$13,0))</f>
-        <v/>
-      </c>
-      <c r="E19" s="56">
-        <f>IF(D19="","",ROUND(D19/26,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="54" t="inlineStr">
-        <is>
-          <t>Lucrar R$ 2.000</t>
-        </is>
-      </c>
-      <c r="B20" s="57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C20" s="57">
-        <f>IF($B$8&lt;=0,"",($B$9+B20)/$B$8)</f>
-        <v/>
-      </c>
-      <c r="D20" s="58">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C20/$B$13,0))</f>
-        <v/>
-      </c>
-      <c r="E20" s="58">
+      <c r="C20" s="55">
+        <f>IF($B$8&lt;=0,"",($B$11+B20)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D20" s="56">
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C20/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="E20" s="56">
         <f>IF(D20="","",ROUND(D20/26,1))</f>
         <v/>
       </c>
@@ -69179,18 +70360,18 @@
     <row r="21">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>Lucrar R$ 3.000</t>
+          <t>Lucrar R$ 500</t>
         </is>
       </c>
       <c r="B21" s="55" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="C21" s="55">
-        <f>IF($B$8&lt;=0,"",($B$9+B21)/$B$8)</f>
+        <f>IF($B$8&lt;=0,"",($B$11+B21)/$B$8)</f>
         <v/>
       </c>
       <c r="D21" s="56">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C21/$B$13,0))</f>
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C21/$B$16,0))</f>
         <v/>
       </c>
       <c r="E21" s="56">
@@ -69199,36 +70380,110 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
+        <is>
+          <t>Lucrar R$ 1.000</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C22" s="55">
+        <f>IF($B$8&lt;=0,"",($B$11+B22)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D22" s="56">
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C22/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="E22" s="56">
+        <f>IF(D22="","",ROUND(D22/26,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>Lucrar R$ 2.000</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C23" s="55">
+        <f>IF($B$8&lt;=0,"",($B$11+B23)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D23" s="56">
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C23/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="E23" s="56">
+        <f>IF(D23="","",ROUND(D23/26,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>Lucrar R$ 3.000</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="55">
+        <f>IF($B$8&lt;=0,"",($B$11+B24)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D24" s="56">
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C24/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="E24" s="56">
+        <f>IF(D24="","",ROUND(D24/26,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Lucrar R$ 5.000</t>
         </is>
       </c>
-      <c r="B22" s="57" t="n">
+      <c r="B25" s="55" t="n">
         <v>5000</v>
       </c>
-      <c r="C22" s="57">
-        <f>IF($B$8&lt;=0,"",($B$9+B22)/$B$8)</f>
-        <v/>
-      </c>
-      <c r="D22" s="58">
-        <f>IF(OR($B$8&lt;=0,$B$13=0),"",ROUNDUP(C22/$B$13,0))</f>
-        <v/>
-      </c>
-      <c r="E22" s="58">
-        <f>IF(D22="","",ROUND(D22/26,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="217">
-        <f>IF(B8&lt;=0,"⚠ ATENÇÃO: a margem de contribuição está negativa ou zerada — os custos variáveis estão consumindo toda a receita. Enquanto isso não for corrigido (preço, frete ou custo de compra), não existe ponto de equilíbrio possível.","✔ Margem de contribuição positiva: cada R$ 100 vendidos deixam R$ "&amp;TEXT(B8*100,"0.00")&amp;" para pagar os custos fixos e gerar lucro.")</f>
-        <v/>
+      <c r="C25" s="55">
+        <f>IF($B$8&lt;=0,"",($B$11+B25)/$B$8)</f>
+        <v/>
+      </c>
+      <c r="D25" s="56">
+        <f>IF(OR($B$8&lt;=0,$B$16=0),"",ROUNDUP(C25/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="E25" s="56">
+        <f>IF(D25="","",ROUND(D25/26,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="217">
+        <f>IF(B8&lt;=0,"⚠ ATENÇÃO: a margem de contribuição está negativa ou zerada — os custos variáveis estão consumindo toda a receita. Enquanto isso não for corrigido (preço, frete ou custo de compra), não existe ponto de equilíbrio possível.","✔ Margem de contribuição positiva: cada R$ 100 vendidos deixam R$ "&amp;TEXT(B8*100,"0.00")&amp;" para pagar os custos fixos, o pró-labore e gerar lucro.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" s="157">
+      <c r="A28" s="248" t="inlineStr">
+        <is>
+          <t>O pró-labore da Edilânia é tudo o que ela gasta do dinheiro da loja (categoria "Pro Labore Edilânia" nas abas dos meses). Por isso ele entra aqui como uma conta fixa: a loja só está "no zero a zero" quando paga todas as despesas E os R$ combinados com ela.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A24:H24"/>
+  <mergeCells count="4">
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -69263,7 +70518,7 @@
     <row r="2">
       <c r="A2" s="218" t="inlineStr">
         <is>
-          <t>Projeção do saldo dos próximos meses. As previsões vêm da média de Jan–Ago; edite as células amarelas com o que você já sabe que vai entrar ou sair.</t>
+          <t>Projeção do saldo dos próximos meses. As previsões vêm da média dos meses já fechados; edite as células amarelas com o que você já sabe que vai entrar ou sair.</t>
         </is>
       </c>
     </row>
@@ -69336,7 +70591,7 @@
         <v/>
       </c>
       <c r="D7" s="65">
-        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23+'Ponto de Equilíbrio'!$B$10)</f>
         <v/>
       </c>
       <c r="E7" s="55">
@@ -69362,7 +70617,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="65">
-        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23+'Ponto de Equilíbrio'!$B$10)</f>
         <v/>
       </c>
       <c r="E8" s="57">
@@ -69388,7 +70643,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="65">
-        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23+'Ponto de Equilíbrio'!$B$10)</f>
         <v/>
       </c>
       <c r="E9" s="55">
@@ -69414,7 +70669,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="65">
-        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23)</f>
+        <f>('DRE Simplificado'!O10+'DRE Simplificado'!O23+'Ponto de Equilíbrio'!$B$10)</f>
         <v/>
       </c>
       <c r="E10" s="57">
@@ -69470,7 +70725,7 @@
     <row r="16">
       <c r="A16" s="219" t="inlineStr">
         <is>
-          <t>Saídas previstas = custos variáveis médios + custos fixos médios (aba DRE). As contas a receber pendentes entram uma única vez, em setembro, pois são vendas já feitas.</t>
+          <t>Saídas previstas = custos variáveis médios + custos fixos médios (aba DRE) + pró-labore combinado da Edilânia. As contas a receber pendentes entram uma única vez, em setembro, pois são vendas já feitas.</t>
         </is>
       </c>
     </row>
@@ -69546,11 +70801,11 @@
     <row r="6">
       <c r="A6" s="54" t="inlineStr">
         <is>
-          <t>Custo fixo médio mensal (aluguel, energia, salários, contabilidade...)</t>
+          <t>Custo fixo médio mensal + pró-labore combinado da Edilânia</t>
         </is>
       </c>
       <c r="B6" s="57">
-        <f>'DRE Simplificado'!O23</f>
+        <f>'DRE Simplificado'!O23+'Ponto de Equilíbrio'!$B$10</f>
         <v/>
       </c>
     </row>
@@ -69711,7 +70966,7 @@
     <row r="24">
       <c r="A24" s="219" t="inlineStr">
         <is>
-          <t>A reserva ideal cobre só os custos fixos. Se quiser cobrir também a compra de mercadoria, aumente os meses de cobertura.</t>
+          <t>A reserva ideal cobre os custos fixos E o pró-labore da Edilânia. Se quiser cobrir também a compra de mercadoria, aumente os meses de cobertura.</t>
         </is>
       </c>
     </row>
@@ -70178,18 +71433,45 @@
       </c>
       <c r="F21" s="59" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Pró-labore Edilânia (combinado)</t>
+        </is>
+      </c>
+      <c r="B22" s="57">
+        <f>'Ponto de Equilíbrio'!$B$10</f>
+        <v/>
+      </c>
+      <c r="C22" s="57">
+        <f>'Ago 2026'!L17</f>
+        <v/>
+      </c>
+      <c r="D22" s="57">
+        <f>C22-B22</f>
+        <v/>
+      </c>
+      <c r="E22" s="64">
+        <f>IF(B22=0,"",C22/B22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="54">
+        <f>IF(B22=0,"",IF(C22&lt;=B22,"✔ Dentro do combinado","Passou "&amp;TEXT(C22-B22,"R$ #,##0.00")))</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="59" t="inlineStr">
         <is>
-          <t>RESULTADO (Faturamento − Despesas)</t>
+          <t>RESULTADO (Faturamento − Despesas − Pró-labore)</t>
         </is>
       </c>
       <c r="B23" s="60">
-        <f>B5-B21</f>
+        <f>B5-B21-B22</f>
         <v/>
       </c>
       <c r="C23" s="60">
-        <f>C5-C21</f>
+        <f>C5-C21-C22</f>
         <v/>
       </c>
       <c r="D23" s="60">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D6" s="119" t="inlineStr">
         <is>
-          <t>SOBRA FINAL (DEPOIS DA EDILÂNIA)</t>
+          <t>SOBRA FINAL (DEPOIS DO PRÓ-LABORE)</t>
         </is>
       </c>
       <c r="E6" s="120" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G10" s="117" t="inlineStr">
         <is>
-          <t>SOBRA MÉDIA/MÊS DEPOIS DELA</t>
+          <t>SOBRA MÉDIA/MÊS DEPOIS DO PRÓ-LABORE</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -38343,7 +38343,7 @@
       <c r="D4" s="160" t="n"/>
       <c r="E4" s="181" t="inlineStr">
         <is>
-          <t>SOBRA FINAL (DEPOIS DA EDILÂNIA)</t>
+          <t>SOBRA FINAL (DEPOIS DO PRÓ-LABORE)</t>
         </is>
       </c>
       <c r="F4" s="160" t="n"/>
@@ -38417,19 +38417,19 @@
     </row>
     <row r="9">
       <c r="A9" s="178">
-        <f>"Melhor mês (sobra final, depois da Edilânia): "&amp;INDEX(A24:A35,MATCH(MAX(G24:G35),G24:G35,0))&amp;" ("&amp;TEXT(MAX(G24:G35),"R$ #,##0.00")&amp;")"</f>
+        <f>"Melhor mês (sobra final, depois do pró-labore): "&amp;INDEX(A24:A35,MATCH(MAX(G24:G35),G24:G35,0))&amp;" ("&amp;TEXT(MAX(G24:G35),"R$ #,##0.00")&amp;")"</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="178">
-        <f>"Mês mais fraco (sobra final, depois da Edilânia): "&amp;INDEX(A24:A35,MATCH(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),G24:G35,0))&amp;" ("&amp;TEXT(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),"R$ #,##0.00")&amp;")"</f>
+        <f>"Mês mais fraco (sobra final, depois do pró-labore): "&amp;INDEX(A24:A35,MATCH(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),G24:G35,0))&amp;" ("&amp;TEXT(_xlfn.MINIFS(G24:G35,B24:B35,"&lt;&gt;0"),"R$ #,##0.00")&amp;")"</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="178">
-        <f>"Meses que fecharam no negativo depois de pagar a Edilânia: "&amp;COUNTIF(G24:G35,"&lt;0")&amp;" de "&amp;COUNTIF(B24:B35,"&lt;&gt;0")&amp;" meses com dados  ·  pró-labore do ano: "&amp;TEXT(F36,"R$ #,##0.00")&amp;" (combinado: "&amp;TEXT('Ponto de Equilíbrio'!$B$10,"R$ #,##0.00")&amp;"/mês)"</f>
+        <f>"Meses que fecharam no negativo depois do pró-labore: "&amp;COUNTIF(G24:G35,"&lt;0")&amp;" de "&amp;COUNTIF(B24:B35,"&lt;&gt;0")&amp;" meses com dados  ·  pró-labore do ano: "&amp;TEXT(F36,"R$ #,##0.00")&amp;" (combinado: "&amp;TEXT('Ponto de Equilíbrio'!$B$10,"R$ #,##0.00")&amp;"/mês)"</f>
         <v/>
       </c>
     </row>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="R4" s="221" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="207" t="inlineStr">
@@ -45345,7 +45345,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -53053,7 +53053,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -56878,7 +56878,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -60162,7 +60162,7 @@
       </c>
       <c r="R4" s="199" t="inlineStr">
         <is>
-          <t>SALDO (ANTES DA EDILÂNIA)</t>
+          <t>SALDO ANTES DO PRÓ-LABORE</t>
         </is>
       </c>
       <c r="T4" s="206" t="inlineStr">
@@ -70255,7 +70255,7 @@
     <row r="12">
       <c r="A12" s="59" t="inlineStr">
         <is>
-          <t>PONTO DE EQUILÍBRIO (faturamento mínimo/mês, já pagando a Edilânia)</t>
+          <t>PONTO DE EQUILÍBRIO (faturamento mínimo/mês, já pagando o pró-labore)</t>
         </is>
       </c>
       <c r="B12" s="60">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51780,36 +51780,16 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="17" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B211" s="18" t="inlineStr">
-        <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
-        </is>
-      </c>
-      <c r="C211" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D211" s="27" t="n">
-        <v>140</v>
-      </c>
-      <c r="E211" s="18" t="inlineStr">
-        <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
+      <c r="A211" s="17" t="n"/>
+      <c r="B211" s="18" t="n"/>
+      <c r="C211" s="18" t="n"/>
+      <c r="D211" s="27" t="n"/>
+      <c r="E211" s="18" t="n"/>
       <c r="F211" s="19" t="n"/>
       <c r="G211" s="19" t="n"/>
       <c r="H211" s="21" t="n"/>
       <c r="I211" s="18" t="n"/>
-      <c r="J211" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0032</t>
-        </is>
-      </c>
+      <c r="J211" s="18" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="44" t="n">
@@ -53282,7 +53262,7 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
@@ -53295,11 +53275,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F9" s="19" t="n"/>
@@ -53307,7 +53287,7 @@
       <c r="H9" s="21" t="n"/>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>Troca na casa (Loteamento Morada Real, Caeira) — segundo purificador; o da Vivencie Turismo foi trocado em 29/09/2026.</t>
+          <t>Venda de 01/10/2026 (troca na casa, Loteamento Morada Real, Caeira) — pagamento recebido via Pix em 05/10/2026. Pix único de R$ 270,00 da Aneilde em 05/10/2026 pagando as duas trocas (casa + Vivencie Turismo), com R$ 10,00 de desconto dividido entre as duas (R$ 135,00 cada).</t>
         </is>
       </c>
       <c r="J9" s="18" t="inlineStr">
@@ -54112,16 +54092,40 @@
       <c r="I32" s="45" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n"/>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="18" t="n"/>
+      <c r="A33" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>135</v>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="21" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 29/09/2026 (troca na Vivencie Turismo, antes em Set 2026) — pagamento recebido via Pix em 05/10/2026. Pix único de R$ 270,00 da Aneilde em 05/10/2026 pagando as duas trocas (casa + Vivencie Turismo), com R$ 10,00 de desconto dividido entre as duas (R$ 135,00 cada).</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="44" t="n"/>
@@ -69434,7 +69438,7 @@
       </c>
       <c r="E146" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F146" s="112">
@@ -69443,7 +69447,7 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026.</t>
+          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
@@ -69530,7 +69534,7 @@
       </c>
       <c r="E149" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F149" s="112">
@@ -69539,7 +69543,7 @@
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 01/10/2026 (casa, Caeira).</t>
+          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54128,15 +54128,36 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="n"/>
-      <c r="B34" s="45" t="n"/>
-      <c r="C34" s="45" t="n"/>
-      <c r="D34" s="46" t="n"/>
-      <c r="E34" s="45" t="n"/>
+      <c r="A34" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>Carneiro Ultra Drogaria LTDA - Filial 01</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro + Botão Everest</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="n">
+        <v>230</v>
+      </c>
+      <c r="E34" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F34" s="47" t="n"/>
       <c r="G34" s="48" t="n"/>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="45" t="n"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>EMP-0043</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -53376,7 +53376,7 @@
     </row>
     <row r="12">
       <c r="A12" s="44" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
@@ -53393,15 +53393,17 @@
       </c>
       <c r="E12" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
-      <c r="F12" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F12" s="47" t="n">
+        <v>16.76</v>
+      </c>
       <c r="G12" s="48" t="n"/>
       <c r="H12" s="49" t="n"/>
       <c r="I12" s="45" t="inlineStr">
         <is>
-          <t>Subsolo — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada).</t>
+          <t>Venda de 01/10/2026 — pagamento recebido em 05/10/2026 no crédito em 3x. Subsolo — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada). Pagamento único de R$ 400,00 (subsolo + 1º andar), taxa total R$ 33,52 dividida entre as duas linhas.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -53875,7 +53877,7 @@
     </row>
     <row r="26">
       <c r="A26" s="44" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
@@ -53892,15 +53894,17 @@
       </c>
       <c r="E26" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
-      <c r="F26" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>16.76</v>
+      </c>
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
       <c r="I26" s="45" t="inlineStr">
         <is>
-          <t>1º Andar — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada).</t>
+          <t>Venda de 02/10/2026 — pagamento recebido em 05/10/2026 no crédito em 3x. 1º Andar — troca do refil (R$ 140,00) + troca dos 2 botões do purificador (R$ 30,00 cada). Pagamento único de R$ 400,00 (subsolo + 1º andar), taxa total R$ 33,52 dividida entre as duas linhas.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -54160,11 +54164,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="18" t="n"/>
+      <c r="A35" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Refil PA 200 FIT</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="21" t="n"/>
@@ -54172,27 +54192,70 @@
       <c r="J35" s="18" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="n"/>
-      <c r="B36" s="45" t="n"/>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="45" t="n"/>
-      <c r="F36" s="47" t="n"/>
+      <c r="A36" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B36" s="45" t="inlineStr">
+        <is>
+          <t>Luiza Exdra Carneiro</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E36" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F36" s="47" t="n">
+        <v>4.91</v>
+      </c>
       <c r="G36" s="48" t="n"/>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="45" t="n"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CLI-0056</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="n"/>
-      <c r="B37" s="18" t="n"/>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="18" t="n"/>
+      <c r="A37" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Igreja Messianica Mundial do Brasil</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n"/>
       <c r="H37" s="21" t="n"/>
       <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0177</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="44" t="n"/>
@@ -65176,7 +65239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -69587,7 +69650,7 @@
       </c>
       <c r="E150" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F150" s="112">
@@ -69596,7 +69659,7 @@
       </c>
       <c r="G150" s="78" t="inlineStr">
         <is>
-          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões).</t>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
@@ -69619,7 +69682,7 @@
       </c>
       <c r="E151" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F151" s="112">
@@ -69628,48 +69691,79 @@
       </c>
       <c r="G151" s="78" t="inlineStr">
         <is>
-          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões).</t>
+          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="152" s="157">
-      <c r="A152" s="86" t="inlineStr">
+      <c r="A152" s="78" t="inlineStr">
+        <is>
+          <t>Igreja Messiânica Mundial do Brasil</t>
+        </is>
+      </c>
+      <c r="B152" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C152" s="77" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D152" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E152" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F152" s="112">
+        <f>IF(OR($E152="Recebido",$C152=""),"",MAX(0,TODAY()-$C152))</f>
+        <v/>
+      </c>
+      <c r="G152" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" s="157">
+      <c r="A153" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D152" s="115">
-        <f>SUMIF(E101:E151,"Pendente",D101:D151)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" s="157">
-      <c r="A153" s="202" t="inlineStr">
+      <c r="D153" s="115">
+        <f>SUMIF(E101:E152,"Pendente",D101:D152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" s="157">
+      <c r="A154" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B153" s="159" t="n"/>
-      <c r="C153" s="159" t="n"/>
-      <c r="D153" s="159" t="n"/>
-      <c r="E153" s="159" t="n"/>
-      <c r="F153" s="159" t="n"/>
-      <c r="G153" s="160" t="n"/>
-    </row>
-    <row r="154" s="157">
-      <c r="A154" s="203">
-        <f>IF(ROUND(D152-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D152-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B154" s="159" t="n"/>
+      <c r="C154" s="159" t="n"/>
+      <c r="D154" s="159" t="n"/>
+      <c r="E154" s="159" t="n"/>
+      <c r="F154" s="159" t="n"/>
+      <c r="G154" s="160" t="n"/>
     </row>
     <row r="155" s="157">
-      <c r="A155" s="203" t="inlineStr">
+      <c r="A155" s="203">
+        <f>IF(ROUND(D153-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D153-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" s="157">
+      <c r="A156" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="156" s="157"/>
     <row r="157" s="157"/>
     <row r="158" s="157"/>
     <row r="159" s="157"/>
@@ -69729,16 +69823,16 @@
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A153:G153"/>
     <mergeCell ref="A98:G98"/>
     <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A155:G155"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E101:E151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E101:E152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -48035,36 +48035,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="81" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B84" s="82" t="inlineStr">
-        <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
-        </is>
-      </c>
-      <c r="C84" s="82" t="inlineStr">
-        <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D84" s="83" t="n">
-        <v>370</v>
-      </c>
-      <c r="E84" s="82" t="inlineStr">
-        <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
+      <c r="A84" s="81" t="n"/>
+      <c r="B84" s="82" t="n"/>
+      <c r="C84" s="82" t="n"/>
+      <c r="D84" s="83" t="n"/>
+      <c r="E84" s="82" t="n"/>
       <c r="F84" s="83" t="n"/>
       <c r="G84" s="83" t="n"/>
       <c r="H84" s="82" t="n"/>
       <c r="I84" s="82" t="n"/>
-      <c r="J84" s="82" t="inlineStr">
-        <is>
-          <t>EMP-0291</t>
-        </is>
-      </c>
+      <c r="J84" s="82" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="77" t="n">
@@ -54258,84 +54238,208 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="n"/>
-      <c r="B38" s="45" t="n"/>
+      <c r="A38" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
       <c r="C38" s="45" t="n"/>
       <c r="D38" s="46" t="n"/>
       <c r="E38" s="45" t="n"/>
       <c r="F38" s="47" t="n"/>
-      <c r="G38" s="48" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="45" t="n"/>
+      <c r="G38" s="48" t="n">
+        <v>980.8099999999999</v>
+      </c>
+      <c r="H38" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I38" s="45" t="inlineStr">
+        <is>
+          <t>Boleto Itaú — NF-e 72869 (emissão 07/05/2026), parcela 5/5 (última), vencimento 04/10/2026 (domingo), pago em 05/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="18" t="n"/>
+      <c r="A39" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Topvel Tropical Veiculos e Pecas</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>370</v>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F39" s="19" t="n"/>
       <c r="G39" s="19" t="n"/>
       <c r="H39" s="21" t="n"/>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="18" t="n"/>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 11/09/2026 (troca nos dois purificadores) — pagamento recebido via TED no BNB em 05/10/2026 (DOC 7793462). Antes em Set 2026.</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0291</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="44" t="n"/>
-      <c r="B40" s="45" t="n"/>
-      <c r="C40" s="45" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="45" t="n"/>
+      <c r="A40" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>Piantare Soluções Ambientais</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>Bebedouro Industrial 100L</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="n">
+        <v>2840</v>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F40" s="47" t="n"/>
       <c r="G40" s="48" t="n"/>
       <c r="H40" s="49" t="n"/>
-      <c r="I40" s="45" t="n"/>
+      <c r="I40" s="45" t="inlineStr">
+        <is>
+          <t>Pagamento recebido via Pix no BNB em 05/10/2026 (DOC 7758853).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="18" t="n"/>
+      <c r="A41" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Tarifa Pix (Cobrança QR Code)</t>
+        </is>
+      </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="27" t="n"/>
       <c r="E41" s="18" t="n"/>
       <c r="F41" s="19" t="n"/>
-      <c r="G41" s="19" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="18" t="n"/>
+      <c r="G41" s="19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>Extrato BNB — TAR PIX COBR QR COD LIQUI, DOC 7417524</t>
+        </is>
+      </c>
       <c r="J41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="44" t="n"/>
-      <c r="B42" s="45" t="n"/>
+      <c r="A42" s="44" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="C42" s="45" t="n"/>
       <c r="D42" s="46" t="n"/>
       <c r="E42" s="45" t="n"/>
       <c r="F42" s="47" t="n"/>
-      <c r="G42" s="48" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="45" t="n"/>
+      <c r="G42" s="48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H42" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I42" s="45" t="inlineStr">
+        <is>
+          <t>Pix da conta Ton/Stone para Edilânia em 05/10/2026 — pró-labore (informado pela Edilânia).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="18" t="n"/>
+      <c r="A43" s="17" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Piso vinílico</t>
+        </is>
+      </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="27" t="n"/>
       <c r="E43" s="18" t="n"/>
       <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="18" t="n"/>
+      <c r="G43" s="19" t="n">
+        <v>124.72</v>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>Despesa da loja (informada pela Edilânia em 05/10/2026).</t>
+        </is>
+      </c>
       <c r="J43" s="18" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="n"/>
-      <c r="B44" s="45" t="n"/>
+      <c r="A44" s="44" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>Marcos Pereira Cirqueira</t>
+        </is>
+      </c>
       <c r="C44" s="45" t="n"/>
       <c r="D44" s="46" t="n"/>
       <c r="E44" s="45" t="n"/>
       <c r="F44" s="47" t="n"/>
-      <c r="G44" s="48" t="n"/>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="45" t="n"/>
+      <c r="G44" s="48" t="n">
+        <v>35</v>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I44" s="45" t="inlineStr">
+        <is>
+          <t>Pix da conta Ton/Stone em 03/10/2026 — gasto pessoal da Edilânia.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -65973,7 +66077,7 @@
       </c>
       <c r="E30" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F30" s="113">
@@ -65982,7 +66086,7 @@
       </c>
       <c r="G30" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 72869 (emissão 07/05/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260508782043000188550060000728691612874239.</t>
+          <t>Pago em 05/10/2026 — lançado em "Out 2026" como "Eversoft" (R$ 980,81). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 72869 (emissão 07/05/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260508782043000188550060000728691612874239.</t>
         </is>
       </c>
     </row>
@@ -69202,7 +69306,7 @@
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F136" s="112">
@@ -69211,7 +69315,7 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores.</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
@@ -70180,13 +70284,15 @@
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>A Devolver</t>
-        </is>
-      </c>
-      <c r="F16" s="40" t="n"/>
+          <t>Devolvido</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>46300</v>
+      </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Pago pelo Adriano via Pix do Banco do Brasil com dinheiro da reserva — 30/09/2026</t>
+          <t>Pago pelo Adriano via Pix do Banco do Brasil com dinheiro da reserva — 30/09/2026. Devolvido em 05/10/2026: a loja transferiu R$ 6.000,00 (conta Ton/Stone → Adriano → Banco do Brasil), sendo R$ 3.272,00 desta devolução e R$ 2.728,00 para a reserva.</t>
         </is>
       </c>
     </row>
@@ -70961,11 +71067,11 @@
         </is>
       </c>
       <c r="B9" s="109" t="n">
-        <v>22728</v>
+        <v>28728</v>
       </c>
       <c r="C9" s="131" t="inlineStr">
         <is>
-          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Pix do BNB para Adriano guardados como reserva (confirmado pela Edilânia em 30/09/2026): R$ 500,00 em 11/09 e R$ 2.000,00 em 25/09. Em 30/09/2026 saíram R$ 3.272,00 da reserva para pagar 2 bebedouros industriais da Knox (a loja deve devolver — ver aba Capital de Giro (BB)). Total guardado: R$ 22.728,00. Em aberto: Pix de R$ 2.000,00 para Adriano em 09/09 — confirmar se já faz parte dos R$ 6.500,00 do mesmo dia.</t>
+          <t>Aporte de Adriano em 03/09/2026: R$ 17.000,00 (R$ 8.135,48 desse valor quitou o saldo devedor do Capital de Giro (BB) — como o Capital de Giro É a reserva do Banco do Brasil, esse dinheiro voltou para a própria reserva ao quitar a dívida). Em 09/09/2026, retirada de R$ 6.500,00 do caixa da loja para a reserva — transferência entre contas da empresa, por isso não foi lançada como saída nas abas mensais. Pix do BNB para Adriano guardados como reserva (confirmado pela Edilânia em 30/09/2026): R$ 500,00 em 11/09 e R$ 2.000,00 em 25/09. Em 30/09/2026 saíram R$ 3.272,00 da reserva para pagar 2 bebedouros industriais da Knox (a loja deve devolver — ver aba Capital de Giro (BB)). Em 05/10/2026 a loja transferiu R$ 6.000,00 para a reserva no Banco do Brasil (via Pix para o Adriano): R$ 3.272,00 devolvendo o que a reserva pagou à Knox + R$ 2.728,00 a mais guardados. Total guardado: R$ 28.728,00. Em aberto: Pix de R$ 2.000,00 para Adriano em 09/09 — confirmar se já faz parte dos R$ 6.500,00 do mesmo dia.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -52633,36 +52633,15 @@
       <c r="J241" s="18" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="44" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B242" s="45" t="inlineStr">
-        <is>
-          <t>PC Jacobina Administradora de Cartões LTDA</t>
-        </is>
-      </c>
-      <c r="C242" s="45" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D242" s="46" t="n">
-        <v>140</v>
-      </c>
-      <c r="E242" s="45" t="inlineStr">
-        <is>
-          <t>Aguardando Pagamento</t>
-        </is>
-      </c>
+      <c r="A242" s="44" t="n"/>
+      <c r="B242" s="45" t="n"/>
+      <c r="C242" s="45" t="n"/>
+      <c r="D242" s="46" t="n"/>
+      <c r="E242" s="45" t="n"/>
       <c r="F242" s="47" t="n"/>
       <c r="G242" s="48" t="n"/>
       <c r="H242" s="49" t="n"/>
       <c r="I242" s="45" t="n"/>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>EMP-0244</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" s="17" t="n"/>
@@ -53829,7 +53808,7 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>Valeriana Studio - Juscelia</t>
+          <t>Juscelia Valeriana (Studio)</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
@@ -53944,7 +53923,7 @@
       </c>
       <c r="I28" s="45" t="inlineStr">
         <is>
-          <t>Etanol — Posto da Praça (Lubrinessa XVI Comércio de Petróleo LTDA, CNPJ 29.922.765/0002-41, Rua Dois de Julho, 70, Centro, Jacobina). Segundo abastecimento do dia.</t>
+          <t>Etanol 2,181 L a R$ 4,59/L — Posto da Praça (Lubrinessa XVI Comércio de Petróleo LTDA, CNPJ 29.922.765/0002-41, Praça 2 de Julho, 70, Centro, Jacobina), NFC-e nº 000385581 de 02/10/2026 12:10 (nota de R$ 10,01). Pago R$ 10,00 em dinheiro.</t>
         </is>
       </c>
     </row>
@@ -54442,61 +54421,158 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="18" t="n"/>
+      <c r="A45" s="17" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Fiolaser Spa (Spa Requião Marques Ltda)</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Conexão Reta Rosca + Mangueira + Serviço</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F45" s="19" t="n"/>
       <c r="G45" s="19" t="n"/>
       <c r="H45" s="21" t="n"/>
-      <c r="I45" s="18" t="n"/>
-      <c r="J45" s="18" t="n"/>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>Conexão reta rosca R$ 25,00 + mangueira R$ 10,00 + serviço R$ 20,00. Cliente também instalou Refil E3.</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0319</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="n"/>
-      <c r="B46" s="45" t="n"/>
+      <c r="A46" s="44" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>Conta de Energia Adriano</t>
+        </is>
+      </c>
       <c r="C46" s="45" t="n"/>
       <c r="D46" s="46" t="n"/>
       <c r="E46" s="45" t="n"/>
       <c r="F46" s="47" t="n"/>
-      <c r="G46" s="48" t="n"/>
-      <c r="H46" s="49" t="n"/>
-      <c r="I46" s="45" t="n"/>
+      <c r="G46" s="48" t="n">
+        <v>435.34</v>
+      </c>
+      <c r="H46" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I46" s="45" t="inlineStr">
+        <is>
+          <t>Neoenergia Coelba — conta pessoal do Adriano (não é da loja), ref. 09/2026, UC 5.158.506.028-83, NF 996180107. Inclui multas/juros de faturas anteriores. Venc. 06/10/2026, pago em 06/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="18" t="n"/>
+      <c r="A47" s="17" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="27" t="n"/>
       <c r="E47" s="18" t="n"/>
       <c r="F47" s="19" t="n"/>
-      <c r="G47" s="19" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="18" t="n"/>
+      <c r="G47" s="19" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>NF 133138 parcela 3/4 — boleto Itaú nosso número 109/00257851-4. Venc. 07/10/2026, pago antecipado em 06/10/2026.</t>
+        </is>
+      </c>
       <c r="J47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="n"/>
-      <c r="B48" s="45" t="n"/>
-      <c r="C48" s="45" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="45" t="n"/>
+      <c r="A48" s="44" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B48" s="45" t="inlineStr">
+        <is>
+          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
+        </is>
+      </c>
+      <c r="C48" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F48" s="47" t="n"/>
       <c r="G48" s="48" t="n"/>
       <c r="H48" s="49" t="n"/>
-      <c r="I48" s="45" t="n"/>
+      <c r="I48" s="45" t="inlineStr">
+        <is>
+          <t>Venda de 30/09/2026 (troca na PC Jacobina / Cartão de Todos, antes em Set 2026) — pagamento recebido via Pix em 06/10/2026.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>EMP-0244</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="18" t="n"/>
+      <c r="A49" s="17" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Velas Tripla Ação</t>
+        </is>
+      </c>
       <c r="C49" s="18" t="n"/>
       <c r="D49" s="27" t="n"/>
       <c r="E49" s="18" t="n"/>
       <c r="F49" s="19" t="n"/>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="18" t="n"/>
+      <c r="G49" s="19" t="n">
+        <v>121.05</v>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>Compra de velas tripla ação (vela filtro 3 ações). Boleto pago em 06/10/2026 — beneficiário Maree Instituição de Pagamento Ltda (CNPJ 38.372.267/0001-82), descrição "VELAS 3 ACAO". Pagadora: Edilânia.</t>
+        </is>
+      </c>
       <c r="J49" s="18" t="n"/>
     </row>
     <row r="50">
@@ -65343,7 +65419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -65394,7 +65470,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D95</f>
+        <f>D96</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -66973,7 +67049,7 @@
       </c>
       <c r="E58" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F58" s="113">
@@ -66982,7 +67058,7 @@
       </c>
       <c r="G58" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Pago em 06/10/2026 (antecipado, venc. 07/10) — lançado em "Out 2026" como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
         </is>
       </c>
     </row>
@@ -67773,7 +67849,7 @@
       </c>
       <c r="E83" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F83" s="112">
@@ -67782,7 +67858,7 @@
       </c>
       <c r="G83" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Pro Labore Edilânia. Fatura residencial em nome de Adriano Silva Fontes (Rua Irmã Lúcia de Fátima, 283 — Mundo Novo), UC 5.158.506.028-83, NF 996180107. Inclui multas/juros de faturas anteriores. Boleto Itaú 341, linha digitável 34191.75207 56491.952935 85832.220009 5 15910000043534. PDF (sem senha) salvo em "boletos planeta agua/Coelba Adriano - venc 06-10-2026.pdf".</t>
+          <t>Categoria: Pro Labore Edilânia. Pago em 06/10/2026 — lançado em "Out 2026" como "Conta de Energia Adriano". Fatura residencial em nome de Adriano Silva Fontes (Rua Irmã Lúcia de Fátima, 283 — Mundo Novo), UC 5.158.506.028-83, NF 996180107. Inclui multas/juros de faturas anteriores. Boleto Itaú 341, linha digitável 34191.75207 56491.952935 85832.220009 5 15910000043534. PDF (sem senha) salvo em "boletos planeta agua/Coelba Adriano - venc 06-10-2026.pdf".</t>
         </is>
       </c>
     </row>
@@ -68075,1010 +68151,1010 @@
       </c>
     </row>
     <row r="93" s="157">
-      <c r="A93" s="86" t="inlineStr">
+      <c r="A93" s="82" t="inlineStr">
+        <is>
+          <t>Neoenergia Coelba</t>
+        </is>
+      </c>
+      <c r="B93" s="82" t="inlineStr">
+        <is>
+          <t>Energia elétrica da loja — REF 09/2026 (fatura em nome de Vitória Maria / Planeta Água)</t>
+        </is>
+      </c>
+      <c r="C93" s="81" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D93" s="83" t="n">
+        <v>168.56</v>
+      </c>
+      <c r="E93" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F93" s="113">
+        <f>IF(OR($E93="Pago",$C93=""),"",MAX(0,TODAY()-$C93))</f>
+        <v/>
+      </c>
+      <c r="G93" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Água, Energia e Internet. Fatura em nome de Vitoria Maria de Freitas Santos (Rua Manoel Novaes, 263, SL-3 — a loja), UC 7.908.588.028-80, NF 996962199, consumo 125 kWh (27/08 a 28/09/2026), bandeira amarela. Boleto Itaú 341. Linha digitável (conferida no PDF da fatura): 34191.75215 02379.112937 85832.220009 3 15920000016856. PDF salvo em "boletos planeta agua/Coelba Loja - venc 07-10-2026.pdf". Código para débito automático: 7044847005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" s="157">
+      <c r="A94" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B93" s="86" t="n"/>
-      <c r="C93" s="114" t="n"/>
-      <c r="D93" s="115">
-        <f>SUMIF(E11:E92,"Pendente",D11:D92)</f>
-        <v/>
-      </c>
-      <c r="E93" s="116" t="n"/>
-      <c r="F93" s="116" t="n"/>
-      <c r="G93" s="86" t="n"/>
-    </row>
-    <row r="94" s="157">
-      <c r="A94" s="144" t="inlineStr">
+      <c r="B94" s="86" t="n"/>
+      <c r="C94" s="114" t="n"/>
+      <c r="D94" s="115">
+        <f>SUMIF(E11:E93,"Pendente",D11:D93)</f>
+        <v/>
+      </c>
+      <c r="E94" s="116" t="n"/>
+      <c r="F94" s="116" t="n"/>
+      <c r="G94" s="86" t="n"/>
+    </row>
+    <row r="95" s="157">
+      <c r="A95" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B94" s="144" t="n"/>
-      <c r="C94" s="145" t="n"/>
-      <c r="D94" s="146">
-        <f>SUMIF(E11:E92,"Previsto",D11:D92)</f>
-        <v/>
-      </c>
-      <c r="E94" s="142" t="n"/>
-      <c r="F94" s="142" t="n"/>
-      <c r="G94" s="144" t="n"/>
-    </row>
-    <row r="95" s="157">
-      <c r="A95" s="86" t="inlineStr">
+      <c r="B95" s="144" t="n"/>
+      <c r="C95" s="145" t="n"/>
+      <c r="D95" s="146">
+        <f>SUMIF(E11:E93,"Previsto",D11:D93)</f>
+        <v/>
+      </c>
+      <c r="E95" s="142" t="n"/>
+      <c r="F95" s="142" t="n"/>
+      <c r="G95" s="144" t="n"/>
+    </row>
+    <row r="96" s="157">
+      <c r="A96" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B95" s="86" t="n"/>
-      <c r="C95" s="114" t="n"/>
-      <c r="D95" s="115">
-        <f>D93+D94</f>
-        <v/>
-      </c>
-      <c r="E95" s="116" t="n"/>
-      <c r="F95" s="116" t="n"/>
-      <c r="G95" s="86" t="n"/>
-    </row>
-    <row r="96" s="157"/>
-    <row r="97" ht="15.75" customHeight="1" s="157"/>
-    <row r="98" ht="15.75" customHeight="1" s="157">
-      <c r="A98" s="200" t="inlineStr">
+      <c r="B96" s="86" t="n"/>
+      <c r="C96" s="114" t="n"/>
+      <c r="D96" s="115">
+        <f>D94+D95</f>
+        <v/>
+      </c>
+      <c r="E96" s="116" t="n"/>
+      <c r="F96" s="116" t="n"/>
+      <c r="G96" s="86" t="n"/>
+    </row>
+    <row r="97" s="157"/>
+    <row r="98" ht="15.75" customHeight="1" s="157"/>
+    <row r="99" ht="15.75" customHeight="1" s="157">
+      <c r="A99" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="99" s="157">
-      <c r="A99" s="194" t="inlineStr">
+    <row r="100" s="157">
+      <c r="A100" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="100" s="157">
-      <c r="A100" s="111" t="inlineStr">
+    <row r="101" s="157">
+      <c r="A101" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B100" s="111" t="inlineStr">
+      <c r="B101" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C100" s="111" t="inlineStr">
+      <c r="C101" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D100" s="111" t="inlineStr">
+      <c r="D101" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E100" s="111" t="inlineStr">
+      <c r="E101" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F100" s="111" t="inlineStr">
+      <c r="F101" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G100" s="111" t="inlineStr">
+      <c r="G101" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="101" s="157">
-      <c r="A101" s="78" t="inlineStr">
+    <row r="102" s="157">
+      <c r="A102" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B101" s="78" t="inlineStr">
+      <c r="B102" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C101" s="77" t="n">
+      <c r="C102" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D101" s="79" t="n">
+      <c r="D102" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E101" s="112" t="inlineStr">
+      <c r="E102" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F101" s="112">
-        <f>IF(OR($E101="Recebido",$C101=""),"",MAX(0,TODAY()-$C101))</f>
-        <v/>
-      </c>
-      <c r="G101" s="78" t="n"/>
-    </row>
-    <row r="102" s="157">
-      <c r="A102" s="82" t="inlineStr">
+      <c r="F102" s="112">
+        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="78" t="n"/>
+    </row>
+    <row r="103" s="157">
+      <c r="A103" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B102" s="82" t="inlineStr">
+      <c r="B103" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C102" s="81" t="n">
+      <c r="C103" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D102" s="83" t="n">
+      <c r="D103" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E102" s="113" t="inlineStr">
+      <c r="E103" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F102" s="113">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="82" t="n"/>
-    </row>
-    <row r="103" s="157">
-      <c r="A103" s="78" t="inlineStr">
+      <c r="F103" s="113">
+        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="82" t="n"/>
+    </row>
+    <row r="104" s="157">
+      <c r="A104" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B103" s="78" t="inlineStr">
+      <c r="B104" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C103" s="77" t="n">
+      <c r="C104" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D103" s="79" t="n">
+      <c r="D104" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E103" s="112" t="inlineStr">
+      <c r="E104" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F103" s="112">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="78" t="inlineStr">
+      <c r="F104" s="112">
+        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="104" s="157">
-      <c r="A104" s="82" t="inlineStr">
+    <row r="105" s="157">
+      <c r="A105" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B104" s="82" t="inlineStr">
+      <c r="B105" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C104" s="81" t="n">
+      <c r="C105" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D104" s="83" t="n">
+      <c r="D105" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E104" s="113" t="inlineStr">
+      <c r="E105" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F104" s="113">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="82" t="inlineStr">
+      <c r="F105" s="113">
+        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="105" s="157">
-      <c r="A105" s="78" t="inlineStr">
+    <row r="106" s="157">
+      <c r="A106" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B105" s="78" t="inlineStr">
+      <c r="B106" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C105" s="77" t="n">
+      <c r="C106" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D105" s="79" t="n">
+      <c r="D106" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E105" s="112" t="inlineStr">
+      <c r="E106" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F105" s="112">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="78" t="inlineStr">
+      <c r="F106" s="112">
+        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="106" s="157">
-      <c r="A106" s="82" t="inlineStr">
+    <row r="107" s="157">
+      <c r="A107" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B106" s="82" t="inlineStr">
+      <c r="B107" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C106" s="81" t="n">
+      <c r="C107" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D106" s="83" t="n">
+      <c r="D107" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E106" s="113" t="inlineStr">
+      <c r="E107" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F106" s="113">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="82" t="inlineStr">
+      <c r="F107" s="113">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="107" s="157">
-      <c r="A107" s="78" t="inlineStr">
+    <row r="108" s="157">
+      <c r="A108" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B107" s="78" t="inlineStr">
+      <c r="B108" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C107" s="77" t="n">
+      <c r="C108" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D107" s="79" t="n">
+      <c r="D108" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E107" s="112" t="inlineStr">
+      <c r="E108" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F107" s="112">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="78" t="inlineStr">
+      <c r="F108" s="112">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="108" s="157">
-      <c r="A108" s="82" t="inlineStr">
+    <row r="109" s="157">
+      <c r="A109" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B108" s="82" t="inlineStr">
+      <c r="B109" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C108" s="81" t="n">
+      <c r="C109" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D108" s="83" t="n">
+      <c r="D109" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E108" s="113" t="inlineStr">
+      <c r="E109" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="113">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="82" t="inlineStr">
+      <c r="F109" s="113">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="109" s="157">
-      <c r="A109" s="78" t="inlineStr">
+    <row r="110" s="157">
+      <c r="A110" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B109" s="78" t="inlineStr">
+      <c r="B110" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C109" s="77" t="n">
+      <c r="C110" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D109" s="79" t="n">
+      <c r="D110" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E109" s="112" t="inlineStr">
+      <c r="E110" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F109" s="112">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="78" t="inlineStr">
+      <c r="F110" s="112">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="110" s="157">
-      <c r="A110" s="82" t="inlineStr">
+    <row r="111" s="157">
+      <c r="A111" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B110" s="82" t="inlineStr">
+      <c r="B111" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C110" s="81" t="n">
+      <c r="C111" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D110" s="83" t="n">
+      <c r="D111" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E110" s="113" t="inlineStr">
+      <c r="E111" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F110" s="113">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="82" t="inlineStr">
+      <c r="F111" s="113">
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="111" s="157">
-      <c r="A111" s="78" t="inlineStr">
+    <row r="112" s="157">
+      <c r="A112" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B111" s="78" t="inlineStr">
+      <c r="B112" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C111" s="77" t="n">
+      <c r="C112" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D111" s="79" t="n">
+      <c r="D112" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E111" s="112" t="inlineStr">
+      <c r="E112" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="112">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="78" t="inlineStr">
+      <c r="F112" s="112">
+        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
+        <v/>
+      </c>
+      <c r="G112" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="112" s="157">
-      <c r="A112" s="82" t="inlineStr">
+    <row r="113" s="157">
+      <c r="A113" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B112" s="82" t="inlineStr">
+      <c r="B113" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C112" s="81" t="n">
+      <c r="C113" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D112" s="83" t="n">
+      <c r="D113" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E112" s="113" t="inlineStr">
+      <c r="E113" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F112" s="113">
-        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="82" t="inlineStr">
+      <c r="F113" s="113">
+        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="113" s="157">
-      <c r="A113" s="78" t="inlineStr">
+    <row r="114" s="157">
+      <c r="A114" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B113" s="78" t="inlineStr">
+      <c r="B114" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C113" s="77" t="n">
+      <c r="C114" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D113" s="79" t="n">
+      <c r="D114" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E113" s="112" t="inlineStr">
+      <c r="E114" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F113" s="112">
-        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="78" t="inlineStr">
+      <c r="F114" s="112">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="114" s="157">
-      <c r="A114" s="82" t="inlineStr">
+    <row r="115" s="157">
+      <c r="A115" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B114" s="82" t="inlineStr">
+      <c r="B115" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C114" s="81" t="n">
+      <c r="C115" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D114" s="83" t="n">
+      <c r="D115" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E114" s="113" t="inlineStr">
+      <c r="E115" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F114" s="113">
-        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="82" t="inlineStr">
+      <c r="F115" s="113">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="115" s="157">
-      <c r="A115" s="78" t="inlineStr">
+    <row r="116" s="157">
+      <c r="A116" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B115" s="78" t="inlineStr">
+      <c r="B116" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C115" s="77" t="n">
+      <c r="C116" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D115" s="79" t="n">
+      <c r="D116" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E115" s="112" t="inlineStr">
+      <c r="E116" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F115" s="112">
-        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="78" t="inlineStr">
+      <c r="F116" s="112">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="116" s="157">
-      <c r="A116" s="82" t="inlineStr">
+    <row r="117" s="157">
+      <c r="A117" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B116" s="82" t="inlineStr">
+      <c r="B117" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C116" s="81" t="n">
+      <c r="C117" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D116" s="83" t="n">
+      <c r="D117" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E116" s="113" t="inlineStr">
+      <c r="E117" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F116" s="113">
-        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="82" t="inlineStr">
+      <c r="F117" s="113">
+        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="117" s="157">
-      <c r="A117" s="78" t="inlineStr">
+    <row r="118" s="157">
+      <c r="A118" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B117" s="78" t="inlineStr">
+      <c r="B118" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C117" s="77" t="n">
+      <c r="C118" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D117" s="79" t="n">
+      <c r="D118" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E117" s="112" t="inlineStr">
+      <c r="E118" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F117" s="112">
-        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
-        <v/>
-      </c>
-      <c r="G117" s="78" t="inlineStr">
+      <c r="F118" s="112">
+        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="118" s="157">
-      <c r="A118" s="82" t="inlineStr">
+    <row r="119" s="157">
+      <c r="A119" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B118" s="82" t="inlineStr">
+      <c r="B119" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C118" s="81" t="n">
+      <c r="C119" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D118" s="83" t="n">
+      <c r="D119" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E118" s="113" t="inlineStr">
+      <c r="E119" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F118" s="113">
-        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
-        <v/>
-      </c>
-      <c r="G118" s="82" t="inlineStr">
+      <c r="F119" s="113">
+        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="119" s="157">
-      <c r="A119" s="78" t="inlineStr">
+    <row r="120" s="157">
+      <c r="A120" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B119" s="78" t="inlineStr">
+      <c r="B120" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C119" s="77" t="n">
+      <c r="C120" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D119" s="79" t="n">
+      <c r="D120" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E119" s="112" t="inlineStr">
+      <c r="E120" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F119" s="112">
-        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
-        <v/>
-      </c>
-      <c r="G119" s="78" t="inlineStr">
+      <c r="F120" s="112">
+        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
+        <v/>
+      </c>
+      <c r="G120" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="120" s="157">
-      <c r="A120" s="82" t="inlineStr">
+    <row r="121" s="157">
+      <c r="A121" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B120" s="82" t="inlineStr">
+      <c r="B121" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C120" s="81" t="n">
+      <c r="C121" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D120" s="83" t="n">
+      <c r="D121" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E120" s="113" t="inlineStr">
+      <c r="E121" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F120" s="113">
-        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
-        <v/>
-      </c>
-      <c r="G120" s="82" t="inlineStr">
+      <c r="F121" s="113">
+        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
+        <v/>
+      </c>
+      <c r="G121" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="121" s="157">
-      <c r="A121" s="78" t="inlineStr">
+    <row r="122" s="157">
+      <c r="A122" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B121" s="78" t="inlineStr">
+      <c r="B122" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C121" s="77" t="n">
+      <c r="C122" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D121" s="79" t="n">
+      <c r="D122" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E121" s="112" t="inlineStr">
+      <c r="E122" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F121" s="112">
-        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
-        <v/>
-      </c>
-      <c r="G121" s="78" t="inlineStr">
+      <c r="F122" s="112">
+        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
+        <v/>
+      </c>
+      <c r="G122" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="122" s="157">
-      <c r="A122" s="82" t="inlineStr">
+    <row r="123" s="157">
+      <c r="A123" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B122" s="82" t="inlineStr">
+      <c r="B123" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C122" s="81" t="n">
+      <c r="C123" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D122" s="83" t="n">
+      <c r="D123" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E122" s="113" t="inlineStr">
+      <c r="E123" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F122" s="113">
-        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
-        <v/>
-      </c>
-      <c r="G122" s="82" t="inlineStr">
+      <c r="F123" s="113">
+        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
+        <v/>
+      </c>
+      <c r="G123" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
-    <row r="123" s="157">
-      <c r="A123" s="78" t="inlineStr">
+    <row r="124" s="157">
+      <c r="A124" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B123" s="78" t="inlineStr">
+      <c r="B124" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C123" s="77" t="n">
+      <c r="C124" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D123" s="79" t="n">
+      <c r="D124" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E123" s="112" t="inlineStr">
+      <c r="E124" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F123" s="112">
-        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
-        <v/>
-      </c>
-      <c r="G123" s="78" t="inlineStr">
+      <c r="F124" s="112">
+        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
+        <v/>
+      </c>
+      <c r="G124" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
         </is>
       </c>
     </row>
-    <row r="124" s="157">
-      <c r="A124" s="82" t="inlineStr">
+    <row r="125" s="157">
+      <c r="A125" s="82" t="inlineStr">
         <is>
           <t>Instituto Paulo Leão</t>
         </is>
       </c>
-      <c r="B124" s="82" t="inlineStr">
+      <c r="B125" s="82" t="inlineStr">
         <is>
           <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
-      <c r="C124" s="81" t="n">
+      <c r="C125" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D124" s="83" t="n">
+      <c r="D125" s="83" t="n">
         <v>160</v>
       </c>
-      <c r="E124" s="113" t="inlineStr">
+      <c r="E125" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F124" s="113">
-        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
-        <v/>
-      </c>
-      <c r="G124" s="82" t="inlineStr">
+      <c r="F125" s="113">
+        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
+        <v/>
+      </c>
+      <c r="G125" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="125" s="157">
-      <c r="A125" s="78" t="inlineStr">
+    <row r="126" s="157">
+      <c r="A126" s="78" t="inlineStr">
         <is>
           <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
-      <c r="B125" s="78" t="inlineStr">
+      <c r="B126" s="78" t="inlineStr">
         <is>
           <t>Pré Filtro</t>
         </is>
       </c>
-      <c r="C125" s="77" t="n">
+      <c r="C126" s="77" t="n">
         <v>46265</v>
       </c>
-      <c r="D125" s="79" t="n">
+      <c r="D126" s="79" t="n">
         <v>60</v>
       </c>
-      <c r="E125" s="112" t="inlineStr">
+      <c r="E126" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F125" s="112">
-        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
-        <v/>
-      </c>
-      <c r="G125" s="78" t="inlineStr">
+      <c r="F126" s="112">
+        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
+        <v/>
+      </c>
+      <c r="G126" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="126" s="157">
-      <c r="A126" s="82" t="inlineStr">
+    <row r="127" s="157">
+      <c r="A127" s="82" t="inlineStr">
         <is>
           <t>Clube dos Mineiros</t>
         </is>
       </c>
-      <c r="B126" s="82" t="inlineStr">
+      <c r="B127" s="82" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C126" s="81" t="n">
+      <c r="C127" s="81" t="n">
         <v>46265</v>
       </c>
-      <c r="D126" s="83" t="n">
+      <c r="D127" s="83" t="n">
         <v>150</v>
       </c>
-      <c r="E126" s="113" t="inlineStr">
+      <c r="E127" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F126" s="113">
-        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
-        <v/>
-      </c>
-      <c r="G126" s="82" t="inlineStr">
+      <c r="F127" s="113">
+        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
+        <v/>
+      </c>
+      <c r="G127" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
-    <row r="127" s="157">
-      <c r="A127" s="78" t="inlineStr">
+    <row r="128" s="157">
+      <c r="A128" s="78" t="inlineStr">
         <is>
           <t>Armazem Cecilio Mota</t>
         </is>
       </c>
-      <c r="B127" s="78" t="inlineStr">
+      <c r="B128" s="78" t="inlineStr">
         <is>
           <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
-      <c r="C127" s="77" t="n">
+      <c r="C128" s="77" t="n">
         <v>46266</v>
       </c>
-      <c r="D127" s="79" t="n">
+      <c r="D128" s="79" t="n">
         <v>225</v>
       </c>
-      <c r="E127" s="112" t="inlineStr">
+      <c r="E128" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F127" s="112">
-        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
-        <v/>
-      </c>
-      <c r="G127" s="78" t="inlineStr">
+      <c r="F128" s="112">
+        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
+        <v/>
+      </c>
+      <c r="G128" s="78" t="inlineStr">
         <is>
           <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" s="157">
-      <c r="A128" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B128" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C128" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D128" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E128" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F128" s="113">
-        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
-        <v/>
-      </c>
-      <c r="G128" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="129" s="157">
       <c r="A129" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>Clebson Dantas Da Silva</t>
         </is>
       </c>
       <c r="B129" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C129" s="81" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D129" s="83" t="n">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="E129" s="113" t="inlineStr">
         <is>
@@ -69091,58 +69167,58 @@
       </c>
       <c r="G129" s="82" t="inlineStr">
         <is>
+          <t>Recebido via Pix em 02/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" s="157">
+      <c r="A130" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B130" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C130" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D130" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E130" s="113" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F130" s="113">
+        <f>IF(OR($E130="Recebido",$C130=""),"",MAX(0,TODAY()-$C130))</f>
+        <v/>
+      </c>
+      <c r="G130" s="82" t="inlineStr">
+        <is>
           <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" s="157">
-      <c r="A130" s="78" t="inlineStr">
-        <is>
-          <t>Cecilio Mota Junior</t>
-        </is>
-      </c>
-      <c r="B130" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C130" s="77" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D130" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E130" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F130" s="112">
-        <f>IF(OR($E130="Recebido",$C130=""),"",MAX(0,TODAY()-$C130))</f>
-        <v/>
-      </c>
-      <c r="G130" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="131" s="157">
       <c r="A131" s="78" t="inlineStr">
         <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B131" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C131" s="77" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D131" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E131" s="112" t="inlineStr">
         <is>
@@ -69155,26 +69231,26 @@
       </c>
       <c r="G131" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="132" s="157">
       <c r="A132" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B132" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C132" s="77" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="D132" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E132" s="112" t="inlineStr">
         <is>
@@ -69187,26 +69263,26 @@
       </c>
       <c r="G132" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="133" s="157">
       <c r="A133" s="78" t="inlineStr">
         <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B133" s="78" t="inlineStr">
         <is>
-          <t>Refil Plissado + Refil BAG</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C133" s="77" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="D133" s="79" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E133" s="112" t="inlineStr">
         <is>
@@ -69219,26 +69295,26 @@
       </c>
       <c r="G133" s="78" t="inlineStr">
         <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="134" s="157">
       <c r="A134" s="78" t="inlineStr">
         <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B134" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C134" s="77" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="D134" s="79" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E134" s="112" t="inlineStr">
         <is>
@@ -69251,26 +69327,26 @@
       </c>
       <c r="G134" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="135" s="157">
       <c r="A135" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B135" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C135" s="77" t="n">
         <v>46275</v>
       </c>
       <c r="D135" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E135" s="112" t="inlineStr">
         <is>
@@ -69290,19 +69366,19 @@
     <row r="136" s="157">
       <c r="A136" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B136" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C136" s="77" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D136" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
@@ -69315,26 +69391,26 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="137" s="157">
       <c r="A137" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B137" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C137" s="77" t="n">
         <v>46276</v>
       </c>
       <c r="D137" s="79" t="n">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="E137" s="112" t="inlineStr">
         <is>
@@ -69347,26 +69423,26 @@
       </c>
       <c r="G137" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="138" s="157">
       <c r="A138" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B138" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C138" s="77" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="D138" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E138" s="112" t="inlineStr">
         <is>
@@ -69379,26 +69455,26 @@
       </c>
       <c r="G138" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="139" s="157">
       <c r="A139" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B139" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C139" s="77" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="D139" s="79" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="E139" s="112" t="inlineStr">
         <is>
@@ -69411,26 +69487,26 @@
       </c>
       <c r="G139" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="140" s="157">
       <c r="A140" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B140" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C140" s="77" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="D140" s="79" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="E140" s="112" t="inlineStr">
         <is>
@@ -69443,26 +69519,26 @@
       </c>
       <c r="G140" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="141" s="157">
       <c r="A141" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Marilda Macedo / José Luciano Costa</t>
         </is>
       </c>
       <c r="B141" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C141" s="77" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="D141" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E141" s="112" t="inlineStr">
         <is>
@@ -69475,14 +69551,14 @@
       </c>
       <c r="G141" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="142" s="157">
       <c r="A142" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>Tatiana Rocha</t>
         </is>
       </c>
       <c r="B142" s="78" t="inlineStr">
@@ -69507,30 +69583,30 @@
       </c>
       <c r="G142" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="143" s="157">
       <c r="A143" s="78" t="inlineStr">
         <is>
-          <t>Centro de Especialidades Odontomédicas</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="B143" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C143" s="77" t="n">
-        <v>46044</v>
+        <v>46286</v>
       </c>
       <c r="D143" s="79" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E143" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F143" s="112">
@@ -69539,26 +69615,26 @@
       </c>
       <c r="G143" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="144" s="157">
       <c r="A144" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B144" s="78" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="C144" s="77" t="n">
-        <v>46073</v>
+        <v>46044</v>
       </c>
       <c r="D144" s="79" t="n">
-        <v>30</v>
+        <v>280</v>
       </c>
       <c r="E144" s="112" t="inlineStr">
         <is>
@@ -69571,26 +69647,26 @@
       </c>
       <c r="G144" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
         </is>
       </c>
     </row>
     <row r="145" s="157">
       <c r="A145" s="78" t="inlineStr">
         <is>
-          <t>Centro Médico de Jacobina</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B145" s="78" t="inlineStr">
         <is>
-          <t>2x Botão Completo</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="C145" s="77" t="n">
-        <v>46203</v>
+        <v>46073</v>
       </c>
       <c r="D145" s="79" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E145" s="112" t="inlineStr">
         <is>
@@ -69603,30 +69679,30 @@
       </c>
       <c r="G145" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="146" s="157">
       <c r="A146" s="78" t="inlineStr">
         <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+          <t>Centro Médico de Jacobina</t>
         </is>
       </c>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Botão Completo</t>
         </is>
       </c>
       <c r="C146" s="77" t="n">
-        <v>46294</v>
+        <v>46203</v>
       </c>
       <c r="D146" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E146" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F146" s="112">
@@ -69635,30 +69711,30 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="147" s="157">
       <c r="A147" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
         </is>
       </c>
       <c r="B147" s="78" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C147" s="77" t="n">
         <v>46294</v>
       </c>
       <c r="D147" s="79" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E147" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F147" s="112">
@@ -69667,26 +69743,26 @@
       </c>
       <c r="G147" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026.</t>
+          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
     <row r="148" s="157">
       <c r="A148" s="78" t="inlineStr">
         <is>
-          <t>PC Jacobina Administradora de Cartões LTDA</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B148" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil C+3</t>
         </is>
       </c>
       <c r="C148" s="77" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="D148" s="79" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="E148" s="112" t="inlineStr">
         <is>
@@ -69699,14 +69775,14 @@
       </c>
       <c r="G148" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 30/09/2026.</t>
+          <t>Pagamento previsto para 30/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="149" s="157">
       <c r="A149" s="78" t="inlineStr">
         <is>
-          <t>Aneilde Rios de Oliveira</t>
+          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
         </is>
       </c>
       <c r="B149" s="78" t="inlineStr">
@@ -69715,7 +69791,7 @@
         </is>
       </c>
       <c r="C149" s="77" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="D149" s="79" t="n">
         <v>140</v>
@@ -69731,26 +69807,26 @@
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>Troca do dia 30/09/2026. Recebido via Pix em 06/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="150" s="157">
       <c r="A150" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Aneilde Rios de Oliveira</t>
         </is>
       </c>
       <c r="B150" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C150" s="77" t="n">
         <v>46296</v>
       </c>
       <c r="D150" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E150" s="112" t="inlineStr">
         <is>
@@ -69763,7 +69839,7 @@
       </c>
       <c r="G150" s="78" t="inlineStr">
         <is>
-          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
@@ -69779,7 +69855,7 @@
         </is>
       </c>
       <c r="C151" s="77" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="D151" s="79" t="n">
         <v>200</v>
@@ -69795,30 +69871,30 @@
       </c>
       <c r="G151" s="78" t="inlineStr">
         <is>
-          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="152" s="157">
       <c r="A152" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
         </is>
       </c>
       <c r="B152" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life + 2x Botão Completo</t>
         </is>
       </c>
       <c r="C152" s="77" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="D152" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E152" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F152" s="112">
@@ -69827,48 +69903,79 @@
       </c>
       <c r="G152" s="78" t="inlineStr">
         <is>
+          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" s="157">
+      <c r="A153" s="78" t="inlineStr">
+        <is>
+          <t>Igreja Messiânica Mundial do Brasil</t>
+        </is>
+      </c>
+      <c r="B153" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C153" s="77" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D153" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E153" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F153" s="112">
+        <f>IF(OR($E153="Recebido",$C153=""),"",MAX(0,TODAY()-$C153))</f>
+        <v/>
+      </c>
+      <c r="G153" s="78" t="inlineStr">
+        <is>
           <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
         </is>
       </c>
     </row>
-    <row r="153" s="157">
-      <c r="A153" s="86" t="inlineStr">
+    <row r="154" s="157">
+      <c r="A154" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D153" s="115">
-        <f>SUMIF(E101:E152,"Pendente",D101:D152)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" s="157">
-      <c r="A154" s="202" t="inlineStr">
+      <c r="D154" s="115">
+        <f>SUMIF(E102:E153,"Pendente",D102:D153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" s="157">
+      <c r="A155" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B154" s="159" t="n"/>
-      <c r="C154" s="159" t="n"/>
-      <c r="D154" s="159" t="n"/>
-      <c r="E154" s="159" t="n"/>
-      <c r="F154" s="159" t="n"/>
-      <c r="G154" s="160" t="n"/>
-    </row>
-    <row r="155" s="157">
-      <c r="A155" s="203">
-        <f>IF(ROUND(D153-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D153-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
+      <c r="B155" s="159" t="n"/>
+      <c r="C155" s="159" t="n"/>
+      <c r="D155" s="159" t="n"/>
+      <c r="E155" s="159" t="n"/>
+      <c r="F155" s="159" t="n"/>
+      <c r="G155" s="160" t="n"/>
     </row>
     <row r="156" s="157">
-      <c r="A156" s="203" t="inlineStr">
+      <c r="A156" s="203">
+        <f>IF(ROUND(D154-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D154-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" s="157">
+      <c r="A157" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="157" s="157"/>
     <row r="158" s="157"/>
     <row r="159" s="157"/>
     <row r="160" s="157"/>
@@ -69922,21 +70029,21 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A154:G154"/>
+    <mergeCell ref="A100:G100"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A98:G98"/>
+    <mergeCell ref="A156:G156"/>
     <mergeCell ref="A99:G99"/>
     <mergeCell ref="A155:G155"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E101:E152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E102:E153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54576,12 +54576,30 @@
       <c r="J49" s="18" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="44" t="n"/>
-      <c r="B50" s="45" t="n"/>
-      <c r="C50" s="45" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="45" t="n"/>
-      <c r="F50" s="47" t="n"/>
+      <c r="A50" s="44" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C50" s="45" t="inlineStr">
+        <is>
+          <t>Refil E3</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E50" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="n">
+        <v>3.16</v>
+      </c>
       <c r="G50" s="48" t="n"/>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="45" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54605,27 +54605,78 @@
       <c r="I50" s="45" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="27" t="n"/>
-      <c r="E51" s="18" t="n"/>
+      <c r="A51" s="17" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Leonardo de Carvalho Cruz</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Instalação de Purificador + Refil E3</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
       <c r="H51" s="21" t="n"/>
-      <c r="I51" s="18" t="n"/>
-      <c r="J51" s="18" t="n"/>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>Instalação R$ 40,00 + Refil E3 R$ 90,00.</t>
+        </is>
+      </c>
+      <c r="J51" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0902</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="n"/>
-      <c r="B52" s="45" t="n"/>
-      <c r="C52" s="45" t="n"/>
-      <c r="D52" s="46" t="n"/>
-      <c r="E52" s="45" t="n"/>
-      <c r="F52" s="47" t="n"/>
+      <c r="A52" s="44" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>Eliene</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Baby Branco</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="n">
+        <v>420</v>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F52" s="47" t="n">
+        <v>33.52</v>
+      </c>
       <c r="G52" s="48" t="n"/>
       <c r="H52" s="49" t="n"/>
-      <c r="I52" s="45" t="n"/>
+      <c r="I52" s="45" t="inlineStr">
+        <is>
+          <t>Parcelado em 6x.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>CLI-0903</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54679,39 +54679,110 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="18" t="n"/>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="19" t="n"/>
+      <c r="A53" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>Guiomar Macedo Freire - Antonio vila</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>9.789999999999999</v>
+      </c>
       <c r="G53" s="19" t="n"/>
       <c r="H53" s="21" t="n"/>
-      <c r="I53" s="18" t="n"/>
-      <c r="J53" s="18" t="n"/>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>Parcelado em 2x.</t>
+        </is>
+      </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0041</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="n"/>
-      <c r="B54" s="45" t="n"/>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="46" t="n"/>
-      <c r="E54" s="45" t="n"/>
+      <c r="A54" s="44" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B54" s="45" t="inlineStr">
+        <is>
+          <t>Geisa Cunha Novais - Marcos</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E54" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F54" s="47" t="n"/>
       <c r="G54" s="48" t="n"/>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="45" t="n"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>CLI-0270</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="27" t="n"/>
-      <c r="E55" s="18" t="n"/>
+      <c r="A55" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Chapada Brindes</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>Purificador Everest Star Branco</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="n">
+        <v>1379</v>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F55" s="19" t="n"/>
       <c r="G55" s="19" t="n"/>
       <c r="H55" s="21" t="n"/>
-      <c r="I55" s="18" t="n"/>
-      <c r="J55" s="18" t="n"/>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>Valor da viagem incluso.</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0102</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54785,15 +54785,42 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="n"/>
-      <c r="B56" s="45" t="n"/>
-      <c r="C56" s="45" t="n"/>
-      <c r="D56" s="46" t="n"/>
-      <c r="E56" s="45" t="n"/>
-      <c r="F56" s="47" t="n"/>
+      <c r="A56" s="44" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>Gabriela Araujo</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Fit Prata</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="n">
+        <v>1486</v>
+      </c>
+      <c r="E56" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F56" s="47" t="n">
+        <v>207.89</v>
+      </c>
       <c r="G56" s="48" t="n"/>
       <c r="H56" s="49" t="n"/>
-      <c r="I56" s="45" t="n"/>
+      <c r="I56" s="45" t="inlineStr">
+        <is>
+          <t>Parcelado em 10x. Instalação na residência (Rua Miguel Guerrera, 92) em 10/10/2026.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>CLI-0038</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54823,61 +54823,141 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="18" t="n"/>
+      <c r="A57" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>Faça Feira Supermercado</t>
+        </is>
+      </c>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="27" t="n"/>
       <c r="E57" s="18" t="n"/>
       <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="21" t="n"/>
-      <c r="I57" s="18" t="n"/>
+      <c r="G57" s="19" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="H57" s="21" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>Copo descartável (Copo Bom) — pago em dinheiro. DAV 790260205.</t>
+        </is>
+      </c>
       <c r="J57" s="18" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="n"/>
-      <c r="B58" s="45" t="n"/>
+      <c r="A58" s="44" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="45" t="inlineStr">
+        <is>
+          <t>Conta de Energia Loja</t>
+        </is>
+      </c>
       <c r="C58" s="45" t="n"/>
       <c r="D58" s="46" t="n"/>
       <c r="E58" s="45" t="n"/>
       <c r="F58" s="47" t="n"/>
-      <c r="G58" s="48" t="n"/>
-      <c r="H58" s="49" t="n"/>
-      <c r="I58" s="45" t="n"/>
+      <c r="G58" s="48" t="n">
+        <v>168.56</v>
+      </c>
+      <c r="H58" s="49" t="inlineStr">
+        <is>
+          <t>Água, Energia e Internet</t>
+        </is>
+      </c>
+      <c r="I58" s="45" t="inlineStr">
+        <is>
+          <t>Neoenergia Coelba — ref. 09/2026, venc. 07/10/2026, pago em 08/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="18" t="n"/>
+      <c r="A59" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="27" t="n"/>
       <c r="E59" s="18" t="n"/>
       <c r="F59" s="19" t="n"/>
-      <c r="G59" s="19" t="n"/>
-      <c r="H59" s="21" t="n"/>
-      <c r="I59" s="18" t="n"/>
+      <c r="G59" s="19" t="n">
+        <v>878.92</v>
+      </c>
+      <c r="H59" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>Boleto Itaú — NF-e 73636 (emissão 10/06/2026), parcela 4/5, vencimento 08/10/2026, pago em 08/10/2026.</t>
+        </is>
+      </c>
       <c r="J59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="n"/>
-      <c r="B60" s="45" t="n"/>
+      <c r="A60" s="44" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B60" s="45" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
       <c r="C60" s="45" t="n"/>
       <c r="D60" s="46" t="n"/>
       <c r="E60" s="45" t="n"/>
       <c r="F60" s="47" t="n"/>
-      <c r="G60" s="48" t="n"/>
-      <c r="H60" s="49" t="n"/>
-      <c r="I60" s="45" t="n"/>
+      <c r="G60" s="48" t="n">
+        <v>500.81</v>
+      </c>
+      <c r="H60" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I60" s="45" t="inlineStr">
+        <is>
+          <t>NF 133812 parcela 2 — boleto Itaú. Venc. 09/10/2026, pago antecipado em 08/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="18" t="n"/>
+      <c r="A61" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Celular da Loja</t>
+        </is>
+      </c>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="27" t="n"/>
       <c r="E61" s="18" t="n"/>
       <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="21" t="n"/>
-      <c r="I61" s="18" t="n"/>
+      <c r="G61" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H61" s="21" t="inlineStr">
+        <is>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>Recarga Claro (74) 98858-2298 via RecargaPay na Drogaria Mais Farma — ID 000074730.</t>
+        </is>
+      </c>
       <c r="J61" s="18" t="n"/>
     </row>
     <row r="62">
@@ -66352,7 +66432,7 @@
       </c>
       <c r="E31" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F31" s="112">
@@ -66361,7 +66441,7 @@
       </c>
       <c r="G31" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Eversoft". Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
         </is>
       </c>
     </row>
@@ -67632,7 +67712,7 @@
       </c>
       <c r="E71" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F71" s="113">
@@ -67641,7 +67721,7 @@
       </c>
       <c r="G71" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -68336,7 +68416,7 @@
       </c>
       <c r="E93" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F93" s="113">
@@ -68345,7 +68425,7 @@
       </c>
       <c r="G93" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Água, Energia e Internet. Fatura em nome de Vitoria Maria de Freitas Santos (Rua Manoel Novaes, 263, SL-3 — a loja), UC 7.908.588.028-80, NF 996962199, consumo 125 kWh (27/08 a 28/09/2026), bandeira amarela. Boleto Itaú 341. Linha digitável (conferida no PDF da fatura): 34191.75215 02379.112937 85832.220009 3 15920000016856. PDF salvo em "boletos planeta agua/Coelba Loja - venc 07-10-2026.pdf". Código para débito automático: 7044847005.</t>
+          <t>Categoria: Água, Energia e Internet. Pago em 08/10/2026 — lançado em Out 2026 como "Conta de Energia Loja". Fatura em nome de Vitoria Maria de Freitas Santos (Rua Manoel Novaes, 263, SL-3 — a loja), UC 7.908.588.028-80, NF 996962199, consumo 125 kWh (27/08 a 28/09/2026), bandeira amarela. Boleto Itaú 341. Linha digitável (conferida no PDF da fatura): 34191.75215 02379.112937 85832.220009 3 15920000016856. PDF salvo em "boletos planeta agua/Coelba Loja - venc 07-10-2026.pdf". Código para débito automático: 7044847005.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54961,50 +54961,150 @@
       <c r="J61" s="18" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="n"/>
-      <c r="B62" s="45" t="n"/>
-      <c r="C62" s="45" t="n"/>
-      <c r="D62" s="46" t="n"/>
-      <c r="E62" s="45" t="n"/>
+      <c r="A62" s="44" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B62" s="45" t="inlineStr">
+        <is>
+          <t>Rafael Landin Ribeiro</t>
+        </is>
+      </c>
+      <c r="C62" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E62" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F62" s="47" t="n"/>
       <c r="G62" s="48" t="n"/>
       <c r="H62" s="49" t="n"/>
-      <c r="I62" s="45" t="n"/>
+      <c r="I62" s="45" t="inlineStr">
+        <is>
+          <t>Troca do dia 09/10/2026.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>CLI-0530</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="19" t="n"/>
+      <c r="A63" s="17" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Refil Universal</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>85</v>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>1.23</v>
+      </c>
       <c r="G63" s="19" t="n"/>
       <c r="H63" s="21" t="n"/>
-      <c r="I63" s="18" t="n"/>
-      <c r="J63" s="18" t="n"/>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>Venda total R$ 170,00 (Refil Pro Life R$ 140,00 + Refil Universal R$ 30,00) — pagamento dividido: R$ 85,00 no débito em 09/10/2026 + R$ 85,00 via Pix (linha abaixo).</t>
+        </is>
+      </c>
+      <c r="J63" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0258</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="n"/>
-      <c r="B64" s="45" t="n"/>
-      <c r="C64" s="45" t="n"/>
-      <c r="D64" s="46" t="n"/>
-      <c r="E64" s="45" t="n"/>
+      <c r="A64" s="44" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="n">
+        <v>85</v>
+      </c>
+      <c r="E64" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F64" s="47" t="n"/>
       <c r="G64" s="48" t="n"/>
       <c r="H64" s="49" t="n"/>
-      <c r="I64" s="45" t="n"/>
+      <c r="I64" s="45" t="inlineStr">
+        <is>
+          <t>Restante da venda de R$ 170,00 — Pix previsto para sexta 16/10/2026.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>EMP-0258</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="n"/>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="27" t="n"/>
-      <c r="E65" s="18" t="n"/>
+      <c r="A65" s="17" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>Tropical Motos LTDA</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F65" s="19" t="n"/>
       <c r="G65" s="19" t="n"/>
       <c r="H65" s="21" t="n"/>
-      <c r="I65" s="18" t="n"/>
-      <c r="J65" s="18" t="n"/>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>Troca do dia 09/10/2026 — purificador do andar de cima (Pro Life, sem pré-filtro).</t>
+        </is>
+      </c>
+      <c r="J65" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0296</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="44" t="n"/>
@@ -65666,7 +65766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -70187,45 +70287,138 @@
       </c>
     </row>
     <row r="154" s="157">
-      <c r="A154" s="86" t="inlineStr">
+      <c r="A154" s="78" t="inlineStr">
+        <is>
+          <t>Rafael Landin Ribeiro</t>
+        </is>
+      </c>
+      <c r="B154" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C154" s="77" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D154" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E154" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F154" s="112">
+        <f>IF(OR($E154="Recebido",$C154=""),"",MAX(0,TODAY()-$C154))</f>
+        <v/>
+      </c>
+      <c r="G154" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 09/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" s="157">
+      <c r="A155" s="78" t="inlineStr">
+        <is>
+          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
+        </is>
+      </c>
+      <c r="B155" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Refil Universal (restante)</t>
+        </is>
+      </c>
+      <c r="C155" s="77" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D155" s="79" t="n">
+        <v>85</v>
+      </c>
+      <c r="E155" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F155" s="112">
+        <f>IF(OR($E155="Recebido",$C155=""),"",MAX(0,TODAY()-$C155))</f>
+        <v/>
+      </c>
+      <c r="G155" s="78" t="inlineStr">
+        <is>
+          <t>Venda de R$ 170,00 — R$ 85,00 pagos no débito em 09/10/2026; restante via Pix previsto para 16/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" s="157">
+      <c r="A156" s="78" t="inlineStr">
+        <is>
+          <t>Tropical Motos LTDA</t>
+        </is>
+      </c>
+      <c r="B156" s="78" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C156" s="77" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D156" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E156" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F156" s="112">
+        <f>IF(OR($E156="Recebido",$C156=""),"",MAX(0,TODAY()-$C156))</f>
+        <v/>
+      </c>
+      <c r="G156" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 09/10/2026 — purificador do andar de cima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" s="157">
+      <c r="A157" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D154" s="115">
-        <f>SUMIF(E102:E153,"Pendente",D102:D153)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" s="157">
-      <c r="A155" s="202" t="inlineStr">
+      <c r="D157" s="115">
+        <f>SUMIF(E102:E156,"Pendente",D102:D156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" s="157">
+      <c r="A158" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B155" s="159" t="n"/>
-      <c r="C155" s="159" t="n"/>
-      <c r="D155" s="159" t="n"/>
-      <c r="E155" s="159" t="n"/>
-      <c r="F155" s="159" t="n"/>
-      <c r="G155" s="160" t="n"/>
-    </row>
-    <row r="156" s="157">
-      <c r="A156" s="203">
-        <f>IF(ROUND(D154-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D154-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" s="157">
-      <c r="A157" s="203" t="inlineStr">
+      <c r="B158" s="159" t="n"/>
+      <c r="C158" s="159" t="n"/>
+      <c r="D158" s="159" t="n"/>
+      <c r="E158" s="159" t="n"/>
+      <c r="F158" s="159" t="n"/>
+      <c r="G158" s="160" t="n"/>
+    </row>
+    <row r="159" s="157">
+      <c r="A159" s="203">
+        <f>IF(ROUND(D157-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D157-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" s="157">
+      <c r="A160" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="158" s="157"/>
-    <row r="159" s="157"/>
-    <row r="160" s="157"/>
     <row r="161" s="157"/>
     <row r="162" s="157"/>
     <row r="163" s="157"/>
@@ -70274,23 +70467,23 @@
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A159:G159"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A158:G158"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A156:G156"/>
     <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A155:G155"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E102:E153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E102:E156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54513,7 +54513,7 @@
     </row>
     <row r="48">
       <c r="A48" s="44" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B48" s="45" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="45" t="inlineStr">
         <is>
-          <t>Venda de 30/09/2026 (troca na PC Jacobina / Cartão de Todos, antes em Set 2026) — pagamento recebido via Pix em 06/10/2026.</t>
+          <t>Venda de 30/09/2026 (troca na PC Jacobina / Cartão de Todos, antes em Set 2026) — pagamento recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026).</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -54979,7 +54979,7 @@
       </c>
       <c r="E62" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F62" s="47" t="n"/>
@@ -54987,7 +54987,7 @@
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="45" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026.</t>
+          <t>Troca do dia 09/10/2026 — pagamento recebido via Pix em 09/10/2026.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -55107,15 +55107,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="n"/>
-      <c r="B66" s="45" t="n"/>
+      <c r="A66" s="44" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B66" s="45" t="inlineStr">
+        <is>
+          <t>Estacionamento (Zona Azul)</t>
+        </is>
+      </c>
       <c r="C66" s="45" t="n"/>
       <c r="D66" s="46" t="n"/>
       <c r="E66" s="45" t="n"/>
       <c r="F66" s="47" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="49" t="n"/>
-      <c r="I66" s="45" t="n"/>
+      <c r="G66" s="48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H66" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I66" s="45" t="inlineStr">
+        <is>
+          <t>Mob Parking — Zona Azul Digital Jacobina, ticket 210571, 09/10/2026 12:00–13:00, placa PLR9I12. Se aparecer Pix de R$ 2,40 para Pagar.me no extrato deste dia, é este mesmo — não lançar de novo.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n"/>
@@ -65766,7 +65782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -70154,7 +70170,7 @@
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 30/09/2026. Recebido via Pix em 06/10/2026 — lançado em "Out 2026".</t>
+          <t>Troca do dia 30/09/2026. Recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026) — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
@@ -70305,7 +70321,7 @@
       </c>
       <c r="E154" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F154" s="112">
@@ -70314,7 +70330,7 @@
       </c>
       <c r="G154" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026.</t>
+          <t>Troca do dia 09/10/2026. Recebido via Pix em 09/10/2026.</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55134,27 +55134,74 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="27" t="n"/>
-      <c r="E67" s="18" t="n"/>
+      <c r="A67" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>Colegio Oasis de Jacobina - Unopar</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado + 2x Carcaça 9"</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="n">
+        <v>400</v>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F67" s="19" t="n"/>
       <c r="G67" s="19" t="n"/>
       <c r="H67" s="21" t="n"/>
-      <c r="I67" s="18" t="n"/>
-      <c r="J67" s="18" t="n"/>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
+        </is>
+      </c>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>ESC-0009</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="44" t="n"/>
-      <c r="B68" s="45" t="n"/>
-      <c r="C68" s="45" t="n"/>
-      <c r="D68" s="46" t="n"/>
-      <c r="E68" s="45" t="n"/>
-      <c r="F68" s="47" t="n"/>
+      <c r="A68" s="44" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B68" s="45" t="inlineStr">
+        <is>
+          <t>Josélia Nascimento da Silva Gomes</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E68" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F68" s="47" t="n">
+        <v>4.91</v>
+      </c>
       <c r="G68" s="48" t="n"/>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="45" t="n"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>CLI-0313</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55204,46 +55204,137 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="18" t="n"/>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="18" t="n"/>
+      <c r="A69" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>Gabriela Araujo</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>Conexão T Everest</t>
+        </is>
+      </c>
+      <c r="D69" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F69" s="19" t="n"/>
       <c r="G69" s="19" t="n"/>
       <c r="H69" s="21" t="n"/>
-      <c r="I69" s="18" t="n"/>
-      <c r="J69" s="18" t="n"/>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>Peça usada na instalação do Purificador Everest Fit Prata (comprado em 08/10/2026).</t>
+        </is>
+      </c>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0038</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="44" t="n"/>
-      <c r="B70" s="45" t="n"/>
-      <c r="C70" s="45" t="n"/>
-      <c r="D70" s="46" t="n"/>
-      <c r="E70" s="45" t="n"/>
-      <c r="F70" s="47" t="n"/>
+      <c r="A70" s="44" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>Michelle Santos de Almeida Rocha</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Grafite</t>
+        </is>
+      </c>
+      <c r="D70" s="46" t="n">
+        <v>1689</v>
+      </c>
+      <c r="E70" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F70" s="47" t="n">
+        <v>236.29</v>
+      </c>
       <c r="G70" s="48" t="n"/>
       <c r="H70" s="49" t="n"/>
-      <c r="I70" s="45" t="n"/>
+      <c r="I70" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 10x. Instalação feita em 10/10/2026.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>CLI-0904</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="n"/>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="27" t="n"/>
-      <c r="E71" s="18" t="n"/>
+      <c r="A71" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>Michelle Santos de Almeida Rocha</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F71" s="19" t="n"/>
       <c r="G71" s="19" t="n"/>
       <c r="H71" s="21" t="n"/>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="n"/>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>Oferecido e vendido na hora da instalação do purificador.</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0904</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="44" t="n"/>
-      <c r="B72" s="45" t="n"/>
-      <c r="C72" s="45" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="45" t="n"/>
+      <c r="A72" s="44" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B72" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C72" s="45" t="inlineStr">
+        <is>
+          <t>Refil Universal</t>
+        </is>
+      </c>
+      <c r="D72" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F72" s="47" t="n"/>
       <c r="G72" s="48" t="n"/>
       <c r="H72" s="49" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55341,27 +55341,70 @@
       <c r="I72" s="45" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="n"/>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="27" t="n"/>
-      <c r="E73" s="18" t="n"/>
+      <c r="A73" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Leonardo Silva de Brito</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira + Limpeza do Purificador</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F73" s="19" t="n"/>
       <c r="G73" s="19" t="n"/>
       <c r="H73" s="21" t="n"/>
       <c r="I73" s="18" t="n"/>
-      <c r="J73" s="18" t="n"/>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>OUT-0103</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="44" t="n"/>
-      <c r="B74" s="45" t="n"/>
-      <c r="C74" s="45" t="n"/>
-      <c r="D74" s="46" t="n"/>
-      <c r="E74" s="45" t="n"/>
-      <c r="F74" s="47" t="n"/>
+      <c r="A74" s="44" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>Lorena Coelho</t>
+        </is>
+      </c>
+      <c r="C74" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D74" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E74" s="45" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F74" s="47" t="n">
+        <v>5.28</v>
+      </c>
       <c r="G74" s="48" t="n"/>
       <c r="H74" s="49" t="n"/>
       <c r="I74" s="45" t="n"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CLI-0905</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55407,211 +55407,499 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="n"/>
-      <c r="B75" s="18" t="n"/>
+      <c r="A75" s="17" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C75" s="18" t="n"/>
       <c r="D75" s="27" t="n"/>
       <c r="E75" s="18" t="n"/>
       <c r="F75" s="19" t="n"/>
-      <c r="G75" s="19" t="n"/>
-      <c r="H75" s="21" t="n"/>
-      <c r="I75" s="18" t="n"/>
+      <c r="G75" s="19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H75" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 01/10/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
+        </is>
+      </c>
       <c r="J75" s="18" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="44" t="n"/>
-      <c r="B76" s="45" t="n"/>
+      <c r="A76" s="44" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B76" s="45" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
       <c r="C76" s="45" t="n"/>
       <c r="D76" s="46" t="n"/>
       <c r="E76" s="45" t="n"/>
       <c r="F76" s="47" t="n"/>
-      <c r="G76" s="48" t="n"/>
-      <c r="H76" s="49" t="n"/>
-      <c r="I76" s="45" t="n"/>
+      <c r="G76" s="48" t="n">
+        <v>35</v>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I76" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 01/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="n"/>
-      <c r="B77" s="18" t="n"/>
+      <c r="A77" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>Maria Eva dos Santos</t>
+        </is>
+      </c>
       <c r="C77" s="18" t="n"/>
       <c r="D77" s="27" t="n"/>
       <c r="E77" s="18" t="n"/>
       <c r="F77" s="19" t="n"/>
-      <c r="G77" s="19" t="n"/>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="18" t="n"/>
+      <c r="G77" s="19" t="n">
+        <v>380</v>
+      </c>
+      <c r="H77" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 02/10/2026.</t>
+        </is>
+      </c>
       <c r="J77" s="18" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="44" t="n"/>
-      <c r="B78" s="45" t="n"/>
+      <c r="A78" s="44" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B78" s="45" t="inlineStr">
+        <is>
+          <t>Cezar Silva Atacado e Varejo (Iene Quedila Nunes Dourado)</t>
+        </is>
+      </c>
       <c r="C78" s="45" t="n"/>
       <c r="D78" s="46" t="n"/>
       <c r="E78" s="45" t="n"/>
       <c r="F78" s="47" t="n"/>
-      <c r="G78" s="48" t="n"/>
-      <c r="H78" s="49" t="n"/>
-      <c r="I78" s="45" t="n"/>
+      <c r="G78" s="48" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H78" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I78" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 02/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="n"/>
-      <c r="B79" s="18" t="n"/>
+      <c r="A79" s="17" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C79" s="18" t="n"/>
       <c r="D79" s="27" t="n"/>
       <c r="E79" s="18" t="n"/>
       <c r="F79" s="19" t="n"/>
-      <c r="G79" s="19" t="n"/>
-      <c r="H79" s="21" t="n"/>
-      <c r="I79" s="18" t="n"/>
+      <c r="G79" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H79" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 02/10/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
+        </is>
+      </c>
       <c r="J79" s="18" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="44" t="n"/>
-      <c r="B80" s="45" t="n"/>
+      <c r="A80" s="44" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B80" s="45" t="inlineStr">
+        <is>
+          <t>Japedido Software</t>
+        </is>
+      </c>
       <c r="C80" s="45" t="n"/>
       <c r="D80" s="46" t="n"/>
       <c r="E80" s="45" t="n"/>
       <c r="F80" s="47" t="n"/>
-      <c r="G80" s="48" t="n"/>
-      <c r="H80" s="49" t="n"/>
-      <c r="I80" s="45" t="n"/>
+      <c r="G80" s="48" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="H80" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I80" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 07/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="n"/>
-      <c r="B81" s="18" t="n"/>
+      <c r="A81" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
       <c r="C81" s="18" t="n"/>
       <c r="D81" s="27" t="n"/>
       <c r="E81" s="18" t="n"/>
       <c r="F81" s="19" t="n"/>
-      <c r="G81" s="19" t="n"/>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="18" t="n"/>
+      <c r="G81" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 08/10/2026.</t>
+        </is>
+      </c>
       <c r="J81" s="18" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="44" t="n"/>
-      <c r="B82" s="45" t="n"/>
+      <c r="A82" s="44" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B82" s="45" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C82" s="45" t="n"/>
       <c r="D82" s="46" t="n"/>
       <c r="E82" s="45" t="n"/>
       <c r="F82" s="47" t="n"/>
-      <c r="G82" s="48" t="n"/>
-      <c r="H82" s="49" t="n"/>
-      <c r="I82" s="45" t="n"/>
+      <c r="G82" s="48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H82" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I82" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 08/10/2026 para Pagar.me Instituição de Pagamento (estacionamento). Diferente do Zona Azul de 09/10.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="n"/>
-      <c r="B83" s="18" t="n"/>
+      <c r="A83" s="17" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>Marcos Pereira Cirqueira</t>
+        </is>
+      </c>
       <c r="C83" s="18" t="n"/>
       <c r="D83" s="27" t="n"/>
       <c r="E83" s="18" t="n"/>
       <c r="F83" s="19" t="n"/>
-      <c r="G83" s="19" t="n"/>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="18" t="n"/>
+      <c r="G83" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 09/10/2026.</t>
+        </is>
+      </c>
       <c r="J83" s="18" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="44" t="n"/>
-      <c r="B84" s="45" t="n"/>
+      <c r="A84" s="44" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B84" s="45" t="inlineStr">
+        <is>
+          <t>Ledson Batista da Silva</t>
+        </is>
+      </c>
       <c r="C84" s="45" t="n"/>
       <c r="D84" s="46" t="n"/>
       <c r="E84" s="45" t="n"/>
       <c r="F84" s="47" t="n"/>
-      <c r="G84" s="48" t="n"/>
-      <c r="H84" s="49" t="n"/>
-      <c r="I84" s="45" t="n"/>
+      <c r="G84" s="48" t="n">
+        <v>120</v>
+      </c>
+      <c r="H84" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I84" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 09/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="n"/>
-      <c r="B85" s="18" t="n"/>
+      <c r="A85" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>App 99 — reembolso Wiliam</t>
+        </is>
+      </c>
       <c r="C85" s="18" t="n"/>
       <c r="D85" s="27" t="n"/>
       <c r="E85" s="18" t="n"/>
       <c r="F85" s="19" t="n"/>
-      <c r="G85" s="19" t="n"/>
-      <c r="H85" s="21" t="n"/>
-      <c r="I85" s="18" t="n"/>
+      <c r="G85" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>Pix para Wiliam Pinto Bispo em 10/10/2026 — reembolso de corridas no 99 para fazer serviços (Extrato Stone).</t>
+        </is>
+      </c>
       <c r="J85" s="18" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="44" t="n"/>
-      <c r="B86" s="45" t="n"/>
+      <c r="A86" s="44" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B86" s="45" t="inlineStr">
+        <is>
+          <t>Dlocal Brasil Instituição de Pagamento</t>
+        </is>
+      </c>
       <c r="C86" s="45" t="n"/>
       <c r="D86" s="46" t="n"/>
       <c r="E86" s="45" t="n"/>
       <c r="F86" s="47" t="n"/>
-      <c r="G86" s="48" t="n"/>
-      <c r="H86" s="49" t="n"/>
-      <c r="I86" s="45" t="n"/>
+      <c r="G86" s="48" t="n">
+        <v>144.61</v>
+      </c>
+      <c r="H86" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I86" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 10/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="17" t="n"/>
-      <c r="B87" s="18" t="n"/>
+      <c r="A87" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>Mercado Pago (Pix Marketplace)</t>
+        </is>
+      </c>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="27" t="n"/>
       <c r="E87" s="18" t="n"/>
       <c r="F87" s="19" t="n"/>
-      <c r="G87" s="19" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="18" t="n"/>
+      <c r="G87" s="19" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="H87" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 10/10/2026.</t>
+        </is>
+      </c>
       <c r="J87" s="18" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="44" t="n"/>
-      <c r="B88" s="45" t="n"/>
+      <c r="A88" s="44" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B88" s="45" t="inlineStr">
+        <is>
+          <t>Janaina dos Santos</t>
+        </is>
+      </c>
       <c r="C88" s="45" t="n"/>
       <c r="D88" s="46" t="n"/>
       <c r="E88" s="45" t="n"/>
       <c r="F88" s="47" t="n"/>
-      <c r="G88" s="48" t="n"/>
-      <c r="H88" s="49" t="n"/>
-      <c r="I88" s="45" t="n"/>
+      <c r="G88" s="48" t="n">
+        <v>61.89</v>
+      </c>
+      <c r="H88" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I88" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 10/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="n"/>
-      <c r="B89" s="18" t="n"/>
+      <c r="A89" s="17" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Maree Instituição de Pagamento</t>
+        </is>
+      </c>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="27" t="n"/>
       <c r="E89" s="18" t="n"/>
       <c r="F89" s="19" t="n"/>
-      <c r="G89" s="19" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="18" t="n"/>
+      <c r="G89" s="19" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 12/10/2026.</t>
+        </is>
+      </c>
       <c r="J89" s="18" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="44" t="n"/>
-      <c r="B90" s="45" t="n"/>
+      <c r="A90" s="44" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B90" s="45" t="inlineStr">
+        <is>
+          <t>Estacionamento (Pagar.me)</t>
+        </is>
+      </c>
       <c r="C90" s="45" t="n"/>
       <c r="D90" s="46" t="n"/>
       <c r="E90" s="45" t="n"/>
       <c r="F90" s="47" t="n"/>
-      <c r="G90" s="48" t="n"/>
-      <c r="H90" s="49" t="n"/>
-      <c r="I90" s="45" t="n"/>
+      <c r="G90" s="48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H90" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I90" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 13/10/2026 para Pagar.me Instituição de Pagamento (estacionamento).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="n"/>
-      <c r="B91" s="18" t="n"/>
+      <c r="A91" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>N de Souza Oliveira Ltda</t>
+        </is>
+      </c>
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="27" t="n"/>
       <c r="E91" s="18" t="n"/>
       <c r="F91" s="19" t="n"/>
-      <c r="G91" s="19" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="18" t="n"/>
+      <c r="G91" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H91" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 13/10/2026.</t>
+        </is>
+      </c>
       <c r="J91" s="18" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="44" t="n"/>
-      <c r="B92" s="45" t="n"/>
+      <c r="A92" s="44" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B92" s="45" t="inlineStr">
+        <is>
+          <t>Japedido Software</t>
+        </is>
+      </c>
       <c r="C92" s="45" t="n"/>
       <c r="D92" s="46" t="n"/>
       <c r="E92" s="45" t="n"/>
       <c r="F92" s="47" t="n"/>
-      <c r="G92" s="48" t="n"/>
-      <c r="H92" s="49" t="n"/>
-      <c r="I92" s="45" t="n"/>
+      <c r="G92" s="48" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="H92" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I92" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 13/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55902,16 +55902,36 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="n"/>
-      <c r="B93" s="18" t="n"/>
-      <c r="C93" s="18" t="n"/>
-      <c r="D93" s="27" t="n"/>
-      <c r="E93" s="18" t="n"/>
+      <c r="A93" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>Olegario Oliveira da Silva</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F93" s="19" t="n"/>
       <c r="G93" s="19" t="n"/>
       <c r="H93" s="21" t="n"/>
       <c r="I93" s="18" t="n"/>
-      <c r="J93" s="18" t="n"/>
+      <c r="J93" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0523</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -51790,7 +51790,7 @@
       </c>
       <c r="E212" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F212" s="47" t="n"/>
@@ -51798,7 +51798,7 @@
       <c r="H212" s="49" t="n"/>
       <c r="I212" s="45" t="inlineStr">
         <is>
-          <t>Preço com desconto de cliente. Pagamento previsto para 30/09/2026.</t>
+          <t>Preço com desconto de cliente. Pagamento previsto para 30/09/2026. Pago em dinheiro em 14/10/2026.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -55934,50 +55934,148 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="44" t="n"/>
-      <c r="B94" s="45" t="n"/>
-      <c r="C94" s="45" t="n"/>
-      <c r="D94" s="46" t="n"/>
-      <c r="E94" s="45" t="n"/>
+      <c r="A94" s="44" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B94" s="45" t="inlineStr">
+        <is>
+          <t>Aldaci Freire de Araujo</t>
+        </is>
+      </c>
+      <c r="C94" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D94" s="46" t="n">
+        <v>130</v>
+      </c>
+      <c r="E94" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F94" s="47" t="n"/>
       <c r="G94" s="48" t="n"/>
       <c r="H94" s="49" t="n"/>
-      <c r="I94" s="45" t="n"/>
+      <c r="I94" s="45" t="inlineStr">
+        <is>
+          <t>Cliente pediu desconto (Pro Life no lugar do Everest do cadastro). Troca do dia 14/10/2026. Com o suporte (linha abaixo), total R$ 150,00 em dinheiro.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CLI-0529</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="n"/>
-      <c r="B95" s="18" t="n"/>
-      <c r="C95" s="18" t="n"/>
-      <c r="D95" s="27" t="n"/>
-      <c r="E95" s="18" t="n"/>
+      <c r="A95" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Aldaci Freire de Araujo</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F95" s="19" t="n"/>
       <c r="G95" s="19" t="n"/>
       <c r="H95" s="21" t="n"/>
-      <c r="I95" s="18" t="n"/>
-      <c r="J95" s="18" t="n"/>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>Suporte do aparelho estava ruim; trocado só um lado (kit suporte normal R$ 40,00).</t>
+        </is>
+      </c>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0529</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="44" t="n"/>
-      <c r="B96" s="45" t="n"/>
-      <c r="C96" s="45" t="n"/>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="45" t="n"/>
-      <c r="F96" s="47" t="n"/>
+      <c r="A96" s="44" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B96" s="45" t="inlineStr">
+        <is>
+          <t>Marilia Silva</t>
+        </is>
+      </c>
+      <c r="C96" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro + Termostato</t>
+        </is>
+      </c>
+      <c r="D96" s="46" t="n">
+        <v>370</v>
+      </c>
+      <c r="E96" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F96" s="47" t="n">
+        <v>12.99</v>
+      </c>
       <c r="G96" s="48" t="n"/>
       <c r="H96" s="49" t="n"/>
-      <c r="I96" s="45" t="n"/>
+      <c r="I96" s="45" t="inlineStr">
+        <is>
+          <t>Termostato trocado por defeito (não desligava). Ao entregar o aparelho consertado, adiantou a troca do refil (vencia no mês que vem). Crédito 1x.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>CLI-0590</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="n"/>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="27" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="19" t="n"/>
+      <c r="A97" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>Reginaldo Novaes de Oliveira - Barbara Novais</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="n">
+        <v>2.03</v>
+      </c>
       <c r="G97" s="19" t="n"/>
       <c r="H97" s="21" t="n"/>
       <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
+      <c r="J97" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0524</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -66420,7 +66420,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D96</f>
+        <f>D97</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -69133,54 +69133,85 @@
       </c>
     </row>
     <row r="94" s="157">
-      <c r="A94" s="86" t="inlineStr">
+      <c r="A94" s="78" t="inlineStr">
+        <is>
+          <t>Proxxima Telecomunicacoes S.A.</t>
+        </is>
+      </c>
+      <c r="B94" s="78" t="inlineStr">
+        <is>
+          <t>Internet da loja — plano Turbinados 700 MB, contrato 578646</t>
+        </is>
+      </c>
+      <c r="C94" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D94" s="79" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="E94" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F94" s="112">
+        <f>IF(OR($E94="Pago",$C94=""),"",MAX(0,TODAY()-$C94))</f>
+        <v/>
+      </c>
+      <c r="G94" s="78" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Água, Energia e Internet. Fatura FAT26091809010676 (emissão 18/09/2026), NFCom 410732, boleto Bradesco 237. Linha digitável 23790.49303 90000.443094 56025.103005 3 16000000006999. Nosso número 09000044309567. Após o vencimento: multa de 2% + mora de 1,20% a.m. A fatura sai em nome do sócio, mas o serviço é da loja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" s="157">
+      <c r="A95" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B94" s="86" t="n"/>
-      <c r="C94" s="114" t="n"/>
-      <c r="D94" s="115">
-        <f>SUMIF(E11:E93,"Pendente",D11:D93)</f>
-        <v/>
-      </c>
-      <c r="E94" s="116" t="n"/>
-      <c r="F94" s="116" t="n"/>
-      <c r="G94" s="86" t="n"/>
-    </row>
-    <row r="95" s="157">
-      <c r="A95" s="144" t="inlineStr">
+      <c r="B95" s="86" t="n"/>
+      <c r="C95" s="114" t="n"/>
+      <c r="D95" s="115">
+        <f>SUMIF(E11:E94,"Pendente",D11:D94)</f>
+        <v/>
+      </c>
+      <c r="E95" s="116" t="n"/>
+      <c r="F95" s="116" t="n"/>
+      <c r="G95" s="86" t="n"/>
+    </row>
+    <row r="96" s="157">
+      <c r="A96" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B95" s="144" t="n"/>
-      <c r="C95" s="145" t="n"/>
-      <c r="D95" s="146">
-        <f>SUMIF(E11:E93,"Previsto",D11:D93)</f>
-        <v/>
-      </c>
-      <c r="E95" s="142" t="n"/>
-      <c r="F95" s="142" t="n"/>
-      <c r="G95" s="144" t="n"/>
-    </row>
-    <row r="96" s="157">
-      <c r="A96" s="86" t="inlineStr">
+      <c r="B96" s="144" t="n"/>
+      <c r="C96" s="145" t="n"/>
+      <c r="D96" s="146">
+        <f>SUMIF(E11:E94,"Previsto",D11:D94)</f>
+        <v/>
+      </c>
+      <c r="E96" s="142" t="n"/>
+      <c r="F96" s="142" t="n"/>
+      <c r="G96" s="144" t="n"/>
+    </row>
+    <row r="97" s="157">
+      <c r="A97" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B96" s="86" t="n"/>
-      <c r="C96" s="114" t="n"/>
-      <c r="D96" s="115">
-        <f>D94+D95</f>
-        <v/>
-      </c>
-      <c r="E96" s="116" t="n"/>
-      <c r="F96" s="116" t="n"/>
-      <c r="G96" s="86" t="n"/>
-    </row>
-    <row r="97" s="157"/>
+      <c r="B97" s="86" t="n"/>
+      <c r="C97" s="114" t="n"/>
+      <c r="D97" s="115">
+        <f>D95+D96</f>
+        <v/>
+      </c>
+      <c r="E97" s="116" t="n"/>
+      <c r="F97" s="116" t="n"/>
+      <c r="G97" s="86" t="n"/>
+    </row>
     <row r="98" ht="15.75" customHeight="1" s="157"/>
     <row r="99" ht="15.75" customHeight="1" s="157">
       <c r="A99" s="200" t="inlineStr">
@@ -71083,7 +71114,7 @@
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
     <dataValidation sqref="E102:E156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56078,73 +56078,186 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="44" t="n"/>
-      <c r="B98" s="45" t="n"/>
-      <c r="C98" s="45" t="n"/>
-      <c r="D98" s="46" t="n"/>
-      <c r="E98" s="45" t="n"/>
+      <c r="A98" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B98" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C98" s="45" t="inlineStr">
+        <is>
+          <t>Torneira para Purificador Latina</t>
+        </is>
+      </c>
+      <c r="D98" s="46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E98" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F98" s="47" t="n"/>
       <c r="G98" s="48" t="n"/>
       <c r="H98" s="49" t="n"/>
       <c r="I98" s="45" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="17" t="n"/>
-      <c r="B99" s="18" t="n"/>
+      <c r="A99" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="27" t="n"/>
       <c r="E99" s="18" t="n"/>
       <c r="F99" s="19" t="n"/>
-      <c r="G99" s="19" t="n"/>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="18" t="n"/>
+      <c r="G99" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>Gasolina comum 1,482 L a R$ 6,75/L — Posto Avenida Jacobina (Avenida Posto de Combustíveis LTDA, CNPJ 46.115.794/0001-30, Av. Orlando Oliveira Pires, 1430, Centro, Jacobina), NFC-e nº 000927128 série 002 de 15/10/2026 09:39. Pago R$ 10,00 em dinheiro.</t>
+        </is>
+      </c>
       <c r="J99" s="18" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="44" t="n"/>
-      <c r="B100" s="45" t="n"/>
+      <c r="A100" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B100" s="45" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C100" s="45" t="n"/>
       <c r="D100" s="46" t="n"/>
       <c r="E100" s="45" t="n"/>
       <c r="F100" s="47" t="n"/>
-      <c r="G100" s="48" t="n"/>
-      <c r="H100" s="49" t="n"/>
-      <c r="I100" s="45" t="n"/>
+      <c r="G100" s="48" t="n">
+        <v>40</v>
+      </c>
+      <c r="H100" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I100" s="45" t="inlineStr">
+        <is>
+          <t>Gasolina aditivada (Ipimax) 5,806 L a R$ 6,89/L — Transvale Derivados de Petróleo LTDA (CNPJ 11.271.229/0002-68, Av. Orlando Oliveira Pires, 1164, Centro, Jacobina), NFC-e nº 000285556 série 001 de 15/10/2026 10:21. Pago R$ 40,00 em dinheiro.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="17" t="n"/>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="27" t="n"/>
-      <c r="E101" s="18" t="n"/>
+      <c r="A101" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>Casa das Portas Comercio de Madeiras LTDA</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D101" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F101" s="19" t="n"/>
       <c r="G101" s="19" t="n"/>
       <c r="H101" s="21" t="n"/>
       <c r="I101" s="18" t="n"/>
-      <c r="J101" s="18" t="n"/>
+      <c r="J101" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0046</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="44" t="n"/>
-      <c r="B102" s="45" t="n"/>
-      <c r="C102" s="45" t="n"/>
-      <c r="D102" s="46" t="n"/>
-      <c r="E102" s="45" t="n"/>
+      <c r="A102" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B102" s="45" t="inlineStr">
+        <is>
+          <t>Casa do Construtor</t>
+        </is>
+      </c>
+      <c r="C102" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D102" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E102" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F102" s="47" t="n"/>
       <c r="G102" s="48" t="n"/>
       <c r="H102" s="49" t="n"/>
       <c r="I102" s="45" t="n"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>EMP-0320</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="17" t="n"/>
-      <c r="B103" s="18" t="n"/>
-      <c r="C103" s="18" t="n"/>
-      <c r="D103" s="27" t="n"/>
-      <c r="E103" s="18" t="n"/>
+      <c r="A103" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>Refil E3 + Refil Everest</t>
+        </is>
+      </c>
+      <c r="D103" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F103" s="19" t="n"/>
       <c r="G103" s="19" t="n"/>
       <c r="H103" s="21" t="n"/>
-      <c r="I103" s="18" t="n"/>
-      <c r="J103" s="18" t="n"/>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
+        </is>
+      </c>
+      <c r="J103" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -53003,7 +53003,7 @@
     </row>
     <row r="5">
       <c r="A5" s="77" t="n">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="B5" s="78" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
       </c>
       <c r="E5" s="78" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F5" s="79" t="n"/>
@@ -53028,7 +53028,7 @@
       <c r="H5" s="78" t="n"/>
       <c r="I5" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC AEMPPO00004453 · NF 000.004.332 de 26/08/2026 · prazo 45 dias · vencimento 10/10/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026</t>
+          <t>Grupo Ânima — OC AEMPPO00004453 · NF 000.004.332 de 26/08/2026 · prazo 45 dias · vencimento 10/10/2026 (desc. 3%) · previsão de pagamento confirmada no portal V360 em 02/09/2026 · Venda de 10/10/2026 — pagamento recebido em 13/10/2026 na conta do BNB (data em que o portal V360 marcou Nota Paga; dia/hora exatos a confirmar com a Edilânia)</t>
         </is>
       </c>
       <c r="J5" s="78" t="inlineStr">
@@ -70092,7 +70092,7 @@
       </c>
       <c r="E124" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F124" s="112">
@@ -70101,7 +70101,7 @@
       </c>
       <c r="G124" s="78" t="inlineStr">
         <is>
-          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias</t>
+          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias · Recebido em 13/10/2026 no BNB (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56260,104 +56260,259 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="44" t="n"/>
-      <c r="B104" s="45" t="n"/>
-      <c r="C104" s="45" t="n"/>
-      <c r="D104" s="46" t="n"/>
-      <c r="E104" s="45" t="n"/>
+      <c r="A104" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" s="45" t="inlineStr">
+        <is>
+          <t>Edinaldo Nunes - Marilene de Souza Oliveira</t>
+        </is>
+      </c>
+      <c r="C104" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D104" s="46" t="n">
+        <v>190</v>
+      </c>
+      <c r="E104" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F104" s="47" t="n"/>
       <c r="G104" s="48" t="n"/>
       <c r="H104" s="49" t="n"/>
       <c r="I104" s="45" t="n"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>CLI-0499</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="17" t="n"/>
-      <c r="B105" s="18" t="n"/>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="27" t="n"/>
-      <c r="E105" s="18" t="n"/>
+      <c r="A105" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F105" s="19" t="n"/>
       <c r="G105" s="19" t="n"/>
       <c r="H105" s="21" t="n"/>
       <c r="I105" s="18" t="n"/>
-      <c r="J105" s="18" t="n"/>
+      <c r="J105" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0253</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="44" t="n"/>
-      <c r="B106" s="45" t="n"/>
+      <c r="A106" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B106" s="45" t="inlineStr">
+        <is>
+          <t>Eversoft</t>
+        </is>
+      </c>
       <c r="C106" s="45" t="n"/>
       <c r="D106" s="46" t="n"/>
       <c r="E106" s="45" t="n"/>
       <c r="F106" s="47" t="n"/>
-      <c r="G106" s="48" t="n"/>
-      <c r="H106" s="49" t="n"/>
-      <c r="I106" s="45" t="n"/>
+      <c r="G106" s="48" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="H106" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I106" s="45" t="inlineStr">
+        <is>
+          <t>Boleto doc. 74454 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="17" t="n"/>
-      <c r="B107" s="18" t="n"/>
+      <c r="A107" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C107" s="18" t="n"/>
       <c r="D107" s="27" t="n"/>
       <c r="E107" s="18" t="n"/>
       <c r="F107" s="19" t="n"/>
-      <c r="G107" s="19" t="n"/>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="18" t="n"/>
+      <c r="G107" s="19" t="n">
+        <v>892.3</v>
+      </c>
+      <c r="H107" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>Boleto doc. 381554 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+        </is>
+      </c>
       <c r="J107" s="18" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="44" t="n"/>
-      <c r="B108" s="45" t="n"/>
+      <c r="A108" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B108" s="45" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C108" s="45" t="n"/>
       <c r="D108" s="46" t="n"/>
       <c r="E108" s="45" t="n"/>
       <c r="F108" s="47" t="n"/>
-      <c r="G108" s="48" t="n"/>
-      <c r="H108" s="49" t="n"/>
-      <c r="I108" s="45" t="n"/>
+      <c r="G108" s="48" t="n">
+        <v>574.27</v>
+      </c>
+      <c r="H108" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I108" s="45" t="inlineStr">
+        <is>
+          <t>Boleto doc. 386188 (emissão 15/09/2026) · parcela 1/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="17" t="n"/>
-      <c r="B109" s="18" t="n"/>
+      <c r="A109" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>Tarcisio Oliveira Lima</t>
+        </is>
+      </c>
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="27" t="n"/>
       <c r="E109" s="18" t="n"/>
       <c r="F109" s="19" t="n"/>
-      <c r="G109" s="19" t="n"/>
-      <c r="H109" s="21" t="n"/>
-      <c r="I109" s="18" t="n"/>
+      <c r="G109" s="19" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="H109" s="21" t="inlineStr">
+        <is>
+          <t>Contabilidade</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>Serviço contábil — boleto Banco do Brasil, venc. 15/10/2026. Pago em 15/10/2026.</t>
+        </is>
+      </c>
       <c r="J109" s="18" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="44" t="n"/>
-      <c r="B110" s="45" t="n"/>
+      <c r="A110" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B110" s="45" t="inlineStr">
+        <is>
+          <t>Proxxima Telecomunicações</t>
+        </is>
+      </c>
       <c r="C110" s="45" t="n"/>
       <c r="D110" s="46" t="n"/>
       <c r="E110" s="45" t="n"/>
       <c r="F110" s="47" t="n"/>
-      <c r="G110" s="48" t="n"/>
-      <c r="H110" s="49" t="n"/>
-      <c r="I110" s="45" t="n"/>
+      <c r="G110" s="48" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="H110" s="49" t="inlineStr">
+        <is>
+          <t>Água, Energia e Internet</t>
+        </is>
+      </c>
+      <c r="I110" s="45" t="inlineStr">
+        <is>
+          <t>Internet da loja — plano Turbinados 700 MB, contrato 578646. Fatura FAT26091809010676, venc. 15/10/2026. Pago em 15/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="17" t="n"/>
-      <c r="B111" s="18" t="n"/>
+      <c r="A111" s="17" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C111" s="18" t="n"/>
       <c r="D111" s="27" t="n"/>
       <c r="E111" s="18" t="n"/>
       <c r="F111" s="19" t="n"/>
-      <c r="G111" s="19" t="n"/>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="18" t="n"/>
+      <c r="G111" s="19" t="n">
+        <v>856.34</v>
+      </c>
+      <c r="H111" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377739 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago antecipado em 15/10/2026.</t>
+        </is>
+      </c>
       <c r="J111" s="18" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="44" t="n"/>
-      <c r="B112" s="45" t="n"/>
-      <c r="C112" s="45" t="n"/>
-      <c r="D112" s="46" t="n"/>
-      <c r="E112" s="45" t="n"/>
-      <c r="F112" s="47" t="n"/>
+      <c r="A112" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B112" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C112" s="45" t="inlineStr">
+        <is>
+          <t>Refil Plissado</t>
+        </is>
+      </c>
+      <c r="D112" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F112" s="47" t="n">
+        <v>3.76</v>
+      </c>
       <c r="G112" s="48" t="n"/>
       <c r="H112" s="49" t="n"/>
       <c r="I112" s="45" t="n"/>
@@ -66482,7 +66637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -67280,7 +67435,7 @@
       </c>
       <c r="E32" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F32" s="113">
@@ -67289,7 +67444,7 @@
       </c>
       <c r="G32" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381. Pago em 15/10/2026 — lançado em "Out 2026" como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -67536,7 +67691,7 @@
       </c>
       <c r="E40" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F40" s="113">
@@ -67545,7 +67700,7 @@
       </c>
       <c r="G40" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -67632,7 +67787,7 @@
       </c>
       <c r="E43" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F43" s="112">
@@ -67641,7 +67796,7 @@
       </c>
       <c r="G43" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377739 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.281,74 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777391313049192.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377739 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.281,74 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777391313049192. Pago em 15/10/2026 (antecipado, venc. 16/10) — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68240,7 +68395,7 @@
       </c>
       <c r="E62" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F62" s="113">
@@ -68249,7 +68404,7 @@
       </c>
       <c r="G62" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -69136,7 +69291,7 @@
       </c>
       <c r="E90" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F90" s="113">
@@ -69145,7 +69300,7 @@
       </c>
       <c r="G90" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Contabilidade. Boleto Banco do Brasil 001-9. Linha digitável 00190.00009 03128.364001 00003.179173 8 16000000048632.</t>
+          <t>Categoria quando pagar: Contabilidade. Boleto Banco do Brasil 001-9. Linha digitável 00190.00009 03128.364001 00003.179173 8 16000000048632. Pago em 15/10/2026 — lançado em "Out 2026" como "Tarcisio Oliveira Lima".</t>
         </is>
       </c>
     </row>
@@ -69264,7 +69419,7 @@
       </c>
       <c r="E94" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F94" s="112">
@@ -69273,7 +69428,7 @@
       </c>
       <c r="G94" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Água, Energia e Internet. Fatura FAT26091809010676 (emissão 18/09/2026), NFCom 410732, boleto Bradesco 237. Linha digitável 23790.49303 90000.443094 56025.103005 3 16000000006999. Nosso número 09000044309567. Após o vencimento: multa de 2% + mora de 1,20% a.m. A fatura sai em nome do sócio, mas o serviço é da loja.</t>
+          <t>Categoria quando pagar: Água, Energia e Internet. Fatura FAT26091809010676 (emissão 18/09/2026), NFCom 410732, boleto Bradesco 237. Linha digitável 23790.49303 90000.443094 56025.103005 3 16000000006999. Nosso número 09000044309567. Após o vencimento: multa de 2% + mora de 1,20% a.m. A fatura sai em nome do sócio, mas o serviço é da loja. Pago em 15/10/2026 — lançado em "Out 2026" como "Proxxima Telecomunicações".</t>
         </is>
       </c>
     </row>
@@ -70860,7 +71015,7 @@
       </c>
       <c r="E148" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F148" s="112">
@@ -70869,7 +71024,7 @@
       </c>
       <c r="G148" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026.</t>
+          <t>Pagamento previsto para 30/09/2026. Recebido em dinheiro em 14/10/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
@@ -71130,46 +71285,170 @@
       </c>
     </row>
     <row r="157" s="157">
-      <c r="A157" s="86" t="inlineStr">
+      <c r="A157" s="78" t="inlineStr">
+        <is>
+          <t>Casa do Construtor</t>
+        </is>
+      </c>
+      <c r="B157" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C157" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D157" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E157" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F157" s="112">
+        <f>IF(OR($E157="Recebido",$C157=""),"",MAX(0,TODAY()-$C157))</f>
+        <v/>
+      </c>
+      <c r="G157" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 15/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" s="157">
+      <c r="A158" s="78" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="B158" s="78" t="inlineStr">
+        <is>
+          <t>Refil E3 + Refil Everest</t>
+        </is>
+      </c>
+      <c r="C158" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D158" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E158" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F158" s="112">
+        <f>IF(OR($E158="Recebido",$C158=""),"",MAX(0,TODAY()-$C158))</f>
+        <v/>
+      </c>
+      <c r="G158" s="78" t="inlineStr">
+        <is>
+          <t>Compra do dia 15/10/2026 — Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" s="157">
+      <c r="A159" s="78" t="inlineStr">
+        <is>
+          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
+        </is>
+      </c>
+      <c r="B159" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C159" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D159" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E159" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F159" s="112">
+        <f>IF(OR($E159="Recebido",$C159=""),"",MAX(0,TODAY()-$C159))</f>
+        <v/>
+      </c>
+      <c r="G159" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 15/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" s="157">
+      <c r="A160" s="78" t="inlineStr">
+        <is>
+          <t>Colegio Oasis de Jacobina - Unopar</t>
+        </is>
+      </c>
+      <c r="B160" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado + 2x Carcaça 9"</t>
+        </is>
+      </c>
+      <c r="C160" s="77" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D160" s="79" t="n">
+        <v>400</v>
+      </c>
+      <c r="E160" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F160" s="112">
+        <f>IF(OR($E160="Recebido",$C160=""),"",MAX(0,TODAY()-$C160))</f>
+        <v/>
+      </c>
+      <c r="G160" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" s="157">
+      <c r="A161" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D157" s="115">
-        <f>SUMIF(E102:E156,"Pendente",D102:D156)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" s="157">
-      <c r="A158" s="202" t="inlineStr">
+      <c r="D161" s="115">
+        <f>SUMIF(E102:E160,"Pendente",D102:D160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" s="157">
+      <c r="A162" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B158" s="159" t="n"/>
-      <c r="C158" s="159" t="n"/>
-      <c r="D158" s="159" t="n"/>
-      <c r="E158" s="159" t="n"/>
-      <c r="F158" s="159" t="n"/>
-      <c r="G158" s="160" t="n"/>
-    </row>
-    <row r="159" s="157">
-      <c r="A159" s="203">
-        <f>IF(ROUND(D157-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D157-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" s="157">
-      <c r="A160" s="203" t="inlineStr">
+      <c r="B162" s="159" t="n"/>
+      <c r="C162" s="159" t="n"/>
+      <c r="D162" s="159" t="n"/>
+      <c r="E162" s="159" t="n"/>
+      <c r="F162" s="159" t="n"/>
+      <c r="G162" s="160" t="n"/>
+    </row>
+    <row r="163" s="157">
+      <c r="A163" s="203">
+        <f>IF(ROUND(D161-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D161-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" s="157">
+      <c r="A164" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="161" s="157"/>
-    <row r="162" s="157"/>
-    <row r="163" s="157"/>
-    <row r="164" s="157"/>
     <row r="165" s="157"/>
     <row r="166" s="157"/>
     <row r="167" s="157"/>
@@ -71214,10 +71493,10 @@
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A159:G159"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A158:G158"/>
+    <mergeCell ref="A162:G162"/>
+    <mergeCell ref="A163:G163"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
@@ -71230,7 +71509,7 @@
     <dataValidation sqref="E11:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E102:E156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E102:E160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56518,23 +56518,65 @@
       <c r="I112" s="45" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="17" t="n"/>
-      <c r="B113" s="18" t="n"/>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="27" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="19" t="n"/>
+      <c r="A113" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>Alcina Rocha Lima Azevedo</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F113" s="19" t="n">
+        <v>11.73</v>
+      </c>
       <c r="G113" s="19" t="n"/>
       <c r="H113" s="21" t="n"/>
-      <c r="I113" s="18" t="n"/>
-      <c r="J113" s="18" t="n"/>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 2x. Instalação à tarde.</t>
+        </is>
+      </c>
+      <c r="J113" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0033</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="44" t="n"/>
-      <c r="B114" s="45" t="n"/>
-      <c r="C114" s="45" t="n"/>
-      <c r="D114" s="46" t="n"/>
-      <c r="E114" s="45" t="n"/>
+      <c r="A114" s="44" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B114" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C114" s="45" t="inlineStr">
+        <is>
+          <t>Refil E3</t>
+        </is>
+      </c>
+      <c r="D114" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E114" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F114" s="47" t="n"/>
       <c r="G114" s="48" t="n"/>
       <c r="H114" s="49" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56274,7 +56274,7 @@
         </is>
       </c>
       <c r="D104" s="46" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="E104" s="45" t="inlineStr">
         <is>
@@ -56284,7 +56284,11 @@
       <c r="F104" s="47" t="n"/>
       <c r="G104" s="48" t="n"/>
       <c r="H104" s="49" t="n"/>
-      <c r="I104" s="45" t="n"/>
+      <c r="I104" s="45" t="inlineStr">
+        <is>
+          <t>Venda de R$ 190,00 com pagamento dividido: R$ 100,00 em dinheiro + R$ 90,00 no Pix.</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>CLI-0499</t>
@@ -56293,7 +56297,7 @@
     </row>
     <row r="105">
       <c r="A105" s="17" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B105" s="18" t="inlineStr">
         <is>
@@ -56310,13 +56314,17 @@
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F105" s="19" t="n"/>
       <c r="G105" s="19" t="n"/>
       <c r="H105" s="21" t="n"/>
-      <c r="I105" s="18" t="n"/>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 15/10/2026 — pagamento recebido em 16/10/2026 via Pix.</t>
+        </is>
+      </c>
       <c r="J105" s="18" t="inlineStr">
         <is>
           <t>EMP-0253</t>
@@ -56583,73 +56591,207 @@
       <c r="I114" s="45" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="17" t="n"/>
-      <c r="B115" s="18" t="n"/>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="27" t="n"/>
-      <c r="E115" s="18" t="n"/>
+      <c r="A115" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F115" s="19" t="n"/>
       <c r="G115" s="19" t="n"/>
       <c r="H115" s="21" t="n"/>
-      <c r="I115" s="18" t="n"/>
-      <c r="J115" s="18" t="n"/>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>Venda de R$ 200,00 com pagamento dividido: R$ 140,00 em dinheiro + R$ 60,00 a receber. Bebedouro da recepção.</t>
+        </is>
+      </c>
+      <c r="J115" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0116</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="44" t="n"/>
-      <c r="B116" s="45" t="n"/>
-      <c r="C116" s="45" t="n"/>
-      <c r="D116" s="46" t="n"/>
-      <c r="E116" s="45" t="n"/>
+      <c r="A116" s="44" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B116" s="45" t="inlineStr">
+        <is>
+          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+        </is>
+      </c>
+      <c r="C116" s="45" t="inlineStr">
+        <is>
+          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
+        </is>
+      </c>
+      <c r="D116" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E116" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F116" s="47" t="n"/>
       <c r="G116" s="48" t="n"/>
       <c r="H116" s="49" t="n"/>
-      <c r="I116" s="45" t="n"/>
+      <c r="I116" s="45" t="inlineStr">
+        <is>
+          <t>Restante da venda de R$ 200,00 (R$ 140,00 pagos em dinheiro). Cliente vai pagar depois.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>EMP-0116</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="17" t="n"/>
-      <c r="B117" s="18" t="n"/>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="27" t="n"/>
-      <c r="E117" s="18" t="n"/>
+      <c r="A117" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>Contabilidade Abreu</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>Termostato</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F117" s="19" t="n"/>
       <c r="G117" s="19" t="n"/>
       <c r="H117" s="21" t="n"/>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>Troca de termostato.</t>
+        </is>
+      </c>
+      <c r="J117" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0105</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="44" t="n"/>
-      <c r="B118" s="45" t="n"/>
-      <c r="C118" s="45" t="n"/>
-      <c r="D118" s="46" t="n"/>
-      <c r="E118" s="45" t="n"/>
+      <c r="A118" s="44" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B118" s="45" t="inlineStr">
+        <is>
+          <t>Edinaldo Nunes - Marilene de Souza Oliveira</t>
+        </is>
+      </c>
+      <c r="C118" s="45" t="inlineStr">
+        <is>
+          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
+        </is>
+      </c>
+      <c r="D118" s="46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E118" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F118" s="47" t="n"/>
       <c r="G118" s="48" t="n"/>
       <c r="H118" s="49" t="n"/>
-      <c r="I118" s="45" t="n"/>
+      <c r="I118" s="45" t="inlineStr">
+        <is>
+          <t>Restante da venda de R$ 190,00 de 15/10 (R$ 100,00 em dinheiro + R$ 90,00 no Pix).</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>CLI-0499</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="17" t="n"/>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="27" t="n"/>
-      <c r="E119" s="18" t="n"/>
+      <c r="A119" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>Eduardo Santos da Silva</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D119" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F119" s="19" t="n"/>
       <c r="G119" s="19" t="n"/>
       <c r="H119" s="21" t="n"/>
       <c r="I119" s="18" t="n"/>
-      <c r="J119" s="18" t="n"/>
+      <c r="J119" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0408</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="44" t="n"/>
-      <c r="B120" s="45" t="n"/>
+      <c r="A120" s="44" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B120" s="45" t="inlineStr">
+        <is>
+          <t>Cezar Silva Atacado e Varejo - A Lojinha Utilidades (Iene Quedila Nunes Dourado)</t>
+        </is>
+      </c>
       <c r="C120" s="45" t="n"/>
       <c r="D120" s="46" t="n"/>
       <c r="E120" s="45" t="n"/>
       <c r="F120" s="47" t="n"/>
-      <c r="G120" s="48" t="n"/>
-      <c r="H120" s="49" t="n"/>
-      <c r="I120" s="45" t="n"/>
+      <c r="G120" s="48" t="n">
+        <v>170</v>
+      </c>
+      <c r="H120" s="49" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I120" s="45" t="inlineStr">
+        <is>
+          <t>Escada média (ferramenta para as instalações). Recibo de 16/10/2026. CNPJ 47.415.949/0002-05 — Rua Manoel Novais, 232, Jacobina-BA.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="n"/>
@@ -66679,7 +66821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -71409,7 +71551,7 @@
       </c>
       <c r="E159" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F159" s="112">
@@ -71418,7 +71560,7 @@
       </c>
       <c r="G159" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026.</t>
+          <t>Troca do dia 15/10/2026. Recebido via Pix em 16/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
@@ -71455,44 +71597,106 @@
       </c>
     </row>
     <row r="161" s="157">
-      <c r="A161" s="86" t="inlineStr">
+      <c r="A161" s="78" t="inlineStr">
+        <is>
+          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+        </is>
+      </c>
+      <c r="B161" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro (restante)</t>
+        </is>
+      </c>
+      <c r="C161" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D161" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E161" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F161" s="112">
+        <f>IF(OR($E161="Recebido",$C161=""),"",MAX(0,TODAY()-$C161))</f>
+        <v/>
+      </c>
+      <c r="G161" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" s="157">
+      <c r="A162" s="78" t="inlineStr">
+        <is>
+          <t>Contabilidade Abreu</t>
+        </is>
+      </c>
+      <c r="B162" s="78" t="inlineStr">
+        <is>
+          <t>Termostato</t>
+        </is>
+      </c>
+      <c r="C162" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D162" s="79" t="n">
+        <v>170</v>
+      </c>
+      <c r="E162" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F162" s="112">
+        <f>IF(OR($E162="Recebido",$C162=""),"",MAX(0,TODAY()-$C162))</f>
+        <v/>
+      </c>
+      <c r="G162" s="78" t="inlineStr">
+        <is>
+          <t>Troca de termostato do dia 16/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" s="157">
+      <c r="A163" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D161" s="115">
-        <f>SUMIF(E102:E160,"Pendente",D102:D160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" s="157">
-      <c r="A162" s="202" t="inlineStr">
+      <c r="D163" s="115">
+        <f>SUMIF(E102:E162,"Pendente",D102:D162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" s="157">
+      <c r="A164" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B162" s="159" t="n"/>
-      <c r="C162" s="159" t="n"/>
-      <c r="D162" s="159" t="n"/>
-      <c r="E162" s="159" t="n"/>
-      <c r="F162" s="159" t="n"/>
-      <c r="G162" s="160" t="n"/>
-    </row>
-    <row r="163" s="157">
-      <c r="A163" s="203">
-        <f>IF(ROUND(D161-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D161-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" s="157">
-      <c r="A164" s="203" t="inlineStr">
+      <c r="B164" s="159" t="n"/>
+      <c r="C164" s="159" t="n"/>
+      <c r="D164" s="159" t="n"/>
+      <c r="E164" s="159" t="n"/>
+      <c r="F164" s="159" t="n"/>
+      <c r="G164" s="160" t="n"/>
+    </row>
+    <row r="165" s="157">
+      <c r="A165" s="203">
+        <f>IF(ROUND(D163-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D163-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" s="157">
+      <c r="A166" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="165" s="157"/>
-    <row r="166" s="157"/>
     <row r="167" s="157"/>
     <row r="168" s="157"/>
     <row r="169" s="157"/>
@@ -71537,21 +71741,21 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A162:G162"/>
-    <mergeCell ref="A163:G163"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
+    <mergeCell ref="A165:G165"/>
     <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A164:G164"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E102:E160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E102:E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56794,38 +56794,86 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="17" t="n"/>
-      <c r="B121" s="18" t="n"/>
+      <c r="A121" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B121" s="18" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C121" s="18" t="n"/>
       <c r="D121" s="27" t="n"/>
       <c r="E121" s="18" t="n"/>
       <c r="F121" s="19" t="n"/>
-      <c r="G121" s="19" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="18" t="n"/>
+      <c r="G121" s="19" t="n">
+        <v>139.32</v>
+      </c>
+      <c r="H121" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377737 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
+        </is>
+      </c>
       <c r="J121" s="18" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="44" t="n"/>
-      <c r="B122" s="45" t="n"/>
+      <c r="A122" s="44" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B122" s="45" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C122" s="45" t="n"/>
       <c r="D122" s="46" t="n"/>
       <c r="E122" s="45" t="n"/>
       <c r="F122" s="47" t="n"/>
-      <c r="G122" s="48" t="n"/>
-      <c r="H122" s="49" t="n"/>
-      <c r="I122" s="45" t="n"/>
+      <c r="G122" s="48" t="n">
+        <v>865.52</v>
+      </c>
+      <c r="H122" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I122" s="45" t="inlineStr">
+        <is>
+          <t>Boleto doc. 377738 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="17" t="n"/>
-      <c r="B123" s="18" t="n"/>
+      <c r="A123" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B123" s="18" t="inlineStr">
+        <is>
+          <t>Patrus Transportes</t>
+        </is>
+      </c>
       <c r="C123" s="18" t="n"/>
       <c r="D123" s="27" t="n"/>
       <c r="E123" s="18" t="n"/>
       <c r="F123" s="19" t="n"/>
-      <c r="G123" s="19" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="18" t="n"/>
+      <c r="G123" s="19" t="n">
+        <v>277.48</v>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I123" s="18" t="inlineStr">
+        <is>
+          <t>Frete — boleto Bradesco, venc. 16/10/2026. Pago em 16/10/2026.</t>
+        </is>
+      </c>
       <c r="J123" s="18" t="n"/>
     </row>
     <row r="124">
@@ -67907,7 +67955,7 @@
       </c>
       <c r="E41" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F41" s="112">
@@ -67916,7 +67964,7 @@
       </c>
       <c r="G41" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377737 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 725,16 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777371117471168.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377737 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 725,16 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777371117471168. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -67939,7 +67987,7 @@
       </c>
       <c r="E42" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F42" s="113">
@@ -67948,7 +67996,7 @@
       </c>
       <c r="G42" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377738 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.327,52 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777381143358478.</t>
+          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377738 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.327,52 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777381143358478. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -69443,7 +69491,7 @@
       </c>
       <c r="E89" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F89" s="112">
@@ -69452,7 +69500,7 @@
       </c>
       <c r="G89" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2. Linha digitável 23791.43007 93484.000265 98003.073701 2 16010000027748.</t>
+          <t>Categoria quando pagar: Transporte e Entregas. Boleto Bradesco 237-2. Linha digitável 23791.43007 93484.000265 98003.073701 2 16010000027748. Pago em 16/10/2026 — lançado em "Out 2026" como "Patrus Transportes".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56877,49 +56877,113 @@
       <c r="J123" s="18" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="44" t="n"/>
-      <c r="B124" s="45" t="n"/>
+      <c r="A124" s="44" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B124" s="45" t="inlineStr">
+        <is>
+          <t>Cloro e Cia (Mello e Castiglioni Ltda)</t>
+        </is>
+      </c>
       <c r="C124" s="45" t="n"/>
       <c r="D124" s="46" t="n"/>
       <c r="E124" s="45" t="n"/>
       <c r="F124" s="47" t="n"/>
-      <c r="G124" s="48" t="n"/>
-      <c r="H124" s="49" t="n"/>
-      <c r="I124" s="45" t="n"/>
+      <c r="G124" s="48" t="n">
+        <v>36</v>
+      </c>
+      <c r="H124" s="49" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I124" s="45" t="inlineStr">
+        <is>
+          <t>DAV 000398 de 17/10/2026 — papel toalha interfolhado, álcool gel 1 L e sabonete líquido 1 L (R$ 37,50 com R$ 1,50 de desconto). Pago em dinheiro.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="17" t="n"/>
-      <c r="B125" s="18" t="n"/>
+      <c r="A125" s="17" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B125" s="18" t="inlineStr">
+        <is>
+          <t>Diarista Eva</t>
+        </is>
+      </c>
       <c r="C125" s="18" t="n"/>
       <c r="D125" s="27" t="n"/>
       <c r="E125" s="18" t="n"/>
       <c r="F125" s="19" t="n"/>
-      <c r="G125" s="19" t="n"/>
-      <c r="H125" s="21" t="n"/>
-      <c r="I125" s="18" t="n"/>
+      <c r="G125" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="H125" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr">
+        <is>
+          <t>Pedido da Edilânia em 17/10/2026 — despesa pessoal.</t>
+        </is>
+      </c>
       <c r="J125" s="18" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="44" t="n"/>
-      <c r="B126" s="45" t="n"/>
+      <c r="A126" s="44" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B126" s="45" t="inlineStr">
+        <is>
+          <t>Compras para casa</t>
+        </is>
+      </c>
       <c r="C126" s="45" t="n"/>
       <c r="D126" s="46" t="n"/>
       <c r="E126" s="45" t="n"/>
       <c r="F126" s="47" t="n"/>
-      <c r="G126" s="48" t="n"/>
-      <c r="H126" s="49" t="n"/>
-      <c r="I126" s="45" t="n"/>
+      <c r="G126" s="48" t="n">
+        <v>200</v>
+      </c>
+      <c r="H126" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I126" s="45" t="inlineStr">
+        <is>
+          <t>Pedido da Edilânia em 17/10/2026 — despesa pessoal.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="17" t="n"/>
-      <c r="B127" s="18" t="n"/>
+      <c r="A127" s="17" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
       <c r="C127" s="18" t="n"/>
       <c r="D127" s="27" t="n"/>
       <c r="E127" s="18" t="n"/>
       <c r="F127" s="19" t="n"/>
-      <c r="G127" s="19" t="n"/>
-      <c r="H127" s="21" t="n"/>
-      <c r="I127" s="18" t="n"/>
+      <c r="G127" s="19" t="n">
+        <v>610</v>
+      </c>
+      <c r="H127" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
+        <is>
+          <t>Comissões da quinzena de 05/10 a 16/10/2026 — R$ 610,00 de R$ 615,00; os R$ 5,00 restantes (venda de pré-filtro de 10/10) ficam para a próxima semana, por falta de troco no caixa.</t>
+        </is>
+      </c>
       <c r="J127" s="18" t="n"/>
     </row>
     <row r="128">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -41159,7 +41159,7 @@
       </c>
       <c r="J46" s="45" t="inlineStr">
         <is>
-          <t>EMP-0165</t>
+          <t>EMP-0138</t>
         </is>
       </c>
     </row>
@@ -56987,141 +56987,400 @@
       <c r="J127" s="18" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="44" t="n"/>
-      <c r="B128" s="45" t="n"/>
-      <c r="C128" s="45" t="n"/>
-      <c r="D128" s="46" t="n"/>
-      <c r="E128" s="45" t="n"/>
+      <c r="A128" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B128" s="45" t="inlineStr">
+        <is>
+          <t>Carneiro Ultra Drogaria LTDA - Filial 02</t>
+        </is>
+      </c>
+      <c r="C128" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D128" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E128" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F128" s="47" t="n"/>
       <c r="G128" s="48" t="n"/>
       <c r="H128" s="49" t="n"/>
       <c r="I128" s="45" t="n"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>EMP-0043</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="17" t="n"/>
-      <c r="B129" s="18" t="n"/>
-      <c r="C129" s="18" t="n"/>
-      <c r="D129" s="27" t="n"/>
-      <c r="E129" s="18" t="n"/>
+      <c r="A129" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>Otica Imagem - José Luciano Viera Costa</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D129" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F129" s="19" t="n"/>
       <c r="G129" s="19" t="n"/>
       <c r="H129" s="21" t="n"/>
-      <c r="I129" s="18" t="n"/>
-      <c r="J129" s="18" t="n"/>
+      <c r="I129" s="18" t="inlineStr">
+        <is>
+          <t>Ótica pagou R$ 280,00 pelas duas trocas (térreo e 1º andar).</t>
+        </is>
+      </c>
+      <c r="J129" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0238</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="44" t="n"/>
-      <c r="B130" s="45" t="n"/>
-      <c r="C130" s="45" t="n"/>
-      <c r="D130" s="46" t="n"/>
-      <c r="E130" s="45" t="n"/>
+      <c r="A130" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B130" s="45" t="inlineStr">
+        <is>
+          <t>Otica Imagem - José Luciano Viera Costa 1 Andar</t>
+        </is>
+      </c>
+      <c r="C130" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D130" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E130" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F130" s="47" t="n"/>
       <c r="G130" s="48" t="n"/>
       <c r="H130" s="49" t="n"/>
-      <c r="I130" s="45" t="n"/>
+      <c r="I130" s="45" t="inlineStr">
+        <is>
+          <t>Ótica pagou R$ 280,00 pelas duas trocas (térreo e 1º andar).</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>EMP-0238</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="17" t="n"/>
-      <c r="B131" s="18" t="n"/>
-      <c r="C131" s="18" t="n"/>
-      <c r="D131" s="27" t="n"/>
-      <c r="E131" s="18" t="n"/>
+      <c r="A131" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>Pedras e Pisos - Loja</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D131" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F131" s="19" t="n"/>
       <c r="G131" s="19" t="n"/>
       <c r="H131" s="21" t="n"/>
       <c r="I131" s="18" t="n"/>
-      <c r="J131" s="18" t="n"/>
+      <c r="J131" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0245</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="44" t="n"/>
-      <c r="B132" s="45" t="n"/>
-      <c r="C132" s="45" t="n"/>
-      <c r="D132" s="46" t="n"/>
-      <c r="E132" s="45" t="n"/>
+      <c r="A132" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B132" s="45" t="inlineStr">
+        <is>
+          <t>Marsilia Marmores e Granitos Erelli</t>
+        </is>
+      </c>
+      <c r="C132" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D132" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E132" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F132" s="47" t="n"/>
       <c r="G132" s="48" t="n"/>
       <c r="H132" s="49" t="n"/>
       <c r="I132" s="45" t="n"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>EMP-0216</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="17" t="n"/>
-      <c r="B133" s="18" t="n"/>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="27" t="n"/>
-      <c r="E133" s="18" t="n"/>
+      <c r="A133" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>Gilberto de Aguiar</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D133" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F133" s="19" t="n"/>
       <c r="G133" s="19" t="n"/>
       <c r="H133" s="21" t="n"/>
       <c r="I133" s="18" t="n"/>
-      <c r="J133" s="18" t="n"/>
+      <c r="J133" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0629</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="44" t="n"/>
-      <c r="B134" s="45" t="n"/>
-      <c r="C134" s="45" t="n"/>
-      <c r="D134" s="46" t="n"/>
-      <c r="E134" s="45" t="n"/>
+      <c r="A134" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B134" s="45" t="inlineStr">
+        <is>
+          <t>A. S. Supermercado</t>
+        </is>
+      </c>
+      <c r="C134" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D134" s="46" t="n">
+        <v>190</v>
+      </c>
+      <c r="E134" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F134" s="47" t="n"/>
       <c r="G134" s="48" t="n"/>
       <c r="H134" s="49" t="n"/>
       <c r="I134" s="45" t="n"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>EMP-0321</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="17" t="n"/>
-      <c r="B135" s="18" t="n"/>
-      <c r="C135" s="18" t="n"/>
-      <c r="D135" s="27" t="n"/>
-      <c r="E135" s="18" t="n"/>
-      <c r="F135" s="19" t="n"/>
+      <c r="A135" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>Raulino Gonçalves dos Santos</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Branco</t>
+        </is>
+      </c>
+      <c r="D135" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F135" s="19" t="n">
+        <v>119.85</v>
+      </c>
       <c r="G135" s="19" t="n"/>
       <c r="H135" s="21" t="n"/>
-      <c r="I135" s="18" t="n"/>
-      <c r="J135" s="18" t="n"/>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>Parcelado em 4x. Instalado em 19/10/2026.</t>
+        </is>
+      </c>
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0906</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="44" t="n"/>
-      <c r="B136" s="45" t="n"/>
-      <c r="C136" s="45" t="n"/>
-      <c r="D136" s="46" t="n"/>
-      <c r="E136" s="45" t="n"/>
+      <c r="A136" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B136" s="45" t="inlineStr">
+        <is>
+          <t>Larissa Sena</t>
+        </is>
+      </c>
+      <c r="C136" s="45" t="inlineStr">
+        <is>
+          <t>Refil FPA14</t>
+        </is>
+      </c>
+      <c r="D136" s="46" t="n">
+        <v>110</v>
+      </c>
+      <c r="E136" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F136" s="47" t="n"/>
       <c r="G136" s="48" t="n"/>
       <c r="H136" s="49" t="n"/>
-      <c r="I136" s="45" t="n"/>
+      <c r="I136" s="45" t="inlineStr">
+        <is>
+          <t>Pix de R$ 250,00 junto com o refil da Int Odontologia (R$ 140,00).</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>CLI-0907</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="17" t="n"/>
-      <c r="B137" s="18" t="n"/>
-      <c r="C137" s="18" t="n"/>
-      <c r="D137" s="27" t="n"/>
-      <c r="E137" s="18" t="n"/>
+      <c r="A137" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>Int Odontologia - Larissa Sena</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F137" s="19" t="n"/>
       <c r="G137" s="19" t="n"/>
       <c r="H137" s="21" t="n"/>
-      <c r="I137" s="18" t="n"/>
-      <c r="J137" s="18" t="n"/>
+      <c r="I137" s="18" t="inlineStr">
+        <is>
+          <t>Pago adiantado em 19/10/2026 no mesmo Pix de R$ 250,00 da Larissa Sena; troca prevista para 20/10/2026.</t>
+        </is>
+      </c>
+      <c r="J137" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0184</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="44" t="n"/>
-      <c r="B138" s="45" t="n"/>
+      <c r="A138" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B138" s="45" t="inlineStr">
+        <is>
+          <t>Combustível</t>
+        </is>
+      </c>
       <c r="C138" s="45" t="n"/>
       <c r="D138" s="46" t="n"/>
       <c r="E138" s="45" t="n"/>
       <c r="F138" s="47" t="n"/>
-      <c r="G138" s="48" t="n"/>
-      <c r="H138" s="49" t="n"/>
-      <c r="I138" s="45" t="n"/>
+      <c r="G138" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="H138" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
+      <c r="I138" s="45" t="inlineStr">
+        <is>
+          <t>Etanol aditivado V-Power 6,186 L a R$ 4,85/L — Posto Avenida Jacobina (Avenida Posto de Combustíveis LTDA, CNPJ 46.115.794/0001-30, Av. Orlando Oliveira Pires, 1430, Centro, Jacobina), NFC-e nº 000930413 série 002 de 19/10/2026 16:34. Pago R$ 30,00 em dinheiro.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="17" t="n"/>
-      <c r="B139" s="18" t="n"/>
+      <c r="A139" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>Vale Edilânia</t>
+        </is>
+      </c>
       <c r="C139" s="18" t="n"/>
       <c r="D139" s="27" t="n"/>
       <c r="E139" s="18" t="n"/>
       <c r="F139" s="19" t="n"/>
-      <c r="G139" s="19" t="n"/>
-      <c r="H139" s="21" t="n"/>
-      <c r="I139" s="18" t="n"/>
+      <c r="G139" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
+        <is>
+          <t>Vale de R$ 20,00 retirado do caixa em 19/10/2026.</t>
+        </is>
+      </c>
       <c r="J139" s="18" t="n"/>
     </row>
     <row r="140">

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -57384,15 +57384,36 @@
       <c r="J139" s="18" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="44" t="n"/>
-      <c r="B140" s="45" t="n"/>
-      <c r="C140" s="45" t="n"/>
-      <c r="D140" s="46" t="n"/>
-      <c r="E140" s="45" t="n"/>
+      <c r="A140" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B140" s="45" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste do Brasil</t>
+        </is>
+      </c>
+      <c r="C140" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D140" s="46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E140" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F140" s="47" t="n"/>
       <c r="G140" s="48" t="n"/>
       <c r="H140" s="49" t="n"/>
       <c r="I140" s="45" t="n"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>EMP-0220</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -57416,96 +57416,250 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="17" t="n"/>
-      <c r="B141" s="18" t="n"/>
+      <c r="A141" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>Receita Federal — Simples Nacional (DAS)</t>
+        </is>
+      </c>
       <c r="C141" s="18" t="n"/>
       <c r="D141" s="27" t="n"/>
       <c r="E141" s="18" t="n"/>
       <c r="F141" s="19" t="n"/>
-      <c r="G141" s="19" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="18" t="n"/>
+      <c r="G141" s="19" t="n">
+        <v>1430.03</v>
+      </c>
+      <c r="H141" s="21" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I141" s="18" t="inlineStr">
+        <is>
+          <t>DAS competência setembro/2026 (doc. 07.20.26292.9598304-7) — venc. 20/10/2026. Detalhe: IRPJ R$ 78,65 · CSLL R$ 50,05 · COFINS R$ 182,19 · PIS R$ 39,47 · INSS R$ 593,46 · ICMS (BA) R$ 486,21. Pago em 20/10/2026 pelo Banco do Nordeste.</t>
+        </is>
+      </c>
       <c r="J141" s="18" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="44" t="n"/>
-      <c r="B142" s="45" t="n"/>
-      <c r="C142" s="45" t="n"/>
-      <c r="D142" s="46" t="n"/>
-      <c r="E142" s="45" t="n"/>
+      <c r="A142" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B142" s="45" t="inlineStr">
+        <is>
+          <t>Sindicato dos Trabalhadores Rurais</t>
+        </is>
+      </c>
+      <c r="C142" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D142" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E142" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F142" s="47" t="n"/>
       <c r="G142" s="48" t="n"/>
       <c r="H142" s="49" t="n"/>
-      <c r="I142" s="45" t="n"/>
+      <c r="I142" s="45" t="inlineStr">
+        <is>
+          <t>Comprou na loja.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>OUT-0087</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="17" t="n"/>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="27" t="n"/>
-      <c r="E143" s="18" t="n"/>
+      <c r="A143" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>Magna dos Santos Carneiro Goncalves - Mirna</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F143" s="19" t="n"/>
       <c r="G143" s="19" t="n"/>
       <c r="H143" s="21" t="n"/>
       <c r="I143" s="18" t="n"/>
-      <c r="J143" s="18" t="n"/>
+      <c r="J143" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0488</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="44" t="n"/>
-      <c r="B144" s="45" t="n"/>
-      <c r="C144" s="45" t="n"/>
-      <c r="D144" s="46" t="n"/>
-      <c r="E144" s="45" t="n"/>
+      <c r="A144" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B144" s="45" t="inlineStr">
+        <is>
+          <t>Real Calçados Loja 1</t>
+        </is>
+      </c>
+      <c r="C144" s="45" t="inlineStr">
+        <is>
+          <t>2x Refil Everest + Refil Pro Life + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D144" s="46" t="n">
+        <v>515</v>
+      </c>
+      <c r="E144" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F144" s="47" t="n"/>
       <c r="G144" s="48" t="n"/>
       <c r="H144" s="49" t="n"/>
-      <c r="I144" s="45" t="n"/>
+      <c r="I144" s="45" t="inlineStr">
+        <is>
+          <t>Loja 1 — térreo: Refil Everest + Pré Filtro · 1º andar: Refil Everest · 2º andar: Refil Pro Life + Pré Filtro. Total R$ 540,00 com desconto de R$ 25,00.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>EMP-0255</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="17" t="n"/>
-      <c r="B145" s="18" t="n"/>
+      <c r="A145" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C145" s="18" t="n"/>
       <c r="D145" s="27" t="n"/>
       <c r="E145" s="18" t="n"/>
       <c r="F145" s="19" t="n"/>
-      <c r="G145" s="19" t="n"/>
-      <c r="H145" s="21" t="n"/>
-      <c r="I145" s="18" t="n"/>
+      <c r="G145" s="19" t="n">
+        <v>874.6799999999999</v>
+      </c>
+      <c r="H145" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
+        <is>
+          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 4/5 — venc. 20/10/2026. Pago em 20/10/2026.</t>
+        </is>
+      </c>
       <c r="J145" s="18" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="44" t="n"/>
-      <c r="B146" s="45" t="n"/>
+      <c r="A146" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B146" s="45" t="inlineStr">
+        <is>
+          <t>FGTS Digital (GFD)</t>
+        </is>
+      </c>
       <c r="C146" s="45" t="n"/>
       <c r="D146" s="46" t="n"/>
       <c r="E146" s="45" t="n"/>
       <c r="F146" s="47" t="n"/>
-      <c r="G146" s="48" t="n"/>
-      <c r="H146" s="49" t="n"/>
-      <c r="I146" s="45" t="n"/>
+      <c r="G146" s="48" t="n">
+        <v>136</v>
+      </c>
+      <c r="H146" s="49" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I146" s="45" t="inlineStr">
+        <is>
+          <t>FGTS mensal — competência 09/2026. Venc. 20/10/2026, pago em 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="17" t="n"/>
-      <c r="B147" s="18" t="n"/>
+      <c r="A147" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>Receita Federal — DARF / INSS</t>
+        </is>
+      </c>
       <c r="C147" s="18" t="n"/>
       <c r="D147" s="27" t="n"/>
       <c r="E147" s="18" t="n"/>
       <c r="F147" s="19" t="n"/>
-      <c r="G147" s="19" t="n"/>
-      <c r="H147" s="21" t="n"/>
-      <c r="I147" s="18" t="n"/>
+      <c r="G147" s="19" t="n">
+        <v>306.99</v>
+      </c>
+      <c r="H147" s="21" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>DARF / INSS — período de apuração setembro/2026. Venc. 20/10/2026, pago em 20/10/2026.</t>
+        </is>
+      </c>
       <c r="J147" s="18" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="44" t="n"/>
-      <c r="B148" s="45" t="n"/>
-      <c r="C148" s="45" t="n"/>
-      <c r="D148" s="46" t="n"/>
-      <c r="E148" s="45" t="n"/>
+      <c r="A148" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B148" s="45" t="inlineStr">
+        <is>
+          <t>Loja da Claro</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>Refil Lacqua</t>
+        </is>
+      </c>
+      <c r="D148" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="E148" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F148" s="47" t="n"/>
       <c r="G148" s="48" t="n"/>
       <c r="H148" s="49" t="n"/>
-      <c r="I148" s="45" t="n"/>
+      <c r="I148" s="45" t="inlineStr">
+        <is>
+          <t>Cliente ainda não cadastrado na Planilha de Clientes.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="17" t="n"/>
@@ -68395,7 +68549,7 @@
       </c>
       <c r="E44" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F44" s="113">
@@ -68404,7 +68558,7 @@
       </c>
       <c r="G44" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249.</t>
+          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249. Pago em 20/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -69899,7 +70053,7 @@
       </c>
       <c r="E91" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F91" s="112">
@@ -69908,7 +70062,7 @@
       </c>
       <c r="G91" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas. Pagamento via QR Code Pix no documento original da guia (GFD).</t>
+          <t>Categoria: Impostos e Taxas. Pagamento via QR Code Pix no documento original da guia (GFD). Pago em 20/10/2026 — lançado em "Out 2026" como "FGTS Digital (GFD)".</t>
         </is>
       </c>
     </row>
@@ -69931,7 +70085,7 @@
       </c>
       <c r="E92" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F92" s="113">
@@ -69940,7 +70094,7 @@
       </c>
       <c r="G92" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Impostos e Taxas. Código de barras 858300000033 069903852621 930716262672 196301377104.</t>
+          <t>Categoria: Impostos e Taxas. Código de barras 858300000033 069903852621 930716262672 196301377104. Pago em 20/10/2026 — lançado em "Out 2026" como "Receita Federal — DARF / INSS".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -57454,11 +57454,11 @@
       </c>
       <c r="C142" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="D142" s="46" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E142" s="45" t="inlineStr">
         <is>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -54239,7 +54239,7 @@
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>Boleto Itaú — NF-e 72869 (emissão 07/05/2026), parcela 5/5 (última), vencimento 04/10/2026 (domingo), pago em 05/10/2026.</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 72869 de 07/05/2026, nota de R$ 4.904,13 em 5 boletos). Boleto Itaú — NF-e 72869 (emissão 07/05/2026), parcela 5/5 (última), vencimento 04/10/2026 (domingo), pago em 05/10/2026.</t>
         </is>
       </c>
     </row>
@@ -54506,7 +54506,7 @@
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>NF 133138 parcela 3/4 — boleto Itaú nosso número 109/00257851-4. Venc. 07/10/2026, pago antecipado em 06/10/2026.</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). NF 133138 parcela 3/4 — boleto Itaú nosso número 109/00257851-4. Venc. 07/10/2026, pago antecipado em 06/10/2026.</t>
         </is>
       </c>
       <c r="J47" s="18" t="n"/>
@@ -54900,7 +54900,7 @@
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
-          <t>Boleto Itaú — NF-e 73636 (emissão 10/06/2026), parcela 4/5, vencimento 08/10/2026, pago em 08/10/2026.</t>
+          <t>Comprado: 100x Refil Everest (NF-e 73636 de 10/06/2026, nota de R$ 4.394,61 em 5 boletos). Boleto Itaú — NF-e 73636 (emissão 10/06/2026), parcela 4/5, vencimento 08/10/2026, pago em 08/10/2026.</t>
         </is>
       </c>
       <c r="J59" s="18" t="n"/>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="I60" s="45" t="inlineStr">
         <is>
-          <t>NF 133812 parcela 2 — boleto Itaú. Venc. 09/10/2026, pago antecipado em 08/10/2026.</t>
+          <t>Comprado: 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4" + 15x Refil Carbon Tech 5" + 4x Refil Plissado 9.3/4" (Poli Flu) + 6x Carcaça Fit 9.3/4" Branca (rosca 3/4") + 5x Regulador de Pressão 3/8" (NF-e 133812 de 28/08/2026, nota de R$ 2.093,55 em 4 boletos). NF 133812 parcela 2 — boleto Itaú. Venc. 09/10/2026, pago antecipado em 08/10/2026.</t>
         </is>
       </c>
     </row>
@@ -56354,7 +56354,7 @@
       </c>
       <c r="I106" s="45" t="inlineStr">
         <is>
-          <t>Boleto doc. 74454 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 74454 de 17/07/2026, nota de R$ 4.904,13 em 5 boletos). Boleto doc. 74454 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
-          <t>Boleto doc. 381554 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+          <t>Comprado: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata (NF-e 381554 de 17/07/2026, nota de R$ 4.461,49 em 5 boletos). Boleto doc. 381554 (emissão 17/07/2026) · parcela 3/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
         </is>
       </c>
       <c r="J107" s="18" t="n"/>
@@ -56409,7 +56409,7 @@
       </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
-          <t>Boleto doc. 386188 (emissão 15/09/2026) · parcela 1/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Boleto doc. 386188 (emissão 15/09/2026) · parcela 1/5 — venc. 15/10/2026. Pago em 15/10/2026.</t>
         </is>
       </c>
     </row>
@@ -56491,7 +56491,7 @@
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
-          <t>Boleto doc. 377739 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago antecipado em 15/10/2026.</t>
+          <t>Comprado: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata (NF-e 377739 de 19/05/2026, nota de R$ 4.281,74 em 5 boletos). Boleto doc. 377739 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago antecipado em 15/10/2026.</t>
         </is>
       </c>
       <c r="J111" s="18" t="n"/>
@@ -56816,7 +56816,7 @@
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
-          <t>Boleto doc. 377737 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
+          <t>Comprado: 12x Conexão T + 30x Registro + 20x Botão Completo de Purificador + 30x Suporte de Parede (NF-e 377737 de 19/05/2026, nota de R$ 725,16 em 5 boletos). Boleto doc. 377737 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
         </is>
       </c>
       <c r="J121" s="18" t="n"/>
@@ -56844,7 +56844,7 @@
       </c>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Boleto doc. 377738 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
+          <t>Comprado: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto (NF-e 377738 de 19/05/2026, nota de R$ 4.327,52 em 5 boletos). Boleto doc. 377738 (emissão 19/05/2026) · parcela 5/5 (última) — venc. 16/10/2026. Pago em 16/10/2026.</t>
         </is>
       </c>
     </row>
@@ -57570,7 +57570,7 @@
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
-          <t>Boleto doc. 379826 (emissão 22/06/2026) · parcela 4/5 — venc. 20/10/2026. Pago em 20/10/2026.</t>
+          <t>Comprado: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco (NF-e 379826 de 22/06/2026, nota de R$ 4.373,40 em 5 boletos). Boleto doc. 379826 (emissão 22/06/2026) · parcela 4/5 — venc. 20/10/2026. Pago em 20/10/2026.</t>
         </is>
       </c>
       <c r="J145" s="18" t="n"/>
@@ -67367,7 +67367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -67418,7 +67418,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D97</f>
+        <f>D102</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -67534,7 +67534,7 @@
       </c>
       <c r="G12" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 31/08/2026 — lançado em "Ago 2026" como "Eversoft" (R$ 878,93).</t>
+          <t>Comprado: 100x Refil Everest (NF-e 72153 de 02/04/2026, nota de R$ 4.394,61 em 5 boletos). Categoria: Fornecedores / Mercadoria. Pago em 31/08/2026 — lançado em "Ago 2026" como "Eversoft" (R$ 878,93).</t>
         </is>
       </c>
     </row>
@@ -67694,7 +67694,7 @@
       </c>
       <c r="G17" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 02/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 5x Refil FP4 + 8x Refil Carbon Tech 5" + 120x Refil E3 + 90x Refil Pré-E3 + 10x Refil Top Multifilter + 4x Refil FPA16 (NF-e 131997 de 08/07/2026, nota de R$ 5.831,67 em 4 boletos). Categoria: Fornecedores / Mercadoria. Pago em 02/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -67726,7 +67726,7 @@
       </c>
       <c r="G18" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 03/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Plus Prata + Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Slim Prata + Purificador Everest Fit Branco (NF-e 374271 de 06/04/2026, nota de R$ 3.533,27 em 5 boletos). Categoria: Fornecedores / Mercadoria. Pago em 03/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -67758,7 +67758,7 @@
       </c>
       <c r="G19" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 04/09/2026 pelo Banco do Nordeste (DOC 5301) — lançado em "Set 2026" como "Eversoft" (R$ 980,83).</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 72869 de 07/05/2026, nota de R$ 4.904,13 em 5 boletos). Categoria: Fornecedores / Mercadoria. Pago em 04/09/2026 pelo Banco do Nordeste (DOC 5301) — lançado em "Set 2026" como "Eversoft" (R$ 980,83).</t>
         </is>
       </c>
     </row>
@@ -67822,7 +67822,7 @@
       </c>
       <c r="G21" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/09/2026 — lançado em Set 2026 como "Eversoft".</t>
+          <t>Comprado: 100x Refil Everest (NF-e 73636 de 10/06/2026, nota de R$ 4.394,61 em 5 boletos). Categoria: Fornecedores / Mercadoria. Pago em 08/09/2026 — lançado em Set 2026 como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -67854,7 +67854,7 @@
       </c>
       <c r="G22" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7, nosso número 109/00257849-8. Pago em 09/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7, nosso número 109/00257849-8. Pago em 09/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -68046,7 +68046,7 @@
       </c>
       <c r="G28" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638767-8. Linha digitável 34191.12283 63876.780303 55679.010003 5 15700000098083. Pago em 15/09/2026 pelo Banco do Nordeste (DOC 91607814) — lançado em "Set 2026" como "Eversoft".</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 74454 de 17/07/2026, nota de R$ 4.904,13 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638767-8. Linha digitável 34191.12283 63876.780303 55679.010003 5 15700000098083. Pago em 15/09/2026 pelo Banco do Nordeste (DOC 91607814) — lançado em "Set 2026" como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -68078,7 +68078,7 @@
       </c>
       <c r="G29" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604587-0. Linha digitável 34191.12333 60458.700303 55679.010003 3 15800000094006. Após o vencimento: juros ao dia + multa de 2%. Pago em 24/09/2026 (antecipado, venc. 25/09) — lançado em "Set 2026" como "Eversoft".</t>
+          <t>Comprado: 100x Refil Everest + 30x Pré Filtro (NF-e 75472 de 26/08/2026, nota de R$ 4.700,32 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604587-0. Linha digitável 34191.12333 60458.700303 55679.010003 3 15800000094006. Após o vencimento: juros ao dia + multa de 2%. Pago em 24/09/2026 (antecipado, venc. 25/09) — lançado em "Set 2026" como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -68110,7 +68110,7 @@
       </c>
       <c r="G30" s="82" t="inlineStr">
         <is>
-          <t>Pago em 05/10/2026 — lançado em "Out 2026" como "Eversoft" (R$ 980,81). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 72869 (emissão 07/05/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260508782043000188550060000728691612874239.</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 72869 de 07/05/2026, nota de R$ 4.904,13 em 5 boletos). Pago em 05/10/2026 — lançado em "Out 2026" como "Eversoft" (R$ 980,81). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/19915315-9. Linha digitável 34191.12192 91531.590304 55679.010003 3 15890000098081. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 72869 (emissão 07/05/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260508782043000188550060000728691612874239.</t>
         </is>
       </c>
     </row>
@@ -68142,7 +68142,7 @@
       </c>
       <c r="G31" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Eversoft". Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
+          <t>Comprado: 100x Refil Everest (NF-e 73636 de 10/06/2026, nota de R$ 4.394,61 em 5 boletos). Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Eversoft". Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142201-6. Linha digitável 34191.12242 14220.160304 55679.010003 7 15930000087892. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
         </is>
       </c>
     </row>
@@ -68174,7 +68174,7 @@
       </c>
       <c r="G32" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381. Pago em 15/10/2026 — lançado em "Out 2026" como "Eversoft".</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 74454 de 17/07/2026, nota de R$ 4.904,13 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/28638818-9. Linha digitável 34191.12283 63881.890303 55679.010003 2 16000000098083. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381. Pago em 15/10/2026 — lançado em "Out 2026" como "Eversoft".</t>
         </is>
       </c>
     </row>
@@ -68206,7 +68206,7 @@
       </c>
       <c r="G33" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604663-9. Linha digitável 34191.12333 60466.390303 55679.010003 1 16100000094006. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
+          <t>Comprado: 100x Refil Everest + 30x Pré Filtro (NF-e 75472 de 26/08/2026, nota de R$ 4.700,32 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/33604663-9. Linha digitável 34191.12333 60466.390303 55679.010003 1 16100000094006. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -68238,7 +68238,7 @@
       </c>
       <c r="G34" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142177-8. Linha digitável 34191.12242 14217.780304 55679.010003 4 16230000087893. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
+          <t>Comprado: 100x Refil Everest (NF-e 73636 de 10/06/2026, nota de R$ 4.394,61 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (Eversoft, CNPJ 08.782.043/0001-88). Nosso número 112/24142177-8. Linha digitável 34191.12242 14217.780304 55679.010003 4 16230000087893. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 73636 (emissão 10/06/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.394,61 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260608782043000188550060000736361998873394.</t>
         </is>
       </c>
     </row>
@@ -68270,7 +68270,7 @@
       </c>
       <c r="G35" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28638136-6. Linha digitável 34191.12283 63813.660303 52238.850003 1 15700000089230. Pago em 15/09/2026 pelo Banco do Nordeste (DOC 91630932) — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata (NF-e 381554 de 17/07/2026, nota de R$ 4.461,49 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28638136-6. Linha digitável 34191.12283 63813.660303 52238.850003 1 15700000089230. Pago em 15/09/2026 pelo Banco do Nordeste (DOC 91630932) — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68302,7 +68302,7 @@
       </c>
       <c r="G36" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336084-8. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: 12x Conexão T + 30x Registro + 20x Botão Completo de Purificador + 30x Suporte de Parede (NF-e 377737 de 19/05/2026, nota de R$ 725,16 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336084-8. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68334,7 +68334,7 @@
       </c>
       <c r="G37" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336022-8. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto (NF-e 377738 de 19/05/2026, nota de R$ 4.327,52 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336022-8. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68366,7 +68366,7 @@
       </c>
       <c r="G38" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336008-7. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata (NF-e 377739 de 19/05/2026, nota de R$ 4.281,74 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21336008-7. Pago em 16/09/2026 — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68398,7 +68398,7 @@
       </c>
       <c r="G39" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528668-7. Linha digitável 34191.12259 52866.870307 52238.850003 7 15750000087468. Após o vencimento: juros ao dia + multa de 2%. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco (NF-e 379826 de 22/06/2026, nota de R$ 4.373,40 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528668-7. Linha digitável 34191.12259 52866.870307 52238.850003 7 15750000087468. Após o vencimento: juros ao dia + multa de 2%. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68430,7 +68430,7 @@
       </c>
       <c r="G40" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata (NF-e 381554 de 17/07/2026, nota de R$ 4.461,49 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/28637900-6. Linha digitável 34191.12283 63790.060303 52238.850003 9 16000000089230. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68462,7 +68462,7 @@
       </c>
       <c r="G41" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377737 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 725,16 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777371117471168. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: 12x Conexão T + 30x Registro + 20x Botão Completo de Purificador + 30x Suporte de Parede (NF-e 377737 de 19/05/2026, nota de R$ 725,16 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335994-9. Linha digitável 34191.12218 33599.490308 52238.850003 1 16010000013932. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377737 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 725,16 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777371117471168. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68494,7 +68494,7 @@
       </c>
       <c r="G42" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377738 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.327,52 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777381143358478. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto (NF-e 377738 de 19/05/2026, nota de R$ 4.327,52 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335634-1. Linha digitável 34191.12218 33563.410308 52238.850003 5 16010000086552. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377738 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.327,52 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777381143358478. Pago em 16/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68526,7 +68526,7 @@
       </c>
       <c r="G43" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377739 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.281,74 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777391313049192. Pago em 15/10/2026 (antecipado, venc. 16/10) — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata (NF-e 377739 de 19/05/2026, nota de R$ 4.281,74 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/21335118-5. Linha digitável 34191.12218 33511.850308 52238.850003 9 16010000085634. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 377739 (emissão 19/05/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.281,74 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260533079641000132550020003777391313049192. Pago em 15/10/2026 (antecipado, venc. 16/10) — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68558,7 +68558,7 @@
       </c>
       <c r="G44" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249. Pago em 20/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco (NF-e 379826 de 22/06/2026, nota de R$ 4.373,40 em 5 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/25528695-0. Linha digitável 34191.12259 52869.500307 52238.850003 1 16050000087468. Após o vencimento: juros ao dia + multa de 2%. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249. Pago em 20/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -68590,7 +68590,7 @@
       </c>
       <c r="G45" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 74454 de 17/07/2026, nota de R$ 4.904,13 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
         </is>
       </c>
     </row>
@@ -68622,7 +68622,7 @@
       </c>
       <c r="G46" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
+          <t>Comprado: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata (NF-e 381554 de 17/07/2026, nota de R$ 4.461,49 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
         </is>
       </c>
     </row>
@@ -68654,7 +68654,7 @@
       </c>
       <c r="G47" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249.</t>
+          <t>Comprado: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco (NF-e 379826 de 22/06/2026, nota de R$ 4.373,40 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 379826 (emissão 22/06/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 379826 (emissão 22/06/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.373,40 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260633079641000132550020003798261298066249.</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="G48" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
+          <t>Comprado: 100x Refil Everest + 30x Pré Filtro (NF-e 75472 de 26/08/2026, nota de R$ 4.700,32 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -68718,7 +68718,7 @@
       </c>
       <c r="G49" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
+          <t>Comprado: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata (NF-e 381554 de 17/07/2026, nota de R$ 4.461,49 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 381554 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 381554 (emissão 17/07/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.461,49 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260733079641000132550020003815541993407325.</t>
         </is>
       </c>
     </row>
@@ -68750,7 +68750,7 @@
       </c>
       <c r="G50" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
+          <t>Comprado: 100x Refil Everest + 50x Pré Filtro (NF-e 74454 de 17/07/2026, nota de R$ 4.904,13 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 74454 (emissão 17/07/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 74454 (emissão 17/07/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.904,13 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora FRACIONE TRANSPORTES EIRELI - ME. Chave da NF-e 33260708782043000188550060000744541603671381.</t>
         </is>
       </c>
     </row>
@@ -68782,7 +68782,7 @@
       </c>
       <c r="G51" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
+          <t>Comprado: 100x Refil Everest + 30x Pré Filtro (NF-e 75472 de 26/08/2026, nota de R$ 4.700,32 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -68814,7 +68814,7 @@
       </c>
       <c r="G52" s="139" t="inlineStr">
         <is>
-          <t>PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
+          <t>Comprado: 100x Refil Everest + 30x Pré Filtro (NF-e 75472 de 26/08/2026, nota de R$ 4.700,32 em 5 boletos). PREVISÃO (aguarda boleto) — o fornecedor ainda não emitiu este boleto. Valor e vencimento conforme as duplicatas da NF 75472 (emissão 26/08/2026). Categoria quando pagar: Fornecedores / Mercadoria. Conferir o boleto quando chegar. | Conferido com o XML da NF-e nº 75472 (emissão 26/08/2026): EVERSOFT INDUSTRIA E COMERCIO DE PLASTICOS LTDA, CNPJ 08.782.043/0001-88, RUA CARDOSO QUINTAO, 671, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 4.700,32 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 33260808782043000188550060000754721160252683.</t>
         </is>
       </c>
     </row>
@@ -68846,7 +68846,7 @@
       </c>
       <c r="G53" s="78" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00255359-0. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 5x Refil FP4 + 8x Refil Carbon Tech 5" + 120x Refil E3 + 90x Refil Pré-E3 + 10x Refil Top Multifilter + 4x Refil FPA16 (NF-e 131997 de 08/07/2026, nota de R$ 5.831,67 em 4 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00255359-0. Pago em 16/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -68942,7 +68942,7 @@
       </c>
       <c r="G56" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257850-6. Linha digitável 34191.09008 25785.061430 81531.550002 4 15780000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 23/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257850-6. Linha digitável 34191.09008 25785.061430 81531.550002 4 15780000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 23/09/2026 — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -69006,7 +69006,7 @@
       </c>
       <c r="G58" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 06/10/2026 (antecipado, venc. 07/10) — lançado em "Out 2026" como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria: Fornecedores / Mercadoria. Pago em 06/10/2026 (antecipado, venc. 07/10) — lançado em "Out 2026" como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257851-4. Linha digitável 34191.09008 25785.141430 81531.550002 6 15920000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
         </is>
       </c>
     </row>
@@ -69038,7 +69038,7 @@
       </c>
       <c r="G59" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
         </is>
       </c>
     </row>
@@ -69134,7 +69134,7 @@
       </c>
       <c r="G62" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841919. Linha digitável 34191.12358 84191.930308 52238.850003 3 16000000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116. Pago em 15/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>
@@ -69166,7 +69166,7 @@
       </c>
       <c r="G63" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842013. Linha digitável 34191.12358 84201.340308 52238.850003 8 16300000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842013. Linha digitável 34191.12358 84201.340308 52238.850003 8 16300000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -69198,7 +69198,7 @@
       </c>
       <c r="G64" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841927. Linha digitável 34191.12358 84192.760308 52238.850003 8 16600000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35841927. Linha digitável 34191.12358 84192.760308 52238.850003 8 16600000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -69230,7 +69230,7 @@
       </c>
       <c r="G65" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842031. Linha digitável 34191.12358 84203.160308 52238.850003 1 16900000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842031. Linha digitável 34191.12358 84203.160308 52238.850003 1 16900000057427. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -69262,7 +69262,7 @@
       </c>
       <c r="G66" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842128. Linha digitável 34191.12358 84212.800308 52238.850003 3 17200000057428. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
+          <t>Comprado: 2x Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Star Prata (NF-e 386188 de 15/09/2026, nota de R$ 2.871,36 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/35842128. Linha digitável 34191.12358 84212.800308 52238.850003 3 17200000057428. Boleto recebido por e-mail em 15/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386188". Após o vencimento: multa de 2% + juros de R$ 0,19 ao dia. | Conferido com o XML da NF-e nº 386188 (emissão 15/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 2.871,36 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003861881095200116.</t>
         </is>
       </c>
     </row>
@@ -69390,7 +69390,7 @@
       </c>
       <c r="G70" s="82" t="inlineStr">
         <is>
-          <t>Boleto substituído pela 2ª via emitida em 21/09/2026 (original: venc. 18/09/2026, R$ 591,12 — pagamento adiado para segunda 21/09). A 2ª via vale SOMENTE para 21/09/2026; se não pagar hoje, precisa gerar outra. Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/15315-5. Nosso número 109/00259098-5. Linha digitável 34191.09008 25909.801430 81531.550002 7 15760000059289. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4" + 15x Refil Carbon Tech 5" + 4x Refil Plissado 9.3/4" (Poli Flu) + 6x Carcaça Fit 9.3/4" Branca (rosca 3/4") + 5x Regulador de Pressão 3/8" (NF-e 133812 de 28/08/2026, nota de R$ 2.093,55 em 4 boletos). Boleto substituído pela 2ª via emitida em 21/09/2026 (original: venc. 18/09/2026, R$ 591,12 — pagamento adiado para segunda 21/09). A 2ª via vale SOMENTE para 21/09/2026; se não pagar hoje, precisa gerar outra. Categoria: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/15315-5. Nosso número 109/00259098-5. Linha digitável 34191.09008 25909.801430 81531.550002 7 15760000059289. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. Pago em 21/09/2026 pelo Banco do Nordeste — lançado em "Set 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -69422,7 +69422,7 @@
       </c>
       <c r="G71" s="82" t="inlineStr">
         <is>
-          <t>Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
+          <t>Comprado: 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4" + 15x Refil Carbon Tech 5" + 4x Refil Plissado 9.3/4" (Poli Flu) + 6x Carcaça Fit 9.3/4" Branca (rosca 3/4") + 5x Regulador de Pressão 3/8" (NF-e 133812 de 28/08/2026, nota de R$ 2.093,55 em 4 boletos). Categoria: Fornecedores / Mercadoria. Pago em 08/10/2026 — lançado em Out 2026 como "Filtros Planeta Água". Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259099-8. Linha digitável 34191.09008 25909.981430 81531.550002 7 15940000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -69454,7 +69454,7 @@
       </c>
       <c r="G72" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259100-4. Linha digitável 34191.09008 25910.041430 81531.550002 2 16150000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
+          <t>Comprado: 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4" + 15x Refil Carbon Tech 5" + 4x Refil Plissado 9.3/4" (Poli Flu) + 6x Carcaça Fit 9.3/4" Branca (rosca 3/4") + 5x Regulador de Pressão 3/8" (NF-e 133812 de 28/08/2026, nota de R$ 2.093,55 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259100-4. Linha digitável 34191.09008 25910.041430 81531.550002 2 16150000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -69486,7 +69486,7 @@
       </c>
       <c r="G73" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259101-2. Linha digitável 34191.09008 25910.121430 81531.550002 2 16360000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
+          <t>Comprado: 30x Refil Pro Life + 2x Refil Carbon Block 9.3/4" + 15x Refil Carbon Tech 5" + 4x Refil Plissado 9.3/4" (Poli Flu) + 6x Carcaça Fit 9.3/4" Branca (rosca 3/4") + 5x Regulador de Pressão 3/8" (NF-e 133812 de 28/08/2026, nota de R$ 2.093,55 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109), agência/código beneficiário 1438/153155. Nosso número 109/00259101-2. Linha digitável 34191.09008 25910.121430 81531.550002 2 16360000050081. NF 133812 de 28/08/2026 (total R$ 2.093,55 em 4 parcelas). Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133812 (emissão 28/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.093,55 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora JAMEF TRANSPORTES LIMITADA. Chave da NF-e 43260805097806000163550010001338121014276984.</t>
         </is>
       </c>
     </row>
@@ -69550,7 +69550,7 @@
       </c>
       <c r="G75" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -69582,7 +69582,7 @@
       </c>
       <c r="G76" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910775. Linha digitável 34191.12366 91077.530300 52238.850003 6 16380000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910775. Linha digitável 34191.12366 91077.530300 52238.850003 6 16380000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -69614,7 +69614,7 @@
       </c>
       <c r="G77" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910730. Linha digitável 34191.12366 91073.080300 52238.850003 7 16680000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910730. Linha digitável 34191.12366 91073.080300 52238.850003 7 16680000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -69646,7 +69646,7 @@
       </c>
       <c r="G78" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910821. Linha digitável 34191.12366 91082.150300 52238.850003 9 16980000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910821. Linha digitável 34191.12366 91082.150300 52238.850003 9 16980000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -69678,7 +69678,7 @@
       </c>
       <c r="G79" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910791. Linha digitável 34191.12366 91079.100300 52238.850003 7 17280000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910791. Linha digitável 34191.12366 91079.100300 52238.850003 7 17280000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
         </is>
       </c>
     </row>
@@ -69838,7 +69838,7 @@
       </c>
       <c r="G84" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879986. Linha digitável 34191.12374 87998.630302 52238.850003 9 16150000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+          <t>Comprado: 2x Purificador Everest Foz Branco + 2x Purificador Everest Foz Grafite (NF-e 387488 de 30/09/2026, nota de R$ 3.167,58 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879986. Linha digitável 34191.12374 87998.630302 52238.850003 9 16150000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
         </is>
       </c>
     </row>
@@ -69870,7 +69870,7 @@
       </c>
       <c r="G85" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879706. Linha digitável 34191.12374 87970.650302 52238.850003 9 16450000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+          <t>Comprado: 2x Purificador Everest Foz Branco + 2x Purificador Everest Foz Grafite (NF-e 387488 de 30/09/2026, nota de R$ 3.167,58 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879706. Linha digitável 34191.12374 87970.650302 52238.850003 9 16450000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
         </is>
       </c>
     </row>
@@ -69902,7 +69902,7 @@
       </c>
       <c r="G86" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879936. Linha digitável 34191.12374 87993.680302 52238.850003 5 16750000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+          <t>Comprado: 2x Purificador Everest Foz Branco + 2x Purificador Everest Foz Grafite (NF-e 387488 de 30/09/2026, nota de R$ 3.167,58 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879936. Linha digitável 34191.12374 87993.680302 52238.850003 5 16750000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
         </is>
       </c>
     </row>
@@ -69934,7 +69934,7 @@
       </c>
       <c r="G87" s="78" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879730. Linha digitável 34191.12374 87973.050302 52238.850003 3 17050000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+          <t>Comprado: 2x Purificador Everest Foz Branco + 2x Purificador Everest Foz Grafite (NF-e 387488 de 30/09/2026, nota de R$ 3.167,58 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879730. Linha digitável 34191.12374 87973.050302 52238.850003 3 17050000063352. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
         </is>
       </c>
     </row>
@@ -69966,7 +69966,7 @@
       </c>
       <c r="G88" s="82" t="inlineStr">
         <is>
-          <t>Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879582. Linha digitável 34191.12374 87958.200302 52238.850003 2 17350000063350. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
+          <t>Comprado: 2x Purificador Everest Foz Branco + 2x Purificador Everest Foz Grafite (NF-e 387488 de 30/09/2026, nota de R$ 3.167,58 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/37879582. Linha digitável 34191.12374 87958.200302 52238.850003 2 17350000063350. Boleto recebido por e-mail em 30/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 387488". Após o vencimento: multa de 2% + juros de R$ 0,21 ao dia.</t>
         </is>
       </c>
     </row>
@@ -70163,1009 +70163,1009 @@
       </c>
     </row>
     <row r="95" s="157">
-      <c r="A95" s="86" t="inlineStr">
+      <c r="A95" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B95" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 388850 (emissão 19/10/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C95" s="81" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D95" s="83" t="n">
+        <v>874.67</v>
+      </c>
+      <c r="E95" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F95" s="113">
+        <f>IF(OR($E95="Pago",$C95=""),"",MAX(0,TODAY()-$C95))</f>
+        <v/>
+      </c>
+      <c r="G95" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: 2x Purificador Everest Star Branco + Purificador Everest Fit Prata + Purificador Everest Star Preto + Purificador Everest Star Prata + Purificador Everest Fit Preto (NF-e 388850 de 19/10/2026, nota de R$ 4.373,37 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/39837740. Linha digitável 34191.12390 83774.010306 52238.850003 8 16340000087467. Boleto recebido por e-mail em 19/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 388850". Após o vencimento: multa de 2% + juros de R$ 0,29 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" s="157">
+      <c r="A96" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B96" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 388850 (emissão 19/10/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C96" s="77" t="n">
+        <v>46374</v>
+      </c>
+      <c r="D96" s="79" t="n">
+        <v>874.67</v>
+      </c>
+      <c r="E96" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F96" s="112">
+        <f>IF(OR($E96="Pago",$C96=""),"",MAX(0,TODAY()-$C96))</f>
+        <v/>
+      </c>
+      <c r="G96" s="78" t="inlineStr">
+        <is>
+          <t>Comprado: 2x Purificador Everest Star Branco + Purificador Everest Fit Prata + Purificador Everest Star Preto + Purificador Everest Star Prata + Purificador Everest Fit Preto (NF-e 388850 de 19/10/2026, nota de R$ 4.373,37 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/39837859. Linha digitável 34191.12390 83785.990306 52238.850003 5 16640000087467. Boleto recebido por e-mail em 19/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 388850". Após o vencimento: multa de 2% + juros de R$ 0,29 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" s="157">
+      <c r="A97" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B97" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 388850 (emissão 19/10/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C97" s="81" t="n">
+        <v>46404</v>
+      </c>
+      <c r="D97" s="83" t="n">
+        <v>874.67</v>
+      </c>
+      <c r="E97" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F97" s="113">
+        <f>IF(OR($E97="Pago",$C97=""),"",MAX(0,TODAY()-$C97))</f>
+        <v/>
+      </c>
+      <c r="G97" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: 2x Purificador Everest Star Branco + Purificador Everest Fit Prata + Purificador Everest Star Preto + Purificador Everest Star Prata + Purificador Everest Fit Preto (NF-e 388850 de 19/10/2026, nota de R$ 4.373,37 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/39837936. Linha digitável 34191.12390 83793.650306 52238.850003 1 16940000087467. Boleto recebido por e-mail em 19/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 388850". Após o vencimento: multa de 2% + juros de R$ 0,29 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" s="157">
+      <c r="A98" s="78" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B98" s="78" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 388850 (emissão 19/10/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C98" s="77" t="n">
+        <v>46434</v>
+      </c>
+      <c r="D98" s="79" t="n">
+        <v>874.67</v>
+      </c>
+      <c r="E98" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F98" s="112">
+        <f>IF(OR($E98="Pago",$C98=""),"",MAX(0,TODAY()-$C98))</f>
+        <v/>
+      </c>
+      <c r="G98" s="78" t="inlineStr">
+        <is>
+          <t>Comprado: 2x Purificador Everest Star Branco + Purificador Everest Fit Prata + Purificador Everest Star Preto + Purificador Everest Star Prata + Purificador Everest Fit Preto (NF-e 388850 de 19/10/2026, nota de R$ 4.373,37 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/39838041. Linha digitável 34191.12390 83804.130306 52238.850003 7 17240000087467. Boleto recebido por e-mail em 19/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 388850". Após o vencimento: multa de 2% + juros de R$ 0,29 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" s="157">
+      <c r="A99" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B99" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 388850 (emissão 19/10/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C99" s="81" t="n">
+        <v>46464</v>
+      </c>
+      <c r="D99" s="83" t="n">
+        <v>874.6900000000001</v>
+      </c>
+      <c r="E99" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F99" s="113">
+        <f>IF(OR($E99="Pago",$C99=""),"",MAX(0,TODAY()-$C99))</f>
+        <v/>
+      </c>
+      <c r="G99" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: 2x Purificador Everest Star Branco + Purificador Everest Fit Prata + Purificador Everest Star Preto + Purificador Everest Star Prata + Purificador Everest Fit Preto (NF-e 388850 de 19/10/2026, nota de R$ 4.373,37 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/39837725. Linha digitável 34191.12390 83772.520306 52238.850003 9 17540000087469. Boleto recebido por e-mail em 19/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 388850". Após o vencimento: multa de 2% + juros de R$ 0,29 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" s="157">
+      <c r="A100" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B95" s="86" t="n"/>
-      <c r="C95" s="114" t="n"/>
-      <c r="D95" s="115">
-        <f>SUMIF(E11:E94,"Pendente",D11:D94)</f>
-        <v/>
-      </c>
-      <c r="E95" s="116" t="n"/>
-      <c r="F95" s="116" t="n"/>
-      <c r="G95" s="86" t="n"/>
-    </row>
-    <row r="96" s="157">
-      <c r="A96" s="144" t="inlineStr">
+      <c r="B100" s="86" t="n"/>
+      <c r="C100" s="114" t="n"/>
+      <c r="D100" s="115">
+        <f>SUMIF(E11:E99,"Pendente",D11:D99)</f>
+        <v/>
+      </c>
+      <c r="E100" s="116" t="n"/>
+      <c r="F100" s="116" t="n"/>
+      <c r="G100" s="86" t="n"/>
+    </row>
+    <row r="101" s="157">
+      <c r="A101" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B96" s="144" t="n"/>
-      <c r="C96" s="145" t="n"/>
-      <c r="D96" s="146">
-        <f>SUMIF(E11:E94,"Previsto",D11:D94)</f>
-        <v/>
-      </c>
-      <c r="E96" s="142" t="n"/>
-      <c r="F96" s="142" t="n"/>
-      <c r="G96" s="144" t="n"/>
-    </row>
-    <row r="97" s="157">
-      <c r="A97" s="86" t="inlineStr">
+      <c r="B101" s="144" t="n"/>
+      <c r="C101" s="145" t="n"/>
+      <c r="D101" s="146">
+        <f>SUMIF(E11:E99,"Previsto",D11:D99)</f>
+        <v/>
+      </c>
+      <c r="E101" s="142" t="n"/>
+      <c r="F101" s="142" t="n"/>
+      <c r="G101" s="144" t="n"/>
+    </row>
+    <row r="102" s="157">
+      <c r="A102" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B97" s="86" t="n"/>
-      <c r="C97" s="114" t="n"/>
-      <c r="D97" s="115">
-        <f>D95+D96</f>
-        <v/>
-      </c>
-      <c r="E97" s="116" t="n"/>
-      <c r="F97" s="116" t="n"/>
-      <c r="G97" s="86" t="n"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" s="157"/>
-    <row r="99" ht="15.75" customHeight="1" s="157">
-      <c r="A99" s="200" t="inlineStr">
+      <c r="B102" s="86" t="n"/>
+      <c r="C102" s="114" t="n"/>
+      <c r="D102" s="115">
+        <f>D100+D101</f>
+        <v/>
+      </c>
+      <c r="E102" s="116" t="n"/>
+      <c r="F102" s="116" t="n"/>
+      <c r="G102" s="86" t="n"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="157"/>
+    <row r="104" ht="15.75" customHeight="1" s="157">
+      <c r="A104" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="100" s="157">
-      <c r="A100" s="194" t="inlineStr">
+    <row r="105" s="157">
+      <c r="A105" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="101" s="157">
-      <c r="A101" s="111" t="inlineStr">
+    <row r="106" s="157">
+      <c r="A106" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B101" s="111" t="inlineStr">
+      <c r="B106" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C101" s="111" t="inlineStr">
+      <c r="C106" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D101" s="111" t="inlineStr">
+      <c r="D106" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E101" s="111" t="inlineStr">
+      <c r="E106" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F101" s="111" t="inlineStr">
+      <c r="F106" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G101" s="111" t="inlineStr">
+      <c r="G106" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="102" s="157">
-      <c r="A102" s="78" t="inlineStr">
+    <row r="107" s="157">
+      <c r="A107" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B102" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C102" s="77" t="n">
+      <c r="C107" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D102" s="79" t="n">
+      <c r="D107" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E102" s="112" t="inlineStr">
+      <c r="E107" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F102" s="112">
-        <f>IF(OR($E102="Recebido",$C102=""),"",MAX(0,TODAY()-$C102))</f>
-        <v/>
-      </c>
-      <c r="G102" s="78" t="n"/>
-    </row>
-    <row r="103" s="157">
-      <c r="A103" s="82" t="inlineStr">
+      <c r="F107" s="112">
+        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
+        <v/>
+      </c>
+      <c r="G107" s="78" t="n"/>
+    </row>
+    <row r="108" s="157">
+      <c r="A108" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B103" s="82" t="inlineStr">
+      <c r="B108" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C103" s="81" t="n">
+      <c r="C108" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D103" s="83" t="n">
+      <c r="D108" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E103" s="113" t="inlineStr">
+      <c r="E108" s="113" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F103" s="113">
-        <f>IF(OR($E103="Recebido",$C103=""),"",MAX(0,TODAY()-$C103))</f>
-        <v/>
-      </c>
-      <c r="G103" s="82" t="n"/>
-    </row>
-    <row r="104" s="157">
-      <c r="A104" s="78" t="inlineStr">
+      <c r="F108" s="113">
+        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
+        <v/>
+      </c>
+      <c r="G108" s="82" t="n"/>
+    </row>
+    <row r="109" s="157">
+      <c r="A109" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B104" s="78" t="inlineStr">
+      <c r="B109" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C104" s="77" t="n">
+      <c r="C109" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D104" s="79" t="n">
+      <c r="D109" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E104" s="112" t="inlineStr">
+      <c r="E109" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F104" s="112">
-        <f>IF(OR($E104="Recebido",$C104=""),"",MAX(0,TODAY()-$C104))</f>
-        <v/>
-      </c>
-      <c r="G104" s="78" t="inlineStr">
+      <c r="F109" s="112">
+        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
+        <v/>
+      </c>
+      <c r="G109" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="105" s="157">
-      <c r="A105" s="82" t="inlineStr">
+    <row r="110" s="157">
+      <c r="A110" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B105" s="82" t="inlineStr">
+      <c r="B110" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C105" s="81" t="n">
+      <c r="C110" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D105" s="83" t="n">
+      <c r="D110" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E105" s="113" t="inlineStr">
+      <c r="E110" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F105" s="113">
-        <f>IF(OR($E105="Recebido",$C105=""),"",MAX(0,TODAY()-$C105))</f>
-        <v/>
-      </c>
-      <c r="G105" s="82" t="inlineStr">
+      <c r="F110" s="113">
+        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
+        <v/>
+      </c>
+      <c r="G110" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="106" s="157">
-      <c r="A106" s="78" t="inlineStr">
+    <row r="111" s="157">
+      <c r="A111" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B111" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C106" s="77" t="n">
+      <c r="C111" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D106" s="79" t="n">
+      <c r="D111" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E106" s="112" t="inlineStr">
+      <c r="E111" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F106" s="112">
-        <f>IF(OR($E106="Recebido",$C106=""),"",MAX(0,TODAY()-$C106))</f>
-        <v/>
-      </c>
-      <c r="G106" s="78" t="inlineStr">
+      <c r="F111" s="112">
+        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
+        <v/>
+      </c>
+      <c r="G111" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="107" s="157">
-      <c r="A107" s="82" t="inlineStr">
+    <row r="112" s="157">
+      <c r="A112" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B107" s="82" t="inlineStr">
+      <c r="B112" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C107" s="81" t="n">
+      <c r="C112" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D107" s="83" t="n">
+      <c r="D112" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E107" s="113" t="inlineStr">
+      <c r="E112" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F107" s="113">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="82" t="inlineStr">
+      <c r="F112" s="113">
+        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
+        <v/>
+      </c>
+      <c r="G112" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="108" s="157">
-      <c r="A108" s="78" t="inlineStr">
+    <row r="113" s="157">
+      <c r="A113" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B108" s="78" t="inlineStr">
+      <c r="B113" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C108" s="77" t="n">
+      <c r="C113" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D108" s="79" t="n">
+      <c r="D113" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E108" s="112" t="inlineStr">
+      <c r="E113" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="112">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="78" t="inlineStr">
+      <c r="F113" s="112">
+        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
+        <v/>
+      </c>
+      <c r="G113" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="109" s="157">
-      <c r="A109" s="82" t="inlineStr">
+    <row r="114" s="157">
+      <c r="A114" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B109" s="82" t="inlineStr">
+      <c r="B114" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C109" s="81" t="n">
+      <c r="C114" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D109" s="83" t="n">
+      <c r="D114" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E109" s="113" t="inlineStr">
+      <c r="E114" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F109" s="113">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="82" t="inlineStr">
+      <c r="F114" s="113">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="110" s="157">
-      <c r="A110" s="78" t="inlineStr">
+    <row r="115" s="157">
+      <c r="A115" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B110" s="78" t="inlineStr">
+      <c r="B115" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C110" s="77" t="n">
+      <c r="C115" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D110" s="79" t="n">
+      <c r="D115" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E110" s="112" t="inlineStr">
+      <c r="E115" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F110" s="112">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="78" t="inlineStr">
+      <c r="F115" s="112">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="111" s="157">
-      <c r="A111" s="82" t="inlineStr">
+    <row r="116" s="157">
+      <c r="A116" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B111" s="82" t="inlineStr">
+      <c r="B116" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C111" s="81" t="n">
+      <c r="C116" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D111" s="83" t="n">
+      <c r="D116" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E111" s="113" t="inlineStr">
+      <c r="E116" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="113">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="82" t="inlineStr">
+      <c r="F116" s="113">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="112" s="157">
-      <c r="A112" s="78" t="inlineStr">
+    <row r="117" s="157">
+      <c r="A117" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B112" s="78" t="inlineStr">
+      <c r="B117" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C112" s="77" t="n">
+      <c r="C117" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D112" s="79" t="n">
+      <c r="D117" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E112" s="112" t="inlineStr">
+      <c r="E117" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F112" s="112">
-        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="78" t="inlineStr">
+      <c r="F117" s="112">
+        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="113" s="157">
-      <c r="A113" s="82" t="inlineStr">
+    <row r="118" s="157">
+      <c r="A118" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B113" s="82" t="inlineStr">
+      <c r="B118" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C113" s="81" t="n">
+      <c r="C118" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D113" s="83" t="n">
+      <c r="D118" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E113" s="113" t="inlineStr">
+      <c r="E118" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F113" s="113">
-        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="82" t="inlineStr">
+      <c r="F118" s="113">
+        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="114" s="157">
-      <c r="A114" s="78" t="inlineStr">
+    <row r="119" s="157">
+      <c r="A119" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B114" s="78" t="inlineStr">
+      <c r="B119" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C114" s="77" t="n">
+      <c r="C119" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D114" s="79" t="n">
+      <c r="D119" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E114" s="112" t="inlineStr">
+      <c r="E119" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F114" s="112">
-        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="78" t="inlineStr">
+      <c r="F119" s="112">
+        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="115" s="157">
-      <c r="A115" s="82" t="inlineStr">
+    <row r="120" s="157">
+      <c r="A120" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B115" s="82" t="inlineStr">
+      <c r="B120" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C115" s="81" t="n">
+      <c r="C120" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D115" s="83" t="n">
+      <c r="D120" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E115" s="113" t="inlineStr">
+      <c r="E120" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F115" s="113">
-        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="82" t="inlineStr">
+      <c r="F120" s="113">
+        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
+        <v/>
+      </c>
+      <c r="G120" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="116" s="157">
-      <c r="A116" s="78" t="inlineStr">
+    <row r="121" s="157">
+      <c r="A121" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B116" s="78" t="inlineStr">
+      <c r="B121" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C116" s="77" t="n">
+      <c r="C121" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D116" s="79" t="n">
+      <c r="D121" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E116" s="112" t="inlineStr">
+      <c r="E121" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F116" s="112">
-        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="78" t="inlineStr">
+      <c r="F121" s="112">
+        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
+        <v/>
+      </c>
+      <c r="G121" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="117" s="157">
-      <c r="A117" s="82" t="inlineStr">
+    <row r="122" s="157">
+      <c r="A122" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B117" s="82" t="inlineStr">
+      <c r="B122" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C117" s="81" t="n">
+      <c r="C122" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D117" s="83" t="n">
+      <c r="D122" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E117" s="113" t="inlineStr">
+      <c r="E122" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F117" s="113">
-        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
-        <v/>
-      </c>
-      <c r="G117" s="82" t="inlineStr">
+      <c r="F122" s="113">
+        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
+        <v/>
+      </c>
+      <c r="G122" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="118" s="157">
-      <c r="A118" s="78" t="inlineStr">
+    <row r="123" s="157">
+      <c r="A123" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B118" s="78" t="inlineStr">
+      <c r="B123" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C118" s="77" t="n">
+      <c r="C123" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D118" s="79" t="n">
+      <c r="D123" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E118" s="112" t="inlineStr">
+      <c r="E123" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F118" s="112">
-        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
-        <v/>
-      </c>
-      <c r="G118" s="78" t="inlineStr">
+      <c r="F123" s="112">
+        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
+        <v/>
+      </c>
+      <c r="G123" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="119" s="157">
-      <c r="A119" s="82" t="inlineStr">
+    <row r="124" s="157">
+      <c r="A124" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B119" s="82" t="inlineStr">
+      <c r="B124" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C119" s="81" t="n">
+      <c r="C124" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D119" s="83" t="n">
+      <c r="D124" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E119" s="113" t="inlineStr">
+      <c r="E124" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F119" s="113">
-        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
-        <v/>
-      </c>
-      <c r="G119" s="82" t="inlineStr">
+      <c r="F124" s="113">
+        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
+        <v/>
+      </c>
+      <c r="G124" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="120" s="157">
-      <c r="A120" s="78" t="inlineStr">
+    <row r="125" s="157">
+      <c r="A125" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B120" s="78" t="inlineStr">
+      <c r="B125" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C120" s="77" t="n">
+      <c r="C125" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D120" s="79" t="n">
+      <c r="D125" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E120" s="112" t="inlineStr">
+      <c r="E125" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F120" s="112">
-        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
-        <v/>
-      </c>
-      <c r="G120" s="78" t="inlineStr">
+      <c r="F125" s="112">
+        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
+        <v/>
+      </c>
+      <c r="G125" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="121" s="157">
-      <c r="A121" s="82" t="inlineStr">
+    <row r="126" s="157">
+      <c r="A126" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B121" s="82" t="inlineStr">
+      <c r="B126" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C121" s="81" t="n">
+      <c r="C126" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D121" s="83" t="n">
+      <c r="D126" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E121" s="113" t="inlineStr">
+      <c r="E126" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F121" s="113">
-        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
-        <v/>
-      </c>
-      <c r="G121" s="82" t="inlineStr">
+      <c r="F126" s="113">
+        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
+        <v/>
+      </c>
+      <c r="G126" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="122" s="157">
-      <c r="A122" s="78" t="inlineStr">
+    <row r="127" s="157">
+      <c r="A127" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B122" s="78" t="inlineStr">
+      <c r="B127" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C122" s="77" t="n">
+      <c r="C127" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D122" s="79" t="n">
+      <c r="D127" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E122" s="112" t="inlineStr">
+      <c r="E127" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F122" s="112">
-        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
-        <v/>
-      </c>
-      <c r="G122" s="78" t="inlineStr">
+      <c r="F127" s="112">
+        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
+        <v/>
+      </c>
+      <c r="G127" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="123" s="157">
-      <c r="A123" s="82" t="inlineStr">
+    <row r="128" s="157">
+      <c r="A128" s="82" t="inlineStr">
         <is>
           <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B123" s="82" t="inlineStr">
+      <c r="B128" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C123" s="81" t="n">
+      <c r="C128" s="81" t="n">
         <v>46290</v>
       </c>
-      <c r="D123" s="83" t="n">
+      <c r="D128" s="83" t="n">
         <v>2095.2</v>
       </c>
-      <c r="E123" s="113" t="inlineStr">
+      <c r="E128" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F123" s="113">
-        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
-        <v/>
-      </c>
-      <c r="G123" s="82" t="inlineStr">
+      <c r="F128" s="113">
+        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
+        <v/>
+      </c>
+      <c r="G128" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
-    <row r="124" s="157">
-      <c r="A124" s="78" t="inlineStr">
+    <row r="129" s="157">
+      <c r="A129" s="78" t="inlineStr">
         <is>
           <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
-      <c r="B124" s="78" t="inlineStr">
+      <c r="B129" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C124" s="77" t="n">
+      <c r="C129" s="77" t="n">
         <v>46305</v>
       </c>
-      <c r="D124" s="79" t="n">
+      <c r="D129" s="79" t="n">
         <v>1188.25</v>
       </c>
-      <c r="E124" s="112" t="inlineStr">
+      <c r="E129" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F124" s="112">
-        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
-        <v/>
-      </c>
-      <c r="G124" s="78" t="inlineStr">
+      <c r="F129" s="112">
+        <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
+        <v/>
+      </c>
+      <c r="G129" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias · Recebido em 13/10/2026 no BNB (Nota Paga no portal V360).</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" s="157">
-      <c r="A125" s="82" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="B125" s="82" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C125" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D125" s="83" t="n">
-        <v>160</v>
-      </c>
-      <c r="E125" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F125" s="113">
-        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
-        <v/>
-      </c>
-      <c r="G125" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" s="157">
-      <c r="A126" s="78" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B126" s="78" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C126" s="77" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D126" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="E126" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F126" s="112">
-        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
-        <v/>
-      </c>
-      <c r="G126" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" s="157">
-      <c r="A127" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B127" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C127" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D127" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E127" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F127" s="113">
-        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
-        <v/>
-      </c>
-      <c r="G127" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" s="157">
-      <c r="A128" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B128" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C128" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D128" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E128" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F128" s="112">
-        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
-        <v/>
-      </c>
-      <c r="G128" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" s="157">
-      <c r="A129" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B129" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C129" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D129" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E129" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F129" s="113">
-        <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
-        <v/>
-      </c>
-      <c r="G129" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="130" s="157">
       <c r="A130" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>Instituto Paulo Leão</t>
         </is>
       </c>
       <c r="B130" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil E3 + Pré Filtro</t>
         </is>
       </c>
       <c r="C130" s="81" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D130" s="83" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="E130" s="113" t="inlineStr">
         <is>
@@ -71178,26 +71178,26 @@
       </c>
       <c r="G130" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="131" s="157">
       <c r="A131" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
       <c r="B131" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="C131" s="77" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D131" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E131" s="112" t="inlineStr">
         <is>
@@ -71210,58 +71210,58 @@
       </c>
       <c r="G131" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="132" s="157">
-      <c r="A132" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B132" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C132" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D132" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E132" s="112" t="inlineStr">
+      <c r="A132" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B132" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C132" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D132" s="83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E132" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F132" s="112">
+      <c r="F132" s="113">
         <f>IF(OR($E132="Recebido",$C132=""),"",MAX(0,TODAY()-$C132))</f>
         <v/>
       </c>
-      <c r="G132" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+      <c r="G132" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="133" s="157">
       <c r="A133" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B133" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C133" s="77" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="D133" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E133" s="112" t="inlineStr">
         <is>
@@ -71279,85 +71279,85 @@
       </c>
     </row>
     <row r="134" s="157">
-      <c r="A134" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B134" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C134" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D134" s="79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E134" s="112" t="inlineStr">
+      <c r="A134" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B134" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C134" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D134" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E134" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F134" s="112">
+      <c r="F134" s="113">
         <f>IF(OR($E134="Recebido",$C134=""),"",MAX(0,TODAY()-$C134))</f>
         <v/>
       </c>
-      <c r="G134" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+      <c r="G134" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="135" s="157">
-      <c r="A135" s="78" t="inlineStr">
-        <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
-        </is>
-      </c>
-      <c r="B135" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C135" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D135" s="79" t="n">
-        <v>140</v>
-      </c>
-      <c r="E135" s="112" t="inlineStr">
+      <c r="A135" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B135" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C135" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D135" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E135" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F135" s="112">
+      <c r="F135" s="113">
         <f>IF(OR($E135="Recebido",$C135=""),"",MAX(0,TODAY()-$C135))</f>
         <v/>
       </c>
-      <c r="G135" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+      <c r="G135" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="136" s="157">
       <c r="A136" s="78" t="inlineStr">
         <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B136" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C136" s="77" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="D136" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
@@ -71370,26 +71370,26 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="137" s="157">
       <c r="A137" s="78" t="inlineStr">
         <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B137" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C137" s="77" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="D137" s="79" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E137" s="112" t="inlineStr">
         <is>
@@ -71402,23 +71402,23 @@
       </c>
       <c r="G137" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="138" s="157">
       <c r="A138" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B138" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C138" s="77" t="n">
-        <v>46276</v>
+        <v>46269</v>
       </c>
       <c r="D138" s="79" t="n">
         <v>140</v>
@@ -71434,26 +71434,26 @@
       </c>
       <c r="G138" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="139" s="157">
       <c r="A139" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B139" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C139" s="77" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D139" s="79" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E139" s="112" t="inlineStr">
         <is>
@@ -71466,26 +71466,26 @@
       </c>
       <c r="G139" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="140" s="157">
       <c r="A140" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B140" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C140" s="77" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D140" s="79" t="n">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E140" s="112" t="inlineStr">
         <is>
@@ -71498,14 +71498,14 @@
       </c>
       <c r="G140" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="141" s="157">
       <c r="A141" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B141" s="78" t="inlineStr">
@@ -71514,7 +71514,7 @@
         </is>
       </c>
       <c r="C141" s="77" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="D141" s="79" t="n">
         <v>200</v>
@@ -71530,26 +71530,26 @@
       </c>
       <c r="G141" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="142" s="157">
       <c r="A142" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B142" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C142" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D142" s="79" t="n">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="E142" s="112" t="inlineStr">
         <is>
@@ -71562,14 +71562,14 @@
       </c>
       <c r="G142" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="143" s="157">
       <c r="A143" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B143" s="78" t="inlineStr">
@@ -71578,7 +71578,7 @@
         </is>
       </c>
       <c r="C143" s="77" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="D143" s="79" t="n">
         <v>140</v>
@@ -71594,30 +71594,30 @@
       </c>
       <c r="G143" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="144" s="157">
       <c r="A144" s="78" t="inlineStr">
         <is>
-          <t>Centro de Especialidades Odontomédicas</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B144" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C144" s="77" t="n">
-        <v>46044</v>
+        <v>46279</v>
       </c>
       <c r="D144" s="79" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="E144" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F144" s="112">
@@ -71626,30 +71626,30 @@
       </c>
       <c r="G144" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="145" s="157">
       <c r="A145" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B145" s="78" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C145" s="77" t="n">
-        <v>46073</v>
+        <v>46281</v>
       </c>
       <c r="D145" s="79" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="E145" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F145" s="112">
@@ -71658,30 +71658,30 @@
       </c>
       <c r="G145" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="146" s="157">
       <c r="A146" s="78" t="inlineStr">
         <is>
-          <t>Centro Médico de Jacobina</t>
+          <t>Marilda Macedo / José Luciano Costa</t>
         </is>
       </c>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>2x Botão Completo</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C146" s="77" t="n">
-        <v>46203</v>
+        <v>46283</v>
       </c>
       <c r="D146" s="79" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E146" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F146" s="112">
@@ -71690,14 +71690,14 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="147" s="157">
       <c r="A147" s="78" t="inlineStr">
         <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+          <t>Tatiana Rocha</t>
         </is>
       </c>
       <c r="B147" s="78" t="inlineStr">
@@ -71706,7 +71706,7 @@
         </is>
       </c>
       <c r="C147" s="77" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="D147" s="79" t="n">
         <v>140</v>
@@ -71722,26 +71722,26 @@
       </c>
       <c r="G147" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="148" s="157">
       <c r="A148" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="B148" s="78" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C148" s="77" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="D148" s="79" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E148" s="112" t="inlineStr">
         <is>
@@ -71754,30 +71754,30 @@
       </c>
       <c r="G148" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026. Recebido em dinheiro em 14/10/2026 — lançado em "Set 2026".</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="149" s="157">
       <c r="A149" s="78" t="inlineStr">
         <is>
-          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B149" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="C149" s="77" t="n">
-        <v>46295</v>
+        <v>46044</v>
       </c>
       <c r="D149" s="79" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E149" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F149" s="112">
@@ -71786,30 +71786,30 @@
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 30/09/2026. Recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026) — lançado em "Out 2026".</t>
+          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
         </is>
       </c>
     </row>
     <row r="150" s="157">
       <c r="A150" s="78" t="inlineStr">
         <is>
-          <t>Aneilde Rios de Oliveira</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B150" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="C150" s="77" t="n">
-        <v>46296</v>
+        <v>46073</v>
       </c>
       <c r="D150" s="79" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="E150" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F150" s="112">
@@ -71818,30 +71818,30 @@
       </c>
       <c r="G150" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="151" s="157">
       <c r="A151" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Centro Médico de Jacobina</t>
         </is>
       </c>
       <c r="B151" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>2x Botão Completo</t>
         </is>
       </c>
       <c r="C151" s="77" t="n">
-        <v>46296</v>
+        <v>46203</v>
       </c>
       <c r="D151" s="79" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E151" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F151" s="112">
@@ -71850,26 +71850,26 @@
       </c>
       <c r="G151" s="78" t="inlineStr">
         <is>
-          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="152" s="157">
       <c r="A152" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
         </is>
       </c>
       <c r="B152" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C152" s="77" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="D152" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E152" s="112" t="inlineStr">
         <is>
@@ -71882,30 +71882,30 @@
       </c>
       <c r="G152" s="78" t="inlineStr">
         <is>
-          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
     <row r="153" s="157">
       <c r="A153" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B153" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil C+3</t>
         </is>
       </c>
       <c r="C153" s="77" t="n">
-        <v>46300</v>
+        <v>46294</v>
       </c>
       <c r="D153" s="79" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="E153" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F153" s="112">
@@ -71914,14 +71914,14 @@
       </c>
       <c r="G153" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
+          <t>Pagamento previsto para 30/09/2026. Recebido em dinheiro em 14/10/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="154" s="157">
       <c r="A154" s="78" t="inlineStr">
         <is>
-          <t>Rafael Landin Ribeiro</t>
+          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
         </is>
       </c>
       <c r="B154" s="78" t="inlineStr">
@@ -71930,7 +71930,7 @@
         </is>
       </c>
       <c r="C154" s="77" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="D154" s="79" t="n">
         <v>140</v>
@@ -71946,30 +71946,30 @@
       </c>
       <c r="G154" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026. Recebido via Pix em 09/10/2026.</t>
+          <t>Troca do dia 30/09/2026. Recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026) — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="155" s="157">
       <c r="A155" s="78" t="inlineStr">
         <is>
-          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
+          <t>Aneilde Rios de Oliveira</t>
         </is>
       </c>
       <c r="B155" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Refil Universal (restante)</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C155" s="77" t="n">
-        <v>46304</v>
+        <v>46296</v>
       </c>
       <c r="D155" s="79" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E155" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F155" s="112">
@@ -71978,30 +71978,30 @@
       </c>
       <c r="G155" s="78" t="inlineStr">
         <is>
-          <t>Venda de R$ 170,00 — R$ 85,00 pagos no débito em 09/10/2026; restante via Pix previsto para 16/10/2026.</t>
+          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
     <row r="156" s="157">
       <c r="A156" s="78" t="inlineStr">
         <is>
-          <t>Tropical Motos LTDA</t>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
         </is>
       </c>
       <c r="B156" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Pro Life + 2x Botão Completo</t>
         </is>
       </c>
       <c r="C156" s="77" t="n">
-        <v>46304</v>
+        <v>46296</v>
       </c>
       <c r="D156" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E156" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F156" s="112">
@@ -72010,30 +72010,30 @@
       </c>
       <c r="G156" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026 — purificador do andar de cima.</t>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="157" s="157">
       <c r="A157" s="78" t="inlineStr">
         <is>
-          <t>Casa do Construtor</t>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
         </is>
       </c>
       <c r="B157" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life + 2x Botão Completo</t>
         </is>
       </c>
       <c r="C157" s="77" t="n">
-        <v>46310</v>
+        <v>46297</v>
       </c>
       <c r="D157" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E157" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F157" s="112">
@@ -72042,26 +72042,26 @@
       </c>
       <c r="G157" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026.</t>
+          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="158" s="157">
       <c r="A158" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B158" s="78" t="inlineStr">
         <is>
-          <t>Refil E3 + Refil Everest</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C158" s="77" t="n">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="D158" s="79" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E158" s="112" t="inlineStr">
         <is>
@@ -72074,14 +72074,14 @@
       </c>
       <c r="G158" s="78" t="inlineStr">
         <is>
-          <t>Compra do dia 15/10/2026 — Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
+          <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
         </is>
       </c>
     </row>
     <row r="159" s="157">
       <c r="A159" s="78" t="inlineStr">
         <is>
-          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
+          <t>Rafael Landin Ribeiro</t>
         </is>
       </c>
       <c r="B159" s="78" t="inlineStr">
@@ -72090,7 +72090,7 @@
         </is>
       </c>
       <c r="C159" s="77" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="D159" s="79" t="n">
         <v>140</v>
@@ -72106,26 +72106,26 @@
       </c>
       <c r="G159" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026. Recebido via Pix em 16/10/2026 — lançado em "Out 2026".</t>
+          <t>Troca do dia 09/10/2026. Recebido via Pix em 09/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="160" s="157">
       <c r="A160" s="78" t="inlineStr">
         <is>
-          <t>Colegio Oasis de Jacobina - Unopar</t>
+          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
         </is>
       </c>
       <c r="B160" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Plissado + 2x Carcaça 9"</t>
+          <t>Refil Pro Life + Refil Universal (restante)</t>
         </is>
       </c>
       <c r="C160" s="77" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="D160" s="79" t="n">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="E160" s="112" t="inlineStr">
         <is>
@@ -72138,26 +72138,26 @@
       </c>
       <c r="G160" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
+          <t>Venda de R$ 170,00 — R$ 85,00 pagos no débito em 09/10/2026; restante via Pix previsto para 16/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="161" s="157">
       <c r="A161" s="78" t="inlineStr">
         <is>
-          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+          <t>Tropical Motos LTDA</t>
         </is>
       </c>
       <c r="B161" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro (restante)</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C161" s="77" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="D161" s="79" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E161" s="112" t="inlineStr">
         <is>
@@ -72170,26 +72170,26 @@
       </c>
       <c r="G161" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00.</t>
+          <t>Troca do dia 09/10/2026 — purificador do andar de cima.</t>
         </is>
       </c>
     </row>
     <row r="162" s="157">
       <c r="A162" s="78" t="inlineStr">
         <is>
-          <t>Contabilidade Abreu</t>
+          <t>Casa do Construtor</t>
         </is>
       </c>
       <c r="B162" s="78" t="inlineStr">
         <is>
-          <t>Termostato</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C162" s="77" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="D162" s="79" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="E162" s="112" t="inlineStr">
         <is>
@@ -72202,52 +72202,207 @@
       </c>
       <c r="G162" s="78" t="inlineStr">
         <is>
+          <t>Troca do dia 15/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" s="157">
+      <c r="A163" s="78" t="inlineStr">
+        <is>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="B163" s="78" t="inlineStr">
+        <is>
+          <t>Refil E3 + Refil Everest</t>
+        </is>
+      </c>
+      <c r="C163" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D163" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E163" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F163" s="112">
+        <f>IF(OR($E163="Recebido",$C163=""),"",MAX(0,TODAY()-$C163))</f>
+        <v/>
+      </c>
+      <c r="G163" s="78" t="inlineStr">
+        <is>
+          <t>Compra do dia 15/10/2026 — Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" s="157">
+      <c r="A164" s="78" t="inlineStr">
+        <is>
+          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
+        </is>
+      </c>
+      <c r="B164" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C164" s="77" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D164" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E164" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="F164" s="112">
+        <f>IF(OR($E164="Recebido",$C164=""),"",MAX(0,TODAY()-$C164))</f>
+        <v/>
+      </c>
+      <c r="G164" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 15/10/2026. Recebido via Pix em 16/10/2026 — lançado em "Out 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" s="157">
+      <c r="A165" s="78" t="inlineStr">
+        <is>
+          <t>Colegio Oasis de Jacobina - Unopar</t>
+        </is>
+      </c>
+      <c r="B165" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado + 2x Carcaça 9"</t>
+        </is>
+      </c>
+      <c r="C165" s="77" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D165" s="79" t="n">
+        <v>400</v>
+      </c>
+      <c r="E165" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F165" s="112">
+        <f>IF(OR($E165="Recebido",$C165=""),"",MAX(0,TODAY()-$C165))</f>
+        <v/>
+      </c>
+      <c r="G165" s="78" t="inlineStr">
+        <is>
+          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" s="157">
+      <c r="A166" s="78" t="inlineStr">
+        <is>
+          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+        </is>
+      </c>
+      <c r="B166" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro (restante)</t>
+        </is>
+      </c>
+      <c r="C166" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D166" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E166" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F166" s="112">
+        <f>IF(OR($E166="Recebido",$C166=""),"",MAX(0,TODAY()-$C166))</f>
+        <v/>
+      </c>
+      <c r="G166" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" s="157">
+      <c r="A167" s="78" t="inlineStr">
+        <is>
+          <t>Contabilidade Abreu</t>
+        </is>
+      </c>
+      <c r="B167" s="78" t="inlineStr">
+        <is>
+          <t>Termostato</t>
+        </is>
+      </c>
+      <c r="C167" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D167" s="79" t="n">
+        <v>170</v>
+      </c>
+      <c r="E167" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F167" s="112">
+        <f>IF(OR($E167="Recebido",$C167=""),"",MAX(0,TODAY()-$C167))</f>
+        <v/>
+      </c>
+      <c r="G167" s="78" t="inlineStr">
+        <is>
           <t>Troca de termostato do dia 16/10/2026.</t>
         </is>
       </c>
     </row>
-    <row r="163" s="157">
-      <c r="A163" s="86" t="inlineStr">
+    <row r="168" s="157">
+      <c r="A168" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D163" s="115">
-        <f>SUMIF(E102:E162,"Pendente",D102:D162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" s="157">
-      <c r="A164" s="202" t="inlineStr">
+      <c r="D168" s="115">
+        <f>SUMIF(E107:E167,"Pendente",D107:D167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" s="157">
+      <c r="A169" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B164" s="159" t="n"/>
-      <c r="C164" s="159" t="n"/>
-      <c r="D164" s="159" t="n"/>
-      <c r="E164" s="159" t="n"/>
-      <c r="F164" s="159" t="n"/>
-      <c r="G164" s="160" t="n"/>
-    </row>
-    <row r="165" s="157">
-      <c r="A165" s="203">
-        <f>IF(ROUND(D163-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D163-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" s="157">
-      <c r="A166" s="203" t="inlineStr">
+      <c r="B169" s="159" t="n"/>
+      <c r="C169" s="159" t="n"/>
+      <c r="D169" s="159" t="n"/>
+      <c r="E169" s="159" t="n"/>
+      <c r="F169" s="159" t="n"/>
+      <c r="G169" s="160" t="n"/>
+    </row>
+    <row r="170" s="157">
+      <c r="A170" s="203">
+        <f>IF(ROUND(D168-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D168-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" s="157">
+      <c r="A171" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="167" s="157"/>
-    <row r="168" s="157"/>
-    <row r="169" s="157"/>
-    <row r="170" s="157"/>
-    <row r="171" s="157"/>
     <row r="172" s="157"/>
     <row r="173" s="157"/>
     <row r="174" s="157"/>
@@ -72281,27 +72436,32 @@
     <row r="202" s="157"/>
     <row r="203" s="157"/>
     <row r="204" s="157"/>
+    <row r="205" s="157"/>
+    <row r="206" s="157"/>
+    <row r="207" s="157"/>
+    <row r="208" s="157"/>
+    <row r="209" s="157"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A169:G169"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A105:G105"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A164:G164"/>
+    <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A170:G170"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E102:E162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E107:E167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -57662,38 +57662,99 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="17" t="n"/>
-      <c r="B149" s="18" t="n"/>
-      <c r="C149" s="18" t="n"/>
-      <c r="D149" s="27" t="n"/>
-      <c r="E149" s="18" t="n"/>
+      <c r="A149" s="17" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>Eliane Lisboa Silva</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D149" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F149" s="19" t="n"/>
       <c r="G149" s="19" t="n"/>
       <c r="H149" s="21" t="n"/>
       <c r="I149" s="18" t="n"/>
-      <c r="J149" s="18" t="n"/>
+      <c r="J149" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0908</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="44" t="n"/>
-      <c r="B150" s="45" t="n"/>
-      <c r="C150" s="45" t="n"/>
-      <c r="D150" s="46" t="n"/>
-      <c r="E150" s="45" t="n"/>
+      <c r="A150" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B150" s="45" t="inlineStr">
+        <is>
+          <t>Studio Malena Lorrane</t>
+        </is>
+      </c>
+      <c r="C150" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D150" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E150" s="45" t="inlineStr">
+        <is>
+          <t>Aguardando Pagamento</t>
+        </is>
+      </c>
       <c r="F150" s="47" t="n"/>
       <c r="G150" s="48" t="n"/>
       <c r="H150" s="49" t="n"/>
-      <c r="I150" s="45" t="n"/>
+      <c r="I150" s="45" t="inlineStr">
+        <is>
+          <t>Venda de R$ 190,00: Refil Everest R$ 130,00 + Pré Filtro R$ 60,00 (o pré-filtro antigo, de 2020, da saída de água foi trocado na hora). R$ 40,00 do refil foram pagos com serviço de sobrancelha feito para a Edilânia; ficou devendo R$ 150,00 (R$ 90,00 do refil + R$ 60,00 do pré-filtro).</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>EMP-0283</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="17" t="n"/>
-      <c r="B151" s="18" t="n"/>
+      <c r="A151" s="17" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>Edivandro De Jesus Bispo</t>
+        </is>
+      </c>
       <c r="C151" s="18" t="n"/>
       <c r="D151" s="27" t="n"/>
       <c r="E151" s="18" t="n"/>
       <c r="F151" s="19" t="n"/>
-      <c r="G151" s="19" t="n"/>
-      <c r="H151" s="21" t="n"/>
-      <c r="I151" s="18" t="n"/>
+      <c r="G151" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="H151" s="21" t="inlineStr">
+        <is>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>Colocação de piso vinílico na loja, na área perto do banheiro. Pix de R$ 200,00 em 21/10/2026 09:56 pelo Banco do Nordeste (ID E07237373202610211255VN1BQCN2DOB).</t>
+        </is>
+      </c>
       <c r="J151" s="18" t="n"/>
     </row>
     <row r="152">
@@ -67367,7 +67428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -72367,52 +72428,182 @@
       </c>
     </row>
     <row r="168" s="157">
-      <c r="A168" s="86" t="inlineStr">
+      <c r="A168" s="78" t="inlineStr">
+        <is>
+          <t>Studio Malena Lorrane</t>
+        </is>
+      </c>
+      <c r="B168" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro (restante)</t>
+        </is>
+      </c>
+      <c r="C168" s="77" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D168" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="E168" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F168" s="112">
+        <f>IF(OR($E168="Recebido",$C168=""),"",MAX(0,TODAY()-$C168))</f>
+        <v/>
+      </c>
+      <c r="G168" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/10/2026. Venda de R$ 190,00; R$ 40,00 pagos com serviço de sobrancelha para a Edilânia. Deve R$ 90,00 do refil + R$ 60,00 do pré-filtro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" s="157">
+      <c r="A169" s="78" t="n"/>
+      <c r="B169" s="78" t="n"/>
+      <c r="C169" s="77" t="n"/>
+      <c r="D169" s="79" t="n"/>
+      <c r="E169" s="112" t="n"/>
+      <c r="F169" s="112">
+        <f>IF(OR($E169="Recebido",$C169=""),"",MAX(0,TODAY()-$C169))</f>
+        <v/>
+      </c>
+      <c r="G169" s="78" t="n"/>
+    </row>
+    <row r="170" s="157">
+      <c r="A170" s="78" t="n"/>
+      <c r="B170" s="78" t="n"/>
+      <c r="C170" s="77" t="n"/>
+      <c r="D170" s="79" t="n"/>
+      <c r="E170" s="112" t="n"/>
+      <c r="F170" s="112">
+        <f>IF(OR($E170="Recebido",$C170=""),"",MAX(0,TODAY()-$C170))</f>
+        <v/>
+      </c>
+      <c r="G170" s="78" t="n"/>
+    </row>
+    <row r="171" s="157">
+      <c r="A171" s="78" t="n"/>
+      <c r="B171" s="78" t="n"/>
+      <c r="C171" s="77" t="n"/>
+      <c r="D171" s="79" t="n"/>
+      <c r="E171" s="112" t="n"/>
+      <c r="F171" s="112">
+        <f>IF(OR($E171="Recebido",$C171=""),"",MAX(0,TODAY()-$C171))</f>
+        <v/>
+      </c>
+      <c r="G171" s="78" t="n"/>
+    </row>
+    <row r="172" s="157">
+      <c r="A172" s="78" t="n"/>
+      <c r="B172" s="78" t="n"/>
+      <c r="C172" s="77" t="n"/>
+      <c r="D172" s="79" t="n"/>
+      <c r="E172" s="112" t="n"/>
+      <c r="F172" s="112">
+        <f>IF(OR($E172="Recebido",$C172=""),"",MAX(0,TODAY()-$C172))</f>
+        <v/>
+      </c>
+      <c r="G172" s="78" t="n"/>
+    </row>
+    <row r="173" s="157">
+      <c r="A173" s="78" t="n"/>
+      <c r="B173" s="78" t="n"/>
+      <c r="C173" s="77" t="n"/>
+      <c r="D173" s="79" t="n"/>
+      <c r="E173" s="112" t="n"/>
+      <c r="F173" s="112">
+        <f>IF(OR($E173="Recebido",$C173=""),"",MAX(0,TODAY()-$C173))</f>
+        <v/>
+      </c>
+      <c r="G173" s="78" t="n"/>
+    </row>
+    <row r="174" s="157">
+      <c r="A174" s="78" t="n"/>
+      <c r="B174" s="78" t="n"/>
+      <c r="C174" s="77" t="n"/>
+      <c r="D174" s="79" t="n"/>
+      <c r="E174" s="112" t="n"/>
+      <c r="F174" s="112">
+        <f>IF(OR($E174="Recebido",$C174=""),"",MAX(0,TODAY()-$C174))</f>
+        <v/>
+      </c>
+      <c r="G174" s="78" t="n"/>
+    </row>
+    <row r="175" s="157">
+      <c r="A175" s="78" t="n"/>
+      <c r="B175" s="78" t="n"/>
+      <c r="C175" s="77" t="n"/>
+      <c r="D175" s="79" t="n"/>
+      <c r="E175" s="112" t="n"/>
+      <c r="F175" s="112">
+        <f>IF(OR($E175="Recebido",$C175=""),"",MAX(0,TODAY()-$C175))</f>
+        <v/>
+      </c>
+      <c r="G175" s="78" t="n"/>
+    </row>
+    <row r="176" s="157">
+      <c r="A176" s="78" t="n"/>
+      <c r="B176" s="78" t="n"/>
+      <c r="C176" s="77" t="n"/>
+      <c r="D176" s="79" t="n"/>
+      <c r="E176" s="112" t="n"/>
+      <c r="F176" s="112">
+        <f>IF(OR($E176="Recebido",$C176=""),"",MAX(0,TODAY()-$C176))</f>
+        <v/>
+      </c>
+      <c r="G176" s="78" t="n"/>
+    </row>
+    <row r="177" s="157">
+      <c r="A177" s="78" t="n"/>
+      <c r="B177" s="78" t="n"/>
+      <c r="C177" s="77" t="n"/>
+      <c r="D177" s="79" t="n"/>
+      <c r="E177" s="112" t="n"/>
+      <c r="F177" s="112">
+        <f>IF(OR($E177="Recebido",$C177=""),"",MAX(0,TODAY()-$C177))</f>
+        <v/>
+      </c>
+      <c r="G177" s="78" t="n"/>
+    </row>
+    <row r="178" s="157">
+      <c r="A178" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D168" s="115">
-        <f>SUMIF(E107:E167,"Pendente",D107:D167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" s="157">
-      <c r="A169" s="202" t="inlineStr">
+      <c r="D178" s="115">
+        <f>SUMIF(E107:E177,"Pendente",D107:D177)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" s="157">
+      <c r="A179" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B169" s="159" t="n"/>
-      <c r="C169" s="159" t="n"/>
-      <c r="D169" s="159" t="n"/>
-      <c r="E169" s="159" t="n"/>
-      <c r="F169" s="159" t="n"/>
-      <c r="G169" s="160" t="n"/>
-    </row>
-    <row r="170" s="157">
-      <c r="A170" s="203">
-        <f>IF(ROUND(D168-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D168-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" s="157">
-      <c r="A171" s="203" t="inlineStr">
+      <c r="B179" s="159" t="n"/>
+      <c r="C179" s="159" t="n"/>
+      <c r="D179" s="159" t="n"/>
+      <c r="E179" s="159" t="n"/>
+      <c r="F179" s="159" t="n"/>
+      <c r="G179" s="160" t="n"/>
+    </row>
+    <row r="180" s="157">
+      <c r="A180" s="203">
+        <f>IF(ROUND(D178-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D178-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" s="157">
+      <c r="A181" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="172" s="157"/>
-    <row r="173" s="157"/>
-    <row r="174" s="157"/>
-    <row r="175" s="157"/>
-    <row r="176" s="157"/>
-    <row r="177" s="157"/>
-    <row r="178" s="157"/>
-    <row r="179" s="157"/>
-    <row r="180" s="157"/>
-    <row r="181" s="157"/>
     <row r="182" s="157"/>
     <row r="183" s="157"/>
     <row r="184" s="157"/>
@@ -72441,10 +72632,19 @@
     <row r="207" s="157"/>
     <row r="208" s="157"/>
     <row r="209" s="157"/>
+    <row r="210" s="157"/>
+    <row r="211" s="157"/>
+    <row r="212" s="157"/>
+    <row r="213" s="157"/>
+    <row r="214" s="157"/>
+    <row r="215" s="157"/>
+    <row r="216" s="157"/>
+    <row r="217" s="157"/>
+    <row r="218" s="157"/>
+    <row r="219" s="157"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A169:G169"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
@@ -72454,14 +72654,15 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="A104:G104"/>
-    <mergeCell ref="A170:G170"/>
+    <mergeCell ref="A179:G179"/>
+    <mergeCell ref="A180:G180"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E11:E99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E107:E167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E107:E177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -57758,84 +57758,203 @@
       <c r="J151" s="18" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="44" t="n"/>
-      <c r="B152" s="45" t="n"/>
-      <c r="C152" s="45" t="n"/>
-      <c r="D152" s="46" t="n"/>
-      <c r="E152" s="45" t="n"/>
-      <c r="F152" s="47" t="n"/>
+      <c r="A152" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B152" s="45" t="inlineStr">
+        <is>
+          <t>Miralva Lopes da Silva</t>
+        </is>
+      </c>
+      <c r="C152" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D152" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E152" s="45" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F152" s="47" t="n">
+        <v>2.03</v>
+      </c>
       <c r="G152" s="48" t="n"/>
       <c r="H152" s="49" t="n"/>
       <c r="I152" s="45" t="n"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>CLI-0390</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="17" t="n"/>
-      <c r="B153" s="18" t="n"/>
+      <c r="A153" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>Cezar Silva Atacado e Varejo (Iene Quedila Nunes Dourado)</t>
+        </is>
+      </c>
       <c r="C153" s="18" t="n"/>
       <c r="D153" s="27" t="n"/>
       <c r="E153" s="18" t="n"/>
       <c r="F153" s="19" t="n"/>
-      <c r="G153" s="19" t="n"/>
-      <c r="H153" s="21" t="n"/>
-      <c r="I153" s="18" t="n"/>
+      <c r="G153" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="H153" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 16/10/2026.</t>
+        </is>
+      </c>
       <c r="J153" s="18" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="44" t="n"/>
-      <c r="B154" s="45" t="n"/>
+      <c r="A154" s="44" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B154" s="45" t="inlineStr">
+        <is>
+          <t>Thiago de Jesus Nascimento</t>
+        </is>
+      </c>
       <c r="C154" s="45" t="n"/>
       <c r="D154" s="46" t="n"/>
       <c r="E154" s="45" t="n"/>
       <c r="F154" s="47" t="n"/>
-      <c r="G154" s="48" t="n"/>
-      <c r="H154" s="49" t="n"/>
-      <c r="I154" s="45" t="n"/>
+      <c r="G154" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="H154" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I154" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 19/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="17" t="n"/>
-      <c r="B155" s="18" t="n"/>
+      <c r="A155" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>Japedido Software</t>
+        </is>
+      </c>
       <c r="C155" s="18" t="n"/>
       <c r="D155" s="27" t="n"/>
       <c r="E155" s="18" t="n"/>
       <c r="F155" s="19" t="n"/>
-      <c r="G155" s="19" t="n"/>
-      <c r="H155" s="21" t="n"/>
-      <c r="I155" s="18" t="n"/>
+      <c r="G155" s="19" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="H155" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 20/10/2026.</t>
+        </is>
+      </c>
       <c r="J155" s="18" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="44" t="n"/>
-      <c r="B156" s="45" t="n"/>
+      <c r="A156" s="44" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B156" s="45" t="inlineStr">
+        <is>
+          <t>Maria Eva dos Santos</t>
+        </is>
+      </c>
       <c r="C156" s="45" t="n"/>
       <c r="D156" s="46" t="n"/>
       <c r="E156" s="45" t="n"/>
       <c r="F156" s="47" t="n"/>
-      <c r="G156" s="48" t="n"/>
-      <c r="H156" s="49" t="n"/>
-      <c r="I156" s="45" t="n"/>
+      <c r="G156" s="48" t="n">
+        <v>350</v>
+      </c>
+      <c r="H156" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I156" s="45" t="inlineStr">
+        <is>
+          <t>Extrato Stone — saída de 20/10/2026. Diarista — não é o mesmo pagamento da "Diarista Eva" de R$ 400,00 de 17/10.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="17" t="n"/>
-      <c r="B157" s="18" t="n"/>
+      <c r="A157" s="17" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>Uellinton Silva de Jesus</t>
+        </is>
+      </c>
       <c r="C157" s="18" t="n"/>
       <c r="D157" s="27" t="n"/>
       <c r="E157" s="18" t="n"/>
       <c r="F157" s="19" t="n"/>
-      <c r="G157" s="19" t="n"/>
-      <c r="H157" s="21" t="n"/>
-      <c r="I157" s="18" t="n"/>
+      <c r="G157" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="H157" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 20/10/2026 18:58 (CNPJ 18.097.008/0001-83). Lançado como gasto pessoal — confirmar com a Edilânia.</t>
+        </is>
+      </c>
       <c r="J157" s="18" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="44" t="n"/>
-      <c r="B158" s="45" t="n"/>
+      <c r="A158" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B158" s="45" t="inlineStr">
+        <is>
+          <t>Fatura Claro TV (Embratel)</t>
+        </is>
+      </c>
       <c r="C158" s="45" t="n"/>
       <c r="D158" s="46" t="n"/>
       <c r="E158" s="45" t="n"/>
       <c r="F158" s="47" t="n"/>
-      <c r="G158" s="48" t="n"/>
-      <c r="H158" s="49" t="n"/>
-      <c r="I158" s="45" t="n"/>
+      <c r="G158" s="48" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="H158" s="49" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I158" s="45" t="inlineStr">
+        <is>
+          <t>TV de casa — despesa pessoal. Pix de R$ 249,70 em 21/10/2026 14:26 pelo Banco do Nordeste para Embratel (ID E07237373202610211726RDWOGZX74RT).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="17" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56926,7 +56926,7 @@
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
-          <t>Pedido da Edilânia em 17/10/2026 — despesa pessoal.</t>
+          <t>Pedido da Edilânia em 17/10/2026 — despesa pessoal. Pago em dinheiro (confirmado em 21/10/2026: é diferente do Pix de R$ 350,00 de 20/10).</t>
         </is>
       </c>
       <c r="J125" s="18" t="n"/>
@@ -57897,7 +57897,7 @@
       </c>
       <c r="I156" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — saída de 20/10/2026. Diarista — não é o mesmo pagamento da "Diarista Eva" de R$ 400,00 de 17/10.</t>
+          <t>Extrato Stone — Pix de 20/10/2026. Diarista — pagamento diferente do de 17/10 (R$ 400,00 em dinheiro); confirmado pela Edilânia em 21/10/2026.</t>
         </is>
       </c>
     </row>
@@ -57907,7 +57907,7 @@
       </c>
       <c r="B157" s="18" t="inlineStr">
         <is>
-          <t>Uellinton Silva de Jesus</t>
+          <t>Mensalidade Academia (Uellinton Silva de Jesus)</t>
         </is>
       </c>
       <c r="C157" s="18" t="n"/>
@@ -57924,7 +57924,7 @@
       </c>
       <c r="I157" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 20/10/2026 18:58 (CNPJ 18.097.008/0001-83). Lançado como gasto pessoal — confirmar com a Edilânia.</t>
+          <t>Extrato Stone — Pix de 20/10/2026 18:58 (CNPJ 18.097.008/0001-83). Mensalidade da academia — despesa pessoal (confirmado pela Edilânia em 21/10/2026).</t>
         </is>
       </c>
       <c r="J157" s="18" t="n"/>
@@ -57957,38 +57957,94 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="17" t="n"/>
-      <c r="B159" s="18" t="n"/>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="27" t="n"/>
-      <c r="E159" s="18" t="n"/>
+      <c r="A159" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>Marmoraria Pedra Bella LTDA</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D159" s="27" t="n">
+        <v>135</v>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F159" s="19" t="n"/>
       <c r="G159" s="19" t="n"/>
       <c r="H159" s="21" t="n"/>
-      <c r="I159" s="18" t="n"/>
-      <c r="J159" s="18" t="n"/>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>Cliente comprou o refil e fez a troca por conta própria em 19/10/2026 (sem serviço da loja).</t>
+        </is>
+      </c>
+      <c r="J159" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0215</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="44" t="n"/>
-      <c r="B160" s="45" t="n"/>
+      <c r="A160" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B160" s="45" t="inlineStr">
+        <is>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
       <c r="C160" s="45" t="n"/>
       <c r="D160" s="46" t="n"/>
       <c r="E160" s="45" t="n"/>
       <c r="F160" s="47" t="n"/>
-      <c r="G160" s="48" t="n"/>
-      <c r="H160" s="49" t="n"/>
-      <c r="I160" s="45" t="n"/>
+      <c r="G160" s="48" t="n">
+        <v>537.9299999999999</v>
+      </c>
+      <c r="H160" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I160" s="45" t="inlineStr">
+        <is>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Boleto doc. 133138/4 (emissão 12/08/2026) · parcela 4/4 (última) — venc. 21/10/2026. Pago em 21/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="17" t="n"/>
-      <c r="B161" s="18" t="n"/>
+      <c r="A161" s="17" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
       <c r="C161" s="18" t="n"/>
       <c r="D161" s="27" t="n"/>
       <c r="E161" s="18" t="n"/>
       <c r="F161" s="19" t="n"/>
-      <c r="G161" s="19" t="n"/>
-      <c r="H161" s="21" t="n"/>
-      <c r="I161" s="18" t="n"/>
+      <c r="G161" s="19" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="H161" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I161" s="18" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Boleto doc. 386838 (emissão 23/09/2026) · parcela 1/5 — venc. 23/10/2026. Pago antecipado em 21/10/2026.</t>
+        </is>
+      </c>
       <c r="J161" s="18" t="n"/>
     </row>
     <row r="162">
@@ -69209,7 +69265,7 @@
       </c>
       <c r="E59" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F59" s="112">
@@ -69218,7 +69274,7 @@
       </c>
       <c r="G59" s="78" t="inlineStr">
         <is>
-          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397.</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397. Pago em 21/10/2026 — lançado em "Out 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -69721,7 +69777,7 @@
       </c>
       <c r="E75" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F75" s="113">
@@ -69730,7 +69786,7 @@
       </c>
       <c r="G75" s="82" t="inlineStr">
         <is>
-          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210.</t>
+          <t>Comprado: Purificador Everest Fit Prata + Purificador Everest Slim Preto + Purificador Everest Star Preto + Purificador Everest Plus Preto (NF-e 386838 de 23/09/2026, nota de R$ 3.065,60 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/36910774. Linha digitável 34191.12366 91077.460300 52238.850003 1 16080000061312. Boleto recebido por e-mail em 23/09/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 386838". Após o vencimento: multa de 2% + juros de R$ 0,20 ao dia. | Conferido com o XML da NF-e nº 386838 (emissão 23/09/2026): EVEREST REFRIGERACAO INDUSTRIA E COMERCIO LTDA., CNPJ 33.079.641/0001-32, RUA CARDOSO QUINTAO, 914, TOMAS COELHO, RIO DE JANEIRO/RJ. Valor total da nota R$ 3.065,60 em 5 parcelas. Frete FOB (frete por conta da loja), transportadora PATRUS TRANSPORTES URGENTES LTDA. Chave da NF-e 33260933079641000132550020003868381733266210. Pago em 21/10/2026 — lançado em "Out 2026" como "Everest Refrigeração".</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -58048,11 +58048,27 @@
       <c r="J161" s="18" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="44" t="n"/>
-      <c r="B162" s="45" t="n"/>
-      <c r="C162" s="45" t="n"/>
-      <c r="D162" s="46" t="n"/>
-      <c r="E162" s="45" t="n"/>
+      <c r="A162" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B162" s="45" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C162" s="45" t="inlineStr">
+        <is>
+          <t>Conexão Reta Rosca</t>
+        </is>
+      </c>
+      <c r="D162" s="46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E162" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F162" s="47" t="n"/>
       <c r="G162" s="48" t="n"/>
       <c r="H162" s="49" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -40567,20 +40567,20 @@
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
-          <t>Supermercado Brasil</t>
+          <t>Marcio Itamar</t>
         </is>
       </c>
       <c r="C26" s="45" t="inlineStr">
         <is>
-          <t>2x Refil Pro Life</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D26" s="46" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E26" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F26" s="47" t="n"/>
@@ -40589,7 +40589,7 @@
       <c r="I26" s="45" t="n"/>
       <c r="J26" s="45" t="inlineStr">
         <is>
-          <t>EMP-0261</t>
+          <t>CLI-0501</t>
         </is>
       </c>
     </row>
@@ -40599,20 +40599,20 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Marcio Itamar</t>
+          <t>Arena Jacobina Society</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Carbon Tech 9"</t>
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F27" s="19" t="n"/>
@@ -40621,7 +40621,7 @@
       <c r="I27" s="18" t="n"/>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>CLI-0501</t>
+          <t>EMP-0004</t>
         </is>
       </c>
     </row>
@@ -40631,20 +40631,20 @@
       </c>
       <c r="B28" s="45" t="inlineStr">
         <is>
-          <t>Arena Jacobina Society</t>
+          <t>Verdes Mares Tintas</t>
         </is>
       </c>
       <c r="C28" s="45" t="inlineStr">
         <is>
-          <t>Refil Carbon Tech 9"</t>
+          <t>Botão do Purificador + Limpeza de Refil</t>
         </is>
       </c>
       <c r="D28" s="46" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E28" s="45" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F28" s="47" t="n"/>
@@ -40653,7 +40653,7 @@
       <c r="I28" s="45" t="n"/>
       <c r="J28" s="45" t="inlineStr">
         <is>
-          <t>EMP-0004</t>
+          <t>EMP-0303</t>
         </is>
       </c>
     </row>
@@ -40663,31 +40663,27 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Verdes Mares Tintas</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Botão do Purificador + Limpeza de Refil</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="18" t="n"/>
       <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0303</t>
-        </is>
-      </c>
+      <c r="G29" s="19" t="n">
+        <v>1674.12</v>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="44" t="n">
@@ -40695,7 +40691,7 @@
       </c>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
+          <t>Eversoft</t>
         </is>
       </c>
       <c r="C30" s="45" t="n"/>
@@ -40703,7 +40699,7 @@
       <c r="E30" s="45" t="n"/>
       <c r="F30" s="47" t="n"/>
       <c r="G30" s="48" t="n">
-        <v>1674.12</v>
+        <v>980.83</v>
       </c>
       <c r="H30" s="49" t="inlineStr">
         <is>
@@ -40712,7 +40708,7 @@
       </c>
       <c r="I30" s="45" t="inlineStr">
         <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
         </is>
       </c>
     </row>
@@ -40722,7 +40718,7 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Eversoft</t>
+          <t>Tarifa Pix</t>
         </is>
       </c>
       <c r="C31" s="18" t="n"/>
@@ -40730,18 +40726,14 @@
       <c r="E31" s="18" t="n"/>
       <c r="F31" s="19" t="n"/>
       <c r="G31" s="19" t="n">
-        <v>980.83</v>
+        <v>6.99</v>
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)" · Compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
-        </is>
-      </c>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="44" t="n">
@@ -40749,7 +40741,7 @@
       </c>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>Tarifa Pix</t>
+          <t>Tarifa Pacote de Tarifas</t>
         </is>
       </c>
       <c r="C32" s="45" t="n"/>
@@ -40757,7 +40749,7 @@
       <c r="E32" s="45" t="n"/>
       <c r="F32" s="47" t="n"/>
       <c r="G32" s="48" t="n">
-        <v>6.99</v>
+        <v>52.5</v>
       </c>
       <c r="H32" s="49" t="inlineStr">
         <is>
@@ -40772,7 +40764,7 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Tarifa Pacote de Tarifas</t>
+          <t>Correios</t>
         </is>
       </c>
       <c r="C33" s="18" t="n"/>
@@ -40780,37 +40772,46 @@
       <c r="E33" s="18" t="n"/>
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias e Cartão</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="44" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B34" s="45" t="inlineStr">
         <is>
-          <t>Correios</t>
-        </is>
-      </c>
-      <c r="C34" s="45" t="n"/>
-      <c r="D34" s="46" t="n"/>
-      <c r="E34" s="45" t="n"/>
+          <t>Silvania Mota</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E34" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F34" s="47" t="n"/>
-      <c r="G34" s="48" t="n">
-        <v>52</v>
-      </c>
-      <c r="H34" s="49" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
+      <c r="G34" s="48" t="n"/>
+      <c r="H34" s="49" t="n"/>
       <c r="I34" s="45" t="n"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CLI-0259</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
@@ -40818,16 +40819,16 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Silvania Mota</t>
+          <t>Ariosvaldo Mendes</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Reinstalação de Purificador + Registro + Refil Everest</t>
         </is>
       </c>
       <c r="D35" s="27" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -40838,11 +40839,7 @@
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="21" t="n"/>
       <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0259</t>
-        </is>
-      </c>
+      <c r="J35" s="18" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="44" t="n">
@@ -40850,25 +40847,21 @@
       </c>
       <c r="B36" s="45" t="inlineStr">
         <is>
-          <t>Ariosvaldo Mendes</t>
-        </is>
-      </c>
-      <c r="C36" s="45" t="inlineStr">
-        <is>
-          <t>Reinstalação de Purificador + Registro + Refil Everest</t>
-        </is>
-      </c>
-      <c r="D36" s="46" t="n">
-        <v>200</v>
-      </c>
-      <c r="E36" s="45" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Correios</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="46" t="n"/>
+      <c r="E36" s="45" t="n"/>
       <c r="F36" s="47" t="n"/>
-      <c r="G36" s="48" t="n"/>
-      <c r="H36" s="49" t="n"/>
+      <c r="G36" s="48" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="H36" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
       <c r="I36" s="45" t="n"/>
     </row>
     <row r="37">
@@ -40877,7 +40870,7 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Correios</t>
+          <t>Comissão Wiliam</t>
         </is>
       </c>
       <c r="C37" s="18" t="n"/>
@@ -40885,36 +40878,42 @@
       <c r="E37" s="18" t="n"/>
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n">
-        <v>167.8</v>
+        <v>150</v>
       </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
+          <t>Salários, Comissões e Encargos</t>
         </is>
       </c>
       <c r="I37" s="18" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="44" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B38" s="45" t="inlineStr">
         <is>
-          <t>Comissão Wiliam</t>
-        </is>
-      </c>
-      <c r="C38" s="45" t="n"/>
-      <c r="D38" s="46" t="n"/>
-      <c r="E38" s="45" t="n"/>
-      <c r="F38" s="47" t="n"/>
-      <c r="G38" s="48" t="n">
-        <v>150</v>
-      </c>
-      <c r="H38" s="49" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="n">
+        <v>130</v>
+      </c>
+      <c r="E38" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F38" s="47" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="G38" s="48" t="n"/>
+      <c r="H38" s="49" t="n"/>
       <c r="I38" s="45" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="157">
@@ -40923,102 +40922,109 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D39" s="27" t="n">
-        <v>130</v>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="21" t="n"/>
+          <t>Comissão Wiliam</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
       <c r="I39" s="18" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="44" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B40" s="45" t="inlineStr">
         <is>
-          <t>Comissão Wiliam</t>
-        </is>
-      </c>
-      <c r="C40" s="45" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="45" t="n"/>
-      <c r="F40" s="47" t="n"/>
-      <c r="G40" s="48" t="n">
-        <v>210</v>
-      </c>
-      <c r="H40" s="49" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
+          <t>Andrea Lopes dos Santos</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Mangueira + Registro</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="n">
+        <v>180</v>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F40" s="47" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G40" s="48" t="n"/>
+      <c r="H40" s="49" t="n"/>
       <c r="I40" s="45" t="n"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CLI-0433</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Andrea Lopes dos Santos</t>
+          <t>Marsilia Marmores e Granitos Erelli</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Mangueira + Registro</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>2.61</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="n"/>
       <c r="G41" s="19" t="n"/>
       <c r="H41" s="21" t="n"/>
-      <c r="I41" s="18" t="n"/>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 10/08/2026 — pagamento recebido em 17/08/2026</t>
+        </is>
+      </c>
       <c r="J41" s="18" t="inlineStr">
         <is>
-          <t>CLI-0433</t>
+          <t>EMP-0216</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="157">
       <c r="A42" s="44" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B42" s="45" t="inlineStr">
         <is>
-          <t>Marsilia Marmores e Granitos Erelli</t>
+          <t>Clinica da Mulher - MR Valois Serviços</t>
         </is>
       </c>
       <c r="C42" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>3x Refil Everest</t>
         </is>
       </c>
       <c r="D42" s="46" t="n">
-        <v>140</v>
+        <v>420</v>
       </c>
       <c r="E42" s="45" t="inlineStr">
         <is>
@@ -41030,50 +41036,38 @@
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>Venda de 10/08/2026 — pagamento recebido em 17/08/2026</t>
+          <t>Venda de 10/08/2026 — pagamento recebido em 20/08/2026</t>
         </is>
       </c>
       <c r="J42" s="45" t="inlineStr">
         <is>
-          <t>EMP-0216</t>
+          <t>EMP-0073</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Clinica da Mulher - MR Valois Serviços</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>3x Refil Everest</t>
-        </is>
-      </c>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n"/>
       <c r="D43" s="27" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F43" s="19" t="n"/>
       <c r="G43" s="19" t="n"/>
       <c r="H43" s="21" t="n"/>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>Venda de 10/08/2026 — pagamento recebido em 20/08/2026</t>
-        </is>
-      </c>
-      <c r="J43" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0073</t>
-        </is>
-      </c>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="44" t="n">
@@ -41081,19 +41075,25 @@
       </c>
       <c r="B44" s="45" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
-        </is>
-      </c>
-      <c r="C44" s="45" t="n"/>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
       <c r="D44" s="46" t="n">
-        <v>900</v>
+        <v>115</v>
       </c>
       <c r="E44" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F44" s="47" t="n"/>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>1.67</v>
+      </c>
       <c r="G44" s="48" t="n"/>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="45" t="n"/>
@@ -41104,28 +41104,35 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
+          <t>Audioclin Clinca Médica LTDA - Tarcisio Nascimento</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>2x Refil Everest + Refil Pro Life</t>
         </is>
       </c>
       <c r="D45" s="27" t="n">
-        <v>115</v>
+        <v>399</v>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="F45" s="19" t="n">
-        <v>1.67</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="n"/>
       <c r="G45" s="19" t="n"/>
       <c r="H45" s="21" t="n"/>
-      <c r="I45" s="18" t="n"/>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>Pago via Pix em 11/08/2026 (venda de 10/08)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>EMP-0138</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="44" t="n">
@@ -41133,35 +41140,27 @@
       </c>
       <c r="B46" s="45" t="inlineStr">
         <is>
-          <t>Audioclin Clinca Médica LTDA - Tarcisio Nascimento</t>
-        </is>
-      </c>
-      <c r="C46" s="45" t="inlineStr">
-        <is>
-          <t>2x Refil Everest + Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="D46" s="46" t="n">
-        <v>399</v>
-      </c>
-      <c r="E46" s="45" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Everest Refrigeração</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="n"/>
+      <c r="D46" s="46" t="n"/>
+      <c r="E46" s="45" t="n"/>
       <c r="F46" s="47" t="n"/>
-      <c r="G46" s="48" t="n"/>
-      <c r="H46" s="49" t="n"/>
+      <c r="G46" s="48" t="n">
+        <v>725.5</v>
+      </c>
+      <c r="H46" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
       <c r="I46" s="45" t="inlineStr">
         <is>
-          <t>Pago via Pix em 11/08/2026 (venda de 10/08)</t>
-        </is>
-      </c>
-      <c r="J46" s="45" t="inlineStr">
-        <is>
-          <t>EMP-0138</t>
-        </is>
-      </c>
+          <t>NF 372597 de 11/03/2026 · parcela 5/5 (venc. 08/08/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto</t>
+        </is>
+      </c>
+      <c r="J46" s="45" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -41169,7 +41168,7 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Everest Refrigeração</t>
+          <t>Eversoft</t>
         </is>
       </c>
       <c r="C47" s="18" t="n"/>
@@ -41177,7 +41176,7 @@
       <c r="E47" s="18" t="n"/>
       <c r="F47" s="19" t="n"/>
       <c r="G47" s="19" t="n">
-        <v>725.5</v>
+        <v>878.92</v>
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
@@ -41186,70 +41185,77 @@
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>NF 372597 de 11/03/2026 · parcela 5/5 (venc. 08/08/2026) · compra total R$ 3.627,42: 2x Purificador Everest Plus Branco + Purificador Everest Fit Preto + Purificador Everest Slim Preto + Purificador Everest Star Preto</t>
+          <t>NF 73636 de 10/06/2026 · parcela 2/5 (venc. 09/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="157">
       <c r="A48" s="44" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B48" s="45" t="inlineStr">
         <is>
-          <t>Eversoft</t>
-        </is>
-      </c>
-      <c r="C48" s="45" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="45" t="n"/>
+          <t>Clinica da Mulher - MR Valois Serviços</t>
+        </is>
+      </c>
+      <c r="C48" s="45" t="inlineStr">
+        <is>
+          <t>Refil Plissado + Carcaça 9" 3/4</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="n">
+        <v>180</v>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F48" s="47" t="n"/>
-      <c r="G48" s="48" t="n">
-        <v>878.92</v>
-      </c>
-      <c r="H48" s="49" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
+      <c r="G48" s="48" t="n"/>
+      <c r="H48" s="49" t="n"/>
       <c r="I48" s="45" t="inlineStr">
         <is>
-          <t>NF 73636 de 10/06/2026 · parcela 2/5 (venc. 09/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
+          <t>Venda de 11/08/2026 — pagamento recebido em 20/08/2026</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>EMP-0073</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>Clinica da Mulher - MR Valois Serviços</t>
+          <t>Maria das Dores e Reje Celia</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Refil Plissado + Carcaça 9" 3/4</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="D49" s="27" t="n">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F49" s="19" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>19.57</v>
+      </c>
       <c r="G49" s="19" t="n"/>
       <c r="H49" s="21" t="n"/>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>Venda de 11/08/2026 — pagamento recebido em 20/08/2026</t>
-        </is>
-      </c>
+      <c r="I49" s="18" t="n"/>
       <c r="J49" s="18" t="inlineStr">
         <is>
-          <t>EMP-0073</t>
+          <t>CLI-0222</t>
         </is>
       </c>
     </row>
@@ -41259,31 +41265,29 @@
       </c>
       <c r="B50" s="45" t="inlineStr">
         <is>
-          <t>Maria das Dores e Reje Celia</t>
+          <t>Nlx Comercio e Serviços Subway - Alexandre Neder</t>
         </is>
       </c>
       <c r="C50" s="45" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D50" s="46" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E50" s="45" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F50" s="47" t="n">
-        <v>19.57</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="n"/>
       <c r="G50" s="48" t="n"/>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="45" t="n"/>
       <c r="J50" s="45" t="inlineStr">
         <is>
-          <t>CLI-0222</t>
+          <t>EMP-0231</t>
         </is>
       </c>
     </row>
@@ -41293,160 +41297,153 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>Nlx Comercio e Serviços Subway - Alexandre Neder</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D51" s="27" t="n">
-        <v>140</v>
-      </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Bucha Redução 3/4 x 1/2 (2 unidades)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="18" t="n"/>
       <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="21" t="n"/>
+      <c r="G51" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
       <c r="I51" s="18" t="n"/>
-      <c r="J51" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0231</t>
-        </is>
-      </c>
+      <c r="J51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="44" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="B52" s="45" t="inlineStr">
         <is>
-          <t>Bucha Redução 3/4 x 1/2 (2 unidades)</t>
-        </is>
-      </c>
-      <c r="C52" s="45" t="n"/>
-      <c r="D52" s="46" t="n"/>
-      <c r="E52" s="45" t="n"/>
+          <t>Tropical Motos LTDA</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="n">
+        <v>820</v>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F52" s="47" t="n"/>
-      <c r="G52" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="49" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I52" s="45" t="n"/>
+      <c r="G52" s="48" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="45" t="inlineStr">
+        <is>
+          <t>Venda de 11/08/2026 — pagamento recebido em 25/08/2026 via TED. NF conferida: 3x Refil Original Everest (R$420) + Refil Pro Life Especial OC (R$140) + 3x Pré Filtro (R$180) + Válvula Reguladora de Pressão Soft (R$80) = R$820, faltava a válvula no lançamento original</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>EMP-0296</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="157">
       <c r="A53" s="17" t="n">
-        <v>46259</v>
+        <v>46245</v>
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>Tropical Motos LTDA</t>
+          <t>Ivanir Carneiro de Oliveira</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
+          <t>Refil Pro Life + Mangueira</t>
         </is>
       </c>
       <c r="D53" s="27" t="n">
-        <v>820</v>
+        <v>150</v>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>10.48</v>
+      </c>
       <c r="G53" s="19" t="n"/>
       <c r="H53" s="21" t="n"/>
-      <c r="I53" s="18" t="inlineStr">
-        <is>
-          <t>Venda de 11/08/2026 — pagamento recebido em 25/08/2026 via TED. NF conferida: 3x Refil Original Everest (R$420) + Refil Pro Life Especial OC (R$140) + 3x Pré Filtro (R$180) + Válvula Reguladora de Pressão Soft (R$80) = R$820, faltava a válvula no lançamento original</t>
-        </is>
-      </c>
+      <c r="I53" s="18" t="n"/>
       <c r="J53" s="18" t="inlineStr">
         <is>
-          <t>EMP-0296</t>
+          <t>CLI-0454</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="44" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B54" s="45" t="inlineStr">
         <is>
-          <t>Ivanir Carneiro de Oliveira</t>
+          <t>Condominio Ilha do Ouro</t>
         </is>
       </c>
       <c r="C54" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Mangueira</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D54" s="46" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E54" s="45" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F54" s="47" t="n">
-        <v>10.48</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F54" s="47" t="n"/>
       <c r="G54" s="48" t="n"/>
       <c r="H54" s="49" t="n"/>
-      <c r="I54" s="45" t="n"/>
+      <c r="I54" s="45" t="inlineStr">
+        <is>
+          <t>Venda de 11/08/2026 — pagamento recebido em 19/08/2026</t>
+        </is>
+      </c>
       <c r="J54" s="45" t="inlineStr">
         <is>
-          <t>CLI-0454</t>
+          <t>EMP-0085</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>Condominio Ilha do Ouro</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D55" s="27" t="n">
-        <v>140</v>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Bucha Redução 3/4 x 1/2 (2 unidades)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="27" t="n"/>
+      <c r="E55" s="18" t="n"/>
       <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>Venda de 11/08/2026 — pagamento recebido em 19/08/2026</t>
-        </is>
-      </c>
-      <c r="J55" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0085</t>
-        </is>
-      </c>
+      <c r="G55" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="21" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="44" t="n">
@@ -41454,7 +41451,7 @@
       </c>
       <c r="B56" s="45" t="inlineStr">
         <is>
-          <t>Bucha Redução 3/4 x 1/2 (2 unidades)</t>
+          <t>Crédito Celular da Loja</t>
         </is>
       </c>
       <c r="C56" s="45" t="n"/>
@@ -41462,11 +41459,11 @@
       <c r="E56" s="45" t="n"/>
       <c r="F56" s="47" t="n"/>
       <c r="G56" s="48" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H56" s="49" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="I56" s="45" t="n"/>
@@ -41477,7 +41474,7 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>Crédito Celular da Loja</t>
+          <t>Crédito Celular de Edilânia</t>
         </is>
       </c>
       <c r="C57" s="18" t="n"/>
@@ -41489,7 +41486,7 @@
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I57" s="18" t="n"/>
@@ -41500,21 +41497,21 @@
       </c>
       <c r="B58" s="45" t="inlineStr">
         <is>
-          <t>Crédito Celular de Edilânia</t>
+          <t>Acerto de Armando</t>
         </is>
       </c>
       <c r="C58" s="45" t="n"/>
-      <c r="D58" s="46" t="n"/>
-      <c r="E58" s="45" t="n"/>
+      <c r="D58" s="46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F58" s="47" t="n"/>
-      <c r="G58" s="48" t="n">
-        <v>25</v>
-      </c>
-      <c r="H58" s="49" t="inlineStr">
-        <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
+      <c r="G58" s="48" t="n"/>
+      <c r="H58" s="49" t="n"/>
       <c r="I58" s="45" t="n"/>
     </row>
     <row r="59">
@@ -41523,21 +41520,21 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="C59" s="18" t="n"/>
-      <c r="D59" s="27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="18" t="n"/>
       <c r="F59" s="19" t="n"/>
-      <c r="G59" s="19" t="n"/>
-      <c r="H59" s="21" t="n"/>
+      <c r="G59" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="I59" s="18" t="n"/>
     </row>
     <row r="60">
@@ -41546,7 +41543,7 @@
       </c>
       <c r="B60" s="45" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Filtros Planeta Água</t>
         </is>
       </c>
       <c r="C60" s="45" t="n"/>
@@ -41554,58 +41551,67 @@
       <c r="E60" s="45" t="n"/>
       <c r="F60" s="47" t="n"/>
       <c r="G60" s="48" t="n">
-        <v>1000</v>
+        <v>504.34</v>
       </c>
       <c r="H60" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I60" s="45" t="n"/>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I60" s="45" t="inlineStr">
+        <is>
+          <t>NF 131442 de 17/06/2026 · parcela 3/4 (venc. 12/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="18" t="n"/>
+          <t>Angelo Marcio Bispo</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n">
-        <v>504.34</v>
-      </c>
-      <c r="H61" s="21" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>NF 131442 de 17/06/2026 · parcela 3/4 (venc. 12/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>CLI-0023</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="44" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B62" s="45" t="inlineStr">
         <is>
-          <t>Angelo Marcio Bispo</t>
+          <t>Cliente Consumidor Final</t>
         </is>
       </c>
       <c r="C62" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="D62" s="46" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E62" s="45" t="inlineStr">
         <is>
@@ -41616,11 +41622,7 @@
       <c r="G62" s="48" t="n"/>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="45" t="n"/>
-      <c r="J62" s="45" t="inlineStr">
-        <is>
-          <t>CLI-0023</t>
-        </is>
-      </c>
+      <c r="J62" s="45" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="157">
       <c r="A63" s="17" t="n">
@@ -41628,23 +41630,21 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>Mangueira</t>
-        </is>
-      </c>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n"/>
       <c r="D63" s="27" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F63" s="19" t="n"/>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>4.91</v>
+      </c>
       <c r="G63" s="19" t="n"/>
       <c r="H63" s="21" t="n"/>
       <c r="I63" s="18" t="n"/>
@@ -41655,32 +41655,39 @@
       </c>
       <c r="B64" s="45" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
-        </is>
-      </c>
-      <c r="C64" s="45" t="n"/>
+          <t>Elio Pereira dos Santos</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
       <c r="D64" s="46" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E64" s="45" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F64" s="47" t="n">
-        <v>4.91</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F64" s="47" t="n"/>
       <c r="G64" s="48" t="n"/>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="45" t="n"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>CLI-0024</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>Elio Pereira dos Santos</t>
+          <t>Maria Madalena de Santana Santos</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -41689,90 +41696,88 @@
         </is>
       </c>
       <c r="D65" s="27" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F65" s="19" t="n"/>
       <c r="G65" s="19" t="n"/>
       <c r="H65" s="21" t="n"/>
-      <c r="I65" s="18" t="n"/>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 13/08/2026 — pagamento recebido em 20/08/2026 (desconto de R$ 10,00)</t>
+        </is>
+      </c>
       <c r="J65" s="18" t="inlineStr">
         <is>
-          <t>CLI-0024</t>
+          <t>CLI-0018</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="44" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="B66" s="45" t="inlineStr">
         <is>
-          <t>Maria Madalena de Santana Santos</t>
+          <t>Marsilia Marmores e Granitos Erelli</t>
         </is>
       </c>
       <c r="C66" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil E3</t>
         </is>
       </c>
       <c r="D66" s="46" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E66" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F66" s="47" t="n"/>
       <c r="G66" s="48" t="n"/>
       <c r="H66" s="49" t="n"/>
-      <c r="I66" s="45" t="inlineStr">
-        <is>
-          <t>Venda de 13/08/2026 — pagamento recebido em 20/08/2026 (desconto de R$ 10,00)</t>
-        </is>
-      </c>
+      <c r="I66" s="45" t="n"/>
       <c r="J66" s="45" t="inlineStr">
         <is>
-          <t>CLI-0018</t>
+          <t>EMP-0216</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>Marsilia Marmores e Granitos Erelli</t>
+          <t>SESC Administração Regional do Estado da Bahia</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>Refil E3</t>
+          <t>4x Refil Carbon Tech 5"</t>
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="n"/>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>8.42</v>
+      </c>
       <c r="G67" s="19" t="n"/>
       <c r="H67" s="21" t="n"/>
       <c r="I67" s="18" t="n"/>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0216</t>
-        </is>
-      </c>
+      <c r="J67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="n">
@@ -41780,24 +41785,24 @@
       </c>
       <c r="B68" s="45" t="inlineStr">
         <is>
-          <t>SESC Administração Regional do Estado da Bahia</t>
+          <t>Lilian Patrícia</t>
         </is>
       </c>
       <c r="C68" s="45" t="inlineStr">
         <is>
-          <t>4x Refil Carbon Tech 5"</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="D68" s="46" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="E68" s="45" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
+          <t>Crédito Parcelado</t>
         </is>
       </c>
       <c r="F68" s="47" t="n">
-        <v>8.42</v>
+        <v>22.37</v>
       </c>
       <c r="G68" s="48" t="n"/>
       <c r="H68" s="49" t="n"/>
@@ -41809,16 +41814,16 @@
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>Lilian Patrícia</t>
+          <t>Natalice da Silva Masquarenhas</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Refil Everest + Mangueira</t>
         </is>
       </c>
       <c r="D69" s="27" t="n">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
@@ -41826,11 +41831,16 @@
         </is>
       </c>
       <c r="F69" s="19" t="n">
-        <v>22.37</v>
+        <v>10.48</v>
       </c>
       <c r="G69" s="19" t="n"/>
       <c r="H69" s="21" t="n"/>
       <c r="I69" s="18" t="n"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>CLI-0051</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="44" t="n">
@@ -41838,16 +41848,16 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>Natalice da Silva Masquarenhas</t>
+          <t>Joelma Almeida</t>
         </is>
       </c>
       <c r="C70" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest + Mangueira</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="D70" s="46" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E70" s="45" t="inlineStr">
         <is>
@@ -41855,79 +41865,80 @@
         </is>
       </c>
       <c r="F70" s="47" t="n">
-        <v>10.48</v>
+        <v>13.98</v>
       </c>
       <c r="G70" s="48" t="n"/>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="45" t="n"/>
       <c r="J70" s="45" t="inlineStr">
         <is>
-          <t>CLI-0051</t>
+          <t>CLI-0450</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>Joelma Almeida</t>
+          <t>Ten Internet</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Carbon Tech 5" + Refil Plissado</t>
         </is>
       </c>
       <c r="D71" s="27" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="n">
-        <v>13.98</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="n"/>
       <c r="G71" s="19" t="n"/>
       <c r="H71" s="21" t="n"/>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0450</t>
-        </is>
-      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 14/08/2026 — pagamento recebido em 19/08/2026</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B72" s="45" t="inlineStr">
         <is>
-          <t>Ten Internet</t>
+          <t>Ivanilton</t>
         </is>
       </c>
       <c r="C72" s="45" t="inlineStr">
         <is>
-          <t>Refil Carbon Tech 5" + Refil Plissado</t>
+          <t>Refil Everest + Engate + Serviço</t>
         </is>
       </c>
       <c r="D72" s="46" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="E72" s="45" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F72" s="47" t="n"/>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F72" s="47" t="n">
+        <v>6.34</v>
+      </c>
       <c r="G72" s="48" t="n"/>
       <c r="H72" s="49" t="n"/>
-      <c r="I72" s="45" t="inlineStr">
-        <is>
-          <t>Venda de 14/08/2026 — pagamento recebido em 19/08/2026</t>
+      <c r="I72" s="45" t="n"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CLI-0401</t>
         </is>
       </c>
     </row>
@@ -41942,20 +41953,18 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest + Engate + Serviço</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="D73" s="27" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
           <t>Débito</t>
         </is>
       </c>
-      <c r="F73" s="19" t="n">
-        <v>6.34</v>
-      </c>
+      <c r="F73" s="19" t="n"/>
       <c r="G73" s="19" t="n"/>
       <c r="H73" s="21" t="n"/>
       <c r="I73" s="18" t="n"/>
@@ -41967,24 +41976,24 @@
     </row>
     <row r="74">
       <c r="A74" s="44" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B74" s="45" t="inlineStr">
         <is>
-          <t>Ivanilton</t>
+          <t>Maria Conceição Dias Da Silva</t>
         </is>
       </c>
       <c r="C74" s="45" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Termostato</t>
         </is>
       </c>
       <c r="D74" s="46" t="n">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="E74" s="45" t="inlineStr">
         <is>
-          <t>Débito</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F74" s="47" t="n"/>
@@ -41993,41 +42002,33 @@
       <c r="I74" s="45" t="n"/>
       <c r="J74" s="45" t="inlineStr">
         <is>
-          <t>CLI-0401</t>
+          <t>CLI-0731</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>Maria Conceição Dias Da Silva</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>Termostato</t>
-        </is>
-      </c>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n"/>
       <c r="D75" s="27" t="n">
-        <v>160</v>
+        <v>1200</v>
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F75" s="19" t="n"/>
       <c r="G75" s="19" t="n"/>
       <c r="H75" s="21" t="n"/>
       <c r="I75" s="18" t="n"/>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0731</t>
-        </is>
-      </c>
+      <c r="J75" s="18" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="44" t="n">
@@ -42035,21 +42036,21 @@
       </c>
       <c r="B76" s="45" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
+          <t>Fracione Transportes</t>
         </is>
       </c>
       <c r="C76" s="45" t="n"/>
-      <c r="D76" s="46" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E76" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+      <c r="D76" s="46" t="n"/>
+      <c r="E76" s="45" t="n"/>
       <c r="F76" s="47" t="n"/>
-      <c r="G76" s="48" t="n"/>
-      <c r="H76" s="49" t="n"/>
+      <c r="G76" s="48" t="n">
+        <v>400.01</v>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
+          <t>Transporte e Entregas</t>
+        </is>
+      </c>
       <c r="I76" s="45" t="n"/>
     </row>
     <row r="77">
@@ -42058,7 +42059,7 @@
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>Fracione Transportes</t>
+          <t>Everest Refrigeração</t>
         </is>
       </c>
       <c r="C77" s="18" t="n"/>
@@ -42066,14 +42067,18 @@
       <c r="E77" s="18" t="n"/>
       <c r="F77" s="19" t="n"/>
       <c r="G77" s="19" t="n">
-        <v>400.01</v>
+        <v>139.31</v>
       </c>
       <c r="H77" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="n"/>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>NF 377737 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="44" t="n">
@@ -42089,7 +42094,7 @@
       <c r="E78" s="45" t="n"/>
       <c r="F78" s="47" t="n"/>
       <c r="G78" s="48" t="n">
-        <v>139.31</v>
+        <v>865.5</v>
       </c>
       <c r="H78" s="49" t="inlineStr">
         <is>
@@ -42098,7 +42103,7 @@
       </c>
       <c r="I78" s="45" t="inlineStr">
         <is>
-          <t>NF 377737 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 725,16 (IPI R$ 28,60): 12x Conexão T + 30x Registro + 20x Botao Completo Purificador (N) + 30x Suporte</t>
+          <t>NF 377738 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto</t>
         </is>
       </c>
     </row>
@@ -42116,7 +42121,7 @@
       <c r="E79" s="18" t="n"/>
       <c r="F79" s="19" t="n"/>
       <c r="G79" s="19" t="n">
-        <v>865.5</v>
+        <v>856.35</v>
       </c>
       <c r="H79" s="21" t="inlineStr">
         <is>
@@ -42125,7 +42130,7 @@
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
-          <t>NF 377738 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.327,52: Purificador Everest Plus Branco + Purificador Everest Plus Prata + Purificador Everest Slim Branco + 2x Purificador Everest Fit Prata + Purificador Everest Fit Preto</t>
+          <t>NF 377739 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata</t>
         </is>
       </c>
     </row>
@@ -42135,7 +42140,7 @@
       </c>
       <c r="B80" s="45" t="inlineStr">
         <is>
-          <t>Everest Refrigeração</t>
+          <t>Eversoft</t>
         </is>
       </c>
       <c r="C80" s="45" t="n"/>
@@ -42143,7 +42148,7 @@
       <c r="E80" s="45" t="n"/>
       <c r="F80" s="47" t="n"/>
       <c r="G80" s="48" t="n">
-        <v>856.35</v>
+        <v>980.83</v>
       </c>
       <c r="H80" s="49" t="inlineStr">
         <is>
@@ -42152,7 +42157,7 @@
       </c>
       <c r="I80" s="45" t="inlineStr">
         <is>
-          <t>NF 377739 de 19/05/2026 · parcela 3/5 (venc. 17/08/2026) · compra total R$ 4.281,74: Purificador Everest Slim Branco + Purificador Everest Slim Preto + Purificador Everest Plus Branco + Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Plus Prata</t>
+          <t>NF 74454 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
         </is>
       </c>
     </row>
@@ -42162,7 +42167,7 @@
       </c>
       <c r="B81" s="18" t="inlineStr">
         <is>
-          <t>Eversoft</t>
+          <t>Everest Refrigeração</t>
         </is>
       </c>
       <c r="C81" s="18" t="n"/>
@@ -42170,7 +42175,7 @@
       <c r="E81" s="18" t="n"/>
       <c r="F81" s="19" t="n"/>
       <c r="G81" s="19" t="n">
-        <v>980.83</v>
+        <v>892.3</v>
       </c>
       <c r="H81" s="21" t="inlineStr">
         <is>
@@ -42179,7 +42184,7 @@
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>NF 74454 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.904,13: 100x Refil Everest + 50x Pré Filtro</t>
+          <t>NF 381554 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.461,49: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata</t>
         </is>
       </c>
     </row>
@@ -42189,7 +42194,7 @@
       </c>
       <c r="B82" s="45" t="inlineStr">
         <is>
-          <t>Everest Refrigeração</t>
+          <t>Tarcisio Oliveira Lima</t>
         </is>
       </c>
       <c r="C82" s="45" t="n"/>
@@ -42197,49 +42202,53 @@
       <c r="E82" s="45" t="n"/>
       <c r="F82" s="47" t="n"/>
       <c r="G82" s="48" t="n">
-        <v>892.3</v>
+        <v>486.32</v>
       </c>
       <c r="H82" s="49" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I82" s="45" t="inlineStr">
-        <is>
-          <t>NF 381554 de 17/07/2026 · parcela 1/5 (venc. 16/08/2026) · compra total R$ 4.461,49: Purificador Everest Fit Branco + Purificador Everest Fit Preto + 2x Purificador Everest Star Branco + Purificador Everest Star Preto + Purificador Everest Plus Prata</t>
-        </is>
-      </c>
+          <t>Contabilidade</t>
+        </is>
+      </c>
+      <c r="I82" s="45" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>Tarcisio Oliveira Lima</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="27" t="n"/>
-      <c r="E83" s="18" t="n"/>
+          <t>Abrigo São Vicente Miguel Calmon</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F83" s="19" t="n"/>
-      <c r="G83" s="19" t="n">
-        <v>486.32</v>
-      </c>
-      <c r="H83" s="21" t="inlineStr">
-        <is>
-          <t>Contabilidade</t>
-        </is>
-      </c>
-      <c r="I83" s="18" t="n"/>
+      <c r="G83" s="19" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 18/08/2026 — pagamento recebido em 19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="44" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B84" s="45" t="inlineStr">
         <is>
-          <t>Abrigo São Vicente Miguel Calmon</t>
+          <t>Caroline Rios</t>
         </is>
       </c>
       <c r="C84" s="45" t="inlineStr">
@@ -42252,15 +42261,18 @@
       </c>
       <c r="E84" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F84" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F84" s="47" t="n">
+        <v>10.48</v>
+      </c>
       <c r="G84" s="48" t="n"/>
       <c r="H84" s="49" t="n"/>
-      <c r="I84" s="45" t="inlineStr">
-        <is>
-          <t>Venda de 18/08/2026 — pagamento recebido em 19/08/2026</t>
+      <c r="I84" s="45" t="n"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>OUT-0054</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42282,7 @@
       </c>
       <c r="B85" s="18" t="inlineStr">
         <is>
-          <t>Caroline Rios</t>
+          <t>Marinez Bráulio</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
@@ -42283,18 +42295,16 @@
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F85" s="19" t="n">
-        <v>10.48</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F85" s="19" t="n"/>
       <c r="G85" s="19" t="n"/>
       <c r="H85" s="21" t="n"/>
       <c r="I85" s="18" t="n"/>
       <c r="J85" s="18" t="inlineStr">
         <is>
-          <t>OUT-0054</t>
+          <t>OUT-0078</t>
         </is>
       </c>
     </row>
@@ -42304,7 +42314,7 @@
       </c>
       <c r="B86" s="45" t="inlineStr">
         <is>
-          <t>Marinez Bráulio</t>
+          <t>Orlanete Souza</t>
         </is>
       </c>
       <c r="C86" s="45" t="inlineStr">
@@ -42317,16 +42327,18 @@
       </c>
       <c r="E86" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F86" s="47" t="n"/>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F86" s="47" t="n">
+        <v>5.27</v>
+      </c>
       <c r="G86" s="48" t="n"/>
       <c r="H86" s="49" t="n"/>
       <c r="I86" s="45" t="n"/>
       <c r="J86" s="45" t="inlineStr">
         <is>
-          <t>OUT-0078</t>
+          <t>OUT-0016</t>
         </is>
       </c>
     </row>
@@ -42336,7 +42348,7 @@
       </c>
       <c r="B87" s="18" t="inlineStr">
         <is>
-          <t>Orlanete Souza</t>
+          <t>Vitor Gabriel</t>
         </is>
       </c>
       <c r="C87" s="18" t="inlineStr">
@@ -42345,24 +42357,18 @@
         </is>
       </c>
       <c r="D87" s="27" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F87" s="19" t="n">
-        <v>5.27</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F87" s="19" t="n"/>
       <c r="G87" s="19" t="n"/>
       <c r="H87" s="21" t="n"/>
       <c r="I87" s="18" t="n"/>
-      <c r="J87" s="18" t="inlineStr">
-        <is>
-          <t>OUT-0016</t>
-        </is>
-      </c>
+      <c r="J87" s="18" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="44" t="n">
@@ -42370,43 +42376,54 @@
       </c>
       <c r="B88" s="45" t="inlineStr">
         <is>
-          <t>Vitor Gabriel</t>
+          <t>Maria Madalena Nunes de Oliveira - Marijane</t>
         </is>
       </c>
       <c r="C88" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life + Pré Filtro</t>
         </is>
       </c>
       <c r="D88" s="46" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E88" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F88" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F88" s="47" t="n">
+        <v>13.98</v>
+      </c>
       <c r="G88" s="48" t="n"/>
       <c r="H88" s="49" t="n"/>
-      <c r="I88" s="45" t="n"/>
+      <c r="I88" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 3x.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>CLI-0362</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B89" s="18" t="inlineStr">
         <is>
-          <t>Maria Madalena Nunes de Oliveira - Marijane</t>
+          <t>Edivaldo Jonas de Oliveira</t>
         </is>
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Pré Filtro</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="D89" s="27" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
@@ -42414,56 +42431,50 @@
         </is>
       </c>
       <c r="F89" s="19" t="n">
-        <v>13.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G89" s="19" t="n"/>
       <c r="H89" s="21" t="n"/>
       <c r="I89" s="18" t="inlineStr">
         <is>
-          <t>Crédito em 3x.</t>
+          <t>Venda de 19/08/2026 — pagamento recebido em 20/08/2026 (crédito 3x)</t>
         </is>
       </c>
       <c r="J89" s="18" t="inlineStr">
         <is>
-          <t>CLI-0362</t>
+          <t>CLI-0211</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="44" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B90" s="45" t="inlineStr">
         <is>
-          <t>Edivaldo Jonas de Oliveira</t>
+          <t>Roup Mania</t>
         </is>
       </c>
       <c r="C90" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="D90" s="46" t="n">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="E90" s="45" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F90" s="47" t="n">
-        <v>9.970000000000001</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F90" s="47" t="n"/>
       <c r="G90" s="48" t="n"/>
       <c r="H90" s="49" t="n"/>
-      <c r="I90" s="45" t="inlineStr">
-        <is>
-          <t>Venda de 19/08/2026 — pagamento recebido em 20/08/2026 (crédito 3x)</t>
-        </is>
-      </c>
+      <c r="I90" s="45" t="n"/>
       <c r="J90" s="45" t="inlineStr">
         <is>
-          <t>CLI-0211</t>
+          <t>EMP-0263</t>
         </is>
       </c>
     </row>
@@ -42473,31 +42484,27 @@
       </c>
       <c r="B91" s="18" t="inlineStr">
         <is>
-          <t>Roup Mania</t>
+          <t>Cliente Consumidor Final</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="D91" s="27" t="n">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F91" s="19" t="n"/>
       <c r="G91" s="19" t="n"/>
       <c r="H91" s="21" t="n"/>
       <c r="I91" s="18" t="n"/>
-      <c r="J91" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0263</t>
-        </is>
-      </c>
+      <c r="J91" s="18" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="44" t="n">
@@ -42505,25 +42512,21 @@
       </c>
       <c r="B92" s="45" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
-        </is>
-      </c>
-      <c r="C92" s="45" t="inlineStr">
-        <is>
-          <t>Mangueira</t>
-        </is>
-      </c>
-      <c r="D92" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Dona Rute (Limpeza)</t>
+        </is>
+      </c>
+      <c r="C92" s="45" t="n"/>
+      <c r="D92" s="46" t="n"/>
+      <c r="E92" s="45" t="n"/>
       <c r="F92" s="47" t="n"/>
-      <c r="G92" s="48" t="n"/>
-      <c r="H92" s="49" t="n"/>
+      <c r="G92" s="48" t="n">
+        <v>50</v>
+      </c>
+      <c r="H92" s="49" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
       <c r="I92" s="45" t="n"/>
     </row>
     <row r="93">
@@ -42532,7 +42535,7 @@
       </c>
       <c r="B93" s="18" t="inlineStr">
         <is>
-          <t>Dona Rute (Limpeza)</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="C93" s="18" t="n"/>
@@ -42544,7 +42547,7 @@
       </c>
       <c r="H93" s="21" t="inlineStr">
         <is>
-          <t>Salários, Comissões e Encargos</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I93" s="18" t="n"/>
@@ -42555,22 +42558,31 @@
       </c>
       <c r="B94" s="45" t="inlineStr">
         <is>
-          <t>Gasolina</t>
-        </is>
-      </c>
-      <c r="C94" s="45" t="n"/>
-      <c r="D94" s="46" t="n"/>
-      <c r="E94" s="45" t="n"/>
+          <t>Dm Contabilidade Acessoria e Consultoria</t>
+        </is>
+      </c>
+      <c r="C94" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D94" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E94" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
       <c r="F94" s="47" t="n"/>
-      <c r="G94" s="48" t="n">
-        <v>50</v>
-      </c>
-      <c r="H94" s="49" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
+      <c r="G94" s="48" t="n"/>
+      <c r="H94" s="49" t="n"/>
       <c r="I94" s="45" t="n"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>EMP-0120</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n">
@@ -42578,12 +42590,12 @@
       </c>
       <c r="B95" s="18" t="inlineStr">
         <is>
-          <t>Dm Contabilidade Acessoria e Consultoria</t>
+          <t>Atacadão Lojão dos Calçados</t>
         </is>
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D95" s="27" t="n">
@@ -42591,7 +42603,7 @@
       </c>
       <c r="E95" s="18" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F95" s="19" t="n"/>
@@ -42600,7 +42612,7 @@
       <c r="I95" s="18" t="n"/>
       <c r="J95" s="18" t="inlineStr">
         <is>
-          <t>EMP-0120</t>
+          <t>EMP-0309</t>
         </is>
       </c>
     </row>
@@ -42610,31 +42622,27 @@
       </c>
       <c r="B96" s="45" t="inlineStr">
         <is>
-          <t>Atacadão Lojão dos Calçados</t>
-        </is>
-      </c>
-      <c r="C96" s="45" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="D96" s="46" t="n">
-        <v>140</v>
-      </c>
-      <c r="E96" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C96" s="45" t="n"/>
+      <c r="D96" s="46" t="n"/>
+      <c r="E96" s="45" t="n"/>
       <c r="F96" s="47" t="n"/>
-      <c r="G96" s="48" t="n"/>
-      <c r="H96" s="49" t="n"/>
-      <c r="I96" s="45" t="n"/>
-      <c r="J96" s="45" t="inlineStr">
-        <is>
-          <t>EMP-0309</t>
-        </is>
-      </c>
+      <c r="G96" s="48" t="n">
+        <v>1385.85</v>
+      </c>
+      <c r="H96" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I96" s="45" t="inlineStr">
+        <is>
+          <t>NF 131997 de 08/07/2026 · parcela 2/4 (venc. 19/08/2026) · compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
+        </is>
+      </c>
+      <c r="J96" s="45" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -42642,24 +42650,29 @@
       </c>
       <c r="B97" s="18" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="27" t="n"/>
-      <c r="E97" s="18" t="n"/>
+          <t>Lapec</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>Refil C+3</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F97" s="19" t="n"/>
-      <c r="G97" s="19" t="n">
-        <v>1385.85</v>
-      </c>
-      <c r="H97" s="21" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I97" s="18" t="inlineStr">
-        <is>
-          <t>NF 131997 de 08/07/2026 · parcela 2/4 (venc. 19/08/2026) · compra total R$ 5.831,67 (IPI R$ 288,26): 5x Refil Fp4 + 8x Refil Carbon Tech 5 Pol + 120x Refil E3 + 90x Refil Pre-E3 + 10x Refil Top Multifilter + 4x Refil Fpa16</t>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>EMP-0199</t>
         </is>
       </c>
     </row>
@@ -42669,54 +42682,57 @@
       </c>
       <c r="B98" s="45" t="inlineStr">
         <is>
-          <t>Lapec</t>
-        </is>
-      </c>
-      <c r="C98" s="45" t="inlineStr">
-        <is>
-          <t>Refil C+3</t>
-        </is>
-      </c>
-      <c r="D98" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="E98" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Canetas e Tesoura</t>
+        </is>
+      </c>
+      <c r="C98" s="45" t="n"/>
+      <c r="D98" s="46" t="n"/>
+      <c r="E98" s="45" t="n"/>
       <c r="F98" s="47" t="n"/>
-      <c r="G98" s="48" t="n"/>
-      <c r="H98" s="49" t="n"/>
+      <c r="G98" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H98" s="49" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
       <c r="I98" s="45" t="n"/>
-      <c r="J98" s="45" t="inlineStr">
-        <is>
-          <t>EMP-0199</t>
-        </is>
-      </c>
+      <c r="J98" s="45" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B99" s="18" t="inlineStr">
         <is>
-          <t>Canetas e Tesoura</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="n"/>
-      <c r="D99" s="27" t="n"/>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="19" t="n"/>
-      <c r="G99" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="H99" s="21" t="inlineStr">
-        <is>
-          <t>Material de Limpeza e Escritório</t>
-        </is>
-      </c>
+          <t>Elvira Rocha Magalhães</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="F99" s="19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G99" s="19" t="n"/>
+      <c r="H99" s="21" t="n"/>
       <c r="I99" s="18" t="n"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>CLI-0885</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="157">
       <c r="A100" s="44" t="n">
@@ -42724,33 +42740,31 @@
       </c>
       <c r="B100" s="45" t="inlineStr">
         <is>
-          <t>Elvira Rocha Magalhães</t>
+          <t>Pedro Sangalo</t>
         </is>
       </c>
       <c r="C100" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Mangueira + Revisão/Manutenção</t>
         </is>
       </c>
       <c r="D100" s="46" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="E100" s="45" t="inlineStr">
         <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="F100" s="47" t="n">
-        <v>2.03</v>
-      </c>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="F100" s="47" t="n"/>
       <c r="G100" s="48" t="n"/>
       <c r="H100" s="49" t="n"/>
-      <c r="I100" s="45" t="n"/>
-      <c r="J100" s="45" t="inlineStr">
-        <is>
-          <t>CLI-0885</t>
-        </is>
-      </c>
+      <c r="I100" s="45" t="inlineStr">
+        <is>
+          <t>Recebido via Pix de Arena Daniel 73 LTDA — DOC 71208662 (20/08/2026)</t>
+        </is>
+      </c>
+      <c r="J100" s="45" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="17" t="n">
@@ -42758,96 +42772,93 @@
       </c>
       <c r="B101" s="18" t="inlineStr">
         <is>
-          <t>Pedro Sangalo</t>
+          <t>Endalba</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>Refil Everest + Mangueira + Revisão/Manutenção</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="D101" s="27" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F101" s="19" t="n"/>
       <c r="G101" s="19" t="n"/>
       <c r="H101" s="21" t="n"/>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t>Recebido via Pix de Arena Daniel 73 LTDA — DOC 71208662 (20/08/2026)</t>
+      <c r="I101" s="18" t="n"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>CLI-0219</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="157">
       <c r="A102" s="44" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B102" s="45" t="inlineStr">
         <is>
-          <t>Endalba</t>
+          <t>Salão de Luciana</t>
         </is>
       </c>
       <c r="C102" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="D102" s="46" t="n">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="E102" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
-      <c r="F102" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F102" s="47" t="n">
+        <v>17.98</v>
+      </c>
       <c r="G102" s="48" t="n"/>
       <c r="H102" s="49" t="n"/>
       <c r="I102" s="45" t="n"/>
       <c r="J102" s="45" t="inlineStr">
         <is>
-          <t>CLI-0219</t>
+          <t>EMP-0268</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B103" s="18" t="inlineStr">
         <is>
-          <t>Salão de Luciana</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="D103" s="27" t="n">
-        <v>225</v>
-      </c>
-      <c r="E103" s="18" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F103" s="19" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="G103" s="19" t="n"/>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="18" t="n"/>
-      <c r="J103" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0268</t>
-        </is>
-      </c>
+          <t>DAS — Documento de Arrecadação do Simples Nacional</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="27" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="19" t="n"/>
+      <c r="G103" s="19" t="n">
+        <v>2330.53</v>
+      </c>
+      <c r="H103" s="21" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+        </is>
+      </c>
+      <c r="J103" s="18" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="157">
       <c r="A104" s="44" t="n">
@@ -42855,7 +42866,7 @@
       </c>
       <c r="B104" s="45" t="inlineStr">
         <is>
-          <t>DAS — Documento de Arrecadação do Simples Nacional</t>
+          <t>FGTS</t>
         </is>
       </c>
       <c r="C104" s="45" t="n"/>
@@ -42863,7 +42874,7 @@
       <c r="E104" s="45" t="n"/>
       <c r="F104" s="47" t="n"/>
       <c r="G104" s="48" t="n">
-        <v>2330.53</v>
+        <v>136</v>
       </c>
       <c r="H104" s="49" t="inlineStr">
         <is>
@@ -42872,7 +42883,7 @@
       </c>
       <c r="I104" s="45" t="inlineStr">
         <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+          <t>Pago via Pix à Caixa Econômica Federal — DOC 70916805 (20/08/2026)</t>
         </is>
       </c>
     </row>
@@ -42882,7 +42893,7 @@
       </c>
       <c r="B105" s="18" t="inlineStr">
         <is>
-          <t>FGTS</t>
+          <t>Pagamento de Tributos — Internet Banking</t>
         </is>
       </c>
       <c r="C105" s="18" t="n"/>
@@ -42890,7 +42901,7 @@
       <c r="E105" s="18" t="n"/>
       <c r="F105" s="19" t="n"/>
       <c r="G105" s="19" t="n">
-        <v>136</v>
+        <v>306.99</v>
       </c>
       <c r="H105" s="21" t="inlineStr">
         <is>
@@ -42899,34 +42910,41 @@
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>Pago via Pix à Caixa Econômica Federal — DOC 70916805 (20/08/2026)</t>
+          <t>Extrato: PGTO TRIBUTOS INTERNBANK — DOC 70953537 (20/08/2026)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="44" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B106" s="45" t="inlineStr">
         <is>
-          <t>Pagamento de Tributos — Internet Banking</t>
-        </is>
-      </c>
-      <c r="C106" s="45" t="n"/>
-      <c r="D106" s="46" t="n"/>
-      <c r="E106" s="45" t="n"/>
-      <c r="F106" s="47" t="n"/>
-      <c r="G106" s="48" t="n">
-        <v>306.99</v>
-      </c>
-      <c r="H106" s="49" t="inlineStr">
-        <is>
-          <t>Impostos e Taxas</t>
-        </is>
-      </c>
-      <c r="I106" s="45" t="inlineStr">
-        <is>
-          <t>Extrato: PGTO TRIBUTOS INTERNBANK — DOC 70953537 (20/08/2026)</t>
+          <t>Luana Mesquita Victoria</t>
+        </is>
+      </c>
+      <c r="C106" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Grafite</t>
+        </is>
+      </c>
+      <c r="D106" s="46" t="n">
+        <v>1689</v>
+      </c>
+      <c r="E106" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F106" s="47" t="n">
+        <v>236.29</v>
+      </c>
+      <c r="G106" s="48" t="n"/>
+      <c r="H106" s="49" t="n"/>
+      <c r="I106" s="45" t="n"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>CLI-0887</t>
         </is>
       </c>
     </row>
@@ -42936,33 +42954,29 @@
       </c>
       <c r="B107" s="18" t="inlineStr">
         <is>
-          <t>Luana Mesquita Victoria</t>
+          <t>Amélia Pinho</t>
         </is>
       </c>
       <c r="C107" s="18" t="inlineStr">
         <is>
-          <t>Purificador Everest Foz Grafite</t>
+          <t>Refil Pro Life + Pré Filtro</t>
         </is>
       </c>
       <c r="D107" s="27" t="n">
-        <v>1689</v>
+        <v>200</v>
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
+          <t>Débito</t>
         </is>
       </c>
       <c r="F107" s="19" t="n">
-        <v>236.29</v>
+        <v>2.9</v>
       </c>
       <c r="G107" s="19" t="n"/>
       <c r="H107" s="21" t="n"/>
       <c r="I107" s="18" t="n"/>
-      <c r="J107" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0887</t>
-        </is>
-      </c>
+      <c r="J107" s="18" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="44" t="n">
@@ -42970,25 +42984,23 @@
       </c>
       <c r="B108" s="45" t="inlineStr">
         <is>
-          <t>Amélia Pinho</t>
+          <t>Colégio Armando Xavier de Oliveira</t>
         </is>
       </c>
       <c r="C108" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Pré Filtro</t>
+          <t>Refil Plissado + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="D108" s="46" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E108" s="45" t="inlineStr">
         <is>
-          <t>Débito</t>
-        </is>
-      </c>
-      <c r="F108" s="47" t="n">
-        <v>2.9</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F108" s="47" t="n"/>
       <c r="G108" s="48" t="n"/>
       <c r="H108" s="49" t="n"/>
       <c r="I108" s="45" t="n"/>
@@ -42999,25 +43011,21 @@
       </c>
       <c r="B109" s="18" t="inlineStr">
         <is>
-          <t>Colégio Armando Xavier de Oliveira</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="D109" s="27" t="n">
-        <v>150</v>
-      </c>
-      <c r="E109" s="18" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Diarista Eva</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="27" t="n"/>
+      <c r="E109" s="18" t="n"/>
       <c r="F109" s="19" t="n"/>
-      <c r="G109" s="19" t="n"/>
-      <c r="H109" s="21" t="n"/>
+      <c r="G109" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="H109" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="I109" s="18" t="n"/>
     </row>
     <row r="110">
@@ -43026,7 +43034,7 @@
       </c>
       <c r="B110" s="45" t="inlineStr">
         <is>
-          <t>Diarista Eva</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="C110" s="45" t="n"/>
@@ -43034,11 +43042,11 @@
       <c r="E110" s="45" t="n"/>
       <c r="F110" s="47" t="n"/>
       <c r="G110" s="48" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="H110" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I110" s="45" t="n"/>
@@ -43049,7 +43057,7 @@
       </c>
       <c r="B111" s="18" t="inlineStr">
         <is>
-          <t>Gasolina</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="C111" s="18" t="n"/>
@@ -43057,73 +43065,78 @@
       <c r="E111" s="18" t="n"/>
       <c r="F111" s="19" t="n"/>
       <c r="G111" s="19" t="n">
-        <v>20</v>
+        <v>874.6799999999999</v>
       </c>
       <c r="H111" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I111" s="18" t="n"/>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>NF 379826 de 22/06/2026 · parcela 2/5 (venc. 21/08/2026) · compra total R$ 4.373,40: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="44" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B112" s="45" t="inlineStr">
         <is>
-          <t>Everest</t>
-        </is>
-      </c>
-      <c r="C112" s="45" t="n"/>
-      <c r="D112" s="46" t="n"/>
-      <c r="E112" s="45" t="n"/>
+          <t>Hospital e Clinica Santa Barbara</t>
+        </is>
+      </c>
+      <c r="C112" s="45" t="inlineStr">
+        <is>
+          <t>Purificador Everest Foz Branco</t>
+        </is>
+      </c>
+      <c r="D112" s="46" t="n">
+        <v>1489</v>
+      </c>
+      <c r="E112" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F112" s="47" t="n"/>
-      <c r="G112" s="48" t="n">
-        <v>874.6799999999999</v>
-      </c>
-      <c r="H112" s="49" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I112" s="45" t="inlineStr">
-        <is>
-          <t>NF 379826 de 22/06/2026 · parcela 2/5 (venc. 21/08/2026) · compra total R$ 4.373,40: 2x Purificador Everest Slim Prata + 2x Purificador Everest Star Prata + Purificador Everest Star Branco + Purificador Everest Fit Branco</t>
+      <c r="G112" s="48" t="n"/>
+      <c r="H112" s="49" t="n"/>
+      <c r="I112" s="45" t="n"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>EMP-0172</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="n">
-        <v>46261</v>
+        <v>46256</v>
       </c>
       <c r="B113" s="18" t="inlineStr">
         <is>
-          <t>Hospital e Clinica Santa Barbara</t>
+          <t>Cliente Consumidor Final</t>
         </is>
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>Purificador Everest Foz Branco</t>
+          <t>Refil FP4</t>
         </is>
       </c>
       <c r="D113" s="27" t="n">
-        <v>1489</v>
+        <v>80</v>
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F113" s="19" t="n"/>
       <c r="G113" s="19" t="n"/>
       <c r="H113" s="21" t="n"/>
       <c r="I113" s="18" t="n"/>
-      <c r="J113" s="18" t="inlineStr">
-        <is>
-          <t>EMP-0172</t>
-        </is>
-      </c>
+      <c r="J113" s="18" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="44" t="n">
@@ -43131,26 +43144,31 @@
       </c>
       <c r="B114" s="45" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
+          <t>Academia Diego Cesar</t>
         </is>
       </c>
       <c r="C114" s="45" t="inlineStr">
         <is>
-          <t>Refil FP4</t>
+          <t>Refil Carbon Tech 9"</t>
         </is>
       </c>
       <c r="D114" s="46" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E114" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F114" s="47" t="n"/>
       <c r="G114" s="48" t="n"/>
       <c r="H114" s="49" t="n"/>
       <c r="I114" s="45" t="n"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>EMP-0310</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="n">
@@ -43158,20 +43176,20 @@
       </c>
       <c r="B115" s="18" t="inlineStr">
         <is>
-          <t>Academia Diego Cesar</t>
+          <t>Pedras e Pisos Depósito</t>
         </is>
       </c>
       <c r="C115" s="18" t="inlineStr">
         <is>
-          <t>Refil Carbon Tech 9"</t>
+          <t>Refil E3</t>
         </is>
       </c>
       <c r="D115" s="27" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F115" s="19" t="n"/>
@@ -43180,49 +43198,45 @@
       <c r="I115" s="18" t="n"/>
       <c r="J115" s="18" t="inlineStr">
         <is>
-          <t>EMP-0310</t>
+          <t>EMP-0245</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="44" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="B116" s="45" t="inlineStr">
         <is>
-          <t>Pedras e Pisos Depósito</t>
-        </is>
-      </c>
-      <c r="C116" s="45" t="inlineStr">
-        <is>
-          <t>Refil E3</t>
-        </is>
-      </c>
-      <c r="D116" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="E116" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Tarifa Pix</t>
+        </is>
+      </c>
+      <c r="C116" s="45" t="n"/>
+      <c r="D116" s="46" t="n"/>
+      <c r="E116" s="45" t="n"/>
       <c r="F116" s="47" t="n"/>
-      <c r="G116" s="48" t="n"/>
-      <c r="H116" s="49" t="n"/>
-      <c r="I116" s="45" t="n"/>
-      <c r="J116" s="45" t="inlineStr">
-        <is>
-          <t>EMP-0245</t>
-        </is>
-      </c>
+      <c r="G116" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="49" t="inlineStr">
+        <is>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I116" s="45" t="inlineStr">
+        <is>
+          <t>Extrato: TAR PIX PAGTO TRANSFERENC — DOC 70819916 (20/08/2026)</t>
+        </is>
+      </c>
+      <c r="J116" s="45" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="17" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B117" s="18" t="inlineStr">
         <is>
-          <t>Tarifa Pix</t>
+          <t>Comissão Wiliam</t>
         </is>
       </c>
       <c r="C117" s="18" t="n"/>
@@ -43230,43 +43244,47 @@
       <c r="E117" s="18" t="n"/>
       <c r="F117" s="19" t="n"/>
       <c r="G117" s="19" t="n">
-        <v>1</v>
+        <v>590</v>
       </c>
       <c r="H117" s="21" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias e Cartão</t>
+          <t>Salários, Comissões e Encargos</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
-          <t>Extrato: TAR PIX PAGTO TRANSFERENC — DOC 70819916 (20/08/2026)</t>
+          <t>Comissões da quinzena de 10/08 a 22/08/2026 — 53 serviços</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="44" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B118" s="45" t="inlineStr">
         <is>
-          <t>Comissão Wiliam</t>
-        </is>
-      </c>
-      <c r="C118" s="45" t="n"/>
-      <c r="D118" s="46" t="n"/>
-      <c r="E118" s="45" t="n"/>
+          <t>UNIFG Brumado (Brumado/BA)</t>
+        </is>
+      </c>
+      <c r="C118" s="45" t="inlineStr">
+        <is>
+          <t>3x Refil E3 + 3x Refil Pré E3 + 2x Refil Carbon Tech 5" + 2x Refil FP4 + 2x Refil Multifilter</t>
+        </is>
+      </c>
+      <c r="D118" s="46" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E118" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F118" s="47" t="n"/>
-      <c r="G118" s="48" t="n">
-        <v>590</v>
-      </c>
-      <c r="H118" s="49" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
+      <c r="G118" s="48" t="n"/>
+      <c r="H118" s="49" t="n"/>
       <c r="I118" s="45" t="inlineStr">
         <is>
-          <t>Comissões da quinzena de 10/08 a 22/08/2026 — 53 serviços</t>
+          <t>Grupo Ânima — OC PO_CESGPO00006007_0 · orçamento de 07/07/2026 (desc. 3%) · pago via Pix pela CESG em 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -43276,16 +43294,16 @@
       </c>
       <c r="B119" s="18" t="inlineStr">
         <is>
-          <t>UNIFG Brumado (Brumado/BA)</t>
+          <t>UNIFG Vasco da Gama (Guanambi/BA)</t>
         </is>
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>3x Refil E3 + 3x Refil Pré E3 + 2x Refil Carbon Tech 5" + 2x Refil FP4 + 2x Refil Multifilter</t>
+          <t>11x Refil E3 + 6x Refil Pré E3</t>
         </is>
       </c>
       <c r="D119" s="27" t="n">
-        <v>1358</v>
+        <v>2320</v>
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
@@ -43297,7 +43315,7 @@
       <c r="H119" s="21" t="n"/>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC PO_CESGPO00006007_0 · orçamento de 07/07/2026 (desc. 3%) · pago via Pix pela CESG em 24/08/2026</t>
+          <t>Grupo Ânima — OC PO_CESGPO00006009_1 · orçamento de 07/07/2026 · pago via Pix pela CESG em 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -43307,16 +43325,16 @@
       </c>
       <c r="B120" s="45" t="inlineStr">
         <is>
-          <t>UNIFG Vasco da Gama (Guanambi/BA)</t>
+          <t>UNP Salgado Filho (Natal/RN)</t>
         </is>
       </c>
       <c r="C120" s="45" t="inlineStr">
         <is>
-          <t>11x Refil E3 + 6x Refil Pré E3</t>
+          <t>8x Refil E3 + 8x Refil Pré E3 + 6x Refil Carbon Tech 9"</t>
         </is>
       </c>
       <c r="D120" s="46" t="n">
-        <v>2320</v>
+        <v>2948.8</v>
       </c>
       <c r="E120" s="45" t="inlineStr">
         <is>
@@ -43328,7 +43346,7 @@
       <c r="H120" s="49" t="n"/>
       <c r="I120" s="45" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC PO_CESGPO00006009_1 · orçamento de 07/07/2026 · pago via Pix pela CESG em 24/08/2026</t>
+          <t>Grupo Ânima — OC PO_APECPO00019433_0 · orçamento de 08/07/2026 (desc. 3%) · pago via Pix pela APEC em 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -43338,16 +43356,16 @@
       </c>
       <c r="B121" s="18" t="inlineStr">
         <is>
-          <t>UNP Salgado Filho (Natal/RN)</t>
+          <t>FG Piedade (Jaboatão/PE)</t>
         </is>
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>8x Refil E3 + 8x Refil Pré E3 + 6x Refil Carbon Tech 9"</t>
+          <t>10x Refil E3 + 10x Refil Pré E3</t>
         </is>
       </c>
       <c r="D121" s="27" t="n">
-        <v>2948.8</v>
+        <v>2600</v>
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
@@ -43359,7 +43377,7 @@
       <c r="H121" s="21" t="n"/>
       <c r="I121" s="18" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC PO_APECPO00019433_0 · orçamento de 08/07/2026 (desc. 3%) · pago via Pix pela APEC em 24/08/2026</t>
+          <t>Grupo Ânima — OC PO_SOCECPO00006536_0 · orçamento de 08/07/2026 · pago via Pix pela SOCEC em 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -43369,16 +43387,16 @@
       </c>
       <c r="B122" s="45" t="inlineStr">
         <is>
-          <t>FG Piedade (Jaboatão/PE)</t>
+          <t>FPB João Pessoa (João Pessoa/PB)</t>
         </is>
       </c>
       <c r="C122" s="45" t="inlineStr">
         <is>
-          <t>10x Refil E3 + 10x Refil Pré E3</t>
+          <t>10x Refil E3 + 10x Refil Pré E3 + 4x Refil BAG + 2x Refil Pro Life</t>
         </is>
       </c>
       <c r="D122" s="46" t="n">
-        <v>2600</v>
+        <v>3181.6</v>
       </c>
       <c r="E122" s="45" t="inlineStr">
         <is>
@@ -43390,38 +43408,34 @@
       <c r="H122" s="49" t="n"/>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC PO_SOCECPO00006536_0 · orçamento de 08/07/2026 · pago via Pix pela SOCEC em 24/08/2026</t>
+          <t>Grupo Ânima — OC PO_ASPECPO00004346_0 · orçamento de 08/07/2026 (desc. 3%) · pago via Pix pela ASPEC em 24/08/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="B123" s="18" t="inlineStr">
         <is>
-          <t>FPB João Pessoa (João Pessoa/PB)</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>10x Refil E3 + 10x Refil Pré E3 + 4x Refil BAG + 2x Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="D123" s="27" t="n">
-        <v>3181.6</v>
-      </c>
-      <c r="E123" s="18" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Click Comércio e Distribuição</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="27" t="n"/>
+      <c r="E123" s="18" t="n"/>
       <c r="F123" s="19" t="n"/>
-      <c r="G123" s="19" t="n"/>
-      <c r="H123" s="21" t="n"/>
+      <c r="G123" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC PO_ASPECPO00004346_0 · orçamento de 08/07/2026 (desc. 3%) · pago via Pix pela ASPEC em 24/08/2026</t>
+          <t>Extrato Stone — Pix de 04/08/2026</t>
         </is>
       </c>
     </row>
@@ -43431,7 +43445,7 @@
       </c>
       <c r="B124" s="45" t="inlineStr">
         <is>
-          <t>Click Comércio e Distribuição</t>
+          <t>Vaz Comércio de Cosméticos</t>
         </is>
       </c>
       <c r="C124" s="45" t="n"/>
@@ -43439,7 +43453,7 @@
       <c r="E124" s="45" t="n"/>
       <c r="F124" s="47" t="n"/>
       <c r="G124" s="48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H124" s="49" t="inlineStr">
         <is>
@@ -43458,7 +43472,7 @@
       </c>
       <c r="B125" s="18" t="inlineStr">
         <is>
-          <t>Vaz Comércio de Cosméticos</t>
+          <t>Estacionamento (Pagar.me)</t>
         </is>
       </c>
       <c r="C125" s="18" t="n"/>
@@ -43466,11 +43480,11 @@
       <c r="E125" s="18" t="n"/>
       <c r="F125" s="19" t="n"/>
       <c r="G125" s="19" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="H125" s="21" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I125" s="18" t="inlineStr">
@@ -43493,7 +43507,7 @@
       <c r="E126" s="45" t="n"/>
       <c r="F126" s="47" t="n"/>
       <c r="G126" s="48" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H126" s="49" t="inlineStr">
         <is>
@@ -43508,7 +43522,7 @@
     </row>
     <row r="127">
       <c r="A127" s="17" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B127" s="18" t="inlineStr">
         <is>
@@ -43529,7 +43543,7 @@
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 04/08/2026</t>
+          <t>Extrato Stone — Pix de 05/08/2026</t>
         </is>
       </c>
     </row>
@@ -43547,7 +43561,7 @@
       <c r="E128" s="45" t="n"/>
       <c r="F128" s="47" t="n"/>
       <c r="G128" s="48" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H128" s="49" t="inlineStr">
         <is>
@@ -43562,7 +43576,7 @@
     </row>
     <row r="129">
       <c r="A129" s="17" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B129" s="18" t="inlineStr">
         <is>
@@ -43574,7 +43588,7 @@
       <c r="E129" s="18" t="n"/>
       <c r="F129" s="19" t="n"/>
       <c r="G129" s="19" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H129" s="21" t="inlineStr">
         <is>
@@ -43583,17 +43597,17 @@
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 05/08/2026</t>
+          <t>Extrato Stone — Pix de 10/08/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="44" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B130" s="45" t="inlineStr">
         <is>
-          <t>Estacionamento (Pagar.me)</t>
+          <t>Claudina dos Santos Morais</t>
         </is>
       </c>
       <c r="C130" s="45" t="n"/>
@@ -43601,16 +43615,16 @@
       <c r="E130" s="45" t="n"/>
       <c r="F130" s="47" t="n"/>
       <c r="G130" s="48" t="n">
-        <v>2.4</v>
+        <v>120</v>
       </c>
       <c r="H130" s="49" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I130" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 10/08/2026</t>
+          <t>Extrato Stone — Pix de 11/08/2026</t>
         </is>
       </c>
     </row>
@@ -43620,7 +43634,7 @@
       </c>
       <c r="B131" s="18" t="inlineStr">
         <is>
-          <t>Claudina dos Santos Morais</t>
+          <t>Gerlaine Vieira Santos Costa</t>
         </is>
       </c>
       <c r="C131" s="18" t="n"/>
@@ -43628,7 +43642,7 @@
       <c r="E131" s="18" t="n"/>
       <c r="F131" s="19" t="n"/>
       <c r="G131" s="19" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H131" s="21" t="inlineStr">
         <is>
@@ -43643,11 +43657,11 @@
     </row>
     <row r="132">
       <c r="A132" s="44" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B132" s="45" t="inlineStr">
         <is>
-          <t>Gerlaine Vieira Santos Costa</t>
+          <t>Malena Lorrane Santos do Nascimento</t>
         </is>
       </c>
       <c r="C132" s="45" t="n"/>
@@ -43655,7 +43669,7 @@
       <c r="E132" s="45" t="n"/>
       <c r="F132" s="47" t="n"/>
       <c r="G132" s="48" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H132" s="49" t="inlineStr">
         <is>
@@ -43664,17 +43678,17 @@
       </c>
       <c r="I132" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 11/08/2026</t>
+          <t>Extrato Stone — Pix de 12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B133" s="18" t="inlineStr">
         <is>
-          <t>Malena Lorrane Santos do Nascimento</t>
+          <t>Evanice Ferreira da Silva</t>
         </is>
       </c>
       <c r="C133" s="18" t="n"/>
@@ -43682,7 +43696,7 @@
       <c r="E133" s="18" t="n"/>
       <c r="F133" s="19" t="n"/>
       <c r="G133" s="19" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="H133" s="21" t="inlineStr">
         <is>
@@ -43691,7 +43705,7 @@
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 12/08/2026</t>
+          <t>Extrato Stone — Pix de 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -43701,7 +43715,7 @@
       </c>
       <c r="B134" s="45" t="inlineStr">
         <is>
-          <t>Evanice Ferreira da Silva</t>
+          <t>Luciana Cruz Freire Santos</t>
         </is>
       </c>
       <c r="C134" s="45" t="n"/>
@@ -43709,7 +43723,7 @@
       <c r="E134" s="45" t="n"/>
       <c r="F134" s="47" t="n"/>
       <c r="G134" s="48" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="H134" s="49" t="inlineStr">
         <is>
@@ -43724,11 +43738,11 @@
     </row>
     <row r="135">
       <c r="A135" s="17" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B135" s="18" t="inlineStr">
         <is>
-          <t>Luciana Cruz Freire Santos</t>
+          <t>Teresinha Almeida Silva Costa</t>
         </is>
       </c>
       <c r="C135" s="18" t="n"/>
@@ -43736,7 +43750,7 @@
       <c r="E135" s="18" t="n"/>
       <c r="F135" s="19" t="n"/>
       <c r="G135" s="19" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="H135" s="21" t="inlineStr">
         <is>
@@ -43745,17 +43759,17 @@
       </c>
       <c r="I135" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 13/08/2026</t>
+          <t>Extrato Stone — Pix de 15/08/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="44" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B136" s="45" t="inlineStr">
         <is>
-          <t>Teresinha Almeida Silva Costa</t>
+          <t>Daniel Barbosa dos Santos (Moto Táxi)</t>
         </is>
       </c>
       <c r="C136" s="45" t="n"/>
@@ -43763,26 +43777,26 @@
       <c r="E136" s="45" t="n"/>
       <c r="F136" s="47" t="n"/>
       <c r="G136" s="48" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H136" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I136" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 15/08/2026</t>
+          <t>Extrato Stone — Pix de 17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B137" s="18" t="inlineStr">
         <is>
-          <t>Daniel Barbosa dos Santos (Moto Táxi)</t>
+          <t>Japedido Software</t>
         </is>
       </c>
       <c r="C137" s="18" t="n"/>
@@ -43790,16 +43804,16 @@
       <c r="E137" s="18" t="n"/>
       <c r="F137" s="19" t="n"/>
       <c r="G137" s="19" t="n">
-        <v>16</v>
+        <v>49.49</v>
       </c>
       <c r="H137" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 17/08/2026</t>
+          <t>Extrato Stone — Pix de 18/08/2026</t>
         </is>
       </c>
     </row>
@@ -43809,7 +43823,7 @@
       </c>
       <c r="B138" s="45" t="inlineStr">
         <is>
-          <t>Japedido Software</t>
+          <t>L. A. Moreira Gráfica e Informática</t>
         </is>
       </c>
       <c r="C138" s="45" t="n"/>
@@ -43817,7 +43831,7 @@
       <c r="E138" s="45" t="n"/>
       <c r="F138" s="47" t="n"/>
       <c r="G138" s="48" t="n">
-        <v>49.49</v>
+        <v>18</v>
       </c>
       <c r="H138" s="49" t="inlineStr">
         <is>
@@ -43836,7 +43850,7 @@
       </c>
       <c r="B139" s="18" t="inlineStr">
         <is>
-          <t>L. A. Moreira Gráfica e Informática</t>
+          <t>Antonia Bizerra Neta</t>
         </is>
       </c>
       <c r="C139" s="18" t="n"/>
@@ -43844,7 +43858,7 @@
       <c r="E139" s="18" t="n"/>
       <c r="F139" s="19" t="n"/>
       <c r="G139" s="19" t="n">
-        <v>18</v>
+        <v>51.6</v>
       </c>
       <c r="H139" s="21" t="inlineStr">
         <is>
@@ -43859,11 +43873,11 @@
     </row>
     <row r="140">
       <c r="A140" s="44" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B140" s="45" t="inlineStr">
         <is>
-          <t>Antonia Bizerra Neta</t>
+          <t>Pampet Club</t>
         </is>
       </c>
       <c r="C140" s="45" t="n"/>
@@ -43871,7 +43885,7 @@
       <c r="E140" s="45" t="n"/>
       <c r="F140" s="47" t="n"/>
       <c r="G140" s="48" t="n">
-        <v>51.6</v>
+        <v>28</v>
       </c>
       <c r="H140" s="49" t="inlineStr">
         <is>
@@ -43880,17 +43894,17 @@
       </c>
       <c r="I140" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 18/08/2026</t>
+          <t>Extrato Stone — Pix de 19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B141" s="18" t="inlineStr">
         <is>
-          <t>Pampet Club</t>
+          <t>Laura Christina Pecanhuk Hutson Schwenker Arcara Sales</t>
         </is>
       </c>
       <c r="C141" s="18" t="n"/>
@@ -43898,7 +43912,7 @@
       <c r="E141" s="18" t="n"/>
       <c r="F141" s="19" t="n"/>
       <c r="G141" s="19" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H141" s="21" t="inlineStr">
         <is>
@@ -43907,17 +43921,17 @@
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 19/08/2026</t>
+          <t>Extrato Stone — Pix de 21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="44" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B142" s="45" t="inlineStr">
         <is>
-          <t>Laura Christina Pecanhuk Hutson Schwenker Arcara Sales</t>
+          <t>Estacionamento (Pagar.me)</t>
         </is>
       </c>
       <c r="C142" s="45" t="n"/>
@@ -43925,16 +43939,16 @@
       <c r="E142" s="45" t="n"/>
       <c r="F142" s="47" t="n"/>
       <c r="G142" s="48" t="n">
-        <v>50</v>
+        <v>2.4</v>
       </c>
       <c r="H142" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I142" s="45" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 21/08/2026</t>
+          <t>Extrato Stone — Pix de 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -43944,7 +43958,7 @@
       </c>
       <c r="B143" s="18" t="inlineStr">
         <is>
-          <t>Estacionamento (Pagar.me)</t>
+          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
         </is>
       </c>
       <c r="C143" s="18" t="n"/>
@@ -43952,11 +43966,11 @@
       <c r="E143" s="18" t="n"/>
       <c r="F143" s="19" t="n"/>
       <c r="G143" s="19" t="n">
-        <v>2.4</v>
+        <v>58.1</v>
       </c>
       <c r="H143" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I143" s="18" t="inlineStr">
@@ -43971,26 +43985,28 @@
       </c>
       <c r="B144" s="45" t="inlineStr">
         <is>
-          <t>Comercial de Estivas e Cereais Rio do Ouro</t>
-        </is>
-      </c>
-      <c r="C144" s="45" t="n"/>
-      <c r="D144" s="46" t="n"/>
-      <c r="E144" s="45" t="n"/>
-      <c r="F144" s="47" t="n"/>
-      <c r="G144" s="48" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="H144" s="49" t="inlineStr">
-        <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I144" s="45" t="inlineStr">
-        <is>
-          <t>Extrato Stone — Pix de 24/08/2026</t>
-        </is>
-      </c>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C144" s="45" t="inlineStr">
+        <is>
+          <t>Refil Universal</t>
+        </is>
+      </c>
+      <c r="D144" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="E144" s="45" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F144" s="47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G144" s="48" t="n"/>
+      <c r="H144" s="49" t="n"/>
+      <c r="I144" s="45" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="17" t="n">
@@ -43998,118 +44014,119 @@
       </c>
       <c r="B145" s="18" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
+          <t>Papelaria Castro</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>Refil Universal</t>
+          <t>Refil Pro Life + Pré Filtro</t>
         </is>
       </c>
       <c r="D145" s="27" t="n">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>Crédito à Vista</t>
-        </is>
-      </c>
-      <c r="F145" s="19" t="n">
-        <v>1.05</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F145" s="19" t="n"/>
       <c r="G145" s="19" t="n"/>
       <c r="H145" s="21" t="n"/>
       <c r="I145" s="18" t="n"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>EMP-0243</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="44" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B146" s="45" t="inlineStr">
         <is>
-          <t>Papelaria Castro</t>
+          <t>Cristiane Lima Procopio</t>
         </is>
       </c>
       <c r="C146" s="45" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Pré Filtro</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="D146" s="50" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E146" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F146" s="47" t="n"/>
       <c r="G146" s="47" t="n"/>
       <c r="H146" s="49" t="n"/>
-      <c r="I146" s="45" t="n"/>
+      <c r="I146" s="45" t="inlineStr">
+        <is>
+          <t>Venda de 24/08/2026 — pagamento recebido via Pix em 25/08/2026</t>
+        </is>
+      </c>
       <c r="J146" s="45" t="inlineStr">
         <is>
-          <t>EMP-0243</t>
+          <t>CLI-0471</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B147" s="18" t="inlineStr">
         <is>
-          <t>Cristiane Lima Procopio</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D147" s="134" t="n">
-        <v>200</v>
-      </c>
-      <c r="E147" s="18" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>ICMS Antecipação Parcial</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="n"/>
+      <c r="D147" s="134" t="n"/>
+      <c r="E147" s="18" t="n"/>
       <c r="F147" s="19" t="n"/>
-      <c r="G147" s="20" t="n"/>
-      <c r="H147" s="21" t="n"/>
-      <c r="I147" s="18" t="inlineStr">
-        <is>
-          <t>Venda de 24/08/2026 — pagamento recebido via Pix em 25/08/2026</t>
-        </is>
-      </c>
-      <c r="J147" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0471</t>
-        </is>
-      </c>
+      <c r="G147" s="20" t="n">
+        <v>2135.72</v>
+      </c>
+      <c r="H147" s="21" t="inlineStr">
+        <is>
+          <t>Impostos e Taxas</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="n"/>
+      <c r="J147" s="18" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="44" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B148" s="45" t="inlineStr">
         <is>
-          <t>ICMS Antecipação Parcial</t>
-        </is>
-      </c>
-      <c r="C148" s="45" t="n"/>
-      <c r="D148" s="50" t="n"/>
-      <c r="E148" s="45" t="n"/>
-      <c r="F148" s="47" t="n"/>
-      <c r="G148" s="47" t="n">
-        <v>2135.72</v>
-      </c>
-      <c r="H148" s="49" t="inlineStr">
-        <is>
-          <t>Impostos e Taxas</t>
-        </is>
-      </c>
+          <t>Clinica Sao Lucas (Caém)</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>Refil Pro Life + Mangueira</t>
+        </is>
+      </c>
+      <c r="D148" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="E148" s="45" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F148" s="47" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G148" s="47" t="n"/>
+      <c r="H148" s="49" t="n"/>
       <c r="I148" s="45" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="157">
@@ -44118,16 +44135,16 @@
       </c>
       <c r="B149" s="18" t="inlineStr">
         <is>
-          <t>Clinica Sao Lucas (Caém)</t>
+          <t>Luciano de Matos Nascimento</t>
         </is>
       </c>
       <c r="C149" s="18" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Mangueira</t>
+          <t>Purificador Everest Star Prata</t>
         </is>
       </c>
       <c r="D149" s="134" t="n">
-        <v>130</v>
+        <v>1486</v>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
@@ -44135,11 +44152,20 @@
         </is>
       </c>
       <c r="F149" s="19" t="n">
-        <v>9.09</v>
+        <v>207.89</v>
       </c>
       <c r="G149" s="20" t="n"/>
       <c r="H149" s="21" t="n"/>
-      <c r="I149" s="18" t="n"/>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 10x</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>CLI-0886</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="44" t="n">
@@ -44147,37 +44173,27 @@
       </c>
       <c r="B150" s="45" t="inlineStr">
         <is>
-          <t>Luciano de Matos Nascimento</t>
-        </is>
-      </c>
-      <c r="C150" s="45" t="inlineStr">
-        <is>
-          <t>Purificador Everest Star Prata</t>
-        </is>
-      </c>
-      <c r="D150" s="50" t="n">
-        <v>1486</v>
-      </c>
-      <c r="E150" s="45" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F150" s="47" t="n">
-        <v>207.89</v>
-      </c>
-      <c r="G150" s="47" t="n"/>
-      <c r="H150" s="49" t="n"/>
+          <t>Filtros Planeta Água</t>
+        </is>
+      </c>
+      <c r="C150" s="45" t="n"/>
+      <c r="D150" s="50" t="n"/>
+      <c r="E150" s="45" t="n"/>
+      <c r="F150" s="47" t="n"/>
+      <c r="G150" s="47" t="n">
+        <v>504.34</v>
+      </c>
+      <c r="H150" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
       <c r="I150" s="45" t="inlineStr">
         <is>
-          <t>Crédito em 10x</t>
-        </is>
-      </c>
-      <c r="J150" s="45" t="inlineStr">
-        <is>
-          <t>CLI-0886</t>
-        </is>
-      </c>
+          <t>NF 131442 de 17/06/2026 · parcela 4/4 (venc. 26/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
+        </is>
+      </c>
+      <c r="J150" s="45" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="17" t="n">
@@ -44185,7 +44201,7 @@
       </c>
       <c r="B151" s="18" t="inlineStr">
         <is>
-          <t>Filtros Planeta Água</t>
+          <t>Fix English School</t>
         </is>
       </c>
       <c r="C151" s="18" t="n"/>
@@ -44193,26 +44209,22 @@
       <c r="E151" s="18" t="n"/>
       <c r="F151" s="19" t="n"/>
       <c r="G151" s="20" t="n">
-        <v>504.34</v>
+        <v>137</v>
       </c>
       <c r="H151" s="21" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I151" s="18" t="inlineStr">
-        <is>
-          <t>NF 131442 de 17/06/2026 · parcela 4/4 (venc. 26/08/2026) · compra total R$ 2.122,28 (IPI R$ 104,91): 25x Refil Pro Life + 5x Refil Fit Poe Pp 9.3/4 + 10x Refil Bebedouro B A G + 8x Refil Carbon Tech 5 Pol + 10x Refil Carbon Tech 9.3/4 Pol + 2x Refil Pa 230 Fit + 4x Refil Fpa16</t>
-        </is>
-      </c>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="44" t="n">
-        <v>46259</v>
+        <v>46251</v>
       </c>
       <c r="B152" s="45" t="inlineStr">
         <is>
-          <t>Fix English School</t>
+          <t>Retirada Complementar — Despesas de 17/08</t>
         </is>
       </c>
       <c r="C152" s="45" t="n"/>
@@ -44220,41 +44232,45 @@
       <c r="E152" s="45" t="n"/>
       <c r="F152" s="47" t="n"/>
       <c r="G152" s="47" t="n">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="H152" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
-        </is>
-      </c>
-      <c r="I152" s="45" t="n"/>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="I152" s="45" t="inlineStr">
+        <is>
+          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B153" s="18" t="inlineStr">
         <is>
-          <t>Retirada Complementar — Despesas de 17/08</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="n"/>
-      <c r="D153" s="134" t="n"/>
-      <c r="E153" s="18" t="n"/>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>Refil Carbon Tech 9"</t>
+        </is>
+      </c>
+      <c r="D153" s="134" t="n">
+        <v>80</v>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F153" s="19" t="n"/>
-      <c r="G153" s="20" t="n">
-        <v>250</v>
-      </c>
-      <c r="H153" s="21" t="inlineStr">
-        <is>
-          <t>Outras Despesas</t>
-        </is>
-      </c>
-      <c r="I153" s="18" t="inlineStr">
-        <is>
-          <t>Financiado por Capital de Giro (BB) — ver aba "Capital de Giro (BB)"</t>
-        </is>
-      </c>
+      <c r="G153" s="20" t="n"/>
+      <c r="H153" s="21" t="n"/>
+      <c r="I153" s="18" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="44" t="n">
@@ -44262,43 +44278,48 @@
       </c>
       <c r="B154" s="45" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
+          <t>Luana Mesquita Victoria</t>
         </is>
       </c>
       <c r="C154" s="45" t="inlineStr">
         <is>
-          <t>Refil Carbon Tech 9"</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="D154" s="50" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E154" s="45" t="inlineStr">
         <is>
-          <t>Dinheiro</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F154" s="47" t="n"/>
       <c r="G154" s="47" t="n"/>
       <c r="H154" s="49" t="n"/>
       <c r="I154" s="45" t="n"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>CLI-0887</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="17" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B155" s="18" t="inlineStr">
         <is>
-          <t>Luana Mesquita Victoria</t>
+          <t>Cícero Lima</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
         <is>
-          <t>Pré Filtro</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="D155" s="134" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
@@ -44311,26 +44332,26 @@
       <c r="I155" s="18" t="n"/>
       <c r="J155" s="18" t="inlineStr">
         <is>
-          <t>CLI-0887</t>
+          <t>CLI-0738</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="44" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B156" s="45" t="inlineStr">
         <is>
-          <t>Cícero Lima</t>
+          <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
       <c r="C156" s="45" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
       <c r="D156" s="50" t="n">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="E156" s="45" t="inlineStr">
         <is>
@@ -44340,12 +44361,12 @@
       <c r="F156" s="47" t="n"/>
       <c r="G156" s="47" t="n"/>
       <c r="H156" s="49" t="n"/>
-      <c r="I156" s="45" t="n"/>
-      <c r="J156" s="45" t="inlineStr">
-        <is>
-          <t>CLI-0738</t>
-        </is>
-      </c>
+      <c r="I156" s="45" t="inlineStr">
+        <is>
+          <t>Venda única de R$ 470,00 (27/08/2026), paga em 28/08/2026 em duas formas: R$ 270,00 Pix (esta linha) + R$ 200,00 crédito 2x (linha seguinte). Os produtos estão listados só aqui.</t>
+        </is>
+      </c>
+      <c r="J156" s="45" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="n">
@@ -44358,58 +44379,50 @@
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
+          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
         </is>
       </c>
       <c r="D157" s="134" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F157" s="19" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F157" s="19" t="n">
+        <v>16.76</v>
+      </c>
       <c r="G157" s="20" t="n"/>
       <c r="H157" s="21" t="n"/>
       <c r="I157" s="18" t="inlineStr">
         <is>
-          <t>Venda única de R$ 470,00 (27/08/2026), paga em 28/08/2026 em duas formas: R$ 270,00 Pix (esta linha) + R$ 200,00 crédito 2x (linha seguinte). Os produtos estão listados só aqui.</t>
+          <t>Parte 2/2 da venda de R$ 470,00 da Promotoria Regional de Jacobina — R$ 200,00 no crédito 2x. NÃO é uma venda nova; os itens já constam na linha anterior.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="44" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B158" s="45" t="inlineStr">
         <is>
-          <t>Promotoria Regional de Jacobina</t>
-        </is>
-      </c>
-      <c r="C158" s="45" t="inlineStr">
-        <is>
-          <t>(Mesma venda acima — 2ª forma de pagamento, sem produtos novos)</t>
-        </is>
-      </c>
+          <t>Acerto de Armando</t>
+        </is>
+      </c>
+      <c r="C158" s="45" t="n"/>
       <c r="D158" s="50" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E158" s="45" t="inlineStr">
         <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F158" s="47" t="n">
-        <v>16.76</v>
-      </c>
+          <t>Dinheiro</t>
+        </is>
+      </c>
+      <c r="F158" s="47" t="n"/>
       <c r="G158" s="47" t="n"/>
       <c r="H158" s="49" t="n"/>
-      <c r="I158" s="45" t="inlineStr">
-        <is>
-          <t>Parte 2/2 da venda de R$ 470,00 da Promotoria Regional de Jacobina — R$ 200,00 no crédito 2x. NÃO é uma venda nova; os itens já constam na linha anterior.</t>
-        </is>
-      </c>
+      <c r="I158" s="45" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="17" t="n">
@@ -44417,22 +44430,26 @@
       </c>
       <c r="B159" s="18" t="inlineStr">
         <is>
-          <t>Acerto de Armando</t>
+          <t>A E G Calçados LTDA</t>
         </is>
       </c>
       <c r="C159" s="18" t="n"/>
-      <c r="D159" s="134" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E159" s="18" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+      <c r="D159" s="134" t="n"/>
+      <c r="E159" s="18" t="n"/>
       <c r="F159" s="19" t="n"/>
-      <c r="G159" s="20" t="n"/>
-      <c r="H159" s="21" t="n"/>
-      <c r="I159" s="18" t="n"/>
+      <c r="G159" s="20" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="H159" s="21" t="inlineStr">
+        <is>
+          <t>Pro Labore Edilânia</t>
+        </is>
+      </c>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>Extrato Stone — Pix de 27/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="44" t="n">
@@ -44440,7 +44457,7 @@
       </c>
       <c r="B160" s="45" t="inlineStr">
         <is>
-          <t>A E G Calçados LTDA</t>
+          <t>Queite Almeida Duarte</t>
         </is>
       </c>
       <c r="C160" s="45" t="n"/>
@@ -44448,7 +44465,7 @@
       <c r="E160" s="45" t="n"/>
       <c r="F160" s="47" t="n"/>
       <c r="G160" s="47" t="n">
-        <v>127.42</v>
+        <v>100</v>
       </c>
       <c r="H160" s="49" t="inlineStr">
         <is>
@@ -44463,11 +44480,11 @@
     </row>
     <row r="161">
       <c r="A161" s="17" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B161" s="18" t="inlineStr">
         <is>
-          <t>Queite Almeida Duarte</t>
+          <t>Edilania Almeida Silva Costa Fontes</t>
         </is>
       </c>
       <c r="C161" s="18" t="n"/>
@@ -44475,7 +44492,7 @@
       <c r="E161" s="18" t="n"/>
       <c r="F161" s="19" t="n"/>
       <c r="G161" s="20" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="H161" s="21" t="inlineStr">
         <is>
@@ -44484,7 +44501,7 @@
       </c>
       <c r="I161" s="18" t="inlineStr">
         <is>
-          <t>Extrato Stone — Pix de 27/08/2026</t>
+          <t>Extrato Stone — Pix de 26/08/2026</t>
         </is>
       </c>
     </row>
@@ -44494,7 +44511,7 @@
       </c>
       <c r="B162" s="45" t="inlineStr">
         <is>
-          <t>Edilania Almeida Silva Costa Fontes</t>
+          <t>Estacionamento (Pagar.me)</t>
         </is>
       </c>
       <c r="C162" s="45" t="n"/>
@@ -44502,11 +44519,11 @@
       <c r="E162" s="45" t="n"/>
       <c r="F162" s="47" t="n"/>
       <c r="G162" s="47" t="n">
-        <v>230</v>
+        <v>1.2</v>
       </c>
       <c r="H162" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I162" s="45" t="inlineStr">
@@ -44517,11 +44534,11 @@
     </row>
     <row r="163">
       <c r="A163" s="17" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B163" s="18" t="inlineStr">
         <is>
-          <t>Estacionamento (Pagar.me)</t>
+          <t>4x Parafuso</t>
         </is>
       </c>
       <c r="C163" s="18" t="n"/>
@@ -44529,18 +44546,14 @@
       <c r="E163" s="18" t="n"/>
       <c r="F163" s="19" t="n"/>
       <c r="G163" s="20" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="H163" s="21" t="inlineStr">
         <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I163" s="18" t="inlineStr">
-        <is>
-          <t>Extrato Stone — Pix de 26/08/2026</t>
-        </is>
-      </c>
+          <t>Manutenção e Reparos</t>
+        </is>
+      </c>
+      <c r="I163" s="18" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="44" t="n">
@@ -44548,22 +44561,30 @@
       </c>
       <c r="B164" s="45" t="inlineStr">
         <is>
-          <t>4x Parafuso</t>
-        </is>
-      </c>
-      <c r="C164" s="45" t="n"/>
-      <c r="D164" s="46" t="n"/>
-      <c r="E164" s="45" t="n"/>
+          <t>FG Boa Vista (Recife/PE)</t>
+        </is>
+      </c>
+      <c r="C164" s="45" t="inlineStr">
+        <is>
+          <t>Refis — troca de julho/2026</t>
+        </is>
+      </c>
+      <c r="D164" s="46" t="n">
+        <v>1008.8</v>
+      </c>
+      <c r="E164" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F164" s="47" t="n"/>
-      <c r="G164" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="H164" s="49" t="inlineStr">
-        <is>
-          <t>Manutenção e Reparos</t>
-        </is>
-      </c>
-      <c r="I164" s="45" t="n"/>
+      <c r="G164" s="48" t="n"/>
+      <c r="H164" s="49" t="n"/>
+      <c r="I164" s="45" t="inlineStr">
+        <is>
+          <t>Grupo Ânima — OC SOCECPO00006537 · NF 000.004.280 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026. OC lista R$ 1.040,00 sem aplicar o desconto de 3%; Lorena confirmou que não há problema. · Pago em 27/08/2026 (confirmado via Pix SOCEC no extrato bancário)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="17" t="n">
@@ -44571,7 +44592,7 @@
       </c>
       <c r="B165" s="18" t="inlineStr">
         <is>
-          <t>FG Boa Vista (Recife/PE)</t>
+          <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
@@ -44580,7 +44601,7 @@
         </is>
       </c>
       <c r="D165" s="27" t="n">
-        <v>1008.8</v>
+        <v>4534.75</v>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
@@ -44592,7 +44613,7 @@
       <c r="H165" s="21" t="n"/>
       <c r="I165" s="18" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC SOCECPO00006537 · NF 000.004.280 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026. OC lista R$ 1.040,00 sem aplicar o desconto de 3%; Lorena confirmou que não há problema. · Pago em 27/08/2026 (confirmado via Pix SOCEC no extrato bancário)</t>
+          <t>Grupo Ânima — OC CESGPO00006036 · NF 000.004.281 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 (desc. 3%) · Pago em 27/08/2026 (confirmado via Pix CESG no extrato bancário)</t>
         </is>
       </c>
       <c r="K165" s="13" t="n"/>
@@ -44604,7 +44625,7 @@
       </c>
       <c r="B166" s="45" t="inlineStr">
         <is>
-          <t>UNIFG Guanambi (Guanambi/BA)</t>
+          <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
       <c r="C166" s="45" t="inlineStr">
@@ -44613,7 +44634,7 @@
         </is>
       </c>
       <c r="D166" s="46" t="n">
-        <v>4534.75</v>
+        <v>870</v>
       </c>
       <c r="E166" s="45" t="inlineStr">
         <is>
@@ -44625,7 +44646,7 @@
       <c r="H166" s="49" t="n"/>
       <c r="I166" s="45" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC CESGPO00006036 · NF 000.004.281 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 (desc. 3%) · Pago em 27/08/2026 (confirmado via Pix CESG no extrato bancário)</t>
+          <t>Grupo Ânima — OC APECPO00019432 · NF 000.004.282 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 · Pago em 27/08/2026 (confirmado via Pix APEC no extrato bancário)</t>
         </is>
       </c>
       <c r="K166" s="42" t="n"/>
@@ -44633,11 +44654,11 @@
     </row>
     <row r="167">
       <c r="A167" s="17" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B167" s="18" t="inlineStr">
         <is>
-          <t>UNP Zona Norte (Natal/RN)</t>
+          <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
       <c r="C167" s="18" t="inlineStr">
@@ -44646,7 +44667,7 @@
         </is>
       </c>
       <c r="D167" s="27" t="n">
-        <v>870</v>
+        <v>440</v>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
@@ -44658,7 +44679,7 @@
       <c r="H167" s="21" t="n"/>
       <c r="I167" s="18" t="inlineStr">
         <is>
-          <t>Grupo Ânima — OC APECPO00019432 · NF 000.004.282 de 28/07/2026 · prazo 30 dias · vencimento 27/08/2026 · Pago em 27/08/2026 (confirmado via Pix APEC no extrato bancário)</t>
+          <t>Grupo Ânima — OC APECPO00019405 · NF 000.004.283 de 28/07/2026 · pago via Pix pela APEC em 27/08/2026 (após o fechamento do relatório do dia)</t>
         </is>
       </c>
       <c r="K167" s="31" t="n"/>
@@ -44670,55 +44691,56 @@
       </c>
       <c r="B168" s="45" t="inlineStr">
         <is>
-          <t>UNP Caicó (Caicó/RN)</t>
-        </is>
-      </c>
-      <c r="C168" s="45" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="D168" s="46" t="n">
-        <v>440</v>
-      </c>
-      <c r="E168" s="45" t="inlineStr">
-        <is>
-          <t>Pix</t>
-        </is>
-      </c>
+          <t>Produtos de Higiene</t>
+        </is>
+      </c>
+      <c r="C168" s="45" t="n"/>
+      <c r="D168" s="46" t="n"/>
+      <c r="E168" s="45" t="n"/>
       <c r="F168" s="47" t="n"/>
-      <c r="G168" s="48" t="n"/>
-      <c r="H168" s="49" t="n"/>
-      <c r="I168" s="45" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — OC APECPO00019405 · NF 000.004.283 de 28/07/2026 · pago via Pix pela APEC em 27/08/2026 (após o fechamento do relatório do dia)</t>
-        </is>
-      </c>
+      <c r="G168" s="48" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H168" s="49" t="inlineStr">
+        <is>
+          <t>Material de Limpeza e Escritório</t>
+        </is>
+      </c>
+      <c r="I168" s="45" t="n"/>
       <c r="K168" s="31" t="n"/>
       <c r="L168" s="31" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="17" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B169" s="18" t="inlineStr">
         <is>
-          <t>Produtos de Higiene</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="27" t="n"/>
-      <c r="E169" s="18" t="n"/>
+          <t>Katiane</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D169" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F169" s="19" t="n"/>
-      <c r="G169" s="19" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H169" s="21" t="inlineStr">
-        <is>
-          <t>Material de Limpeza e Escritório</t>
-        </is>
-      </c>
+      <c r="G169" s="19" t="n"/>
+      <c r="H169" s="21" t="n"/>
       <c r="I169" s="18" t="n"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>CLI-0449</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="44" t="n">
@@ -44726,31 +44748,27 @@
       </c>
       <c r="B170" s="45" t="inlineStr">
         <is>
-          <t>Katiane</t>
-        </is>
-      </c>
-      <c r="C170" s="45" t="inlineStr">
-        <is>
-          <t>Refil Everest + Mangueira</t>
-        </is>
-      </c>
-      <c r="D170" s="46" t="n">
-        <v>150</v>
-      </c>
-      <c r="E170" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Eversoft</t>
+        </is>
+      </c>
+      <c r="C170" s="45" t="n"/>
+      <c r="D170" s="46" t="n"/>
+      <c r="E170" s="45" t="n"/>
       <c r="F170" s="47" t="n"/>
-      <c r="G170" s="48" t="n"/>
-      <c r="H170" s="49" t="n"/>
-      <c r="I170" s="45" t="n"/>
-      <c r="J170" s="45" t="inlineStr">
-        <is>
-          <t>CLI-0449</t>
-        </is>
-      </c>
+      <c r="G170" s="48" t="n">
+        <v>878.9299999999999</v>
+      </c>
+      <c r="H170" s="49" t="inlineStr">
+        <is>
+          <t>Fornecedores / Mercadoria</t>
+        </is>
+      </c>
+      <c r="I170" s="45" t="inlineStr">
+        <is>
+          <t>NF 72153 de 02/04/2026 · parcela 5/5 (venc. 30/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
+        </is>
+      </c>
+      <c r="J170" s="45" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="17" t="n">
@@ -44758,26 +44776,26 @@
       </c>
       <c r="B171" s="18" t="inlineStr">
         <is>
-          <t>Eversoft</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="n"/>
-      <c r="D171" s="27" t="n"/>
-      <c r="E171" s="18" t="n"/>
+          <t>Cliente Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>Refil E3</t>
+        </is>
+      </c>
+      <c r="D171" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>Dinheiro</t>
+        </is>
+      </c>
       <c r="F171" s="19" t="n"/>
-      <c r="G171" s="19" t="n">
-        <v>878.9299999999999</v>
-      </c>
-      <c r="H171" s="21" t="inlineStr">
-        <is>
-          <t>Fornecedores / Mercadoria</t>
-        </is>
-      </c>
-      <c r="I171" s="18" t="inlineStr">
-        <is>
-          <t>NF 72153 de 02/04/2026 · parcela 5/5 (venc. 30/08/2026) · compra total R$ 4.394,61: 100x Refil Everest</t>
-        </is>
-      </c>
+      <c r="G171" s="19" t="n"/>
+      <c r="H171" s="21" t="n"/>
+      <c r="I171" s="18" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="44" t="n">
@@ -44785,25 +44803,21 @@
       </c>
       <c r="B172" s="45" t="inlineStr">
         <is>
-          <t>Cliente Consumidor Final</t>
-        </is>
-      </c>
-      <c r="C172" s="45" t="inlineStr">
-        <is>
-          <t>Refil E3</t>
-        </is>
-      </c>
-      <c r="D172" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="E172" s="45" t="inlineStr">
-        <is>
-          <t>Dinheiro</t>
-        </is>
-      </c>
+          <t>Salário Erick (Estagiário)</t>
+        </is>
+      </c>
+      <c r="C172" s="45" t="n"/>
+      <c r="D172" s="46" t="n"/>
+      <c r="E172" s="45" t="n"/>
       <c r="F172" s="47" t="n"/>
-      <c r="G172" s="48" t="n"/>
-      <c r="H172" s="49" t="n"/>
+      <c r="G172" s="48" t="n">
+        <v>600</v>
+      </c>
+      <c r="H172" s="49" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
       <c r="I172" s="45" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="157">
@@ -44812,21 +44826,25 @@
       </c>
       <c r="B173" s="18" t="inlineStr">
         <is>
-          <t>Salário Erick (Estagiário)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="n"/>
-      <c r="D173" s="27" t="n"/>
-      <c r="E173" s="18" t="n"/>
+          <t>Marcelo Pioverzan Pinheiro</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>Bebedouro Industrial 50L + Engate</t>
+        </is>
+      </c>
+      <c r="D173" s="27" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F173" s="19" t="n"/>
-      <c r="G173" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="H173" s="21" t="inlineStr">
-        <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
+      <c r="G173" s="19" t="n"/>
+      <c r="H173" s="21" t="n"/>
       <c r="I173" s="18" t="n"/>
     </row>
     <row r="174">
@@ -44835,26 +44853,37 @@
       </c>
       <c r="B174" s="45" t="inlineStr">
         <is>
-          <t>Marcelo Pioverzan Pinheiro</t>
+          <t>Raiane Melo do Rosario</t>
         </is>
       </c>
       <c r="C174" s="45" t="inlineStr">
         <is>
-          <t>Bebedouro Industrial 50L + Engate</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="D174" s="50" t="n">
-        <v>2020</v>
+        <v>200</v>
       </c>
       <c r="E174" s="45" t="inlineStr">
         <is>
-          <t>Pix</t>
-        </is>
-      </c>
-      <c r="F174" s="47" t="n"/>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F174" s="47" t="n">
+        <v>15.98</v>
+      </c>
       <c r="G174" s="47" t="n"/>
       <c r="H174" s="49" t="n"/>
-      <c r="I174" s="45" t="n"/>
+      <c r="I174" s="45" t="inlineStr">
+        <is>
+          <t>Crédito em 4x</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>CLI-0405</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="17" t="n">
@@ -44862,37 +44891,23 @@
       </c>
       <c r="B175" s="18" t="inlineStr">
         <is>
-          <t>Raiane Melo do Rosario</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="D175" s="134" t="n">
-        <v>200</v>
-      </c>
-      <c r="E175" s="18" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F175" s="19" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="G175" s="20" t="n"/>
-      <c r="H175" s="21" t="n"/>
-      <c r="I175" s="18" t="inlineStr">
-        <is>
-          <t>Crédito em 4x</t>
-        </is>
-      </c>
-      <c r="J175" s="18" t="inlineStr">
-        <is>
-          <t>CLI-0405</t>
-        </is>
-      </c>
+          <t>Salário Wiliam</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="n"/>
+      <c r="D175" s="134" t="n"/>
+      <c r="E175" s="18" t="n"/>
+      <c r="F175" s="19" t="n"/>
+      <c r="G175" s="20" t="n">
+        <v>1571.32</v>
+      </c>
+      <c r="H175" s="21" t="inlineStr">
+        <is>
+          <t>Salários, Comissões e Encargos</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="n"/>
+      <c r="J175" s="18" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="157">
       <c r="A176" s="44" t="n">
@@ -44900,7 +44915,7 @@
       </c>
       <c r="B176" s="45" t="inlineStr">
         <is>
-          <t>Salário Wiliam</t>
+          <t>Tarifa Pix (14 lançamentos)</t>
         </is>
       </c>
       <c r="C176" s="45" t="n"/>
@@ -44908,14 +44923,18 @@
       <c r="E176" s="45" t="n"/>
       <c r="F176" s="47" t="n"/>
       <c r="G176" s="47" t="n">
-        <v>1571.32</v>
+        <v>48.25</v>
       </c>
       <c r="H176" s="49" t="inlineStr">
         <is>
-          <t>Salários, Comissões e Encargos</t>
-        </is>
-      </c>
-      <c r="I176" s="45" t="n"/>
+          <t>Tarifas Bancárias e Cartão</t>
+        </is>
+      </c>
+      <c r="I176" s="45" t="inlineStr">
+        <is>
+          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="17" t="n">
@@ -44923,7 +44942,7 @@
       </c>
       <c r="B177" s="18" t="inlineStr">
         <is>
-          <t>Tarifa Pix (14 lançamentos)</t>
+          <t>Pix Pessoal (4 lançamentos)</t>
         </is>
       </c>
       <c r="C177" s="18" t="n"/>
@@ -44931,16 +44950,16 @@
       <c r="E177" s="18" t="n"/>
       <c r="F177" s="19" t="n"/>
       <c r="G177" s="20" t="n">
-        <v>48.25</v>
+        <v>221.5</v>
       </c>
       <c r="H177" s="21" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias e Cartão</t>
+          <t>Pro Labore Edilânia</t>
         </is>
       </c>
       <c r="I177" s="18" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 14 tarifas Pix individuais</t>
+          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
         </is>
       </c>
     </row>
@@ -44950,7 +44969,7 @@
       </c>
       <c r="B178" s="45" t="inlineStr">
         <is>
-          <t>Pix Pessoal (4 lançamentos)</t>
+          <t>Compras p/Loja (2 lançamentos)</t>
         </is>
       </c>
       <c r="C178" s="45" t="n"/>
@@ -44958,16 +44977,16 @@
       <c r="E178" s="45" t="n"/>
       <c r="F178" s="47" t="n"/>
       <c r="G178" s="47" t="n">
-        <v>221.5</v>
+        <v>131.29</v>
       </c>
       <c r="H178" s="49" t="inlineStr">
         <is>
-          <t>Pro Labore Edilânia</t>
+          <t>Fornecedores / Mercadoria</t>
         </is>
       </c>
       <c r="I178" s="45" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 4 Pix pessoais de Adriano/Edilânia</t>
+          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
         </is>
       </c>
     </row>
@@ -44977,7 +44996,7 @@
       </c>
       <c r="B179" s="18" t="inlineStr">
         <is>
-          <t>Compras p/Loja (2 lançamentos)</t>
+          <t>Estacionamento (2 lançamentos)</t>
         </is>
       </c>
       <c r="C179" s="18" t="n"/>
@@ -44985,16 +45004,16 @@
       <c r="E179" s="18" t="n"/>
       <c r="F179" s="19" t="n"/>
       <c r="G179" s="20" t="n">
-        <v>131.29</v>
+        <v>6</v>
       </c>
       <c r="H179" s="21" t="inlineStr">
         <is>
-          <t>Fornecedores / Mercadoria</t>
+          <t>Transporte e Entregas</t>
         </is>
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 compras para a loja</t>
+          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
         </is>
       </c>
     </row>
@@ -45004,7 +45023,7 @@
       </c>
       <c r="B180" s="45" t="inlineStr">
         <is>
-          <t>Estacionamento (2 lançamentos)</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="C180" s="45" t="n"/>
@@ -45012,45 +45031,47 @@
       <c r="E180" s="45" t="n"/>
       <c r="F180" s="47" t="n"/>
       <c r="G180" s="47" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H180" s="49" t="inlineStr">
         <is>
           <t>Transporte e Entregas</t>
         </is>
       </c>
-      <c r="I180" s="45" t="inlineStr">
-        <is>
-          <t>Extrato BNB agosto/2026 — soma de 2 lançamentos de estacionamento</t>
-        </is>
-      </c>
+      <c r="I180" s="45" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="17" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B181" s="18" t="inlineStr">
         <is>
-          <t>Gasolina</t>
+          <t>Cliente de Armando</t>
         </is>
       </c>
       <c r="C181" s="18" t="n"/>
-      <c r="D181" s="134" t="n"/>
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="19" t="n"/>
-      <c r="G181" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="H181" s="21" t="inlineStr">
-        <is>
-          <t>Transporte e Entregas</t>
-        </is>
-      </c>
-      <c r="I181" s="18" t="n"/>
+      <c r="D181" s="134" t="n">
+        <v>160</v>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
+        <is>
+          <t>Crédito Parcelado</t>
+        </is>
+      </c>
+      <c r="F181" s="19" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="G181" s="20" t="n"/>
+      <c r="H181" s="21" t="n"/>
+      <c r="I181" s="18" t="inlineStr">
+        <is>
+          <t>Crédito em 3x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="44" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B182" s="45" t="inlineStr">
         <is>
@@ -45059,7 +45080,7 @@
       </c>
       <c r="C182" s="45" t="n"/>
       <c r="D182" s="50" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E182" s="45" t="inlineStr">
         <is>
@@ -45067,44 +45088,26 @@
         </is>
       </c>
       <c r="F182" s="47" t="n">
-        <v>11.18</v>
+        <v>13.98</v>
       </c>
       <c r="G182" s="47" t="n"/>
       <c r="H182" s="49" t="n"/>
       <c r="I182" s="45" t="inlineStr">
         <is>
-          <t>Crédito em 3x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
+          <t>Crédito em 2x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="17" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B183" s="18" t="inlineStr">
-        <is>
-          <t>Cliente de Armando</t>
-        </is>
-      </c>
+      <c r="A183" s="17" t="n"/>
+      <c r="B183" s="18" t="n"/>
       <c r="C183" s="18" t="n"/>
-      <c r="D183" s="134" t="n">
-        <v>200</v>
-      </c>
-      <c r="E183" s="18" t="inlineStr">
-        <is>
-          <t>Crédito Parcelado</t>
-        </is>
-      </c>
-      <c r="F183" s="19" t="n">
-        <v>13.98</v>
-      </c>
+      <c r="D183" s="134" t="n"/>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="19" t="n"/>
       <c r="G183" s="20" t="n"/>
       <c r="H183" s="21" t="n"/>
-      <c r="I183" s="18" t="inlineStr">
-        <is>
-          <t>Crédito em 2x. Venda do relatório de prestação de contas do Armando (14/09/2026) — lançada em 21/09/2026.</t>
-        </is>
-      </c>
+      <c r="I183" s="18" t="n"/>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="157">
       <c r="A184" s="44" t="n"/>
@@ -56193,7 +56196,7 @@
     </row>
     <row r="102">
       <c r="A102" s="44" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="B102" s="45" t="inlineStr">
         <is>
@@ -56210,13 +56213,17 @@
       </c>
       <c r="E102" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="F102" s="47" t="n"/>
       <c r="G102" s="48" t="n"/>
       <c r="H102" s="49" t="n"/>
-      <c r="I102" s="45" t="n"/>
+      <c r="I102" s="45" t="inlineStr">
+        <is>
+          <t>Venda de 15/10/2026 — pagamento recebido em 21/10/2026</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>EMP-0320</t>
@@ -56628,7 +56635,7 @@
     </row>
     <row r="116">
       <c r="A116" s="44" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="B116" s="45" t="inlineStr">
         <is>
@@ -56645,7 +56652,7 @@
       </c>
       <c r="E116" s="45" t="inlineStr">
         <is>
-          <t>Aguardando Pagamento</t>
+          <t>Dinheiro</t>
         </is>
       </c>
       <c r="F116" s="47" t="n"/>
@@ -56653,7 +56660,7 @@
       <c r="H116" s="49" t="n"/>
       <c r="I116" s="45" t="inlineStr">
         <is>
-          <t>Restante da venda de R$ 200,00 (R$ 140,00 pagos em dinheiro). Cliente vai pagar depois.</t>
+          <t>Venda de 16/10/2026 — pagamento recebido em dinheiro em 20/10/2026. Restante da venda de R$ 200,00 (R$ 140,00 pagos em dinheiro no dia 16/10).</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -57994,7 +58001,7 @@
     </row>
     <row r="160">
       <c r="A160" s="44" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B160" s="45" t="inlineStr">
         <is>
@@ -58015,7 +58022,7 @@
       </c>
       <c r="I160" s="45" t="inlineStr">
         <is>
-          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Boleto doc. 133138/4 (emissão 12/08/2026) · parcela 4/4 (última) — venc. 21/10/2026. Pago em 21/10/2026.</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Boleto doc. 133138/4 (emissão 12/08/2026) · parcela 4/4 (última) — venc. 21/10/2026. Pago antecipado em 20/10/2026.</t>
         </is>
       </c>
     </row>
@@ -58075,16 +58082,40 @@
       <c r="I162" s="45" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="17" t="n"/>
-      <c r="B163" s="18" t="n"/>
-      <c r="C163" s="18" t="n"/>
-      <c r="D163" s="27" t="n"/>
-      <c r="E163" s="18" t="n"/>
+      <c r="A163" s="17" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t>Supermercado Brasil</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>2x Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="D163" s="27" t="n">
+        <v>280</v>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F163" s="19" t="n"/>
       <c r="G163" s="19" t="n"/>
       <c r="H163" s="21" t="n"/>
-      <c r="I163" s="18" t="n"/>
-      <c r="J163" s="18" t="n"/>
+      <c r="I163" s="18" t="inlineStr">
+        <is>
+          <t>Venda de 05/08/2026 — pagamento recebido em 22/10/2026 via Pix</t>
+        </is>
+      </c>
+      <c r="J163" s="18" t="inlineStr">
+        <is>
+          <t>EMP-0261</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="44" t="n"/>
@@ -69290,7 +69321,7 @@
       </c>
       <c r="G59" s="78" t="inlineStr">
         <is>
-          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397. Pago em 21/10/2026 — lançado em "Out 2026" como "Filtros Planeta Água".</t>
+          <t>Comprado: 10x Refil Fit PP 9.3/4" + 5x Refil Universal Rosca Curta + 5x Refil Universal Rosca Longa + 5x Refil Universal Rosca Média + 5x Refil Top Color + 3x Refil Acquatec + 5x Refil CP500 + 30x Refil Carbon Tech 9" + 20x Refil Plissado 9.3/4" (Poli Flu) + 5x Refil E3 Compacto + Carcaça Fit 9.3/4" Branca (rosca 1/2") (NF-e 133138 de 12/08/2026, nota de R$ 2.263,62 em 4 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7 (carteira 109). Nosso número 109/00257852-2. Linha digitável 34191.09008 25785.221430 81531.550002 6 16060000053793. Após o vencimento: multa de 1,9% + juros de 0,1% ao dia; protesto no 5º dia útil. | Conferido com o XML da NF-e nº 133138 (emissão 12/08/2026): FILTROS PLANETA AGUA INDUSTRIA E COMERCIO LTDA, CNPJ 05.097.806/0001-63, RUA FRANCISCO BALBINOT, 139, SAO ROQUE, FARROUPILHA/RS. Valor total da nota R$ 2.263,62 em 4 parcelas. Frete CIF (frete por conta do fornecedor), transportadora PATRUS TRANSPORTES URGENTES. Chave da NF-e 43260805097806000163550010001331381847671397. Pago antecipado em 20/10/2026 — lançado em "Out 2026" como "Filtros Planeta Água".</t>
         </is>
       </c>
     </row>
@@ -70721,14 +70752,18 @@
       </c>
       <c r="E108" s="113" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F108" s="113">
         <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
         <v/>
       </c>
-      <c r="G108" s="82" t="n"/>
+      <c r="G108" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 22/10/2026 — lançado em "Out 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="109" s="157">
       <c r="A109" s="78" t="inlineStr">
@@ -72445,7 +72480,7 @@
       </c>
       <c r="E162" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F162" s="112">
@@ -72454,7 +72489,7 @@
       </c>
       <c r="G162" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026.</t>
+          <t>Troca do dia 15/10/2026. Recebido via Pix em 21/10/2026.</t>
         </is>
       </c>
     </row>
@@ -72573,7 +72608,7 @@
       </c>
       <c r="E166" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F166" s="112">
@@ -72582,7 +72617,7 @@
       </c>
       <c r="G166" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00.</t>
+          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00. Recebido em dinheiro em 20/10/2026.</t>
         </is>
       </c>
     </row>
@@ -72651,52 +72686,132 @@
       </c>
     </row>
     <row r="169" s="157">
-      <c r="A169" s="78" t="n"/>
-      <c r="B169" s="78" t="n"/>
-      <c r="C169" s="77" t="n"/>
-      <c r="D169" s="79" t="n"/>
-      <c r="E169" s="112" t="n"/>
+      <c r="A169" s="78" t="inlineStr">
+        <is>
+          <t>Marsilia Marmores e Granitos Erelli</t>
+        </is>
+      </c>
+      <c r="B169" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C169" s="77" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D169" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E169" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F169" s="112">
         <f>IF(OR($E169="Recebido",$C169=""),"",MAX(0,TODAY()-$C169))</f>
         <v/>
       </c>
-      <c r="G169" s="78" t="n"/>
+      <c r="G169" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 19/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="170" s="157">
-      <c r="A170" s="78" t="n"/>
-      <c r="B170" s="78" t="n"/>
-      <c r="C170" s="77" t="n"/>
-      <c r="D170" s="79" t="n"/>
-      <c r="E170" s="112" t="n"/>
+      <c r="A170" s="78" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste do Brasil</t>
+        </is>
+      </c>
+      <c r="B170" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C170" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D170" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E170" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F170" s="112">
         <f>IF(OR($E170="Recebido",$C170=""),"",MAX(0,TODAY()-$C170))</f>
         <v/>
       </c>
-      <c r="G170" s="78" t="n"/>
+      <c r="G170" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="171" s="157">
-      <c r="A171" s="78" t="n"/>
-      <c r="B171" s="78" t="n"/>
-      <c r="C171" s="77" t="n"/>
-      <c r="D171" s="79" t="n"/>
-      <c r="E171" s="112" t="n"/>
+      <c r="A171" s="78" t="inlineStr">
+        <is>
+          <t>Magna dos Santos Carneiro Goncalves - Mirna</t>
+        </is>
+      </c>
+      <c r="B171" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C171" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D171" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E171" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F171" s="112">
         <f>IF(OR($E171="Recebido",$C171=""),"",MAX(0,TODAY()-$C171))</f>
         <v/>
       </c>
-      <c r="G171" s="78" t="n"/>
+      <c r="G171" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="172" s="157">
-      <c r="A172" s="78" t="n"/>
-      <c r="B172" s="78" t="n"/>
-      <c r="C172" s="77" t="n"/>
-      <c r="D172" s="79" t="n"/>
-      <c r="E172" s="112" t="n"/>
+      <c r="A172" s="78" t="inlineStr">
+        <is>
+          <t>Loja da Claro</t>
+        </is>
+      </c>
+      <c r="B172" s="78" t="inlineStr">
+        <is>
+          <t>Refil Lacqua</t>
+        </is>
+      </c>
+      <c r="C172" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D172" s="79" t="n">
+        <v>80</v>
+      </c>
+      <c r="E172" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F172" s="112">
         <f>IF(OR($E172="Recebido",$C172=""),"",MAX(0,TODAY()-$C172))</f>
         <v/>
       </c>
-      <c r="G172" s="78" t="n"/>
+      <c r="G172" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="173" s="157">
       <c r="A173" s="78" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -56747,7 +56747,7 @@
       </c>
       <c r="B119" s="18" t="inlineStr">
         <is>
-          <t>Eduardo Santos da Silva</t>
+          <t>Tania Dourado - Eduardo Dourado</t>
         </is>
       </c>
       <c r="C119" s="18" t="inlineStr">
@@ -56769,7 +56769,7 @@
       <c r="I119" s="18" t="n"/>
       <c r="J119" s="18" t="inlineStr">
         <is>
-          <t>CLI-0408</t>
+          <t>CLI-0525</t>
         </is>
       </c>
     </row>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -58118,27 +58118,70 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="44" t="n"/>
-      <c r="B164" s="45" t="n"/>
-      <c r="C164" s="45" t="n"/>
-      <c r="D164" s="46" t="n"/>
-      <c r="E164" s="45" t="n"/>
+      <c r="A164" s="44" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B164" s="45" t="inlineStr">
+        <is>
+          <t>Alessandra Carvalho Vieira - Paulo Sergio</t>
+        </is>
+      </c>
+      <c r="C164" s="45" t="inlineStr">
+        <is>
+          <t>Refil Everest + Mangueira</t>
+        </is>
+      </c>
+      <c r="D164" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E164" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F164" s="47" t="n"/>
       <c r="G164" s="48" t="n"/>
       <c r="H164" s="49" t="n"/>
       <c r="I164" s="45" t="n"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>CLI-0586</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="17" t="n"/>
-      <c r="B165" s="18" t="n"/>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="27" t="n"/>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="19" t="n"/>
+      <c r="A165" s="17" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>Rita Mesquita</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="D165" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>Crédito à Vista</t>
+        </is>
+      </c>
+      <c r="F165" s="19" t="n">
+        <v>4.91</v>
+      </c>
       <c r="G165" s="19" t="n"/>
       <c r="H165" s="21" t="n"/>
       <c r="I165" s="18" t="n"/>
-      <c r="J165" s="18" t="n"/>
+      <c r="J165" s="18" t="inlineStr">
+        <is>
+          <t>CLI-0554</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="44" t="n"/>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -67693,7 +67693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="157" min="1" max="1"/>
@@ -67744,7 +67744,7 @@
     </row>
     <row r="5">
       <c r="A5" s="189">
-        <f>D102</f>
+        <f>D109</f>
         <v/>
       </c>
       <c r="C5" s="204">
@@ -70649,1013 +70649,1013 @@
       </c>
     </row>
     <row r="100" s="157">
-      <c r="A100" s="86" t="inlineStr">
+      <c r="A100" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B100" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 389424 (emissão 22/10/2026) · parcela 1/5</t>
+        </is>
+      </c>
+      <c r="C100" s="81" t="n">
+        <v>46347</v>
+      </c>
+      <c r="D100" s="83" t="n">
+        <v>675.84</v>
+      </c>
+      <c r="E100" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F100" s="113">
+        <f>IF(OR($E100="Pago",$C100=""),"",MAX(0,TODAY()-$C100))</f>
+        <v/>
+      </c>
+      <c r="G100" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Slim Preto + 4x Purificador Everest Baby Preto (NF-e 389424 de 22/10/2026, nota de R$ 3.379,19 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/40350414. Linha digitável 34191.12408 35041.480308 52238.850003 7 16370000067584. Boleto recebido por e-mail em 22/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 389424". Após o vencimento: multa de 2% + juros de R$ 0,23 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" s="157">
+      <c r="A101" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B101" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 389424 (emissão 22/10/2026) · parcela 2/5</t>
+        </is>
+      </c>
+      <c r="C101" s="81" t="n">
+        <v>46377</v>
+      </c>
+      <c r="D101" s="83" t="n">
+        <v>675.84</v>
+      </c>
+      <c r="E101" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F101" s="113">
+        <f>IF(OR($E101="Pago",$C101=""),"",MAX(0,TODAY()-$C101))</f>
+        <v/>
+      </c>
+      <c r="G101" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Slim Preto + 4x Purificador Everest Baby Preto (NF-e 389424 de 22/10/2026, nota de R$ 3.379,19 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/40350342. Linha digitável 34191.12408 35034.210308 52238.850003 7 16670000067584. Boleto recebido por e-mail em 22/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 389424". Após o vencimento: multa de 2% + juros de R$ 0,23 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" s="157">
+      <c r="A102" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B102" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 389424 (emissão 22/10/2026) · parcela 3/5</t>
+        </is>
+      </c>
+      <c r="C102" s="81" t="n">
+        <v>46407</v>
+      </c>
+      <c r="D102" s="83" t="n">
+        <v>675.84</v>
+      </c>
+      <c r="E102" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F102" s="113">
+        <f>IF(OR($E102="Pago",$C102=""),"",MAX(0,TODAY()-$C102))</f>
+        <v/>
+      </c>
+      <c r="G102" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Slim Preto + 4x Purificador Everest Baby Preto (NF-e 389424 de 22/10/2026, nota de R$ 3.379,19 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/40350264. Linha digitável 34191.12408 35026.470308 52238.850003 3 16970000067584. Boleto recebido por e-mail em 22/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 389424". Após o vencimento: multa de 2% + juros de R$ 0,23 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="157">
+      <c r="A103" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B103" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 389424 (emissão 22/10/2026) · parcela 4/5</t>
+        </is>
+      </c>
+      <c r="C103" s="81" t="n">
+        <v>46437</v>
+      </c>
+      <c r="D103" s="83" t="n">
+        <v>675.84</v>
+      </c>
+      <c r="E103" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F103" s="113">
+        <f>IF(OR($E103="Pago",$C103=""),"",MAX(0,TODAY()-$C103))</f>
+        <v/>
+      </c>
+      <c r="G103" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Slim Preto + 4x Purificador Everest Baby Preto (NF-e 389424 de 22/10/2026, nota de R$ 3.379,19 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/40350393. Linha digitável 34191.12408 35039.340308 52238.850003 5 17270000067584. Boleto recebido por e-mail em 22/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 389424". Após o vencimento: multa de 2% + juros de R$ 0,23 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" s="157">
+      <c r="A104" s="82" t="inlineStr">
+        <is>
+          <t>Everest Refrigeracao e Industria</t>
+        </is>
+      </c>
+      <c r="B104" s="82" t="inlineStr">
+        <is>
+          <t>Mercadoria — doc. 389424 (emissão 22/10/2026) · parcela 5/5 (última)</t>
+        </is>
+      </c>
+      <c r="C104" s="81" t="n">
+        <v>46467</v>
+      </c>
+      <c r="D104" s="83" t="n">
+        <v>675.83</v>
+      </c>
+      <c r="E104" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F104" s="113">
+        <f>IF(OR($E104="Pago",$C104=""),"",MAX(0,TODAY()-$C104))</f>
+        <v/>
+      </c>
+      <c r="G104" s="82" t="inlineStr">
+        <is>
+          <t>Comprado: Purificador Everest Star Branco + Purificador Everest Fit Branco + Purificador Everest Slim Branco + Purificador Everest Slim Preto + 4x Purificador Everest Baby Preto (NF-e 389424 de 22/10/2026, nota de R$ 3.379,19 em 5 boletos). Categoria quando pagar: Fornecedores / Mercadoria. Boleto Itaú 341-7. Nosso número 112/40350359. Linha digitável 34191.12408 35035.950308 52238.850003 4 17570000067583. Boleto recebido por e-mail em 22/10/2026; PDF salvo em "03 - Despesas e Contas a Pagar/Boletos Everest NF 389424". Após o vencimento: multa de 2% + juros de R$ 0,23 ao dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" s="157">
+      <c r="A105" s="82" t="inlineStr">
+        <is>
+          <t>SEFAZ-BA — DAE ICMS Antecipação Parcial</t>
+        </is>
+      </c>
+      <c r="B105" s="82" t="inlineStr">
+        <is>
+          <t>ICMS Antecipação Parcial — referência 09/2026 (cód. receita 2175, nº 1971838234)</t>
+        </is>
+      </c>
+      <c r="C105" s="81" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D105" s="83" t="n">
+        <v>983.48</v>
+      </c>
+      <c r="E105" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F105" s="113">
+        <f>IF(OR($E105="Pago",$C105=""),"",MAX(0,TODAY()-$C105))</f>
+        <v/>
+      </c>
+      <c r="G105" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Impostos e Taxas. Inscrição Estadual 066.200.856 — Planeta Agua Ltda, CNPJ 07.341.784/0001-60. Notas fiscais da guia (4): 386188 // 134720 // 386838 // 387488. Código de barras 85820000009 0 83480005202 7 61026197183 8 82342175193 2. Pode pagar por código de barras ou Pix (QR Code). Guia emitida em 19/10/2026; vale para pagamento até 26/10/2026 — depois disso precisa emitir outro DAE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" s="157">
+      <c r="A106" s="82" t="inlineStr">
+        <is>
+          <t>Empresa Baiana de Aguas e Saneamento SA (Embasa)</t>
+        </is>
+      </c>
+      <c r="B106" s="82" t="inlineStr">
+        <is>
+          <t>Conta de água — despesa pessoal do dono (não é da loja) — ref. 11/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="81" t="n">
+        <v>46327</v>
+      </c>
+      <c r="D106" s="83" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="E106" s="113" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F106" s="113">
+        <f>IF(OR($E106="Pago",$C106=""),"",MAX(0,TODAY()-$C106))</f>
+        <v/>
+      </c>
+      <c r="G106" s="82" t="inlineStr">
+        <is>
+          <t>Categoria quando pagar: Pro Labore Edilânia (despesa pessoal do dono). Conta em nome de Adriano Silva Fontes, matrícula 0531718-70, consumo 10 m³. Código de barras 82600000000-8 51850047820-2 53171870112-5 60000000000-7. Pode pagar por Pix (QR Code da conta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" s="157">
+      <c r="A107" s="86" t="inlineStr">
         <is>
           <t>TOTAL A PAGAR — COM BOLETO EM MÃOS</t>
         </is>
       </c>
-      <c r="B100" s="86" t="n"/>
-      <c r="C100" s="114" t="n"/>
-      <c r="D100" s="115">
-        <f>SUMIF(E11:E99,"Pendente",D11:D99)</f>
-        <v/>
-      </c>
-      <c r="E100" s="116" t="n"/>
-      <c r="F100" s="116" t="n"/>
-      <c r="G100" s="86" t="n"/>
-    </row>
-    <row r="101" s="157">
-      <c r="A101" s="144" t="inlineStr">
+      <c r="B107" s="86" t="n"/>
+      <c r="C107" s="114" t="n"/>
+      <c r="D107" s="115">
+        <f>SUMIF(E11:E106,"Pendente",D11:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="116" t="n"/>
+      <c r="F107" s="116" t="n"/>
+      <c r="G107" s="86" t="n"/>
+    </row>
+    <row r="108" s="157">
+      <c r="A108" s="144" t="inlineStr">
         <is>
           <t>PREVISTO — compromisso certo que ainda não está documentado</t>
         </is>
       </c>
-      <c r="B101" s="144" t="n"/>
-      <c r="C101" s="145" t="n"/>
-      <c r="D101" s="146">
-        <f>SUMIF(E11:E99,"Previsto",D11:D99)</f>
-        <v/>
-      </c>
-      <c r="E101" s="142" t="n"/>
-      <c r="F101" s="142" t="n"/>
-      <c r="G101" s="144" t="n"/>
-    </row>
-    <row r="102" s="157">
-      <c r="A102" s="86" t="inlineStr">
+      <c r="B108" s="144" t="n"/>
+      <c r="C108" s="145" t="n"/>
+      <c r="D108" s="146">
+        <f>SUMIF(E11:E106,"Previsto",D11:D106)</f>
+        <v/>
+      </c>
+      <c r="E108" s="142" t="n"/>
+      <c r="F108" s="142" t="n"/>
+      <c r="G108" s="144" t="n"/>
+    </row>
+    <row r="109" s="157">
+      <c r="A109" s="86" t="inlineStr">
         <is>
           <t>TOTAL GERAL A PAGAR (boletos + previsão)</t>
         </is>
       </c>
-      <c r="B102" s="86" t="n"/>
-      <c r="C102" s="114" t="n"/>
-      <c r="D102" s="115">
-        <f>D100+D101</f>
-        <v/>
-      </c>
-      <c r="E102" s="116" t="n"/>
-      <c r="F102" s="116" t="n"/>
-      <c r="G102" s="86" t="n"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" s="157"/>
-    <row r="104" ht="15.75" customHeight="1" s="157">
-      <c r="A104" s="200" t="inlineStr">
+      <c r="B109" s="86" t="n"/>
+      <c r="C109" s="114" t="n"/>
+      <c r="D109" s="115">
+        <f>D107+D108</f>
+        <v/>
+      </c>
+      <c r="E109" s="116" t="n"/>
+      <c r="F109" s="116" t="n"/>
+      <c r="G109" s="86" t="n"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1" s="157"/>
+    <row r="111" ht="15.75" customHeight="1" s="157">
+      <c r="A111" s="200" t="inlineStr">
         <is>
           <t>CONTAS A RECEBER  —  vendas feitas e ainda não pagas</t>
         </is>
       </c>
     </row>
-    <row r="105" s="157">
-      <c r="A105" s="194" t="inlineStr">
+    <row r="112" s="157">
+      <c r="A112" s="194" t="inlineStr">
         <is>
           <t>Espelho das vendas marcadas como "Aguardando Pagamento" nas abas dos meses. Ao receber, mude a Forma de Pagamento na aba do mês E o Status aqui. A linha de conferência avisa se os dois deixarem de bater.</t>
         </is>
       </c>
     </row>
-    <row r="106" s="157">
-      <c r="A106" s="111" t="inlineStr">
+    <row r="113" s="157">
+      <c r="A113" s="111" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B106" s="111" t="inlineStr">
+      <c r="B113" s="111" t="inlineStr">
         <is>
           <t>Produto / Referência</t>
         </is>
       </c>
-      <c r="C106" s="111" t="inlineStr">
+      <c r="C113" s="111" t="inlineStr">
         <is>
           <t>Data da Venda</t>
         </is>
       </c>
-      <c r="D106" s="111" t="inlineStr">
+      <c r="D113" s="111" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="E106" s="111" t="inlineStr">
+      <c r="E113" s="111" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F106" s="111" t="inlineStr">
+      <c r="F113" s="111" t="inlineStr">
         <is>
           <t>Dias em Atraso</t>
         </is>
       </c>
-      <c r="G106" s="111" t="inlineStr">
+      <c r="G113" s="111" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="107" s="157">
-      <c r="A107" s="78" t="inlineStr">
+    <row r="114" s="157">
+      <c r="A114" s="78" t="inlineStr">
         <is>
           <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
-      <c r="B107" s="78" t="inlineStr">
+      <c r="B114" s="78" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C107" s="77" t="n">
+      <c r="C114" s="77" t="n">
         <v>46239</v>
       </c>
-      <c r="D107" s="79" t="n">
+      <c r="D114" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E107" s="112" t="inlineStr">
+      <c r="E114" s="112" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="F107" s="112">
-        <f>IF(OR($E107="Recebido",$C107=""),"",MAX(0,TODAY()-$C107))</f>
-        <v/>
-      </c>
-      <c r="G107" s="78" t="n"/>
-    </row>
-    <row r="108" s="157">
-      <c r="A108" s="82" t="inlineStr">
+      <c r="F114" s="112">
+        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
+        <v/>
+      </c>
+      <c r="G114" s="78" t="n"/>
+    </row>
+    <row r="115" s="157">
+      <c r="A115" s="82" t="inlineStr">
         <is>
           <t>Supermercado Brasil</t>
         </is>
       </c>
-      <c r="B108" s="82" t="inlineStr">
+      <c r="B115" s="82" t="inlineStr">
         <is>
           <t>2x Refil Pro Life</t>
         </is>
       </c>
-      <c r="C108" s="81" t="n">
+      <c r="C115" s="81" t="n">
         <v>46239</v>
       </c>
-      <c r="D108" s="83" t="n">
+      <c r="D115" s="83" t="n">
         <v>280</v>
       </c>
-      <c r="E108" s="113" t="inlineStr">
+      <c r="E115" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F108" s="113">
-        <f>IF(OR($E108="Recebido",$C108=""),"",MAX(0,TODAY()-$C108))</f>
-        <v/>
-      </c>
-      <c r="G108" s="82" t="inlineStr">
+      <c r="F115" s="113">
+        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
+        <v/>
+      </c>
+      <c r="G115" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 22/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
-    <row r="109" s="157">
-      <c r="A109" s="78" t="inlineStr">
+    <row r="116" s="157">
+      <c r="A116" s="78" t="inlineStr">
         <is>
           <t>Tropical Motos LTDA</t>
         </is>
       </c>
-      <c r="B109" s="78" t="inlineStr">
+      <c r="B116" s="78" t="inlineStr">
         <is>
           <t>3x Refil Everest + Refil Pro Life + 3x Pré Filtro + Válvula Reguladora de Pressão</t>
         </is>
       </c>
-      <c r="C109" s="77" t="n">
+      <c r="C116" s="77" t="n">
         <v>46245</v>
       </c>
-      <c r="D109" s="79" t="n">
+      <c r="D116" s="79" t="n">
         <v>820</v>
       </c>
-      <c r="E109" s="112" t="inlineStr">
+      <c r="E116" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F109" s="112">
-        <f>IF(OR($E109="Recebido",$C109=""),"",MAX(0,TODAY()-$C109))</f>
-        <v/>
-      </c>
-      <c r="G109" s="78" t="inlineStr">
+      <c r="F116" s="112">
+        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
+        <v/>
+      </c>
+      <c r="G116" s="78" t="inlineStr">
         <is>
           <t>Recebido via TED em 25/08/2026. NF conferida: valor correto é R$820 (faltava a válvula no lançamento original de R$740).</t>
         </is>
       </c>
     </row>
-    <row r="110" s="157">
-      <c r="A110" s="82" t="inlineStr">
+    <row r="117" s="157">
+      <c r="A117" s="82" t="inlineStr">
         <is>
           <t>Free Way</t>
         </is>
       </c>
-      <c r="B110" s="82" t="inlineStr">
+      <c r="B117" s="82" t="inlineStr">
         <is>
           <t>5x Refil Everest</t>
         </is>
       </c>
-      <c r="C110" s="81" t="n">
+      <c r="C117" s="81" t="n">
         <v>46251</v>
       </c>
-      <c r="D110" s="83" t="n">
+      <c r="D117" s="83" t="n">
         <v>700</v>
       </c>
-      <c r="E110" s="113" t="inlineStr">
+      <c r="E117" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F110" s="113">
-        <f>IF(OR($E110="Recebido",$C110=""),"",MAX(0,TODAY()-$C110))</f>
-        <v/>
-      </c>
-      <c r="G110" s="82" t="inlineStr">
+      <c r="F117" s="113">
+        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
+        <v/>
+      </c>
+      <c r="G117" s="82" t="inlineStr">
         <is>
           <t>Recebido via TED em 02/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="111" s="157">
-      <c r="A111" s="78" t="inlineStr">
+    <row r="118" s="157">
+      <c r="A118" s="78" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B111" s="78" t="inlineStr">
+      <c r="B118" s="78" t="inlineStr">
         <is>
           <t>Refil Pro Life</t>
         </is>
       </c>
-      <c r="C111" s="77" t="n">
+      <c r="C118" s="77" t="n">
         <v>46254</v>
       </c>
-      <c r="D111" s="79" t="n">
+      <c r="D118" s="79" t="n">
         <v>140</v>
       </c>
-      <c r="E111" s="112" t="inlineStr">
+      <c r="E118" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F111" s="112">
-        <f>IF(OR($E111="Recebido",$C111=""),"",MAX(0,TODAY()-$C111))</f>
-        <v/>
-      </c>
-      <c r="G111" s="78" t="inlineStr">
+      <c r="F118" s="112">
+        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
+        <v/>
+      </c>
+      <c r="G118" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="112" s="157">
-      <c r="A112" s="82" t="inlineStr">
+    <row r="119" s="157">
+      <c r="A119" s="82" t="inlineStr">
         <is>
           <t>Neli Sena Rego</t>
         </is>
       </c>
-      <c r="B112" s="82" t="inlineStr">
+      <c r="B119" s="82" t="inlineStr">
         <is>
           <t>Conexão + Mangueira</t>
         </is>
       </c>
-      <c r="C112" s="81" t="n">
+      <c r="C119" s="81" t="n">
         <v>46255</v>
       </c>
-      <c r="D112" s="83" t="n">
+      <c r="D119" s="83" t="n">
         <v>40</v>
       </c>
-      <c r="E112" s="113" t="inlineStr">
+      <c r="E119" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F112" s="113">
-        <f>IF(OR($E112="Recebido",$C112=""),"",MAX(0,TODAY()-$C112))</f>
-        <v/>
-      </c>
-      <c r="G112" s="82" t="inlineStr">
+      <c r="F119" s="113">
+        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
+        <v/>
+      </c>
+      <c r="G119" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 01/09/2026 (R$ 170,00 pelas duas vendas)</t>
         </is>
       </c>
     </row>
-    <row r="113" s="157">
-      <c r="A113" s="78" t="inlineStr">
+    <row r="120" s="157">
+      <c r="A120" s="78" t="inlineStr">
         <is>
           <t>Lapec</t>
         </is>
       </c>
-      <c r="B113" s="78" t="inlineStr">
+      <c r="B120" s="78" t="inlineStr">
         <is>
           <t>4x Refil Everest</t>
         </is>
       </c>
-      <c r="C113" s="77" t="n">
+      <c r="C120" s="77" t="n">
         <v>46258</v>
       </c>
-      <c r="D113" s="79" t="n">
+      <c r="D120" s="79" t="n">
         <v>480</v>
       </c>
-      <c r="E113" s="112" t="inlineStr">
+      <c r="E120" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F113" s="112">
-        <f>IF(OR($E113="Recebido",$C113=""),"",MAX(0,TODAY()-$C113))</f>
-        <v/>
-      </c>
-      <c r="G113" s="78" t="inlineStr">
+      <c r="F120" s="112">
+        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
+        <v/>
+      </c>
+      <c r="G120" s="78" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="114" s="157">
-      <c r="A114" s="82" t="inlineStr">
+    <row r="121" s="157">
+      <c r="A121" s="82" t="inlineStr">
         <is>
           <t>Cícero Lima</t>
         </is>
       </c>
-      <c r="B114" s="82" t="inlineStr">
+      <c r="B121" s="82" t="inlineStr">
         <is>
           <t>Refil Everest</t>
         </is>
       </c>
-      <c r="C114" s="81" t="n">
+      <c r="C121" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D114" s="83" t="n">
+      <c r="D121" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="E114" s="113" t="inlineStr">
+      <c r="E121" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F114" s="113">
-        <f>IF(OR($E114="Recebido",$C114=""),"",MAX(0,TODAY()-$C114))</f>
-        <v/>
-      </c>
-      <c r="G114" s="82" t="inlineStr">
+      <c r="F121" s="113">
+        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
+        <v/>
+      </c>
+      <c r="G121" s="82" t="inlineStr">
         <is>
           <t>Recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="115" s="157">
-      <c r="A115" s="78" t="inlineStr">
+    <row r="122" s="157">
+      <c r="A122" s="78" t="inlineStr">
         <is>
           <t>Promotoria Regional de Jacobina</t>
         </is>
       </c>
-      <c r="B115" s="78" t="inlineStr">
+      <c r="B122" s="78" t="inlineStr">
         <is>
           <t>2x Carcaça 9" + 2x Refil Plissado 9" + Conexão Reta Rosca</t>
         </is>
       </c>
-      <c r="C115" s="77" t="n">
+      <c r="C122" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D115" s="79" t="n">
+      <c r="D122" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="E115" s="112" t="inlineStr">
+      <c r="E122" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F115" s="112">
-        <f>IF(OR($E115="Recebido",$C115=""),"",MAX(0,TODAY()-$C115))</f>
-        <v/>
-      </c>
-      <c r="G115" s="78" t="inlineStr">
+      <c r="F122" s="112">
+        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
+        <v/>
+      </c>
+      <c r="G122" s="78" t="inlineStr">
         <is>
           <t>Pago em 28/08/2026 em duas formas: R$ 270,00 Pix + R$ 200,00 crédito 2x</t>
         </is>
       </c>
     </row>
-    <row r="116" s="157">
-      <c r="A116" s="82" t="inlineStr">
+    <row r="123" s="157">
+      <c r="A123" s="82" t="inlineStr">
         <is>
           <t>Lucas Souza</t>
         </is>
       </c>
-      <c r="B116" s="82" t="inlineStr">
+      <c r="B123" s="82" t="inlineStr">
         <is>
           <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
-      <c r="C116" s="81" t="n">
+      <c r="C123" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D116" s="83" t="n">
+      <c r="D123" s="83" t="n">
         <v>200</v>
       </c>
-      <c r="E116" s="113" t="inlineStr">
+      <c r="E123" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F116" s="113">
-        <f>IF(OR($E116="Recebido",$C116=""),"",MAX(0,TODAY()-$C116))</f>
-        <v/>
-      </c>
-      <c r="G116" s="82" t="inlineStr">
+      <c r="F123" s="113">
+        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
+        <v/>
+      </c>
+      <c r="G123" s="82" t="inlineStr">
         <is>
           <t>Recebido em dinheiro em 03/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
-    <row r="117" s="157">
-      <c r="A117" s="78" t="inlineStr">
+    <row r="124" s="157">
+      <c r="A124" s="78" t="inlineStr">
         <is>
           <t>FG Boa Vista (Recife/PE)</t>
         </is>
       </c>
-      <c r="B117" s="78" t="inlineStr">
+      <c r="B124" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C117" s="77" t="n">
+      <c r="C124" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D117" s="79" t="n">
+      <c r="D124" s="79" t="n">
         <v>1008.8</v>
       </c>
-      <c r="E117" s="112" t="inlineStr">
+      <c r="E124" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F117" s="112">
-        <f>IF(OR($E117="Recebido",$C117=""),"",MAX(0,TODAY()-$C117))</f>
-        <v/>
-      </c>
-      <c r="G117" s="78" t="inlineStr">
+      <c r="F124" s="112">
+        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
+        <v/>
+      </c>
+      <c r="G124" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.280 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="118" s="157">
-      <c r="A118" s="82" t="inlineStr">
+    <row r="125" s="157">
+      <c r="A125" s="82" t="inlineStr">
         <is>
           <t>UNIFG Guanambi (Guanambi/BA)</t>
         </is>
       </c>
-      <c r="B118" s="82" t="inlineStr">
+      <c r="B125" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C118" s="81" t="n">
+      <c r="C125" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D118" s="83" t="n">
+      <c r="D125" s="83" t="n">
         <v>4534.75</v>
       </c>
-      <c r="E118" s="113" t="inlineStr">
+      <c r="E125" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F118" s="113">
-        <f>IF(OR($E118="Recebido",$C118=""),"",MAX(0,TODAY()-$C118))</f>
-        <v/>
-      </c>
-      <c r="G118" s="82" t="inlineStr">
+      <c r="F125" s="113">
+        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
+        <v/>
+      </c>
+      <c r="G125" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.281 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="119" s="157">
-      <c r="A119" s="78" t="inlineStr">
+    <row r="126" s="157">
+      <c r="A126" s="78" t="inlineStr">
         <is>
           <t>UNP Zona Norte (Natal/RN)</t>
         </is>
       </c>
-      <c r="B119" s="78" t="inlineStr">
+      <c r="B126" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C119" s="77" t="n">
+      <c r="C126" s="77" t="n">
         <v>46261</v>
       </c>
-      <c r="D119" s="79" t="n">
+      <c r="D126" s="79" t="n">
         <v>870</v>
       </c>
-      <c r="E119" s="112" t="inlineStr">
+      <c r="E126" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F119" s="112">
-        <f>IF(OR($E119="Recebido",$C119=""),"",MAX(0,TODAY()-$C119))</f>
-        <v/>
-      </c>
-      <c r="G119" s="78" t="inlineStr">
+      <c r="F126" s="112">
+        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
+        <v/>
+      </c>
+      <c r="G126" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.282 · recebido em 30/08/2026 (Nota Paga no portal V360)</t>
         </is>
       </c>
     </row>
-    <row r="120" s="157">
-      <c r="A120" s="82" t="inlineStr">
+    <row r="127" s="157">
+      <c r="A127" s="82" t="inlineStr">
         <is>
           <t>UNP Caicó (Caicó/RN)</t>
         </is>
       </c>
-      <c r="B120" s="82" t="inlineStr">
+      <c r="B127" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C120" s="81" t="n">
+      <c r="C127" s="81" t="n">
         <v>46261</v>
       </c>
-      <c r="D120" s="83" t="n">
+      <c r="D127" s="83" t="n">
         <v>440</v>
       </c>
-      <c r="E120" s="113" t="inlineStr">
+      <c r="E127" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F120" s="113">
-        <f>IF(OR($E120="Recebido",$C120=""),"",MAX(0,TODAY()-$C120))</f>
-        <v/>
-      </c>
-      <c r="G120" s="82" t="inlineStr">
+      <c r="F127" s="113">
+        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
+        <v/>
+      </c>
+      <c r="G127" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.283 · recebido via Pix em 27/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="121" s="157">
-      <c r="A121" s="78" t="inlineStr">
+    <row r="128" s="157">
+      <c r="A128" s="78" t="inlineStr">
         <is>
           <t>AGES Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B121" s="78" t="inlineStr">
+      <c r="B128" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C121" s="77" t="n">
+      <c r="C128" s="77" t="n">
         <v>46269</v>
       </c>
-      <c r="D121" s="79" t="n">
+      <c r="D128" s="79" t="n">
         <v>1338.6</v>
       </c>
-      <c r="E121" s="112" t="inlineStr">
+      <c r="E128" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F121" s="112">
-        <f>IF(OR($E121="Recebido",$C121=""),"",MAX(0,TODAY()-$C121))</f>
-        <v/>
-      </c>
-      <c r="G121" s="78" t="inlineStr">
+      <c r="F128" s="112">
+        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
+        <v/>
+      </c>
+      <c r="G128" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.294 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="122" s="157">
-      <c r="A122" s="82" t="inlineStr">
+    <row r="129" s="157">
+      <c r="A129" s="82" t="inlineStr">
         <is>
           <t>CIS Irecê (Irecê/BA)</t>
         </is>
       </c>
-      <c r="B122" s="82" t="inlineStr">
+      <c r="B129" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C122" s="81" t="n">
+      <c r="C129" s="81" t="n">
         <v>46269</v>
       </c>
-      <c r="D122" s="83" t="n">
+      <c r="D129" s="83" t="n">
         <v>1358</v>
       </c>
-      <c r="E122" s="113" t="inlineStr">
+      <c r="E129" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F122" s="113">
-        <f>IF(OR($E122="Recebido",$C122=""),"",MAX(0,TODAY()-$C122))</f>
-        <v/>
-      </c>
-      <c r="G122" s="82" t="inlineStr">
+      <c r="F129" s="113">
+        <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
+        <v/>
+      </c>
+      <c r="G129" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.295 · recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="123" s="157">
-      <c r="A123" s="78" t="inlineStr">
+    <row r="130" s="157">
+      <c r="A130" s="78" t="inlineStr">
         <is>
           <t>AGES Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B123" s="78" t="inlineStr">
+      <c r="B130" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C123" s="77" t="n">
+      <c r="C130" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D123" s="79" t="n">
+      <c r="D130" s="79" t="n">
         <v>649.9</v>
       </c>
-      <c r="E123" s="112" t="inlineStr">
+      <c r="E130" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F123" s="112">
-        <f>IF(OR($E123="Recebido",$C123=""),"",MAX(0,TODAY()-$C123))</f>
-        <v/>
-      </c>
-      <c r="G123" s="78" t="inlineStr">
+      <c r="F130" s="112">
+        <f>IF(OR($E130="Recebido",$C130=""),"",MAX(0,TODAY()-$C130))</f>
+        <v/>
+      </c>
+      <c r="G130" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.298 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="124" s="157">
-      <c r="A124" s="82" t="inlineStr">
+    <row r="131" s="157">
+      <c r="A131" s="82" t="inlineStr">
         <is>
           <t>CIS Senhor do Bonfim (S. do Bonfim/BA)</t>
         </is>
       </c>
-      <c r="B124" s="82" t="inlineStr">
+      <c r="B131" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C124" s="81" t="n">
+      <c r="C131" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D124" s="83" t="n">
+      <c r="D131" s="83" t="n">
         <v>562.6</v>
       </c>
-      <c r="E124" s="113" t="inlineStr">
+      <c r="E131" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F124" s="113">
-        <f>IF(OR($E124="Recebido",$C124=""),"",MAX(0,TODAY()-$C124))</f>
-        <v/>
-      </c>
-      <c r="G124" s="82" t="inlineStr">
+      <c r="F131" s="113">
+        <f>IF(OR($E131="Recebido",$C131=""),"",MAX(0,TODAY()-$C131))</f>
+        <v/>
+      </c>
+      <c r="G131" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.299 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="125" s="157">
-      <c r="A125" s="78" t="inlineStr">
+    <row r="132" s="157">
+      <c r="A132" s="78" t="inlineStr">
         <is>
           <t>AGES Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B125" s="78" t="inlineStr">
+      <c r="B132" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C125" s="77" t="n">
+      <c r="C132" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D125" s="79" t="n">
+      <c r="D132" s="79" t="n">
         <v>1086.4</v>
       </c>
-      <c r="E125" s="112" t="inlineStr">
+      <c r="E132" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F125" s="112">
-        <f>IF(OR($E125="Recebido",$C125=""),"",MAX(0,TODAY()-$C125))</f>
-        <v/>
-      </c>
-      <c r="G125" s="78" t="inlineStr">
+      <c r="F132" s="112">
+        <f>IF(OR($E132="Recebido",$C132=""),"",MAX(0,TODAY()-$C132))</f>
+        <v/>
+      </c>
+      <c r="G132" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.300 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="126" s="157">
-      <c r="A126" s="82" t="inlineStr">
+    <row r="133" s="157">
+      <c r="A133" s="82" t="inlineStr">
         <is>
           <t>Clínica Veterinária Paripiranga (Paripiranga/BA)</t>
         </is>
       </c>
-      <c r="B126" s="82" t="inlineStr">
+      <c r="B133" s="82" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C126" s="81" t="n">
+      <c r="C133" s="81" t="n">
         <v>46270</v>
       </c>
-      <c r="D126" s="83" t="n">
+      <c r="D133" s="83" t="n">
         <v>1265.85</v>
       </c>
-      <c r="E126" s="113" t="inlineStr">
+      <c r="E133" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F126" s="113">
-        <f>IF(OR($E126="Recebido",$C126=""),"",MAX(0,TODAY()-$C126))</f>
-        <v/>
-      </c>
-      <c r="G126" s="82" t="inlineStr">
+      <c r="F133" s="113">
+        <f>IF(OR($E133="Recebido",$C133=""),"",MAX(0,TODAY()-$C133))</f>
+        <v/>
+      </c>
+      <c r="G133" s="82" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.301 · recebido via Pix em 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="127" s="157">
-      <c r="A127" s="78" t="inlineStr">
+    <row r="134" s="157">
+      <c r="A134" s="78" t="inlineStr">
         <is>
           <t>UNP Mossoró (Mossoró/RN)</t>
         </is>
       </c>
-      <c r="B127" s="78" t="inlineStr">
+      <c r="B134" s="78" t="inlineStr">
         <is>
           <t>Refis — troca de julho/2026</t>
         </is>
       </c>
-      <c r="C127" s="77" t="n">
+      <c r="C134" s="77" t="n">
         <v>46270</v>
       </c>
-      <c r="D127" s="79" t="n">
+      <c r="D134" s="79" t="n">
         <v>1867.25</v>
       </c>
-      <c r="E127" s="112" t="inlineStr">
+      <c r="E134" s="112" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F127" s="112">
-        <f>IF(OR($E127="Recebido",$C127=""),"",MAX(0,TODAY()-$C127))</f>
-        <v/>
-      </c>
-      <c r="G127" s="78" t="inlineStr">
+      <c r="F134" s="112">
+        <f>IF(OR($E134="Recebido",$C134=""),"",MAX(0,TODAY()-$C134))</f>
+        <v/>
+      </c>
+      <c r="G134" s="78" t="inlineStr">
         <is>
           <t>Grupo Ânima — NF 000.004.302 · recebido via Pix em 08/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" s="157">
-      <c r="A128" s="82" t="inlineStr">
-        <is>
-          <t>CIS Jacobina (Jacobina/BA)</t>
-        </is>
-      </c>
-      <c r="B128" s="82" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C128" s="81" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D128" s="83" t="n">
-        <v>2095.2</v>
-      </c>
-      <c r="E128" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F128" s="113">
-        <f>IF(OR($E128="Recebido",$C128=""),"",MAX(0,TODAY()-$C128))</f>
-        <v/>
-      </c>
-      <c r="G128" s="82" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" s="157">
-      <c r="A129" s="78" t="inlineStr">
-        <is>
-          <t>AGES Jacobina (Jacobina/BA)</t>
-        </is>
-      </c>
-      <c r="B129" s="78" t="inlineStr">
-        <is>
-          <t>Refis — troca de julho/2026</t>
-        </is>
-      </c>
-      <c r="C129" s="77" t="n">
-        <v>46305</v>
-      </c>
-      <c r="D129" s="79" t="n">
-        <v>1188.25</v>
-      </c>
-      <c r="E129" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F129" s="112">
-        <f>IF(OR($E129="Recebido",$C129=""),"",MAX(0,TODAY()-$C129))</f>
-        <v/>
-      </c>
-      <c r="G129" s="78" t="inlineStr">
-        <is>
-          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias · Recebido em 13/10/2026 no BNB (Nota Paga no portal V360).</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" s="157">
-      <c r="A130" s="82" t="inlineStr">
-        <is>
-          <t>Instituto Paulo Leão</t>
-        </is>
-      </c>
-      <c r="B130" s="82" t="inlineStr">
-        <is>
-          <t>Refil E3 + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C130" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D130" s="83" t="n">
-        <v>160</v>
-      </c>
-      <c r="E130" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F130" s="113">
-        <f>IF(OR($E130="Recebido",$C130=""),"",MAX(0,TODAY()-$C130))</f>
-        <v/>
-      </c>
-      <c r="G130" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" s="157">
-      <c r="A131" s="78" t="inlineStr">
-        <is>
-          <t>Eletronic Segurança Eletronica</t>
-        </is>
-      </c>
-      <c r="B131" s="78" t="inlineStr">
-        <is>
-          <t>Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C131" s="77" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D131" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="E131" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F131" s="112">
-        <f>IF(OR($E131="Recebido",$C131=""),"",MAX(0,TODAY()-$C131))</f>
-        <v/>
-      </c>
-      <c r="G131" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 03/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" s="157">
-      <c r="A132" s="82" t="inlineStr">
-        <is>
-          <t>Clube dos Mineiros</t>
-        </is>
-      </c>
-      <c r="B132" s="82" t="inlineStr">
-        <is>
-          <t>Refil Pro Life</t>
-        </is>
-      </c>
-      <c r="C132" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D132" s="83" t="n">
-        <v>150</v>
-      </c>
-      <c r="E132" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F132" s="113">
-        <f>IF(OR($E132="Recebido",$C132=""),"",MAX(0,TODAY()-$C132))</f>
-        <v/>
-      </c>
-      <c r="G132" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" s="157">
-      <c r="A133" s="78" t="inlineStr">
-        <is>
-          <t>Armazem Cecilio Mota</t>
-        </is>
-      </c>
-      <c r="B133" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Refil Carbon 9"</t>
-        </is>
-      </c>
-      <c r="C133" s="77" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D133" s="79" t="n">
-        <v>225</v>
-      </c>
-      <c r="E133" s="112" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F133" s="112">
-        <f>IF(OR($E133="Recebido",$C133=""),"",MAX(0,TODAY()-$C133))</f>
-        <v/>
-      </c>
-      <c r="G133" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" s="157">
-      <c r="A134" s="82" t="inlineStr">
-        <is>
-          <t>Clebson Dantas Da Silva</t>
-        </is>
-      </c>
-      <c r="B134" s="82" t="inlineStr">
-        <is>
-          <t>Refil Everest</t>
-        </is>
-      </c>
-      <c r="C134" s="81" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D134" s="83" t="n">
-        <v>140</v>
-      </c>
-      <c r="E134" s="113" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="F134" s="113">
-        <f>IF(OR($E134="Recebido",$C134=""),"",MAX(0,TODAY()-$C134))</f>
-        <v/>
-      </c>
-      <c r="G134" s="82" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="135" s="157">
       <c r="A135" s="82" t="inlineStr">
         <is>
-          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+          <t>CIS Jacobina (Jacobina/BA)</t>
         </is>
       </c>
       <c r="B135" s="82" t="inlineStr">
         <is>
-          <t>3x Refil Everest + 2x Pré Filtro</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C135" s="81" t="n">
-        <v>46267</v>
+        <v>46290</v>
       </c>
       <c r="D135" s="83" t="n">
-        <v>540</v>
+        <v>2095.2</v>
       </c>
       <c r="E135" s="113" t="inlineStr">
         <is>
@@ -71668,26 +71668,26 @@
       </c>
       <c r="G135" s="82" t="inlineStr">
         <is>
-          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
+          <t>Grupo Ânima — NF 000.004.333 de 26/08/2026 · OC AEMPPO00004452 · 30 dias · recebido via Pix em 25/09/2026 (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
     <row r="136" s="157">
       <c r="A136" s="78" t="inlineStr">
         <is>
-          <t>Cecilio Mota Junior</t>
+          <t>AGES Jacobina (Jacobina/BA)</t>
         </is>
       </c>
       <c r="B136" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refis — troca de julho/2026</t>
         </is>
       </c>
       <c r="C136" s="77" t="n">
-        <v>46267</v>
+        <v>46305</v>
       </c>
       <c r="D136" s="79" t="n">
-        <v>140</v>
+        <v>1188.25</v>
       </c>
       <c r="E136" s="112" t="inlineStr">
         <is>
@@ -71700,58 +71700,58 @@
       </c>
       <c r="G136" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Grupo Ânima — NF 000.004.332 de 26/08/2026 · OC AEMPPO00004453 · 45 dias · Recebido em 13/10/2026 no BNB (Nota Paga no portal V360).</t>
         </is>
       </c>
     </row>
     <row r="137" s="157">
-      <c r="A137" s="78" t="inlineStr">
-        <is>
-          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
-        </is>
-      </c>
-      <c r="B137" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C137" s="77" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D137" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E137" s="112" t="inlineStr">
+      <c r="A137" s="82" t="inlineStr">
+        <is>
+          <t>Instituto Paulo Leão</t>
+        </is>
+      </c>
+      <c r="B137" s="82" t="inlineStr">
+        <is>
+          <t>Refil E3 + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C137" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D137" s="83" t="n">
+        <v>160</v>
+      </c>
+      <c r="E137" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F137" s="112">
+      <c r="F137" s="113">
         <f>IF(OR($E137="Recebido",$C137=""),"",MAX(0,TODAY()-$C137))</f>
         <v/>
       </c>
-      <c r="G137" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 04/09/2026.</t>
+      <c r="G137" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="138" s="157">
       <c r="A138" s="78" t="inlineStr">
         <is>
-          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
+          <t>Eletronic Segurança Eletronica</t>
         </is>
       </c>
       <c r="B138" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Pré Filtro</t>
         </is>
       </c>
       <c r="C138" s="77" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="D138" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E138" s="112" t="inlineStr">
         <is>
@@ -71764,58 +71764,58 @@
       </c>
       <c r="G138" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 03/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="139" s="157">
-      <c r="A139" s="78" t="inlineStr">
-        <is>
-          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
-        </is>
-      </c>
-      <c r="B139" s="78" t="inlineStr">
-        <is>
-          <t>Refil Plissado + Refil BAG</t>
-        </is>
-      </c>
-      <c r="C139" s="77" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D139" s="79" t="n">
+      <c r="A139" s="82" t="inlineStr">
+        <is>
+          <t>Clube dos Mineiros</t>
+        </is>
+      </c>
+      <c r="B139" s="82" t="inlineStr">
+        <is>
+          <t>Refil Pro Life</t>
+        </is>
+      </c>
+      <c r="C139" s="81" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D139" s="83" t="n">
         <v>150</v>
       </c>
-      <c r="E139" s="112" t="inlineStr">
+      <c r="E139" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F139" s="112">
+      <c r="F139" s="113">
         <f>IF(OR($E139="Recebido",$C139=""),"",MAX(0,TODAY()-$C139))</f>
         <v/>
       </c>
-      <c r="G139" s="78" t="inlineStr">
-        <is>
-          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
+      <c r="G139" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 01/09/2026 (pagador: Sindicato dos Mineiros de Jacobina).</t>
         </is>
       </c>
     </row>
     <row r="140" s="157">
       <c r="A140" s="78" t="inlineStr">
         <is>
-          <t>Adriadne (Hotel Jovem Jota)</t>
+          <t>Armazem Cecilio Mota</t>
         </is>
       </c>
       <c r="B140" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Refil Carbon 9"</t>
         </is>
       </c>
       <c r="C140" s="77" t="n">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="D140" s="79" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="E140" s="112" t="inlineStr">
         <is>
@@ -71828,78 +71828,78 @@
       </c>
       <c r="G140" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="141" s="157">
-      <c r="A141" s="78" t="inlineStr">
-        <is>
-          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
-        </is>
-      </c>
-      <c r="B141" s="78" t="inlineStr">
-        <is>
-          <t>Refil Everest + Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C141" s="77" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D141" s="79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E141" s="112" t="inlineStr">
+      <c r="A141" s="82" t="inlineStr">
+        <is>
+          <t>Clebson Dantas Da Silva</t>
+        </is>
+      </c>
+      <c r="B141" s="82" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C141" s="81" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D141" s="83" t="n">
+        <v>140</v>
+      </c>
+      <c r="E141" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F141" s="112">
+      <c r="F141" s="113">
         <f>IF(OR($E141="Recebido",$C141=""),"",MAX(0,TODAY()-$C141))</f>
         <v/>
       </c>
-      <c r="G141" s="78" t="inlineStr">
-        <is>
-          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
+      <c r="G141" s="82" t="inlineStr">
+        <is>
+          <t>Recebido via Pix em 02/09/2026</t>
         </is>
       </c>
     </row>
     <row r="142" s="157">
-      <c r="A142" s="78" t="inlineStr">
-        <is>
-          <t>Topvel Tropical Veiculos e Pecas</t>
-        </is>
-      </c>
-      <c r="B142" s="78" t="inlineStr">
-        <is>
-          <t>2x Refil Everest + 2x Pré Filtro</t>
-        </is>
-      </c>
-      <c r="C142" s="77" t="n">
-        <v>46276</v>
-      </c>
-      <c r="D142" s="79" t="n">
-        <v>370</v>
-      </c>
-      <c r="E142" s="112" t="inlineStr">
+      <c r="A142" s="82" t="inlineStr">
+        <is>
+          <t>Tesla Imagem Medicina Diagnostica Ltda</t>
+        </is>
+      </c>
+      <c r="B142" s="82" t="inlineStr">
+        <is>
+          <t>3x Refil Everest + 2x Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C142" s="81" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D142" s="83" t="n">
+        <v>540</v>
+      </c>
+      <c r="E142" s="113" t="inlineStr">
         <is>
           <t>Recebido</t>
         </is>
       </c>
-      <c r="F142" s="112">
+      <c r="F142" s="113">
         <f>IF(OR($E142="Recebido",$C142=""),"",MAX(0,TODAY()-$C142))</f>
         <v/>
       </c>
-      <c r="G142" s="78" t="inlineStr">
-        <is>
-          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
+      <c r="G142" s="82" t="inlineStr">
+        <is>
+          <t>Troca do dia 02/09/2026 — 1º Andar, Térreo e Copa. Recebido via Pix em 08/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="143" s="157">
       <c r="A143" s="78" t="inlineStr">
         <is>
-          <t>J Diesel Motores e Reparos - Gilmara</t>
+          <t>Cecilio Mota Junior</t>
         </is>
       </c>
       <c r="B143" s="78" t="inlineStr">
@@ -71908,7 +71908,7 @@
         </is>
       </c>
       <c r="C143" s="77" t="n">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="D143" s="79" t="n">
         <v>140</v>
@@ -71924,14 +71924,14 @@
       </c>
       <c r="G143" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 11/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="144" s="157">
       <c r="A144" s="78" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>Tereza Cristina Aquino Martins - Luiz Augusto</t>
         </is>
       </c>
       <c r="B144" s="78" t="inlineStr">
@@ -71940,7 +71940,7 @@
         </is>
       </c>
       <c r="C144" s="77" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="D144" s="79" t="n">
         <v>200</v>
@@ -71956,26 +71956,26 @@
       </c>
       <c r="G144" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 14/09/2026.</t>
+          <t>Recebido via Pix em 04/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="145" s="157">
       <c r="A145" s="78" t="inlineStr">
         <is>
-          <t>Clínica Santa Cecília</t>
+          <t>Samille Fiscina Lima Lordello - Tiago (Cartório)</t>
         </is>
       </c>
       <c r="B145" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Termostato</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C145" s="77" t="n">
-        <v>46281</v>
+        <v>46269</v>
       </c>
       <c r="D145" s="79" t="n">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="E145" s="112" t="inlineStr">
         <is>
@@ -71988,26 +71988,26 @@
       </c>
       <c r="G145" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
+          <t>Recebido via Pix em 10/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="146" s="157">
       <c r="A146" s="78" t="inlineStr">
         <is>
-          <t>Marilda Macedo / José Luciano Costa</t>
+          <t>Bomboniere Doce Mania - Veronildo Basilio</t>
         </is>
       </c>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil Plissado + Refil BAG</t>
         </is>
       </c>
       <c r="C146" s="77" t="n">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="D146" s="79" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E146" s="112" t="inlineStr">
         <is>
@@ -72020,14 +72020,14 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido em dinheiro em 16/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="147" s="157">
       <c r="A147" s="78" t="inlineStr">
         <is>
-          <t>Tatiana Rocha</t>
+          <t>Adriadne (Hotel Jovem Jota)</t>
         </is>
       </c>
       <c r="B147" s="78" t="inlineStr">
@@ -72036,7 +72036,7 @@
         </is>
       </c>
       <c r="C147" s="77" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D147" s="79" t="n">
         <v>140</v>
@@ -72052,26 +72052,26 @@
       </c>
       <c r="G147" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="148" s="157">
       <c r="A148" s="78" t="inlineStr">
         <is>
-          <t>Cleone Gomes de Andrade</t>
+          <t>Pousada Triunfo Ltda (Hotel Triunfo)</t>
         </is>
       </c>
       <c r="B148" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C148" s="77" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="D148" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E148" s="112" t="inlineStr">
         <is>
@@ -72084,30 +72084,30 @@
       </c>
       <c r="G148" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
+          <t>Recebido via Pix em 11/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="149" s="157">
       <c r="A149" s="78" t="inlineStr">
         <is>
-          <t>Centro de Especialidades Odontomédicas</t>
+          <t>Topvel Tropical Veiculos e Pecas</t>
         </is>
       </c>
       <c r="B149" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Everest</t>
+          <t>2x Refil Everest + 2x Pré Filtro</t>
         </is>
       </c>
       <c r="C149" s="77" t="n">
-        <v>46044</v>
+        <v>46276</v>
       </c>
       <c r="D149" s="79" t="n">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="E149" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F149" s="112">
@@ -72116,30 +72116,30 @@
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
+          <t>Troca do dia 11/09/2026 — dois purificadores. Recebido via TED no BNB em 05/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="150" s="157">
       <c r="A150" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>J Diesel Motores e Reparos - Gilmara</t>
         </is>
       </c>
       <c r="B150" s="78" t="inlineStr">
         <is>
-          <t>Mangueira</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C150" s="77" t="n">
-        <v>46073</v>
+        <v>46276</v>
       </c>
       <c r="D150" s="79" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="E150" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F150" s="112">
@@ -72148,30 +72148,30 @@
       </c>
       <c r="G150" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Troca do dia 11/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="151" s="157">
       <c r="A151" s="78" t="inlineStr">
         <is>
-          <t>Centro Médico de Jacobina</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="B151" s="78" t="inlineStr">
         <is>
-          <t>2x Botão Completo</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C151" s="77" t="n">
-        <v>46203</v>
+        <v>46279</v>
       </c>
       <c r="D151" s="79" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E151" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F151" s="112">
@@ -72180,26 +72180,26 @@
       </c>
       <c r="G151" s="78" t="inlineStr">
         <is>
-          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
+          <t>Troca do dia 14/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="152" s="157">
       <c r="A152" s="78" t="inlineStr">
         <is>
-          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
+          <t>Clínica Santa Cecília</t>
         </is>
       </c>
       <c r="B152" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Everest + Termostato</t>
         </is>
       </c>
       <c r="C152" s="77" t="n">
-        <v>46294</v>
+        <v>46281</v>
       </c>
       <c r="D152" s="79" t="n">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="E152" s="112" t="inlineStr">
         <is>
@@ -72212,26 +72212,26 @@
       </c>
       <c r="G152" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>Troca do dia 16/09/2026 — refil + troca de termostato. Recebido via Pix em 29/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="153" s="157">
       <c r="A153" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Marilda Macedo / José Luciano Costa</t>
         </is>
       </c>
       <c r="B153" s="78" t="inlineStr">
         <is>
-          <t>Refil C+3</t>
+          <t>Refil Everest + Pré Filtro</t>
         </is>
       </c>
       <c r="C153" s="77" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="D153" s="79" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E153" s="112" t="inlineStr">
         <is>
@@ -72244,14 +72244,14 @@
       </c>
       <c r="G153" s="78" t="inlineStr">
         <is>
-          <t>Pagamento previsto para 30/09/2026. Recebido em dinheiro em 14/10/2026 — lançado em "Set 2026".</t>
+          <t>Recebido via Pix em 19/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="154" s="157">
       <c r="A154" s="78" t="inlineStr">
         <is>
-          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
+          <t>Tatiana Rocha</t>
         </is>
       </c>
       <c r="B154" s="78" t="inlineStr">
@@ -72260,7 +72260,7 @@
         </is>
       </c>
       <c r="C154" s="77" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="D154" s="79" t="n">
         <v>140</v>
@@ -72276,14 +72276,14 @@
       </c>
       <c r="G154" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 30/09/2026. Recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026) — lançado em "Out 2026".</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 22/09/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="155" s="157">
       <c r="A155" s="78" t="inlineStr">
         <is>
-          <t>Aneilde Rios de Oliveira</t>
+          <t>Cleone Gomes de Andrade</t>
         </is>
       </c>
       <c r="B155" s="78" t="inlineStr">
@@ -72292,7 +72292,7 @@
         </is>
       </c>
       <c r="C155" s="77" t="n">
-        <v>46296</v>
+        <v>46286</v>
       </c>
       <c r="D155" s="79" t="n">
         <v>140</v>
@@ -72308,30 +72308,30 @@
       </c>
       <c r="G155" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
+          <t>Troca do dia 21/09/2026. Recebido via Pix em 21/09/2026.</t>
         </is>
       </c>
     </row>
     <row r="156" s="157">
       <c r="A156" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Centro de Especialidades Odontomédicas</t>
         </is>
       </c>
       <c r="B156" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>2x Refil Everest</t>
         </is>
       </c>
       <c r="C156" s="77" t="n">
-        <v>46296</v>
+        <v>46044</v>
       </c>
       <c r="D156" s="79" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="E156" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F156" s="112">
@@ -72340,30 +72340,30 @@
       </c>
       <c r="G156" s="78" t="inlineStr">
         <is>
-          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>NF-e 4039 de 22/01/2026 (CNPJ 54.747.945/0001-09). Venda anterior ao controle manual (aba Jan 2026 vem do Livro Caixa). Conferido no DigiSat em 28/09/2026: não recebido. Mesmo cliente tem outra pendência de 05/08/2026 (R$ 140,00).</t>
         </is>
       </c>
     </row>
     <row r="157" s="157">
       <c r="A157" s="78" t="inlineStr">
         <is>
-          <t>Centro Medico da Chapada Diamantina LTDA</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B157" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + 2x Botão Completo</t>
+          <t>Mangueira</t>
         </is>
       </c>
       <c r="C157" s="77" t="n">
-        <v>46297</v>
+        <v>46073</v>
       </c>
       <c r="D157" s="79" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="E157" s="112" t="inlineStr">
         <is>
-          <t>Recebido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="F157" s="112">
@@ -72372,26 +72372,26 @@
       </c>
       <c r="G157" s="78" t="inlineStr">
         <is>
-          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
+          <t>NF-e 4075 de 20/02/2026 (CNPJ 62.647.383/0063-44). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="158" s="157">
       <c r="A158" s="78" t="inlineStr">
         <is>
-          <t>Igreja Messiânica Mundial do Brasil</t>
+          <t>Centro Médico de Jacobina</t>
         </is>
       </c>
       <c r="B158" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>2x Botão Completo</t>
         </is>
       </c>
       <c r="C158" s="77" t="n">
-        <v>46300</v>
+        <v>46203</v>
       </c>
       <c r="D158" s="79" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E158" s="112" t="inlineStr">
         <is>
@@ -72404,14 +72404,14 @@
       </c>
       <c r="G158" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
+          <t>NF-e 4242 de 30/06/2026 (CNPJ 13.228.432/0001-04). Conferido no DigiSat em 28/09/2026: não recebido.</t>
         </is>
       </c>
     </row>
     <row r="159" s="157">
       <c r="A159" s="78" t="inlineStr">
         <is>
-          <t>Rafael Landin Ribeiro</t>
+          <t>Vivencie Turismo Agencia de Viagens - Aneildes Rios</t>
         </is>
       </c>
       <c r="B159" s="78" t="inlineStr">
@@ -72420,7 +72420,7 @@
         </is>
       </c>
       <c r="C159" s="77" t="n">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="D159" s="79" t="n">
         <v>140</v>
@@ -72436,30 +72436,30 @@
       </c>
       <c r="G159" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026. Recebido via Pix em 09/10/2026.</t>
+          <t>Troca do dia 29/09/2026. Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
     <row r="160" s="157">
       <c r="A160" s="78" t="inlineStr">
         <is>
-          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B160" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life + Refil Universal (restante)</t>
+          <t>Refil C+3</t>
         </is>
       </c>
       <c r="C160" s="77" t="n">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="D160" s="79" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E160" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F160" s="112">
@@ -72468,30 +72468,30 @@
       </c>
       <c r="G160" s="78" t="inlineStr">
         <is>
-          <t>Venda de R$ 170,00 — R$ 85,00 pagos no débito em 09/10/2026; restante via Pix previsto para 16/10/2026.</t>
+          <t>Pagamento previsto para 30/09/2026. Recebido em dinheiro em 14/10/2026 — lançado em "Set 2026".</t>
         </is>
       </c>
     </row>
     <row r="161" s="157">
       <c r="A161" s="78" t="inlineStr">
         <is>
-          <t>Tropical Motos LTDA</t>
+          <t>PC Jacobina Administradora de Cartões LTDA - Cartão de Todos</t>
         </is>
       </c>
       <c r="B161" s="78" t="inlineStr">
         <is>
-          <t>Refil Pro Life</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C161" s="77" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="D161" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E161" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F161" s="112">
@@ -72500,14 +72500,14 @@
       </c>
       <c r="G161" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 09/10/2026 — purificador do andar de cima.</t>
+          <t>Troca do dia 30/09/2026. Recebido via Pix em 01/10/2026 (comprovante enviado em 06/10/2026) — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="162" s="157">
       <c r="A162" s="78" t="inlineStr">
         <is>
-          <t>Casa do Construtor</t>
+          <t>Aneilde Rios de Oliveira</t>
         </is>
       </c>
       <c r="B162" s="78" t="inlineStr">
@@ -72516,7 +72516,7 @@
         </is>
       </c>
       <c r="C162" s="77" t="n">
-        <v>46310</v>
+        <v>46296</v>
       </c>
       <c r="D162" s="79" t="n">
         <v>140</v>
@@ -72532,30 +72532,30 @@
       </c>
       <c r="G162" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026. Recebido via Pix em 21/10/2026.</t>
+          <t>Troca do dia 01/10/2026 (casa, Caeira). Recebido via Pix em 05/10/2026 — R$ 135,00 (Pix único de R$ 270,00 com as duas trocas; R$ 10,00 de desconto dividido).</t>
         </is>
       </c>
     </row>
     <row r="163" s="157">
       <c r="A163" s="78" t="inlineStr">
         <is>
-          <t>Lapec</t>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
         </is>
       </c>
       <c r="B163" s="78" t="inlineStr">
         <is>
-          <t>Refil E3 + Refil Everest</t>
+          <t>Refil Pro Life + 2x Botão Completo</t>
         </is>
       </c>
       <c r="C163" s="77" t="n">
-        <v>46310</v>
+        <v>46296</v>
       </c>
       <c r="D163" s="79" t="n">
         <v>200</v>
       </c>
       <c r="E163" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F163" s="112">
@@ -72564,26 +72564,26 @@
       </c>
       <c r="G163" s="78" t="inlineStr">
         <is>
-          <t>Compra do dia 15/10/2026 — Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
+          <t>Subsolo — troca do dia 01/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="164" s="157">
       <c r="A164" s="78" t="inlineStr">
         <is>
-          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
+          <t>Centro Medico da Chapada Diamantina LTDA</t>
         </is>
       </c>
       <c r="B164" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest</t>
+          <t>Refil Pro Life + 2x Botão Completo</t>
         </is>
       </c>
       <c r="C164" s="77" t="n">
-        <v>46310</v>
+        <v>46297</v>
       </c>
       <c r="D164" s="79" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E164" s="112" t="inlineStr">
         <is>
@@ -72596,26 +72596,26 @@
       </c>
       <c r="G164" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 15/10/2026. Recebido via Pix em 16/10/2026 — lançado em "Out 2026".</t>
+          <t>1º Andar — troca do dia 02/10/2026 (refil + 2 botões). Recebido em 05/10/2026 no crédito em 3x (pagamento único de R$ 400,00 pelas duas trocas).</t>
         </is>
       </c>
     </row>
     <row r="165" s="157">
       <c r="A165" s="78" t="inlineStr">
         <is>
-          <t>Colegio Oasis de Jacobina - Unopar</t>
+          <t>Igreja Messiânica Mundial do Brasil</t>
         </is>
       </c>
       <c r="B165" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Plissado + 2x Carcaça 9"</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C165" s="77" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="D165" s="79" t="n">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="E165" s="112" t="inlineStr">
         <is>
@@ -72628,26 +72628,26 @@
       </c>
       <c r="G165" s="78" t="inlineStr">
         <is>
-          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
+          <t>Troca do dia 05/10/2026. Mesmo cliente tem pendência de 20/02/2026 (Mangueira, R$ 30,00).</t>
         </is>
       </c>
     </row>
     <row r="166" s="157">
       <c r="A166" s="78" t="inlineStr">
         <is>
-          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+          <t>Rafael Landin Ribeiro</t>
         </is>
       </c>
       <c r="B166" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro (restante)</t>
+          <t>Refil Everest</t>
         </is>
       </c>
       <c r="C166" s="77" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="D166" s="79" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E166" s="112" t="inlineStr">
         <is>
@@ -72660,26 +72660,26 @@
       </c>
       <c r="G166" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00. Recebido em dinheiro em 20/10/2026.</t>
+          <t>Troca do dia 09/10/2026. Recebido via Pix em 09/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="167" s="157">
       <c r="A167" s="78" t="inlineStr">
         <is>
-          <t>Contabilidade Abreu</t>
+          <t>Restaurante Bonzão Bode - Aloisio Queiroz</t>
         </is>
       </c>
       <c r="B167" s="78" t="inlineStr">
         <is>
-          <t>Termostato</t>
+          <t>Refil Pro Life + Refil Universal (restante)</t>
         </is>
       </c>
       <c r="C167" s="77" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="D167" s="79" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="E167" s="112" t="inlineStr">
         <is>
@@ -72692,26 +72692,26 @@
       </c>
       <c r="G167" s="78" t="inlineStr">
         <is>
-          <t>Troca de termostato do dia 16/10/2026.</t>
+          <t>Venda de R$ 170,00 — R$ 85,00 pagos no débito em 09/10/2026; restante via Pix previsto para 16/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="168" s="157">
       <c r="A168" s="78" t="inlineStr">
         <is>
-          <t>Studio Malena Lorrane</t>
+          <t>Tropical Motos LTDA</t>
         </is>
       </c>
       <c r="B168" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro (restante)</t>
+          <t>Refil Pro Life</t>
         </is>
       </c>
       <c r="C168" s="77" t="n">
-        <v>46316</v>
+        <v>46304</v>
       </c>
       <c r="D168" s="79" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E168" s="112" t="inlineStr">
         <is>
@@ -72724,14 +72724,14 @@
       </c>
       <c r="G168" s="78" t="inlineStr">
         <is>
-          <t>Troca do dia 21/10/2026. Venda de R$ 190,00; R$ 40,00 pagos com serviço de sobrancelha para a Edilânia. Deve R$ 90,00 do refil + R$ 60,00 do pré-filtro.</t>
+          <t>Troca do dia 09/10/2026 — purificador do andar de cima.</t>
         </is>
       </c>
     </row>
     <row r="169" s="157">
       <c r="A169" s="78" t="inlineStr">
         <is>
-          <t>Marsilia Marmores e Granitos Erelli</t>
+          <t>Casa do Construtor</t>
         </is>
       </c>
       <c r="B169" s="78" t="inlineStr">
@@ -72740,14 +72740,14 @@
         </is>
       </c>
       <c r="C169" s="77" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="D169" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E169" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F169" s="112">
@@ -72756,23 +72756,23 @@
       </c>
       <c r="G169" s="78" t="inlineStr">
         <is>
-          <t>Venda de 19/10/2026.</t>
+          <t>Troca do dia 15/10/2026. Recebido via Pix em 21/10/2026.</t>
         </is>
       </c>
     </row>
     <row r="170" s="157">
       <c r="A170" s="78" t="inlineStr">
         <is>
-          <t>Banco do Nordeste do Brasil</t>
+          <t>Lapec</t>
         </is>
       </c>
       <c r="B170" s="78" t="inlineStr">
         <is>
-          <t>Refil Everest + Pré Filtro</t>
+          <t>Refil E3 + Refil Everest</t>
         </is>
       </c>
       <c r="C170" s="77" t="n">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="D170" s="79" t="n">
         <v>200</v>
@@ -72788,14 +72788,14 @@
       </c>
       <c r="G170" s="78" t="inlineStr">
         <is>
-          <t>Venda de 20/10/2026.</t>
+          <t>Compra do dia 15/10/2026 — Refil E3 R$ 80,00 + Refil Everest R$ 120,00.</t>
         </is>
       </c>
     </row>
     <row r="171" s="157">
       <c r="A171" s="78" t="inlineStr">
         <is>
-          <t>Magna dos Santos Carneiro Goncalves - Mirna</t>
+          <t>Primeiro Tabelionato de Notas - Tatiana Miranda Siqueira</t>
         </is>
       </c>
       <c r="B171" s="78" t="inlineStr">
@@ -72804,14 +72804,14 @@
         </is>
       </c>
       <c r="C171" s="77" t="n">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="D171" s="79" t="n">
         <v>140</v>
       </c>
       <c r="E171" s="112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recebido</t>
         </is>
       </c>
       <c r="F171" s="112">
@@ -72820,26 +72820,26 @@
       </c>
       <c r="G171" s="78" t="inlineStr">
         <is>
-          <t>Venda de 20/10/2026.</t>
+          <t>Troca do dia 15/10/2026. Recebido via Pix em 16/10/2026 — lançado em "Out 2026".</t>
         </is>
       </c>
     </row>
     <row r="172" s="157">
       <c r="A172" s="78" t="inlineStr">
         <is>
-          <t>Loja da Claro</t>
+          <t>Colegio Oasis de Jacobina - Unopar</t>
         </is>
       </c>
       <c r="B172" s="78" t="inlineStr">
         <is>
-          <t>Refil Lacqua</t>
+          <t>2x Refil Plissado + 2x Carcaça 9"</t>
         </is>
       </c>
       <c r="C172" s="77" t="n">
-        <v>46315</v>
+        <v>46305</v>
       </c>
       <c r="D172" s="79" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="E172" s="112" t="inlineStr">
         <is>
@@ -72852,114 +72852,331 @@
       </c>
       <c r="G172" s="78" t="inlineStr">
         <is>
-          <t>Venda de 20/10/2026.</t>
+          <t>2x Refil Plissado R$ 80,00 cada + 2x Carcaça 9" R$ 120,00 cada. Cláudio assinou para pagar depois. Falta enviar a NF.</t>
         </is>
       </c>
     </row>
     <row r="173" s="157">
-      <c r="A173" s="78" t="n"/>
-      <c r="B173" s="78" t="n"/>
-      <c r="C173" s="77" t="n"/>
-      <c r="D173" s="79" t="n"/>
-      <c r="E173" s="112" t="n"/>
+      <c r="A173" s="78" t="inlineStr">
+        <is>
+          <t>DFLL Serviços Medicos Ltda - ImCardio - Instituto Materno Cardiologico</t>
+        </is>
+      </c>
+      <c r="B173" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro (restante)</t>
+        </is>
+      </c>
+      <c r="C173" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D173" s="79" t="n">
+        <v>60</v>
+      </c>
+      <c r="E173" s="112" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
       <c r="F173" s="112">
         <f>IF(OR($E173="Recebido",$C173=""),"",MAX(0,TODAY()-$C173))</f>
         <v/>
       </c>
-      <c r="G173" s="78" t="n"/>
+      <c r="G173" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 16/10/2026 — bebedouro da recepção. Venda de R$ 200,00: R$ 140,00 pagos em dinheiro em 16/10/2026; falta R$ 60,00. Recebido em dinheiro em 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="174" s="157">
-      <c r="A174" s="78" t="n"/>
-      <c r="B174" s="78" t="n"/>
-      <c r="C174" s="77" t="n"/>
-      <c r="D174" s="79" t="n"/>
-      <c r="E174" s="112" t="n"/>
+      <c r="A174" s="78" t="inlineStr">
+        <is>
+          <t>Contabilidade Abreu</t>
+        </is>
+      </c>
+      <c r="B174" s="78" t="inlineStr">
+        <is>
+          <t>Termostato</t>
+        </is>
+      </c>
+      <c r="C174" s="77" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D174" s="79" t="n">
+        <v>170</v>
+      </c>
+      <c r="E174" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F174" s="112">
         <f>IF(OR($E174="Recebido",$C174=""),"",MAX(0,TODAY()-$C174))</f>
         <v/>
       </c>
-      <c r="G174" s="78" t="n"/>
+      <c r="G174" s="78" t="inlineStr">
+        <is>
+          <t>Troca de termostato do dia 16/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="175" s="157">
-      <c r="A175" s="78" t="n"/>
-      <c r="B175" s="78" t="n"/>
-      <c r="C175" s="77" t="n"/>
-      <c r="D175" s="79" t="n"/>
-      <c r="E175" s="112" t="n"/>
+      <c r="A175" s="78" t="inlineStr">
+        <is>
+          <t>Studio Malena Lorrane</t>
+        </is>
+      </c>
+      <c r="B175" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro (restante)</t>
+        </is>
+      </c>
+      <c r="C175" s="77" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D175" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="E175" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F175" s="112">
         <f>IF(OR($E175="Recebido",$C175=""),"",MAX(0,TODAY()-$C175))</f>
         <v/>
       </c>
-      <c r="G175" s="78" t="n"/>
+      <c r="G175" s="78" t="inlineStr">
+        <is>
+          <t>Troca do dia 21/10/2026. Venda de R$ 190,00; R$ 40,00 pagos com serviço de sobrancelha para a Edilânia. Deve R$ 90,00 do refil + R$ 60,00 do pré-filtro.</t>
+        </is>
+      </c>
     </row>
     <row r="176" s="157">
-      <c r="A176" s="78" t="n"/>
-      <c r="B176" s="78" t="n"/>
-      <c r="C176" s="77" t="n"/>
-      <c r="D176" s="79" t="n"/>
-      <c r="E176" s="112" t="n"/>
+      <c r="A176" s="78" t="inlineStr">
+        <is>
+          <t>Marsilia Marmores e Granitos Erelli</t>
+        </is>
+      </c>
+      <c r="B176" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C176" s="77" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D176" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E176" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F176" s="112">
         <f>IF(OR($E176="Recebido",$C176=""),"",MAX(0,TODAY()-$C176))</f>
         <v/>
       </c>
-      <c r="G176" s="78" t="n"/>
+      <c r="G176" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 19/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="177" s="157">
-      <c r="A177" s="78" t="n"/>
-      <c r="B177" s="78" t="n"/>
-      <c r="C177" s="77" t="n"/>
-      <c r="D177" s="79" t="n"/>
-      <c r="E177" s="112" t="n"/>
+      <c r="A177" s="78" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste do Brasil</t>
+        </is>
+      </c>
+      <c r="B177" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest + Pré Filtro</t>
+        </is>
+      </c>
+      <c r="C177" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D177" s="79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E177" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
       <c r="F177" s="112">
         <f>IF(OR($E177="Recebido",$C177=""),"",MAX(0,TODAY()-$C177))</f>
         <v/>
       </c>
-      <c r="G177" s="78" t="n"/>
+      <c r="G177" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="178" s="157">
-      <c r="A178" s="86" t="inlineStr">
+      <c r="A178" s="78" t="inlineStr">
+        <is>
+          <t>Magna dos Santos Carneiro Goncalves - Mirna</t>
+        </is>
+      </c>
+      <c r="B178" s="78" t="inlineStr">
+        <is>
+          <t>Refil Everest</t>
+        </is>
+      </c>
+      <c r="C178" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D178" s="79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E178" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F178" s="112">
+        <f>IF(OR($E178="Recebido",$C178=""),"",MAX(0,TODAY()-$C178))</f>
+        <v/>
+      </c>
+      <c r="G178" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" s="157">
+      <c r="A179" s="78" t="inlineStr">
+        <is>
+          <t>Loja da Claro</t>
+        </is>
+      </c>
+      <c r="B179" s="78" t="inlineStr">
+        <is>
+          <t>Refil Lacqua</t>
+        </is>
+      </c>
+      <c r="C179" s="77" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D179" s="79" t="n">
+        <v>80</v>
+      </c>
+      <c r="E179" s="112" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="F179" s="112">
+        <f>IF(OR($E179="Recebido",$C179=""),"",MAX(0,TODAY()-$C179))</f>
+        <v/>
+      </c>
+      <c r="G179" s="78" t="inlineStr">
+        <is>
+          <t>Venda de 20/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" s="157">
+      <c r="A180" s="78" t="n"/>
+      <c r="B180" s="78" t="n"/>
+      <c r="C180" s="77" t="n"/>
+      <c r="D180" s="79" t="n"/>
+      <c r="E180" s="112" t="n"/>
+      <c r="F180" s="112">
+        <f>IF(OR($E180="Recebido",$C180=""),"",MAX(0,TODAY()-$C180))</f>
+        <v/>
+      </c>
+      <c r="G180" s="78" t="n"/>
+    </row>
+    <row r="181" s="157">
+      <c r="A181" s="78" t="n"/>
+      <c r="B181" s="78" t="n"/>
+      <c r="C181" s="77" t="n"/>
+      <c r="D181" s="79" t="n"/>
+      <c r="E181" s="112" t="n"/>
+      <c r="F181" s="112">
+        <f>IF(OR($E181="Recebido",$C181=""),"",MAX(0,TODAY()-$C181))</f>
+        <v/>
+      </c>
+      <c r="G181" s="78" t="n"/>
+    </row>
+    <row r="182" s="157">
+      <c r="A182" s="78" t="n"/>
+      <c r="B182" s="78" t="n"/>
+      <c r="C182" s="77" t="n"/>
+      <c r="D182" s="79" t="n"/>
+      <c r="E182" s="112" t="n"/>
+      <c r="F182" s="112">
+        <f>IF(OR($E182="Recebido",$C182=""),"",MAX(0,TODAY()-$C182))</f>
+        <v/>
+      </c>
+      <c r="G182" s="78" t="n"/>
+    </row>
+    <row r="183" s="157">
+      <c r="A183" s="78" t="n"/>
+      <c r="B183" s="78" t="n"/>
+      <c r="C183" s="77" t="n"/>
+      <c r="D183" s="79" t="n"/>
+      <c r="E183" s="112" t="n"/>
+      <c r="F183" s="112">
+        <f>IF(OR($E183="Recebido",$C183=""),"",MAX(0,TODAY()-$C183))</f>
+        <v/>
+      </c>
+      <c r="G183" s="78" t="n"/>
+    </row>
+    <row r="184" s="157">
+      <c r="A184" s="78" t="n"/>
+      <c r="B184" s="78" t="n"/>
+      <c r="C184" s="77" t="n"/>
+      <c r="D184" s="79" t="n"/>
+      <c r="E184" s="112" t="n"/>
+      <c r="F184" s="112">
+        <f>IF(OR($E184="Recebido",$C184=""),"",MAX(0,TODAY()-$C184))</f>
+        <v/>
+      </c>
+      <c r="G184" s="78" t="n"/>
+    </row>
+    <row r="185" s="157">
+      <c r="A185" s="86" t="inlineStr">
         <is>
           <t>TOTAL EM ABERTO A RECEBER (detalhe)</t>
         </is>
       </c>
-      <c r="D178" s="115">
-        <f>SUMIF(E107:E177,"Pendente",D107:D177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179" s="157">
-      <c r="A179" s="202" t="inlineStr">
+      <c r="D185" s="115">
+        <f>SUMIF(E114:E184,"Pendente",D114:D184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" s="157">
+      <c r="A186" s="202" t="inlineStr">
         <is>
           <t>CONFERÊNCIA COM AS ABAS DOS MESES</t>
         </is>
       </c>
-      <c r="B179" s="159" t="n"/>
-      <c r="C179" s="159" t="n"/>
-      <c r="D179" s="159" t="n"/>
-      <c r="E179" s="159" t="n"/>
-      <c r="F179" s="159" t="n"/>
-      <c r="G179" s="160" t="n"/>
-    </row>
-    <row r="180" s="157">
-      <c r="A180" s="203">
-        <f>IF(ROUND(D178-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D178-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" s="157">
-      <c r="A181" s="203" t="inlineStr">
+      <c r="B186" s="159" t="n"/>
+      <c r="C186" s="159" t="n"/>
+      <c r="D186" s="159" t="n"/>
+      <c r="E186" s="159" t="n"/>
+      <c r="F186" s="159" t="n"/>
+      <c r="G186" s="160" t="n"/>
+    </row>
+    <row r="187" s="157">
+      <c r="A187" s="203">
+        <f>IF(ROUND(D185-C5,2)=0,"OK — o detalhe acima bate com as vendas marcadas como Aguardando Pagamento nas abas dos meses.","ATENÇÃO: diferença de R$ "&amp;TEXT(ABS(D185-C5),"#,##0.00")&amp;" entre este detalhe e as abas dos meses — alguma venda mudou de status em um lado só.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" s="157">
+      <c r="A188" s="203" t="inlineStr">
         <is>
           <t>As contas a pagar do DigiSat (pendentes até 27/07/2026) foram todas quitadas — confirmado em 19/08/2026. A única dívida em aberto hoje é o Capital de Giro do Banco do Brasil. Lance aqui novos compromissos conforme surgirem.</t>
         </is>
       </c>
     </row>
-    <row r="182" s="157"/>
-    <row r="183" s="157"/>
-    <row r="184" s="157"/>
-    <row r="185" s="157"/>
-    <row r="186" s="157"/>
-    <row r="187" s="157"/>
-    <row r="188" s="157"/>
     <row r="189" s="157"/>
     <row r="190" s="157"/>
     <row r="191" s="157"/>
@@ -72994,24 +73211,24 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A111:G111"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A105:G105"/>
+    <mergeCell ref="A186:G186"/>
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A187:G187"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E5:F6"/>
-    <mergeCell ref="A104:G104"/>
-    <mergeCell ref="A179:G179"/>
-    <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A112:G112"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E11:E99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11:E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Pago,Previsto"</formula1>
     </dataValidation>
-    <dataValidation sqref="E107:E177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E114:E184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendente,Recebido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Relatorio_Financeiro_2026.xlsx
+++ b/Relatorio_Financeiro_2026.xlsx
@@ -58184,15 +58184,40 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="44" t="n"/>
-      <c r="B166" s="45" t="n"/>
-      <c r="C166" s="45" t="n"/>
-      <c r="D166" s="46" t="n"/>
-      <c r="E166" s="45" t="n"/>
+      <c r="A166" s="44" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B166" s="45" t="inlineStr">
+        <is>
+          <t>Condominio Ilha do Ouro</t>
+        </is>
+      </c>
+      <c r="C166" s="45" t="inlineStr">
+        <is>
+          <t>2x Refil Everest</t>
+        </is>
+      </c>
+      <c r="D166" s="46" t="n">
+        <v>280</v>
+      </c>
+      <c r="E166" s="45" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
       <c r="F166" s="47" t="n"/>
       <c r="G166" s="48" t="n"/>
       <c r="H166" s="49" t="n"/>
-      <c r="I166" s="45" t="n"/>
+      <c r="I166" s="45" t="inlineStr">
+        <is>
+          <t>Só compra dos refis — sem troca de refil</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>EMP-0085</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="17" t="n"/>
